--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="401">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1303,6 +1303,10 @@
   </si>
   <si>
     <t>这是我们的责任。</t>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1689,7 +1693,7 @@
     <col min="3" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" style="6" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="10.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="7.75" style="1"/>
@@ -6078,7 +6082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>1339</v>
       </c>
@@ -6104,12 +6108,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>2001</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>14</v>
@@ -6167,7 +6171,7 @@
         <v>2003</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>14</v>
@@ -6249,12 +6253,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>2006</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>14</v>
@@ -6365,12 +6369,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>2010</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>14</v>
@@ -6510,12 +6514,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>2015</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>14</v>
@@ -6742,12 +6746,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>2023</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>14</v>
@@ -6800,12 +6804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>2025</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>14</v>
@@ -6945,12 +6949,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>2030</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>14</v>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>1006</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>1007</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1008</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>1009</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>1011</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>1012</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>1013</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>1014</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>1015</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>1016</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>1017</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>1018</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>1019</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>1020</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>1021</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1022</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>1023</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>1024</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>1025</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>1026</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>1027</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>1028</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>1029</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>1030</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>1031</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>1032</v>
       </c>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>1033</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>1034</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>1035</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>1036</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>1037</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>1038</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>1039</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>1040</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>1041</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>1042</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>1043</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>1044</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>1045</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>1046</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>1047</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>1048</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>1049</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>1050</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>1051</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>1052</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>1053</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>1054</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>1055</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>1056</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>1057</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>1058</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>1059</v>
       </c>
@@ -3326,7 +3326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>1060</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>1061</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>1062</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>1063</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>1064</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>1065</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>1066</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>1067</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>1068</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>1069</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>1070</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>1071</v>
       </c>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>1072</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>1073</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>1074</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>1075</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>1076</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>1077</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>1078</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>1079</v>
       </c>
@@ -3846,7 +3846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>1080</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>1081</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>1082</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>1083</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>1084</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>1085</v>
       </c>
@@ -4002,7 +4002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>1086</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>1100</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>1101</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>1102</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>1103</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>1104</v>
       </c>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="94.5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>1105</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="94.5" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>1106</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>1107</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>1108</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>1109</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>1110</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>1111</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>1112</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>1113</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>1114</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>1115</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>1116</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>1117</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>1118</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>1119</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="94.5" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>1200</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>1201</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>1202</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>1203</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>1204</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>1205</v>
       </c>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>1206</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>1207</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>1208</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>1209</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>1210</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>1211</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>1212</v>
       </c>
@@ -4886,7 +4886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>1213</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>1214</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>1215</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>1216</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>1217</v>
       </c>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>1218</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>1219</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>1300</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>1301</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>1302</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>1303</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>1304</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>1305</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>1306</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>1307</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>1308</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>1309</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>1310</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>1311</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>1312</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>1313</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>1314</v>
       </c>
@@ -5458,7 +5458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>1315</v>
       </c>
@@ -5484,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>1316</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>1317</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>1318</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>1319</v>
       </c>
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>1320</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>1321</v>
       </c>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>1322</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>1323</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>1324</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>1325</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>1326</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>1328</v>
       </c>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>1329</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>1331</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>1332</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>1333</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>1334</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>1335</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>1336</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>1337</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>1338</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>2002</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>2004</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>2005</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="I175" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.15">
@@ -6282,7 +6282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>2007</v>
       </c>
@@ -6311,7 +6311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>2008</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>2009</v>
       </c>
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>2011</v>
       </c>
@@ -6427,7 +6427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>2012</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="94.5" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>2013</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>2014</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>2016</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>2017</v>
       </c>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>2018</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>2019</v>
       </c>
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>2020</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>2021</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>2022</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="108" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>2024</v>
       </c>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="108" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>2026</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>2027</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>2028</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>2029</v>
       </c>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>2031</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>2032</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="94.5" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:9" ht="54" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>2033</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>2034</v>
       </c>
@@ -7091,7 +7091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>1400</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>1401</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>1402</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>1403</v>
       </c>
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>1404</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>1405</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>1406</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>1407</v>
       </c>
@@ -7299,7 +7299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>1408</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>1409</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>1410</v>
       </c>
@@ -7377,7 +7377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>1411</v>
       </c>
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>1412</v>
       </c>
@@ -7429,7 +7429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>1413</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>1414</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>1415</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>1416</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>1417</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>1418</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>1419</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>1420</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>1421</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>1422</v>
       </c>
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>1423</v>
       </c>
@@ -7715,7 +7715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>1424</v>
       </c>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>1425</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>1426</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>1427</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>1428</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>1429</v>
       </c>
@@ -7871,7 +7871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
         <v>1430</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
         <v>1431</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
         <v>1432</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
         <v>1433</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
         <v>1434</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
         <v>1435</v>
       </c>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>1436</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="81" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>1437</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>1438</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>1439</v>
       </c>
@@ -8131,7 +8131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>1440</v>
       </c>
@@ -8157,7 +8157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>1441</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>1442</v>
       </c>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
         <v>1443</v>
       </c>
@@ -8235,7 +8235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
         <v>1444</v>
       </c>
@@ -8261,7 +8261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
         <v>1445</v>
       </c>
@@ -8287,7 +8287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
         <v>1446</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
         <v>1447</v>
       </c>
@@ -8339,7 +8339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
         <v>1448</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
         <v>1450</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
         <v>1452</v>
       </c>
@@ -8469,7 +8469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
         <v>1453</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
         <v>1454</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
         <v>1455</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
         <v>1457</v>
       </c>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
         <v>1458</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
         <v>1459</v>
       </c>
@@ -8651,7 +8651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
         <v>1460</v>
       </c>
@@ -8677,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
         <v>1461</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
         <v>1470</v>
       </c>
@@ -8729,7 +8729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
         <v>1471</v>
       </c>
@@ -8755,7 +8755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
         <v>1472</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
         <v>1473</v>
       </c>
@@ -8807,7 +8807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
         <v>1474</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
         <v>1475</v>
       </c>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
         <v>1476</v>
       </c>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
         <v>1477</v>
       </c>
@@ -8911,7 +8911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
         <v>1478</v>
       </c>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
         <v>1479</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
         <v>1480</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
         <v>1481</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
         <v>1482</v>
       </c>
@@ -9041,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
         <v>1500</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
         <v>1502</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
         <v>1503</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
         <v>1504</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
         <v>1505</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
         <v>1506</v>
       </c>
@@ -9223,7 +9223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
         <v>1507</v>
       </c>
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
         <v>1508</v>
       </c>
@@ -9275,7 +9275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
         <v>1509</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>1510</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>1511</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>1513</v>
       </c>
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>1514</v>
       </c>
@@ -9449,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>1515</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>1516</v>
       </c>
@@ -9507,7 +9507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>1517</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>1518</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>1519</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:9" ht="27" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>1600</v>
       </c>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="404">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1306,6 +1306,18 @@
   </si>
   <si>
     <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1685,7 +1697,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:I300"/>
+  <dimension ref="A2:I301"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -1774,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>21</v>
@@ -1803,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>22</v>
@@ -1832,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>23</v>
@@ -1858,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>329</v>
@@ -1884,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>25</v>
@@ -1910,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>26</v>
@@ -1936,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>27</v>
@@ -1962,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>330</v>
@@ -1988,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>331</v>
@@ -2014,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>332</v>
@@ -2040,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>333</v>
@@ -2066,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
@@ -2092,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>334</v>
@@ -2118,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>34</v>
@@ -2144,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>335</v>
@@ -2170,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>36</v>
@@ -2196,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>336</v>
@@ -2222,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>337</v>
@@ -2248,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>39</v>
@@ -2274,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>40</v>
@@ -2300,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>41</v>
@@ -2326,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>42</v>
@@ -2352,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>43</v>
@@ -2378,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>44</v>
@@ -2404,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>45</v>
@@ -2430,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>338</v>
@@ -2456,7 +2468,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>47</v>
@@ -2482,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>339</v>
@@ -2508,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>49</v>
@@ -2534,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>340</v>
@@ -2560,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>51</v>
@@ -2586,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>52</v>
@@ -2612,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>53</v>
@@ -2638,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>54</v>
@@ -2664,7 +2676,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>341</v>
@@ -2690,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>56</v>
@@ -2716,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>57</v>
@@ -2742,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>58</v>
@@ -2768,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>59</v>
@@ -2794,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>342</v>
@@ -2820,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>61</v>
@@ -2846,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>343</v>
@@ -2872,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>62</v>
@@ -2898,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>63</v>
@@ -2924,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>64</v>
@@ -2950,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>344</v>
@@ -2976,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>345</v>
@@ -3002,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>346</v>
@@ -3028,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>347</v>
@@ -3054,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>348</v>
@@ -3080,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>65</v>
@@ -3106,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>349</v>
@@ -3132,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>66</v>
@@ -3158,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>67</v>
@@ -3184,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>68</v>
@@ -3210,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>69</v>
@@ -3236,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>70</v>
@@ -3262,7 +3274,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>350</v>
@@ -3288,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>351</v>
@@ -3314,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>352</v>
@@ -3340,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>353</v>
@@ -3366,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>354</v>
@@ -3392,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>355</v>
@@ -3418,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>74</v>
@@ -3444,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>356</v>
@@ -3470,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>76</v>
@@ -3496,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>77</v>
@@ -3522,7 +3534,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>78</v>
@@ -3548,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>79</v>
@@ -3574,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>80</v>
@@ -3600,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>81</v>
@@ -3626,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>82</v>
@@ -3652,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>83</v>
@@ -3678,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>84</v>
@@ -3704,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>85</v>
@@ -3730,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>86</v>
@@ -3756,7 +3768,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>87</v>
@@ -3782,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>88</v>
@@ -3808,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>89</v>
@@ -3834,7 +3846,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>90</v>
@@ -3860,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>91</v>
@@ -3886,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>92</v>
@@ -3912,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>93</v>
@@ -3938,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>94</v>
@@ -3964,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>95</v>
@@ -3990,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>96</v>
@@ -4016,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>97</v>
@@ -4042,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>98</v>
@@ -4068,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>357</v>
@@ -4094,7 +4106,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>100</v>
@@ -4120,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>358</v>
@@ -4146,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>102</v>
@@ -4172,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>103</v>
@@ -4198,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>104</v>
@@ -4224,7 +4236,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>359</v>
@@ -4250,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>105</v>
@@ -4276,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>106</v>
@@ -4302,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>107</v>
@@ -4328,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>108</v>
@@ -4354,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>360</v>
@@ -4380,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>110</v>
@@ -4406,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>111</v>
@@ -4432,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>112</v>
@@ -4458,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>113</v>
@@ -4484,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>114</v>
@@ -4510,7 +4522,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>115</v>
@@ -4536,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>116</v>
@@ -4562,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>117</v>
@@ -4588,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>118</v>
@@ -4614,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>119</v>
@@ -4640,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>120</v>
@@ -4666,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>121</v>
@@ -4692,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>122</v>
@@ -4718,7 +4730,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>123</v>
@@ -4744,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>124</v>
@@ -4770,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>125</v>
@@ -4796,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>126</v>
@@ -4822,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>127</v>
@@ -4848,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>128</v>
@@ -4874,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>129</v>
@@ -4900,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>130</v>
@@ -4926,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>131</v>
@@ -4952,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>132</v>
@@ -4978,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>133</v>
@@ -5004,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>134</v>
@@ -5030,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>135</v>
@@ -5056,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>136</v>
@@ -5082,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>137</v>
@@ -5108,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>138</v>
@@ -5134,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>139</v>
@@ -5160,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>140</v>
@@ -5186,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>141</v>
@@ -5212,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>142</v>
@@ -5238,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>143</v>
@@ -5264,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>144</v>
@@ -5290,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>145</v>
@@ -5316,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>146</v>
@@ -5342,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>147</v>
@@ -5368,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>148</v>
@@ -5394,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>149</v>
@@ -5420,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>150</v>
@@ -5446,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>151</v>
@@ -5472,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>152</v>
@@ -5498,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>153</v>
@@ -5524,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>154</v>
@@ -5550,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>155</v>
@@ -5576,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>156</v>
@@ -5602,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>157</v>
@@ -5628,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>158</v>
@@ -5654,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>159</v>
@@ -5680,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>160</v>
@@ -5706,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G155" s="1" t="s">
         <v>161</v>
@@ -5732,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>162</v>
@@ -5758,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>163</v>
@@ -5784,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>164</v>
@@ -5810,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>165</v>
@@ -5836,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>166</v>
@@ -5862,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>164</v>
@@ -5888,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>167</v>
@@ -5914,7 +5926,7 @@
         <v>0</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>168</v>
@@ -5940,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>169</v>
@@ -5966,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G165" s="1" t="s">
         <v>166</v>
@@ -5992,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>161</v>
@@ -6018,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>170</v>
@@ -6044,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>171</v>
@@ -6070,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>172</v>
@@ -6096,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G170" s="1" t="s">
         <v>157</v>
@@ -6415,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>182</v>
@@ -6444,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>183</v>
@@ -6502,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>185</v>
@@ -6589,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>188</v>
@@ -6676,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>191</v>
@@ -6763,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>368</v>
@@ -6908,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G198" s="1" t="s">
         <v>370</v>
@@ -6937,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G199" s="1" t="s">
         <v>199</v>
@@ -6995,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G201" s="1" t="s">
         <v>201</v>
@@ -7053,7 +7065,7 @@
         <v>0</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G203" s="1" t="s">
         <v>203</v>
@@ -7079,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G204" s="1" t="s">
         <v>204</v>
@@ -7105,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G205" s="1" t="s">
         <v>205</v>
@@ -7131,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G206" s="1" t="s">
         <v>371</v>
@@ -7157,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G207" s="1" t="s">
         <v>207</v>
@@ -7183,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G208" s="1" t="s">
         <v>208</v>
@@ -7209,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>372</v>
@@ -7235,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G210" s="1" t="s">
         <v>373</v>
@@ -7261,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G211" s="1" t="s">
         <v>210</v>
@@ -7287,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>211</v>
@@ -7313,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>212</v>
@@ -7339,7 +7351,7 @@
         <v>0</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>213</v>
@@ -7365,7 +7377,7 @@
         <v>0</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>214</v>
@@ -7391,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>215</v>
@@ -7417,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>216</v>
@@ -7443,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G218" s="1" t="s">
         <v>217</v>
@@ -7469,7 +7481,7 @@
         <v>0</v>
       </c>
       <c r="F219" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>374</v>
@@ -7495,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G220" s="1" t="s">
         <v>219</v>
@@ -7521,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="F221" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>220</v>
@@ -7547,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="F222" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G222" s="1" t="s">
         <v>221</v>
@@ -7573,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="F223" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G223" s="1" t="s">
         <v>375</v>
@@ -7599,7 +7611,7 @@
         <v>0</v>
       </c>
       <c r="F224" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G224" s="1" t="s">
         <v>223</v>
@@ -7625,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>224</v>
@@ -7651,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="F226" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G226" s="1" t="s">
         <v>376</v>
@@ -7677,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="F227" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>225</v>
@@ -7703,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="F228" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>226</v>
@@ -7729,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="F229" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G229" s="1" t="s">
         <v>227</v>
@@ -7755,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="F230" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>228</v>
@@ -7781,7 +7793,7 @@
         <v>0</v>
       </c>
       <c r="F231" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G231" s="1" t="s">
         <v>229</v>
@@ -7807,7 +7819,7 @@
         <v>0</v>
       </c>
       <c r="F232" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G232" s="1" t="s">
         <v>230</v>
@@ -7833,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="F233" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G233" s="1" t="s">
         <v>231</v>
@@ -7859,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="F234" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G234" s="1" t="s">
         <v>232</v>
@@ -7885,7 +7897,7 @@
         <v>0</v>
       </c>
       <c r="F235" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G235" s="1" t="s">
         <v>233</v>
@@ -7911,7 +7923,7 @@
         <v>0</v>
       </c>
       <c r="F236" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G236" s="1" t="s">
         <v>234</v>
@@ -7937,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="F237" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>235</v>
@@ -7963,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="F238" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>236</v>
@@ -7989,7 +8001,7 @@
         <v>0</v>
       </c>
       <c r="F239" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G239" s="1" t="s">
         <v>237</v>
@@ -8015,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="F240" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>238</v>
@@ -8041,7 +8053,7 @@
         <v>0</v>
       </c>
       <c r="F241" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G241" s="1" t="s">
         <v>239</v>
@@ -8067,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="F242" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G242" s="1" t="s">
         <v>240</v>
@@ -8093,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="F243" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G243" s="1" t="s">
         <v>241</v>
@@ -8119,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="F244" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G244" s="1" t="s">
         <v>242</v>
@@ -8145,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="F245" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G245" s="1" t="s">
         <v>243</v>
@@ -8171,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="F246" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G246" s="1" t="s">
         <v>244</v>
@@ -8197,7 +8209,7 @@
         <v>0</v>
       </c>
       <c r="F247" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G247" s="1" t="s">
         <v>245</v>
@@ -8223,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="F248" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G248" s="1" t="s">
         <v>246</v>
@@ -8249,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="F249" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G249" s="1" t="s">
         <v>247</v>
@@ -8275,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="F250" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G250" s="1" t="s">
         <v>248</v>
@@ -8301,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="F251" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>249</v>
@@ -8327,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="F252" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G252" s="1" t="s">
         <v>250</v>
@@ -8353,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="F253" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G253" s="1" t="s">
         <v>251</v>
@@ -8379,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="F254" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G254" s="1" t="s">
         <v>377</v>
@@ -8405,7 +8417,7 @@
         <v>0</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G255" s="1" t="s">
         <v>253</v>
@@ -8431,7 +8443,7 @@
         <v>0</v>
       </c>
       <c r="F256" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G256" s="1" t="s">
         <v>378</v>
@@ -8457,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="F257" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G257" s="1" t="s">
         <v>379</v>
@@ -8483,7 +8495,7 @@
         <v>0</v>
       </c>
       <c r="F258" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G258" s="1" t="s">
         <v>380</v>
@@ -8509,7 +8521,7 @@
         <v>0</v>
       </c>
       <c r="F259" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G259" s="1" t="s">
         <v>381</v>
@@ -8535,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="F260" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G260" s="1" t="s">
         <v>382</v>
@@ -8561,7 +8573,7 @@
         <v>0</v>
       </c>
       <c r="F261" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G261" s="1" t="s">
         <v>383</v>
@@ -8587,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="F262" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G262" s="1" t="s">
         <v>384</v>
@@ -8613,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="F263" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G263" s="1" t="s">
         <v>258</v>
@@ -8639,7 +8651,7 @@
         <v>0</v>
       </c>
       <c r="F264" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>259</v>
@@ -8665,7 +8677,7 @@
         <v>0</v>
       </c>
       <c r="F265" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G265" s="1" t="s">
         <v>385</v>
@@ -8691,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="F266" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G266" s="1" t="s">
         <v>261</v>
@@ -8717,7 +8729,7 @@
         <v>0</v>
       </c>
       <c r="F267" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G267" s="1" t="s">
         <v>386</v>
@@ -8743,7 +8755,7 @@
         <v>0</v>
       </c>
       <c r="F268" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G268" s="1" t="s">
         <v>387</v>
@@ -8769,7 +8781,7 @@
         <v>0</v>
       </c>
       <c r="F269" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G269" s="1" t="s">
         <v>388</v>
@@ -8795,7 +8807,7 @@
         <v>0</v>
       </c>
       <c r="F270" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G270" s="1" t="s">
         <v>389</v>
@@ -8821,7 +8833,7 @@
         <v>0</v>
       </c>
       <c r="F271" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G271" s="1" t="s">
         <v>390</v>
@@ -8847,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="F272" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G272" s="1" t="s">
         <v>391</v>
@@ -8873,7 +8885,7 @@
         <v>0</v>
       </c>
       <c r="F273" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G273" s="1" t="s">
         <v>392</v>
@@ -8899,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="F274" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G274" s="1" t="s">
         <v>393</v>
@@ -8925,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="F275" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G275" s="1" t="s">
         <v>265</v>
@@ -8951,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="F276" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>266</v>
@@ -8977,7 +8989,7 @@
         <v>0</v>
       </c>
       <c r="F277" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G277" s="1" t="s">
         <v>267</v>
@@ -9003,7 +9015,7 @@
         <v>0</v>
       </c>
       <c r="F278" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>268</v>
@@ -9029,7 +9041,7 @@
         <v>0</v>
       </c>
       <c r="F279" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G279" s="1" t="s">
         <v>269</v>
@@ -9055,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="F280" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G280" s="1" t="s">
         <v>394</v>
@@ -9081,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="F281" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G281" s="1" t="s">
         <v>271</v>
@@ -9107,7 +9119,7 @@
         <v>0</v>
       </c>
       <c r="F282" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>272</v>
@@ -9133,7 +9145,7 @@
         <v>0</v>
       </c>
       <c r="F283" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>395</v>
@@ -9159,7 +9171,7 @@
         <v>0</v>
       </c>
       <c r="F284" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G284" s="1" t="s">
         <v>273</v>
@@ -9185,7 +9197,7 @@
         <v>0</v>
       </c>
       <c r="F285" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G285" s="1" t="s">
         <v>274</v>
@@ -9211,7 +9223,7 @@
         <v>0</v>
       </c>
       <c r="F286" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>275</v>
@@ -9237,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="F287" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G287" s="1" t="s">
         <v>276</v>
@@ -9263,7 +9275,7 @@
         <v>0</v>
       </c>
       <c r="F288" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>277</v>
@@ -9292,7 +9304,7 @@
         <v>0</v>
       </c>
       <c r="F289" s="6" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="G289" s="1" t="s">
         <v>278</v>
@@ -9321,7 +9333,7 @@
         <v>0</v>
       </c>
       <c r="F290" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G290" s="1" t="s">
         <v>398</v>
@@ -9350,7 +9362,7 @@
         <v>0</v>
       </c>
       <c r="F291" s="6" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="G291" s="1" t="s">
         <v>279</v>
@@ -9379,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="F292" s="6" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="G292" s="1" t="s">
         <v>280</v>
@@ -9408,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="F293" s="6" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="G293" s="1" t="s">
         <v>281</v>
@@ -9437,7 +9449,7 @@
         <v>0</v>
       </c>
       <c r="F294" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>282</v>
@@ -9466,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="F295" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>283</v>
@@ -9495,7 +9507,7 @@
         <v>0</v>
       </c>
       <c r="F296" s="6" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="G296" s="1" t="s">
         <v>284</v>
@@ -9524,7 +9536,7 @@
         <v>0</v>
       </c>
       <c r="F297" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G297" s="1" t="s">
         <v>285</v>
@@ -9553,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="F298" s="6" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>286</v>
@@ -9582,7 +9594,7 @@
         <v>0</v>
       </c>
       <c r="F299" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G299" s="1" t="s">
         <v>399</v>
@@ -9608,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="F300" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G300" s="1" t="s">
         <v>287</v>
@@ -9617,6 +9629,29 @@
         <v>0</v>
       </c>
       <c r="I300" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A301" s="1">
+        <v>8888</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E301" s="1">
+        <v>0</v>
+      </c>
+      <c r="F301" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G301" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="H301" s="1">
+        <v>0</v>
+      </c>
+      <c r="I301" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="413">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1318,6 +1318,38 @@
   </si>
   <si>
     <t>false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy</t>
+  </si>
+  <si>
+    <t>Head/Boy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Boy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Girl</t>
+  </si>
+  <si>
+    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/Bussiness</t>
+  </si>
+  <si>
+    <t>Head/OldMan</t>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DisplayClose</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1697,7 +1729,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:I301"/>
+  <dimension ref="A2:J301"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -1711,7 +1743,7 @@
     <col min="10" max="16384" width="7.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>323</v>
       </c>
@@ -1739,8 +1771,11 @@
       <c r="I2" s="1" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J2" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>326</v>
       </c>
@@ -1768,8 +1803,11 @@
       <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J3" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
         <v>1000</v>
       </c>
@@ -1797,8 +1835,11 @@
       <c r="I4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
@@ -1826,8 +1867,11 @@
       <c r="I5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
@@ -1855,8 +1899,11 @@
       <c r="I6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
@@ -1881,8 +1928,11 @@
       <c r="I7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
@@ -1907,8 +1957,11 @@
       <c r="I8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
@@ -1933,8 +1986,11 @@
       <c r="I9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>1006</v>
       </c>
@@ -1959,8 +2015,11 @@
       <c r="I10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>1007</v>
       </c>
@@ -1985,8 +2044,11 @@
       <c r="I11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>1008</v>
       </c>
@@ -2011,8 +2073,11 @@
       <c r="I12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>1009</v>
       </c>
@@ -2037,8 +2102,11 @@
       <c r="I13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>1010</v>
       </c>
@@ -2063,8 +2131,11 @@
       <c r="I14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>1011</v>
       </c>
@@ -2089,8 +2160,11 @@
       <c r="I15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>1012</v>
       </c>
@@ -2115,8 +2189,11 @@
       <c r="I16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>1013</v>
       </c>
@@ -2141,8 +2218,11 @@
       <c r="I17" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>1014</v>
       </c>
@@ -2167,8 +2247,11 @@
       <c r="I18" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>1015</v>
       </c>
@@ -2193,8 +2276,11 @@
       <c r="I19" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>1016</v>
       </c>
@@ -2219,8 +2305,11 @@
       <c r="I20" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>1017</v>
       </c>
@@ -2245,8 +2334,11 @@
       <c r="I21" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>1018</v>
       </c>
@@ -2271,8 +2363,11 @@
       <c r="I22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>1019</v>
       </c>
@@ -2297,8 +2392,11 @@
       <c r="I23" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>1020</v>
       </c>
@@ -2323,8 +2421,11 @@
       <c r="I24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>1021</v>
       </c>
@@ -2349,8 +2450,11 @@
       <c r="I25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1022</v>
       </c>
@@ -2375,8 +2479,11 @@
       <c r="I26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>1023</v>
       </c>
@@ -2401,8 +2508,11 @@
       <c r="I27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>1024</v>
       </c>
@@ -2427,8 +2537,11 @@
       <c r="I28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>1025</v>
       </c>
@@ -2453,8 +2566,11 @@
       <c r="I29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>1026</v>
       </c>
@@ -2479,8 +2595,11 @@
       <c r="I30" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>1027</v>
       </c>
@@ -2505,8 +2624,11 @@
       <c r="I31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>1028</v>
       </c>
@@ -2531,8 +2653,11 @@
       <c r="I32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>1029</v>
       </c>
@@ -2557,8 +2682,11 @@
       <c r="I33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>1030</v>
       </c>
@@ -2583,8 +2711,11 @@
       <c r="I34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>1031</v>
       </c>
@@ -2609,8 +2740,11 @@
       <c r="I35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>1032</v>
       </c>
@@ -2635,8 +2769,11 @@
       <c r="I36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>1033</v>
       </c>
@@ -2661,8 +2798,11 @@
       <c r="I37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J37" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>1034</v>
       </c>
@@ -2687,8 +2827,11 @@
       <c r="I38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>1035</v>
       </c>
@@ -2713,8 +2856,11 @@
       <c r="I39" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J39" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>1036</v>
       </c>
@@ -2739,8 +2885,11 @@
       <c r="I40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>1037</v>
       </c>
@@ -2765,8 +2914,11 @@
       <c r="I41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J41" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>1038</v>
       </c>
@@ -2791,8 +2943,11 @@
       <c r="I42" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>1039</v>
       </c>
@@ -2817,8 +2972,11 @@
       <c r="I43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>1040</v>
       </c>
@@ -2843,8 +3001,11 @@
       <c r="I44" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J44" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>1041</v>
       </c>
@@ -2869,8 +3030,11 @@
       <c r="I45" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J45" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>1042</v>
       </c>
@@ -2895,8 +3059,11 @@
       <c r="I46" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>1043</v>
       </c>
@@ -2921,8 +3088,11 @@
       <c r="I47" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>1044</v>
       </c>
@@ -2947,8 +3117,11 @@
       <c r="I48" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J48" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>1045</v>
       </c>
@@ -2973,8 +3146,11 @@
       <c r="I49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J49" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>1046</v>
       </c>
@@ -2999,8 +3175,11 @@
       <c r="I50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J50" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>1047</v>
       </c>
@@ -3025,8 +3204,11 @@
       <c r="I51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J51" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>1048</v>
       </c>
@@ -3051,8 +3233,11 @@
       <c r="I52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J52" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>1049</v>
       </c>
@@ -3077,8 +3262,11 @@
       <c r="I53" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J53" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>1050</v>
       </c>
@@ -3103,8 +3291,11 @@
       <c r="I54" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J54" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>1051</v>
       </c>
@@ -3129,8 +3320,11 @@
       <c r="I55" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J55" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>1052</v>
       </c>
@@ -3155,8 +3349,11 @@
       <c r="I56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J56" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>1053</v>
       </c>
@@ -3181,8 +3378,11 @@
       <c r="I57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J57" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>1054</v>
       </c>
@@ -3207,8 +3407,11 @@
       <c r="I58" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>1055</v>
       </c>
@@ -3233,8 +3436,11 @@
       <c r="I59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J59" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>1056</v>
       </c>
@@ -3259,8 +3465,11 @@
       <c r="I60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>1057</v>
       </c>
@@ -3285,8 +3494,11 @@
       <c r="I61" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J61" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>1058</v>
       </c>
@@ -3311,8 +3523,11 @@
       <c r="I62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>1059</v>
       </c>
@@ -3337,8 +3552,11 @@
       <c r="I63" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>1060</v>
       </c>
@@ -3363,8 +3581,11 @@
       <c r="I64" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J64" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>1061</v>
       </c>
@@ -3389,8 +3610,11 @@
       <c r="I65" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J65" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>1062</v>
       </c>
@@ -3415,8 +3639,11 @@
       <c r="I66" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J66" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>1063</v>
       </c>
@@ -3441,8 +3668,11 @@
       <c r="I67" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J67" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>1064</v>
       </c>
@@ -3467,8 +3697,11 @@
       <c r="I68" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J68" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>1065</v>
       </c>
@@ -3493,8 +3726,11 @@
       <c r="I69" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J69" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>1066</v>
       </c>
@@ -3519,8 +3755,11 @@
       <c r="I70" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J70" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>1067</v>
       </c>
@@ -3545,8 +3784,11 @@
       <c r="I71" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J71" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>1068</v>
       </c>
@@ -3571,8 +3813,11 @@
       <c r="I72" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J72" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>1069</v>
       </c>
@@ -3597,8 +3842,11 @@
       <c r="I73" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J73" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>1070</v>
       </c>
@@ -3623,8 +3871,11 @@
       <c r="I74" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J74" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>1071</v>
       </c>
@@ -3649,8 +3900,11 @@
       <c r="I75" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J75" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>1072</v>
       </c>
@@ -3675,8 +3929,11 @@
       <c r="I76" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J76" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>1073</v>
       </c>
@@ -3701,8 +3958,11 @@
       <c r="I77" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J77" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>1074</v>
       </c>
@@ -3727,8 +3987,11 @@
       <c r="I78" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J78" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>1075</v>
       </c>
@@ -3753,8 +4016,11 @@
       <c r="I79" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J79" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>1076</v>
       </c>
@@ -3779,8 +4045,11 @@
       <c r="I80" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J80" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>1077</v>
       </c>
@@ -3805,8 +4074,11 @@
       <c r="I81" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J81" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>1078</v>
       </c>
@@ -3831,8 +4103,11 @@
       <c r="I82" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J82" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>1079</v>
       </c>
@@ -3857,8 +4132,11 @@
       <c r="I83" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J83" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>1080</v>
       </c>
@@ -3883,8 +4161,11 @@
       <c r="I84" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J84" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>1081</v>
       </c>
@@ -3909,8 +4190,11 @@
       <c r="I85" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J85" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>1082</v>
       </c>
@@ -3935,8 +4219,11 @@
       <c r="I86" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J86" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>1083</v>
       </c>
@@ -3961,8 +4248,11 @@
       <c r="I87" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J87" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>1084</v>
       </c>
@@ -3987,8 +4277,11 @@
       <c r="I88" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J88" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>1085</v>
       </c>
@@ -4013,8 +4306,11 @@
       <c r="I89" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J89" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>1086</v>
       </c>
@@ -4039,8 +4335,11 @@
       <c r="I90" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J90" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>1100</v>
       </c>
@@ -4065,8 +4364,11 @@
       <c r="I91" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J91" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>1101</v>
       </c>
@@ -4091,8 +4393,11 @@
       <c r="I92" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J92" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>1102</v>
       </c>
@@ -4117,8 +4422,11 @@
       <c r="I93" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J93" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>1103</v>
       </c>
@@ -4143,8 +4451,11 @@
       <c r="I94" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J94" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>1104</v>
       </c>
@@ -4169,8 +4480,11 @@
       <c r="I95" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J95" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>1105</v>
       </c>
@@ -4187,7 +4501,7 @@
         <v>315</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>103</v>
+        <v>408</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -4195,8 +4509,11 @@
       <c r="I96" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J96" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>1106</v>
       </c>
@@ -4221,8 +4538,11 @@
       <c r="I97" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J97" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>1107</v>
       </c>
@@ -4247,8 +4567,11 @@
       <c r="I98" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J98" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>1108</v>
       </c>
@@ -4273,8 +4596,11 @@
       <c r="I99" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J99" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>1109</v>
       </c>
@@ -4299,8 +4625,11 @@
       <c r="I100" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J100" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>1110</v>
       </c>
@@ -4325,8 +4654,11 @@
       <c r="I101" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J101" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>1111</v>
       </c>
@@ -4351,8 +4683,11 @@
       <c r="I102" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J102" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>1112</v>
       </c>
@@ -4377,8 +4712,11 @@
       <c r="I103" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J103" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>1113</v>
       </c>
@@ -4403,8 +4741,11 @@
       <c r="I104" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J104" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>1114</v>
       </c>
@@ -4429,8 +4770,11 @@
       <c r="I105" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J105" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>1115</v>
       </c>
@@ -4455,8 +4799,11 @@
       <c r="I106" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J106" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>1116</v>
       </c>
@@ -4481,8 +4828,11 @@
       <c r="I107" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J107" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>1117</v>
       </c>
@@ -4507,8 +4857,11 @@
       <c r="I108" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J108" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>1118</v>
       </c>
@@ -4533,8 +4886,11 @@
       <c r="I109" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J109" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>1119</v>
       </c>
@@ -4559,8 +4915,11 @@
       <c r="I110" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="J110" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>1200</v>
       </c>
@@ -4585,8 +4944,11 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J111" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>1201</v>
       </c>
@@ -4611,8 +4973,11 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J112" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>1202</v>
       </c>
@@ -4637,8 +5002,11 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J113" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>1203</v>
       </c>
@@ -4663,8 +5031,11 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J114" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>1204</v>
       </c>
@@ -4689,8 +5060,11 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J115" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>1205</v>
       </c>
@@ -4715,8 +5089,11 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J116" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>1206</v>
       </c>
@@ -4741,8 +5118,11 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J117" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>1207</v>
       </c>
@@ -4767,8 +5147,11 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J118" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>1208</v>
       </c>
@@ -4793,8 +5176,11 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J119" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>1209</v>
       </c>
@@ -4819,8 +5205,11 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J120" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>1210</v>
       </c>
@@ -4845,8 +5234,11 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J121" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>1211</v>
       </c>
@@ -4871,8 +5263,11 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J122" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>1212</v>
       </c>
@@ -4897,8 +5292,11 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J123" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>1213</v>
       </c>
@@ -4923,8 +5321,11 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J124" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>1214</v>
       </c>
@@ -4949,8 +5350,11 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J125" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>1215</v>
       </c>
@@ -4975,8 +5379,11 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J126" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>1216</v>
       </c>
@@ -5001,8 +5408,11 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J127" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>1217</v>
       </c>
@@ -5027,8 +5437,11 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J128" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>1218</v>
       </c>
@@ -5053,8 +5466,11 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J129" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>1219</v>
       </c>
@@ -5079,8 +5495,11 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J130" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>1300</v>
       </c>
@@ -5105,8 +5524,11 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J131" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>1301</v>
       </c>
@@ -5131,8 +5553,11 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J132" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>1302</v>
       </c>
@@ -5157,8 +5582,11 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J133" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>1303</v>
       </c>
@@ -5183,8 +5611,11 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J134" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>1304</v>
       </c>
@@ -5209,8 +5640,11 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J135" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>1305</v>
       </c>
@@ -5235,8 +5669,11 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J136" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>1306</v>
       </c>
@@ -5261,8 +5698,11 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J137" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>1307</v>
       </c>
@@ -5287,8 +5727,11 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J138" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>1308</v>
       </c>
@@ -5313,8 +5756,11 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J139" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>1309</v>
       </c>
@@ -5339,8 +5785,11 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J140" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>1310</v>
       </c>
@@ -5365,8 +5814,11 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J141" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>1311</v>
       </c>
@@ -5391,8 +5843,11 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J142" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>1312</v>
       </c>
@@ -5417,8 +5872,11 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J143" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>1313</v>
       </c>
@@ -5443,8 +5901,11 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J144" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>1314</v>
       </c>
@@ -5469,8 +5930,11 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J145" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>1315</v>
       </c>
@@ -5495,8 +5959,11 @@
       <c r="I146" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J146" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>1316</v>
       </c>
@@ -5521,8 +5988,11 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J147" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>1317</v>
       </c>
@@ -5547,8 +6017,11 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J148" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>1318</v>
       </c>
@@ -5573,8 +6046,11 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J149" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>1319</v>
       </c>
@@ -5599,8 +6075,11 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J150" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>1320</v>
       </c>
@@ -5625,8 +6104,11 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J151" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>1321</v>
       </c>
@@ -5651,8 +6133,11 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J152" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>1322</v>
       </c>
@@ -5677,8 +6162,11 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J153" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>1323</v>
       </c>
@@ -5703,8 +6191,11 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J154" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>1324</v>
       </c>
@@ -5729,8 +6220,11 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J155" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>1325</v>
       </c>
@@ -5755,8 +6249,11 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J156" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>1326</v>
       </c>
@@ -5781,8 +6278,11 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J157" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>1327</v>
       </c>
@@ -5807,8 +6307,11 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J158" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>1328</v>
       </c>
@@ -5833,8 +6336,11 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J159" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>1329</v>
       </c>
@@ -5859,8 +6365,11 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J160" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>1330</v>
       </c>
@@ -5885,8 +6394,11 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J161" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>1331</v>
       </c>
@@ -5911,8 +6423,11 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J162" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>1332</v>
       </c>
@@ -5937,8 +6452,11 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J163" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>1333</v>
       </c>
@@ -5963,8 +6481,11 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J164" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>1334</v>
       </c>
@@ -5989,8 +6510,11 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J165" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>1335</v>
       </c>
@@ -6015,8 +6539,11 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J166" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>1336</v>
       </c>
@@ -6041,8 +6568,11 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J167" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>1337</v>
       </c>
@@ -6067,8 +6597,11 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J168" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>1338</v>
       </c>
@@ -6093,8 +6626,11 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J169" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>1339</v>
       </c>
@@ -6119,8 +6655,11 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J170" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>2001</v>
       </c>
@@ -6137,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>361</v>
@@ -6148,8 +6687,11 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J171" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>2002</v>
       </c>
@@ -6160,10 +6702,10 @@
         <v>2</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>318</v>
+        <v>409</v>
       </c>
       <c r="E172" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>328</v>
@@ -6177,8 +6719,11 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J172" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>2003</v>
       </c>
@@ -6206,8 +6751,11 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J173" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>2004</v>
       </c>
@@ -6218,10 +6766,10 @@
         <v>2</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>318</v>
+        <v>409</v>
       </c>
       <c r="E174" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>328</v>
@@ -6235,8 +6783,11 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J174" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>2005</v>
       </c>
@@ -6247,10 +6798,10 @@
         <v>2</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>318</v>
+        <v>409</v>
       </c>
       <c r="E175" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>328</v>
@@ -6264,8 +6815,11 @@
       <c r="I175" s="1">
         <v>14</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J175" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>2006</v>
       </c>
@@ -6293,8 +6847,11 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J176" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>2007</v>
       </c>
@@ -6305,10 +6862,10 @@
         <v>2</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>318</v>
+        <v>409</v>
       </c>
       <c r="E177" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>328</v>
@@ -6322,8 +6879,11 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J177" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>2008</v>
       </c>
@@ -6334,7 +6894,7 @@
         <v>17</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E178" s="1">
         <v>0</v>
@@ -6351,8 +6911,11 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J178" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>2009</v>
       </c>
@@ -6363,7 +6926,7 @@
         <v>17</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E179" s="1">
         <v>0</v>
@@ -6380,8 +6943,11 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J179" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>2010</v>
       </c>
@@ -6409,8 +6975,11 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J180" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>2011</v>
       </c>
@@ -6421,7 +6990,7 @@
         <v>17</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E181" s="1">
         <v>0</v>
@@ -6438,8 +7007,11 @@
       <c r="I181" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J181" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>2012</v>
       </c>
@@ -6450,7 +7022,7 @@
         <v>17</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E182" s="1">
         <v>0</v>
@@ -6467,8 +7039,11 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="J182" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>2013</v>
       </c>
@@ -6479,7 +7054,7 @@
         <v>17</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E183" s="1">
         <v>0</v>
@@ -6496,8 +7071,11 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J183" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>2014</v>
       </c>
@@ -6508,7 +7086,7 @@
         <v>17</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
@@ -6525,8 +7103,11 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J184" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>2015</v>
       </c>
@@ -6554,8 +7135,11 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J185" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>2016</v>
       </c>
@@ -6566,7 +7150,7 @@
         <v>17</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E186" s="1">
         <v>0</v>
@@ -6583,8 +7167,11 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J186" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>2017</v>
       </c>
@@ -6595,7 +7182,7 @@
         <v>17</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
@@ -6612,8 +7199,11 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J187" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>2018</v>
       </c>
@@ -6641,8 +7231,11 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J188" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>2019</v>
       </c>
@@ -6653,7 +7246,7 @@
         <v>17</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
@@ -6670,8 +7263,11 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J189" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>2020</v>
       </c>
@@ -6682,7 +7278,7 @@
         <v>17</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
@@ -6699,8 +7295,11 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J190" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>2021</v>
       </c>
@@ -6711,7 +7310,7 @@
         <v>17</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E191" s="1">
         <v>0</v>
@@ -6728,8 +7327,11 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J191" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>2022</v>
       </c>
@@ -6740,7 +7342,7 @@
         <v>17</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E192" s="1">
         <v>0</v>
@@ -6757,8 +7359,11 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J192" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>2023</v>
       </c>
@@ -6786,8 +7391,11 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="J193" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>2024</v>
       </c>
@@ -6798,7 +7406,7 @@
         <v>17</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E194" s="1">
         <v>0</v>
@@ -6815,8 +7423,11 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J194" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>2025</v>
       </c>
@@ -6844,8 +7455,11 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="J195" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>2026</v>
       </c>
@@ -6856,7 +7470,7 @@
         <v>17</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E196" s="1">
         <v>0</v>
@@ -6873,8 +7487,11 @@
       <c r="I196" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J196" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>2027</v>
       </c>
@@ -6885,7 +7502,7 @@
         <v>17</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E197" s="1">
         <v>0</v>
@@ -6902,8 +7519,11 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J197" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>2028</v>
       </c>
@@ -6914,7 +7534,7 @@
         <v>17</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E198" s="1">
         <v>0</v>
@@ -6931,8 +7551,11 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J198" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>2029</v>
       </c>
@@ -6943,7 +7566,7 @@
         <v>17</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E199" s="1">
         <v>0</v>
@@ -6960,8 +7583,11 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J199" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>2030</v>
       </c>
@@ -6989,8 +7615,11 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J200" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>2031</v>
       </c>
@@ -7001,7 +7630,7 @@
         <v>17</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E201" s="1">
         <v>0</v>
@@ -7018,8 +7647,11 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J201" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>2032</v>
       </c>
@@ -7030,7 +7662,7 @@
         <v>17</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E202" s="1">
         <v>0</v>
@@ -7047,8 +7679,11 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" ht="54" x14ac:dyDescent="0.15">
+      <c r="J202" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>2033</v>
       </c>
@@ -7059,7 +7694,7 @@
         <v>17</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>319</v>
+        <v>410</v>
       </c>
       <c r="E203" s="1">
         <v>0</v>
@@ -7076,8 +7711,11 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J203" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>2034</v>
       </c>
@@ -7102,8 +7740,11 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J204" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>1400</v>
       </c>
@@ -7128,8 +7769,11 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J205" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>1401</v>
       </c>
@@ -7154,8 +7798,11 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J206" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>1402</v>
       </c>
@@ -7180,8 +7827,11 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J207" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>1403</v>
       </c>
@@ -7206,8 +7856,11 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J208" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>1404</v>
       </c>
@@ -7232,8 +7885,11 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J209" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>1405</v>
       </c>
@@ -7258,8 +7914,11 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J210" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>1406</v>
       </c>
@@ -7284,8 +7943,11 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J211" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>1407</v>
       </c>
@@ -7310,8 +7972,11 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J212" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>1408</v>
       </c>
@@ -7336,8 +8001,11 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J213" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>1409</v>
       </c>
@@ -7362,8 +8030,11 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J214" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>1410</v>
       </c>
@@ -7388,8 +8059,11 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="216" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J215" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>1411</v>
       </c>
@@ -7414,8 +8088,11 @@
       <c r="I216" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J216" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>1412</v>
       </c>
@@ -7440,8 +8117,11 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J217" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>1413</v>
       </c>
@@ -7466,8 +8146,11 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J218" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>1414</v>
       </c>
@@ -7492,8 +8175,11 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J219" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>1415</v>
       </c>
@@ -7518,8 +8204,11 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J220" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>1416</v>
       </c>
@@ -7544,8 +8233,11 @@
       <c r="I221" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J221" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>1417</v>
       </c>
@@ -7570,8 +8262,11 @@
       <c r="I222" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J222" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>1418</v>
       </c>
@@ -7596,8 +8291,11 @@
       <c r="I223" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J223" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>1419</v>
       </c>
@@ -7622,8 +8320,11 @@
       <c r="I224" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J224" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>1420</v>
       </c>
@@ -7648,8 +8349,11 @@
       <c r="I225" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J225" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>1421</v>
       </c>
@@ -7674,8 +8378,11 @@
       <c r="I226" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J226" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>1422</v>
       </c>
@@ -7700,8 +8407,11 @@
       <c r="I227" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J227" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>1423</v>
       </c>
@@ -7726,8 +8436,11 @@
       <c r="I228" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J228" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>1424</v>
       </c>
@@ -7752,8 +8465,11 @@
       <c r="I229" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J229" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>1425</v>
       </c>
@@ -7778,8 +8494,11 @@
       <c r="I230" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J230" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>1426</v>
       </c>
@@ -7804,8 +8523,11 @@
       <c r="I231" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="232" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J231" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>1427</v>
       </c>
@@ -7830,8 +8552,11 @@
       <c r="I232" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J232" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>1428</v>
       </c>
@@ -7856,8 +8581,11 @@
       <c r="I233" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J233" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>1429</v>
       </c>
@@ -7882,8 +8610,11 @@
       <c r="I234" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J234" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
         <v>1430</v>
       </c>
@@ -7908,8 +8639,11 @@
       <c r="I235" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J235" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
         <v>1431</v>
       </c>
@@ -7934,8 +8668,11 @@
       <c r="I236" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="237" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J236" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
         <v>1432</v>
       </c>
@@ -7960,8 +8697,11 @@
       <c r="I237" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J237" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
         <v>1433</v>
       </c>
@@ -7986,8 +8726,11 @@
       <c r="I238" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J238" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
         <v>1434</v>
       </c>
@@ -8012,8 +8755,11 @@
       <c r="I239" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J239" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
         <v>1435</v>
       </c>
@@ -8038,8 +8784,11 @@
       <c r="I240" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J240" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
         <v>1436</v>
       </c>
@@ -8064,8 +8813,11 @@
       <c r="I241" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J241" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
         <v>1437</v>
       </c>
@@ -8090,8 +8842,11 @@
       <c r="I242" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J242" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
         <v>1438</v>
       </c>
@@ -8116,8 +8871,11 @@
       <c r="I243" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J243" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
         <v>1439</v>
       </c>
@@ -8142,8 +8900,11 @@
       <c r="I244" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J244" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
         <v>1440</v>
       </c>
@@ -8168,8 +8929,11 @@
       <c r="I245" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J245" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
         <v>1441</v>
       </c>
@@ -8194,8 +8958,11 @@
       <c r="I246" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J246" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
         <v>1442</v>
       </c>
@@ -8220,8 +8987,11 @@
       <c r="I247" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="248" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J247" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
         <v>1443</v>
       </c>
@@ -8246,8 +9016,11 @@
       <c r="I248" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J248" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
         <v>1444</v>
       </c>
@@ -8272,8 +9045,11 @@
       <c r="I249" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J249" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
         <v>1445</v>
       </c>
@@ -8298,8 +9074,11 @@
       <c r="I250" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="251" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J250" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
         <v>1446</v>
       </c>
@@ -8324,8 +9103,11 @@
       <c r="I251" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="252" spans="1:9" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="J251" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
         <v>1447</v>
       </c>
@@ -8350,8 +9132,11 @@
       <c r="I252" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J252" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
         <v>1448</v>
       </c>
@@ -8376,8 +9161,11 @@
       <c r="I253" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J253" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
         <v>1449</v>
       </c>
@@ -8402,8 +9190,11 @@
       <c r="I254" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J254" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
         <v>1450</v>
       </c>
@@ -8428,8 +9219,11 @@
       <c r="I255" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J255" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
         <v>1451</v>
       </c>
@@ -8454,8 +9248,11 @@
       <c r="I256" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J256" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
         <v>1452</v>
       </c>
@@ -8480,8 +9277,11 @@
       <c r="I257" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J257" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
         <v>1453</v>
       </c>
@@ -8506,8 +9306,11 @@
       <c r="I258" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J258" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
         <v>1454</v>
       </c>
@@ -8532,8 +9335,11 @@
       <c r="I259" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="260" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J259" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
         <v>1455</v>
       </c>
@@ -8558,8 +9364,11 @@
       <c r="I260" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J260" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
         <v>1456</v>
       </c>
@@ -8584,8 +9393,11 @@
       <c r="I261" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J261" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
         <v>1457</v>
       </c>
@@ -8610,8 +9422,11 @@
       <c r="I262" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J262" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
         <v>1458</v>
       </c>
@@ -8636,8 +9451,11 @@
       <c r="I263" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="264" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J263" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
         <v>1459</v>
       </c>
@@ -8662,8 +9480,11 @@
       <c r="I264" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J264" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
         <v>1460</v>
       </c>
@@ -8688,8 +9509,11 @@
       <c r="I265" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J265" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
         <v>1461</v>
       </c>
@@ -8714,8 +9538,11 @@
       <c r="I266" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J266" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
         <v>1470</v>
       </c>
@@ -8740,8 +9567,11 @@
       <c r="I267" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J267" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
         <v>1471</v>
       </c>
@@ -8766,8 +9596,11 @@
       <c r="I268" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J268" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
         <v>1472</v>
       </c>
@@ -8792,8 +9625,11 @@
       <c r="I269" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J269" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
         <v>1473</v>
       </c>
@@ -8818,8 +9654,11 @@
       <c r="I270" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="271" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J270" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
         <v>1474</v>
       </c>
@@ -8844,8 +9683,11 @@
       <c r="I271" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J271" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
         <v>1475</v>
       </c>
@@ -8870,8 +9712,11 @@
       <c r="I272" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J272" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
         <v>1476</v>
       </c>
@@ -8896,8 +9741,11 @@
       <c r="I273" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J273" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
         <v>1477</v>
       </c>
@@ -8922,8 +9770,11 @@
       <c r="I274" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J274" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
         <v>1478</v>
       </c>
@@ -8948,8 +9799,11 @@
       <c r="I275" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J275" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
         <v>1479</v>
       </c>
@@ -8974,8 +9828,11 @@
       <c r="I276" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J276" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
         <v>1480</v>
       </c>
@@ -9000,8 +9857,11 @@
       <c r="I277" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J277" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
         <v>1481</v>
       </c>
@@ -9026,8 +9886,11 @@
       <c r="I278" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="279" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J278" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
         <v>1482</v>
       </c>
@@ -9052,8 +9915,11 @@
       <c r="I279" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J279" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
         <v>1500</v>
       </c>
@@ -9078,8 +9944,11 @@
       <c r="I280" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J280" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
         <v>1501</v>
       </c>
@@ -9104,8 +9973,11 @@
       <c r="I281" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J281" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
         <v>1502</v>
       </c>
@@ -9130,8 +10002,11 @@
       <c r="I282" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="283" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J282" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
         <v>1503</v>
       </c>
@@ -9156,8 +10031,11 @@
       <c r="I283" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="284" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J283" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
         <v>1504</v>
       </c>
@@ -9182,8 +10060,11 @@
       <c r="I284" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="285" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J284" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
         <v>1505</v>
       </c>
@@ -9208,8 +10089,11 @@
       <c r="I285" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="286" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J285" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
         <v>1506</v>
       </c>
@@ -9234,8 +10118,11 @@
       <c r="I286" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="287" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J286" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
         <v>1507</v>
       </c>
@@ -9260,8 +10147,11 @@
       <c r="I287" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="288" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J287" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
         <v>1508</v>
       </c>
@@ -9286,8 +10176,11 @@
       <c r="I288" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="289" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J288" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
         <v>1509</v>
       </c>
@@ -9298,7 +10191,7 @@
         <v>396</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>320</v>
+        <v>407</v>
       </c>
       <c r="E289" s="1">
         <v>0</v>
@@ -9315,8 +10208,11 @@
       <c r="I289" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="290" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J289" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
         <v>1510</v>
       </c>
@@ -9327,7 +10223,7 @@
         <v>397</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>321</v>
+        <v>406</v>
       </c>
       <c r="E290" s="1">
         <v>0</v>
@@ -9344,8 +10240,11 @@
       <c r="I290" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="291" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J290" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
         <v>1511</v>
       </c>
@@ -9373,8 +10272,11 @@
       <c r="I291" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J291" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
         <v>1512</v>
       </c>
@@ -9385,7 +10287,7 @@
         <v>396</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>320</v>
+        <v>407</v>
       </c>
       <c r="E292" s="1">
         <v>0</v>
@@ -9402,8 +10304,11 @@
       <c r="I292" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J292" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
         <v>1513</v>
       </c>
@@ -9414,7 +10319,7 @@
         <v>397</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>321</v>
+        <v>405</v>
       </c>
       <c r="E293" s="1">
         <v>0</v>
@@ -9431,8 +10336,11 @@
       <c r="I293" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="294" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J293" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
         <v>1514</v>
       </c>
@@ -9460,8 +10368,11 @@
       <c r="I294" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="295" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J294" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
         <v>1515</v>
       </c>
@@ -9489,8 +10400,11 @@
       <c r="I295" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="296" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J295" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
         <v>1516</v>
       </c>
@@ -9501,7 +10415,7 @@
         <v>397</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>321</v>
+        <v>404</v>
       </c>
       <c r="E296" s="1">
         <v>0</v>
@@ -9518,8 +10432,11 @@
       <c r="I296" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J296" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
         <v>1517</v>
       </c>
@@ -9530,7 +10447,7 @@
         <v>396</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>320</v>
+        <v>407</v>
       </c>
       <c r="E297" s="1">
         <v>0</v>
@@ -9547,8 +10464,11 @@
       <c r="I297" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="298" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J297" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
         <v>1518</v>
       </c>
@@ -9576,8 +10496,11 @@
       <c r="I298" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J298" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
         <v>1519</v>
       </c>
@@ -9588,7 +10511,7 @@
         <v>397</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>321</v>
+        <v>404</v>
       </c>
       <c r="E299" s="1">
         <v>0</v>
@@ -9605,8 +10528,11 @@
       <c r="I299" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="300" spans="1:9" ht="27" x14ac:dyDescent="0.15">
+      <c r="J299" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
         <v>1600</v>
       </c>
@@ -9631,8 +10557,11 @@
       <c r="I300" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="J300" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
         <v>8888</v>
       </c>
@@ -9652,6 +10581,9 @@
         <v>0</v>
       </c>
       <c r="I301" s="1">
+        <v>0</v>
+      </c>
+      <c r="J301" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -6877,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="I177" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J177" s="1" t="b">
         <v>0</v>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -6897,10 +6897,10 @@
         <v>410</v>
       </c>
       <c r="E178" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>179</v>
@@ -6929,10 +6929,10 @@
         <v>410</v>
       </c>
       <c r="E179" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>180</v>
@@ -6993,10 +6993,10 @@
         <v>410</v>
       </c>
       <c r="E181" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>182</v>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2511" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="416">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1350,6 +1350,18 @@
   </si>
   <si>
     <t>DisplayClose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今天你已经很累了,走吧,我带你回家。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以后这就是你的家了，早点休息吧，明天我会来叫醒你的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我先走了，晚安</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1729,7 +1741,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J301"/>
+  <dimension ref="A2:J303"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -6979,7 +6991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>2011</v>
       </c>
@@ -6999,13 +7011,13 @@
         <v>328</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>182</v>
+        <v>413</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
       </c>
       <c r="I181" s="1">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J181" s="1" t="b">
         <v>0</v>
@@ -7013,7 +7025,7 @@
     </row>
     <row r="182" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>2012</v>
+        <v>2100</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>328</v>
@@ -7025,16 +7037,16 @@
         <v>410</v>
       </c>
       <c r="E182" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>183</v>
+        <v>414</v>
       </c>
       <c r="H182" s="1">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
@@ -7043,9 +7055,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>2013</v>
+        <v>2101</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>328</v>
@@ -7057,27 +7069,27 @@
         <v>410</v>
       </c>
       <c r="E183" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" s="6" t="s">
         <v>328</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>184</v>
+        <v>415</v>
       </c>
       <c r="H183" s="1">
-        <v>2014</v>
+        <v>0</v>
       </c>
       <c r="I183" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J183" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>328</v>
@@ -7095,7 +7107,7 @@
         <v>402</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -7107,18 +7119,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>316</v>
+        <v>410</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
@@ -7127,10 +7139,10 @@
         <v>328</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>365</v>
+        <v>184</v>
       </c>
       <c r="H185" s="1">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
@@ -7139,9 +7151,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>328</v>
@@ -7156,88 +7168,88 @@
         <v>0</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G186" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H186" s="1">
+        <v>0</v>
+      </c>
+      <c r="I186" s="1">
+        <v>0</v>
+      </c>
+      <c r="J186" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A187" s="1">
+        <v>2015</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E187" s="1">
+        <v>0</v>
+      </c>
+      <c r="F187" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="H187" s="1">
+        <v>2016</v>
+      </c>
+      <c r="I187" s="1">
+        <v>0</v>
+      </c>
+      <c r="J187" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A188" s="1">
+        <v>2016</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E188" s="1">
+        <v>0</v>
+      </c>
+      <c r="F188" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="G188" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="H186" s="1">
+      <c r="H188" s="1">
         <v>2017</v>
       </c>
-      <c r="I186" s="1">
-        <v>0</v>
-      </c>
-      <c r="J186" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A187" s="1">
+      <c r="I188" s="1">
+        <v>0</v>
+      </c>
+      <c r="J188" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A189" s="1">
         <v>2017</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="E187" s="1">
-        <v>0</v>
-      </c>
-      <c r="F187" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H187" s="1">
-        <v>0</v>
-      </c>
-      <c r="I187" s="1">
-        <v>0</v>
-      </c>
-      <c r="J187" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A188" s="1">
-        <v>2018</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E188" s="1">
-        <v>0</v>
-      </c>
-      <c r="F188" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="G188" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="H188" s="1">
-        <v>2019</v>
-      </c>
-      <c r="I188" s="1">
-        <v>0</v>
-      </c>
-      <c r="J188" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A189" s="1">
-        <v>2019</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>328</v>
@@ -7252,13 +7264,13 @@
         <v>0</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H189" s="1">
-        <v>2020</v>
+        <v>0</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
@@ -7267,30 +7279,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>410</v>
+        <v>316</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>191</v>
+        <v>366</v>
       </c>
       <c r="H190" s="1">
-        <v>0</v>
+        <v>2019</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
@@ -7299,9 +7311,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>328</v>
@@ -7319,10 +7331,10 @@
         <v>328</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H191" s="1">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
@@ -7331,9 +7343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>328</v>
@@ -7348,13 +7360,13 @@
         <v>0</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>367</v>
+        <v>191</v>
       </c>
       <c r="H192" s="1">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="I192" s="1">
         <v>0</v>
@@ -7363,30 +7375,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>316</v>
+        <v>410</v>
       </c>
       <c r="E193" s="1">
         <v>0</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>368</v>
+        <v>192</v>
       </c>
       <c r="H193" s="1">
-        <v>0</v>
+        <v>2022</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
@@ -7395,9 +7407,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>328</v>
@@ -7415,10 +7427,10 @@
         <v>328</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>195</v>
+        <v>367</v>
       </c>
       <c r="H194" s="1">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
@@ -7429,7 +7441,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>400</v>
@@ -7444,13 +7456,13 @@
         <v>0</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H195" s="1">
-        <v>2026</v>
+        <v>0</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
@@ -7461,7 +7473,7 @@
     </row>
     <row r="196" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>328</v>
@@ -7479,10 +7491,10 @@
         <v>328</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H196" s="1">
-        <v>0</v>
+        <v>2025</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
@@ -7493,16 +7505,16 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>410</v>
+        <v>316</v>
       </c>
       <c r="E197" s="1">
         <v>0</v>
@@ -7511,10 +7523,10 @@
         <v>328</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>197</v>
+        <v>369</v>
       </c>
       <c r="H197" s="1">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
@@ -7523,9 +7535,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>328</v>
@@ -7540,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>370</v>
+        <v>196</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -7557,7 +7569,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>328</v>
@@ -7572,13 +7584,13 @@
         <v>0</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H199" s="1">
-        <v>0</v>
+        <v>2028</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
@@ -7589,28 +7601,28 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>316</v>
+        <v>410</v>
       </c>
       <c r="E200" s="1">
         <v>0</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>328</v>
+        <v>402</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="H200" s="1">
-        <v>2031</v>
+        <v>0</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
@@ -7619,9 +7631,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>328</v>
@@ -7639,7 +7651,7 @@
         <v>402</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H201" s="1">
         <v>0</v>
@@ -7651,18 +7663,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>410</v>
+        <v>316</v>
       </c>
       <c r="E202" s="1">
         <v>0</v>
@@ -7671,10 +7683,10 @@
         <v>328</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H202" s="1">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
@@ -7683,9 +7695,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>328</v>
@@ -7703,7 +7715,7 @@
         <v>402</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H203" s="1">
         <v>0</v>
@@ -7715,27 +7727,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>328</v>
       </c>
+      <c r="C204" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D204" s="1" t="s">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="E204" s="1">
         <v>0</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>402</v>
+        <v>328</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H204" s="1">
-        <v>0</v>
+        <v>2033</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
@@ -7744,15 +7759,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>1400</v>
+        <v>2033</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>328</v>
       </c>
+      <c r="C205" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="D205" s="1" t="s">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="E205" s="1">
         <v>0</v>
@@ -7761,7 +7779,7 @@
         <v>402</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -7773,9 +7791,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>1401</v>
+        <v>2034</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>328</v>
@@ -7790,7 +7808,7 @@
         <v>402</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>371</v>
+        <v>204</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
@@ -7804,7 +7822,7 @@
     </row>
     <row r="207" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>328</v>
@@ -7819,7 +7837,7 @@
         <v>402</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -7831,9 +7849,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>328</v>
@@ -7848,7 +7866,7 @@
         <v>402</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>208</v>
+        <v>371</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -7862,7 +7880,7 @@
     </row>
     <row r="209" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>328</v>
@@ -7877,7 +7895,7 @@
         <v>402</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>372</v>
+        <v>207</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
@@ -7891,7 +7909,7 @@
     </row>
     <row r="210" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>328</v>
@@ -7906,7 +7924,7 @@
         <v>402</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>373</v>
+        <v>208</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
@@ -7920,7 +7938,7 @@
     </row>
     <row r="211" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>328</v>
@@ -7935,7 +7953,7 @@
         <v>402</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>210</v>
+        <v>372</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -7947,9 +7965,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>328</v>
@@ -7964,7 +7982,7 @@
         <v>402</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>211</v>
+        <v>373</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
@@ -7978,7 +7996,7 @@
     </row>
     <row r="213" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>328</v>
@@ -7993,7 +8011,7 @@
         <v>402</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -8005,9 +8023,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="B214" s="6" t="s">
         <v>328</v>
@@ -8022,7 +8040,7 @@
         <v>402</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -8036,7 +8054,7 @@
     </row>
     <row r="215" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>328</v>
@@ -8051,7 +8069,7 @@
         <v>402</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -8065,7 +8083,7 @@
     </row>
     <row r="216" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>328</v>
@@ -8080,7 +8098,7 @@
         <v>402</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -8094,7 +8112,7 @@
     </row>
     <row r="217" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B217" s="6" t="s">
         <v>328</v>
@@ -8109,7 +8127,7 @@
         <v>402</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H217" s="1">
         <v>0</v>
@@ -8123,7 +8141,7 @@
     </row>
     <row r="218" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>328</v>
@@ -8138,7 +8156,7 @@
         <v>402</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
@@ -8150,9 +8168,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>328</v>
@@ -8167,7 +8185,7 @@
         <v>402</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>374</v>
+        <v>216</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
@@ -8179,9 +8197,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>328</v>
@@ -8196,7 +8214,7 @@
         <v>402</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H220" s="1">
         <v>0</v>
@@ -8210,7 +8228,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>328</v>
@@ -8225,7 +8243,7 @@
         <v>402</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>220</v>
+        <v>374</v>
       </c>
       <c r="H221" s="1">
         <v>0</v>
@@ -8237,9 +8255,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>328</v>
@@ -8254,7 +8272,7 @@
         <v>402</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -8268,7 +8286,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>328</v>
@@ -8283,7 +8301,7 @@
         <v>402</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>375</v>
+        <v>220</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -8295,9 +8313,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>328</v>
@@ -8312,7 +8330,7 @@
         <v>402</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H224" s="1">
         <v>0</v>
@@ -8324,9 +8342,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>328</v>
@@ -8341,7 +8359,7 @@
         <v>402</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>224</v>
+        <v>375</v>
       </c>
       <c r="H225" s="1">
         <v>0</v>
@@ -8355,7 +8373,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>328</v>
@@ -8370,7 +8388,7 @@
         <v>402</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>376</v>
+        <v>223</v>
       </c>
       <c r="H226" s="1">
         <v>0</v>
@@ -8382,9 +8400,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>328</v>
@@ -8399,7 +8417,7 @@
         <v>402</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
@@ -8411,9 +8429,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>328</v>
@@ -8428,7 +8446,7 @@
         <v>402</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>226</v>
+        <v>376</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -8440,9 +8458,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>328</v>
@@ -8457,7 +8475,7 @@
         <v>402</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -8471,7 +8489,7 @@
     </row>
     <row r="230" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>328</v>
@@ -8486,7 +8504,7 @@
         <v>402</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H230" s="1">
         <v>0</v>
@@ -8500,7 +8518,7 @@
     </row>
     <row r="231" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>328</v>
@@ -8515,7 +8533,7 @@
         <v>402</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -8529,7 +8547,7 @@
     </row>
     <row r="232" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>328</v>
@@ -8544,7 +8562,7 @@
         <v>402</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -8556,9 +8574,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>328</v>
@@ -8573,7 +8591,7 @@
         <v>402</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H233" s="1">
         <v>0</v>
@@ -8587,7 +8605,7 @@
     </row>
     <row r="234" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>328</v>
@@ -8602,7 +8620,7 @@
         <v>402</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
@@ -8616,7 +8634,7 @@
     </row>
     <row r="235" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>328</v>
@@ -8631,7 +8649,7 @@
         <v>402</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -8645,7 +8663,7 @@
     </row>
     <row r="236" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>328</v>
@@ -8660,7 +8678,7 @@
         <v>402</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -8672,9 +8690,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>328</v>
@@ -8689,7 +8707,7 @@
         <v>402</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -8703,7 +8721,7 @@
     </row>
     <row r="238" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>328</v>
@@ -8718,7 +8736,7 @@
         <v>402</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -8732,7 +8750,7 @@
     </row>
     <row r="239" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>328</v>
@@ -8747,7 +8765,7 @@
         <v>402</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
@@ -8761,7 +8779,7 @@
     </row>
     <row r="240" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>328</v>
@@ -8776,7 +8794,7 @@
         <v>402</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H240" s="1">
         <v>0</v>
@@ -8788,9 +8806,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>328</v>
@@ -8805,7 +8823,7 @@
         <v>402</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H241" s="1">
         <v>0</v>
@@ -8817,9 +8835,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>328</v>
@@ -8834,7 +8852,7 @@
         <v>402</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H242" s="1">
         <v>0</v>
@@ -8846,9 +8864,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>328</v>
@@ -8863,7 +8881,7 @@
         <v>402</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H243" s="1">
         <v>0</v>
@@ -8875,9 +8893,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>328</v>
@@ -8892,7 +8910,7 @@
         <v>402</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H244" s="1">
         <v>0</v>
@@ -8906,7 +8924,7 @@
     </row>
     <row r="245" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>328</v>
@@ -8921,7 +8939,7 @@
         <v>402</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
@@ -8933,9 +8951,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>328</v>
@@ -8950,7 +8968,7 @@
         <v>402</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H246" s="1">
         <v>0</v>
@@ -8964,7 +8982,7 @@
     </row>
     <row r="247" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>328</v>
@@ -8979,7 +8997,7 @@
         <v>402</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -8993,7 +9011,7 @@
     </row>
     <row r="248" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>328</v>
@@ -9008,7 +9026,7 @@
         <v>402</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -9022,7 +9040,7 @@
     </row>
     <row r="249" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>328</v>
@@ -9037,7 +9055,7 @@
         <v>402</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
@@ -9051,7 +9069,7 @@
     </row>
     <row r="250" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>328</v>
@@ -9066,7 +9084,7 @@
         <v>402</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
@@ -9080,7 +9098,7 @@
     </row>
     <row r="251" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>328</v>
@@ -9095,7 +9113,7 @@
         <v>402</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H251" s="1">
         <v>0</v>
@@ -9107,9 +9125,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>328</v>
@@ -9124,7 +9142,7 @@
         <v>402</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
@@ -9138,7 +9156,7 @@
     </row>
     <row r="253" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>328</v>
@@ -9153,7 +9171,7 @@
         <v>402</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H253" s="1">
         <v>0</v>
@@ -9165,9 +9183,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>328</v>
@@ -9182,7 +9200,7 @@
         <v>402</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>377</v>
+        <v>250</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
@@ -9194,9 +9212,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>328</v>
@@ -9211,7 +9229,7 @@
         <v>402</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H255" s="1">
         <v>0</v>
@@ -9225,7 +9243,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>328</v>
@@ -9240,7 +9258,7 @@
         <v>402</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H256" s="1">
         <v>0</v>
@@ -9254,7 +9272,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>328</v>
@@ -9269,7 +9287,7 @@
         <v>402</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>379</v>
+        <v>253</v>
       </c>
       <c r="H257" s="1">
         <v>0</v>
@@ -9283,7 +9301,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>328</v>
@@ -9298,7 +9316,7 @@
         <v>402</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H258" s="1">
         <v>0</v>
@@ -9312,7 +9330,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>328</v>
@@ -9327,7 +9345,7 @@
         <v>402</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
@@ -9339,9 +9357,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>328</v>
@@ -9356,7 +9374,7 @@
         <v>402</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H260" s="1">
         <v>0</v>
@@ -9370,7 +9388,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>328</v>
@@ -9385,7 +9403,7 @@
         <v>402</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -9397,9 +9415,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>328</v>
@@ -9414,7 +9432,7 @@
         <v>402</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H262" s="1">
         <v>0</v>
@@ -9428,7 +9446,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>328</v>
@@ -9443,7 +9461,7 @@
         <v>402</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>258</v>
+        <v>383</v>
       </c>
       <c r="H263" s="1">
         <v>0</v>
@@ -9455,9 +9473,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>328</v>
@@ -9472,7 +9490,7 @@
         <v>402</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>259</v>
+        <v>384</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
@@ -9486,7 +9504,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>328</v>
@@ -9501,7 +9519,7 @@
         <v>402</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>385</v>
+        <v>258</v>
       </c>
       <c r="H265" s="1">
         <v>0</v>
@@ -9513,9 +9531,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>328</v>
@@ -9530,7 +9548,7 @@
         <v>402</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H266" s="1">
         <v>0</v>
@@ -9544,7 +9562,7 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>1470</v>
+        <v>1460</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>328</v>
@@ -9559,7 +9577,7 @@
         <v>402</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H267" s="1">
         <v>0</v>
@@ -9573,7 +9591,7 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>1471</v>
+        <v>1461</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>328</v>
@@ -9588,7 +9606,7 @@
         <v>402</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>387</v>
+        <v>261</v>
       </c>
       <c r="H268" s="1">
         <v>0</v>
@@ -9602,7 +9620,7 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>328</v>
@@ -9617,7 +9635,7 @@
         <v>402</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H269" s="1">
         <v>0</v>
@@ -9631,7 +9649,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>328</v>
@@ -9646,7 +9664,7 @@
         <v>402</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H270" s="1">
         <v>0</v>
@@ -9658,9 +9676,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>328</v>
@@ -9675,7 +9693,7 @@
         <v>402</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H271" s="1">
         <v>0</v>
@@ -9689,7 +9707,7 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>328</v>
@@ -9704,7 +9722,7 @@
         <v>402</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H272" s="1">
         <v>0</v>
@@ -9716,9 +9734,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>328</v>
@@ -9733,7 +9751,7 @@
         <v>402</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H273" s="1">
         <v>0</v>
@@ -9747,7 +9765,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>328</v>
@@ -9762,7 +9780,7 @@
         <v>402</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H274" s="1">
         <v>0</v>
@@ -9776,7 +9794,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>328</v>
@@ -9791,7 +9809,7 @@
         <v>402</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>265</v>
+        <v>392</v>
       </c>
       <c r="H275" s="1">
         <v>0</v>
@@ -9805,7 +9823,7 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>328</v>
@@ -9820,7 +9838,7 @@
         <v>402</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>266</v>
+        <v>393</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
@@ -9834,7 +9852,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>328</v>
@@ -9849,7 +9867,7 @@
         <v>402</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H277" s="1">
         <v>0</v>
@@ -9863,7 +9881,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>328</v>
@@ -9878,7 +9896,7 @@
         <v>402</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H278" s="1">
         <v>0</v>
@@ -9890,9 +9908,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>328</v>
@@ -9907,7 +9925,7 @@
         <v>402</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H279" s="1">
         <v>0</v>
@@ -9921,7 +9939,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1500</v>
+        <v>1481</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>328</v>
@@ -9936,7 +9954,7 @@
         <v>402</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>394</v>
+        <v>268</v>
       </c>
       <c r="H280" s="1">
         <v>0</v>
@@ -9948,9 +9966,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1501</v>
+        <v>1482</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>328</v>
@@ -9965,7 +9983,7 @@
         <v>402</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H281" s="1">
         <v>0</v>
@@ -9979,7 +9997,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>328</v>
@@ -9994,7 +10012,7 @@
         <v>402</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>272</v>
+        <v>394</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
@@ -10006,9 +10024,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B283" s="6" t="s">
         <v>328</v>
@@ -10023,7 +10041,7 @@
         <v>402</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>395</v>
+        <v>271</v>
       </c>
       <c r="H283" s="1">
         <v>0</v>
@@ -10035,9 +10053,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>328</v>
@@ -10052,7 +10070,7 @@
         <v>402</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H284" s="1">
         <v>0</v>
@@ -10066,7 +10084,7 @@
     </row>
     <row r="285" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>328</v>
@@ -10081,7 +10099,7 @@
         <v>402</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>274</v>
+        <v>395</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
@@ -10095,7 +10113,7 @@
     </row>
     <row r="286" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>328</v>
@@ -10110,7 +10128,7 @@
         <v>402</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H286" s="1">
         <v>0</v>
@@ -10124,7 +10142,7 @@
     </row>
     <row r="287" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>328</v>
@@ -10139,7 +10157,7 @@
         <v>402</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H287" s="1">
         <v>0</v>
@@ -10153,7 +10171,7 @@
     </row>
     <row r="288" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>328</v>
@@ -10168,7 +10186,7 @@
         <v>402</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H288" s="1">
         <v>0</v>
@@ -10182,28 +10200,25 @@
     </row>
     <row r="289" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="B289" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="C289" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="D289" s="1" t="s">
-        <v>407</v>
+        <v>317</v>
       </c>
       <c r="E289" s="1">
         <v>0</v>
       </c>
       <c r="F289" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H289" s="1">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="I289" s="1">
         <v>0</v>
@@ -10214,16 +10229,13 @@
     </row>
     <row r="290" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="C290" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="D290" s="1" t="s">
-        <v>406</v>
+        <v>317</v>
       </c>
       <c r="E290" s="1">
         <v>0</v>
@@ -10232,7 +10244,7 @@
         <v>402</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>398</v>
+        <v>277</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -10246,16 +10258,16 @@
     </row>
     <row r="291" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="E291" s="1">
         <v>0</v>
@@ -10264,10 +10276,10 @@
         <v>403</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H291" s="1">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="I291" s="1">
         <v>0</v>
@@ -10276,30 +10288,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E292" s="1">
         <v>0</v>
       </c>
       <c r="F292" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>280</v>
+        <v>398</v>
       </c>
       <c r="H292" s="1">
-        <v>1513</v>
+        <v>0</v>
       </c>
       <c r="I292" s="1">
         <v>0</v>
@@ -10310,16 +10322,16 @@
     </row>
     <row r="293" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>405</v>
+        <v>322</v>
       </c>
       <c r="E293" s="1">
         <v>0</v>
@@ -10328,10 +10340,10 @@
         <v>403</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H293" s="1">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="I293" s="1">
         <v>0</v>
@@ -10340,30 +10352,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>322</v>
+        <v>407</v>
       </c>
       <c r="E294" s="1">
         <v>0</v>
       </c>
       <c r="F294" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H294" s="1">
-        <v>0</v>
+        <v>1513</v>
       </c>
       <c r="I294" s="1">
         <v>0</v>
@@ -10374,28 +10386,28 @@
     </row>
     <row r="295" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>20</v>
+        <v>397</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>322</v>
+        <v>405</v>
       </c>
       <c r="E295" s="1">
         <v>0</v>
       </c>
       <c r="F295" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H295" s="1">
-        <v>0</v>
+        <v>1514</v>
       </c>
       <c r="I295" s="1">
         <v>0</v>
@@ -10406,28 +10418,28 @@
     </row>
     <row r="296" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B296" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>397</v>
+        <v>20</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>404</v>
+        <v>322</v>
       </c>
       <c r="E296" s="1">
         <v>0</v>
       </c>
       <c r="F296" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H296" s="1">
-        <v>1517</v>
+        <v>0</v>
       </c>
       <c r="I296" s="1">
         <v>0</v>
@@ -10438,16 +10450,16 @@
     </row>
     <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>407</v>
+        <v>322</v>
       </c>
       <c r="E297" s="1">
         <v>0</v>
@@ -10456,7 +10468,7 @@
         <v>402</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -10470,16 +10482,16 @@
     </row>
     <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="B298" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>20</v>
+        <v>397</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="E298" s="1">
         <v>0</v>
@@ -10488,10 +10500,10 @@
         <v>403</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H298" s="1">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="I298" s="1">
         <v>0</v>
@@ -10500,18 +10512,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>328</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E299" s="1">
         <v>0</v>
@@ -10520,7 +10532,7 @@
         <v>402</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>399</v>
+        <v>285</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
@@ -10534,25 +10546,28 @@
     </row>
     <row r="300" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1600</v>
+        <v>1518</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>328</v>
       </c>
+      <c r="C300" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="D300" s="1" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E300" s="1">
         <v>0</v>
       </c>
       <c r="F300" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H300" s="1">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="I300" s="1">
         <v>0</v>
@@ -10563,10 +10578,16 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>8888</v>
+        <v>1519</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>328</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="E301" s="1">
         <v>0</v>
@@ -10575,15 +10596,70 @@
         <v>402</v>
       </c>
       <c r="G301" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H301" s="1">
+        <v>0</v>
+      </c>
+      <c r="I301" s="1">
+        <v>0</v>
+      </c>
+      <c r="J301" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A302" s="1">
+        <v>1600</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E302" s="1">
+        <v>0</v>
+      </c>
+      <c r="F302" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G302" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H302" s="1">
+        <v>0</v>
+      </c>
+      <c r="I302" s="1">
+        <v>0</v>
+      </c>
+      <c r="J302" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A303" s="1">
+        <v>8888</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E303" s="1">
+        <v>0</v>
+      </c>
+      <c r="F303" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="G303" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H301" s="1">
-        <v>0</v>
-      </c>
-      <c r="I301" s="1">
-        <v>0</v>
-      </c>
-      <c r="J301" s="1" t="b">
+      <c r="H303" s="1">
+        <v>0</v>
+      </c>
+      <c r="I303" s="1">
+        <v>0</v>
+      </c>
+      <c r="J303" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2521" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="420">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1362,6 +1362,22 @@
   </si>
   <si>
     <t>我先走了，晚安</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我很累了,应该先休息一下才行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我没有锄头，没办法锄地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这块地已经平整过了，\n不需要再锄地了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1741,7 +1757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J303"/>
+  <dimension ref="A2:J306"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -6673,10 +6689,10 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>2001</v>
+        <v>1400</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>14</v>
@@ -6705,7 +6721,7 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>2002</v>
+        <v>1401</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>328</v>
@@ -6737,10 +6753,10 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>2003</v>
+        <v>1402</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>14</v>
@@ -6769,7 +6785,7 @@
     </row>
     <row r="174" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>2004</v>
+        <v>1403</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>328</v>
@@ -6801,7 +6817,7 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>2005</v>
+        <v>1404</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>328</v>
@@ -6833,10 +6849,10 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>2006</v>
+        <v>1405</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>14</v>
@@ -6865,7 +6881,7 @@
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>2007</v>
+        <v>1406</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>328</v>
@@ -6897,7 +6913,7 @@
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>2008</v>
+        <v>1407</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>328</v>
@@ -6929,7 +6945,7 @@
     </row>
     <row r="179" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>2009</v>
+        <v>1408</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>328</v>
@@ -6961,10 +6977,10 @@
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>2010</v>
+        <v>1409</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>14</v>
@@ -6993,7 +7009,7 @@
     </row>
     <row r="181" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>2011</v>
+        <v>1410</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>328</v>
@@ -7025,7 +7041,7 @@
     </row>
     <row r="182" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>2100</v>
+        <v>1411</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>328</v>
@@ -7057,7 +7073,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>2101</v>
+        <v>1412</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>328</v>
@@ -7089,7 +7105,7 @@
     </row>
     <row r="184" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>2012</v>
+        <v>1413</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>328</v>
@@ -7121,7 +7137,7 @@
     </row>
     <row r="185" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>2013</v>
+        <v>1414</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>328</v>
@@ -7153,7 +7169,7 @@
     </row>
     <row r="186" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>2014</v>
+        <v>1415</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>328</v>
@@ -7185,10 +7201,10 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>2015</v>
+        <v>1416</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>14</v>
@@ -7217,7 +7233,7 @@
     </row>
     <row r="188" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>2016</v>
+        <v>1417</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>328</v>
@@ -7249,7 +7265,7 @@
     </row>
     <row r="189" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>2017</v>
+        <v>1418</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>328</v>
@@ -7281,7 +7297,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>2018</v>
+        <v>1419</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>328</v>
@@ -7313,7 +7329,7 @@
     </row>
     <row r="191" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>2019</v>
+        <v>1420</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>328</v>
@@ -7345,7 +7361,7 @@
     </row>
     <row r="192" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>2020</v>
+        <v>1421</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>328</v>
@@ -7377,7 +7393,7 @@
     </row>
     <row r="193" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>2021</v>
+        <v>1422</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>328</v>
@@ -7409,7 +7425,7 @@
     </row>
     <row r="194" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>2022</v>
+        <v>1423</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>328</v>
@@ -7441,10 +7457,10 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>2023</v>
+        <v>1424</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>14</v>
@@ -7473,7 +7489,7 @@
     </row>
     <row r="196" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>2024</v>
+        <v>1425</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>328</v>
@@ -7505,10 +7521,10 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>2025</v>
+        <v>1426</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>14</v>
@@ -7537,7 +7553,7 @@
     </row>
     <row r="198" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>2026</v>
+        <v>1427</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>328</v>
@@ -7569,7 +7585,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>2027</v>
+        <v>1428</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>328</v>
@@ -7601,7 +7617,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>2028</v>
+        <v>1429</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>328</v>
@@ -7633,7 +7649,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>2029</v>
+        <v>1430</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>328</v>
@@ -7665,10 +7681,10 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>2030</v>
+        <v>1431</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>14</v>
@@ -7697,7 +7713,7 @@
     </row>
     <row r="203" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>2031</v>
+        <v>1432</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>328</v>
@@ -7729,7 +7745,7 @@
     </row>
     <row r="204" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>2032</v>
+        <v>1433</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>328</v>
@@ -7761,7 +7777,7 @@
     </row>
     <row r="205" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>2033</v>
+        <v>1434</v>
       </c>
       <c r="B205" s="6" t="s">
         <v>328</v>
@@ -7793,7 +7809,7 @@
     </row>
     <row r="206" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>2034</v>
+        <v>1435</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>328</v>
@@ -7822,7 +7838,7 @@
     </row>
     <row r="207" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>1400</v>
+        <v>1436</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>328</v>
@@ -7851,7 +7867,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>1401</v>
+        <v>1437</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>328</v>
@@ -7880,7 +7896,7 @@
     </row>
     <row r="209" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>1402</v>
+        <v>1438</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>328</v>
@@ -7909,7 +7925,7 @@
     </row>
     <row r="210" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>1403</v>
+        <v>1439</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>328</v>
@@ -7938,7 +7954,7 @@
     </row>
     <row r="211" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>1404</v>
+        <v>1440</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>328</v>
@@ -7967,7 +7983,7 @@
     </row>
     <row r="212" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>1405</v>
+        <v>1441</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>328</v>
@@ -7996,7 +8012,7 @@
     </row>
     <row r="213" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>1406</v>
+        <v>1442</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>328</v>
@@ -8025,7 +8041,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>1407</v>
+        <v>1443</v>
       </c>
       <c r="B214" s="6" t="s">
         <v>328</v>
@@ -8054,7 +8070,7 @@
     </row>
     <row r="215" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>1408</v>
+        <v>1444</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>328</v>
@@ -8083,7 +8099,7 @@
     </row>
     <row r="216" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>1409</v>
+        <v>1445</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>328</v>
@@ -8112,7 +8128,7 @@
     </row>
     <row r="217" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>1410</v>
+        <v>1446</v>
       </c>
       <c r="B217" s="6" t="s">
         <v>328</v>
@@ -8141,7 +8157,7 @@
     </row>
     <row r="218" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1411</v>
+        <v>1447</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>328</v>
@@ -8170,7 +8186,7 @@
     </row>
     <row r="219" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1412</v>
+        <v>1448</v>
       </c>
       <c r="B219" s="6" t="s">
         <v>328</v>
@@ -8199,7 +8215,7 @@
     </row>
     <row r="220" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1413</v>
+        <v>1449</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>328</v>
@@ -8228,7 +8244,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1414</v>
+        <v>1450</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>328</v>
@@ -8257,7 +8273,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1415</v>
+        <v>1451</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>328</v>
@@ -8286,7 +8302,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1416</v>
+        <v>1452</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>328</v>
@@ -8315,7 +8331,7 @@
     </row>
     <row r="224" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1417</v>
+        <v>1453</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>328</v>
@@ -8344,7 +8360,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1418</v>
+        <v>1454</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>328</v>
@@ -8373,7 +8389,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1419</v>
+        <v>1455</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>328</v>
@@ -8402,7 +8418,7 @@
     </row>
     <row r="227" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1420</v>
+        <v>1456</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>328</v>
@@ -8431,7 +8447,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1421</v>
+        <v>1457</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>328</v>
@@ -8460,7 +8476,7 @@
     </row>
     <row r="229" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1422</v>
+        <v>1458</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>328</v>
@@ -8489,7 +8505,7 @@
     </row>
     <row r="230" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1423</v>
+        <v>1459</v>
       </c>
       <c r="B230" s="6" t="s">
         <v>328</v>
@@ -8518,7 +8534,7 @@
     </row>
     <row r="231" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>1424</v>
+        <v>1460</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>328</v>
@@ -8547,7 +8563,7 @@
     </row>
     <row r="232" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>1425</v>
+        <v>1461</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>328</v>
@@ -8576,7 +8592,7 @@
     </row>
     <row r="233" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>1426</v>
+        <v>1470</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>328</v>
@@ -8605,7 +8621,7 @@
     </row>
     <row r="234" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>1427</v>
+        <v>1471</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>328</v>
@@ -8634,7 +8650,7 @@
     </row>
     <row r="235" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1428</v>
+        <v>1472</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>328</v>
@@ -8663,7 +8679,7 @@
     </row>
     <row r="236" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1429</v>
+        <v>1473</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>328</v>
@@ -8692,7 +8708,7 @@
     </row>
     <row r="237" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1430</v>
+        <v>1474</v>
       </c>
       <c r="B237" s="6" t="s">
         <v>328</v>
@@ -8721,7 +8737,7 @@
     </row>
     <row r="238" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1431</v>
+        <v>1475</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>328</v>
@@ -8750,7 +8766,7 @@
     </row>
     <row r="239" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1432</v>
+        <v>1476</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>328</v>
@@ -8779,7 +8795,7 @@
     </row>
     <row r="240" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1433</v>
+        <v>1477</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>328</v>
@@ -8808,7 +8824,7 @@
     </row>
     <row r="241" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>1434</v>
+        <v>1478</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>328</v>
@@ -8837,7 +8853,7 @@
     </row>
     <row r="242" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>1435</v>
+        <v>1479</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>328</v>
@@ -8866,7 +8882,7 @@
     </row>
     <row r="243" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>1436</v>
+        <v>1480</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>328</v>
@@ -8895,7 +8911,7 @@
     </row>
     <row r="244" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>1437</v>
+        <v>1481</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>328</v>
@@ -8924,7 +8940,7 @@
     </row>
     <row r="245" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>1438</v>
+        <v>1482</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>328</v>
@@ -8953,7 +8969,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>1439</v>
+        <v>1500</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>328</v>
@@ -8982,7 +8998,7 @@
     </row>
     <row r="247" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>1440</v>
+        <v>1501</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>328</v>
@@ -9011,7 +9027,7 @@
     </row>
     <row r="248" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>1441</v>
+        <v>1502</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>328</v>
@@ -9040,7 +9056,7 @@
     </row>
     <row r="249" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>1442</v>
+        <v>1503</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>328</v>
@@ -9069,7 +9085,7 @@
     </row>
     <row r="250" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>1443</v>
+        <v>1504</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>328</v>
@@ -9098,7 +9114,7 @@
     </row>
     <row r="251" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>1444</v>
+        <v>1505</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>328</v>
@@ -9127,7 +9143,7 @@
     </row>
     <row r="252" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>1445</v>
+        <v>1506</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>328</v>
@@ -9156,7 +9172,7 @@
     </row>
     <row r="253" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>1446</v>
+        <v>1507</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>328</v>
@@ -9185,7 +9201,7 @@
     </row>
     <row r="254" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>1447</v>
+        <v>1508</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>328</v>
@@ -9214,7 +9230,7 @@
     </row>
     <row r="255" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>1448</v>
+        <v>1509</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>328</v>
@@ -9243,7 +9259,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>1449</v>
+        <v>1510</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>328</v>
@@ -9272,7 +9288,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>1450</v>
+        <v>1511</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>328</v>
@@ -9301,7 +9317,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>1451</v>
+        <v>1512</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>328</v>
@@ -9330,7 +9346,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>1452</v>
+        <v>1513</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>328</v>
@@ -9359,7 +9375,7 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>1453</v>
+        <v>1514</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>328</v>
@@ -9388,7 +9404,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>1454</v>
+        <v>1515</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>328</v>
@@ -9417,7 +9433,7 @@
     </row>
     <row r="262" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>1455</v>
+        <v>1516</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>328</v>
@@ -9446,7 +9462,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>1456</v>
+        <v>1517</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>328</v>
@@ -9475,7 +9491,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>1457</v>
+        <v>1518</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>328</v>
@@ -9504,7 +9520,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>1458</v>
+        <v>1519</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>328</v>
@@ -9533,7 +9549,7 @@
     </row>
     <row r="266" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>1459</v>
+        <v>1600</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>328</v>
@@ -9562,10 +9578,10 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>1460</v>
+        <v>2001</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>317</v>
@@ -9591,7 +9607,7 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>1461</v>
+        <v>2002</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>328</v>
@@ -9620,10 +9636,10 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>1470</v>
+        <v>2003</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>317</v>
@@ -9649,7 +9665,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>1471</v>
+        <v>2004</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>328</v>
@@ -9678,7 +9694,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>1472</v>
+        <v>2005</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>328</v>
@@ -9707,10 +9723,10 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>1473</v>
+        <v>2006</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>317</v>
@@ -9736,7 +9752,7 @@
     </row>
     <row r="273" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>1474</v>
+        <v>2007</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>328</v>
@@ -9765,7 +9781,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>1475</v>
+        <v>2008</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>328</v>
@@ -9794,7 +9810,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>1476</v>
+        <v>2009</v>
       </c>
       <c r="B275" s="6" t="s">
         <v>328</v>
@@ -9823,10 +9839,10 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>1477</v>
+        <v>2010</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>317</v>
@@ -9852,7 +9868,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>1478</v>
+        <v>2011</v>
       </c>
       <c r="B277" s="6" t="s">
         <v>328</v>
@@ -9881,7 +9897,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>1479</v>
+        <v>2012</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>328</v>
@@ -9910,7 +9926,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>1480</v>
+        <v>2013</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>328</v>
@@ -9939,7 +9955,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>1481</v>
+        <v>2014</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>328</v>
@@ -9968,10 +9984,10 @@
     </row>
     <row r="281" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>1482</v>
+        <v>2015</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>317</v>
@@ -9997,7 +10013,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>1500</v>
+        <v>2016</v>
       </c>
       <c r="B282" s="6" t="s">
         <v>328</v>
@@ -10026,7 +10042,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>1501</v>
+        <v>2017</v>
       </c>
       <c r="B283" s="6" t="s">
         <v>328</v>
@@ -10055,7 +10071,7 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>1502</v>
+        <v>2018</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>328</v>
@@ -10084,7 +10100,7 @@
     </row>
     <row r="285" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>1503</v>
+        <v>2019</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>328</v>
@@ -10113,7 +10129,7 @@
     </row>
     <row r="286" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>1504</v>
+        <v>2020</v>
       </c>
       <c r="B286" s="6" t="s">
         <v>328</v>
@@ -10142,7 +10158,7 @@
     </row>
     <row r="287" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>1505</v>
+        <v>2021</v>
       </c>
       <c r="B287" s="6" t="s">
         <v>328</v>
@@ -10171,7 +10187,7 @@
     </row>
     <row r="288" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>1506</v>
+        <v>2022</v>
       </c>
       <c r="B288" s="6" t="s">
         <v>328</v>
@@ -10200,10 +10216,10 @@
     </row>
     <row r="289" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>1507</v>
+        <v>2023</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>317</v>
@@ -10229,7 +10245,7 @@
     </row>
     <row r="290" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>1508</v>
+        <v>2024</v>
       </c>
       <c r="B290" s="6" t="s">
         <v>328</v>
@@ -10258,10 +10274,10 @@
     </row>
     <row r="291" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>1509</v>
+        <v>2025</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>396</v>
@@ -10290,7 +10306,7 @@
     </row>
     <row r="292" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>1510</v>
+        <v>2026</v>
       </c>
       <c r="B292" s="6" t="s">
         <v>328</v>
@@ -10322,7 +10338,7 @@
     </row>
     <row r="293" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>1511</v>
+        <v>2027</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>328</v>
@@ -10354,7 +10370,7 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>1512</v>
+        <v>2028</v>
       </c>
       <c r="B294" s="6" t="s">
         <v>328</v>
@@ -10386,7 +10402,7 @@
     </row>
     <row r="295" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>1513</v>
+        <v>2029</v>
       </c>
       <c r="B295" s="6" t="s">
         <v>328</v>
@@ -10418,10 +10434,10 @@
     </row>
     <row r="296" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>1514</v>
+        <v>2030</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>20</v>
@@ -10450,7 +10466,7 @@
     </row>
     <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>1515</v>
+        <v>2031</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>328</v>
@@ -10482,7 +10498,7 @@
     </row>
     <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>1516</v>
+        <v>2032</v>
       </c>
       <c r="B298" s="6" t="s">
         <v>328</v>
@@ -10514,7 +10530,7 @@
     </row>
     <row r="299" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>1517</v>
+        <v>2033</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>328</v>
@@ -10546,7 +10562,7 @@
     </row>
     <row r="300" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>1518</v>
+        <v>2034</v>
       </c>
       <c r="B300" s="6" t="s">
         <v>328</v>
@@ -10578,7 +10594,7 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>1519</v>
+        <v>2100</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>328</v>
@@ -10610,7 +10626,7 @@
     </row>
     <row r="302" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>1600</v>
+        <v>2101</v>
       </c>
       <c r="B302" s="6" t="s">
         <v>328</v>
@@ -10663,10 +10679,97 @@
         <v>0</v>
       </c>
     </row>
+    <row r="304" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A304" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E304" s="1">
+        <v>0</v>
+      </c>
+      <c r="F304" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="H304" s="1">
+        <v>0</v>
+      </c>
+      <c r="I304" s="1">
+        <v>0</v>
+      </c>
+      <c r="J304" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A305" s="1">
+        <v>3001</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E305" s="1">
+        <v>0</v>
+      </c>
+      <c r="F305" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H305" s="1">
+        <v>0</v>
+      </c>
+      <c r="I305" s="1">
+        <v>0</v>
+      </c>
+      <c r="J305" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A306" s="1">
+        <v>3002</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E306" s="1">
+        <v>0</v>
+      </c>
+      <c r="F306" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G306" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H306" s="1">
+        <v>0</v>
+      </c>
+      <c r="I306" s="1">
+        <v>0</v>
+      </c>
+      <c r="J306" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:B3">
-    <sortState ref="A4:K127">
-      <sortCondition ref="A3:A127"/>
+    <sortState ref="A4:B303">
+      <sortCondition ref="A3"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="422">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1378,6 +1378,14 @@
   </si>
   <si>
     <t>这块地已经平整过了，\n不需要再锄地了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果不选择种子，\n是没办法种地的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这块地无法种植</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1757,7 +1765,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J306"/>
+  <dimension ref="A2:J308"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -10763,6 +10771,64 @@
         <v>0</v>
       </c>
       <c r="J306" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A307" s="1">
+        <v>3003</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E307" s="1">
+        <v>0</v>
+      </c>
+      <c r="F307" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G307" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H307" s="1">
+        <v>0</v>
+      </c>
+      <c r="I307" s="1">
+        <v>0</v>
+      </c>
+      <c r="J307" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A308" s="1">
+        <v>3004</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E308" s="1">
+        <v>0</v>
+      </c>
+      <c r="F308" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G308" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H308" s="1">
+        <v>0</v>
+      </c>
+      <c r="I308" s="1">
+        <v>0</v>
+      </c>
+      <c r="J308" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="425">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1386,6 +1386,18 @@
   </si>
   <si>
     <t>这块地无法种植</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这块地已经不需要浇水了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不使用水壶的话,\n我没办法浇水</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1765,7 +1777,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J308"/>
+  <dimension ref="A2:J310"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -10829,6 +10841,64 @@
         <v>0</v>
       </c>
       <c r="J308" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A309" s="1">
+        <v>3005</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E309" s="1">
+        <v>0</v>
+      </c>
+      <c r="F309" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H309" s="1">
+        <v>0</v>
+      </c>
+      <c r="I309" s="1">
+        <v>0</v>
+      </c>
+      <c r="J309" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A310" s="1">
+        <v>3006</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E310" s="1">
+        <v>0</v>
+      </c>
+      <c r="F310" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H310" s="1">
+        <v>0</v>
+      </c>
+      <c r="I310" s="1">
+        <v>0</v>
+      </c>
+      <c r="J310" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="428">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1397,7 +1397,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水壶里没有水了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>不使用水壶的话,\n我没办法浇水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水壶已经满了,\n不需要再装水了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1777,7 +1789,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J310"/>
+  <dimension ref="A2:J312"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -10861,7 +10873,7 @@
         <v>315</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H309" s="1">
         <v>0</v>
@@ -10899,6 +10911,64 @@
         <v>0</v>
       </c>
       <c r="J310" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A311" s="1">
+        <v>3007</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E311" s="1">
+        <v>0</v>
+      </c>
+      <c r="F311" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H311" s="1">
+        <v>0</v>
+      </c>
+      <c r="I311" s="1">
+        <v>0</v>
+      </c>
+      <c r="J311" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A312" s="1">
+        <v>3008</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E312" s="1">
+        <v>0</v>
+      </c>
+      <c r="F312" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G312" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H312" s="1">
+        <v>0</v>
+      </c>
+      <c r="I312" s="1">
+        <v>0</v>
+      </c>
+      <c r="J312" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2557" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="430">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1410,6 +1410,14 @@
   </si>
   <si>
     <t>水壶已经满了,\n不需要再装水了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的背包没有空间了,\n我应该至少在背包中留一个空位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗯，还是先留着为好</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1789,7 +1797,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J312"/>
+  <dimension ref="A2:J314"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -10969,6 +10977,64 @@
         <v>0</v>
       </c>
       <c r="J312" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A313" s="1">
+        <v>3010</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E313" s="1">
+        <v>0</v>
+      </c>
+      <c r="F313" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G313" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="H313" s="1">
+        <v>0</v>
+      </c>
+      <c r="I313" s="1">
+        <v>0</v>
+      </c>
+      <c r="J313" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A314" s="1">
+        <v>3011</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E314" s="1">
+        <v>0</v>
+      </c>
+      <c r="F314" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G314" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H314" s="1">
+        <v>0</v>
+      </c>
+      <c r="I314" s="1">
+        <v>0</v>
+      </c>
+      <c r="J314" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="432">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1418,6 +1418,14 @@
   </si>
   <si>
     <t>嗯，还是先留着为好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我累了,还是先休息,明天再出去</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1797,7 +1805,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J314"/>
+  <dimension ref="A2:J315"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -6732,7 +6740,7 @@
         <v>1400</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>14</v>
@@ -6750,7 +6758,7 @@
         <v>361</v>
       </c>
       <c r="H171" s="1">
-        <v>2002</v>
+        <v>1401</v>
       </c>
       <c r="I171" s="1">
         <v>0</v>
@@ -6782,7 +6790,7 @@
         <v>362</v>
       </c>
       <c r="H172" s="1">
-        <v>2003</v>
+        <v>1402</v>
       </c>
       <c r="I172" s="1">
         <v>0</v>
@@ -6796,7 +6804,7 @@
         <v>1402</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>14</v>
@@ -6814,7 +6822,7 @@
         <v>363</v>
       </c>
       <c r="H173" s="1">
-        <v>2004</v>
+        <v>1403</v>
       </c>
       <c r="I173" s="1">
         <v>0</v>
@@ -6846,7 +6854,7 @@
         <v>175</v>
       </c>
       <c r="H174" s="1">
-        <v>2005</v>
+        <v>1404</v>
       </c>
       <c r="I174" s="1">
         <v>0</v>
@@ -6892,7 +6900,7 @@
         <v>1405</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>14</v>
@@ -6910,7 +6918,7 @@
         <v>364</v>
       </c>
       <c r="H176" s="1">
-        <v>2007</v>
+        <v>1406</v>
       </c>
       <c r="I176" s="1">
         <v>0</v>
@@ -6974,7 +6982,7 @@
         <v>179</v>
       </c>
       <c r="H178" s="1">
-        <v>2009</v>
+        <v>1408</v>
       </c>
       <c r="I178" s="1">
         <v>0</v>
@@ -7006,7 +7014,7 @@
         <v>180</v>
       </c>
       <c r="H179" s="1">
-        <v>2010</v>
+        <v>1409</v>
       </c>
       <c r="I179" s="1">
         <v>0</v>
@@ -7020,7 +7028,7 @@
         <v>1409</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>14</v>
@@ -7038,7 +7046,7 @@
         <v>181</v>
       </c>
       <c r="H180" s="1">
-        <v>2011</v>
+        <v>1410</v>
       </c>
       <c r="I180" s="1">
         <v>0</v>
@@ -7102,7 +7110,7 @@
         <v>414</v>
       </c>
       <c r="H182" s="1">
-        <v>2101</v>
+        <v>1412</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
@@ -7198,7 +7206,7 @@
         <v>184</v>
       </c>
       <c r="H185" s="1">
-        <v>2014</v>
+        <v>1415</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
@@ -7244,7 +7252,7 @@
         <v>1416</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>14</v>
@@ -7262,7 +7270,7 @@
         <v>365</v>
       </c>
       <c r="H187" s="1">
-        <v>2016</v>
+        <v>1417</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
@@ -7294,7 +7302,7 @@
         <v>187</v>
       </c>
       <c r="H188" s="1">
-        <v>2017</v>
+        <v>1418</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
@@ -7340,7 +7348,7 @@
         <v>1419</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>14</v>
@@ -7358,7 +7366,7 @@
         <v>366</v>
       </c>
       <c r="H190" s="1">
-        <v>2019</v>
+        <v>1420</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
@@ -7390,7 +7398,7 @@
         <v>190</v>
       </c>
       <c r="H191" s="1">
-        <v>2020</v>
+        <v>1421</v>
       </c>
       <c r="I191" s="1">
         <v>0</v>
@@ -7454,7 +7462,7 @@
         <v>192</v>
       </c>
       <c r="H193" s="1">
-        <v>2022</v>
+        <v>1423</v>
       </c>
       <c r="I193" s="1">
         <v>0</v>
@@ -7486,7 +7494,7 @@
         <v>367</v>
       </c>
       <c r="H194" s="1">
-        <v>2023</v>
+        <v>1424</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
@@ -7500,7 +7508,7 @@
         <v>1424</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>14</v>
@@ -7550,7 +7558,7 @@
         <v>195</v>
       </c>
       <c r="H196" s="1">
-        <v>2025</v>
+        <v>1426</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
@@ -7564,7 +7572,7 @@
         <v>1426</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>14</v>
@@ -7582,7 +7590,7 @@
         <v>369</v>
       </c>
       <c r="H197" s="1">
-        <v>2026</v>
+        <v>1427</v>
       </c>
       <c r="I197" s="1">
         <v>0</v>
@@ -7646,7 +7654,7 @@
         <v>197</v>
       </c>
       <c r="H199" s="1">
-        <v>2028</v>
+        <v>1429</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
@@ -7724,7 +7732,7 @@
         <v>1431</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>14</v>
@@ -7742,7 +7750,7 @@
         <v>200</v>
       </c>
       <c r="H202" s="1">
-        <v>2031</v>
+        <v>1432</v>
       </c>
       <c r="I202" s="1">
         <v>0</v>
@@ -7806,7 +7814,7 @@
         <v>202</v>
       </c>
       <c r="H204" s="1">
-        <v>2033</v>
+        <v>1434</v>
       </c>
       <c r="I204" s="1">
         <v>0</v>
@@ -11035,6 +11043,35 @@
         <v>0</v>
       </c>
       <c r="J314" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A315" s="1">
+        <v>3012</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E315" s="1">
+        <v>0</v>
+      </c>
+      <c r="F315" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="G315" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="H315" s="1">
+        <v>0</v>
+      </c>
+      <c r="I315" s="1">
+        <v>0</v>
+      </c>
+      <c r="J315" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="356">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -57,15 +57,6 @@
     <t>玛德琳</t>
   </si>
   <si>
-    <t>空空的衣柜,看起来没什么用,以后也许会有用吧。</t>
-  </si>
-  <si>
-    <t>一个古朴的镜子,一张帅气的脸映在镜子里。</t>
-  </si>
-  <si>
-    <t>这个抽屉被锁上了,里面有什么呢？</t>
-  </si>
-  <si>
     <t>嗯..你,要干嘛？</t>
   </si>
   <si>
@@ -322,9 +313,6 @@
   </si>
   <si>
     <t>你听到了什么？可不要到处乱说啊,这都是我们年轻时发生的事。</t>
-  </si>
-  <si>
-    <t>帕特里克那个老固执还是每天都到广场独坐啊,明明过去那么久了…</t>
   </si>
   <si>
     <t>传说我们人鱼族有一位女孩的鱼尾变成了双脚,走上了陆地呢…</t>
@@ -1086,14 +1074,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1111,6 +1091,48 @@
   </si>
   <si>
     <t>talkSource</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克那个老固执在干什么呢？..明明过去那么久了…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹是个好孩子，如果他的父母还在的话…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好呀，小家伙，称年轻要好好享受生活哟..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有烦心事的话，来和奶奶说，我会帮助你的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做一个好农夫也不容易呢，要加油哦！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>你好,你的房子好大呀！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我来买东西！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我来逛逛你的商店,\n今天有什么好东西呀？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1478,11 +1500,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J316"/>
+  <dimension ref="A2:J320"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.875" style="4" customWidth="1"/>
     <col min="3" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" style="4" customWidth="1"/>
@@ -1494,42 +1516,42 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -1553,7 +1575,7 @@
         <v>7</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.15">
@@ -1561,22 +1583,19 @@
         <v>1000</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>232</v>
+        <v>351</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>11</v>
+        <v>354</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -1588,27 +1607,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>353</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -1625,22 +1641,19 @@
         <v>1002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
+        <v>355</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -1657,19 +1670,19 @@
         <v>1003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1686,19 +1699,19 @@
         <v>1004</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1715,19 +1728,19 @@
         <v>1005</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -1744,19 +1757,19 @@
         <v>1006</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -1773,19 +1786,19 @@
         <v>1007</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -1802,19 +1815,19 @@
         <v>1008</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -1831,19 +1844,19 @@
         <v>1009</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -1860,19 +1873,19 @@
         <v>1010</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -1889,19 +1902,19 @@
         <v>1011</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -1918,19 +1931,19 @@
         <v>1012</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -1947,19 +1960,19 @@
         <v>1013</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -1976,19 +1989,19 @@
         <v>1014</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -2005,19 +2018,19 @@
         <v>1015</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -2034,19 +2047,19 @@
         <v>1016</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -2063,19 +2076,19 @@
         <v>1017</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -2092,19 +2105,19 @@
         <v>1018</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -2121,19 +2134,19 @@
         <v>1019</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -2150,19 +2163,19 @@
         <v>1020</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -2179,19 +2192,19 @@
         <v>1021</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2208,19 +2221,19 @@
         <v>1022</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -2237,19 +2250,19 @@
         <v>1023</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2266,19 +2279,19 @@
         <v>1024</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -2298,16 +2311,16 @@
         <v>2</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2327,16 +2340,16 @@
         <v>2</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2356,16 +2369,16 @@
         <v>2</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -2385,16 +2398,16 @@
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2414,16 +2427,16 @@
         <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2443,16 +2456,16 @@
         <v>2</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E34" s="1">
         <v>0</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -2472,16 +2485,16 @@
         <v>2</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E35" s="1">
         <v>0</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -2501,16 +2514,16 @@
         <v>2</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E36" s="1">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -2530,16 +2543,16 @@
         <v>2</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -2559,16 +2572,16 @@
         <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -2588,16 +2601,16 @@
         <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -2617,16 +2630,16 @@
         <v>2</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E40" s="1">
         <v>0</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -2646,16 +2659,16 @@
         <v>2</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -2675,16 +2688,16 @@
         <v>2</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -2704,16 +2717,16 @@
         <v>2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -2733,16 +2746,16 @@
         <v>2</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -2762,16 +2775,16 @@
         <v>2</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -2791,16 +2804,16 @@
         <v>2</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -2820,16 +2833,16 @@
         <v>2</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -2849,16 +2862,16 @@
         <v>2</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -2878,16 +2891,16 @@
         <v>2</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -2907,16 +2920,16 @@
         <v>2</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -2936,16 +2949,16 @@
         <v>2</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -2965,16 +2978,16 @@
         <v>2</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
@@ -2994,16 +3007,16 @@
         <v>2</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -3023,16 +3036,16 @@
         <v>2</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -3052,16 +3065,16 @@
         <v>2</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -3081,16 +3094,16 @@
         <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H56" s="1">
         <v>0</v>
@@ -3110,16 +3123,16 @@
         <v>2</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -3139,16 +3152,16 @@
         <v>2</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H58" s="1">
         <v>0</v>
@@ -3168,16 +3181,16 @@
         <v>2</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H59" s="1">
         <v>0</v>
@@ -3197,16 +3210,16 @@
         <v>2</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H60" s="1">
         <v>0</v>
@@ -3226,16 +3239,16 @@
         <v>2</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
@@ -3255,16 +3268,16 @@
         <v>2</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="H62" s="1">
         <v>0</v>
@@ -3284,16 +3297,16 @@
         <v>2</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -3313,16 +3326,16 @@
         <v>2</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H64" s="1">
         <v>0</v>
@@ -3342,16 +3355,16 @@
         <v>2</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -3371,16 +3384,16 @@
         <v>2</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -3400,16 +3413,16 @@
         <v>2</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -3429,16 +3442,16 @@
         <v>2</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E68" s="1">
         <v>0</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -3458,16 +3471,16 @@
         <v>2</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -3487,16 +3500,16 @@
         <v>2</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -3516,16 +3529,16 @@
         <v>2</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -3545,16 +3558,16 @@
         <v>2</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -3574,16 +3587,16 @@
         <v>2</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -3603,16 +3616,16 @@
         <v>2</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -3632,16 +3645,16 @@
         <v>2</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -3661,16 +3674,16 @@
         <v>2</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -3690,16 +3703,16 @@
         <v>2</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -3719,16 +3732,16 @@
         <v>2</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
@@ -3748,16 +3761,16 @@
         <v>2</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E79" s="1">
         <v>0</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -3777,16 +3790,16 @@
         <v>2</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E80" s="1">
         <v>0</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -3806,16 +3819,16 @@
         <v>2</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E81" s="1">
         <v>0</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -3835,16 +3848,16 @@
         <v>2</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -3864,16 +3877,16 @@
         <v>2</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
@@ -3893,16 +3906,16 @@
         <v>2</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
@@ -3922,16 +3935,16 @@
         <v>2</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -3951,16 +3964,16 @@
         <v>2</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H86" s="1">
         <v>0</v>
@@ -3980,16 +3993,16 @@
         <v>2</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -4009,16 +4022,16 @@
         <v>2</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -4038,16 +4051,16 @@
         <v>2</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -4067,16 +4080,16 @@
         <v>2</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -4096,16 +4109,16 @@
         <v>2</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -4125,16 +4138,16 @@
         <v>2</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -4154,16 +4167,16 @@
         <v>2</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
@@ -4183,16 +4196,16 @@
         <v>2</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -4212,16 +4225,16 @@
         <v>2</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -4241,16 +4254,16 @@
         <v>2</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E96" s="1">
         <v>0</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -4270,16 +4283,16 @@
         <v>2</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E97" s="1">
         <v>0</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -4299,16 +4312,16 @@
         <v>2</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -4328,16 +4341,16 @@
         <v>2</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -4357,16 +4370,16 @@
         <v>2</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -4386,16 +4399,16 @@
         <v>2</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -4415,16 +4428,16 @@
         <v>2</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1">
         <v>0</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -4444,16 +4457,16 @@
         <v>2</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -4473,16 +4486,16 @@
         <v>2</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1">
         <v>0</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -4502,16 +4515,16 @@
         <v>2</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -4531,16 +4544,16 @@
         <v>2</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -4560,16 +4573,16 @@
         <v>2</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -4589,16 +4602,16 @@
         <v>2</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -4618,16 +4631,16 @@
         <v>2</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -4647,16 +4660,16 @@
         <v>2</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -4676,16 +4689,16 @@
         <v>2</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -4705,16 +4718,16 @@
         <v>2</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -4734,16 +4747,16 @@
         <v>2</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -4763,16 +4776,16 @@
         <v>2</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -4792,16 +4805,16 @@
         <v>2</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -4821,16 +4834,16 @@
         <v>2</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E116" s="1">
         <v>0</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -4850,16 +4863,16 @@
         <v>2</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E117" s="1">
         <v>0</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -4879,16 +4892,16 @@
         <v>2</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E118" s="1">
         <v>0</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -4908,16 +4921,16 @@
         <v>2</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E119" s="1">
         <v>0</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -4937,16 +4950,16 @@
         <v>2</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E120" s="1">
         <v>0</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -4966,16 +4979,16 @@
         <v>2</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E121" s="1">
         <v>0</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -4995,16 +5008,16 @@
         <v>2</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E122" s="1">
         <v>0</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -5024,16 +5037,16 @@
         <v>2</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E123" s="1">
         <v>0</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
@@ -5053,16 +5066,16 @@
         <v>2</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E124" s="1">
         <v>0</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
@@ -5076,22 +5089,22 @@
     </row>
     <row r="125" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B125" s="4">
         <v>2</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
@@ -5105,22 +5118,22 @@
     </row>
     <row r="126" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B126" s="4">
         <v>2</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E126" s="1">
         <v>0</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
@@ -5132,24 +5145,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B127" s="4">
         <v>2</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E127" s="1">
         <v>0</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H127" s="1">
         <v>0</v>
@@ -5163,22 +5176,22 @@
     </row>
     <row r="128" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>1219</v>
+        <v>1301</v>
       </c>
       <c r="B128" s="4">
         <v>2</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
@@ -5192,22 +5205,22 @@
     </row>
     <row r="129" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B129" s="4">
         <v>2</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
@@ -5219,24 +5232,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B130" s="4">
         <v>2</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H130" s="1">
         <v>0</v>
@@ -5250,22 +5263,22 @@
     </row>
     <row r="131" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B131" s="4">
         <v>2</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H131" s="1">
         <v>0</v>
@@ -5277,24 +5290,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B132" s="4">
         <v>2</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="H132" s="1">
         <v>0</v>
@@ -5308,22 +5321,22 @@
     </row>
     <row r="133" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B133" s="4">
         <v>2</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H133" s="1">
         <v>0</v>
@@ -5337,22 +5350,22 @@
     </row>
     <row r="134" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B134" s="4">
         <v>2</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H134" s="1">
         <v>0</v>
@@ -5364,24 +5377,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B135" s="4">
         <v>2</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H135" s="1">
         <v>0</v>
@@ -5393,24 +5406,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B136" s="4">
         <v>2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H136" s="1">
         <v>0</v>
@@ -5424,22 +5437,22 @@
     </row>
     <row r="137" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B137" s="4">
         <v>2</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H137" s="1">
         <v>0</v>
@@ -5451,24 +5464,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B138" s="4">
         <v>2</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H138" s="1">
         <v>0</v>
@@ -5482,22 +5495,22 @@
     </row>
     <row r="139" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B139" s="4">
         <v>2</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
@@ -5511,225 +5524,225 @@
     </row>
     <row r="140" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B140" s="4">
         <v>2</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E140" s="1">
         <v>0</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G140" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+      <c r="I140" s="1">
+        <v>0</v>
+      </c>
+      <c r="J140" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A141" s="1">
+        <v>1314</v>
+      </c>
+      <c r="B141" s="4">
+        <v>2</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
+      </c>
+      <c r="I141" s="1">
+        <v>0</v>
+      </c>
+      <c r="J141" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A142" s="1">
+        <v>1315</v>
+      </c>
+      <c r="B142" s="4">
+        <v>2</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E142" s="1">
+        <v>0</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+      <c r="I142" s="1">
+        <v>0</v>
+      </c>
+      <c r="J142" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A143" s="1">
+        <v>1316</v>
+      </c>
+      <c r="B143" s="4">
+        <v>2</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E143" s="1">
+        <v>0</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G143" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H140" s="1">
-        <v>0</v>
-      </c>
-      <c r="I140" s="1">
-        <v>0</v>
-      </c>
-      <c r="J140" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A141" s="1">
-        <v>1313</v>
-      </c>
-      <c r="B141" s="4">
-        <v>2</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E141" s="1">
-        <v>0</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G141" s="1" t="s">
+      <c r="H143" s="1">
+        <v>0</v>
+      </c>
+      <c r="I143" s="1">
+        <v>0</v>
+      </c>
+      <c r="J143" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A144" s="1">
+        <v>1317</v>
+      </c>
+      <c r="B144" s="4">
+        <v>2</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E144" s="1">
+        <v>0</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G144" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H141" s="1">
-        <v>0</v>
-      </c>
-      <c r="I141" s="1">
-        <v>0</v>
-      </c>
-      <c r="J141" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A142" s="1">
-        <v>1314</v>
-      </c>
-      <c r="B142" s="4">
-        <v>2</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E142" s="1">
-        <v>0</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G142" s="1" t="s">
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+      <c r="I144" s="1">
+        <v>0</v>
+      </c>
+      <c r="J144" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A145" s="1">
+        <v>1318</v>
+      </c>
+      <c r="B145" s="4">
+        <v>2</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E145" s="1">
+        <v>0</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G145" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H142" s="1">
-        <v>0</v>
-      </c>
-      <c r="I142" s="1">
-        <v>0</v>
-      </c>
-      <c r="J142" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A143" s="1">
-        <v>1315</v>
-      </c>
-      <c r="B143" s="4">
-        <v>2</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E143" s="1">
-        <v>0</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G143" s="1" t="s">
+      <c r="H145" s="1">
+        <v>0</v>
+      </c>
+      <c r="I145" s="1">
+        <v>0</v>
+      </c>
+      <c r="J145" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A146" s="1">
+        <v>1319</v>
+      </c>
+      <c r="B146" s="4">
+        <v>2</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G146" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="H143" s="1">
-        <v>0</v>
-      </c>
-      <c r="I143" s="1">
-        <v>0</v>
-      </c>
-      <c r="J143" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A144" s="1">
-        <v>1316</v>
-      </c>
-      <c r="B144" s="4">
-        <v>2</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E144" s="1">
-        <v>0</v>
-      </c>
-      <c r="F144" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G144" s="1" t="s">
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+      <c r="I146" s="1">
+        <v>0</v>
+      </c>
+      <c r="J146" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A147" s="1">
+        <v>1320</v>
+      </c>
+      <c r="B147" s="4">
+        <v>2</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E147" s="1">
+        <v>0</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G147" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="H144" s="1">
-        <v>0</v>
-      </c>
-      <c r="I144" s="1">
-        <v>0</v>
-      </c>
-      <c r="J144" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A145" s="1">
-        <v>1317</v>
-      </c>
-      <c r="B145" s="4">
-        <v>2</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E145" s="1">
-        <v>0</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H145" s="1">
-        <v>0</v>
-      </c>
-      <c r="I145" s="1">
-        <v>0</v>
-      </c>
-      <c r="J145" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A146" s="1">
-        <v>1318</v>
-      </c>
-      <c r="B146" s="4">
-        <v>2</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E146" s="1">
-        <v>0</v>
-      </c>
-      <c r="F146" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H146" s="1">
-        <v>0</v>
-      </c>
-      <c r="I146" s="1">
-        <v>0</v>
-      </c>
-      <c r="J146" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A147" s="1">
-        <v>1319</v>
-      </c>
-      <c r="B147" s="4">
-        <v>2</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E147" s="1">
-        <v>0</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
@@ -5743,22 +5756,22 @@
     </row>
     <row r="148" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B148" s="4">
         <v>2</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E148" s="1">
         <v>0</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
@@ -5772,22 +5785,22 @@
     </row>
     <row r="149" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B149" s="4">
         <v>2</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E149" s="1">
         <v>0</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
@@ -5799,24 +5812,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B150" s="4">
         <v>2</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E150" s="1">
         <v>0</v>
       </c>
       <c r="F150" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H150" s="1">
         <v>0</v>
@@ -5828,24 +5841,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B151" s="4">
         <v>2</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E151" s="1">
         <v>0</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
@@ -5859,22 +5872,22 @@
     </row>
     <row r="152" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B152" s="4">
         <v>2</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E152" s="1">
         <v>0</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
@@ -5888,22 +5901,22 @@
     </row>
     <row r="153" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B153" s="4">
         <v>2</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E153" s="1">
         <v>0</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H153" s="1">
         <v>0</v>
@@ -5915,24 +5928,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B154" s="4">
         <v>2</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E154" s="1">
         <v>0</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H154" s="1">
         <v>0</v>
@@ -5944,24 +5957,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B155" s="4">
         <v>2</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E155" s="1">
         <v>0</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
@@ -5975,22 +5988,22 @@
     </row>
     <row r="156" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B156" s="4">
         <v>2</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E156" s="1">
         <v>0</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
@@ -6002,24 +6015,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B157" s="4">
         <v>2</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E157" s="1">
         <v>0</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H157" s="1">
         <v>0</v>
@@ -6031,24 +6044,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B158" s="4">
         <v>2</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E158" s="1">
         <v>0</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H158" s="1">
         <v>0</v>
@@ -6062,22 +6075,22 @@
     </row>
     <row r="159" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B159" s="4">
         <v>2</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E159" s="1">
         <v>0</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -6091,22 +6104,22 @@
     </row>
     <row r="160" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B160" s="4">
         <v>2</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E160" s="1">
         <v>0</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
@@ -6120,22 +6133,22 @@
     </row>
     <row r="161" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B161" s="4">
         <v>2</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E161" s="1">
         <v>0</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H161" s="1">
         <v>0</v>
@@ -6149,22 +6162,22 @@
     </row>
     <row r="162" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B162" s="4">
         <v>2</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E162" s="1">
         <v>0</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H162" s="1">
         <v>0</v>
@@ -6178,22 +6191,22 @@
     </row>
     <row r="163" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B163" s="4">
         <v>2</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E163" s="1">
         <v>0</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
@@ -6207,22 +6220,22 @@
     </row>
     <row r="164" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B164" s="4">
         <v>2</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E164" s="1">
         <v>0</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H164" s="1">
         <v>0</v>
@@ -6236,22 +6249,22 @@
     </row>
     <row r="165" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B165" s="4">
         <v>2</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E165" s="1">
         <v>0</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H165" s="1">
         <v>0</v>
@@ -6265,22 +6278,22 @@
     </row>
     <row r="166" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B166" s="4">
         <v>2</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E166" s="1">
         <v>0</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="H166" s="1">
         <v>0</v>
@@ -6292,27 +6305,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>1339</v>
+        <v>1400</v>
       </c>
       <c r="B167" s="4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E167" s="1">
         <v>0</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>123</v>
+        <v>268</v>
       </c>
       <c r="H167" s="1">
-        <v>0</v>
+        <v>1401</v>
       </c>
       <c r="I167" s="1">
         <v>0</v>
@@ -6323,28 +6339,28 @@
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B168" s="4">
+        <v>2</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E168" s="1">
         <v>1</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E168" s="1">
-        <v>0</v>
-      </c>
       <c r="F168" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H168" s="1">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="I168" s="1">
         <v>0</v>
@@ -6355,60 +6371,60 @@
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B169" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="E169" s="1">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H169" s="1">
+        <v>1403</v>
+      </c>
+      <c r="I169" s="1">
+        <v>0</v>
+      </c>
+      <c r="J169" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A170" s="1">
+        <v>1403</v>
+      </c>
+      <c r="B170" s="4">
+        <v>2</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E170" s="1">
         <v>1</v>
       </c>
-      <c r="F169" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H169" s="1">
-        <v>1402</v>
-      </c>
-      <c r="I169" s="1">
-        <v>0</v>
-      </c>
-      <c r="J169" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A170" s="1">
-        <v>1402</v>
-      </c>
-      <c r="B170" s="4">
-        <v>1</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E170" s="1">
-        <v>0</v>
-      </c>
       <c r="F170" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>274</v>
+        <v>135</v>
       </c>
       <c r="H170" s="1">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="I170" s="1">
         <v>0</v>
@@ -6417,9 +6433,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B171" s="4">
         <v>2</v>
@@ -6428,22 +6444,22 @@
         <v>0</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H171" s="1">
-        <v>1404</v>
+        <v>0</v>
       </c>
       <c r="I171" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J171" s="1" t="b">
         <v>0</v>
@@ -6451,31 +6467,31 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B172" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>319</v>
+        <v>228</v>
       </c>
       <c r="E172" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>140</v>
+        <v>271</v>
       </c>
       <c r="H172" s="1">
-        <v>0</v>
+        <v>1406</v>
       </c>
       <c r="I172" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J172" s="1" t="b">
         <v>0</v>
@@ -6483,31 +6499,31 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B173" s="4">
+        <v>2</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E173" s="1">
         <v>1</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E173" s="1">
-        <v>0</v>
-      </c>
       <c r="F173" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>275</v>
+        <v>137</v>
       </c>
       <c r="H173" s="1">
-        <v>1406</v>
+        <v>0</v>
       </c>
       <c r="I173" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J173" s="1" t="b">
         <v>0</v>
@@ -6515,39 +6531,39 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B174" s="4">
         <v>2</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H174" s="1">
-        <v>0</v>
+        <v>1408</v>
       </c>
       <c r="I174" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J174" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B175" s="4">
         <v>2</v>
@@ -6556,19 +6572,19 @@
         <v>9</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E175" s="1">
         <v>1</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H175" s="1">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="I175" s="1">
         <v>0</v>
@@ -6577,73 +6593,73 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B176" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C176" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E176" s="1">
+        <v>0</v>
+      </c>
+      <c r="F176" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H176" s="1">
+        <v>1410</v>
+      </c>
+      <c r="I176" s="1">
+        <v>0</v>
+      </c>
+      <c r="J176" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A177" s="1">
+        <v>1410</v>
+      </c>
+      <c r="B177" s="4">
+        <v>2</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E176" s="1">
+      <c r="D177" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E177" s="1">
         <v>1</v>
       </c>
-      <c r="F176" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G176" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H176" s="1">
-        <v>1409</v>
-      </c>
-      <c r="I176" s="1">
-        <v>0</v>
-      </c>
-      <c r="J176" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A177" s="1">
-        <v>1409</v>
-      </c>
-      <c r="B177" s="4">
-        <v>1</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E177" s="1">
-        <v>0</v>
-      </c>
       <c r="F177" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>144</v>
+        <v>319</v>
       </c>
       <c r="H177" s="1">
-        <v>1410</v>
+        <v>0</v>
       </c>
       <c r="I177" s="1">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J177" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B178" s="4">
         <v>2</v>
@@ -6652,30 +6668,30 @@
         <v>9</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H178" s="1">
-        <v>0</v>
+        <v>1412</v>
       </c>
       <c r="I178" s="1">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J178" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B179" s="4">
         <v>2</v>
@@ -6684,30 +6700,30 @@
         <v>9</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H179" s="1">
-        <v>1412</v>
+        <v>0</v>
       </c>
       <c r="I179" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J179" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B180" s="4">
         <v>2</v>
@@ -6716,30 +6732,30 @@
         <v>9</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E180" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>325</v>
+        <v>141</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
       <c r="I180" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J180" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B181" s="4">
         <v>2</v>
@@ -6748,19 +6764,19 @@
         <v>9</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E181" s="1">
         <v>0</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H181" s="1">
-        <v>0</v>
+        <v>1415</v>
       </c>
       <c r="I181" s="1">
         <v>0</v>
@@ -6769,9 +6785,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B182" s="4">
         <v>2</v>
@@ -6780,19 +6796,19 @@
         <v>9</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E182" s="1">
         <v>0</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H182" s="1">
-        <v>1415</v>
+        <v>0</v>
       </c>
       <c r="I182" s="1">
         <v>0</v>
@@ -6801,62 +6817,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B183" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C183" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E183" s="1">
+        <v>0</v>
+      </c>
+      <c r="F183" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="H183" s="1">
+        <v>1417</v>
+      </c>
+      <c r="I183" s="1">
+        <v>0</v>
+      </c>
+      <c r="J183" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A184" s="1">
+        <v>1417</v>
+      </c>
+      <c r="B184" s="4">
+        <v>2</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D183" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E183" s="1">
-        <v>0</v>
-      </c>
-      <c r="F183" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H183" s="1">
-        <v>0</v>
-      </c>
-      <c r="I183" s="1">
-        <v>0</v>
-      </c>
-      <c r="J183" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A184" s="1">
-        <v>1416</v>
-      </c>
-      <c r="B184" s="4">
-        <v>1</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D184" s="1" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="E184" s="1">
         <v>0</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>276</v>
+        <v>144</v>
       </c>
       <c r="H184" s="1">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="I184" s="1">
         <v>0</v>
@@ -6865,9 +6881,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B185" s="4">
         <v>2</v>
@@ -6876,19 +6892,19 @@
         <v>9</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E185" s="1">
         <v>0</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H185" s="1">
-        <v>1418</v>
+        <v>0</v>
       </c>
       <c r="I185" s="1">
         <v>0</v>
@@ -6897,62 +6913,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B186" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C186" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E186" s="1">
+        <v>0</v>
+      </c>
+      <c r="F186" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H186" s="1">
+        <v>1420</v>
+      </c>
+      <c r="I186" s="1">
+        <v>0</v>
+      </c>
+      <c r="J186" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A187" s="1">
+        <v>1420</v>
+      </c>
+      <c r="B187" s="4">
+        <v>2</v>
+      </c>
+      <c r="C187" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D186" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E186" s="1">
-        <v>0</v>
-      </c>
-      <c r="F186" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="H186" s="1">
-        <v>0</v>
-      </c>
-      <c r="I186" s="1">
-        <v>0</v>
-      </c>
-      <c r="J186" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A187" s="1">
-        <v>1419</v>
-      </c>
-      <c r="B187" s="4">
-        <v>1</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D187" s="1" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="E187" s="1">
         <v>0</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>277</v>
+        <v>146</v>
       </c>
       <c r="H187" s="1">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="I187" s="1">
         <v>0</v>
@@ -6963,7 +6979,7 @@
     </row>
     <row r="188" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B188" s="4">
         <v>2</v>
@@ -6972,19 +6988,19 @@
         <v>9</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E188" s="1">
         <v>0</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="H188" s="1">
-        <v>1421</v>
+        <v>0</v>
       </c>
       <c r="I188" s="1">
         <v>0</v>
@@ -6993,9 +7009,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B189" s="4">
         <v>2</v>
@@ -7004,19 +7020,19 @@
         <v>9</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E189" s="1">
         <v>0</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="H189" s="1">
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="I189" s="1">
         <v>0</v>
@@ -7027,7 +7043,7 @@
     </row>
     <row r="190" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B190" s="4">
         <v>2</v>
@@ -7036,19 +7052,19 @@
         <v>9</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E190" s="1">
         <v>0</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>152</v>
+        <v>274</v>
       </c>
       <c r="H190" s="1">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="I190" s="1">
         <v>0</v>
@@ -7057,126 +7073,126 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B191" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E191" s="1">
+        <v>0</v>
+      </c>
+      <c r="F191" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H191" s="1">
+        <v>0</v>
+      </c>
+      <c r="I191" s="1">
+        <v>0</v>
+      </c>
+      <c r="J191" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+      <c r="A192" s="1">
+        <v>1425</v>
+      </c>
+      <c r="B192" s="4">
+        <v>2</v>
+      </c>
+      <c r="C192" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E191" s="1">
-        <v>0</v>
-      </c>
-      <c r="F191" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="H191" s="1">
-        <v>1424</v>
-      </c>
-      <c r="I191" s="1">
-        <v>0</v>
-      </c>
-      <c r="J191" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A192" s="1">
-        <v>1424</v>
-      </c>
-      <c r="B192" s="4">
+      <c r="D192" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E192" s="1">
+        <v>0</v>
+      </c>
+      <c r="F192" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="H192" s="1">
+        <v>1426</v>
+      </c>
+      <c r="I192" s="1">
+        <v>0</v>
+      </c>
+      <c r="J192" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A193" s="1">
+        <v>1426</v>
+      </c>
+      <c r="B193" s="4">
         <v>1</v>
       </c>
-      <c r="C192" s="1" t="s">
+      <c r="C193" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D192" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E192" s="1">
-        <v>0</v>
-      </c>
-      <c r="F192" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="H192" s="1">
-        <v>0</v>
-      </c>
-      <c r="I192" s="1">
-        <v>0</v>
-      </c>
-      <c r="J192" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10" ht="54" x14ac:dyDescent="0.15">
-      <c r="A193" s="1">
-        <v>1425</v>
-      </c>
-      <c r="B193" s="4">
-        <v>2</v>
-      </c>
-      <c r="C193" s="1" t="s">
+      <c r="D193" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E193" s="1">
+        <v>0</v>
+      </c>
+      <c r="F193" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H193" s="1">
+        <v>1427</v>
+      </c>
+      <c r="I193" s="1">
+        <v>0</v>
+      </c>
+      <c r="J193" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+      <c r="A194" s="1">
+        <v>1427</v>
+      </c>
+      <c r="B194" s="4">
+        <v>2</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E193" s="1">
-        <v>0</v>
-      </c>
-      <c r="F193" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G193" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H193" s="1">
-        <v>1426</v>
-      </c>
-      <c r="I193" s="1">
-        <v>0</v>
-      </c>
-      <c r="J193" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A194" s="1">
-        <v>1426</v>
-      </c>
-      <c r="B194" s="4">
-        <v>1</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D194" s="1" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="E194" s="1">
         <v>0</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="H194" s="1">
-        <v>1427</v>
+        <v>0</v>
       </c>
       <c r="I194" s="1">
         <v>0</v>
@@ -7185,9 +7201,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B195" s="4">
         <v>2</v>
@@ -7196,19 +7212,19 @@
         <v>9</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E195" s="1">
         <v>0</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H195" s="1">
-        <v>0</v>
+        <v>1429</v>
       </c>
       <c r="I195" s="1">
         <v>0</v>
@@ -7219,7 +7235,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B196" s="4">
         <v>2</v>
@@ -7228,19 +7244,19 @@
         <v>9</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E196" s="1">
         <v>0</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="H196" s="1">
-        <v>1429</v>
+        <v>0</v>
       </c>
       <c r="I196" s="1">
         <v>0</v>
@@ -7251,7 +7267,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B197" s="4">
         <v>2</v>
@@ -7260,16 +7276,16 @@
         <v>9</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E197" s="1">
         <v>0</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>281</v>
+        <v>152</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
@@ -7283,60 +7299,60 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B198" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C198" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E198" s="1">
+        <v>0</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H198" s="1">
+        <v>1432</v>
+      </c>
+      <c r="I198" s="1">
+        <v>0</v>
+      </c>
+      <c r="J198" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A199" s="1">
+        <v>1432</v>
+      </c>
+      <c r="B199" s="4">
+        <v>2</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E198" s="1">
-        <v>0</v>
-      </c>
-      <c r="F198" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G198" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H198" s="1">
-        <v>0</v>
-      </c>
-      <c r="I198" s="1">
-        <v>0</v>
-      </c>
-      <c r="J198" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A199" s="1">
-        <v>1431</v>
-      </c>
-      <c r="B199" s="4">
-        <v>1</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D199" s="1" t="s">
-        <v>232</v>
+        <v>316</v>
       </c>
       <c r="E199" s="1">
         <v>0</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H199" s="1">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="I199" s="1">
         <v>0</v>
@@ -7347,7 +7363,7 @@
     </row>
     <row r="200" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B200" s="4">
         <v>2</v>
@@ -7356,19 +7372,19 @@
         <v>9</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E200" s="1">
         <v>0</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>312</v>
+        <v>235</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H200" s="1">
-        <v>0</v>
+        <v>1434</v>
       </c>
       <c r="I200" s="1">
         <v>0</v>
@@ -7377,9 +7393,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B201" s="4">
         <v>2</v>
@@ -7388,135 +7404,132 @@
         <v>9</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E201" s="1">
         <v>0</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="G201" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H201" s="1">
+        <v>0</v>
+      </c>
+      <c r="I201" s="1">
+        <v>0</v>
+      </c>
+      <c r="J201" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A202" s="1">
+        <v>1435</v>
+      </c>
+      <c r="B202" s="4">
+        <v>2</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E202" s="1">
+        <v>0</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H202" s="1">
+        <v>0</v>
+      </c>
+      <c r="I202" s="1">
+        <v>0</v>
+      </c>
+      <c r="J202" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A203" s="1">
+        <v>1436</v>
+      </c>
+      <c r="B203" s="4">
+        <v>2</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E203" s="1">
+        <v>0</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H203" s="1">
+        <v>0</v>
+      </c>
+      <c r="I203" s="1">
+        <v>0</v>
+      </c>
+      <c r="J203" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A204" s="1">
+        <v>1437</v>
+      </c>
+      <c r="B204" s="4">
+        <v>2</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E204" s="1">
+        <v>0</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H204" s="1">
+        <v>0</v>
+      </c>
+      <c r="I204" s="1">
+        <v>0</v>
+      </c>
+      <c r="J204" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A205" s="1">
+        <v>1438</v>
+      </c>
+      <c r="B205" s="4">
+        <v>2</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E205" s="1">
+        <v>0</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G205" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="H201" s="1">
-        <v>1434</v>
-      </c>
-      <c r="I201" s="1">
-        <v>0</v>
-      </c>
-      <c r="J201" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:10" ht="54" x14ac:dyDescent="0.15">
-      <c r="A202" s="1">
-        <v>1434</v>
-      </c>
-      <c r="B202" s="4">
-        <v>2</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E202" s="1">
-        <v>0</v>
-      </c>
-      <c r="F202" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H202" s="1">
-        <v>0</v>
-      </c>
-      <c r="I202" s="1">
-        <v>0</v>
-      </c>
-      <c r="J202" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A203" s="1">
-        <v>1435</v>
-      </c>
-      <c r="B203" s="4">
-        <v>2</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E203" s="1">
-        <v>0</v>
-      </c>
-      <c r="F203" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G203" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="H203" s="1">
-        <v>0</v>
-      </c>
-      <c r="I203" s="1">
-        <v>0</v>
-      </c>
-      <c r="J203" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A204" s="1">
-        <v>1436</v>
-      </c>
-      <c r="B204" s="4">
-        <v>2</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E204" s="1">
-        <v>0</v>
-      </c>
-      <c r="F204" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G204" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H204" s="1">
-        <v>0</v>
-      </c>
-      <c r="I204" s="1">
-        <v>0</v>
-      </c>
-      <c r="J204" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A205" s="1">
-        <v>1437</v>
-      </c>
-      <c r="B205" s="4">
-        <v>2</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E205" s="1">
-        <v>0</v>
-      </c>
-      <c r="F205" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G205" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -7530,22 +7543,22 @@
     </row>
     <row r="206" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B206" s="4">
         <v>2</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E206" s="1">
         <v>0</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
@@ -7559,22 +7572,22 @@
     </row>
     <row r="207" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B207" s="4">
         <v>2</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E207" s="1">
         <v>0</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>164</v>
+        <v>279</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -7588,22 +7601,22 @@
     </row>
     <row r="208" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B208" s="4">
         <v>2</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E208" s="1">
         <v>0</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -7617,22 +7630,22 @@
     </row>
     <row r="209" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B209" s="4">
         <v>2</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E209" s="1">
         <v>0</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
@@ -7644,24 +7657,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B210" s="4">
         <v>2</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E210" s="1">
         <v>0</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
@@ -7673,24 +7686,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B211" s="4">
         <v>2</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -7704,22 +7717,22 @@
     </row>
     <row r="212" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B212" s="4">
         <v>2</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E212" s="1">
         <v>0</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
@@ -7733,22 +7746,22 @@
     </row>
     <row r="213" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B213" s="4">
         <v>2</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E213" s="1">
         <v>0</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -7762,22 +7775,22 @@
     </row>
     <row r="214" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B214" s="4">
         <v>2</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E214" s="1">
         <v>0</v>
       </c>
       <c r="F214" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -7791,22 +7804,22 @@
     </row>
     <row r="215" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B215" s="4">
         <v>2</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E215" s="1">
         <v>0</v>
       </c>
       <c r="F215" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -7820,22 +7833,22 @@
     </row>
     <row r="216" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B216" s="4">
         <v>2</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E216" s="1">
         <v>0</v>
       </c>
       <c r="F216" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -7847,24 +7860,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B217" s="4">
         <v>2</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E217" s="1">
         <v>0</v>
       </c>
       <c r="F217" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>172</v>
+        <v>281</v>
       </c>
       <c r="H217" s="1">
         <v>0</v>
@@ -7878,22 +7891,22 @@
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B218" s="4">
         <v>2</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E218" s="1">
         <v>0</v>
       </c>
       <c r="F218" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>285</v>
+        <v>169</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
@@ -7907,22 +7920,22 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B219" s="4">
         <v>2</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E219" s="1">
         <v>0</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
@@ -7934,24 +7947,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B220" s="4">
         <v>2</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E220" s="1">
         <v>0</v>
       </c>
       <c r="F220" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H220" s="1">
         <v>0</v>
@@ -7963,24 +7976,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B221" s="4">
         <v>2</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E221" s="1">
         <v>0</v>
       </c>
       <c r="F221" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>175</v>
+        <v>282</v>
       </c>
       <c r="H221" s="1">
         <v>0</v>
@@ -7994,22 +8007,22 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B222" s="4">
         <v>2</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E222" s="1">
         <v>0</v>
       </c>
       <c r="F222" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -8021,24 +8034,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B223" s="4">
         <v>2</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E223" s="1">
         <v>0</v>
       </c>
       <c r="F223" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -8050,24 +8063,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B224" s="4">
         <v>2</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E224" s="1">
         <v>0</v>
       </c>
       <c r="F224" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="H224" s="1">
         <v>0</v>
@@ -8079,24 +8092,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B225" s="4">
         <v>2</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E225" s="1">
         <v>0</v>
       </c>
       <c r="F225" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>287</v>
+        <v>174</v>
       </c>
       <c r="H225" s="1">
         <v>0</v>
@@ -8108,24 +8121,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B226" s="4">
         <v>2</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E226" s="1">
         <v>0</v>
       </c>
       <c r="F226" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H226" s="1">
         <v>0</v>
@@ -8139,22 +8152,22 @@
     </row>
     <row r="227" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B227" s="4">
         <v>2</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E227" s="1">
         <v>0</v>
       </c>
       <c r="F227" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
@@ -8168,22 +8181,22 @@
     </row>
     <row r="228" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B228" s="4">
         <v>2</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E228" s="1">
         <v>0</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -8197,22 +8210,22 @@
     </row>
     <row r="229" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1461</v>
+        <v>1470</v>
       </c>
       <c r="B229" s="4">
         <v>2</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E229" s="1">
         <v>0</v>
       </c>
       <c r="F229" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -8226,138 +8239,138 @@
     </row>
     <row r="230" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B230" s="4">
         <v>2</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E230" s="1">
         <v>0</v>
       </c>
       <c r="F230" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G230" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="H230" s="1">
+        <v>0</v>
+      </c>
+      <c r="I230" s="1">
+        <v>0</v>
+      </c>
+      <c r="J230" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A231" s="1">
+        <v>1472</v>
+      </c>
+      <c r="B231" s="4">
+        <v>2</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E231" s="1">
+        <v>0</v>
+      </c>
+      <c r="F231" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H231" s="1">
+        <v>0</v>
+      </c>
+      <c r="I231" s="1">
+        <v>0</v>
+      </c>
+      <c r="J231" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A232" s="1">
+        <v>1473</v>
+      </c>
+      <c r="B232" s="4">
+        <v>2</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E232" s="1">
+        <v>0</v>
+      </c>
+      <c r="F232" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H232" s="1">
+        <v>0</v>
+      </c>
+      <c r="I232" s="1">
+        <v>0</v>
+      </c>
+      <c r="J232" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A233" s="1">
+        <v>1474</v>
+      </c>
+      <c r="B233" s="4">
+        <v>2</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E233" s="1">
+        <v>0</v>
+      </c>
+      <c r="F233" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G233" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H230" s="1">
-        <v>0</v>
-      </c>
-      <c r="I230" s="1">
-        <v>0</v>
-      </c>
-      <c r="J230" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A231" s="1">
-        <v>1471</v>
-      </c>
-      <c r="B231" s="4">
-        <v>2</v>
-      </c>
-      <c r="D231" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E231" s="1">
-        <v>0</v>
-      </c>
-      <c r="F231" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G231" s="1" t="s">
+      <c r="H233" s="1">
+        <v>0</v>
+      </c>
+      <c r="I233" s="1">
+        <v>0</v>
+      </c>
+      <c r="J233" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A234" s="1">
+        <v>1475</v>
+      </c>
+      <c r="B234" s="4">
+        <v>2</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E234" s="1">
+        <v>0</v>
+      </c>
+      <c r="F234" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G234" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="H231" s="1">
-        <v>0</v>
-      </c>
-      <c r="I231" s="1">
-        <v>0</v>
-      </c>
-      <c r="J231" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A232" s="1">
-        <v>1472</v>
-      </c>
-      <c r="B232" s="4">
-        <v>2</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E232" s="1">
-        <v>0</v>
-      </c>
-      <c r="F232" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H232" s="1">
-        <v>0</v>
-      </c>
-      <c r="I232" s="1">
-        <v>0</v>
-      </c>
-      <c r="J232" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A233" s="1">
-        <v>1473</v>
-      </c>
-      <c r="B233" s="4">
-        <v>2</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E233" s="1">
-        <v>0</v>
-      </c>
-      <c r="F233" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H233" s="1">
-        <v>0</v>
-      </c>
-      <c r="I233" s="1">
-        <v>0</v>
-      </c>
-      <c r="J233" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A234" s="1">
-        <v>1474</v>
-      </c>
-      <c r="B234" s="4">
-        <v>2</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E234" s="1">
-        <v>0</v>
-      </c>
-      <c r="F234" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
@@ -8371,22 +8384,22 @@
     </row>
     <row r="235" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B235" s="4">
         <v>2</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E235" s="1">
         <v>0</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -8400,22 +8413,22 @@
     </row>
     <row r="236" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B236" s="4">
         <v>2</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E236" s="1">
         <v>0</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -8429,22 +8442,22 @@
     </row>
     <row r="237" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B237" s="4">
         <v>2</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E237" s="1">
         <v>0</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -8458,22 +8471,22 @@
     </row>
     <row r="238" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B238" s="4">
         <v>2</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E238" s="1">
         <v>0</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -8485,24 +8498,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B239" s="4">
         <v>2</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E239" s="1">
         <v>0</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
@@ -8516,109 +8529,109 @@
     </row>
     <row r="240" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B240" s="4">
         <v>2</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E240" s="1">
         <v>0</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G240" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H240" s="1">
+        <v>0</v>
+      </c>
+      <c r="I240" s="1">
+        <v>0</v>
+      </c>
+      <c r="J240" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A241" s="1">
+        <v>1482</v>
+      </c>
+      <c r="B241" s="4">
+        <v>2</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E241" s="1">
+        <v>0</v>
+      </c>
+      <c r="F241" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="H241" s="1">
+        <v>0</v>
+      </c>
+      <c r="I241" s="1">
+        <v>0</v>
+      </c>
+      <c r="J241" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A242" s="1">
+        <v>1500</v>
+      </c>
+      <c r="B242" s="4">
+        <v>2</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E242" s="1">
+        <v>0</v>
+      </c>
+      <c r="F242" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H242" s="1">
+        <v>0</v>
+      </c>
+      <c r="I242" s="1">
+        <v>0</v>
+      </c>
+      <c r="J242" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A243" s="1">
+        <v>1501</v>
+      </c>
+      <c r="B243" s="4">
+        <v>2</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E243" s="1">
+        <v>0</v>
+      </c>
+      <c r="F243" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G243" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="H240" s="1">
-        <v>0</v>
-      </c>
-      <c r="I240" s="1">
-        <v>0</v>
-      </c>
-      <c r="J240" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A241" s="1">
-        <v>1481</v>
-      </c>
-      <c r="B241" s="4">
-        <v>2</v>
-      </c>
-      <c r="D241" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E241" s="1">
-        <v>0</v>
-      </c>
-      <c r="F241" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G241" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="H241" s="1">
-        <v>0</v>
-      </c>
-      <c r="I241" s="1">
-        <v>0</v>
-      </c>
-      <c r="J241" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A242" s="1">
-        <v>1482</v>
-      </c>
-      <c r="B242" s="4">
-        <v>2</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E242" s="1">
-        <v>0</v>
-      </c>
-      <c r="F242" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G242" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H242" s="1">
-        <v>0</v>
-      </c>
-      <c r="I242" s="1">
-        <v>0</v>
-      </c>
-      <c r="J242" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A243" s="1">
-        <v>1500</v>
-      </c>
-      <c r="B243" s="4">
-        <v>2</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E243" s="1">
-        <v>0</v>
-      </c>
-      <c r="F243" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="H243" s="1">
         <v>0</v>
@@ -8632,22 +8645,22 @@
     </row>
     <row r="244" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B244" s="4">
         <v>2</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E244" s="1">
         <v>0</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H244" s="1">
         <v>0</v>
@@ -8661,22 +8674,22 @@
     </row>
     <row r="245" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B245" s="4">
         <v>2</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E245" s="1">
         <v>0</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
@@ -8690,22 +8703,22 @@
     </row>
     <row r="246" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B246" s="4">
         <v>2</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E246" s="1">
         <v>0</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H246" s="1">
         <v>0</v>
@@ -8719,22 +8732,22 @@
     </row>
     <row r="247" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B247" s="4">
         <v>2</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E247" s="1">
         <v>0</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -8748,22 +8761,22 @@
     </row>
     <row r="248" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B248" s="4">
         <v>2</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E248" s="1">
         <v>0</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -8777,22 +8790,22 @@
     </row>
     <row r="249" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B249" s="4">
         <v>2</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E249" s="1">
         <v>0</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
@@ -8804,24 +8817,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B250" s="4">
         <v>2</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E250" s="1">
         <v>0</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
@@ -8833,24 +8846,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B251" s="4">
         <v>2</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E251" s="1">
         <v>0</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H251" s="1">
         <v>0</v>
@@ -8862,24 +8875,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B252" s="4">
         <v>2</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E252" s="1">
         <v>0</v>
       </c>
       <c r="F252" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>204</v>
+        <v>284</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
@@ -8893,22 +8906,22 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B253" s="4">
         <v>2</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E253" s="1">
         <v>0</v>
       </c>
       <c r="F253" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="H253" s="1">
         <v>0</v>
@@ -8922,22 +8935,22 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B254" s="4">
         <v>2</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E254" s="1">
         <v>0</v>
       </c>
       <c r="F254" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
@@ -8951,22 +8964,22 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B255" s="4">
         <v>2</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E255" s="1">
         <v>0</v>
       </c>
       <c r="F255" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H255" s="1">
         <v>0</v>
@@ -8980,22 +8993,22 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B256" s="4">
         <v>2</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E256" s="1">
         <v>0</v>
       </c>
       <c r="F256" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H256" s="1">
         <v>0</v>
@@ -9009,22 +9022,22 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B257" s="4">
         <v>2</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E257" s="1">
         <v>0</v>
       </c>
       <c r="F257" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H257" s="1">
         <v>0</v>
@@ -9036,24 +9049,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B258" s="4">
         <v>2</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E258" s="1">
         <v>0</v>
       </c>
       <c r="F258" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H258" s="1">
         <v>0</v>
@@ -9065,24 +9078,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B259" s="4">
         <v>2</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E259" s="1">
         <v>0</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
@@ -9096,22 +9109,22 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B260" s="4">
         <v>2</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E260" s="1">
         <v>0</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H260" s="1">
         <v>0</v>
@@ -9125,22 +9138,22 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B261" s="4">
         <v>2</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E261" s="1">
         <v>0</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>295</v>
+        <v>202</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -9152,24 +9165,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>1519</v>
+        <v>1600</v>
       </c>
       <c r="B262" s="4">
         <v>2</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E262" s="1">
         <v>0</v>
       </c>
       <c r="F262" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H262" s="1">
         <v>0</v>
@@ -9181,24 +9194,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>1600</v>
+        <v>2001</v>
       </c>
       <c r="B263" s="4">
         <v>2</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E263" s="1">
         <v>0</v>
       </c>
       <c r="F263" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="H263" s="1">
         <v>0</v>
@@ -9212,22 +9225,22 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B264" s="4">
         <v>2</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E264" s="1">
         <v>0</v>
       </c>
       <c r="F264" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>296</v>
+        <v>204</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
@@ -9241,22 +9254,22 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B265" s="4">
         <v>2</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E265" s="1">
         <v>0</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
       <c r="H265" s="1">
         <v>0</v>
@@ -9270,22 +9283,22 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B266" s="4">
         <v>2</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E266" s="1">
         <v>0</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H266" s="1">
         <v>0</v>
@@ -9299,22 +9312,22 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B267" s="4">
         <v>2</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E267" s="1">
         <v>0</v>
       </c>
       <c r="F267" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H267" s="1">
         <v>0</v>
@@ -9328,22 +9341,22 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B268" s="4">
         <v>2</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E268" s="1">
         <v>0</v>
       </c>
       <c r="F268" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H268" s="1">
         <v>0</v>
@@ -9355,24 +9368,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B269" s="4">
         <v>2</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E269" s="1">
         <v>0</v>
       </c>
       <c r="F269" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H269" s="1">
         <v>0</v>
@@ -9384,24 +9397,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B270" s="4">
         <v>2</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E270" s="1">
         <v>0</v>
       </c>
       <c r="F270" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H270" s="1">
         <v>0</v>
@@ -9415,22 +9428,22 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B271" s="4">
         <v>2</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E271" s="1">
         <v>0</v>
       </c>
       <c r="F271" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H271" s="1">
         <v>0</v>
@@ -9444,22 +9457,22 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B272" s="4">
         <v>2</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E272" s="1">
         <v>0</v>
       </c>
       <c r="F272" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H272" s="1">
         <v>0</v>
@@ -9473,22 +9486,22 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B273" s="4">
         <v>2</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E273" s="1">
         <v>0</v>
       </c>
       <c r="F273" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>304</v>
+        <v>205</v>
       </c>
       <c r="H273" s="1">
         <v>0</v>
@@ -9502,22 +9515,22 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B274" s="4">
         <v>2</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E274" s="1">
         <v>0</v>
       </c>
       <c r="F274" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H274" s="1">
         <v>0</v>
@@ -9531,22 +9544,22 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B275" s="4">
         <v>2</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E275" s="1">
         <v>0</v>
       </c>
       <c r="F275" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H275" s="1">
         <v>0</v>
@@ -9560,22 +9573,22 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B276" s="4">
         <v>2</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E276" s="1">
         <v>0</v>
       </c>
       <c r="F276" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
@@ -9587,24 +9600,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B277" s="4">
         <v>2</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E277" s="1">
         <v>0</v>
       </c>
       <c r="F277" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H277" s="1">
         <v>0</v>
@@ -9616,24 +9629,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B278" s="4">
         <v>2</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E278" s="1">
         <v>0</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>213</v>
+        <v>301</v>
       </c>
       <c r="H278" s="1">
         <v>0</v>
@@ -9647,22 +9660,22 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B279" s="4">
         <v>2</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E279" s="1">
         <v>0</v>
       </c>
       <c r="F279" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>305</v>
+        <v>210</v>
       </c>
       <c r="H279" s="1">
         <v>0</v>
@@ -9676,22 +9689,22 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B280" s="4">
         <v>2</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E280" s="1">
         <v>0</v>
       </c>
       <c r="F280" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H280" s="1">
         <v>0</v>
@@ -9703,24 +9716,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B281" s="4">
         <v>2</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E281" s="1">
         <v>0</v>
       </c>
       <c r="F281" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="H281" s="1">
         <v>0</v>
@@ -9734,22 +9747,22 @@
     </row>
     <row r="282" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B282" s="4">
         <v>2</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E282" s="1">
         <v>0</v>
       </c>
       <c r="F282" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>306</v>
+        <v>212</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
@@ -9763,22 +9776,22 @@
     </row>
     <row r="283" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B283" s="4">
         <v>2</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E283" s="1">
         <v>0</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H283" s="1">
         <v>0</v>
@@ -9792,22 +9805,22 @@
     </row>
     <row r="284" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B284" s="4">
         <v>2</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E284" s="1">
         <v>0</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H284" s="1">
         <v>0</v>
@@ -9821,22 +9834,22 @@
     </row>
     <row r="285" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B285" s="4">
         <v>2</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E285" s="1">
         <v>0</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
@@ -9850,22 +9863,22 @@
     </row>
     <row r="286" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B286" s="4">
         <v>2</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E286" s="1">
         <v>0</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H286" s="1">
         <v>0</v>
@@ -9879,25 +9892,28 @@
     </row>
     <row r="287" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B287" s="4">
         <v>2</v>
       </c>
+      <c r="C287" s="1" t="s">
+        <v>303</v>
+      </c>
       <c r="D287" s="1" t="s">
-        <v>233</v>
+        <v>313</v>
       </c>
       <c r="E287" s="1">
         <v>0</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H287" s="1">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="I287" s="1">
         <v>0</v>
@@ -9908,28 +9924,28 @@
     </row>
     <row r="288" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B288" s="4">
         <v>2</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E288" s="1">
         <v>0</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>221</v>
+        <v>305</v>
       </c>
       <c r="H288" s="1">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="I288" s="1">
         <v>0</v>
@@ -9940,60 +9956,60 @@
     </row>
     <row r="289" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B289" s="4">
         <v>2</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>308</v>
+        <v>10</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>316</v>
+        <v>230</v>
       </c>
       <c r="E289" s="1">
         <v>0</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G289" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H289" s="1">
+        <v>1512</v>
+      </c>
+      <c r="I289" s="1">
+        <v>0</v>
+      </c>
+      <c r="J289" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A290" s="1">
+        <v>2028</v>
+      </c>
+      <c r="B290" s="4">
+        <v>2</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E290" s="1">
+        <v>0</v>
+      </c>
+      <c r="F290" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="H289" s="1">
-        <v>0</v>
-      </c>
-      <c r="I289" s="1">
-        <v>0</v>
-      </c>
-      <c r="J289" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A290" s="1">
-        <v>2027</v>
-      </c>
-      <c r="B290" s="4">
-        <v>2</v>
-      </c>
-      <c r="C290" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E290" s="1">
-        <v>0</v>
-      </c>
-      <c r="F290" s="4" t="s">
-        <v>313</v>
-      </c>
       <c r="G290" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H290" s="1">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="I290" s="1">
         <v>0</v>
@@ -10002,30 +10018,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B291" s="4">
         <v>2</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="E291" s="1">
         <v>0</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H291" s="1">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="I291" s="1">
         <v>0</v>
@@ -10036,28 +10052,28 @@
     </row>
     <row r="292" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B292" s="4">
         <v>2</v>
       </c>
       <c r="C292" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E292" s="1">
+        <v>0</v>
+      </c>
+      <c r="F292" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D292" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E292" s="1">
-        <v>0</v>
-      </c>
-      <c r="F292" s="4" t="s">
-        <v>313</v>
-      </c>
       <c r="G292" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H292" s="1">
-        <v>1514</v>
+        <v>0</v>
       </c>
       <c r="I292" s="1">
         <v>0</v>
@@ -10068,7 +10084,7 @@
     </row>
     <row r="293" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B293" s="4">
         <v>2</v>
@@ -10077,16 +10093,16 @@
         <v>10</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E293" s="1">
         <v>0</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H293" s="1">
         <v>0</v>
@@ -10100,28 +10116,28 @@
     </row>
     <row r="294" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B294" s="4">
         <v>2</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>10</v>
+        <v>304</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="E294" s="1">
         <v>0</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H294" s="1">
-        <v>0</v>
+        <v>1517</v>
       </c>
       <c r="I294" s="1">
         <v>0</v>
@@ -10132,28 +10148,28 @@
     </row>
     <row r="295" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B295" s="4">
         <v>2</v>
       </c>
       <c r="C295" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E295" s="1">
+        <v>0</v>
+      </c>
+      <c r="F295" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D295" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E295" s="1">
-        <v>0</v>
-      </c>
-      <c r="F295" s="4" t="s">
-        <v>313</v>
-      </c>
       <c r="G295" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H295" s="1">
-        <v>1517</v>
+        <v>0</v>
       </c>
       <c r="I295" s="1">
         <v>0</v>
@@ -10164,119 +10180,116 @@
     </row>
     <row r="296" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B296" s="4">
         <v>2</v>
       </c>
       <c r="C296" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E296" s="1">
+        <v>0</v>
+      </c>
+      <c r="F296" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H296" s="1">
+        <v>1519</v>
+      </c>
+      <c r="I296" s="1">
+        <v>0</v>
+      </c>
+      <c r="J296" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A297" s="1">
+        <v>2100</v>
+      </c>
+      <c r="B297" s="4">
+        <v>2</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E297" s="1">
+        <v>0</v>
+      </c>
+      <c r="F297" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H297" s="1">
+        <v>0</v>
+      </c>
+      <c r="I297" s="1">
+        <v>0</v>
+      </c>
+      <c r="J297" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A298" s="1">
+        <v>2101</v>
+      </c>
+      <c r="B298" s="4">
+        <v>2</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E298" s="1">
+        <v>0</v>
+      </c>
+      <c r="F298" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H298" s="1">
+        <v>0</v>
+      </c>
+      <c r="I298" s="1">
+        <v>0</v>
+      </c>
+      <c r="J298" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A299" s="1">
+        <v>8888</v>
+      </c>
+      <c r="B299" s="4">
+        <v>2</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E299" s="1">
+        <v>0</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G299" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D296" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E296" s="1">
-        <v>0</v>
-      </c>
-      <c r="F296" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="H296" s="1">
-        <v>0</v>
-      </c>
-      <c r="I296" s="1">
-        <v>0</v>
-      </c>
-      <c r="J296" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A297" s="1">
-        <v>2034</v>
-      </c>
-      <c r="B297" s="4">
-        <v>2</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E297" s="1">
-        <v>0</v>
-      </c>
-      <c r="F297" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H297" s="1">
-        <v>1519</v>
-      </c>
-      <c r="I297" s="1">
-        <v>0</v>
-      </c>
-      <c r="J297" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A298" s="1">
-        <v>2100</v>
-      </c>
-      <c r="B298" s="4">
-        <v>2</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E298" s="1">
-        <v>0</v>
-      </c>
-      <c r="F298" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="H298" s="1">
-        <v>0</v>
-      </c>
-      <c r="I298" s="1">
-        <v>0</v>
-      </c>
-      <c r="J298" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A299" s="1">
-        <v>2101</v>
-      </c>
-      <c r="B299" s="4">
-        <v>2</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E299" s="1">
-        <v>0</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="G299" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="H299" s="1">
         <v>0</v>
       </c>
@@ -10287,24 +10300,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>8888</v>
+        <v>3000</v>
       </c>
       <c r="B300" s="4">
         <v>2</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E300" s="1">
         <v>0</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>312</v>
+        <v>227</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="H300" s="1">
         <v>0</v>
@@ -10316,24 +10329,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="B301" s="4">
         <v>2</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E301" s="1">
         <v>0</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H301" s="1">
         <v>0</v>
@@ -10345,24 +10358,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="B302" s="4">
         <v>2</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E302" s="1">
         <v>0</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H302" s="1">
         <v>0</v>
@@ -10376,109 +10389,109 @@
     </row>
     <row r="303" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="B303" s="4">
         <v>2</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E303" s="1">
         <v>0</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G303" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H303" s="1">
+        <v>0</v>
+      </c>
+      <c r="I303" s="1">
+        <v>0</v>
+      </c>
+      <c r="J303" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A304" s="1">
+        <v>3004</v>
+      </c>
+      <c r="B304" s="4">
+        <v>2</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E304" s="1">
+        <v>0</v>
+      </c>
+      <c r="F304" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G304" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H304" s="1">
+        <v>0</v>
+      </c>
+      <c r="I304" s="1">
+        <v>0</v>
+      </c>
+      <c r="J304" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A305" s="1">
+        <v>3005</v>
+      </c>
+      <c r="B305" s="4">
+        <v>2</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E305" s="1">
+        <v>0</v>
+      </c>
+      <c r="F305" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G305" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="H305" s="1">
+        <v>0</v>
+      </c>
+      <c r="I305" s="1">
+        <v>0</v>
+      </c>
+      <c r="J305" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A306" s="1">
+        <v>3006</v>
+      </c>
+      <c r="B306" s="4">
+        <v>2</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="H303" s="1">
-        <v>0</v>
-      </c>
-      <c r="I303" s="1">
-        <v>0</v>
-      </c>
-      <c r="J303" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A304" s="1">
-        <v>3003</v>
-      </c>
-      <c r="B304" s="4">
-        <v>2</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E304" s="1">
-        <v>0</v>
-      </c>
-      <c r="F304" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G304" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="H304" s="1">
-        <v>0</v>
-      </c>
-      <c r="I304" s="1">
-        <v>0</v>
-      </c>
-      <c r="J304" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A305" s="1">
-        <v>3004</v>
-      </c>
-      <c r="B305" s="4">
-        <v>2</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E305" s="1">
-        <v>0</v>
-      </c>
-      <c r="F305" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G305" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="H305" s="1">
-        <v>0</v>
-      </c>
-      <c r="I305" s="1">
-        <v>0</v>
-      </c>
-      <c r="J305" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A306" s="1">
-        <v>3005</v>
-      </c>
-      <c r="B306" s="4">
-        <v>2</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="E306" s="1">
         <v>0</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -10492,168 +10505,168 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="B307" s="4">
         <v>2</v>
       </c>
       <c r="D307" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E307" s="1">
+        <v>0</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="G307" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H307" s="1">
+        <v>0</v>
+      </c>
+      <c r="I307" s="1">
+        <v>0</v>
+      </c>
+      <c r="J307" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A308" s="1">
+        <v>3008</v>
+      </c>
+      <c r="B308" s="4">
+        <v>2</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E308" s="1">
+        <v>0</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G308" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E307" s="1">
-        <v>0</v>
-      </c>
-      <c r="F307" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G307" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="H307" s="1">
-        <v>0</v>
-      </c>
-      <c r="I307" s="1">
-        <v>0</v>
-      </c>
-      <c r="J307" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A308" s="1">
-        <v>3007</v>
-      </c>
-      <c r="B308" s="4">
-        <v>2</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E308" s="1">
-        <v>0</v>
-      </c>
-      <c r="F308" s="4" t="s">
+      <c r="H308" s="1">
+        <v>0</v>
+      </c>
+      <c r="I308" s="1">
+        <v>0</v>
+      </c>
+      <c r="J308" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A309" s="1">
+        <v>3010</v>
+      </c>
+      <c r="B309" s="4">
+        <v>2</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E309" s="1">
+        <v>0</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G309" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H309" s="1">
+        <v>0</v>
+      </c>
+      <c r="I309" s="1">
+        <v>0</v>
+      </c>
+      <c r="J309" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A310" s="1">
+        <v>3011</v>
+      </c>
+      <c r="B310" s="4">
+        <v>2</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E310" s="1">
+        <v>0</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G310" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="G308" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="H308" s="1">
-        <v>0</v>
-      </c>
-      <c r="I308" s="1">
-        <v>0</v>
-      </c>
-      <c r="J308" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A309" s="1">
-        <v>3008</v>
-      </c>
-      <c r="B309" s="4">
-        <v>2</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E309" s="1">
-        <v>0</v>
-      </c>
-      <c r="F309" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G309" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="H309" s="1">
-        <v>0</v>
-      </c>
-      <c r="I309" s="1">
-        <v>0</v>
-      </c>
-      <c r="J309" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A310" s="1">
-        <v>3010</v>
-      </c>
-      <c r="B310" s="4">
-        <v>2</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E310" s="1">
-        <v>0</v>
-      </c>
-      <c r="F310" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G310" s="1" t="s">
+      <c r="H310" s="1">
+        <v>0</v>
+      </c>
+      <c r="I310" s="1">
+        <v>0</v>
+      </c>
+      <c r="J310" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A311" s="1">
+        <v>3012</v>
+      </c>
+      <c r="B311" s="4">
+        <v>2</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E311" s="1">
+        <v>0</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="H311" s="1">
+        <v>0</v>
+      </c>
+      <c r="I311" s="1">
+        <v>0</v>
+      </c>
+      <c r="J311" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A312" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E312" s="1">
+        <v>0</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G312" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="H310" s="1">
-        <v>0</v>
-      </c>
-      <c r="I310" s="1">
-        <v>0</v>
-      </c>
-      <c r="J310" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A311" s="1">
-        <v>3011</v>
-      </c>
-      <c r="B311" s="4">
-        <v>2</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E311" s="1">
-        <v>0</v>
-      </c>
-      <c r="F311" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G311" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H311" s="1">
-        <v>0</v>
-      </c>
-      <c r="I311" s="1">
-        <v>0</v>
-      </c>
-      <c r="J311" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A312" s="1">
-        <v>3012</v>
-      </c>
-      <c r="B312" s="4">
-        <v>2</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E312" s="1">
-        <v>0</v>
-      </c>
-      <c r="F312" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G312" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="H312" s="1">
         <v>0</v>
       </c>
@@ -10661,27 +10674,27 @@
         <v>0</v>
       </c>
       <c r="J312" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>332</v>
+        <v>229</v>
       </c>
       <c r="E313" s="1">
         <v>0</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>342</v>
+        <v>67</v>
       </c>
       <c r="H313" s="1">
         <v>0</v>
@@ -10693,24 +10706,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E314" s="1">
         <v>0</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>70</v>
+        <v>336</v>
       </c>
       <c r="H314" s="1">
         <v>0</v>
@@ -10722,24 +10735,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E315" s="1">
         <v>0</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="H315" s="1">
         <v>0</v>
@@ -10751,32 +10764,148 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>4004</v>
+        <v>4011</v>
       </c>
       <c r="B316" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E316" s="1">
+        <v>0</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G316" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="H316" s="1">
+        <v>0</v>
+      </c>
+      <c r="I316" s="1">
+        <v>0</v>
+      </c>
+      <c r="J316" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A317" s="1">
+        <v>4012</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E317" s="1">
+        <v>0</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G317" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D316" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E316" s="1">
-        <v>0</v>
-      </c>
-      <c r="F316" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G316" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="H316" s="1">
-        <v>0</v>
-      </c>
-      <c r="I316" s="1">
-        <v>0</v>
-      </c>
-      <c r="J316" s="1" t="b">
+      <c r="H317" s="1">
+        <v>0</v>
+      </c>
+      <c r="I317" s="1">
+        <v>0</v>
+      </c>
+      <c r="J317" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A318" s="1">
+        <v>4013</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E318" s="1">
+        <v>0</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G318" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H318" s="1">
+        <v>0</v>
+      </c>
+      <c r="I318" s="1">
+        <v>0</v>
+      </c>
+      <c r="J318" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A319" s="1">
+        <v>4014</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E319" s="1">
+        <v>0</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H319" s="1">
+        <v>0</v>
+      </c>
+      <c r="I319" s="1">
+        <v>0</v>
+      </c>
+      <c r="J319" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A320" s="1">
+        <v>4015</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E320" s="1">
+        <v>0</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G320" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H320" s="1">
+        <v>0</v>
+      </c>
+      <c r="I320" s="1">
+        <v>0</v>
+      </c>
+      <c r="J320" s="1" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="357">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1133,6 +1133,10 @@
   </si>
   <si>
     <t>我来逛逛你的商店,\n今天有什么好东西呀？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有买到想要的东西，我有点不开心。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1500,7 +1504,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J320"/>
+  <dimension ref="A2:J321"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -10909,6 +10913,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="321" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A321" s="1">
+        <v>5001</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E321" s="1">
+        <v>0</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G321" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H321" s="1">
+        <v>0</v>
+      </c>
+      <c r="I321" s="1">
+        <v>0</v>
+      </c>
+      <c r="J321" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:B3">
     <sortState ref="A4:B90">

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="345">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1103,6 +1103,14 @@
   </si>
   <si>
     <t>谢谢你的礼物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我缺少建造材料，我得先收集一些才行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>太好了,这下可以饲养动物了！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1470,7 +1478,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J307"/>
+  <dimension ref="A2:J309"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -9981,12 +9989,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>4001</v>
-      </c>
-      <c r="B290" s="4" t="s">
-        <v>319</v>
+        <v>3013</v>
+      </c>
+      <c r="B290" s="4">
+        <v>2</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>306</v>
@@ -9998,7 +10006,7 @@
         <v>205</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -10007,18 +10015,18 @@
         <v>0</v>
       </c>
       <c r="J290" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>4002</v>
-      </c>
-      <c r="B291" s="4" t="s">
-        <v>320</v>
+        <v>3014</v>
+      </c>
+      <c r="B291" s="4">
+        <v>2</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="E291" s="1">
         <v>0</v>
@@ -10027,7 +10035,7 @@
         <v>205</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>45</v>
+        <v>344</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -10036,18 +10044,18 @@
         <v>0</v>
       </c>
       <c r="J291" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:10" ht="54" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="E292" s="1">
         <v>0</v>
@@ -10056,7 +10064,7 @@
         <v>205</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H292" s="1">
         <v>0</v>
@@ -10068,12 +10076,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>207</v>
@@ -10085,7 +10093,7 @@
         <v>205</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="H293" s="1">
         <v>0</v>
@@ -10097,12 +10105,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>4011</v>
+        <v>4003</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>207</v>
@@ -10114,7 +10122,7 @@
         <v>205</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H294" s="1">
         <v>0</v>
@@ -10126,12 +10134,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>4012</v>
+        <v>4004</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>207</v>
@@ -10143,7 +10151,7 @@
         <v>205</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="H295" s="1">
         <v>0</v>
@@ -10155,9 +10163,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="B296" s="4" t="s">
         <v>323</v>
@@ -10172,7 +10180,7 @@
         <v>205</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -10186,7 +10194,7 @@
     </row>
     <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="B297" s="4" t="s">
         <v>323</v>
@@ -10201,7 +10209,7 @@
         <v>205</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -10215,7 +10223,7 @@
     </row>
     <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="B298" s="4" t="s">
         <v>323</v>
@@ -10230,7 +10238,7 @@
         <v>205</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H298" s="1">
         <v>0</v>
@@ -10244,65 +10252,65 @@
     </row>
     <row r="299" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
+        <v>4014</v>
+      </c>
+      <c r="B299" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E299" s="1">
+        <v>0</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G299" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H299" s="1">
+        <v>0</v>
+      </c>
+      <c r="I299" s="1">
+        <v>0</v>
+      </c>
+      <c r="J299" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A300" s="1">
+        <v>4015</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E300" s="1">
+        <v>0</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G300" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H300" s="1">
+        <v>0</v>
+      </c>
+      <c r="I300" s="1">
+        <v>0</v>
+      </c>
+      <c r="J300" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A301" s="1">
         <v>5001</v>
-      </c>
-      <c r="B299" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E299" s="1">
-        <v>0</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G299" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="H299" s="1">
-        <v>0</v>
-      </c>
-      <c r="I299" s="1">
-        <v>0</v>
-      </c>
-      <c r="J299" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A300" s="1">
-        <v>6000</v>
-      </c>
-      <c r="B300" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E300" s="1">
-        <v>0</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G300" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="H300" s="1">
-        <v>0</v>
-      </c>
-      <c r="I300" s="1">
-        <v>0</v>
-      </c>
-      <c r="J300" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A301" s="1">
-        <v>6001</v>
       </c>
       <c r="B301" s="4" t="s">
         <v>319</v>
@@ -10317,7 +10325,7 @@
         <v>205</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H301" s="1">
         <v>0</v>
@@ -10331,7 +10339,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>6002</v>
+        <v>6000</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>319</v>
@@ -10346,7 +10354,7 @@
         <v>205</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H302" s="1">
         <v>0</v>
@@ -10360,7 +10368,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="B303" s="4" t="s">
         <v>319</v>
@@ -10375,7 +10383,7 @@
         <v>205</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H303" s="1">
         <v>0</v>
@@ -10389,7 +10397,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="B304" s="4" t="s">
         <v>319</v>
@@ -10404,7 +10412,7 @@
         <v>205</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -10418,7 +10426,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="B305" s="4" t="s">
         <v>319</v>
@@ -10433,7 +10441,7 @@
         <v>205</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
@@ -10447,7 +10455,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="B306" s="4" t="s">
         <v>319</v>
@@ -10462,7 +10470,7 @@
         <v>205</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -10476,7 +10484,7 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>6100</v>
+        <v>6005</v>
       </c>
       <c r="B307" s="4" t="s">
         <v>319</v>
@@ -10491,15 +10499,73 @@
         <v>205</v>
       </c>
       <c r="G307" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H307" s="1">
+        <v>0</v>
+      </c>
+      <c r="I307" s="1">
+        <v>0</v>
+      </c>
+      <c r="J307" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A308" s="1">
+        <v>6006</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E308" s="1">
+        <v>0</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G308" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H308" s="1">
+        <v>0</v>
+      </c>
+      <c r="I308" s="1">
+        <v>0</v>
+      </c>
+      <c r="J308" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A309" s="1">
+        <v>6100</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E309" s="1">
+        <v>0</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G309" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H307" s="1">
-        <v>0</v>
-      </c>
-      <c r="I307" s="1">
-        <v>0</v>
-      </c>
-      <c r="J307" s="1" t="b">
+      <c r="H309" s="1">
+        <v>0</v>
+      </c>
+      <c r="I309" s="1">
+        <v>0</v>
+      </c>
+      <c r="J309" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -21,8 +21,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>flyer</author>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve"> Player = 1, Fixed = 2, Dynamic = 3</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="351">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1111,6 +1145,30 @@
   </si>
   <si>
     <t>太好了,这下可以饲养动物了！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔总是想着去冒险，我还是希望他能在小镇安稳的生活。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你好啊，平静的生活就是最大的幸福，你觉得的呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我很喜欢和动物们相处，它们既单纯又可爱。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相比温顺的动物，我更喜欢能和我一起战斗的伙伴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你如果要去冒险的话，一定要带上我呀。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有的人天生就是主角，你看我像不像，哈哈</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1118,7 +1176,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1133,6 +1191,19 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1476,13 +1547,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J309"/>
+  <dimension ref="A2:J318"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="4" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
@@ -10308,9 +10379,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>5001</v>
+        <v>4016</v>
       </c>
       <c r="B301" s="4" t="s">
         <v>319</v>
@@ -10324,8 +10395,8 @@
       <c r="F301" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="G301" s="1" t="s">
-        <v>334</v>
+      <c r="G301" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H301" s="1">
         <v>0</v>
@@ -10334,12 +10405,12 @@
         <v>0</v>
       </c>
       <c r="J301" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>6000</v>
+        <v>4017</v>
       </c>
       <c r="B302" s="4" t="s">
         <v>319</v>
@@ -10354,7 +10425,7 @@
         <v>205</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="H302" s="1">
         <v>0</v>
@@ -10363,12 +10434,12 @@
         <v>0</v>
       </c>
       <c r="J302" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>6001</v>
+        <v>4018</v>
       </c>
       <c r="B303" s="4" t="s">
         <v>319</v>
@@ -10383,7 +10454,7 @@
         <v>205</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="H303" s="1">
         <v>0</v>
@@ -10392,12 +10463,12 @@
         <v>0</v>
       </c>
       <c r="J303" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>6002</v>
+        <v>4019</v>
       </c>
       <c r="B304" s="4" t="s">
         <v>319</v>
@@ -10412,7 +10483,7 @@
         <v>205</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -10421,12 +10492,12 @@
         <v>0</v>
       </c>
       <c r="J304" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>6003</v>
+        <v>4020</v>
       </c>
       <c r="B305" s="4" t="s">
         <v>319</v>
@@ -10441,7 +10512,7 @@
         <v>205</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>338</v>
+        <v>243</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
@@ -10450,12 +10521,12 @@
         <v>0</v>
       </c>
       <c r="J305" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>6004</v>
+        <v>4021</v>
       </c>
       <c r="B306" s="4" t="s">
         <v>319</v>
@@ -10470,7 +10541,7 @@
         <v>205</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>339</v>
+        <v>46</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -10479,12 +10550,12 @@
         <v>0</v>
       </c>
       <c r="J306" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>6005</v>
+        <v>4022</v>
       </c>
       <c r="B307" s="4" t="s">
         <v>319</v>
@@ -10499,7 +10570,7 @@
         <v>205</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="H307" s="1">
         <v>0</v>
@@ -10508,12 +10579,12 @@
         <v>0</v>
       </c>
       <c r="J307" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>6006</v>
+        <v>4023</v>
       </c>
       <c r="B308" s="4" t="s">
         <v>319</v>
@@ -10528,7 +10599,7 @@
         <v>205</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="H308" s="1">
         <v>0</v>
@@ -10537,12 +10608,12 @@
         <v>0</v>
       </c>
       <c r="J308" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>6100</v>
+        <v>4024</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>319</v>
@@ -10557,15 +10628,276 @@
         <v>205</v>
       </c>
       <c r="G309" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H309" s="1">
+        <v>0</v>
+      </c>
+      <c r="I309" s="1">
+        <v>0</v>
+      </c>
+      <c r="J309" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A310" s="1">
+        <v>5001</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E310" s="1">
+        <v>0</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G310" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H310" s="1">
+        <v>0</v>
+      </c>
+      <c r="I310" s="1">
+        <v>0</v>
+      </c>
+      <c r="J310" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A311" s="1">
+        <v>6000</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E311" s="1">
+        <v>0</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G311" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="H311" s="1">
+        <v>0</v>
+      </c>
+      <c r="I311" s="1">
+        <v>0</v>
+      </c>
+      <c r="J311" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A312" s="1">
+        <v>6001</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E312" s="1">
+        <v>0</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G312" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H312" s="1">
+        <v>0</v>
+      </c>
+      <c r="I312" s="1">
+        <v>0</v>
+      </c>
+      <c r="J312" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A313" s="1">
+        <v>6002</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E313" s="1">
+        <v>0</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G313" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H313" s="1">
+        <v>0</v>
+      </c>
+      <c r="I313" s="1">
+        <v>0</v>
+      </c>
+      <c r="J313" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A314" s="1">
+        <v>6003</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E314" s="1">
+        <v>0</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G314" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H314" s="1">
+        <v>0</v>
+      </c>
+      <c r="I314" s="1">
+        <v>0</v>
+      </c>
+      <c r="J314" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A315" s="1">
+        <v>6004</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E315" s="1">
+        <v>0</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G315" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H315" s="1">
+        <v>0</v>
+      </c>
+      <c r="I315" s="1">
+        <v>0</v>
+      </c>
+      <c r="J315" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A316" s="1">
+        <v>6005</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E316" s="1">
+        <v>0</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G316" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H316" s="1">
+        <v>0</v>
+      </c>
+      <c r="I316" s="1">
+        <v>0</v>
+      </c>
+      <c r="J316" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A317" s="1">
+        <v>6006</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E317" s="1">
+        <v>0</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G317" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H317" s="1">
+        <v>0</v>
+      </c>
+      <c r="I317" s="1">
+        <v>0</v>
+      </c>
+      <c r="J317" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A318" s="1">
+        <v>6100</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E318" s="1">
+        <v>0</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G318" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H309" s="1">
-        <v>0</v>
-      </c>
-      <c r="I309" s="1">
-        <v>0</v>
-      </c>
-      <c r="J309" s="1" t="b">
+      <c r="H318" s="1">
+        <v>0</v>
+      </c>
+      <c r="I318" s="1">
+        <v>0</v>
+      </c>
+      <c r="J318" s="1" t="b">
         <v>0</v>
       </c>
     </row>
@@ -10578,5 +10910,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="353">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1169,6 +1169,14 @@
   </si>
   <si>
     <t>有的人天生就是主角，你看我像不像，哈哈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咯咯..咯咯..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1549,7 +1557,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J318"/>
+  <dimension ref="A2:J319"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -10901,6 +10909,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A319" s="1">
+        <v>8100</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E319" s="1">
+        <v>0</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H319" s="1">
+        <v>0</v>
+      </c>
+      <c r="I319" s="1">
+        <v>0</v>
+      </c>
+      <c r="J319" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A3:B3">
     <sortState ref="A4:B90">

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="355">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1177,6 +1177,14 @@
   </si>
   <si>
     <t>咯咯..咯咯..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我没有鱼竿，没法钓鱼！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我缺少鱼饵，不能钓鱼！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1557,7 +1565,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J319"/>
+  <dimension ref="A2:J321"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -10128,10 +10136,10 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>4001</v>
-      </c>
-      <c r="B292" s="4" t="s">
-        <v>319</v>
+        <v>3200</v>
+      </c>
+      <c r="B292" s="4">
+        <v>2</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>306</v>
@@ -10143,65 +10151,65 @@
         <v>205</v>
       </c>
       <c r="G292" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H292" s="1">
+        <v>0</v>
+      </c>
+      <c r="I292" s="1">
+        <v>0</v>
+      </c>
+      <c r="J292" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A293" s="1">
+        <v>3201</v>
+      </c>
+      <c r="B293" s="4">
+        <v>2</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E293" s="1">
+        <v>0</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H293" s="1">
+        <v>0</v>
+      </c>
+      <c r="I293" s="1">
+        <v>0</v>
+      </c>
+      <c r="J293" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A294" s="1">
+        <v>4001</v>
+      </c>
+      <c r="B294" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="E294" s="1">
+        <v>0</v>
+      </c>
+      <c r="F294" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G294" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="H292" s="1">
-        <v>0</v>
-      </c>
-      <c r="I292" s="1">
-        <v>0</v>
-      </c>
-      <c r="J292" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A293" s="1">
-        <v>4002</v>
-      </c>
-      <c r="B293" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E293" s="1">
-        <v>0</v>
-      </c>
-      <c r="F293" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G293" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H293" s="1">
-        <v>0</v>
-      </c>
-      <c r="I293" s="1">
-        <v>0</v>
-      </c>
-      <c r="J293" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:10" ht="54" x14ac:dyDescent="0.15">
-      <c r="A294" s="1">
-        <v>4003</v>
-      </c>
-      <c r="B294" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E294" s="1">
-        <v>0</v>
-      </c>
-      <c r="F294" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="H294" s="1">
         <v>0</v>
@@ -10213,12 +10221,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>4004</v>
+        <v>4002</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>207</v>
@@ -10230,7 +10238,7 @@
         <v>205</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>315</v>
+        <v>45</v>
       </c>
       <c r="H295" s="1">
         <v>0</v>
@@ -10242,12 +10250,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:10" ht="54" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>4011</v>
+        <v>4003</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>207</v>
@@ -10259,7 +10267,7 @@
         <v>205</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -10271,12 +10279,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>4012</v>
+        <v>4004</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>207</v>
@@ -10288,7 +10296,7 @@
         <v>205</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -10300,9 +10308,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>4013</v>
+        <v>4011</v>
       </c>
       <c r="B298" s="4" t="s">
         <v>323</v>
@@ -10317,7 +10325,7 @@
         <v>205</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H298" s="1">
         <v>0</v>
@@ -10331,7 +10339,7 @@
     </row>
     <row r="299" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>4014</v>
+        <v>4012</v>
       </c>
       <c r="B299" s="4" t="s">
         <v>323</v>
@@ -10346,7 +10354,7 @@
         <v>205</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
@@ -10360,7 +10368,7 @@
     </row>
     <row r="300" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>4015</v>
+        <v>4013</v>
       </c>
       <c r="B300" s="4" t="s">
         <v>323</v>
@@ -10375,7 +10383,7 @@
         <v>205</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H300" s="1">
         <v>0</v>
@@ -10387,12 +10395,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>4016</v>
+        <v>4014</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>207</v>
@@ -10403,8 +10411,8 @@
       <c r="F301" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="G301" s="2" t="s">
-        <v>50</v>
+      <c r="G301" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="H301" s="1">
         <v>0</v>
@@ -10416,12 +10424,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>4017</v>
+        <v>4015</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>207</v>
@@ -10433,7 +10441,7 @@
         <v>205</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="H302" s="1">
         <v>0</v>
@@ -10445,9 +10453,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>4018</v>
+        <v>4016</v>
       </c>
       <c r="B303" s="4" t="s">
         <v>319</v>
@@ -10461,8 +10469,8 @@
       <c r="F303" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="G303" s="1" t="s">
-        <v>346</v>
+      <c r="G303" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="H303" s="1">
         <v>0</v>
@@ -10474,9 +10482,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>4019</v>
+        <v>4017</v>
       </c>
       <c r="B304" s="4" t="s">
         <v>319</v>
@@ -10491,7 +10499,7 @@
         <v>205</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -10503,9 +10511,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="B305" s="4" t="s">
         <v>319</v>
@@ -10520,7 +10528,7 @@
         <v>205</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>243</v>
+        <v>346</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
@@ -10534,7 +10542,7 @@
     </row>
     <row r="306" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>4021</v>
+        <v>4019</v>
       </c>
       <c r="B306" s="4" t="s">
         <v>319</v>
@@ -10549,7 +10557,7 @@
         <v>205</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>46</v>
+        <v>347</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
@@ -10561,9 +10569,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:10" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>4022</v>
+        <v>4020</v>
       </c>
       <c r="B307" s="4" t="s">
         <v>319</v>
@@ -10578,7 +10586,7 @@
         <v>205</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>348</v>
+        <v>243</v>
       </c>
       <c r="H307" s="1">
         <v>0</v>
@@ -10592,7 +10600,7 @@
     </row>
     <row r="308" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>4023</v>
+        <v>4021</v>
       </c>
       <c r="B308" s="4" t="s">
         <v>319</v>
@@ -10607,7 +10615,7 @@
         <v>205</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>349</v>
+        <v>46</v>
       </c>
       <c r="H308" s="1">
         <v>0</v>
@@ -10621,7 +10629,7 @@
     </row>
     <row r="309" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>4024</v>
+        <v>4022</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>319</v>
@@ -10636,7 +10644,7 @@
         <v>205</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H309" s="1">
         <v>0</v>
@@ -10650,7 +10658,7 @@
     </row>
     <row r="310" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>5001</v>
+        <v>4023</v>
       </c>
       <c r="B310" s="4" t="s">
         <v>319</v>
@@ -10665,7 +10673,7 @@
         <v>205</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="H310" s="1">
         <v>0</v>
@@ -10674,12 +10682,12 @@
         <v>0</v>
       </c>
       <c r="J310" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>6000</v>
+        <v>4024</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>319</v>
@@ -10694,7 +10702,7 @@
         <v>205</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="H311" s="1">
         <v>0</v>
@@ -10703,12 +10711,12 @@
         <v>0</v>
       </c>
       <c r="J311" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>6001</v>
+        <v>5001</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>319</v>
@@ -10723,7 +10731,7 @@
         <v>205</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H312" s="1">
         <v>0</v>
@@ -10737,7 +10745,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>6002</v>
+        <v>6000</v>
       </c>
       <c r="B313" s="4" t="s">
         <v>319</v>
@@ -10752,7 +10760,7 @@
         <v>205</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H313" s="1">
         <v>0</v>
@@ -10766,7 +10774,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="B314" s="4" t="s">
         <v>319</v>
@@ -10781,7 +10789,7 @@
         <v>205</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H314" s="1">
         <v>0</v>
@@ -10795,7 +10803,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>319</v>
@@ -10810,7 +10818,7 @@
         <v>205</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H315" s="1">
         <v>0</v>
@@ -10824,7 +10832,7 @@
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="B316" s="4" t="s">
         <v>319</v>
@@ -10839,7 +10847,7 @@
         <v>205</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H316" s="1">
         <v>0</v>
@@ -10853,7 +10861,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="B317" s="4" t="s">
         <v>319</v>
@@ -10868,7 +10876,7 @@
         <v>205</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H317" s="1">
         <v>0</v>
@@ -10882,7 +10890,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>6100</v>
+        <v>6005</v>
       </c>
       <c r="B318" s="4" t="s">
         <v>319</v>
@@ -10897,7 +10905,7 @@
         <v>205</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H318" s="1">
         <v>0</v>
@@ -10911,30 +10919,88 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
+        <v>6006</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E319" s="1">
+        <v>0</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="H319" s="1">
+        <v>0</v>
+      </c>
+      <c r="I319" s="1">
+        <v>0</v>
+      </c>
+      <c r="J319" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A320" s="1">
+        <v>6100</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E320" s="1">
+        <v>0</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G320" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H320" s="1">
+        <v>0</v>
+      </c>
+      <c r="I320" s="1">
+        <v>0</v>
+      </c>
+      <c r="J320" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A321" s="1">
         <v>8100</v>
       </c>
-      <c r="B319" s="4" t="s">
+      <c r="B321" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D319" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E319" s="1">
-        <v>0</v>
-      </c>
-      <c r="F319" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G319" s="1" t="s">
+      <c r="D321" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E321" s="1">
+        <v>0</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G321" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="H319" s="1">
-        <v>0</v>
-      </c>
-      <c r="I319" s="1">
-        <v>0</v>
-      </c>
-      <c r="J319" s="1" t="b">
+      <c r="H321" s="1">
+        <v>0</v>
+      </c>
+      <c r="I321" s="1">
+        <v>0</v>
+      </c>
+      <c r="J321" s="1" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -35,6 +35,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve"> Player = 1, Fixed = 2, Dynamic = 3</t>
@@ -44,6 +45,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="498">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1640,6 +1642,10 @@
   </si>
   <si>
     <t>好好在这里生活吧，你的外公也会很欣慰的。</t>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1666,6 +1672,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1673,6 +1680,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -10650,8 +10658,14 @@
       <c r="A294" s="1">
         <v>4000</v>
       </c>
+      <c r="B294" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D294" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E294" s="1">
+        <v>0</v>
       </c>
       <c r="F294" s="4" t="s">
         <v>193</v>
@@ -10673,8 +10687,14 @@
       <c r="A295" s="1">
         <v>4001</v>
       </c>
+      <c r="B295" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D295" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E295" s="1">
+        <v>0</v>
       </c>
       <c r="F295" s="4" t="s">
         <v>193</v>
@@ -10696,8 +10716,14 @@
       <c r="A296" s="1">
         <v>4002</v>
       </c>
+      <c r="B296" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D296" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E296" s="1">
+        <v>0</v>
       </c>
       <c r="F296" s="4" t="s">
         <v>193</v>
@@ -10719,8 +10745,14 @@
       <c r="A297" s="1">
         <v>4003</v>
       </c>
+      <c r="B297" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D297" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E297" s="1">
+        <v>0</v>
       </c>
       <c r="F297" s="4" t="s">
         <v>193</v>
@@ -10742,8 +10774,14 @@
       <c r="A298" s="1">
         <v>4004</v>
       </c>
+      <c r="B298" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D298" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E298" s="1">
+        <v>0</v>
       </c>
       <c r="F298" s="4" t="s">
         <v>193</v>
@@ -10765,8 +10803,14 @@
       <c r="A299" s="1">
         <v>4005</v>
       </c>
+      <c r="B299" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D299" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E299" s="1">
+        <v>0</v>
       </c>
       <c r="F299" s="4" t="s">
         <v>193</v>
@@ -10788,8 +10832,14 @@
       <c r="A300" s="1">
         <v>4006</v>
       </c>
+      <c r="B300" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D300" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E300" s="1">
+        <v>0</v>
       </c>
       <c r="F300" s="4" t="s">
         <v>193</v>
@@ -10811,8 +10861,14 @@
       <c r="A301" s="1">
         <v>4007</v>
       </c>
+      <c r="B301" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D301" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E301" s="1">
+        <v>0</v>
       </c>
       <c r="F301" s="4" t="s">
         <v>193</v>
@@ -10834,8 +10890,14 @@
       <c r="A302" s="1">
         <v>4008</v>
       </c>
+      <c r="B302" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D302" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E302" s="1">
+        <v>0</v>
       </c>
       <c r="F302" s="4" t="s">
         <v>193</v>
@@ -10857,8 +10919,14 @@
       <c r="A303" s="1">
         <v>4009</v>
       </c>
+      <c r="B303" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D303" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E303" s="1">
+        <v>0</v>
       </c>
       <c r="F303" s="4" t="s">
         <v>193</v>
@@ -10880,8 +10948,14 @@
       <c r="A304" s="1">
         <v>4010</v>
       </c>
+      <c r="B304" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D304" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E304" s="1">
+        <v>0</v>
       </c>
       <c r="F304" s="4" t="s">
         <v>193</v>
@@ -10903,8 +10977,14 @@
       <c r="A305" s="1">
         <v>4011</v>
       </c>
+      <c r="B305" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D305" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E305" s="1">
+        <v>0</v>
       </c>
       <c r="F305" s="4" t="s">
         <v>193</v>
@@ -10926,8 +11006,14 @@
       <c r="A306" s="1">
         <v>4012</v>
       </c>
+      <c r="B306" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D306" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E306" s="1">
+        <v>0</v>
       </c>
       <c r="F306" s="4" t="s">
         <v>193</v>
@@ -10949,8 +11035,14 @@
       <c r="A307" s="1">
         <v>4013</v>
       </c>
+      <c r="B307" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D307" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E307" s="1">
+        <v>0</v>
       </c>
       <c r="F307" s="4" t="s">
         <v>193</v>
@@ -10972,8 +11064,14 @@
       <c r="A308" s="1">
         <v>4014</v>
       </c>
+      <c r="B308" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D308" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E308" s="1">
+        <v>0</v>
       </c>
       <c r="F308" s="4" t="s">
         <v>193</v>
@@ -10995,8 +11093,14 @@
       <c r="A309" s="1">
         <v>4015</v>
       </c>
+      <c r="B309" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D309" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E309" s="1">
+        <v>0</v>
       </c>
       <c r="F309" s="4" t="s">
         <v>193</v>
@@ -11018,8 +11122,14 @@
       <c r="A310" s="1">
         <v>4016</v>
       </c>
+      <c r="B310" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D310" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E310" s="1">
+        <v>0</v>
       </c>
       <c r="F310" s="4" t="s">
         <v>193</v>
@@ -11041,8 +11151,14 @@
       <c r="A311" s="1">
         <v>4017</v>
       </c>
+      <c r="B311" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D311" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E311" s="1">
+        <v>0</v>
       </c>
       <c r="F311" s="4" t="s">
         <v>193</v>
@@ -11064,8 +11180,14 @@
       <c r="A312" s="1">
         <v>4018</v>
       </c>
+      <c r="B312" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D312" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E312" s="1">
+        <v>0</v>
       </c>
       <c r="F312" s="4" t="s">
         <v>193</v>
@@ -11087,8 +11209,14 @@
       <c r="A313" s="1">
         <v>4019</v>
       </c>
+      <c r="B313" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D313" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E313" s="1">
+        <v>0</v>
       </c>
       <c r="F313" s="4" t="s">
         <v>193</v>
@@ -11110,8 +11238,14 @@
       <c r="A314" s="1">
         <v>4020</v>
       </c>
+      <c r="B314" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D314" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E314" s="1">
+        <v>0</v>
       </c>
       <c r="F314" s="4" t="s">
         <v>193</v>
@@ -11133,8 +11267,14 @@
       <c r="A315" s="1">
         <v>4021</v>
       </c>
+      <c r="B315" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D315" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E315" s="1">
+        <v>0</v>
       </c>
       <c r="F315" s="4" t="s">
         <v>193</v>
@@ -11156,8 +11296,14 @@
       <c r="A316" s="1">
         <v>4022</v>
       </c>
+      <c r="B316" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D316" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E316" s="1">
+        <v>0</v>
       </c>
       <c r="F316" s="4" t="s">
         <v>193</v>
@@ -11179,8 +11325,14 @@
       <c r="A317" s="1">
         <v>4023</v>
       </c>
+      <c r="B317" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D317" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E317" s="1">
+        <v>0</v>
       </c>
       <c r="F317" s="4" t="s">
         <v>193</v>
@@ -11202,8 +11354,14 @@
       <c r="A318" s="1">
         <v>4024</v>
       </c>
+      <c r="B318" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D318" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E318" s="1">
+        <v>0</v>
       </c>
       <c r="F318" s="4" t="s">
         <v>193</v>
@@ -11225,8 +11383,14 @@
       <c r="A319" s="1">
         <v>4025</v>
       </c>
+      <c r="B319" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D319" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E319" s="1">
+        <v>0</v>
       </c>
       <c r="F319" s="4" t="s">
         <v>193</v>
@@ -11248,8 +11412,14 @@
       <c r="A320" s="1">
         <v>4026</v>
       </c>
+      <c r="B320" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D320" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E320" s="1">
+        <v>0</v>
       </c>
       <c r="F320" s="4" t="s">
         <v>193</v>
@@ -11271,8 +11441,14 @@
       <c r="A321" s="1">
         <v>4027</v>
       </c>
+      <c r="B321" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D321" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E321" s="1">
+        <v>0</v>
       </c>
       <c r="F321" s="4" t="s">
         <v>193</v>
@@ -11294,8 +11470,14 @@
       <c r="A322" s="1">
         <v>4028</v>
       </c>
+      <c r="B322" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D322" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E322" s="1">
+        <v>0</v>
       </c>
       <c r="F322" s="4" t="s">
         <v>193</v>
@@ -11317,8 +11499,14 @@
       <c r="A323" s="1">
         <v>4029</v>
       </c>
+      <c r="B323" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D323" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E323" s="1">
+        <v>0</v>
       </c>
       <c r="F323" s="4" t="s">
         <v>193</v>
@@ -11340,8 +11528,14 @@
       <c r="A324" s="1">
         <v>4030</v>
       </c>
+      <c r="B324" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D324" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E324" s="1">
+        <v>0</v>
       </c>
       <c r="F324" s="4" t="s">
         <v>193</v>
@@ -11363,8 +11557,14 @@
       <c r="A325" s="1">
         <v>4031</v>
       </c>
+      <c r="B325" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D325" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E325" s="1">
+        <v>0</v>
       </c>
       <c r="F325" s="4" t="s">
         <v>193</v>
@@ -11386,8 +11586,14 @@
       <c r="A326" s="1">
         <v>4032</v>
       </c>
+      <c r="B326" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D326" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E326" s="1">
+        <v>0</v>
       </c>
       <c r="F326" s="4" t="s">
         <v>193</v>
@@ -11409,8 +11615,14 @@
       <c r="A327" s="1">
         <v>4033</v>
       </c>
+      <c r="B327" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D327" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E327" s="1">
+        <v>0</v>
       </c>
       <c r="F327" s="4" t="s">
         <v>193</v>
@@ -11432,8 +11644,14 @@
       <c r="A328" s="1">
         <v>4034</v>
       </c>
+      <c r="B328" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D328" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E328" s="1">
+        <v>0</v>
       </c>
       <c r="F328" s="4" t="s">
         <v>193</v>
@@ -11455,8 +11673,14 @@
       <c r="A329" s="1">
         <v>4035</v>
       </c>
+      <c r="B329" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D329" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E329" s="1">
+        <v>0</v>
       </c>
       <c r="F329" s="4" t="s">
         <v>193</v>
@@ -11478,8 +11702,14 @@
       <c r="A330" s="1">
         <v>4036</v>
       </c>
+      <c r="B330" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D330" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E330" s="1">
+        <v>0</v>
       </c>
       <c r="F330" s="4" t="s">
         <v>193</v>
@@ -11501,8 +11731,14 @@
       <c r="A331" s="1">
         <v>4037</v>
       </c>
+      <c r="B331" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D331" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E331" s="1">
+        <v>0</v>
       </c>
       <c r="F331" s="4" t="s">
         <v>193</v>
@@ -11524,8 +11760,14 @@
       <c r="A332" s="1">
         <v>4038</v>
       </c>
+      <c r="B332" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D332" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E332" s="1">
+        <v>0</v>
       </c>
       <c r="F332" s="4" t="s">
         <v>193</v>
@@ -11547,8 +11789,14 @@
       <c r="A333" s="1">
         <v>4039</v>
       </c>
+      <c r="B333" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D333" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E333" s="1">
+        <v>0</v>
       </c>
       <c r="F333" s="4" t="s">
         <v>193</v>
@@ -11570,8 +11818,14 @@
       <c r="A334" s="1">
         <v>4040</v>
       </c>
+      <c r="B334" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D334" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E334" s="1">
+        <v>0</v>
       </c>
       <c r="F334" s="4" t="s">
         <v>193</v>
@@ -11593,8 +11847,14 @@
       <c r="A335" s="1">
         <v>4041</v>
       </c>
+      <c r="B335" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D335" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E335" s="1">
+        <v>0</v>
       </c>
       <c r="F335" s="4" t="s">
         <v>193</v>
@@ -11616,8 +11876,14 @@
       <c r="A336" s="1">
         <v>4042</v>
       </c>
+      <c r="B336" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D336" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E336" s="1">
+        <v>0</v>
       </c>
       <c r="F336" s="4" t="s">
         <v>193</v>
@@ -11639,8 +11905,14 @@
       <c r="A337" s="1">
         <v>4043</v>
       </c>
+      <c r="B337" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D337" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E337" s="1">
+        <v>0</v>
       </c>
       <c r="F337" s="4" t="s">
         <v>193</v>
@@ -11662,8 +11934,14 @@
       <c r="A338" s="1">
         <v>4044</v>
       </c>
+      <c r="B338" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D338" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E338" s="1">
+        <v>0</v>
       </c>
       <c r="F338" s="4" t="s">
         <v>193</v>
@@ -11685,8 +11963,14 @@
       <c r="A339" s="1">
         <v>4045</v>
       </c>
+      <c r="B339" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D339" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E339" s="1">
+        <v>0</v>
       </c>
       <c r="F339" s="4" t="s">
         <v>193</v>
@@ -11708,8 +11992,14 @@
       <c r="A340" s="1">
         <v>4046</v>
       </c>
+      <c r="B340" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D340" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E340" s="1">
+        <v>0</v>
       </c>
       <c r="F340" s="4" t="s">
         <v>193</v>
@@ -11731,8 +12021,14 @@
       <c r="A341" s="1">
         <v>4047</v>
       </c>
+      <c r="B341" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D341" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E341" s="1">
+        <v>0</v>
       </c>
       <c r="F341" s="4" t="s">
         <v>193</v>
@@ -11754,8 +12050,14 @@
       <c r="A342" s="1">
         <v>4048</v>
       </c>
+      <c r="B342" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D342" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E342" s="1">
+        <v>0</v>
       </c>
       <c r="F342" s="4" t="s">
         <v>193</v>
@@ -11777,8 +12079,14 @@
       <c r="A343" s="1">
         <v>4049</v>
       </c>
+      <c r="B343" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D343" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E343" s="1">
+        <v>0</v>
       </c>
       <c r="F343" s="4" t="s">
         <v>193</v>
@@ -11800,8 +12108,14 @@
       <c r="A344" s="1">
         <v>4050</v>
       </c>
+      <c r="B344" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D344" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E344" s="1">
+        <v>0</v>
       </c>
       <c r="F344" s="4" t="s">
         <v>193</v>
@@ -11823,8 +12137,14 @@
       <c r="A345" s="1">
         <v>4051</v>
       </c>
+      <c r="B345" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D345" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E345" s="1">
+        <v>0</v>
       </c>
       <c r="F345" s="4" t="s">
         <v>193</v>
@@ -11846,8 +12166,14 @@
       <c r="A346" s="1">
         <v>4052</v>
       </c>
+      <c r="B346" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D346" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E346" s="1">
+        <v>0</v>
       </c>
       <c r="F346" s="4" t="s">
         <v>193</v>
@@ -11869,8 +12195,14 @@
       <c r="A347" s="1">
         <v>4053</v>
       </c>
+      <c r="B347" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D347" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E347" s="1">
+        <v>0</v>
       </c>
       <c r="F347" s="4" t="s">
         <v>193</v>
@@ -11892,8 +12224,14 @@
       <c r="A348" s="1">
         <v>4054</v>
       </c>
+      <c r="B348" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D348" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E348" s="1">
+        <v>0</v>
       </c>
       <c r="F348" s="4" t="s">
         <v>193</v>
@@ -11915,8 +12253,14 @@
       <c r="A349" s="1">
         <v>4055</v>
       </c>
+      <c r="B349" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D349" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E349" s="1">
+        <v>0</v>
       </c>
       <c r="F349" s="4" t="s">
         <v>193</v>
@@ -11938,8 +12282,14 @@
       <c r="A350" s="1">
         <v>4056</v>
       </c>
+      <c r="B350" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D350" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E350" s="1">
+        <v>0</v>
       </c>
       <c r="F350" s="4" t="s">
         <v>193</v>
@@ -11961,8 +12311,14 @@
       <c r="A351" s="1">
         <v>4057</v>
       </c>
+      <c r="B351" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D351" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E351" s="1">
+        <v>0</v>
       </c>
       <c r="F351" s="4" t="s">
         <v>193</v>
@@ -11984,8 +12340,14 @@
       <c r="A352" s="1">
         <v>4058</v>
       </c>
+      <c r="B352" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D352" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E352" s="1">
+        <v>0</v>
       </c>
       <c r="F352" s="4" t="s">
         <v>193</v>
@@ -12007,8 +12369,14 @@
       <c r="A353" s="1">
         <v>4059</v>
       </c>
+      <c r="B353" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D353" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E353" s="1">
+        <v>0</v>
       </c>
       <c r="F353" s="4" t="s">
         <v>193</v>
@@ -12030,8 +12398,14 @@
       <c r="A354" s="1">
         <v>4060</v>
       </c>
+      <c r="B354" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D354" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E354" s="1">
+        <v>0</v>
       </c>
       <c r="F354" s="4" t="s">
         <v>193</v>
@@ -12053,8 +12427,14 @@
       <c r="A355" s="1">
         <v>4061</v>
       </c>
+      <c r="B355" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D355" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E355" s="1">
+        <v>0</v>
       </c>
       <c r="F355" s="4" t="s">
         <v>193</v>
@@ -12076,8 +12456,14 @@
       <c r="A356" s="1">
         <v>4062</v>
       </c>
+      <c r="B356" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D356" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E356" s="1">
+        <v>0</v>
       </c>
       <c r="F356" s="4" t="s">
         <v>193</v>
@@ -12099,8 +12485,14 @@
       <c r="A357" s="1">
         <v>4063</v>
       </c>
+      <c r="B357" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D357" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E357" s="1">
+        <v>0</v>
       </c>
       <c r="F357" s="4" t="s">
         <v>193</v>
@@ -12122,8 +12514,14 @@
       <c r="A358" s="1">
         <v>4064</v>
       </c>
+      <c r="B358" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D358" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E358" s="1">
+        <v>0</v>
       </c>
       <c r="F358" s="4" t="s">
         <v>193</v>
@@ -12145,8 +12543,14 @@
       <c r="A359" s="1">
         <v>4065</v>
       </c>
+      <c r="B359" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D359" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E359" s="1">
+        <v>0</v>
       </c>
       <c r="F359" s="4" t="s">
         <v>193</v>
@@ -12168,8 +12572,14 @@
       <c r="A360" s="1">
         <v>4066</v>
       </c>
+      <c r="B360" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D360" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E360" s="1">
+        <v>0</v>
       </c>
       <c r="F360" s="4" t="s">
         <v>193</v>
@@ -12191,8 +12601,14 @@
       <c r="A361" s="1">
         <v>4067</v>
       </c>
+      <c r="B361" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D361" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E361" s="1">
+        <v>0</v>
       </c>
       <c r="F361" s="4" t="s">
         <v>193</v>
@@ -12214,8 +12630,14 @@
       <c r="A362" s="1">
         <v>4068</v>
       </c>
+      <c r="B362" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D362" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E362" s="1">
+        <v>0</v>
       </c>
       <c r="F362" s="4" t="s">
         <v>193</v>
@@ -12237,8 +12659,14 @@
       <c r="A363" s="1">
         <v>4069</v>
       </c>
+      <c r="B363" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D363" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E363" s="1">
+        <v>0</v>
       </c>
       <c r="F363" s="4" t="s">
         <v>193</v>
@@ -12260,8 +12688,14 @@
       <c r="A364" s="1">
         <v>4070</v>
       </c>
+      <c r="B364" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D364" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E364" s="1">
+        <v>0</v>
       </c>
       <c r="F364" s="4" t="s">
         <v>193</v>
@@ -12283,8 +12717,14 @@
       <c r="A365" s="1">
         <v>4071</v>
       </c>
+      <c r="B365" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D365" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E365" s="1">
+        <v>0</v>
       </c>
       <c r="F365" s="4" t="s">
         <v>193</v>
@@ -12306,8 +12746,14 @@
       <c r="A366" s="1">
         <v>4072</v>
       </c>
+      <c r="B366" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D366" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E366" s="1">
+        <v>0</v>
       </c>
       <c r="F366" s="4" t="s">
         <v>193</v>
@@ -12329,8 +12775,14 @@
       <c r="A367" s="1">
         <v>4073</v>
       </c>
+      <c r="B367" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D367" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E367" s="1">
+        <v>0</v>
       </c>
       <c r="F367" s="4" t="s">
         <v>193</v>
@@ -12352,8 +12804,14 @@
       <c r="A368" s="1">
         <v>4074</v>
       </c>
+      <c r="B368" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D368" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E368" s="1">
+        <v>0</v>
       </c>
       <c r="F368" s="4" t="s">
         <v>193</v>
@@ -12375,8 +12833,14 @@
       <c r="A369" s="1">
         <v>4075</v>
       </c>
+      <c r="B369" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D369" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E369" s="1">
+        <v>0</v>
       </c>
       <c r="F369" s="4" t="s">
         <v>193</v>
@@ -12398,8 +12862,14 @@
       <c r="A370" s="1">
         <v>4076</v>
       </c>
+      <c r="B370" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D370" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E370" s="1">
+        <v>0</v>
       </c>
       <c r="F370" s="4" t="s">
         <v>193</v>
@@ -12421,8 +12891,14 @@
       <c r="A371" s="1">
         <v>4077</v>
       </c>
+      <c r="B371" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D371" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E371" s="1">
+        <v>0</v>
       </c>
       <c r="F371" s="4" t="s">
         <v>193</v>
@@ -12444,8 +12920,14 @@
       <c r="A372" s="1">
         <v>4078</v>
       </c>
+      <c r="B372" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D372" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E372" s="1">
+        <v>0</v>
       </c>
       <c r="F372" s="4" t="s">
         <v>193</v>
@@ -12467,8 +12949,14 @@
       <c r="A373" s="1">
         <v>4079</v>
       </c>
+      <c r="B373" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D373" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E373" s="1">
+        <v>0</v>
       </c>
       <c r="F373" s="4" t="s">
         <v>193</v>
@@ -12490,8 +12978,14 @@
       <c r="A374" s="1">
         <v>4080</v>
       </c>
+      <c r="B374" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D374" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E374" s="1">
+        <v>0</v>
       </c>
       <c r="F374" s="4" t="s">
         <v>193</v>
@@ -12513,8 +13007,14 @@
       <c r="A375" s="1">
         <v>4081</v>
       </c>
+      <c r="B375" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D375" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E375" s="1">
+        <v>0</v>
       </c>
       <c r="F375" s="4" t="s">
         <v>193</v>
@@ -12536,8 +13036,14 @@
       <c r="A376" s="1">
         <v>4082</v>
       </c>
+      <c r="B376" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D376" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E376" s="1">
+        <v>0</v>
       </c>
       <c r="F376" s="4" t="s">
         <v>193</v>
@@ -12559,8 +13065,14 @@
       <c r="A377" s="1">
         <v>4083</v>
       </c>
+      <c r="B377" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D377" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E377" s="1">
+        <v>0</v>
       </c>
       <c r="F377" s="4" t="s">
         <v>193</v>
@@ -12582,8 +13094,14 @@
       <c r="A378" s="1">
         <v>4084</v>
       </c>
+      <c r="B378" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D378" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E378" s="1">
+        <v>0</v>
       </c>
       <c r="F378" s="4" t="s">
         <v>193</v>
@@ -12605,8 +13123,14 @@
       <c r="A379" s="1">
         <v>4085</v>
       </c>
+      <c r="B379" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D379" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E379" s="1">
+        <v>0</v>
       </c>
       <c r="F379" s="4" t="s">
         <v>193</v>
@@ -12628,8 +13152,14 @@
       <c r="A380" s="1">
         <v>4086</v>
       </c>
+      <c r="B380" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D380" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E380" s="1">
+        <v>0</v>
       </c>
       <c r="F380" s="4" t="s">
         <v>193</v>
@@ -12651,8 +13181,14 @@
       <c r="A381" s="1">
         <v>4087</v>
       </c>
+      <c r="B381" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D381" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E381" s="1">
+        <v>0</v>
       </c>
       <c r="F381" s="4" t="s">
         <v>193</v>
@@ -12674,8 +13210,14 @@
       <c r="A382" s="1">
         <v>4088</v>
       </c>
+      <c r="B382" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D382" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E382" s="1">
+        <v>0</v>
       </c>
       <c r="F382" s="4" t="s">
         <v>193</v>
@@ -12697,8 +13239,14 @@
       <c r="A383" s="1">
         <v>4089</v>
       </c>
+      <c r="B383" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D383" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E383" s="1">
+        <v>0</v>
       </c>
       <c r="F383" s="4" t="s">
         <v>193</v>
@@ -12720,8 +13268,14 @@
       <c r="A384" s="1">
         <v>4090</v>
       </c>
+      <c r="B384" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D384" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E384" s="1">
+        <v>0</v>
       </c>
       <c r="F384" s="4" t="s">
         <v>193</v>
@@ -12743,8 +13297,14 @@
       <c r="A385" s="1">
         <v>4091</v>
       </c>
+      <c r="B385" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D385" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E385" s="1">
+        <v>0</v>
       </c>
       <c r="F385" s="4" t="s">
         <v>193</v>
@@ -12766,8 +13326,14 @@
       <c r="A386" s="1">
         <v>4092</v>
       </c>
+      <c r="B386" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D386" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E386" s="1">
+        <v>0</v>
       </c>
       <c r="F386" s="4" t="s">
         <v>193</v>
@@ -12789,8 +13355,14 @@
       <c r="A387" s="1">
         <v>4093</v>
       </c>
+      <c r="B387" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D387" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E387" s="1">
+        <v>0</v>
       </c>
       <c r="F387" s="4" t="s">
         <v>193</v>
@@ -12812,8 +13384,14 @@
       <c r="A388" s="1">
         <v>4094</v>
       </c>
+      <c r="B388" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D388" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E388" s="1">
+        <v>0</v>
       </c>
       <c r="F388" s="4" t="s">
         <v>193</v>
@@ -12835,8 +13413,14 @@
       <c r="A389" s="1">
         <v>4095</v>
       </c>
+      <c r="B389" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D389" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E389" s="1">
+        <v>0</v>
       </c>
       <c r="F389" s="4" t="s">
         <v>193</v>
@@ -12858,8 +13442,14 @@
       <c r="A390" s="1">
         <v>4096</v>
       </c>
+      <c r="B390" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D390" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E390" s="1">
+        <v>0</v>
       </c>
       <c r="F390" s="4" t="s">
         <v>193</v>
@@ -12881,8 +13471,14 @@
       <c r="A391" s="1">
         <v>4097</v>
       </c>
+      <c r="B391" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D391" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E391" s="1">
+        <v>0</v>
       </c>
       <c r="F391" s="4" t="s">
         <v>193</v>
@@ -12904,8 +13500,14 @@
       <c r="A392" s="1">
         <v>4098</v>
       </c>
+      <c r="B392" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D392" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E392" s="1">
+        <v>0</v>
       </c>
       <c r="F392" s="4" t="s">
         <v>193</v>
@@ -12927,8 +13529,14 @@
       <c r="A393" s="1">
         <v>4099</v>
       </c>
+      <c r="B393" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D393" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E393" s="1">
+        <v>0</v>
       </c>
       <c r="F393" s="4" t="s">
         <v>193</v>
@@ -12950,8 +13558,14 @@
       <c r="A394" s="1">
         <v>4100</v>
       </c>
+      <c r="B394" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D394" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E394" s="1">
+        <v>0</v>
       </c>
       <c r="F394" s="4" t="s">
         <v>193</v>
@@ -12973,8 +13587,14 @@
       <c r="A395" s="1">
         <v>4101</v>
       </c>
+      <c r="B395" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D395" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E395" s="1">
+        <v>0</v>
       </c>
       <c r="F395" s="4" t="s">
         <v>193</v>
@@ -12996,8 +13616,14 @@
       <c r="A396" s="1">
         <v>4102</v>
       </c>
+      <c r="B396" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D396" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E396" s="1">
+        <v>0</v>
       </c>
       <c r="F396" s="4" t="s">
         <v>193</v>
@@ -13019,8 +13645,14 @@
       <c r="A397" s="1">
         <v>4103</v>
       </c>
+      <c r="B397" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D397" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E397" s="1">
+        <v>0</v>
       </c>
       <c r="F397" s="4" t="s">
         <v>193</v>
@@ -13042,8 +13674,14 @@
       <c r="A398" s="1">
         <v>4104</v>
       </c>
+      <c r="B398" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D398" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E398" s="1">
+        <v>0</v>
       </c>
       <c r="F398" s="4" t="s">
         <v>193</v>
@@ -13065,8 +13703,14 @@
       <c r="A399" s="1">
         <v>4105</v>
       </c>
+      <c r="B399" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D399" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E399" s="1">
+        <v>0</v>
       </c>
       <c r="F399" s="4" t="s">
         <v>193</v>
@@ -13088,8 +13732,14 @@
       <c r="A400" s="1">
         <v>4106</v>
       </c>
+      <c r="B400" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D400" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E400" s="1">
+        <v>0</v>
       </c>
       <c r="F400" s="4" t="s">
         <v>193</v>
@@ -13111,8 +13761,14 @@
       <c r="A401" s="1">
         <v>4107</v>
       </c>
+      <c r="B401" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D401" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E401" s="1">
+        <v>0</v>
       </c>
       <c r="F401" s="4" t="s">
         <v>193</v>
@@ -13134,8 +13790,14 @@
       <c r="A402" s="1">
         <v>4108</v>
       </c>
+      <c r="B402" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D402" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E402" s="1">
+        <v>0</v>
       </c>
       <c r="F402" s="4" t="s">
         <v>193</v>
@@ -13157,8 +13819,14 @@
       <c r="A403" s="1">
         <v>4109</v>
       </c>
+      <c r="B403" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D403" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E403" s="1">
+        <v>0</v>
       </c>
       <c r="F403" s="4" t="s">
         <v>193</v>
@@ -13180,8 +13848,14 @@
       <c r="A404" s="1">
         <v>4110</v>
       </c>
+      <c r="B404" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D404" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E404" s="1">
+        <v>0</v>
       </c>
       <c r="F404" s="4" t="s">
         <v>193</v>
@@ -13203,8 +13877,14 @@
       <c r="A405" s="1">
         <v>4111</v>
       </c>
+      <c r="B405" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D405" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E405" s="1">
+        <v>0</v>
       </c>
       <c r="F405" s="4" t="s">
         <v>193</v>
@@ -13226,8 +13906,14 @@
       <c r="A406" s="1">
         <v>4112</v>
       </c>
+      <c r="B406" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D406" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E406" s="1">
+        <v>0</v>
       </c>
       <c r="F406" s="4" t="s">
         <v>193</v>
@@ -13249,8 +13935,14 @@
       <c r="A407" s="1">
         <v>4113</v>
       </c>
+      <c r="B407" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D407" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E407" s="1">
+        <v>0</v>
       </c>
       <c r="F407" s="4" t="s">
         <v>193</v>
@@ -13272,8 +13964,14 @@
       <c r="A408" s="1">
         <v>4114</v>
       </c>
+      <c r="B408" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D408" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E408" s="1">
+        <v>0</v>
       </c>
       <c r="F408" s="4" t="s">
         <v>193</v>
@@ -13295,8 +13993,14 @@
       <c r="A409" s="1">
         <v>4115</v>
       </c>
+      <c r="B409" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D409" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E409" s="1">
+        <v>0</v>
       </c>
       <c r="F409" s="4" t="s">
         <v>193</v>
@@ -13318,8 +14022,14 @@
       <c r="A410" s="1">
         <v>4116</v>
       </c>
+      <c r="B410" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D410" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E410" s="1">
+        <v>0</v>
       </c>
       <c r="F410" s="4" t="s">
         <v>193</v>
@@ -13341,8 +14051,14 @@
       <c r="A411" s="1">
         <v>4117</v>
       </c>
+      <c r="B411" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D411" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E411" s="1">
+        <v>0</v>
       </c>
       <c r="F411" s="4" t="s">
         <v>193</v>
@@ -13364,8 +14080,14 @@
       <c r="A412" s="1">
         <v>4118</v>
       </c>
+      <c r="B412" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D412" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E412" s="1">
+        <v>0</v>
       </c>
       <c r="F412" s="4" t="s">
         <v>193</v>
@@ -13387,8 +14109,14 @@
       <c r="A413" s="1">
         <v>4119</v>
       </c>
+      <c r="B413" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D413" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E413" s="1">
+        <v>0</v>
       </c>
       <c r="F413" s="4" t="s">
         <v>193</v>
@@ -13410,8 +14138,14 @@
       <c r="A414" s="1">
         <v>4120</v>
       </c>
+      <c r="B414" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D414" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E414" s="1">
+        <v>0</v>
       </c>
       <c r="F414" s="4" t="s">
         <v>193</v>
@@ -13433,8 +14167,14 @@
       <c r="A415" s="1">
         <v>4121</v>
       </c>
+      <c r="B415" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D415" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E415" s="1">
+        <v>0</v>
       </c>
       <c r="F415" s="4" t="s">
         <v>193</v>
@@ -13456,8 +14196,14 @@
       <c r="A416" s="1">
         <v>4122</v>
       </c>
+      <c r="B416" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D416" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E416" s="1">
+        <v>0</v>
       </c>
       <c r="F416" s="4" t="s">
         <v>193</v>
@@ -13479,8 +14225,14 @@
       <c r="A417" s="1">
         <v>4123</v>
       </c>
+      <c r="B417" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D417" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E417" s="1">
+        <v>0</v>
       </c>
       <c r="F417" s="4" t="s">
         <v>193</v>
@@ -13502,8 +14254,14 @@
       <c r="A418" s="1">
         <v>4124</v>
       </c>
+      <c r="B418" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D418" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E418" s="1">
+        <v>0</v>
       </c>
       <c r="F418" s="4" t="s">
         <v>193</v>
@@ -13525,8 +14283,14 @@
       <c r="A419" s="1">
         <v>4125</v>
       </c>
+      <c r="B419" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D419" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E419" s="1">
+        <v>0</v>
       </c>
       <c r="F419" s="4" t="s">
         <v>193</v>
@@ -13548,8 +14312,14 @@
       <c r="A420" s="1">
         <v>4126</v>
       </c>
+      <c r="B420" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D420" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E420" s="1">
+        <v>0</v>
       </c>
       <c r="F420" s="4" t="s">
         <v>193</v>
@@ -13571,8 +14341,14 @@
       <c r="A421" s="1">
         <v>4127</v>
       </c>
+      <c r="B421" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D421" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E421" s="1">
+        <v>0</v>
       </c>
       <c r="F421" s="4" t="s">
         <v>193</v>
@@ -13594,8 +14370,14 @@
       <c r="A422" s="1">
         <v>4128</v>
       </c>
+      <c r="B422" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D422" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E422" s="1">
+        <v>0</v>
       </c>
       <c r="F422" s="4" t="s">
         <v>193</v>
@@ -13617,8 +14399,14 @@
       <c r="A423" s="1">
         <v>4129</v>
       </c>
+      <c r="B423" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D423" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E423" s="1">
+        <v>0</v>
       </c>
       <c r="F423" s="4" t="s">
         <v>193</v>
@@ -13640,8 +14428,14 @@
       <c r="A424" s="1">
         <v>4130</v>
       </c>
+      <c r="B424" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D424" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E424" s="1">
+        <v>0</v>
       </c>
       <c r="F424" s="4" t="s">
         <v>193</v>
@@ -13663,8 +14457,14 @@
       <c r="A425" s="1">
         <v>4131</v>
       </c>
+      <c r="B425" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D425" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E425" s="1">
+        <v>0</v>
       </c>
       <c r="F425" s="4" t="s">
         <v>193</v>
@@ -13686,8 +14486,14 @@
       <c r="A426" s="1">
         <v>4132</v>
       </c>
+      <c r="B426" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D426" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E426" s="1">
+        <v>0</v>
       </c>
       <c r="F426" s="4" t="s">
         <v>193</v>
@@ -13709,8 +14515,14 @@
       <c r="A427" s="1">
         <v>4133</v>
       </c>
+      <c r="B427" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D427" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E427" s="1">
+        <v>0</v>
       </c>
       <c r="F427" s="4" t="s">
         <v>193</v>
@@ -13732,8 +14544,14 @@
       <c r="A428" s="1">
         <v>4134</v>
       </c>
+      <c r="B428" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D428" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E428" s="1">
+        <v>0</v>
       </c>
       <c r="F428" s="4" t="s">
         <v>193</v>
@@ -13755,8 +14573,14 @@
       <c r="A429" s="1">
         <v>4135</v>
       </c>
+      <c r="B429" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D429" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E429" s="1">
+        <v>0</v>
       </c>
       <c r="F429" s="4" t="s">
         <v>193</v>
@@ -13778,8 +14602,14 @@
       <c r="A430" s="1">
         <v>4136</v>
       </c>
+      <c r="B430" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D430" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E430" s="1">
+        <v>0</v>
       </c>
       <c r="F430" s="4" t="s">
         <v>193</v>
@@ -13801,8 +14631,14 @@
       <c r="A431" s="1">
         <v>4137</v>
       </c>
+      <c r="B431" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D431" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E431" s="1">
+        <v>0</v>
       </c>
       <c r="F431" s="4" t="s">
         <v>193</v>
@@ -13824,8 +14660,14 @@
       <c r="A432" s="1">
         <v>4138</v>
       </c>
+      <c r="B432" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D432" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E432" s="1">
+        <v>0</v>
       </c>
       <c r="F432" s="4" t="s">
         <v>193</v>
@@ -13847,8 +14689,14 @@
       <c r="A433" s="1">
         <v>4139</v>
       </c>
+      <c r="B433" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D433" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E433" s="1">
+        <v>0</v>
       </c>
       <c r="F433" s="4" t="s">
         <v>193</v>
@@ -13870,8 +14718,14 @@
       <c r="A434" s="1">
         <v>4140</v>
       </c>
+      <c r="B434" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D434" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E434" s="1">
+        <v>0</v>
       </c>
       <c r="F434" s="4" t="s">
         <v>193</v>
@@ -13893,8 +14747,14 @@
       <c r="A435" s="1">
         <v>4141</v>
       </c>
+      <c r="B435" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D435" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E435" s="1">
+        <v>0</v>
       </c>
       <c r="F435" s="4" t="s">
         <v>193</v>
@@ -13916,8 +14776,14 @@
       <c r="A436" s="1">
         <v>4142</v>
       </c>
+      <c r="B436" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D436" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E436" s="1">
+        <v>0</v>
       </c>
       <c r="F436" s="4" t="s">
         <v>193</v>
@@ -13939,8 +14805,14 @@
       <c r="A437" s="1">
         <v>4143</v>
       </c>
+      <c r="B437" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D437" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E437" s="1">
+        <v>0</v>
       </c>
       <c r="F437" s="4" t="s">
         <v>193</v>
@@ -13962,8 +14834,14 @@
       <c r="A438" s="1">
         <v>4144</v>
       </c>
+      <c r="B438" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D438" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E438" s="1">
+        <v>0</v>
       </c>
       <c r="F438" s="4" t="s">
         <v>193</v>
@@ -13985,8 +14863,14 @@
       <c r="A439" s="1">
         <v>4145</v>
       </c>
+      <c r="B439" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D439" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E439" s="1">
+        <v>0</v>
       </c>
       <c r="F439" s="4" t="s">
         <v>193</v>
@@ -14008,8 +14892,14 @@
       <c r="A440" s="1">
         <v>4146</v>
       </c>
+      <c r="B440" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D440" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E440" s="1">
+        <v>0</v>
       </c>
       <c r="F440" s="4" t="s">
         <v>193</v>
@@ -14031,8 +14921,14 @@
       <c r="A441" s="1">
         <v>4147</v>
       </c>
+      <c r="B441" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D441" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E441" s="1">
+        <v>0</v>
       </c>
       <c r="F441" s="4" t="s">
         <v>193</v>
@@ -14054,8 +14950,14 @@
       <c r="A442" s="1">
         <v>4148</v>
       </c>
+      <c r="B442" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D442" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E442" s="1">
+        <v>0</v>
       </c>
       <c r="F442" s="4" t="s">
         <v>193</v>
@@ -14077,8 +14979,14 @@
       <c r="A443" s="1">
         <v>4149</v>
       </c>
+      <c r="B443" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D443" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E443" s="1">
+        <v>0</v>
       </c>
       <c r="F443" s="4" t="s">
         <v>193</v>
@@ -14100,8 +15008,14 @@
       <c r="A444" s="1">
         <v>4150</v>
       </c>
+      <c r="B444" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D444" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E444" s="1">
+        <v>0</v>
       </c>
       <c r="F444" s="4" t="s">
         <v>193</v>
@@ -14123,8 +15037,14 @@
       <c r="A445" s="1">
         <v>4151</v>
       </c>
+      <c r="B445" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D445" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E445" s="1">
+        <v>0</v>
       </c>
       <c r="F445" s="4" t="s">
         <v>193</v>
@@ -14146,8 +15066,14 @@
       <c r="A446" s="1">
         <v>4152</v>
       </c>
+      <c r="B446" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D446" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E446" s="1">
+        <v>0</v>
       </c>
       <c r="F446" s="4" t="s">
         <v>193</v>
@@ -14169,8 +15095,14 @@
       <c r="A447" s="1">
         <v>4153</v>
       </c>
+      <c r="B447" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D447" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E447" s="1">
+        <v>0</v>
       </c>
       <c r="F447" s="4" t="s">
         <v>193</v>
@@ -14192,8 +15124,14 @@
       <c r="A448" s="1">
         <v>4154</v>
       </c>
+      <c r="B448" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D448" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E448" s="1">
+        <v>0</v>
       </c>
       <c r="F448" s="4" t="s">
         <v>193</v>
@@ -14215,8 +15153,14 @@
       <c r="A449" s="1">
         <v>4155</v>
       </c>
+      <c r="B449" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D449" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E449" s="1">
+        <v>0</v>
       </c>
       <c r="F449" s="4" t="s">
         <v>193</v>
@@ -14238,8 +15182,14 @@
       <c r="A450" s="1">
         <v>4156</v>
       </c>
+      <c r="B450" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D450" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E450" s="1">
+        <v>0</v>
       </c>
       <c r="F450" s="4" t="s">
         <v>193</v>
@@ -14261,8 +15211,14 @@
       <c r="A451" s="1">
         <v>4157</v>
       </c>
+      <c r="B451" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D451" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E451" s="1">
+        <v>0</v>
       </c>
       <c r="F451" s="4" t="s">
         <v>193</v>
@@ -14284,8 +15240,14 @@
       <c r="A452" s="1">
         <v>4158</v>
       </c>
+      <c r="B452" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D452" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E452" s="1">
+        <v>0</v>
       </c>
       <c r="F452" s="4" t="s">
         <v>193</v>
@@ -14307,8 +15269,14 @@
       <c r="A453" s="1">
         <v>4159</v>
       </c>
+      <c r="B453" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D453" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E453" s="1">
+        <v>0</v>
       </c>
       <c r="F453" s="4" t="s">
         <v>193</v>
@@ -14330,8 +15298,14 @@
       <c r="A454" s="1">
         <v>4160</v>
       </c>
+      <c r="B454" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D454" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E454" s="1">
+        <v>0</v>
       </c>
       <c r="F454" s="4" t="s">
         <v>193</v>
@@ -14353,8 +15327,14 @@
       <c r="A455" s="1">
         <v>4161</v>
       </c>
+      <c r="B455" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="D455" s="1" t="s">
         <v>291</v>
+      </c>
+      <c r="E455" s="1">
+        <v>0</v>
       </c>
       <c r="F455" s="4" t="s">
         <v>193</v>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory_hub\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Rune Factory\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380"/>
   </bookViews>
   <sheets>
     <sheet name="TalkData" sheetId="1" r:id="rId1"/>
@@ -6538,7 +6538,7 @@
         <v>1404</v>
       </c>
       <c r="I148" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J148" s="1" t="b">
         <v>0</v>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -7060,10 +7060,10 @@
         <v>560</v>
       </c>
       <c r="H164" s="1">
-        <v>1420</v>
+        <v>0</v>
       </c>
       <c r="I164" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J164" s="1" t="b">
         <v>0</v>
@@ -7095,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="I165" s="1">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J165" s="1" t="b">
         <v>0</v>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -9,14 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TalkData" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Chart1" sheetId="3" r:id="rId1"/>
+    <sheet name="TalkData" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$465</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TalkData!$A$3:$J$466</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="572">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1884,6 +1885,10 @@
   </si>
   <si>
     <t>别急,还差最后一步呢,种下的植物需要浇水,现在去河边打水回来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldWoman</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1983,6 +1988,852 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>TalkData!$A$169:$J$169</c:f>
+              <c:numCache>
+                <c:formatCode>@</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>1424</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-469A-455C-A869-043053ADB3E3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1721976016"/>
+        <c:axId val="1721980176"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1721976016"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1721980176"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1721980176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1721976016"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="9311355" cy="6079977"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2273,7 +3124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J465"/>
+  <dimension ref="A2:J466"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -7136,7 +7987,7 @@
         <v>564</v>
       </c>
       <c r="H166" s="1">
-        <v>0</v>
+        <v>1422</v>
       </c>
       <c r="I166" s="1">
         <v>0</v>
@@ -7220,22 +8071,22 @@
         <v>10</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>184</v>
+        <v>571</v>
       </c>
       <c r="E169" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>559</v>
       </c>
       <c r="H169" s="1">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I169" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J169" s="1" t="b">
         <v>0</v>
@@ -7243,31 +8094,31 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>1425</v>
+        <v>1600</v>
       </c>
       <c r="B170" s="3">
         <v>2</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>262</v>
+        <v>571</v>
       </c>
       <c r="E170" s="1">
         <v>1</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H170" s="1">
-        <v>1426</v>
+        <v>0</v>
       </c>
       <c r="I170" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J170" s="1" t="b">
         <v>0</v>
@@ -7275,31 +8126,31 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B171" s="3">
         <v>2</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="E171" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="H171" s="1">
-        <v>0</v>
+        <v>1426</v>
       </c>
       <c r="I171" s="1">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J171" s="1" t="b">
         <v>0</v>
@@ -7307,31 +8158,31 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B172" s="3">
         <v>2</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>262</v>
+        <v>184</v>
       </c>
       <c r="E172" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H172" s="1">
-        <v>1428</v>
+        <v>0</v>
       </c>
       <c r="I172" s="1">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="J172" s="1" t="b">
         <v>0</v>
@@ -7339,7 +8190,7 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B173" s="3">
         <v>2</v>
@@ -7351,19 +8202,19 @@
         <v>262</v>
       </c>
       <c r="E173" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H173" s="1">
-        <v>0</v>
+        <v>1428</v>
       </c>
       <c r="I173" s="1">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J173" s="1" t="b">
         <v>0</v>
@@ -7371,10 +8222,10 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>1429</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>561</v>
+        <v>1428</v>
+      </c>
+      <c r="B174" s="3">
+        <v>2</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>9</v>
@@ -7389,13 +8240,13 @@
         <v>189</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H174" s="1">
         <v>0</v>
       </c>
       <c r="I174" s="1">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="J174" s="1" t="b">
         <v>0</v>
@@ -7403,10 +8254,10 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>1430</v>
-      </c>
-      <c r="B175" s="3">
-        <v>2</v>
+        <v>1429</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>9</v>
@@ -7421,13 +8272,13 @@
         <v>189</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
       </c>
       <c r="I175" s="1">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="J175" s="1" t="b">
         <v>0</v>
@@ -7435,71 +8286,71 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B176" s="3">
         <v>2</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="E176" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G176" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="H176" s="1">
+        <v>0</v>
+      </c>
+      <c r="I176" s="1">
+        <v>82</v>
+      </c>
+      <c r="J176" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A177" s="1">
+        <v>1431</v>
+      </c>
+      <c r="B177" s="3">
+        <v>2</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E177" s="1">
+        <v>0</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G177" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H176" s="1">
+      <c r="H177" s="1">
         <v>1432</v>
       </c>
-      <c r="I176" s="1">
-        <v>0</v>
-      </c>
-      <c r="J176" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A177" s="1">
+      <c r="I177" s="1">
+        <v>0</v>
+      </c>
+      <c r="J177" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A178" s="1">
         <v>1432</v>
-      </c>
-      <c r="B177" s="3">
-        <v>2</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E177" s="1">
-        <v>1</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G177" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="H177" s="1">
-        <v>0</v>
-      </c>
-      <c r="I177" s="1">
-        <v>33</v>
-      </c>
-      <c r="J177" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A178" s="1">
-        <v>1433</v>
       </c>
       <c r="B178" s="3">
         <v>2</v>
@@ -7514,24 +8365,24 @@
         <v>1</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>111</v>
+        <v>570</v>
       </c>
       <c r="H178" s="1">
-        <v>1434</v>
+        <v>0</v>
       </c>
       <c r="I178" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J178" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B179" s="3">
         <v>2</v>
@@ -7546,24 +8397,24 @@
         <v>1</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>563</v>
+        <v>111</v>
       </c>
       <c r="H179" s="1">
-        <v>0</v>
+        <v>1434</v>
       </c>
       <c r="I179" s="1">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J179" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B180" s="3">
         <v>2</v>
@@ -7581,36 +8432,39 @@
         <v>255</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>112</v>
+        <v>563</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
       <c r="I180" s="1">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J180" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>1610</v>
+        <v>1435</v>
       </c>
       <c r="B181" s="3">
         <v>2</v>
       </c>
+      <c r="C181" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="D181" s="1" t="s">
-        <v>183</v>
+        <v>262</v>
       </c>
       <c r="E181" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -7624,7 +8478,7 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B182" s="3">
         <v>2</v>
@@ -7639,7 +8493,7 @@
         <v>255</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -7653,7 +8507,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B183" s="3">
         <v>2</v>
@@ -7668,7 +8522,7 @@
         <v>255</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>114</v>
+        <v>225</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -7682,7 +8536,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="B184" s="3">
         <v>2</v>
@@ -7697,7 +8551,7 @@
         <v>255</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -7711,7 +8565,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B185" s="3">
         <v>2</v>
@@ -7726,7 +8580,7 @@
         <v>255</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -7740,7 +8594,7 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B186" s="3">
         <v>2</v>
@@ -7755,7 +8609,7 @@
         <v>255</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -7769,7 +8623,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B187" s="3">
         <v>2</v>
@@ -7784,7 +8638,7 @@
         <v>255</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>116</v>
+        <v>227</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
@@ -7798,7 +8652,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B188" s="3">
         <v>2</v>
@@ -7813,7 +8667,7 @@
         <v>255</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
@@ -7827,7 +8681,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B189" s="3">
         <v>2</v>
@@ -7842,7 +8696,7 @@
         <v>255</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
@@ -7856,7 +8710,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B190" s="3">
         <v>2</v>
@@ -7871,7 +8725,7 @@
         <v>255</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -7885,7 +8739,7 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B191" s="3">
         <v>2</v>
@@ -7900,7 +8754,7 @@
         <v>255</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -7914,7 +8768,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B192" s="3">
         <v>2</v>
@@ -7929,7 +8783,7 @@
         <v>255</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -7943,7 +8797,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B193" s="3">
         <v>2</v>
@@ -7958,7 +8812,7 @@
         <v>255</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
@@ -7972,7 +8826,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B194" s="3">
         <v>2</v>
@@ -7987,7 +8841,7 @@
         <v>255</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
@@ -8001,7 +8855,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B195" s="3">
         <v>2</v>
@@ -8016,7 +8870,7 @@
         <v>255</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>228</v>
+        <v>123</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
@@ -8030,7 +8884,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B196" s="3">
         <v>2</v>
@@ -8045,7 +8899,7 @@
         <v>255</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>124</v>
+        <v>228</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -8059,7 +8913,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B197" s="3">
         <v>2</v>
@@ -8074,7 +8928,7 @@
         <v>255</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
@@ -8088,7 +8942,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B198" s="3">
         <v>2</v>
@@ -8103,7 +8957,7 @@
         <v>255</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -8117,7 +8971,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B199" s="3">
         <v>2</v>
@@ -8132,7 +8986,7 @@
         <v>255</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="H199" s="1">
         <v>0</v>
@@ -8146,7 +9000,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="B200" s="3">
         <v>2</v>
@@ -8161,7 +9015,7 @@
         <v>255</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="H200" s="1">
         <v>0</v>
@@ -8175,7 +9029,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B201" s="3">
         <v>2</v>
@@ -8190,7 +9044,7 @@
         <v>255</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H201" s="1">
         <v>0</v>
@@ -8204,7 +9058,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="B202" s="3">
         <v>2</v>
@@ -8219,7 +9073,7 @@
         <v>255</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
@@ -8231,9 +9085,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="B203" s="3">
         <v>2</v>
@@ -8248,7 +9102,7 @@
         <v>255</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>129</v>
+        <v>230</v>
       </c>
       <c r="H203" s="1">
         <v>0</v>
@@ -8260,9 +9114,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B204" s="3">
         <v>2</v>
@@ -8277,7 +9131,7 @@
         <v>255</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -8291,7 +9145,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B205" s="3">
         <v>2</v>
@@ -8306,7 +9160,7 @@
         <v>255</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -8320,7 +9174,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B206" s="3">
         <v>2</v>
@@ -8335,7 +9189,7 @@
         <v>255</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
@@ -8349,7 +9203,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="B207" s="3">
         <v>2</v>
@@ -8364,7 +9218,7 @@
         <v>255</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -8378,7 +9232,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="B208" s="3">
         <v>2</v>
@@ -8393,7 +9247,7 @@
         <v>255</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -8405,9 +9259,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B209" s="3">
         <v>2</v>
@@ -8422,7 +9276,7 @@
         <v>255</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
@@ -8434,9 +9288,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B210" s="3">
         <v>2</v>
@@ -8451,7 +9305,7 @@
         <v>255</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
@@ -8463,9 +9317,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B211" s="3">
         <v>2</v>
@@ -8480,7 +9334,7 @@
         <v>255</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -8492,9 +9346,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B212" s="3">
         <v>2</v>
@@ -8509,7 +9363,7 @@
         <v>255</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
@@ -8523,7 +9377,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="B213" s="3">
         <v>2</v>
@@ -8538,7 +9392,7 @@
         <v>255</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -8552,7 +9406,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B214" s="3">
         <v>2</v>
@@ -8567,7 +9421,7 @@
         <v>255</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -8581,7 +9435,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="B215" s="3">
         <v>2</v>
@@ -8596,7 +9450,7 @@
         <v>255</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -8610,7 +9464,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B216" s="3">
         <v>2</v>
@@ -8625,7 +9479,7 @@
         <v>255</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -8637,9 +9491,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B217" s="3">
         <v>2</v>
@@ -8654,7 +9508,7 @@
         <v>255</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H217" s="1">
         <v>0</v>
@@ -8668,7 +9522,7 @@
     </row>
     <row r="218" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="B218" s="3">
         <v>2</v>
@@ -8683,7 +9537,7 @@
         <v>255</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>307</v>
+        <v>143</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
@@ -8695,9 +9549,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="B219" s="3">
         <v>2</v>
@@ -8712,7 +9566,7 @@
         <v>255</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>144</v>
+        <v>307</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
@@ -8726,7 +9580,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1500</v>
+        <v>1648</v>
       </c>
       <c r="B220" s="3">
         <v>2</v>
@@ -8741,7 +9595,7 @@
         <v>255</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H220" s="1">
         <v>0</v>
@@ -8755,7 +9609,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B221" s="3">
         <v>2</v>
@@ -8770,7 +9624,7 @@
         <v>255</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H221" s="1">
         <v>0</v>
@@ -8784,7 +9638,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B222" s="3">
         <v>2</v>
@@ -8799,7 +9653,7 @@
         <v>255</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -8813,7 +9667,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B223" s="3">
         <v>2</v>
@@ -8828,7 +9682,7 @@
         <v>255</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -8842,7 +9696,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B224" s="3">
         <v>2</v>
@@ -8857,7 +9711,7 @@
         <v>255</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H224" s="1">
         <v>0</v>
@@ -8871,7 +9725,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B225" s="3">
         <v>2</v>
@@ -8886,7 +9740,7 @@
         <v>255</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H225" s="1">
         <v>0</v>
@@ -8900,7 +9754,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B226" s="3">
         <v>2</v>
@@ -8915,7 +9769,7 @@
         <v>255</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H226" s="1">
         <v>0</v>
@@ -8929,7 +9783,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B227" s="3">
         <v>2</v>
@@ -8944,7 +9798,7 @@
         <v>255</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
@@ -8958,7 +9812,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B228" s="3">
         <v>2</v>
@@ -8973,7 +9827,7 @@
         <v>255</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -8987,7 +9841,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B229" s="3">
         <v>2</v>
@@ -9002,7 +9856,7 @@
         <v>255</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -9016,7 +9870,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B230" s="3">
         <v>2</v>
@@ -9031,7 +9885,7 @@
         <v>255</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>231</v>
+        <v>154</v>
       </c>
       <c r="H230" s="1">
         <v>0</v>
@@ -9045,7 +9899,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B231" s="3">
         <v>2</v>
@@ -9060,7 +9914,7 @@
         <v>255</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -9074,7 +9928,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B232" s="3">
         <v>2</v>
@@ -9089,7 +9943,7 @@
         <v>255</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>232</v>
+        <v>155</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -9103,7 +9957,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B233" s="3">
         <v>2</v>
@@ -9118,7 +9972,7 @@
         <v>255</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H233" s="1">
         <v>0</v>
@@ -9132,7 +9986,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B234" s="3">
         <v>2</v>
@@ -9147,7 +10001,7 @@
         <v>255</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
@@ -9161,7 +10015,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="B235" s="3">
         <v>2</v>
@@ -9176,7 +10030,7 @@
         <v>255</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -9190,7 +10044,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B236" s="3">
         <v>2</v>
@@ -9205,7 +10059,7 @@
         <v>255</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -9219,7 +10073,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B237" s="3">
         <v>2</v>
@@ -9234,7 +10088,7 @@
         <v>255</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -9248,7 +10102,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B238" s="3">
         <v>2</v>
@@ -9263,7 +10117,7 @@
         <v>255</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -9277,7 +10131,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B239" s="3">
         <v>2</v>
@@ -9292,7 +10146,7 @@
         <v>255</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
@@ -9306,7 +10160,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1600</v>
+        <v>1519</v>
       </c>
       <c r="B240" s="3">
         <v>2</v>
@@ -9321,7 +10175,7 @@
         <v>255</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H240" s="1">
         <v>0</v>
@@ -9335,7 +10189,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>2001</v>
+        <v>1600</v>
       </c>
       <c r="B241" s="3">
         <v>2</v>
@@ -9350,7 +10204,7 @@
         <v>255</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>239</v>
+        <v>157</v>
       </c>
       <c r="H241" s="1">
         <v>0</v>
@@ -9364,7 +10218,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B242" s="3">
         <v>2</v>
@@ -9379,7 +10233,7 @@
         <v>255</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>158</v>
+        <v>239</v>
       </c>
       <c r="H242" s="1">
         <v>0</v>
@@ -9393,7 +10247,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B243" s="3">
         <v>2</v>
@@ -9408,7 +10262,7 @@
         <v>255</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="H243" s="1">
         <v>0</v>
@@ -9422,7 +10276,7 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B244" s="3">
         <v>2</v>
@@ -9437,7 +10291,7 @@
         <v>255</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H244" s="1">
         <v>0</v>
@@ -9451,7 +10305,7 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B245" s="3">
         <v>2</v>
@@ -9466,7 +10320,7 @@
         <v>255</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
@@ -9480,7 +10334,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B246" s="3">
         <v>2</v>
@@ -9495,7 +10349,7 @@
         <v>255</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H246" s="1">
         <v>0</v>
@@ -9509,7 +10363,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B247" s="3">
         <v>2</v>
@@ -9524,7 +10378,7 @@
         <v>255</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -9538,7 +10392,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B248" s="3">
         <v>2</v>
@@ -9553,7 +10407,7 @@
         <v>255</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -9567,7 +10421,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B249" s="3">
         <v>2</v>
@@ -9582,7 +10436,7 @@
         <v>255</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
@@ -9596,7 +10450,7 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B250" s="3">
         <v>2</v>
@@ -9611,7 +10465,7 @@
         <v>255</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
@@ -9625,7 +10479,7 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B251" s="3">
         <v>2</v>
@@ -9640,7 +10494,7 @@
         <v>255</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>159</v>
+        <v>247</v>
       </c>
       <c r="H251" s="1">
         <v>0</v>
@@ -9654,7 +10508,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B252" s="3">
         <v>2</v>
@@ -9669,7 +10523,7 @@
         <v>255</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
@@ -9683,7 +10537,7 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B253" s="3">
         <v>2</v>
@@ -9698,7 +10552,7 @@
         <v>255</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H253" s="1">
         <v>0</v>
@@ -9712,7 +10566,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B254" s="3">
         <v>2</v>
@@ -9727,7 +10581,7 @@
         <v>255</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
@@ -9741,7 +10595,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B255" s="3">
         <v>2</v>
@@ -9756,7 +10610,7 @@
         <v>255</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H255" s="1">
         <v>0</v>
@@ -9770,7 +10624,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B256" s="3">
         <v>2</v>
@@ -9785,7 +10639,7 @@
         <v>255</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>248</v>
+        <v>163</v>
       </c>
       <c r="H256" s="1">
         <v>0</v>
@@ -9799,7 +10653,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B257" s="3">
         <v>2</v>
@@ -9814,7 +10668,7 @@
         <v>255</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>164</v>
+        <v>248</v>
       </c>
       <c r="H257" s="1">
         <v>0</v>
@@ -9828,7 +10682,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B258" s="3">
         <v>2</v>
@@ -9843,7 +10697,7 @@
         <v>255</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H258" s="1">
         <v>0</v>
@@ -9857,7 +10711,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B259" s="3">
         <v>2</v>
@@ -9872,7 +10726,7 @@
         <v>255</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
@@ -9886,7 +10740,7 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B260" s="3">
         <v>2</v>
@@ -9901,7 +10755,7 @@
         <v>255</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="H260" s="1">
         <v>0</v>
@@ -9915,7 +10769,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B261" s="3">
         <v>2</v>
@@ -9930,7 +10784,7 @@
         <v>255</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -9944,7 +10798,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B262" s="3">
         <v>2</v>
@@ -9959,7 +10813,7 @@
         <v>255</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H262" s="1">
         <v>0</v>
@@ -9973,7 +10827,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B263" s="3">
         <v>2</v>
@@ -9988,7 +10842,7 @@
         <v>255</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H263" s="1">
         <v>0</v>
@@ -10002,7 +10856,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B264" s="3">
         <v>2</v>
@@ -10017,7 +10871,7 @@
         <v>255</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
@@ -10031,28 +10885,25 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B265" s="3">
         <v>2</v>
       </c>
-      <c r="C265" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="D265" s="1" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="E265" s="1">
         <v>0</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H265" s="1">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="I265" s="1">
         <v>0</v>
@@ -10063,28 +10914,28 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B266" s="3">
         <v>2</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E266" s="1">
         <v>0</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>252</v>
+        <v>171</v>
       </c>
       <c r="H266" s="1">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="I266" s="1">
         <v>0</v>
@@ -10095,28 +10946,28 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B267" s="3">
         <v>2</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>10</v>
+        <v>251</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="E267" s="1">
         <v>0</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>172</v>
+        <v>252</v>
       </c>
       <c r="H267" s="1">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="I267" s="1">
         <v>0</v>
@@ -10127,16 +10978,16 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B268" s="3">
         <v>2</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
       <c r="E268" s="1">
         <v>0</v>
@@ -10145,10 +10996,10 @@
         <v>256</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H268" s="1">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="I268" s="1">
         <v>0</v>
@@ -10159,16 +11010,16 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B269" s="3">
         <v>2</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E269" s="1">
         <v>0</v>
@@ -10177,10 +11028,10 @@
         <v>256</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H269" s="1">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="I269" s="1">
         <v>0</v>
@@ -10191,28 +11042,28 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B270" s="3">
         <v>2</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>10</v>
+        <v>251</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="E270" s="1">
         <v>0</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H270" s="1">
-        <v>0</v>
+        <v>1514</v>
       </c>
       <c r="I270" s="1">
         <v>0</v>
@@ -10223,7 +11074,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B271" s="3">
         <v>2</v>
@@ -10241,7 +11092,7 @@
         <v>255</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H271" s="1">
         <v>0</v>
@@ -10255,28 +11106,28 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B272" s="3">
         <v>2</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>257</v>
+        <v>184</v>
       </c>
       <c r="E272" s="1">
         <v>0</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H272" s="1">
-        <v>1517</v>
+        <v>0</v>
       </c>
       <c r="I272" s="1">
         <v>0</v>
@@ -10287,28 +11138,28 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B273" s="3">
         <v>2</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E273" s="1">
         <v>0</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H273" s="1">
-        <v>0</v>
+        <v>1517</v>
       </c>
       <c r="I273" s="1">
         <v>0</v>
@@ -10319,28 +11170,28 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B274" s="3">
         <v>2</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="E274" s="1">
         <v>0</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H274" s="1">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="I274" s="1">
         <v>0</v>
@@ -10351,28 +11202,28 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>2100</v>
+        <v>2034</v>
       </c>
       <c r="B275" s="3">
         <v>2</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>257</v>
+        <v>184</v>
       </c>
       <c r="E275" s="1">
         <v>0</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>253</v>
+        <v>179</v>
       </c>
       <c r="H275" s="1">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="I275" s="1">
         <v>0</v>
@@ -10383,13 +11234,16 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B276" s="3">
         <v>2</v>
       </c>
+      <c r="C276" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="D276" s="1" t="s">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="E276" s="1">
         <v>0</v>
@@ -10398,7 +11252,7 @@
         <v>255</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
@@ -10412,7 +11266,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>8888</v>
+        <v>2101</v>
       </c>
       <c r="B277" s="3">
         <v>2</v>
@@ -10427,7 +11281,7 @@
         <v>255</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="H277" s="1">
         <v>0</v>
@@ -10441,7 +11295,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>3000</v>
+        <v>8888</v>
       </c>
       <c r="B278" s="3">
         <v>2</v>
@@ -10453,10 +11307,10 @@
         <v>0</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="H278" s="1">
         <v>0</v>
@@ -10470,7 +11324,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="B279" s="3">
         <v>2</v>
@@ -10485,7 +11339,7 @@
         <v>181</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H279" s="1">
         <v>0</v>
@@ -10499,7 +11353,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B280" s="3">
         <v>2</v>
@@ -10514,7 +11368,7 @@
         <v>181</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H280" s="1">
         <v>0</v>
@@ -10528,7 +11382,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="B281" s="3">
         <v>2</v>
@@ -10543,7 +11397,7 @@
         <v>181</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H281" s="1">
         <v>0</v>
@@ -10557,7 +11411,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B282" s="3">
         <v>2</v>
@@ -10572,7 +11426,7 @@
         <v>181</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
@@ -10586,7 +11440,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="B283" s="3">
         <v>2</v>
@@ -10601,7 +11455,7 @@
         <v>181</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="H283" s="1">
         <v>0</v>
@@ -10615,13 +11469,13 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B284" s="3">
         <v>2</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="E284" s="1">
         <v>0</v>
@@ -10630,7 +11484,7 @@
         <v>181</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H284" s="1">
         <v>0</v>
@@ -10644,7 +11498,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B285" s="3">
         <v>2</v>
@@ -10656,10 +11510,10 @@
         <v>0</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
@@ -10673,7 +11527,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B286" s="3">
         <v>2</v>
@@ -10685,10 +11539,10 @@
         <v>0</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H286" s="1">
         <v>0</v>
@@ -10702,7 +11556,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="B287" s="3">
         <v>2</v>
@@ -10717,7 +11571,7 @@
         <v>181</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H287" s="1">
         <v>0</v>
@@ -10731,7 +11585,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B288" s="3">
         <v>2</v>
@@ -10746,7 +11600,7 @@
         <v>181</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H288" s="1">
         <v>0</v>
@@ -10760,7 +11614,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="B289" s="3">
         <v>2</v>
@@ -10775,7 +11629,7 @@
         <v>181</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H289" s="1">
         <v>0</v>
@@ -10789,7 +11643,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B290" s="3">
         <v>2</v>
@@ -10804,7 +11658,7 @@
         <v>181</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -10818,7 +11672,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B291" s="3">
         <v>2</v>
@@ -10833,7 +11687,7 @@
         <v>181</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -10847,7 +11701,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>3200</v>
+        <v>3014</v>
       </c>
       <c r="B292" s="3">
         <v>2</v>
@@ -10862,7 +11716,7 @@
         <v>181</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H292" s="1">
         <v>0</v>
@@ -10876,7 +11730,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B293" s="3">
         <v>2</v>
@@ -10891,7 +11745,7 @@
         <v>181</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H293" s="1">
         <v>0</v>
@@ -10905,10 +11759,10 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>4000</v>
-      </c>
-      <c r="B294" s="3" t="s">
-        <v>480</v>
+        <v>3201</v>
+      </c>
+      <c r="B294" s="3">
+        <v>2</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>274</v>
@@ -10920,7 +11774,7 @@
         <v>181</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="H294" s="1">
         <v>0</v>
@@ -10929,12 +11783,12 @@
         <v>0</v>
       </c>
       <c r="J294" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>480</v>
@@ -10949,21 +11803,21 @@
         <v>181</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H295" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I295" s="1">
         <v>0</v>
       </c>
       <c r="J295" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>480</v>
@@ -10978,7 +11832,7 @@
         <v>181</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>45</v>
+        <v>354</v>
       </c>
       <c r="H296" s="1">
         <v>4000</v>
@@ -10990,9 +11844,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>480</v>
@@ -11007,7 +11861,7 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>355</v>
+        <v>45</v>
       </c>
       <c r="H297" s="1">
         <v>4000</v>
@@ -11019,9 +11873,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>480</v>
@@ -11036,7 +11890,7 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H298" s="1">
         <v>4000</v>
@@ -11050,7 +11904,7 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>480</v>
@@ -11065,21 +11919,21 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H299" s="1">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I299" s="1">
         <v>0</v>
       </c>
       <c r="J299" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>480</v>
@@ -11094,21 +11948,21 @@
         <v>181</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H300" s="1">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="I300" s="1">
         <v>0</v>
       </c>
       <c r="J300" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>480</v>
@@ -11123,7 +11977,7 @@
         <v>181</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H301" s="1">
         <v>4005</v>
@@ -11137,7 +11991,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>480</v>
@@ -11152,7 +12006,7 @@
         <v>181</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H302" s="1">
         <v>4005</v>
@@ -11166,7 +12020,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>480</v>
@@ -11181,7 +12035,7 @@
         <v>181</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H303" s="1">
         <v>4005</v>
@@ -11195,7 +12049,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>480</v>
@@ -11210,7 +12064,7 @@
         <v>181</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H304" s="1">
         <v>4005</v>
@@ -11224,7 +12078,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>480</v>
@@ -11239,21 +12093,21 @@
         <v>181</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H305" s="1">
-        <v>0</v>
+        <v>4005</v>
       </c>
       <c r="I305" s="1">
         <v>0</v>
       </c>
       <c r="J305" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>480</v>
@@ -11268,21 +12122,21 @@
         <v>181</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>49</v>
+        <v>363</v>
       </c>
       <c r="H306" s="1">
-        <v>4011</v>
+        <v>0</v>
       </c>
       <c r="I306" s="1">
         <v>0</v>
       </c>
       <c r="J306" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>480</v>
@@ -11297,7 +12151,7 @@
         <v>181</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>364</v>
+        <v>49</v>
       </c>
       <c r="H307" s="1">
         <v>4011</v>
@@ -11309,9 +12163,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>480</v>
@@ -11326,7 +12180,7 @@
         <v>181</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H308" s="1">
         <v>4011</v>
@@ -11340,7 +12194,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>480</v>
@@ -11355,7 +12209,7 @@
         <v>181</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H309" s="1">
         <v>4011</v>
@@ -11369,7 +12223,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>480</v>
@@ -11384,21 +12238,21 @@
         <v>181</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H310" s="1">
-        <v>0</v>
+        <v>4011</v>
       </c>
       <c r="I310" s="1">
         <v>0</v>
       </c>
       <c r="J310" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>480</v>
@@ -11413,21 +12267,21 @@
         <v>181</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>56</v>
+        <v>367</v>
       </c>
       <c r="H311" s="1">
-        <v>4016</v>
+        <v>0</v>
       </c>
       <c r="I311" s="1">
         <v>0</v>
       </c>
       <c r="J311" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>480</v>
@@ -11442,7 +12296,7 @@
         <v>181</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="H312" s="1">
         <v>4016</v>
@@ -11456,7 +12310,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>480</v>
@@ -11471,7 +12325,7 @@
         <v>181</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H313" s="1">
         <v>4016</v>
@@ -11485,7 +12339,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>480</v>
@@ -11500,7 +12354,7 @@
         <v>181</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H314" s="1">
         <v>4016</v>
@@ -11514,7 +12368,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>480</v>
@@ -11529,21 +12383,21 @@
         <v>181</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H315" s="1">
-        <v>0</v>
+        <v>4016</v>
       </c>
       <c r="I315" s="1">
         <v>0</v>
       </c>
       <c r="J315" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>480</v>
@@ -11558,21 +12412,21 @@
         <v>181</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H316" s="1">
-        <v>4021</v>
+        <v>0</v>
       </c>
       <c r="I316" s="1">
         <v>0</v>
       </c>
       <c r="J316" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>480</v>
@@ -11587,7 +12441,7 @@
         <v>181</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H317" s="1">
         <v>4021</v>
@@ -11599,9 +12453,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>480</v>
@@ -11616,7 +12470,7 @@
         <v>181</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H318" s="1">
         <v>4021</v>
@@ -11628,9 +12482,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>480</v>
@@ -11645,7 +12499,7 @@
         <v>181</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H319" s="1">
         <v>4021</v>
@@ -11657,9 +12511,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>480</v>
@@ -11674,21 +12528,21 @@
         <v>181</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H320" s="1">
-        <v>0</v>
+        <v>4021</v>
       </c>
       <c r="I320" s="1">
         <v>0</v>
       </c>
       <c r="J320" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>480</v>
@@ -11703,21 +12557,21 @@
         <v>181</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H321" s="1">
-        <v>4026</v>
+        <v>0</v>
       </c>
       <c r="I321" s="1">
         <v>0</v>
       </c>
       <c r="J321" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>480</v>
@@ -11732,7 +12586,7 @@
         <v>181</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H322" s="1">
         <v>4026</v>
@@ -11746,7 +12600,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>480</v>
@@ -11761,7 +12615,7 @@
         <v>181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H323" s="1">
         <v>4026</v>
@@ -11775,7 +12629,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>480</v>
@@ -11790,7 +12644,7 @@
         <v>181</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H324" s="1">
         <v>4026</v>
@@ -11804,7 +12658,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>480</v>
@@ -11819,21 +12673,21 @@
         <v>181</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H325" s="1">
-        <v>0</v>
+        <v>4026</v>
       </c>
       <c r="I325" s="1">
         <v>0</v>
       </c>
       <c r="J325" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>480</v>
@@ -11848,21 +12702,21 @@
         <v>181</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H326" s="1">
-        <v>4031</v>
+        <v>0</v>
       </c>
       <c r="I326" s="1">
         <v>0</v>
       </c>
       <c r="J326" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>480</v>
@@ -11877,7 +12731,7 @@
         <v>181</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H327" s="1">
         <v>4031</v>
@@ -11889,9 +12743,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>480</v>
@@ -11906,7 +12760,7 @@
         <v>181</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H328" s="1">
         <v>4031</v>
@@ -11918,9 +12772,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>480</v>
@@ -11935,7 +12789,7 @@
         <v>181</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H329" s="1">
         <v>4031</v>
@@ -11947,9 +12801,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>480</v>
@@ -11964,21 +12818,21 @@
         <v>181</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H330" s="1">
-        <v>0</v>
+        <v>4031</v>
       </c>
       <c r="I330" s="1">
         <v>0</v>
       </c>
       <c r="J330" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>480</v>
@@ -11993,21 +12847,21 @@
         <v>181</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H331" s="1">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="I331" s="1">
         <v>0</v>
       </c>
       <c r="J331" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>480</v>
@@ -12022,7 +12876,7 @@
         <v>181</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H332" s="1">
         <v>4036</v>
@@ -12036,7 +12890,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>480</v>
@@ -12051,7 +12905,7 @@
         <v>181</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H333" s="1">
         <v>4036</v>
@@ -12065,7 +12919,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>480</v>
@@ -12080,7 +12934,7 @@
         <v>181</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H334" s="1">
         <v>4036</v>
@@ -12094,7 +12948,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>480</v>
@@ -12109,21 +12963,21 @@
         <v>181</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H335" s="1">
-        <v>0</v>
+        <v>4036</v>
       </c>
       <c r="I335" s="1">
         <v>0</v>
       </c>
       <c r="J335" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>480</v>
@@ -12138,21 +12992,21 @@
         <v>181</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H336" s="1">
-        <v>4041</v>
+        <v>0</v>
       </c>
       <c r="I336" s="1">
         <v>0</v>
       </c>
       <c r="J336" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>480</v>
@@ -12167,7 +13021,7 @@
         <v>181</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="H337" s="1">
         <v>4041</v>
@@ -12179,9 +13033,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>480</v>
@@ -12196,7 +13050,7 @@
         <v>181</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="H338" s="1">
         <v>4041</v>
@@ -12210,7 +13064,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>480</v>
@@ -12225,7 +13079,7 @@
         <v>181</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>393</v>
+        <v>219</v>
       </c>
       <c r="H339" s="1">
         <v>4041</v>
@@ -12239,7 +13093,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>480</v>
@@ -12254,21 +13108,21 @@
         <v>181</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H340" s="1">
-        <v>0</v>
+        <v>4041</v>
       </c>
       <c r="I340" s="1">
         <v>0</v>
       </c>
       <c r="J340" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>480</v>
@@ -12283,21 +13137,21 @@
         <v>181</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H341" s="1">
-        <v>4046</v>
+        <v>0</v>
       </c>
       <c r="I341" s="1">
         <v>0</v>
       </c>
       <c r="J341" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>480</v>
@@ -12312,7 +13166,7 @@
         <v>181</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>61</v>
+        <v>395</v>
       </c>
       <c r="H342" s="1">
         <v>4046</v>
@@ -12324,9 +13178,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>480</v>
@@ -12341,7 +13195,7 @@
         <v>181</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H343" s="1">
         <v>4046</v>
@@ -12355,7 +13209,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>4050</v>
+        <v>4049</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>480</v>
@@ -12370,7 +13224,7 @@
         <v>181</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>396</v>
+        <v>62</v>
       </c>
       <c r="H344" s="1">
         <v>4046</v>
@@ -12384,7 +13238,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>480</v>
@@ -12399,21 +13253,21 @@
         <v>181</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H345" s="1">
-        <v>0</v>
+        <v>4046</v>
       </c>
       <c r="I345" s="1">
         <v>0</v>
       </c>
       <c r="J345" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>480</v>
@@ -12428,21 +13282,21 @@
         <v>181</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H346" s="1">
-        <v>4051</v>
+        <v>0</v>
       </c>
       <c r="I346" s="1">
         <v>0</v>
       </c>
       <c r="J346" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>480</v>
@@ -12457,7 +13311,7 @@
         <v>181</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H347" s="1">
         <v>4051</v>
@@ -12471,7 +13325,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>480</v>
@@ -12486,7 +13340,7 @@
         <v>181</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H348" s="1">
         <v>4051</v>
@@ -12500,7 +13354,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>480</v>
@@ -12515,7 +13369,7 @@
         <v>181</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H349" s="1">
         <v>4051</v>
@@ -12529,7 +13383,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>4056</v>
+        <v>4055</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>480</v>
@@ -12544,21 +13398,21 @@
         <v>181</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H350" s="1">
-        <v>0</v>
+        <v>4051</v>
       </c>
       <c r="I350" s="1">
         <v>0</v>
       </c>
       <c r="J350" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>480</v>
@@ -12573,21 +13427,21 @@
         <v>181</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H351" s="1">
-        <v>4056</v>
+        <v>0</v>
       </c>
       <c r="I351" s="1">
         <v>0</v>
       </c>
       <c r="J351" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>480</v>
@@ -12602,7 +13456,7 @@
         <v>181</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H352" s="1">
         <v>4056</v>
@@ -12616,7 +13470,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>480</v>
@@ -12631,7 +13485,7 @@
         <v>181</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H353" s="1">
         <v>4056</v>
@@ -12645,7 +13499,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>480</v>
@@ -12660,7 +13514,7 @@
         <v>181</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H354" s="1">
         <v>4056</v>
@@ -12674,7 +13528,7 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>4061</v>
+        <v>4060</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>480</v>
@@ -12689,21 +13543,21 @@
         <v>181</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H355" s="1">
-        <v>0</v>
+        <v>4056</v>
       </c>
       <c r="I355" s="1">
         <v>0</v>
       </c>
       <c r="J355" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>480</v>
@@ -12718,21 +13572,21 @@
         <v>181</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H356" s="1">
-        <v>4061</v>
+        <v>0</v>
       </c>
       <c r="I356" s="1">
         <v>0</v>
       </c>
       <c r="J356" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>480</v>
@@ -12747,7 +13601,7 @@
         <v>181</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>51</v>
+        <v>408</v>
       </c>
       <c r="H357" s="1">
         <v>4061</v>
@@ -12759,9 +13613,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>480</v>
@@ -12776,7 +13630,7 @@
         <v>181</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H358" s="1">
         <v>4061</v>
@@ -12790,7 +13644,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>480</v>
@@ -12805,7 +13659,7 @@
         <v>181</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>409</v>
+        <v>58</v>
       </c>
       <c r="H359" s="1">
         <v>4061</v>
@@ -12817,9 +13671,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>4066</v>
+        <v>4065</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>480</v>
@@ -12834,21 +13688,21 @@
         <v>181</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H360" s="1">
-        <v>0</v>
+        <v>4061</v>
       </c>
       <c r="I360" s="1">
         <v>0</v>
       </c>
       <c r="J360" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>480</v>
@@ -12863,21 +13717,21 @@
         <v>181</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="H361" s="1">
-        <v>4066</v>
+        <v>0</v>
       </c>
       <c r="I361" s="1">
         <v>0</v>
       </c>
       <c r="J361" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>480</v>
@@ -12892,7 +13746,7 @@
         <v>181</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="H362" s="1">
         <v>4066</v>
@@ -12904,9 +13758,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>4069</v>
+        <v>4068</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>480</v>
@@ -12921,7 +13775,7 @@
         <v>181</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>65</v>
+        <v>411</v>
       </c>
       <c r="H363" s="1">
         <v>4066</v>
@@ -12933,9 +13787,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>480</v>
@@ -12950,7 +13804,7 @@
         <v>181</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>412</v>
+        <v>65</v>
       </c>
       <c r="H364" s="1">
         <v>4066</v>
@@ -12964,7 +13818,7 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>480</v>
@@ -12979,21 +13833,21 @@
         <v>181</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H365" s="1">
-        <v>0</v>
+        <v>4066</v>
       </c>
       <c r="I365" s="1">
         <v>0</v>
       </c>
       <c r="J365" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>480</v>
@@ -13008,21 +13862,21 @@
         <v>181</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>68</v>
+        <v>413</v>
       </c>
       <c r="H366" s="1">
-        <v>4071</v>
+        <v>0</v>
       </c>
       <c r="I366" s="1">
         <v>0</v>
       </c>
       <c r="J366" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>480</v>
@@ -13037,7 +13891,7 @@
         <v>181</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H367" s="1">
         <v>4071</v>
@@ -13051,7 +13905,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>480</v>
@@ -13066,7 +13920,7 @@
         <v>181</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="H368" s="1">
         <v>4071</v>
@@ -13080,7 +13934,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>480</v>
@@ -13095,7 +13949,7 @@
         <v>181</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H369" s="1">
         <v>4071</v>
@@ -13109,7 +13963,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>480</v>
@@ -13124,21 +13978,21 @@
         <v>181</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H370" s="1">
-        <v>0</v>
+        <v>4071</v>
       </c>
       <c r="I370" s="1">
         <v>0</v>
       </c>
       <c r="J370" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>480</v>
@@ -13153,21 +14007,21 @@
         <v>181</v>
       </c>
       <c r="G371" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H371" s="1">
-        <v>4076</v>
+        <v>0</v>
       </c>
       <c r="I371" s="1">
         <v>0</v>
       </c>
       <c r="J371" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>480</v>
@@ -13182,7 +14036,7 @@
         <v>181</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H372" s="1">
         <v>4076</v>
@@ -13196,7 +14050,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>480</v>
@@ -13211,7 +14065,7 @@
         <v>181</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H373" s="1">
         <v>4076</v>
@@ -13225,7 +14079,7 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>4080</v>
+        <v>4079</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>480</v>
@@ -13240,7 +14094,7 @@
         <v>181</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H374" s="1">
         <v>4076</v>
@@ -13254,7 +14108,7 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>4081</v>
+        <v>4080</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>480</v>
@@ -13269,21 +14123,21 @@
         <v>181</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H375" s="1">
-        <v>0</v>
+        <v>4076</v>
       </c>
       <c r="I375" s="1">
         <v>0</v>
       </c>
       <c r="J375" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>480</v>
@@ -13298,21 +14152,21 @@
         <v>181</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="H376" s="1">
-        <v>4081</v>
+        <v>0</v>
       </c>
       <c r="I376" s="1">
         <v>0</v>
       </c>
       <c r="J376" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>480</v>
@@ -13327,7 +14181,7 @@
         <v>181</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H377" s="1">
         <v>4081</v>
@@ -13341,7 +14195,7 @@
     </row>
     <row r="378" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>4084</v>
+        <v>4083</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>480</v>
@@ -13356,7 +14210,7 @@
         <v>181</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>329</v>
+        <v>59</v>
       </c>
       <c r="H378" s="1">
         <v>4081</v>
@@ -13368,9 +14222,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>480</v>
@@ -13385,7 +14239,7 @@
         <v>181</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>422</v>
+        <v>329</v>
       </c>
       <c r="H379" s="1">
         <v>4081</v>
@@ -13399,7 +14253,7 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>480</v>
@@ -13414,21 +14268,21 @@
         <v>181</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H380" s="1">
-        <v>0</v>
+        <v>4081</v>
       </c>
       <c r="I380" s="1">
         <v>0</v>
       </c>
       <c r="J380" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>4087</v>
+        <v>4086</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>480</v>
@@ -13443,21 +14297,21 @@
         <v>181</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H381" s="1">
-        <v>4086</v>
+        <v>0</v>
       </c>
       <c r="I381" s="1">
         <v>0</v>
       </c>
       <c r="J381" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>4088</v>
+        <v>4087</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>480</v>
@@ -13472,7 +14326,7 @@
         <v>181</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H382" s="1">
         <v>4086</v>
@@ -13486,7 +14340,7 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>4089</v>
+        <v>4088</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>480</v>
@@ -13501,7 +14355,7 @@
         <v>181</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H383" s="1">
         <v>4086</v>
@@ -13515,7 +14369,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>480</v>
@@ -13530,7 +14384,7 @@
         <v>181</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H384" s="1">
         <v>4086</v>
@@ -13544,7 +14398,7 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>4091</v>
+        <v>4090</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>480</v>
@@ -13559,21 +14413,21 @@
         <v>181</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H385" s="1">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="I385" s="1">
         <v>0</v>
       </c>
       <c r="J385" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>480</v>
@@ -13588,21 +14442,21 @@
         <v>181</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H386" s="1">
-        <v>4091</v>
+        <v>0</v>
       </c>
       <c r="I386" s="1">
         <v>0</v>
       </c>
       <c r="J386" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>4093</v>
+        <v>4092</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>480</v>
@@ -13617,7 +14471,7 @@
         <v>181</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H387" s="1">
         <v>4091</v>
@@ -13631,7 +14485,7 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>4094</v>
+        <v>4093</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>480</v>
@@ -13646,7 +14500,7 @@
         <v>181</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H388" s="1">
         <v>4091</v>
@@ -13660,7 +14514,7 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>4095</v>
+        <v>4094</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>480</v>
@@ -13675,7 +14529,7 @@
         <v>181</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H389" s="1">
         <v>4091</v>
@@ -13689,7 +14543,7 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>480</v>
@@ -13704,21 +14558,21 @@
         <v>181</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H390" s="1">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="I390" s="1">
         <v>0</v>
       </c>
       <c r="J390" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>4097</v>
+        <v>4096</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>480</v>
@@ -13733,21 +14587,21 @@
         <v>181</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H391" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="I391" s="1">
         <v>0</v>
       </c>
       <c r="J391" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>4098</v>
+        <v>4097</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>480</v>
@@ -13762,7 +14616,7 @@
         <v>181</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H392" s="1">
         <v>4096</v>
@@ -13776,7 +14630,7 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>4099</v>
+        <v>4098</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>480</v>
@@ -13791,7 +14645,7 @@
         <v>181</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H393" s="1">
         <v>4096</v>
@@ -13805,7 +14659,7 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>4100</v>
+        <v>4099</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>480</v>
@@ -13820,7 +14674,7 @@
         <v>181</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H394" s="1">
         <v>4096</v>
@@ -13834,7 +14688,7 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>480</v>
@@ -13849,21 +14703,21 @@
         <v>181</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H395" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="I395" s="1">
         <v>0</v>
       </c>
       <c r="J395" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>480</v>
@@ -13878,21 +14732,21 @@
         <v>181</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="H396" s="1">
-        <v>4101</v>
+        <v>0</v>
       </c>
       <c r="I396" s="1">
         <v>0</v>
       </c>
       <c r="J396" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>480</v>
@@ -13907,7 +14761,7 @@
         <v>181</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H397" s="1">
         <v>4101</v>
@@ -13919,9 +14773,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>480</v>
@@ -13936,7 +14790,7 @@
         <v>181</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="H398" s="1">
         <v>4101</v>
@@ -13950,7 +14804,7 @@
     </row>
     <row r="399" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>480</v>
@@ -13965,7 +14819,7 @@
         <v>181</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>439</v>
+        <v>218</v>
       </c>
       <c r="H399" s="1">
         <v>4101</v>
@@ -13977,9 +14831,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>480</v>
@@ -13994,21 +14848,21 @@
         <v>181</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H400" s="1">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="I400" s="1">
         <v>0</v>
       </c>
       <c r="J400" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>480</v>
@@ -14023,21 +14877,21 @@
         <v>181</v>
       </c>
       <c r="G401" s="1" t="s">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="H401" s="1">
-        <v>4106</v>
+        <v>0</v>
       </c>
       <c r="I401" s="1">
         <v>0</v>
       </c>
       <c r="J401" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>480</v>
@@ -14052,7 +14906,7 @@
         <v>181</v>
       </c>
       <c r="G402" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="H402" s="1">
         <v>4106</v>
@@ -14066,7 +14920,7 @@
     </row>
     <row r="403" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>480</v>
@@ -14081,7 +14935,7 @@
         <v>181</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H403" s="1">
         <v>4106</v>
@@ -14093,9 +14947,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>480</v>
@@ -14110,7 +14964,7 @@
         <v>181</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>441</v>
+        <v>67</v>
       </c>
       <c r="H404" s="1">
         <v>4106</v>
@@ -14124,7 +14978,7 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>480</v>
@@ -14139,21 +14993,21 @@
         <v>181</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H405" s="1">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="I405" s="1">
         <v>0</v>
       </c>
       <c r="J405" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>480</v>
@@ -14168,21 +15022,21 @@
         <v>181</v>
       </c>
       <c r="G406" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H406" s="1">
-        <v>4111</v>
+        <v>0</v>
       </c>
       <c r="I406" s="1">
         <v>0</v>
       </c>
       <c r="J406" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>480</v>
@@ -14197,7 +15051,7 @@
         <v>181</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H407" s="1">
         <v>4111</v>
@@ -14211,7 +15065,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>480</v>
@@ -14225,8 +15079,8 @@
       <c r="F408" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G408" s="2" t="s">
-        <v>445</v>
+      <c r="G408" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="H408" s="1">
         <v>4111</v>
@@ -14240,7 +15094,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>480</v>
@@ -14254,8 +15108,8 @@
       <c r="F409" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G409" s="1" t="s">
-        <v>446</v>
+      <c r="G409" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="H409" s="1">
         <v>4111</v>
@@ -14269,7 +15123,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>480</v>
@@ -14284,21 +15138,21 @@
         <v>181</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H410" s="1">
-        <v>0</v>
+        <v>4111</v>
       </c>
       <c r="I410" s="1">
         <v>0</v>
       </c>
       <c r="J410" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="411" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>480</v>
@@ -14313,21 +15167,21 @@
         <v>181</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>70</v>
+        <v>447</v>
       </c>
       <c r="H411" s="1">
-        <v>4116</v>
+        <v>0</v>
       </c>
       <c r="I411" s="1">
         <v>0</v>
       </c>
       <c r="J411" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>480</v>
@@ -14342,7 +15196,7 @@
         <v>181</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="H412" s="1">
         <v>4116</v>
@@ -14354,9 +15208,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>480</v>
@@ -14371,7 +15225,7 @@
         <v>181</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H413" s="1">
         <v>4116</v>
@@ -14385,7 +15239,7 @@
     </row>
     <row r="414" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>480</v>
@@ -14400,7 +15254,7 @@
         <v>181</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>448</v>
+        <v>63</v>
       </c>
       <c r="H414" s="1">
         <v>4116</v>
@@ -14412,9 +15266,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
-        <v>4121</v>
+        <v>4120</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>480</v>
@@ -14429,21 +15283,21 @@
         <v>181</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H415" s="1">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="I415" s="1">
         <v>0</v>
       </c>
       <c r="J415" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>480</v>
@@ -14458,21 +15312,21 @@
         <v>181</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H416" s="1">
-        <v>4121</v>
+        <v>0</v>
       </c>
       <c r="I416" s="1">
         <v>0</v>
       </c>
       <c r="J416" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>480</v>
@@ -14487,7 +15341,7 @@
         <v>181</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H417" s="1">
         <v>4121</v>
@@ -14501,7 +15355,7 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
-        <v>4124</v>
+        <v>4123</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>480</v>
@@ -14516,7 +15370,7 @@
         <v>181</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H418" s="1">
         <v>4121</v>
@@ -14530,7 +15384,7 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
-        <v>4125</v>
+        <v>4124</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>480</v>
@@ -14545,7 +15399,7 @@
         <v>181</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H419" s="1">
         <v>4121</v>
@@ -14559,7 +15413,7 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
-        <v>4126</v>
+        <v>4125</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>480</v>
@@ -14574,21 +15428,21 @@
         <v>181</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H420" s="1">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="I420" s="1">
         <v>0</v>
       </c>
       <c r="J420" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>480</v>
@@ -14603,21 +15457,21 @@
         <v>181</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>71</v>
+        <v>454</v>
       </c>
       <c r="H421" s="1">
-        <v>4126</v>
+        <v>0</v>
       </c>
       <c r="I421" s="1">
         <v>0</v>
       </c>
       <c r="J421" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>480</v>
@@ -14632,7 +15486,7 @@
         <v>181</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H422" s="1">
         <v>4126</v>
@@ -14644,9 +15498,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
-        <v>4129</v>
+        <v>4128</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>480</v>
@@ -14661,7 +15515,7 @@
         <v>181</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H423" s="1">
         <v>4126</v>
@@ -14673,9 +15527,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
-        <v>4130</v>
+        <v>4129</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>480</v>
@@ -14690,7 +15544,7 @@
         <v>181</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H424" s="1">
         <v>4126</v>
@@ -14702,9 +15556,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>480</v>
@@ -14719,7 +15573,7 @@
         <v>181</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>455</v>
+        <v>55</v>
       </c>
       <c r="H425" s="1">
         <v>4126</v>
@@ -14731,9 +15585,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>480</v>
@@ -14748,21 +15602,21 @@
         <v>181</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H426" s="1">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="I426" s="1">
         <v>0</v>
       </c>
       <c r="J426" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>480</v>
@@ -14777,21 +15631,21 @@
         <v>181</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="H427" s="1">
-        <v>4132</v>
+        <v>0</v>
       </c>
       <c r="I427" s="1">
         <v>0</v>
       </c>
       <c r="J427" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
-        <v>4134</v>
+        <v>4133</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>480</v>
@@ -14806,7 +15660,7 @@
         <v>181</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="H428" s="1">
         <v>4132</v>
@@ -14818,9 +15672,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
-        <v>4135</v>
+        <v>4134</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>480</v>
@@ -14835,7 +15689,7 @@
         <v>181</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>66</v>
+        <v>457</v>
       </c>
       <c r="H429" s="1">
         <v>4132</v>
@@ -14847,9 +15701,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
-        <v>4136</v>
+        <v>4135</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>480</v>
@@ -14864,7 +15718,7 @@
         <v>181</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>458</v>
+        <v>66</v>
       </c>
       <c r="H430" s="1">
         <v>4132</v>
@@ -14876,9 +15730,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
-        <v>4137</v>
+        <v>4136</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>480</v>
@@ -14893,21 +15747,21 @@
         <v>181</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H431" s="1">
-        <v>0</v>
+        <v>4132</v>
       </c>
       <c r="I431" s="1">
         <v>0</v>
       </c>
       <c r="J431" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
-        <v>4138</v>
+        <v>4137</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>480</v>
@@ -14922,21 +15776,21 @@
         <v>181</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H432" s="1">
-        <v>4137</v>
+        <v>0</v>
       </c>
       <c r="I432" s="1">
         <v>0</v>
       </c>
       <c r="J432" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
-        <v>4139</v>
+        <v>4138</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>480</v>
@@ -14951,7 +15805,7 @@
         <v>181</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H433" s="1">
         <v>4137</v>
@@ -14963,9 +15817,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>480</v>
@@ -14980,7 +15834,7 @@
         <v>181</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H434" s="1">
         <v>4137</v>
@@ -14994,7 +15848,7 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
-        <v>4141</v>
+        <v>4140</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>480</v>
@@ -15009,7 +15863,7 @@
         <v>181</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H435" s="1">
         <v>4137</v>
@@ -15023,7 +15877,7 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>480</v>
@@ -15038,21 +15892,21 @@
         <v>181</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H436" s="1">
-        <v>0</v>
+        <v>4137</v>
       </c>
       <c r="I436" s="1">
         <v>0</v>
       </c>
       <c r="J436" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
-        <v>4143</v>
+        <v>4142</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>480</v>
@@ -15067,21 +15921,21 @@
         <v>181</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H437" s="1">
-        <v>4142</v>
+        <v>0</v>
       </c>
       <c r="I437" s="1">
         <v>0</v>
       </c>
       <c r="J437" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
-        <v>4144</v>
+        <v>4143</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>480</v>
@@ -15096,7 +15950,7 @@
         <v>181</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>48</v>
+        <v>465</v>
       </c>
       <c r="H438" s="1">
         <v>4142</v>
@@ -15108,9 +15962,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
-        <v>4145</v>
+        <v>4144</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>480</v>
@@ -15125,7 +15979,7 @@
         <v>181</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H439" s="1">
         <v>4142</v>
@@ -15139,7 +15993,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>480</v>
@@ -15154,7 +16008,7 @@
         <v>181</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>466</v>
+        <v>60</v>
       </c>
       <c r="H440" s="1">
         <v>4142</v>
@@ -15168,7 +16022,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>480</v>
@@ -15183,21 +16037,21 @@
         <v>181</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H441" s="1">
-        <v>0</v>
+        <v>4142</v>
       </c>
       <c r="I441" s="1">
         <v>0</v>
       </c>
       <c r="J441" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>480</v>
@@ -15212,21 +16066,21 @@
         <v>181</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>79</v>
+        <v>467</v>
       </c>
       <c r="H442" s="1">
-        <v>4147</v>
+        <v>0</v>
       </c>
       <c r="I442" s="1">
         <v>0</v>
       </c>
       <c r="J442" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>480</v>
@@ -15241,7 +16095,7 @@
         <v>181</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>468</v>
+        <v>79</v>
       </c>
       <c r="H443" s="1">
         <v>4147</v>
@@ -15255,7 +16109,7 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>480</v>
@@ -15270,7 +16124,7 @@
         <v>181</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H444" s="1">
         <v>4147</v>
@@ -15284,7 +16138,7 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>480</v>
@@ -15299,7 +16153,7 @@
         <v>181</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H445" s="1">
         <v>4147</v>
@@ -15313,7 +16167,7 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>480</v>
@@ -15328,21 +16182,21 @@
         <v>181</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H446" s="1">
-        <v>0</v>
+        <v>4147</v>
       </c>
       <c r="I446" s="1">
         <v>0</v>
       </c>
       <c r="J446" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>480</v>
@@ -15357,21 +16211,21 @@
         <v>181</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H447" s="1">
-        <v>4152</v>
+        <v>0</v>
       </c>
       <c r="I447" s="1">
         <v>0</v>
       </c>
       <c r="J447" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
-        <v>4154</v>
+        <v>4153</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>480</v>
@@ -15386,7 +16240,7 @@
         <v>181</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H448" s="1">
         <v>4152</v>
@@ -15400,7 +16254,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
-        <v>4155</v>
+        <v>4154</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>480</v>
@@ -15415,7 +16269,7 @@
         <v>181</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H449" s="1">
         <v>4152</v>
@@ -15429,7 +16283,7 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
-        <v>4156</v>
+        <v>4155</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>480</v>
@@ -15444,7 +16298,7 @@
         <v>181</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H450" s="1">
         <v>4152</v>
@@ -15458,7 +16312,7 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
-        <v>4157</v>
+        <v>4156</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>480</v>
@@ -15473,21 +16327,21 @@
         <v>181</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H451" s="1">
-        <v>0</v>
+        <v>4152</v>
       </c>
       <c r="I451" s="1">
         <v>0</v>
       </c>
       <c r="J451" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
-        <v>4158</v>
+        <v>4157</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>480</v>
@@ -15502,21 +16356,21 @@
         <v>181</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>52</v>
+        <v>476</v>
       </c>
       <c r="H452" s="1">
-        <v>4157</v>
+        <v>0</v>
       </c>
       <c r="I452" s="1">
         <v>0</v>
       </c>
       <c r="J452" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>480</v>
@@ -15531,7 +16385,7 @@
         <v>181</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>477</v>
+        <v>52</v>
       </c>
       <c r="H453" s="1">
         <v>4157</v>
@@ -15545,7 +16399,7 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>480</v>
@@ -15560,7 +16414,7 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H454" s="1">
         <v>4157</v>
@@ -15574,7 +16428,7 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
-        <v>4161</v>
+        <v>4160</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>480</v>
@@ -15589,7 +16443,7 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H455" s="1">
         <v>4157</v>
@@ -15603,13 +16457,13 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
-        <v>5001</v>
+        <v>4161</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
@@ -15618,10 +16472,10 @@
         <v>181</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>291</v>
+        <v>479</v>
       </c>
       <c r="H456" s="1">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="I456" s="1">
         <v>0</v>
@@ -15632,7 +16486,7 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
-        <v>6000</v>
+        <v>5001</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>284</v>
@@ -15647,7 +16501,7 @@
         <v>181</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H457" s="1">
         <v>0</v>
@@ -15661,7 +16515,7 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>284</v>
@@ -15676,7 +16530,7 @@
         <v>181</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H458" s="1">
         <v>0</v>
@@ -15690,7 +16544,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>284</v>
@@ -15705,7 +16559,7 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H459" s="1">
         <v>0</v>
@@ -15719,7 +16573,7 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>284</v>
@@ -15734,7 +16588,7 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H460" s="1">
         <v>0</v>
@@ -15748,7 +16602,7 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>284</v>
@@ -15763,7 +16617,7 @@
         <v>181</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H461" s="1">
         <v>0</v>
@@ -15777,7 +16631,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>284</v>
@@ -15792,7 +16646,7 @@
         <v>181</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H462" s="1">
         <v>0</v>
@@ -15806,7 +16660,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>284</v>
@@ -15821,7 +16675,7 @@
         <v>181</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H463" s="1">
         <v>0</v>
@@ -15835,7 +16689,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>6100</v>
+        <v>6006</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>284</v>
@@ -15850,7 +16704,7 @@
         <v>181</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H464" s="1">
         <v>0</v>
@@ -15864,35 +16718,64 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
+        <v>6100</v>
+      </c>
+      <c r="B465" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E465" s="1">
+        <v>0</v>
+      </c>
+      <c r="F465" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G465" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H465" s="1">
+        <v>0</v>
+      </c>
+      <c r="I465" s="1">
+        <v>0</v>
+      </c>
+      <c r="J465" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A466" s="1">
         <v>8100</v>
       </c>
-      <c r="B465" s="3" t="s">
+      <c r="B466" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D465" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E465" s="1">
-        <v>0</v>
-      </c>
-      <c r="F465" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G465" s="1" t="s">
+      <c r="D466" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E466" s="1">
+        <v>0</v>
+      </c>
+      <c r="F466" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G466" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H465" s="1">
-        <v>0</v>
-      </c>
-      <c r="I465" s="1">
-        <v>0</v>
-      </c>
-      <c r="J465" s="1" t="b">
+      <c r="H466" s="1">
+        <v>0</v>
+      </c>
+      <c r="I466" s="1">
+        <v>0</v>
+      </c>
+      <c r="J466" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J465"/>
+  <autoFilter ref="A3:J466"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TalkData!$A$3:$J$466</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TalkData!$A$3:$J$465</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="572">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -2082,7 +2082,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="General">
-                  <c:v>1600</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="General">
                   <c:v>0</c:v>
@@ -3124,7 +3124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J466"/>
+  <dimension ref="A2:J465"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -8083,7 +8083,7 @@
         <v>559</v>
       </c>
       <c r="H169" s="1">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="I169" s="1">
         <v>0</v>
@@ -8094,31 +8094,31 @@
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>1600</v>
+        <v>1425</v>
       </c>
       <c r="B170" s="3">
         <v>2</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>571</v>
+        <v>262</v>
       </c>
       <c r="E170" s="1">
         <v>1</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H170" s="1">
-        <v>0</v>
+        <v>1426</v>
       </c>
       <c r="I170" s="1">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J170" s="1" t="b">
         <v>0</v>
@@ -8126,16 +8126,16 @@
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B171" s="3">
         <v>2</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>262</v>
+        <v>571</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -8144,13 +8144,13 @@
         <v>189</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="H171" s="1">
-        <v>1426</v>
+        <v>0</v>
       </c>
       <c r="I171" s="1">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="J171" s="1" t="b">
         <v>0</v>
@@ -8158,31 +8158,31 @@
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B172" s="3">
         <v>2</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="E172" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H172" s="1">
-        <v>0</v>
+        <v>1428</v>
       </c>
       <c r="I172" s="1">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J172" s="1" t="b">
         <v>0</v>
@@ -8190,7 +8190,7 @@
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B173" s="3">
         <v>2</v>
@@ -8202,19 +8202,19 @@
         <v>262</v>
       </c>
       <c r="E173" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H173" s="1">
-        <v>1428</v>
+        <v>0</v>
       </c>
       <c r="I173" s="1">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="J173" s="1" t="b">
         <v>0</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>1428</v>
-      </c>
-      <c r="B174" s="3">
-        <v>2</v>
+        <v>1429</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>9</v>
@@ -8240,13 +8240,13 @@
         <v>189</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H174" s="1">
         <v>0</v>
       </c>
       <c r="I174" s="1">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="J174" s="1" t="b">
         <v>0</v>
@@ -8254,10 +8254,10 @@
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>1429</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>561</v>
+        <v>1430</v>
+      </c>
+      <c r="B175" s="3">
+        <v>2</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>9</v>
@@ -8272,13 +8272,13 @@
         <v>189</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
       </c>
       <c r="I175" s="1">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="J175" s="1" t="b">
         <v>0</v>
@@ -8286,71 +8286,71 @@
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B176" s="3">
         <v>2</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>262</v>
+        <v>182</v>
       </c>
       <c r="E176" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>189</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>569</v>
+        <v>110</v>
       </c>
       <c r="H176" s="1">
-        <v>0</v>
+        <v>1432</v>
       </c>
       <c r="I176" s="1">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="J176" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B177" s="3">
         <v>2</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="E177" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>110</v>
+        <v>570</v>
       </c>
       <c r="H177" s="1">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="I177" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J177" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B178" s="3">
         <v>2</v>
@@ -8365,24 +8365,24 @@
         <v>1</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>570</v>
+        <v>111</v>
       </c>
       <c r="H178" s="1">
-        <v>0</v>
+        <v>1434</v>
       </c>
       <c r="I178" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J178" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B179" s="3">
         <v>2</v>
@@ -8397,24 +8397,24 @@
         <v>1</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>111</v>
+        <v>563</v>
       </c>
       <c r="H179" s="1">
-        <v>1434</v>
+        <v>0</v>
       </c>
       <c r="I179" s="1">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J179" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B180" s="3">
         <v>2</v>
@@ -8432,39 +8432,36 @@
         <v>255</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>563</v>
+        <v>112</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
       <c r="I180" s="1">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J180" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>1435</v>
+        <v>1610</v>
       </c>
       <c r="B181" s="3">
         <v>2</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D181" s="1" t="s">
-        <v>262</v>
+        <v>183</v>
       </c>
       <c r="E181" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -8478,7 +8475,7 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B182" s="3">
         <v>2</v>
@@ -8493,7 +8490,7 @@
         <v>255</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>113</v>
+        <v>225</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -8507,7 +8504,7 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B183" s="3">
         <v>2</v>
@@ -8522,7 +8519,7 @@
         <v>255</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>225</v>
+        <v>114</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -8536,7 +8533,7 @@
     </row>
     <row r="184" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B184" s="3">
         <v>2</v>
@@ -8551,7 +8548,7 @@
         <v>255</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -8565,7 +8562,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B185" s="3">
         <v>2</v>
@@ -8580,7 +8577,7 @@
         <v>255</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>115</v>
+        <v>226</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -8594,7 +8591,7 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B186" s="3">
         <v>2</v>
@@ -8609,7 +8606,7 @@
         <v>255</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -8623,7 +8620,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B187" s="3">
         <v>2</v>
@@ -8638,7 +8635,7 @@
         <v>255</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>227</v>
+        <v>116</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
@@ -8652,7 +8649,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B188" s="3">
         <v>2</v>
@@ -8667,7 +8664,7 @@
         <v>255</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
@@ -8681,7 +8678,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B189" s="3">
         <v>2</v>
@@ -8696,7 +8693,7 @@
         <v>255</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
@@ -8710,7 +8707,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B190" s="3">
         <v>2</v>
@@ -8725,7 +8722,7 @@
         <v>255</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -8739,7 +8736,7 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B191" s="3">
         <v>2</v>
@@ -8754,7 +8751,7 @@
         <v>255</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -8768,7 +8765,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B192" s="3">
         <v>2</v>
@@ -8783,7 +8780,7 @@
         <v>255</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -8797,7 +8794,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B193" s="3">
         <v>2</v>
@@ -8812,7 +8809,7 @@
         <v>255</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
@@ -8826,7 +8823,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B194" s="3">
         <v>2</v>
@@ -8841,7 +8838,7 @@
         <v>255</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
@@ -8855,7 +8852,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B195" s="3">
         <v>2</v>
@@ -8870,7 +8867,7 @@
         <v>255</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>123</v>
+        <v>228</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
@@ -8884,7 +8881,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B196" s="3">
         <v>2</v>
@@ -8899,7 +8896,7 @@
         <v>255</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>228</v>
+        <v>124</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -8913,7 +8910,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B197" s="3">
         <v>2</v>
@@ -8928,7 +8925,7 @@
         <v>255</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
@@ -8942,7 +8939,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B198" s="3">
         <v>2</v>
@@ -8957,7 +8954,7 @@
         <v>255</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -8971,7 +8968,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B199" s="3">
         <v>2</v>
@@ -8986,7 +8983,7 @@
         <v>255</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>126</v>
+        <v>229</v>
       </c>
       <c r="H199" s="1">
         <v>0</v>
@@ -9000,7 +8997,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B200" s="3">
         <v>2</v>
@@ -9015,7 +9012,7 @@
         <v>255</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>229</v>
+        <v>127</v>
       </c>
       <c r="H200" s="1">
         <v>0</v>
@@ -9029,7 +9026,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B201" s="3">
         <v>2</v>
@@ -9044,7 +9041,7 @@
         <v>255</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H201" s="1">
         <v>0</v>
@@ -9058,7 +9055,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B202" s="3">
         <v>2</v>
@@ -9073,7 +9070,7 @@
         <v>255</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
@@ -9085,9 +9082,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B203" s="3">
         <v>2</v>
@@ -9102,7 +9099,7 @@
         <v>255</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>230</v>
+        <v>129</v>
       </c>
       <c r="H203" s="1">
         <v>0</v>
@@ -9114,9 +9111,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B204" s="3">
         <v>2</v>
@@ -9131,7 +9128,7 @@
         <v>255</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -9145,7 +9142,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B205" s="3">
         <v>2</v>
@@ -9160,7 +9157,7 @@
         <v>255</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -9174,7 +9171,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B206" s="3">
         <v>2</v>
@@ -9189,7 +9186,7 @@
         <v>255</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
@@ -9203,7 +9200,7 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B207" s="3">
         <v>2</v>
@@ -9218,7 +9215,7 @@
         <v>255</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -9232,7 +9229,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B208" s="3">
         <v>2</v>
@@ -9247,7 +9244,7 @@
         <v>255</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -9259,9 +9256,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B209" s="3">
         <v>2</v>
@@ -9276,7 +9273,7 @@
         <v>255</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
@@ -9288,9 +9285,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B210" s="3">
         <v>2</v>
@@ -9305,7 +9302,7 @@
         <v>255</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
@@ -9317,9 +9314,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B211" s="3">
         <v>2</v>
@@ -9334,7 +9331,7 @@
         <v>255</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -9346,9 +9343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B212" s="3">
         <v>2</v>
@@ -9363,7 +9360,7 @@
         <v>255</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
@@ -9377,7 +9374,7 @@
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B213" s="3">
         <v>2</v>
@@ -9392,7 +9389,7 @@
         <v>255</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -9406,7 +9403,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B214" s="3">
         <v>2</v>
@@ -9421,7 +9418,7 @@
         <v>255</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -9435,7 +9432,7 @@
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B215" s="3">
         <v>2</v>
@@ -9450,7 +9447,7 @@
         <v>255</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -9464,7 +9461,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B216" s="3">
         <v>2</v>
@@ -9479,7 +9476,7 @@
         <v>255</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -9491,9 +9488,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B217" s="3">
         <v>2</v>
@@ -9508,7 +9505,7 @@
         <v>255</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H217" s="1">
         <v>0</v>
@@ -9522,7 +9519,7 @@
     </row>
     <row r="218" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B218" s="3">
         <v>2</v>
@@ -9537,7 +9534,7 @@
         <v>255</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>143</v>
+        <v>307</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
@@ -9549,9 +9546,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B219" s="3">
         <v>2</v>
@@ -9566,7 +9563,7 @@
         <v>255</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
@@ -9580,7 +9577,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1648</v>
+        <v>1500</v>
       </c>
       <c r="B220" s="3">
         <v>2</v>
@@ -9595,7 +9592,7 @@
         <v>255</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H220" s="1">
         <v>0</v>
@@ -9609,7 +9606,7 @@
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B221" s="3">
         <v>2</v>
@@ -9624,7 +9621,7 @@
         <v>255</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H221" s="1">
         <v>0</v>
@@ -9638,7 +9635,7 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B222" s="3">
         <v>2</v>
@@ -9653,7 +9650,7 @@
         <v>255</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -9667,7 +9664,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B223" s="3">
         <v>2</v>
@@ -9682,7 +9679,7 @@
         <v>255</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -9696,7 +9693,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B224" s="3">
         <v>2</v>
@@ -9711,7 +9708,7 @@
         <v>255</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H224" s="1">
         <v>0</v>
@@ -9725,7 +9722,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B225" s="3">
         <v>2</v>
@@ -9740,7 +9737,7 @@
         <v>255</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H225" s="1">
         <v>0</v>
@@ -9754,7 +9751,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B226" s="3">
         <v>2</v>
@@ -9769,7 +9766,7 @@
         <v>255</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H226" s="1">
         <v>0</v>
@@ -9783,7 +9780,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B227" s="3">
         <v>2</v>
@@ -9798,7 +9795,7 @@
         <v>255</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
@@ -9812,7 +9809,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B228" s="3">
         <v>2</v>
@@ -9827,7 +9824,7 @@
         <v>255</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -9841,7 +9838,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B229" s="3">
         <v>2</v>
@@ -9856,7 +9853,7 @@
         <v>255</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -9870,7 +9867,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B230" s="3">
         <v>2</v>
@@ -9885,7 +9882,7 @@
         <v>255</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="H230" s="1">
         <v>0</v>
@@ -9899,7 +9896,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B231" s="3">
         <v>2</v>
@@ -9914,7 +9911,7 @@
         <v>255</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>231</v>
+        <v>155</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -9928,7 +9925,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B232" s="3">
         <v>2</v>
@@ -9943,7 +9940,7 @@
         <v>255</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -9957,7 +9954,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B233" s="3">
         <v>2</v>
@@ -9972,7 +9969,7 @@
         <v>255</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H233" s="1">
         <v>0</v>
@@ -9986,7 +9983,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B234" s="3">
         <v>2</v>
@@ -10001,7 +9998,7 @@
         <v>255</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
@@ -10015,7 +10012,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B235" s="3">
         <v>2</v>
@@ -10030,7 +10027,7 @@
         <v>255</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -10044,7 +10041,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B236" s="3">
         <v>2</v>
@@ -10059,7 +10056,7 @@
         <v>255</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -10073,7 +10070,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B237" s="3">
         <v>2</v>
@@ -10088,7 +10085,7 @@
         <v>255</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -10102,7 +10099,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B238" s="3">
         <v>2</v>
@@ -10117,7 +10114,7 @@
         <v>255</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -10131,7 +10128,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B239" s="3">
         <v>2</v>
@@ -10146,7 +10143,7 @@
         <v>255</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>238</v>
+        <v>156</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
@@ -10160,7 +10157,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B240" s="3">
         <v>2</v>
@@ -10175,7 +10172,7 @@
         <v>255</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H240" s="1">
         <v>0</v>
@@ -10189,7 +10186,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>1600</v>
+        <v>2001</v>
       </c>
       <c r="B241" s="3">
         <v>2</v>
@@ -10204,7 +10201,7 @@
         <v>255</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>157</v>
+        <v>239</v>
       </c>
       <c r="H241" s="1">
         <v>0</v>
@@ -10218,7 +10215,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B242" s="3">
         <v>2</v>
@@ -10233,7 +10230,7 @@
         <v>255</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>239</v>
+        <v>158</v>
       </c>
       <c r="H242" s="1">
         <v>0</v>
@@ -10247,7 +10244,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B243" s="3">
         <v>2</v>
@@ -10262,7 +10259,7 @@
         <v>255</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>158</v>
+        <v>240</v>
       </c>
       <c r="H243" s="1">
         <v>0</v>
@@ -10276,7 +10273,7 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B244" s="3">
         <v>2</v>
@@ -10291,7 +10288,7 @@
         <v>255</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H244" s="1">
         <v>0</v>
@@ -10305,7 +10302,7 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B245" s="3">
         <v>2</v>
@@ -10320,7 +10317,7 @@
         <v>255</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
@@ -10334,7 +10331,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B246" s="3">
         <v>2</v>
@@ -10349,7 +10346,7 @@
         <v>255</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H246" s="1">
         <v>0</v>
@@ -10363,7 +10360,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B247" s="3">
         <v>2</v>
@@ -10378,7 +10375,7 @@
         <v>255</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -10392,7 +10389,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B248" s="3">
         <v>2</v>
@@ -10407,7 +10404,7 @@
         <v>255</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -10421,7 +10418,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B249" s="3">
         <v>2</v>
@@ -10436,7 +10433,7 @@
         <v>255</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
@@ -10450,7 +10447,7 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B250" s="3">
         <v>2</v>
@@ -10465,7 +10462,7 @@
         <v>255</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
@@ -10479,7 +10476,7 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B251" s="3">
         <v>2</v>
@@ -10494,7 +10491,7 @@
         <v>255</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>247</v>
+        <v>159</v>
       </c>
       <c r="H251" s="1">
         <v>0</v>
@@ -10508,7 +10505,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B252" s="3">
         <v>2</v>
@@ -10523,7 +10520,7 @@
         <v>255</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
@@ -10537,7 +10534,7 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B253" s="3">
         <v>2</v>
@@ -10552,7 +10549,7 @@
         <v>255</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H253" s="1">
         <v>0</v>
@@ -10566,7 +10563,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B254" s="3">
         <v>2</v>
@@ -10581,7 +10578,7 @@
         <v>255</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
@@ -10595,7 +10592,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B255" s="3">
         <v>2</v>
@@ -10610,7 +10607,7 @@
         <v>255</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H255" s="1">
         <v>0</v>
@@ -10624,7 +10621,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B256" s="3">
         <v>2</v>
@@ -10639,7 +10636,7 @@
         <v>255</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>163</v>
+        <v>248</v>
       </c>
       <c r="H256" s="1">
         <v>0</v>
@@ -10653,7 +10650,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B257" s="3">
         <v>2</v>
@@ -10668,7 +10665,7 @@
         <v>255</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>248</v>
+        <v>164</v>
       </c>
       <c r="H257" s="1">
         <v>0</v>
@@ -10682,7 +10679,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B258" s="3">
         <v>2</v>
@@ -10697,7 +10694,7 @@
         <v>255</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H258" s="1">
         <v>0</v>
@@ -10711,7 +10708,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B259" s="3">
         <v>2</v>
@@ -10726,7 +10723,7 @@
         <v>255</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>165</v>
+        <v>249</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
@@ -10740,7 +10737,7 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B260" s="3">
         <v>2</v>
@@ -10755,7 +10752,7 @@
         <v>255</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>249</v>
+        <v>166</v>
       </c>
       <c r="H260" s="1">
         <v>0</v>
@@ -10769,7 +10766,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B261" s="3">
         <v>2</v>
@@ -10784,7 +10781,7 @@
         <v>255</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -10798,7 +10795,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B262" s="3">
         <v>2</v>
@@ -10813,7 +10810,7 @@
         <v>255</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H262" s="1">
         <v>0</v>
@@ -10827,7 +10824,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B263" s="3">
         <v>2</v>
@@ -10842,7 +10839,7 @@
         <v>255</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H263" s="1">
         <v>0</v>
@@ -10856,7 +10853,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B264" s="3">
         <v>2</v>
@@ -10871,7 +10868,7 @@
         <v>255</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
@@ -10885,25 +10882,28 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B265" s="3">
         <v>2</v>
       </c>
+      <c r="C265" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="D265" s="1" t="s">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="E265" s="1">
         <v>0</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H265" s="1">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="I265" s="1">
         <v>0</v>
@@ -10914,28 +10914,28 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B266" s="3">
         <v>2</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E266" s="1">
         <v>0</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="H266" s="1">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="I266" s="1">
         <v>0</v>
@@ -10946,28 +10946,28 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B267" s="3">
         <v>2</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="E267" s="1">
         <v>0</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="H267" s="1">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="I267" s="1">
         <v>0</v>
@@ -10978,16 +10978,16 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B268" s="3">
         <v>2</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>184</v>
+        <v>260</v>
       </c>
       <c r="E268" s="1">
         <v>0</v>
@@ -10996,10 +10996,10 @@
         <v>256</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H268" s="1">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="I268" s="1">
         <v>0</v>
@@ -11010,16 +11010,16 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B269" s="3">
         <v>2</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E269" s="1">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>256</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H269" s="1">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="I269" s="1">
         <v>0</v>
@@ -11042,28 +11042,28 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B270" s="3">
         <v>2</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="E270" s="1">
         <v>0</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H270" s="1">
-        <v>1514</v>
+        <v>0</v>
       </c>
       <c r="I270" s="1">
         <v>0</v>
@@ -11074,7 +11074,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="B271" s="3">
         <v>2</v>
@@ -11092,7 +11092,7 @@
         <v>255</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H271" s="1">
         <v>0</v>
@@ -11106,28 +11106,28 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B272" s="3">
         <v>2</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>10</v>
+        <v>251</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="E272" s="1">
         <v>0</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H272" s="1">
-        <v>0</v>
+        <v>1517</v>
       </c>
       <c r="I272" s="1">
         <v>0</v>
@@ -11138,28 +11138,28 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B273" s="3">
         <v>2</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E273" s="1">
         <v>0</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H273" s="1">
-        <v>1517</v>
+        <v>0</v>
       </c>
       <c r="I273" s="1">
         <v>0</v>
@@ -11170,28 +11170,28 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B274" s="3">
         <v>2</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
       <c r="E274" s="1">
         <v>0</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H274" s="1">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="I274" s="1">
         <v>0</v>
@@ -11202,28 +11202,28 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>2034</v>
+        <v>2100</v>
       </c>
       <c r="B275" s="3">
         <v>2</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>10</v>
+        <v>251</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="E275" s="1">
         <v>0</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>179</v>
+        <v>253</v>
       </c>
       <c r="H275" s="1">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="I275" s="1">
         <v>0</v>
@@ -11234,16 +11234,13 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B276" s="3">
         <v>2</v>
       </c>
-      <c r="C276" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="D276" s="1" t="s">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="E276" s="1">
         <v>0</v>
@@ -11252,7 +11249,7 @@
         <v>255</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>253</v>
+        <v>180</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
@@ -11266,7 +11263,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>2101</v>
+        <v>8888</v>
       </c>
       <c r="B277" s="3">
         <v>2</v>
@@ -11281,7 +11278,7 @@
         <v>255</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="H277" s="1">
         <v>0</v>
@@ -11295,7 +11292,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>8888</v>
+        <v>3000</v>
       </c>
       <c r="B278" s="3">
         <v>2</v>
@@ -11307,10 +11304,10 @@
         <v>0</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="H278" s="1">
         <v>0</v>
@@ -11324,7 +11321,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>3000</v>
+        <v>3001</v>
       </c>
       <c r="B279" s="3">
         <v>2</v>
@@ -11339,7 +11336,7 @@
         <v>181</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H279" s="1">
         <v>0</v>
@@ -11353,7 +11350,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="B280" s="3">
         <v>2</v>
@@ -11368,7 +11365,7 @@
         <v>181</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H280" s="1">
         <v>0</v>
@@ -11382,7 +11379,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="B281" s="3">
         <v>2</v>
@@ -11397,7 +11394,7 @@
         <v>181</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H281" s="1">
         <v>0</v>
@@ -11411,7 +11408,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="B282" s="3">
         <v>2</v>
@@ -11426,7 +11423,7 @@
         <v>181</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
@@ -11440,7 +11437,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="B283" s="3">
         <v>2</v>
@@ -11455,7 +11452,7 @@
         <v>181</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H283" s="1">
         <v>0</v>
@@ -11469,13 +11466,13 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="B284" s="3">
         <v>2</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="E284" s="1">
         <v>0</v>
@@ -11484,7 +11481,7 @@
         <v>181</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="H284" s="1">
         <v>0</v>
@@ -11498,7 +11495,7 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="B285" s="3">
         <v>2</v>
@@ -11510,10 +11507,10 @@
         <v>0</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
@@ -11527,7 +11524,7 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="B286" s="3">
         <v>2</v>
@@ -11539,10 +11536,10 @@
         <v>0</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H286" s="1">
         <v>0</v>
@@ -11556,7 +11553,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>3008</v>
+        <v>3010</v>
       </c>
       <c r="B287" s="3">
         <v>2</v>
@@ -11571,7 +11568,7 @@
         <v>181</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H287" s="1">
         <v>0</v>
@@ -11585,7 +11582,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="B288" s="3">
         <v>2</v>
@@ -11600,7 +11597,7 @@
         <v>181</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H288" s="1">
         <v>0</v>
@@ -11614,7 +11611,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="B289" s="3">
         <v>2</v>
@@ -11629,7 +11626,7 @@
         <v>181</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H289" s="1">
         <v>0</v>
@@ -11643,7 +11640,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="B290" s="3">
         <v>2</v>
@@ -11658,7 +11655,7 @@
         <v>181</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -11672,7 +11669,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="B291" s="3">
         <v>2</v>
@@ -11687,7 +11684,7 @@
         <v>181</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -11701,7 +11698,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>3014</v>
+        <v>3200</v>
       </c>
       <c r="B292" s="3">
         <v>2</v>
@@ -11716,7 +11713,7 @@
         <v>181</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="H292" s="1">
         <v>0</v>
@@ -11730,7 +11727,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="B293" s="3">
         <v>2</v>
@@ -11745,7 +11742,7 @@
         <v>181</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H293" s="1">
         <v>0</v>
@@ -11759,10 +11756,10 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>3201</v>
-      </c>
-      <c r="B294" s="3">
-        <v>2</v>
+        <v>4000</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>480</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>274</v>
@@ -11774,7 +11771,7 @@
         <v>181</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>305</v>
+        <v>353</v>
       </c>
       <c r="H294" s="1">
         <v>0</v>
@@ -11783,12 +11780,12 @@
         <v>0</v>
       </c>
       <c r="J294" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>4000</v>
+        <v>4001</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>480</v>
@@ -11803,21 +11800,21 @@
         <v>181</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H295" s="1">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I295" s="1">
         <v>0</v>
       </c>
       <c r="J295" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>480</v>
@@ -11832,7 +11829,7 @@
         <v>181</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>354</v>
+        <v>45</v>
       </c>
       <c r="H296" s="1">
         <v>4000</v>
@@ -11844,9 +11841,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>480</v>
@@ -11861,7 +11858,7 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>45</v>
+        <v>355</v>
       </c>
       <c r="H297" s="1">
         <v>4000</v>
@@ -11873,9 +11870,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>4003</v>
+        <v>4004</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>480</v>
@@ -11890,7 +11887,7 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H298" s="1">
         <v>4000</v>
@@ -11904,7 +11901,7 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>4004</v>
+        <v>4005</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>480</v>
@@ -11919,21 +11916,21 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H299" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I299" s="1">
         <v>0</v>
       </c>
       <c r="J299" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>4005</v>
+        <v>4006</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>480</v>
@@ -11948,21 +11945,21 @@
         <v>181</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H300" s="1">
-        <v>0</v>
+        <v>4005</v>
       </c>
       <c r="I300" s="1">
         <v>0</v>
       </c>
       <c r="J300" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>4006</v>
+        <v>4007</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>480</v>
@@ -11977,7 +11974,7 @@
         <v>181</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H301" s="1">
         <v>4005</v>
@@ -11991,7 +11988,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>4007</v>
+        <v>4008</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>480</v>
@@ -12006,7 +12003,7 @@
         <v>181</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H302" s="1">
         <v>4005</v>
@@ -12020,7 +12017,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>4008</v>
+        <v>4009</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>480</v>
@@ -12035,7 +12032,7 @@
         <v>181</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H303" s="1">
         <v>4005</v>
@@ -12049,7 +12046,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>4009</v>
+        <v>4010</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>480</v>
@@ -12064,7 +12061,7 @@
         <v>181</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H304" s="1">
         <v>4005</v>
@@ -12078,7 +12075,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>4010</v>
+        <v>4011</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>480</v>
@@ -12093,21 +12090,21 @@
         <v>181</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H305" s="1">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="I305" s="1">
         <v>0</v>
       </c>
       <c r="J305" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>480</v>
@@ -12122,21 +12119,21 @@
         <v>181</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>363</v>
+        <v>49</v>
       </c>
       <c r="H306" s="1">
-        <v>0</v>
+        <v>4011</v>
       </c>
       <c r="I306" s="1">
         <v>0</v>
       </c>
       <c r="J306" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>4012</v>
+        <v>4013</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>480</v>
@@ -12151,7 +12148,7 @@
         <v>181</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>49</v>
+        <v>364</v>
       </c>
       <c r="H307" s="1">
         <v>4011</v>
@@ -12163,9 +12160,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>4013</v>
+        <v>4014</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>480</v>
@@ -12180,7 +12177,7 @@
         <v>181</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H308" s="1">
         <v>4011</v>
@@ -12194,7 +12191,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>4014</v>
+        <v>4015</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>480</v>
@@ -12209,7 +12206,7 @@
         <v>181</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H309" s="1">
         <v>4011</v>
@@ -12223,7 +12220,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>4015</v>
+        <v>4016</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>480</v>
@@ -12238,21 +12235,21 @@
         <v>181</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H310" s="1">
-        <v>4011</v>
+        <v>0</v>
       </c>
       <c r="I310" s="1">
         <v>0</v>
       </c>
       <c r="J310" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>480</v>
@@ -12267,21 +12264,21 @@
         <v>181</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>367</v>
+        <v>56</v>
       </c>
       <c r="H311" s="1">
-        <v>0</v>
+        <v>4016</v>
       </c>
       <c r="I311" s="1">
         <v>0</v>
       </c>
       <c r="J311" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>4017</v>
+        <v>4018</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>480</v>
@@ -12296,7 +12293,7 @@
         <v>181</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>56</v>
+        <v>368</v>
       </c>
       <c r="H312" s="1">
         <v>4016</v>
@@ -12310,7 +12307,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>4018</v>
+        <v>4019</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>480</v>
@@ -12325,7 +12322,7 @@
         <v>181</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H313" s="1">
         <v>4016</v>
@@ -12339,7 +12336,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>4019</v>
+        <v>4020</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>480</v>
@@ -12354,7 +12351,7 @@
         <v>181</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H314" s="1">
         <v>4016</v>
@@ -12368,7 +12365,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>4020</v>
+        <v>4021</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>480</v>
@@ -12383,21 +12380,21 @@
         <v>181</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H315" s="1">
-        <v>4016</v>
+        <v>0</v>
       </c>
       <c r="I315" s="1">
         <v>0</v>
       </c>
       <c r="J315" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>4021</v>
+        <v>4022</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>480</v>
@@ -12412,21 +12409,21 @@
         <v>181</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H316" s="1">
-        <v>0</v>
+        <v>4021</v>
       </c>
       <c r="I316" s="1">
         <v>0</v>
       </c>
       <c r="J316" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>4022</v>
+        <v>4023</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>480</v>
@@ -12441,7 +12438,7 @@
         <v>181</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H317" s="1">
         <v>4021</v>
@@ -12453,9 +12450,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>4023</v>
+        <v>4024</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>480</v>
@@ -12470,7 +12467,7 @@
         <v>181</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H318" s="1">
         <v>4021</v>
@@ -12482,9 +12479,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>4024</v>
+        <v>4025</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>480</v>
@@ -12499,7 +12496,7 @@
         <v>181</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H319" s="1">
         <v>4021</v>
@@ -12511,9 +12508,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>4025</v>
+        <v>4026</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>480</v>
@@ -12528,21 +12525,21 @@
         <v>181</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H320" s="1">
-        <v>4021</v>
+        <v>0</v>
       </c>
       <c r="I320" s="1">
         <v>0</v>
       </c>
       <c r="J320" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>4026</v>
+        <v>4027</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>480</v>
@@ -12557,21 +12554,21 @@
         <v>181</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H321" s="1">
-        <v>0</v>
+        <v>4026</v>
       </c>
       <c r="I321" s="1">
         <v>0</v>
       </c>
       <c r="J321" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="322" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>4027</v>
+        <v>4028</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>480</v>
@@ -12586,7 +12583,7 @@
         <v>181</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H322" s="1">
         <v>4026</v>
@@ -12600,7 +12597,7 @@
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>4028</v>
+        <v>4029</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>480</v>
@@ -12615,7 +12612,7 @@
         <v>181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H323" s="1">
         <v>4026</v>
@@ -12629,7 +12626,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>4029</v>
+        <v>4030</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>480</v>
@@ -12644,7 +12641,7 @@
         <v>181</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H324" s="1">
         <v>4026</v>
@@ -12658,7 +12655,7 @@
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>480</v>
@@ -12673,21 +12670,21 @@
         <v>181</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H325" s="1">
-        <v>4026</v>
+        <v>0</v>
       </c>
       <c r="I325" s="1">
         <v>0</v>
       </c>
       <c r="J325" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>4031</v>
+        <v>4032</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>480</v>
@@ -12702,21 +12699,21 @@
         <v>181</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H326" s="1">
-        <v>0</v>
+        <v>4031</v>
       </c>
       <c r="I326" s="1">
         <v>0</v>
       </c>
       <c r="J326" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>480</v>
@@ -12731,7 +12728,7 @@
         <v>181</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H327" s="1">
         <v>4031</v>
@@ -12743,9 +12740,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>4033</v>
+        <v>4034</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>480</v>
@@ -12760,7 +12757,7 @@
         <v>181</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H328" s="1">
         <v>4031</v>
@@ -12772,9 +12769,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>4034</v>
+        <v>4035</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>480</v>
@@ -12789,7 +12786,7 @@
         <v>181</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H329" s="1">
         <v>4031</v>
@@ -12801,9 +12798,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>4035</v>
+        <v>4036</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>480</v>
@@ -12818,21 +12815,21 @@
         <v>181</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H330" s="1">
-        <v>4031</v>
+        <v>0</v>
       </c>
       <c r="I330" s="1">
         <v>0</v>
       </c>
       <c r="J330" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>4036</v>
+        <v>4037</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>480</v>
@@ -12847,21 +12844,21 @@
         <v>181</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H331" s="1">
-        <v>0</v>
+        <v>4036</v>
       </c>
       <c r="I331" s="1">
         <v>0</v>
       </c>
       <c r="J331" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>4037</v>
+        <v>4038</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>480</v>
@@ -12876,7 +12873,7 @@
         <v>181</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H332" s="1">
         <v>4036</v>
@@ -12890,7 +12887,7 @@
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>480</v>
@@ -12905,7 +12902,7 @@
         <v>181</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H333" s="1">
         <v>4036</v>
@@ -12919,7 +12916,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>4039</v>
+        <v>4040</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>480</v>
@@ -12934,7 +12931,7 @@
         <v>181</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H334" s="1">
         <v>4036</v>
@@ -12948,7 +12945,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>480</v>
@@ -12963,21 +12960,21 @@
         <v>181</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H335" s="1">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="I335" s="1">
         <v>0</v>
       </c>
       <c r="J335" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>480</v>
@@ -12992,21 +12989,21 @@
         <v>181</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H336" s="1">
-        <v>0</v>
+        <v>4041</v>
       </c>
       <c r="I336" s="1">
         <v>0</v>
       </c>
       <c r="J336" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>480</v>
@@ -13021,7 +13018,7 @@
         <v>181</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>392</v>
+        <v>78</v>
       </c>
       <c r="H337" s="1">
         <v>4041</v>
@@ -13033,9 +13030,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>480</v>
@@ -13050,7 +13047,7 @@
         <v>181</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="H338" s="1">
         <v>4041</v>
@@ -13064,7 +13061,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>480</v>
@@ -13079,7 +13076,7 @@
         <v>181</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>219</v>
+        <v>393</v>
       </c>
       <c r="H339" s="1">
         <v>4041</v>
@@ -13093,7 +13090,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>480</v>
@@ -13108,21 +13105,21 @@
         <v>181</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H340" s="1">
-        <v>4041</v>
+        <v>0</v>
       </c>
       <c r="I340" s="1">
         <v>0</v>
       </c>
       <c r="J340" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>4046</v>
+        <v>4047</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>480</v>
@@ -13137,21 +13134,21 @@
         <v>181</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H341" s="1">
-        <v>0</v>
+        <v>4046</v>
       </c>
       <c r="I341" s="1">
         <v>0</v>
       </c>
       <c r="J341" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>4047</v>
+        <v>4048</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>480</v>
@@ -13166,7 +13163,7 @@
         <v>181</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>395</v>
+        <v>61</v>
       </c>
       <c r="H342" s="1">
         <v>4046</v>
@@ -13178,9 +13175,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>4048</v>
+        <v>4049</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>480</v>
@@ -13195,7 +13192,7 @@
         <v>181</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H343" s="1">
         <v>4046</v>
@@ -13209,7 +13206,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>4049</v>
+        <v>4050</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>480</v>
@@ -13224,7 +13221,7 @@
         <v>181</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>62</v>
+        <v>396</v>
       </c>
       <c r="H344" s="1">
         <v>4046</v>
@@ -13238,7 +13235,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>4050</v>
+        <v>4051</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>480</v>
@@ -13253,21 +13250,21 @@
         <v>181</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H345" s="1">
-        <v>4046</v>
+        <v>0</v>
       </c>
       <c r="I345" s="1">
         <v>0</v>
       </c>
       <c r="J345" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>480</v>
@@ -13282,21 +13279,21 @@
         <v>181</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H346" s="1">
-        <v>0</v>
+        <v>4051</v>
       </c>
       <c r="I346" s="1">
         <v>0</v>
       </c>
       <c r="J346" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>480</v>
@@ -13311,7 +13308,7 @@
         <v>181</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H347" s="1">
         <v>4051</v>
@@ -13325,7 +13322,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>4053</v>
+        <v>4054</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>480</v>
@@ -13340,7 +13337,7 @@
         <v>181</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H348" s="1">
         <v>4051</v>
@@ -13354,7 +13351,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>480</v>
@@ -13369,7 +13366,7 @@
         <v>181</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H349" s="1">
         <v>4051</v>
@@ -13383,7 +13380,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>4055</v>
+        <v>4056</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>480</v>
@@ -13398,21 +13395,21 @@
         <v>181</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H350" s="1">
-        <v>4051</v>
+        <v>0</v>
       </c>
       <c r="I350" s="1">
         <v>0</v>
       </c>
       <c r="J350" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>480</v>
@@ -13427,21 +13424,21 @@
         <v>181</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H351" s="1">
-        <v>0</v>
+        <v>4056</v>
       </c>
       <c r="I351" s="1">
         <v>0</v>
       </c>
       <c r="J351" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>4057</v>
+        <v>4058</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>480</v>
@@ -13456,7 +13453,7 @@
         <v>181</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H352" s="1">
         <v>4056</v>
@@ -13470,7 +13467,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>4058</v>
+        <v>4059</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>480</v>
@@ -13485,7 +13482,7 @@
         <v>181</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H353" s="1">
         <v>4056</v>
@@ -13499,7 +13496,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>480</v>
@@ -13514,7 +13511,7 @@
         <v>181</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H354" s="1">
         <v>4056</v>
@@ -13528,7 +13525,7 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>4060</v>
+        <v>4061</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>480</v>
@@ -13543,21 +13540,21 @@
         <v>181</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H355" s="1">
-        <v>4056</v>
+        <v>0</v>
       </c>
       <c r="I355" s="1">
         <v>0</v>
       </c>
       <c r="J355" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>480</v>
@@ -13572,21 +13569,21 @@
         <v>181</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H356" s="1">
-        <v>0</v>
+        <v>4061</v>
       </c>
       <c r="I356" s="1">
         <v>0</v>
       </c>
       <c r="J356" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>4062</v>
+        <v>4063</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>480</v>
@@ -13601,7 +13598,7 @@
         <v>181</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>408</v>
+        <v>51</v>
       </c>
       <c r="H357" s="1">
         <v>4061</v>
@@ -13613,9 +13610,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>4063</v>
+        <v>4064</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>480</v>
@@ -13630,7 +13627,7 @@
         <v>181</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H358" s="1">
         <v>4061</v>
@@ -13644,7 +13641,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>480</v>
@@ -13659,7 +13656,7 @@
         <v>181</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>58</v>
+        <v>409</v>
       </c>
       <c r="H359" s="1">
         <v>4061</v>
@@ -13671,9 +13668,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>4065</v>
+        <v>4066</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>480</v>
@@ -13688,21 +13685,21 @@
         <v>181</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H360" s="1">
-        <v>4061</v>
+        <v>0</v>
       </c>
       <c r="I360" s="1">
         <v>0</v>
       </c>
       <c r="J360" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>480</v>
@@ -13717,21 +13714,21 @@
         <v>181</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="H361" s="1">
-        <v>0</v>
+        <v>4066</v>
       </c>
       <c r="I361" s="1">
         <v>0</v>
       </c>
       <c r="J361" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>4067</v>
+        <v>4068</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>480</v>
@@ -13746,7 +13743,7 @@
         <v>181</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>81</v>
+        <v>411</v>
       </c>
       <c r="H362" s="1">
         <v>4066</v>
@@ -13758,9 +13755,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>4068</v>
+        <v>4069</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>480</v>
@@ -13775,7 +13772,7 @@
         <v>181</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>411</v>
+        <v>65</v>
       </c>
       <c r="H363" s="1">
         <v>4066</v>
@@ -13787,9 +13784,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>4069</v>
+        <v>4070</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>480</v>
@@ -13804,7 +13801,7 @@
         <v>181</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>65</v>
+        <v>412</v>
       </c>
       <c r="H364" s="1">
         <v>4066</v>
@@ -13818,7 +13815,7 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>4070</v>
+        <v>4071</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>480</v>
@@ -13833,21 +13830,21 @@
         <v>181</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H365" s="1">
-        <v>4066</v>
+        <v>0</v>
       </c>
       <c r="I365" s="1">
         <v>0</v>
       </c>
       <c r="J365" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>4071</v>
+        <v>4072</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>480</v>
@@ -13862,21 +13859,21 @@
         <v>181</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>413</v>
+        <v>68</v>
       </c>
       <c r="H366" s="1">
-        <v>0</v>
+        <v>4071</v>
       </c>
       <c r="I366" s="1">
         <v>0</v>
       </c>
       <c r="J366" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>480</v>
@@ -13891,7 +13888,7 @@
         <v>181</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H367" s="1">
         <v>4071</v>
@@ -13905,7 +13902,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>4073</v>
+        <v>4074</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>480</v>
@@ -13920,7 +13917,7 @@
         <v>181</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="H368" s="1">
         <v>4071</v>
@@ -13934,7 +13931,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>480</v>
@@ -13949,7 +13946,7 @@
         <v>181</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H369" s="1">
         <v>4071</v>
@@ -13963,7 +13960,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>4075</v>
+        <v>4076</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>480</v>
@@ -13978,21 +13975,21 @@
         <v>181</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H370" s="1">
-        <v>4071</v>
+        <v>0</v>
       </c>
       <c r="I370" s="1">
         <v>0</v>
       </c>
       <c r="J370" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>480</v>
@@ -14007,21 +14004,21 @@
         <v>181</v>
       </c>
       <c r="G371" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H371" s="1">
-        <v>0</v>
+        <v>4076</v>
       </c>
       <c r="I371" s="1">
         <v>0</v>
       </c>
       <c r="J371" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>4077</v>
+        <v>4078</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>480</v>
@@ -14036,7 +14033,7 @@
         <v>181</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H372" s="1">
         <v>4076</v>
@@ -14050,7 +14047,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>480</v>
@@ -14065,7 +14062,7 @@
         <v>181</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H373" s="1">
         <v>4076</v>
@@ -14079,7 +14076,7 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>4079</v>
+        <v>4080</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>480</v>
@@ -14094,7 +14091,7 @@
         <v>181</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H374" s="1">
         <v>4076</v>
@@ -14108,7 +14105,7 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>480</v>
@@ -14123,21 +14120,21 @@
         <v>181</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H375" s="1">
-        <v>4076</v>
+        <v>0</v>
       </c>
       <c r="I375" s="1">
         <v>0</v>
       </c>
       <c r="J375" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>4081</v>
+        <v>4082</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>480</v>
@@ -14152,21 +14149,21 @@
         <v>181</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>421</v>
+        <v>80</v>
       </c>
       <c r="H376" s="1">
-        <v>0</v>
+        <v>4081</v>
       </c>
       <c r="I376" s="1">
         <v>0</v>
       </c>
       <c r="J376" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>4082</v>
+        <v>4083</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>480</v>
@@ -14181,7 +14178,7 @@
         <v>181</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="H377" s="1">
         <v>4081</v>
@@ -14195,7 +14192,7 @@
     </row>
     <row r="378" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>4083</v>
+        <v>4084</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>480</v>
@@ -14210,7 +14207,7 @@
         <v>181</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>59</v>
+        <v>329</v>
       </c>
       <c r="H378" s="1">
         <v>4081</v>
@@ -14222,9 +14219,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>4084</v>
+        <v>4085</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>480</v>
@@ -14239,7 +14236,7 @@
         <v>181</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>329</v>
+        <v>422</v>
       </c>
       <c r="H379" s="1">
         <v>4081</v>
@@ -14253,7 +14250,7 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>4085</v>
+        <v>4086</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>480</v>
@@ -14268,21 +14265,21 @@
         <v>181</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H380" s="1">
-        <v>4081</v>
+        <v>0</v>
       </c>
       <c r="I380" s="1">
         <v>0</v>
       </c>
       <c r="J380" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>4086</v>
+        <v>4087</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>480</v>
@@ -14297,21 +14294,21 @@
         <v>181</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H381" s="1">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="I381" s="1">
         <v>0</v>
       </c>
       <c r="J381" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>480</v>
@@ -14326,7 +14323,7 @@
         <v>181</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H382" s="1">
         <v>4086</v>
@@ -14340,7 +14337,7 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>480</v>
@@ -14355,7 +14352,7 @@
         <v>181</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H383" s="1">
         <v>4086</v>
@@ -14369,7 +14366,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>4089</v>
+        <v>4090</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>480</v>
@@ -14384,7 +14381,7 @@
         <v>181</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H384" s="1">
         <v>4086</v>
@@ -14398,7 +14395,7 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>4090</v>
+        <v>4091</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>480</v>
@@ -14413,21 +14410,21 @@
         <v>181</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H385" s="1">
-        <v>4086</v>
+        <v>0</v>
       </c>
       <c r="I385" s="1">
         <v>0</v>
       </c>
       <c r="J385" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>4091</v>
+        <v>4092</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>480</v>
@@ -14442,21 +14439,21 @@
         <v>181</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H386" s="1">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="I386" s="1">
         <v>0</v>
       </c>
       <c r="J386" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="387" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>480</v>
@@ -14471,7 +14468,7 @@
         <v>181</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H387" s="1">
         <v>4091</v>
@@ -14485,7 +14482,7 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>4093</v>
+        <v>4094</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>480</v>
@@ -14500,7 +14497,7 @@
         <v>181</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H388" s="1">
         <v>4091</v>
@@ -14514,7 +14511,7 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>480</v>
@@ -14529,7 +14526,7 @@
         <v>181</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H389" s="1">
         <v>4091</v>
@@ -14543,7 +14540,7 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>4095</v>
+        <v>4096</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>480</v>
@@ -14558,21 +14555,21 @@
         <v>181</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H390" s="1">
-        <v>4091</v>
+        <v>0</v>
       </c>
       <c r="I390" s="1">
         <v>0</v>
       </c>
       <c r="J390" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>4096</v>
+        <v>4097</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>480</v>
@@ -14587,21 +14584,21 @@
         <v>181</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H391" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="I391" s="1">
         <v>0</v>
       </c>
       <c r="J391" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>4097</v>
+        <v>4098</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>480</v>
@@ -14616,7 +14613,7 @@
         <v>181</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H392" s="1">
         <v>4096</v>
@@ -14630,7 +14627,7 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>4098</v>
+        <v>4099</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>480</v>
@@ -14645,7 +14642,7 @@
         <v>181</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H393" s="1">
         <v>4096</v>
@@ -14659,7 +14656,7 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>4099</v>
+        <v>4100</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>480</v>
@@ -14674,7 +14671,7 @@
         <v>181</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H394" s="1">
         <v>4096</v>
@@ -14688,7 +14685,7 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>4100</v>
+        <v>4101</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>480</v>
@@ -14703,21 +14700,21 @@
         <v>181</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H395" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="I395" s="1">
         <v>0</v>
       </c>
       <c r="J395" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>4101</v>
+        <v>4102</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>480</v>
@@ -14732,21 +14729,21 @@
         <v>181</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="H396" s="1">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="I396" s="1">
         <v>0</v>
       </c>
       <c r="J396" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>4102</v>
+        <v>4103</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>480</v>
@@ -14761,7 +14758,7 @@
         <v>181</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H397" s="1">
         <v>4101</v>
@@ -14773,9 +14770,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>4103</v>
+        <v>4104</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>480</v>
@@ -14790,7 +14787,7 @@
         <v>181</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>74</v>
+        <v>218</v>
       </c>
       <c r="H398" s="1">
         <v>4101</v>
@@ -14804,7 +14801,7 @@
     </row>
     <row r="399" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
-        <v>4104</v>
+        <v>4105</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>480</v>
@@ -14819,7 +14816,7 @@
         <v>181</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>218</v>
+        <v>439</v>
       </c>
       <c r="H399" s="1">
         <v>4101</v>
@@ -14831,9 +14828,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>4105</v>
+        <v>4106</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>480</v>
@@ -14848,21 +14845,21 @@
         <v>181</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H400" s="1">
-        <v>4101</v>
+        <v>0</v>
       </c>
       <c r="I400" s="1">
         <v>0</v>
       </c>
       <c r="J400" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>4106</v>
+        <v>4107</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>480</v>
@@ -14877,21 +14874,21 @@
         <v>181</v>
       </c>
       <c r="G401" s="1" t="s">
-        <v>440</v>
+        <v>75</v>
       </c>
       <c r="H401" s="1">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="I401" s="1">
         <v>0</v>
       </c>
       <c r="J401" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>4107</v>
+        <v>4108</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>480</v>
@@ -14906,7 +14903,7 @@
         <v>181</v>
       </c>
       <c r="G402" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="H402" s="1">
         <v>4106</v>
@@ -14920,7 +14917,7 @@
     </row>
     <row r="403" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
-        <v>4108</v>
+        <v>4109</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>480</v>
@@ -14935,7 +14932,7 @@
         <v>181</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H403" s="1">
         <v>4106</v>
@@ -14947,9 +14944,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
-        <v>4109</v>
+        <v>4110</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>480</v>
@@ -14964,7 +14961,7 @@
         <v>181</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>67</v>
+        <v>441</v>
       </c>
       <c r="H404" s="1">
         <v>4106</v>
@@ -14978,7 +14975,7 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
-        <v>4110</v>
+        <v>4111</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>480</v>
@@ -14993,21 +14990,21 @@
         <v>181</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H405" s="1">
-        <v>4106</v>
+        <v>0</v>
       </c>
       <c r="I405" s="1">
         <v>0</v>
       </c>
       <c r="J405" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
-        <v>4111</v>
+        <v>4112</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>480</v>
@@ -15022,21 +15019,21 @@
         <v>181</v>
       </c>
       <c r="G406" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H406" s="1">
-        <v>0</v>
+        <v>4111</v>
       </c>
       <c r="I406" s="1">
         <v>0</v>
       </c>
       <c r="J406" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
-        <v>4112</v>
+        <v>4113</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>480</v>
@@ -15051,7 +15048,7 @@
         <v>181</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H407" s="1">
         <v>4111</v>
@@ -15065,7 +15062,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
-        <v>4113</v>
+        <v>4114</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>480</v>
@@ -15079,8 +15076,8 @@
       <c r="F408" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G408" s="1" t="s">
-        <v>444</v>
+      <c r="G408" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="H408" s="1">
         <v>4111</v>
@@ -15094,7 +15091,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
-        <v>4114</v>
+        <v>4115</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>480</v>
@@ -15108,8 +15105,8 @@
       <c r="F409" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G409" s="2" t="s">
-        <v>445</v>
+      <c r="G409" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="H409" s="1">
         <v>4111</v>
@@ -15123,7 +15120,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
-        <v>4115</v>
+        <v>4116</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>480</v>
@@ -15138,21 +15135,21 @@
         <v>181</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H410" s="1">
-        <v>4111</v>
+        <v>0</v>
       </c>
       <c r="I410" s="1">
         <v>0</v>
       </c>
       <c r="J410" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
-        <v>4116</v>
+        <v>4117</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>480</v>
@@ -15167,21 +15164,21 @@
         <v>181</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>447</v>
+        <v>70</v>
       </c>
       <c r="H411" s="1">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="I411" s="1">
         <v>0</v>
       </c>
       <c r="J411" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="412" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
-        <v>4117</v>
+        <v>4118</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>480</v>
@@ -15196,7 +15193,7 @@
         <v>181</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H412" s="1">
         <v>4116</v>
@@ -15208,9 +15205,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
-        <v>4118</v>
+        <v>4119</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>480</v>
@@ -15225,7 +15222,7 @@
         <v>181</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H413" s="1">
         <v>4116</v>
@@ -15239,7 +15236,7 @@
     </row>
     <row r="414" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>480</v>
@@ -15254,7 +15251,7 @@
         <v>181</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>63</v>
+        <v>448</v>
       </c>
       <c r="H414" s="1">
         <v>4116</v>
@@ -15266,9 +15263,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
-        <v>4120</v>
+        <v>4121</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>480</v>
@@ -15283,21 +15280,21 @@
         <v>181</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H415" s="1">
-        <v>4116</v>
+        <v>0</v>
       </c>
       <c r="I415" s="1">
         <v>0</v>
       </c>
       <c r="J415" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
-        <v>4121</v>
+        <v>4122</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>480</v>
@@ -15312,21 +15309,21 @@
         <v>181</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H416" s="1">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="I416" s="1">
         <v>0</v>
       </c>
       <c r="J416" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
-        <v>4122</v>
+        <v>4123</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>480</v>
@@ -15341,7 +15338,7 @@
         <v>181</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H417" s="1">
         <v>4121</v>
@@ -15355,7 +15352,7 @@
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
-        <v>4123</v>
+        <v>4124</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>480</v>
@@ -15370,7 +15367,7 @@
         <v>181</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H418" s="1">
         <v>4121</v>
@@ -15384,7 +15381,7 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
-        <v>4124</v>
+        <v>4125</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>480</v>
@@ -15399,7 +15396,7 @@
         <v>181</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H419" s="1">
         <v>4121</v>
@@ -15413,7 +15410,7 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
-        <v>4125</v>
+        <v>4126</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>480</v>
@@ -15428,21 +15425,21 @@
         <v>181</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H420" s="1">
-        <v>4121</v>
+        <v>0</v>
       </c>
       <c r="I420" s="1">
         <v>0</v>
       </c>
       <c r="J420" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
-        <v>4126</v>
+        <v>4127</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>480</v>
@@ -15457,21 +15454,21 @@
         <v>181</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>454</v>
+        <v>71</v>
       </c>
       <c r="H421" s="1">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="I421" s="1">
         <v>0</v>
       </c>
       <c r="J421" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
-        <v>4127</v>
+        <v>4128</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>480</v>
@@ -15486,7 +15483,7 @@
         <v>181</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H422" s="1">
         <v>4126</v>
@@ -15498,9 +15495,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
-        <v>4128</v>
+        <v>4129</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>480</v>
@@ -15515,7 +15512,7 @@
         <v>181</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H423" s="1">
         <v>4126</v>
@@ -15527,9 +15524,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
-        <v>4129</v>
+        <v>4130</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>480</v>
@@ -15544,7 +15541,7 @@
         <v>181</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="H424" s="1">
         <v>4126</v>
@@ -15556,9 +15553,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
-        <v>4130</v>
+        <v>4131</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>480</v>
@@ -15573,7 +15570,7 @@
         <v>181</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>55</v>
+        <v>455</v>
       </c>
       <c r="H425" s="1">
         <v>4126</v>
@@ -15585,9 +15582,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
-        <v>4131</v>
+        <v>4132</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>480</v>
@@ -15602,21 +15599,21 @@
         <v>181</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H426" s="1">
-        <v>4126</v>
+        <v>0</v>
       </c>
       <c r="I426" s="1">
         <v>0</v>
       </c>
       <c r="J426" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>480</v>
@@ -15631,21 +15628,21 @@
         <v>181</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="H427" s="1">
-        <v>0</v>
+        <v>4132</v>
       </c>
       <c r="I427" s="1">
         <v>0</v>
       </c>
       <c r="J427" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
-        <v>4133</v>
+        <v>4134</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>480</v>
@@ -15660,7 +15657,7 @@
         <v>181</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="H428" s="1">
         <v>4132</v>
@@ -15672,9 +15669,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
-        <v>4134</v>
+        <v>4135</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>480</v>
@@ -15689,7 +15686,7 @@
         <v>181</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>457</v>
+        <v>66</v>
       </c>
       <c r="H429" s="1">
         <v>4132</v>
@@ -15701,9 +15698,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
-        <v>4135</v>
+        <v>4136</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>480</v>
@@ -15718,7 +15715,7 @@
         <v>181</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>66</v>
+        <v>458</v>
       </c>
       <c r="H430" s="1">
         <v>4132</v>
@@ -15730,9 +15727,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
-        <v>4136</v>
+        <v>4137</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>480</v>
@@ -15747,21 +15744,21 @@
         <v>181</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H431" s="1">
-        <v>4132</v>
+        <v>0</v>
       </c>
       <c r="I431" s="1">
         <v>0</v>
       </c>
       <c r="J431" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
-        <v>4137</v>
+        <v>4138</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>480</v>
@@ -15776,21 +15773,21 @@
         <v>181</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H432" s="1">
-        <v>0</v>
+        <v>4137</v>
       </c>
       <c r="I432" s="1">
         <v>0</v>
       </c>
       <c r="J432" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
-        <v>4138</v>
+        <v>4139</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>480</v>
@@ -15805,7 +15802,7 @@
         <v>181</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H433" s="1">
         <v>4137</v>
@@ -15817,9 +15814,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
-        <v>4139</v>
+        <v>4140</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>480</v>
@@ -15834,7 +15831,7 @@
         <v>181</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H434" s="1">
         <v>4137</v>
@@ -15848,7 +15845,7 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
-        <v>4140</v>
+        <v>4141</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>480</v>
@@ -15863,7 +15860,7 @@
         <v>181</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H435" s="1">
         <v>4137</v>
@@ -15877,7 +15874,7 @@
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
-        <v>4141</v>
+        <v>4142</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>480</v>
@@ -15892,21 +15889,21 @@
         <v>181</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H436" s="1">
-        <v>4137</v>
+        <v>0</v>
       </c>
       <c r="I436" s="1">
         <v>0</v>
       </c>
       <c r="J436" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
-        <v>4142</v>
+        <v>4143</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>480</v>
@@ -15921,21 +15918,21 @@
         <v>181</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H437" s="1">
-        <v>0</v>
+        <v>4142</v>
       </c>
       <c r="I437" s="1">
         <v>0</v>
       </c>
       <c r="J437" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
-        <v>4143</v>
+        <v>4144</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>480</v>
@@ -15950,7 +15947,7 @@
         <v>181</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>465</v>
+        <v>48</v>
       </c>
       <c r="H438" s="1">
         <v>4142</v>
@@ -15962,9 +15959,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>480</v>
@@ -15979,7 +15976,7 @@
         <v>181</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H439" s="1">
         <v>4142</v>
@@ -15993,7 +15990,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
-        <v>4145</v>
+        <v>4146</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>480</v>
@@ -16008,7 +16005,7 @@
         <v>181</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>60</v>
+        <v>466</v>
       </c>
       <c r="H440" s="1">
         <v>4142</v>
@@ -16022,7 +16019,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
-        <v>4146</v>
+        <v>4147</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>480</v>
@@ -16037,21 +16034,21 @@
         <v>181</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H441" s="1">
-        <v>4142</v>
+        <v>0</v>
       </c>
       <c r="I441" s="1">
         <v>0</v>
       </c>
       <c r="J441" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
-        <v>4147</v>
+        <v>4148</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>480</v>
@@ -16066,21 +16063,21 @@
         <v>181</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>467</v>
+        <v>79</v>
       </c>
       <c r="H442" s="1">
-        <v>0</v>
+        <v>4147</v>
       </c>
       <c r="I442" s="1">
         <v>0</v>
       </c>
       <c r="J442" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
-        <v>4148</v>
+        <v>4149</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>480</v>
@@ -16095,7 +16092,7 @@
         <v>181</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>79</v>
+        <v>468</v>
       </c>
       <c r="H443" s="1">
         <v>4147</v>
@@ -16109,7 +16106,7 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
-        <v>4149</v>
+        <v>4150</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>480</v>
@@ -16124,7 +16121,7 @@
         <v>181</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H444" s="1">
         <v>4147</v>
@@ -16138,7 +16135,7 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
-        <v>4150</v>
+        <v>4151</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>480</v>
@@ -16153,7 +16150,7 @@
         <v>181</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H445" s="1">
         <v>4147</v>
@@ -16167,7 +16164,7 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
-        <v>4151</v>
+        <v>4152</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>480</v>
@@ -16182,21 +16179,21 @@
         <v>181</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H446" s="1">
-        <v>4147</v>
+        <v>0</v>
       </c>
       <c r="I446" s="1">
         <v>0</v>
       </c>
       <c r="J446" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
-        <v>4152</v>
+        <v>4153</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>480</v>
@@ -16211,21 +16208,21 @@
         <v>181</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H447" s="1">
-        <v>0</v>
+        <v>4152</v>
       </c>
       <c r="I447" s="1">
         <v>0</v>
       </c>
       <c r="J447" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
-        <v>4153</v>
+        <v>4154</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>480</v>
@@ -16240,7 +16237,7 @@
         <v>181</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H448" s="1">
         <v>4152</v>
@@ -16254,7 +16251,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
-        <v>4154</v>
+        <v>4155</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>480</v>
@@ -16269,7 +16266,7 @@
         <v>181</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H449" s="1">
         <v>4152</v>
@@ -16283,7 +16280,7 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
-        <v>4155</v>
+        <v>4156</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>480</v>
@@ -16298,7 +16295,7 @@
         <v>181</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H450" s="1">
         <v>4152</v>
@@ -16312,7 +16309,7 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
-        <v>4156</v>
+        <v>4157</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>480</v>
@@ -16327,21 +16324,21 @@
         <v>181</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H451" s="1">
-        <v>4152</v>
+        <v>0</v>
       </c>
       <c r="I451" s="1">
         <v>0</v>
       </c>
       <c r="J451" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
-        <v>4157</v>
+        <v>4158</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>480</v>
@@ -16356,21 +16353,21 @@
         <v>181</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>476</v>
+        <v>52</v>
       </c>
       <c r="H452" s="1">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="I452" s="1">
         <v>0</v>
       </c>
       <c r="J452" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="453" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
-        <v>4158</v>
+        <v>4159</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>480</v>
@@ -16385,7 +16382,7 @@
         <v>181</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>52</v>
+        <v>477</v>
       </c>
       <c r="H453" s="1">
         <v>4157</v>
@@ -16399,7 +16396,7 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
-        <v>4159</v>
+        <v>4160</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>480</v>
@@ -16414,7 +16411,7 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H454" s="1">
         <v>4157</v>
@@ -16428,7 +16425,7 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
-        <v>4160</v>
+        <v>4161</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>480</v>
@@ -16443,7 +16440,7 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H455" s="1">
         <v>4157</v>
@@ -16457,13 +16454,13 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
-        <v>4161</v>
+        <v>5001</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>480</v>
+        <v>284</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="E456" s="1">
         <v>0</v>
@@ -16472,10 +16469,10 @@
         <v>181</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>479</v>
+        <v>291</v>
       </c>
       <c r="H456" s="1">
-        <v>4157</v>
+        <v>0</v>
       </c>
       <c r="I456" s="1">
         <v>0</v>
@@ -16486,7 +16483,7 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
-        <v>5001</v>
+        <v>6000</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>284</v>
@@ -16501,7 +16498,7 @@
         <v>181</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H457" s="1">
         <v>0</v>
@@ -16515,7 +16512,7 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
-        <v>6000</v>
+        <v>6001</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>284</v>
@@ -16530,7 +16527,7 @@
         <v>181</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H458" s="1">
         <v>0</v>
@@ -16544,7 +16541,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>284</v>
@@ -16559,7 +16556,7 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H459" s="1">
         <v>0</v>
@@ -16573,7 +16570,7 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>284</v>
@@ -16588,7 +16585,7 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H460" s="1">
         <v>0</v>
@@ -16602,7 +16599,7 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>284</v>
@@ -16617,7 +16614,7 @@
         <v>181</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H461" s="1">
         <v>0</v>
@@ -16631,7 +16628,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
-        <v>6004</v>
+        <v>6005</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>284</v>
@@ -16646,7 +16643,7 @@
         <v>181</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H462" s="1">
         <v>0</v>
@@ -16660,7 +16657,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>6005</v>
+        <v>6006</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>284</v>
@@ -16675,7 +16672,7 @@
         <v>181</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H463" s="1">
         <v>0</v>
@@ -16689,7 +16686,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>6006</v>
+        <v>6100</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>284</v>
@@ -16704,7 +16701,7 @@
         <v>181</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H464" s="1">
         <v>0</v>
@@ -16718,10 +16715,10 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
-        <v>6100</v>
+        <v>8100</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D465" s="1" t="s">
         <v>183</v>
@@ -16733,7 +16730,7 @@
         <v>181</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="H465" s="1">
         <v>0</v>
@@ -16742,40 +16739,11 @@
         <v>0</v>
       </c>
       <c r="J465" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A466" s="1">
-        <v>8100</v>
-      </c>
-      <c r="B466" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="D466" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E466" s="1">
-        <v>0</v>
-      </c>
-      <c r="F466" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G466" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="H466" s="1">
-        <v>0</v>
-      </c>
-      <c r="I466" s="1">
-        <v>0</v>
-      </c>
-      <c r="J466" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J466"/>
+  <autoFilter ref="A3:J465"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -9,15 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="135" windowWidth="9675" windowHeight="7380"/>
   </bookViews>
   <sheets>
-    <sheet name="Chart1" sheetId="3" r:id="rId1"/>
-    <sheet name="TalkData" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="TalkData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TalkData!$A$3:$J$465</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$469</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="579">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1868,10 +1867,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这里以后就归你管理了,现在准备种植吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>第一步,先将农具从背包里拿出来。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1889,6 +1884,38 @@
   </si>
   <si>
     <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢，我会好好使用的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里就是农场，以后就归你管理了,现在准备种植吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前面就是春之山脉的入口，今天就让我这个老头子陪你闯一下吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在前进走到光圈中，开始今天的探索。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打起精神来，现在前进吧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1988,852 +2015,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="zh-CN"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:val>
-            <c:numRef>
-              <c:f>TalkData!$A$169:$J$169</c:f>
-              <c:numCache>
-                <c:formatCode>@</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0" formatCode="General">
-                  <c:v>1424</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="General">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="General">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-469A-455C-A869-043053ADB3E3}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="1721976016"/>
-        <c:axId val="1721980176"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1721976016"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1721980176"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1721980176"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1721976016"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
-    </a:p>
-  </c:txPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</chartsheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:absoluteAnchor>
-    <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9311355" cy="6079977"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks noGrp="1"/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:absoluteAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3124,7 +2305,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J465"/>
+  <dimension ref="A2:J469"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -8071,7 +7252,7 @@
         <v>10</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -8135,7 +7316,7 @@
         <v>10</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -8160,14 +7341,14 @@
       <c r="A172" s="1">
         <v>1427</v>
       </c>
-      <c r="B172" s="3">
-        <v>2</v>
+      <c r="B172" s="3" t="s">
+        <v>561</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>262</v>
+        <v>182</v>
       </c>
       <c r="E172" s="1">
         <v>0</v>
@@ -8176,13 +7357,13 @@
         <v>189</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="H172" s="1">
-        <v>1428</v>
+        <v>0</v>
       </c>
       <c r="I172" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="J172" s="1" t="b">
         <v>0</v>
@@ -8205,16 +7386,16 @@
         <v>1</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="H173" s="1">
-        <v>0</v>
+        <v>1429</v>
       </c>
       <c r="I173" s="1">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J173" s="1" t="b">
         <v>0</v>
@@ -8224,8 +7405,8 @@
       <c r="A174" s="1">
         <v>1429</v>
       </c>
-      <c r="B174" s="3" t="s">
-        <v>561</v>
+      <c r="B174" s="3">
+        <v>2</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>9</v>
@@ -8237,16 +7418,16 @@
         <v>1</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H174" s="1">
         <v>0</v>
       </c>
       <c r="I174" s="1">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="J174" s="1" t="b">
         <v>0</v>
@@ -8269,16 +7450,16 @@
         <v>1</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
       </c>
       <c r="I175" s="1">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="J175" s="1" t="b">
         <v>0</v>
@@ -8292,68 +7473,68 @@
         <v>2</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>182</v>
+        <v>262</v>
       </c>
       <c r="E176" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>110</v>
+        <v>568</v>
       </c>
       <c r="H176" s="1">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="I176" s="1">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="J176" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>1432</v>
       </c>
-      <c r="B177" s="3">
-        <v>2</v>
+      <c r="B177" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>262</v>
+        <v>182</v>
       </c>
       <c r="E177" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>570</v>
+        <v>110</v>
       </c>
       <c r="H177" s="1">
-        <v>0</v>
+        <v>1433</v>
       </c>
       <c r="I177" s="1">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J177" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>1433</v>
       </c>
-      <c r="B178" s="3">
-        <v>2</v>
+      <c r="B178" s="3" t="s">
+        <v>573</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>9</v>
@@ -8365,22 +7546,22 @@
         <v>1</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>111</v>
+        <v>569</v>
       </c>
       <c r="H178" s="1">
-        <v>1434</v>
+        <v>0</v>
       </c>
       <c r="I178" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J178" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>1434</v>
       </c>
@@ -8397,22 +7578,22 @@
         <v>1</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>255</v>
+        <v>189</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>563</v>
+        <v>111</v>
       </c>
       <c r="H179" s="1">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="I179" s="1">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="J179" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>1435</v>
       </c>
@@ -8432,36 +7613,39 @@
         <v>255</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>112</v>
+        <v>563</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
       <c r="I180" s="1">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J180" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>1610</v>
+        <v>1436</v>
       </c>
       <c r="B181" s="3">
         <v>2</v>
       </c>
+      <c r="C181" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="D181" s="1" t="s">
-        <v>183</v>
+        <v>262</v>
       </c>
       <c r="E181" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>113</v>
+        <v>575</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -8475,28 +7659,31 @@
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>1611</v>
+        <v>1438</v>
       </c>
       <c r="B182" s="3">
         <v>2</v>
       </c>
+      <c r="C182" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="D182" s="1" t="s">
-        <v>183</v>
+        <v>262</v>
       </c>
       <c r="E182" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>225</v>
+        <v>576</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
       </c>
       <c r="I182" s="1">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J182" s="1" t="b">
         <v>0</v>
@@ -8504,51 +7691,57 @@
     </row>
     <row r="183" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>1612</v>
-      </c>
-      <c r="B183" s="3">
-        <v>2</v>
+        <v>1439</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>183</v>
+        <v>262</v>
       </c>
       <c r="E183" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>114</v>
+        <v>578</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
       </c>
       <c r="I183" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J183" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>1613</v>
+        <v>1440</v>
       </c>
       <c r="B184" s="3">
         <v>2</v>
       </c>
+      <c r="C184" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="D184" s="1" t="s">
-        <v>183</v>
+        <v>262</v>
       </c>
       <c r="E184" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>255</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
@@ -8562,7 +7755,7 @@
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>1614</v>
+        <v>1610</v>
       </c>
       <c r="B185" s="3">
         <v>2</v>
@@ -8577,7 +7770,7 @@
         <v>255</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
@@ -8591,7 +7784,7 @@
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>1615</v>
+        <v>1611</v>
       </c>
       <c r="B186" s="3">
         <v>2</v>
@@ -8606,7 +7799,7 @@
         <v>255</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
@@ -8620,7 +7813,7 @@
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="B187" s="3">
         <v>2</v>
@@ -8635,7 +7828,7 @@
         <v>255</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
@@ -8649,7 +7842,7 @@
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>1617</v>
+        <v>1613</v>
       </c>
       <c r="B188" s="3">
         <v>2</v>
@@ -8664,7 +7857,7 @@
         <v>255</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
@@ -8678,7 +7871,7 @@
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>1618</v>
+        <v>1614</v>
       </c>
       <c r="B189" s="3">
         <v>2</v>
@@ -8693,7 +7886,7 @@
         <v>255</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>118</v>
+        <v>226</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
@@ -8707,7 +7900,7 @@
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>1619</v>
+        <v>1615</v>
       </c>
       <c r="B190" s="3">
         <v>2</v>
@@ -8722,7 +7915,7 @@
         <v>255</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>119</v>
+        <v>227</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
@@ -8736,7 +7929,7 @@
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="B191" s="3">
         <v>2</v>
@@ -8751,7 +7944,7 @@
         <v>255</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
@@ -8765,7 +7958,7 @@
     </row>
     <row r="192" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>1621</v>
+        <v>1617</v>
       </c>
       <c r="B192" s="3">
         <v>2</v>
@@ -8780,7 +7973,7 @@
         <v>255</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
@@ -8794,7 +7987,7 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="B193" s="3">
         <v>2</v>
@@ -8809,7 +8002,7 @@
         <v>255</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
@@ -8823,7 +8016,7 @@
     </row>
     <row r="194" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="B194" s="3">
         <v>2</v>
@@ -8838,7 +8031,7 @@
         <v>255</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
@@ -8852,7 +8045,7 @@
     </row>
     <row r="195" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="B195" s="3">
         <v>2</v>
@@ -8867,7 +8060,7 @@
         <v>255</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
@@ -8881,7 +8074,7 @@
     </row>
     <row r="196" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>1625</v>
+        <v>1621</v>
       </c>
       <c r="B196" s="3">
         <v>2</v>
@@ -8896,7 +8089,7 @@
         <v>255</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
@@ -8910,7 +8103,7 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>1626</v>
+        <v>1622</v>
       </c>
       <c r="B197" s="3">
         <v>2</v>
@@ -8925,7 +8118,7 @@
         <v>255</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
@@ -8939,7 +8132,7 @@
     </row>
     <row r="198" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>1627</v>
+        <v>1623</v>
       </c>
       <c r="B198" s="3">
         <v>2</v>
@@ -8954,7 +8147,7 @@
         <v>255</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
@@ -8968,7 +8161,7 @@
     </row>
     <row r="199" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>1628</v>
+        <v>1624</v>
       </c>
       <c r="B199" s="3">
         <v>2</v>
@@ -8983,7 +8176,7 @@
         <v>255</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H199" s="1">
         <v>0</v>
@@ -8997,7 +8190,7 @@
     </row>
     <row r="200" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>1629</v>
+        <v>1625</v>
       </c>
       <c r="B200" s="3">
         <v>2</v>
@@ -9012,7 +8205,7 @@
         <v>255</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H200" s="1">
         <v>0</v>
@@ -9026,7 +8219,7 @@
     </row>
     <row r="201" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>1630</v>
+        <v>1626</v>
       </c>
       <c r="B201" s="3">
         <v>2</v>
@@ -9041,7 +8234,7 @@
         <v>255</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H201" s="1">
         <v>0</v>
@@ -9055,7 +8248,7 @@
     </row>
     <row r="202" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>1631</v>
+        <v>1627</v>
       </c>
       <c r="B202" s="3">
         <v>2</v>
@@ -9070,7 +8263,7 @@
         <v>255</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
       <c r="H202" s="1">
         <v>0</v>
@@ -9082,9 +8275,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>1632</v>
+        <v>1628</v>
       </c>
       <c r="B203" s="3">
         <v>2</v>
@@ -9099,7 +8292,7 @@
         <v>255</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>129</v>
+        <v>229</v>
       </c>
       <c r="H203" s="1">
         <v>0</v>
@@ -9113,7 +8306,7 @@
     </row>
     <row r="204" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>1633</v>
+        <v>1629</v>
       </c>
       <c r="B204" s="3">
         <v>2</v>
@@ -9128,7 +8321,7 @@
         <v>255</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
@@ -9142,7 +8335,7 @@
     </row>
     <row r="205" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>1634</v>
+        <v>1630</v>
       </c>
       <c r="B205" s="3">
         <v>2</v>
@@ -9157,7 +8350,7 @@
         <v>255</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
@@ -9171,7 +8364,7 @@
     </row>
     <row r="206" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>1635</v>
+        <v>1631</v>
       </c>
       <c r="B206" s="3">
         <v>2</v>
@@ -9186,7 +8379,7 @@
         <v>255</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>132</v>
+        <v>230</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
@@ -9198,9 +8391,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="B207" s="3">
         <v>2</v>
@@ -9215,7 +8408,7 @@
         <v>255</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
@@ -9229,7 +8422,7 @@
     </row>
     <row r="208" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>1637</v>
+        <v>1633</v>
       </c>
       <c r="B208" s="3">
         <v>2</v>
@@ -9244,7 +8437,7 @@
         <v>255</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
@@ -9256,9 +8449,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="B209" s="3">
         <v>2</v>
@@ -9273,7 +8466,7 @@
         <v>255</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
@@ -9287,7 +8480,7 @@
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="B210" s="3">
         <v>2</v>
@@ -9302,7 +8495,7 @@
         <v>255</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
@@ -9314,9 +8507,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="B211" s="3">
         <v>2</v>
@@ -9331,7 +8524,7 @@
         <v>255</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
@@ -9345,7 +8538,7 @@
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="B212" s="3">
         <v>2</v>
@@ -9360,7 +8553,7 @@
         <v>255</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
@@ -9372,9 +8565,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="B213" s="3">
         <v>2</v>
@@ -9389,7 +8582,7 @@
         <v>255</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
@@ -9403,7 +8596,7 @@
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>1643</v>
+        <v>1639</v>
       </c>
       <c r="B214" s="3">
         <v>2</v>
@@ -9418,7 +8611,7 @@
         <v>255</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
@@ -9430,9 +8623,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>1644</v>
+        <v>1640</v>
       </c>
       <c r="B215" s="3">
         <v>2</v>
@@ -9447,7 +8640,7 @@
         <v>255</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
@@ -9461,7 +8654,7 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>1645</v>
+        <v>1641</v>
       </c>
       <c r="B216" s="3">
         <v>2</v>
@@ -9476,7 +8669,7 @@
         <v>255</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
@@ -9488,9 +8681,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>1646</v>
+        <v>1642</v>
       </c>
       <c r="B217" s="3">
         <v>2</v>
@@ -9505,7 +8698,7 @@
         <v>255</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H217" s="1">
         <v>0</v>
@@ -9517,9 +8710,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="B218" s="3">
         <v>2</v>
@@ -9534,7 +8727,7 @@
         <v>255</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>307</v>
+        <v>140</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
@@ -9548,7 +8741,7 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>1648</v>
+        <v>1644</v>
       </c>
       <c r="B219" s="3">
         <v>2</v>
@@ -9563,7 +8756,7 @@
         <v>255</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
@@ -9577,7 +8770,7 @@
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>1500</v>
+        <v>1645</v>
       </c>
       <c r="B220" s="3">
         <v>2</v>
@@ -9592,7 +8785,7 @@
         <v>255</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H220" s="1">
         <v>0</v>
@@ -9604,9 +8797,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>1501</v>
+        <v>1646</v>
       </c>
       <c r="B221" s="3">
         <v>2</v>
@@ -9621,7 +8814,7 @@
         <v>255</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H221" s="1">
         <v>0</v>
@@ -9633,9 +8826,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>1502</v>
+        <v>1647</v>
       </c>
       <c r="B222" s="3">
         <v>2</v>
@@ -9650,7 +8843,7 @@
         <v>255</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>147</v>
+        <v>307</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -9664,7 +8857,7 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>1503</v>
+        <v>1648</v>
       </c>
       <c r="B223" s="3">
         <v>2</v>
@@ -9679,7 +8872,7 @@
         <v>255</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
@@ -9693,7 +8886,7 @@
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="B224" s="3">
         <v>2</v>
@@ -9708,7 +8901,7 @@
         <v>255</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H224" s="1">
         <v>0</v>
@@ -9722,7 +8915,7 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="B225" s="3">
         <v>2</v>
@@ -9737,7 +8930,7 @@
         <v>255</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H225" s="1">
         <v>0</v>
@@ -9751,7 +8944,7 @@
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="B226" s="3">
         <v>2</v>
@@ -9766,7 +8959,7 @@
         <v>255</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H226" s="1">
         <v>0</v>
@@ -9780,7 +8973,7 @@
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="B227" s="3">
         <v>2</v>
@@ -9795,7 +8988,7 @@
         <v>255</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
@@ -9809,7 +9002,7 @@
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="B228" s="3">
         <v>2</v>
@@ -9824,7 +9017,7 @@
         <v>255</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
@@ -9838,7 +9031,7 @@
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="B229" s="3">
         <v>2</v>
@@ -9853,7 +9046,7 @@
         <v>255</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
@@ -9867,7 +9060,7 @@
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="B230" s="3">
         <v>2</v>
@@ -9882,7 +9075,7 @@
         <v>255</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>231</v>
+        <v>151</v>
       </c>
       <c r="H230" s="1">
         <v>0</v>
@@ -9896,7 +9089,7 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="B231" s="3">
         <v>2</v>
@@ -9911,7 +9104,7 @@
         <v>255</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
@@ -9925,7 +9118,7 @@
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>1512</v>
+        <v>1508</v>
       </c>
       <c r="B232" s="3">
         <v>2</v>
@@ -9940,7 +9133,7 @@
         <v>255</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
@@ -9954,7 +9147,7 @@
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>1513</v>
+        <v>1509</v>
       </c>
       <c r="B233" s="3">
         <v>2</v>
@@ -9969,7 +9162,7 @@
         <v>255</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="H233" s="1">
         <v>0</v>
@@ -9983,7 +9176,7 @@
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="B234" s="3">
         <v>2</v>
@@ -9998,7 +9191,7 @@
         <v>255</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
@@ -10012,7 +9205,7 @@
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="B235" s="3">
         <v>2</v>
@@ -10027,7 +9220,7 @@
         <v>255</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>235</v>
+        <v>155</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
@@ -10041,7 +9234,7 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="B236" s="3">
         <v>2</v>
@@ -10056,7 +9249,7 @@
         <v>255</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
@@ -10070,7 +9263,7 @@
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="B237" s="3">
         <v>2</v>
@@ -10085,7 +9278,7 @@
         <v>255</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
@@ -10099,7 +9292,7 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="B238" s="3">
         <v>2</v>
@@ -10114,7 +9307,7 @@
         <v>255</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
@@ -10128,7 +9321,7 @@
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="B239" s="3">
         <v>2</v>
@@ -10143,7 +9336,7 @@
         <v>255</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>156</v>
+        <v>235</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
@@ -10157,7 +9350,7 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="B240" s="3">
         <v>2</v>
@@ -10172,7 +9365,7 @@
         <v>255</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>157</v>
+        <v>236</v>
       </c>
       <c r="H240" s="1">
         <v>0</v>
@@ -10186,7 +9379,7 @@
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>2001</v>
+        <v>1517</v>
       </c>
       <c r="B241" s="3">
         <v>2</v>
@@ -10201,7 +9394,7 @@
         <v>255</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H241" s="1">
         <v>0</v>
@@ -10215,7 +9408,7 @@
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>2002</v>
+        <v>1518</v>
       </c>
       <c r="B242" s="3">
         <v>2</v>
@@ -10230,7 +9423,7 @@
         <v>255</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="H242" s="1">
         <v>0</v>
@@ -10244,7 +9437,7 @@
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>2003</v>
+        <v>1519</v>
       </c>
       <c r="B243" s="3">
         <v>2</v>
@@ -10259,7 +9452,7 @@
         <v>255</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>240</v>
+        <v>156</v>
       </c>
       <c r="H243" s="1">
         <v>0</v>
@@ -10273,7 +9466,7 @@
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>2004</v>
+        <v>1520</v>
       </c>
       <c r="B244" s="3">
         <v>2</v>
@@ -10288,7 +9481,7 @@
         <v>255</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>241</v>
+        <v>157</v>
       </c>
       <c r="H244" s="1">
         <v>0</v>
@@ -10302,7 +9495,7 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="B245" s="3">
         <v>2</v>
@@ -10317,7 +9510,7 @@
         <v>255</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
@@ -10331,7 +9524,7 @@
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="B246" s="3">
         <v>2</v>
@@ -10346,7 +9539,7 @@
         <v>255</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>243</v>
+        <v>158</v>
       </c>
       <c r="H246" s="1">
         <v>0</v>
@@ -10360,7 +9553,7 @@
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B247" s="3">
         <v>2</v>
@@ -10375,7 +9568,7 @@
         <v>255</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
@@ -10389,7 +9582,7 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B248" s="3">
         <v>2</v>
@@ -10404,7 +9597,7 @@
         <v>255</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
@@ -10418,7 +9611,7 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B249" s="3">
         <v>2</v>
@@ -10433,7 +9626,7 @@
         <v>255</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
@@ -10447,7 +9640,7 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B250" s="3">
         <v>2</v>
@@ -10462,7 +9655,7 @@
         <v>255</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
@@ -10476,7 +9669,7 @@
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A251" s="1">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B251" s="3">
         <v>2</v>
@@ -10491,7 +9684,7 @@
         <v>255</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>159</v>
+        <v>244</v>
       </c>
       <c r="H251" s="1">
         <v>0</v>
@@ -10505,7 +9698,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A252" s="1">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="B252" s="3">
         <v>2</v>
@@ -10520,7 +9713,7 @@
         <v>255</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
@@ -10534,7 +9727,7 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A253" s="1">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="B253" s="3">
         <v>2</v>
@@ -10549,7 +9742,7 @@
         <v>255</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>161</v>
+        <v>246</v>
       </c>
       <c r="H253" s="1">
         <v>0</v>
@@ -10563,7 +9756,7 @@
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A254" s="1">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B254" s="3">
         <v>2</v>
@@ -10578,7 +9771,7 @@
         <v>255</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>162</v>
+        <v>247</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
@@ -10592,7 +9785,7 @@
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A255" s="1">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="B255" s="3">
         <v>2</v>
@@ -10607,7 +9800,7 @@
         <v>255</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H255" s="1">
         <v>0</v>
@@ -10621,7 +9814,7 @@
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" s="1">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="B256" s="3">
         <v>2</v>
@@ -10636,7 +9829,7 @@
         <v>255</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="H256" s="1">
         <v>0</v>
@@ -10650,7 +9843,7 @@
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" s="1">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="B257" s="3">
         <v>2</v>
@@ -10665,7 +9858,7 @@
         <v>255</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H257" s="1">
         <v>0</v>
@@ -10679,7 +9872,7 @@
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" s="1">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B258" s="3">
         <v>2</v>
@@ -10694,7 +9887,7 @@
         <v>255</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H258" s="1">
         <v>0</v>
@@ -10708,7 +9901,7 @@
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" s="1">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B259" s="3">
         <v>2</v>
@@ -10723,7 +9916,7 @@
         <v>255</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>249</v>
+        <v>163</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
@@ -10737,7 +9930,7 @@
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" s="1">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="B260" s="3">
         <v>2</v>
@@ -10752,7 +9945,7 @@
         <v>255</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="H260" s="1">
         <v>0</v>
@@ -10766,7 +9959,7 @@
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" s="1">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B261" s="3">
         <v>2</v>
@@ -10781,7 +9974,7 @@
         <v>255</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
@@ -10795,7 +9988,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A262" s="1">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="B262" s="3">
         <v>2</v>
@@ -10810,7 +10003,7 @@
         <v>255</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H262" s="1">
         <v>0</v>
@@ -10824,7 +10017,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" s="1">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="B263" s="3">
         <v>2</v>
@@ -10839,7 +10032,7 @@
         <v>255</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="H263" s="1">
         <v>0</v>
@@ -10853,7 +10046,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" s="1">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="B264" s="3">
         <v>2</v>
@@ -10868,7 +10061,7 @@
         <v>255</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
@@ -10882,28 +10075,25 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" s="1">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="B265" s="3">
         <v>2</v>
       </c>
-      <c r="C265" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="D265" s="1" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="E265" s="1">
         <v>0</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H265" s="1">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="I265" s="1">
         <v>0</v>
@@ -10914,16 +10104,13 @@
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A266" s="1">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="B266" s="3">
         <v>2</v>
       </c>
-      <c r="C266" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="D266" s="1" t="s">
-        <v>259</v>
+        <v>183</v>
       </c>
       <c r="E266" s="1">
         <v>0</v>
@@ -10932,7 +10119,7 @@
         <v>255</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="H266" s="1">
         <v>0</v>
@@ -10946,28 +10133,25 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A267" s="1">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="B267" s="3">
         <v>2</v>
       </c>
-      <c r="C267" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="D267" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E267" s="1">
         <v>0</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H267" s="1">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="I267" s="1">
         <v>0</v>
@@ -10978,28 +10162,25 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A268" s="1">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="B268" s="3">
         <v>2</v>
       </c>
-      <c r="C268" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="D268" s="1" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="E268" s="1">
         <v>0</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="H268" s="1">
-        <v>1513</v>
+        <v>0</v>
       </c>
       <c r="I268" s="1">
         <v>0</v>
@@ -11010,16 +10191,16 @@
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A269" s="1">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="B269" s="3">
         <v>2</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E269" s="1">
         <v>0</v>
@@ -11028,10 +10209,10 @@
         <v>256</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H269" s="1">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="I269" s="1">
         <v>0</v>
@@ -11042,16 +10223,16 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A270" s="1">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="B270" s="3">
         <v>2</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>10</v>
+        <v>251</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="E270" s="1">
         <v>0</v>
@@ -11060,7 +10241,7 @@
         <v>255</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>175</v>
+        <v>252</v>
       </c>
       <c r="H270" s="1">
         <v>0</v>
@@ -11074,7 +10255,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A271" s="1">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="B271" s="3">
         <v>2</v>
@@ -11089,13 +10270,13 @@
         <v>0</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H271" s="1">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="I271" s="1">
         <v>0</v>
@@ -11106,16 +10287,16 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A272" s="1">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="B272" s="3">
         <v>2</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E272" s="1">
         <v>0</v>
@@ -11124,10 +10305,10 @@
         <v>256</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H272" s="1">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="I272" s="1">
         <v>0</v>
@@ -11138,28 +10319,28 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A273" s="1">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="B273" s="3">
         <v>2</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E273" s="1">
         <v>0</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H273" s="1">
-        <v>0</v>
+        <v>1514</v>
       </c>
       <c r="I273" s="1">
         <v>0</v>
@@ -11170,7 +10351,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A274" s="1">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="B274" s="3">
         <v>2</v>
@@ -11185,13 +10366,13 @@
         <v>0</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H274" s="1">
-        <v>1519</v>
+        <v>0</v>
       </c>
       <c r="I274" s="1">
         <v>0</v>
@@ -11202,16 +10383,16 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A275" s="1">
-        <v>2100</v>
+        <v>2031</v>
       </c>
       <c r="B275" s="3">
         <v>2</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>257</v>
+        <v>184</v>
       </c>
       <c r="E275" s="1">
         <v>0</v>
@@ -11220,7 +10401,7 @@
         <v>255</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>253</v>
+        <v>176</v>
       </c>
       <c r="H275" s="1">
         <v>0</v>
@@ -11234,25 +10415,28 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A276" s="1">
-        <v>2101</v>
+        <v>2032</v>
       </c>
       <c r="B276" s="3">
         <v>2</v>
       </c>
+      <c r="C276" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="D276" s="1" t="s">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="E276" s="1">
         <v>0</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H276" s="1">
-        <v>0</v>
+        <v>1517</v>
       </c>
       <c r="I276" s="1">
         <v>0</v>
@@ -11263,13 +10447,16 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A277" s="1">
-        <v>8888</v>
+        <v>2033</v>
       </c>
       <c r="B277" s="3">
         <v>2</v>
       </c>
+      <c r="C277" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="D277" s="1" t="s">
-        <v>183</v>
+        <v>260</v>
       </c>
       <c r="E277" s="1">
         <v>0</v>
@@ -11278,7 +10465,7 @@
         <v>255</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>254</v>
+        <v>178</v>
       </c>
       <c r="H277" s="1">
         <v>0</v>
@@ -11292,25 +10479,28 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A278" s="1">
-        <v>3000</v>
+        <v>2034</v>
       </c>
       <c r="B278" s="3">
         <v>2</v>
       </c>
+      <c r="C278" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D278" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E278" s="1">
         <v>0</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>268</v>
+        <v>179</v>
       </c>
       <c r="H278" s="1">
-        <v>0</v>
+        <v>1519</v>
       </c>
       <c r="I278" s="1">
         <v>0</v>
@@ -11321,22 +10511,25 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A279" s="1">
-        <v>3001</v>
+        <v>2100</v>
       </c>
       <c r="B279" s="3">
         <v>2</v>
       </c>
+      <c r="C279" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="D279" s="1" t="s">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="E279" s="1">
         <v>0</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="H279" s="1">
         <v>0</v>
@@ -11350,7 +10543,7 @@
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A280" s="1">
-        <v>3002</v>
+        <v>2101</v>
       </c>
       <c r="B280" s="3">
         <v>2</v>
@@ -11362,10 +10555,10 @@
         <v>0</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="H280" s="1">
         <v>0</v>
@@ -11379,7 +10572,7 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A281" s="1">
-        <v>3003</v>
+        <v>8888</v>
       </c>
       <c r="B281" s="3">
         <v>2</v>
@@ -11391,10 +10584,10 @@
         <v>0</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="H281" s="1">
         <v>0</v>
@@ -11408,7 +10601,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A282" s="1">
-        <v>3004</v>
+        <v>3000</v>
       </c>
       <c r="B282" s="3">
         <v>2</v>
@@ -11423,7 +10616,7 @@
         <v>181</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
@@ -11437,7 +10630,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A283" s="1">
-        <v>3005</v>
+        <v>3001</v>
       </c>
       <c r="B283" s="3">
         <v>2</v>
@@ -11452,7 +10645,7 @@
         <v>181</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="H283" s="1">
         <v>0</v>
@@ -11466,13 +10659,13 @@
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A284" s="1">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="B284" s="3">
         <v>2</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="E284" s="1">
         <v>0</v>
@@ -11481,7 +10674,7 @@
         <v>181</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H284" s="1">
         <v>0</v>
@@ -11495,22 +10688,22 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A285" s="1">
-        <v>3007</v>
+        <v>3003</v>
       </c>
       <c r="B285" s="3">
         <v>2</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="E285" s="1">
         <v>0</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>275</v>
+        <v>181</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
@@ -11524,13 +10717,13 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A286" s="1">
-        <v>3008</v>
+        <v>3004</v>
       </c>
       <c r="B286" s="3">
         <v>2</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="E286" s="1">
         <v>0</v>
@@ -11539,7 +10732,7 @@
         <v>181</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H286" s="1">
         <v>0</v>
@@ -11553,13 +10746,13 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A287" s="1">
-        <v>3010</v>
+        <v>3005</v>
       </c>
       <c r="B287" s="3">
         <v>2</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="E287" s="1">
         <v>0</v>
@@ -11568,7 +10761,7 @@
         <v>181</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="H287" s="1">
         <v>0</v>
@@ -11582,7 +10775,7 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A288" s="1">
-        <v>3011</v>
+        <v>3006</v>
       </c>
       <c r="B288" s="3">
         <v>2</v>
@@ -11597,7 +10790,7 @@
         <v>181</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="H288" s="1">
         <v>0</v>
@@ -11611,7 +10804,7 @@
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A289" s="1">
-        <v>3012</v>
+        <v>3007</v>
       </c>
       <c r="B289" s="3">
         <v>2</v>
@@ -11623,10 +10816,10 @@
         <v>0</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>181</v>
+        <v>275</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="H289" s="1">
         <v>0</v>
@@ -11640,7 +10833,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A290" s="1">
-        <v>3013</v>
+        <v>3008</v>
       </c>
       <c r="B290" s="3">
         <v>2</v>
@@ -11655,7 +10848,7 @@
         <v>181</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
@@ -11669,7 +10862,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A291" s="1">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="B291" s="3">
         <v>2</v>
@@ -11684,7 +10877,7 @@
         <v>181</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
@@ -11698,7 +10891,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A292" s="1">
-        <v>3200</v>
+        <v>3011</v>
       </c>
       <c r="B292" s="3">
         <v>2</v>
@@ -11713,7 +10906,7 @@
         <v>181</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="H292" s="1">
         <v>0</v>
@@ -11727,7 +10920,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A293" s="1">
-        <v>3201</v>
+        <v>3012</v>
       </c>
       <c r="B293" s="3">
         <v>2</v>
@@ -11742,7 +10935,7 @@
         <v>181</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="H293" s="1">
         <v>0</v>
@@ -11756,10 +10949,10 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A294" s="1">
-        <v>4000</v>
-      </c>
-      <c r="B294" s="3" t="s">
-        <v>480</v>
+        <v>3013</v>
+      </c>
+      <c r="B294" s="3">
+        <v>2</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>274</v>
@@ -11771,7 +10964,7 @@
         <v>181</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="H294" s="1">
         <v>0</v>
@@ -11780,15 +10973,15 @@
         <v>0</v>
       </c>
       <c r="J294" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A295" s="1">
-        <v>4001</v>
-      </c>
-      <c r="B295" s="3" t="s">
-        <v>480</v>
+        <v>3014</v>
+      </c>
+      <c r="B295" s="3">
+        <v>2</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>274</v>
@@ -11800,10 +10993,10 @@
         <v>181</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>354</v>
+        <v>301</v>
       </c>
       <c r="H295" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I295" s="1">
         <v>0</v>
@@ -11814,10 +11007,10 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>4002</v>
-      </c>
-      <c r="B296" s="3" t="s">
-        <v>480</v>
+        <v>3200</v>
+      </c>
+      <c r="B296" s="3">
+        <v>2</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>274</v>
@@ -11829,10 +11022,10 @@
         <v>181</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="H296" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I296" s="1">
         <v>0</v>
@@ -11841,12 +11034,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>4003</v>
-      </c>
-      <c r="B297" s="3" t="s">
-        <v>480</v>
+        <v>3201</v>
+      </c>
+      <c r="B297" s="3">
+        <v>2</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>274</v>
@@ -11858,10 +11051,10 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>355</v>
+        <v>305</v>
       </c>
       <c r="H297" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I297" s="1">
         <v>0</v>
@@ -11872,7 +11065,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>4004</v>
+        <v>4000</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>480</v>
@@ -11887,21 +11080,21 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="H298" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I298" s="1">
         <v>0</v>
       </c>
       <c r="J298" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>4005</v>
+        <v>4001</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>480</v>
@@ -11916,21 +11109,21 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="H299" s="1">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I299" s="1">
         <v>0</v>
       </c>
       <c r="J299" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>4006</v>
+        <v>4002</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>480</v>
@@ -11945,10 +11138,10 @@
         <v>181</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>358</v>
+        <v>45</v>
       </c>
       <c r="H300" s="1">
-        <v>4005</v>
+        <v>4000</v>
       </c>
       <c r="I300" s="1">
         <v>0</v>
@@ -11957,9 +11150,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>4007</v>
+        <v>4003</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>480</v>
@@ -11974,10 +11167,10 @@
         <v>181</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H301" s="1">
-        <v>4005</v>
+        <v>4000</v>
       </c>
       <c r="I301" s="1">
         <v>0</v>
@@ -11988,7 +11181,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>4008</v>
+        <v>4004</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>480</v>
@@ -12003,10 +11196,10 @@
         <v>181</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H302" s="1">
-        <v>4005</v>
+        <v>4000</v>
       </c>
       <c r="I302" s="1">
         <v>0</v>
@@ -12017,7 +11210,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>4009</v>
+        <v>4005</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>480</v>
@@ -12032,21 +11225,21 @@
         <v>181</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="H303" s="1">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="I303" s="1">
         <v>0</v>
       </c>
       <c r="J303" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>4010</v>
+        <v>4006</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>480</v>
@@ -12061,7 +11254,7 @@
         <v>181</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="H304" s="1">
         <v>4005</v>
@@ -12075,7 +11268,7 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>4011</v>
+        <v>4007</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>480</v>
@@ -12090,21 +11283,21 @@
         <v>181</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="H305" s="1">
-        <v>0</v>
+        <v>4005</v>
       </c>
       <c r="I305" s="1">
         <v>0</v>
       </c>
       <c r="J305" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>4012</v>
+        <v>4008</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>480</v>
@@ -12119,10 +11312,10 @@
         <v>181</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>49</v>
+        <v>360</v>
       </c>
       <c r="H306" s="1">
-        <v>4011</v>
+        <v>4005</v>
       </c>
       <c r="I306" s="1">
         <v>0</v>
@@ -12131,9 +11324,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>4013</v>
+        <v>4009</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>480</v>
@@ -12148,10 +11341,10 @@
         <v>181</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="H307" s="1">
-        <v>4011</v>
+        <v>4005</v>
       </c>
       <c r="I307" s="1">
         <v>0</v>
@@ -12162,7 +11355,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>4014</v>
+        <v>4010</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>480</v>
@@ -12177,10 +11370,10 @@
         <v>181</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H308" s="1">
-        <v>4011</v>
+        <v>4005</v>
       </c>
       <c r="I308" s="1">
         <v>0</v>
@@ -12191,7 +11384,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>4015</v>
+        <v>4011</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>480</v>
@@ -12206,21 +11399,21 @@
         <v>181</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H309" s="1">
-        <v>4011</v>
+        <v>0</v>
       </c>
       <c r="I309" s="1">
         <v>0</v>
       </c>
       <c r="J309" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>4016</v>
+        <v>4012</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>480</v>
@@ -12235,21 +11428,21 @@
         <v>181</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>367</v>
+        <v>49</v>
       </c>
       <c r="H310" s="1">
-        <v>0</v>
+        <v>4011</v>
       </c>
       <c r="I310" s="1">
         <v>0</v>
       </c>
       <c r="J310" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>4017</v>
+        <v>4013</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>480</v>
@@ -12264,10 +11457,10 @@
         <v>181</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>56</v>
+        <v>364</v>
       </c>
       <c r="H311" s="1">
-        <v>4016</v>
+        <v>4011</v>
       </c>
       <c r="I311" s="1">
         <v>0</v>
@@ -12278,7 +11471,7 @@
     </row>
     <row r="312" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>4018</v>
+        <v>4014</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>480</v>
@@ -12293,10 +11486,10 @@
         <v>181</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H312" s="1">
-        <v>4016</v>
+        <v>4011</v>
       </c>
       <c r="I312" s="1">
         <v>0</v>
@@ -12307,7 +11500,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>4019</v>
+        <v>4015</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>480</v>
@@ -12322,10 +11515,10 @@
         <v>181</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H313" s="1">
-        <v>4016</v>
+        <v>4011</v>
       </c>
       <c r="I313" s="1">
         <v>0</v>
@@ -12336,7 +11529,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>4020</v>
+        <v>4016</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>480</v>
@@ -12351,21 +11544,21 @@
         <v>181</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H314" s="1">
-        <v>4016</v>
+        <v>0</v>
       </c>
       <c r="I314" s="1">
         <v>0</v>
       </c>
       <c r="J314" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>4021</v>
+        <v>4017</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>480</v>
@@ -12380,21 +11573,21 @@
         <v>181</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>371</v>
+        <v>56</v>
       </c>
       <c r="H315" s="1">
-        <v>0</v>
+        <v>4016</v>
       </c>
       <c r="I315" s="1">
         <v>0</v>
       </c>
       <c r="J315" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>4022</v>
+        <v>4018</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>480</v>
@@ -12409,10 +11602,10 @@
         <v>181</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="H316" s="1">
-        <v>4021</v>
+        <v>4016</v>
       </c>
       <c r="I316" s="1">
         <v>0</v>
@@ -12421,9 +11614,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>4023</v>
+        <v>4019</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>480</v>
@@ -12438,10 +11631,10 @@
         <v>181</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="H317" s="1">
-        <v>4021</v>
+        <v>4016</v>
       </c>
       <c r="I317" s="1">
         <v>0</v>
@@ -12452,7 +11645,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>4024</v>
+        <v>4020</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>480</v>
@@ -12467,21 +11660,21 @@
         <v>181</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="H318" s="1">
+        <v>4016</v>
+      </c>
+      <c r="I318" s="1">
+        <v>0</v>
+      </c>
+      <c r="J318" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A319" s="1">
         <v>4021</v>
-      </c>
-      <c r="I318" s="1">
-        <v>0</v>
-      </c>
-      <c r="J318" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A319" s="1">
-        <v>4025</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>480</v>
@@ -12496,21 +11689,21 @@
         <v>181</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H319" s="1">
-        <v>4021</v>
+        <v>0</v>
       </c>
       <c r="I319" s="1">
         <v>0</v>
       </c>
       <c r="J319" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>4026</v>
+        <v>4022</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>480</v>
@@ -12525,21 +11718,21 @@
         <v>181</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H320" s="1">
-        <v>0</v>
+        <v>4021</v>
       </c>
       <c r="I320" s="1">
         <v>0</v>
       </c>
       <c r="J320" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>4027</v>
+        <v>4023</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>480</v>
@@ -12554,10 +11747,10 @@
         <v>181</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H321" s="1">
-        <v>4026</v>
+        <v>4021</v>
       </c>
       <c r="I321" s="1">
         <v>0</v>
@@ -12568,7 +11761,7 @@
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>4028</v>
+        <v>4024</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>480</v>
@@ -12583,10 +11776,10 @@
         <v>181</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H322" s="1">
-        <v>4026</v>
+        <v>4021</v>
       </c>
       <c r="I322" s="1">
         <v>0</v>
@@ -12595,9 +11788,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>4029</v>
+        <v>4025</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>480</v>
@@ -12612,10 +11805,10 @@
         <v>181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H323" s="1">
-        <v>4026</v>
+        <v>4021</v>
       </c>
       <c r="I323" s="1">
         <v>0</v>
@@ -12626,7 +11819,7 @@
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>4030</v>
+        <v>4026</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>480</v>
@@ -12641,21 +11834,21 @@
         <v>181</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="H324" s="1">
-        <v>4026</v>
+        <v>0</v>
       </c>
       <c r="I324" s="1">
         <v>0</v>
       </c>
       <c r="J324" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>4031</v>
+        <v>4027</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>480</v>
@@ -12670,21 +11863,21 @@
         <v>181</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="H325" s="1">
-        <v>0</v>
+        <v>4026</v>
       </c>
       <c r="I325" s="1">
         <v>0</v>
       </c>
       <c r="J325" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>4032</v>
+        <v>4028</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>480</v>
@@ -12699,10 +11892,10 @@
         <v>181</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="H326" s="1">
-        <v>4031</v>
+        <v>4026</v>
       </c>
       <c r="I326" s="1">
         <v>0</v>
@@ -12711,9 +11904,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>4033</v>
+        <v>4029</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>480</v>
@@ -12728,10 +11921,10 @@
         <v>181</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="H327" s="1">
-        <v>4031</v>
+        <v>4026</v>
       </c>
       <c r="I327" s="1">
         <v>0</v>
@@ -12742,7 +11935,7 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>4034</v>
+        <v>4030</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>480</v>
@@ -12757,21 +11950,21 @@
         <v>181</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H328" s="1">
+        <v>4026</v>
+      </c>
+      <c r="I328" s="1">
+        <v>0</v>
+      </c>
+      <c r="J328" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A329" s="1">
         <v>4031</v>
-      </c>
-      <c r="I328" s="1">
-        <v>0</v>
-      </c>
-      <c r="J328" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A329" s="1">
-        <v>4035</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>480</v>
@@ -12786,21 +11979,21 @@
         <v>181</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="H329" s="1">
-        <v>4031</v>
+        <v>0</v>
       </c>
       <c r="I329" s="1">
         <v>0</v>
       </c>
       <c r="J329" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>4036</v>
+        <v>4032</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>480</v>
@@ -12815,21 +12008,21 @@
         <v>181</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H330" s="1">
-        <v>0</v>
+        <v>4031</v>
       </c>
       <c r="I330" s="1">
         <v>0</v>
       </c>
       <c r="J330" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>4037</v>
+        <v>4033</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>480</v>
@@ -12844,10 +12037,10 @@
         <v>181</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="H331" s="1">
-        <v>4036</v>
+        <v>4031</v>
       </c>
       <c r="I331" s="1">
         <v>0</v>
@@ -12858,7 +12051,7 @@
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>4038</v>
+        <v>4034</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>480</v>
@@ -12873,10 +12066,10 @@
         <v>181</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H332" s="1">
-        <v>4036</v>
+        <v>4031</v>
       </c>
       <c r="I332" s="1">
         <v>0</v>
@@ -12885,9 +12078,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>4039</v>
+        <v>4035</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>480</v>
@@ -12902,10 +12095,10 @@
         <v>181</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H333" s="1">
-        <v>4036</v>
+        <v>4031</v>
       </c>
       <c r="I333" s="1">
         <v>0</v>
@@ -12916,7 +12109,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>4040</v>
+        <v>4036</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>480</v>
@@ -12931,21 +12124,21 @@
         <v>181</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H334" s="1">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="I334" s="1">
         <v>0</v>
       </c>
       <c r="J334" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>4041</v>
+        <v>4037</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>480</v>
@@ -12960,21 +12153,21 @@
         <v>181</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H335" s="1">
-        <v>0</v>
+        <v>4036</v>
       </c>
       <c r="I335" s="1">
         <v>0</v>
       </c>
       <c r="J335" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>4042</v>
+        <v>4038</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>480</v>
@@ -12989,10 +12182,10 @@
         <v>181</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="H336" s="1">
-        <v>4041</v>
+        <v>4036</v>
       </c>
       <c r="I336" s="1">
         <v>0</v>
@@ -13001,9 +12194,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>4043</v>
+        <v>4039</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>480</v>
@@ -13018,10 +12211,10 @@
         <v>181</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="H337" s="1">
-        <v>4041</v>
+        <v>4036</v>
       </c>
       <c r="I337" s="1">
         <v>0</v>
@@ -13032,7 +12225,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>4044</v>
+        <v>4040</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>480</v>
@@ -13047,10 +12240,10 @@
         <v>181</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>219</v>
+        <v>390</v>
       </c>
       <c r="H338" s="1">
-        <v>4041</v>
+        <v>4036</v>
       </c>
       <c r="I338" s="1">
         <v>0</v>
@@ -13061,7 +12254,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>4045</v>
+        <v>4041</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>480</v>
@@ -13076,21 +12269,21 @@
         <v>181</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H339" s="1">
-        <v>4041</v>
+        <v>0</v>
       </c>
       <c r="I339" s="1">
         <v>0</v>
       </c>
       <c r="J339" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>4046</v>
+        <v>4042</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>480</v>
@@ -13105,21 +12298,21 @@
         <v>181</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H340" s="1">
-        <v>0</v>
+        <v>4041</v>
       </c>
       <c r="I340" s="1">
         <v>0</v>
       </c>
       <c r="J340" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>4047</v>
+        <v>4043</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>480</v>
@@ -13134,10 +12327,10 @@
         <v>181</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="H341" s="1">
-        <v>4046</v>
+        <v>4041</v>
       </c>
       <c r="I341" s="1">
         <v>0</v>
@@ -13146,9 +12339,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>4048</v>
+        <v>4044</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>480</v>
@@ -13163,10 +12356,10 @@
         <v>181</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>61</v>
+        <v>219</v>
       </c>
       <c r="H342" s="1">
-        <v>4046</v>
+        <v>4041</v>
       </c>
       <c r="I342" s="1">
         <v>0</v>
@@ -13177,7 +12370,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>4049</v>
+        <v>4045</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>480</v>
@@ -13192,10 +12385,10 @@
         <v>181</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>62</v>
+        <v>393</v>
       </c>
       <c r="H343" s="1">
-        <v>4046</v>
+        <v>4041</v>
       </c>
       <c r="I343" s="1">
         <v>0</v>
@@ -13206,7 +12399,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>4050</v>
+        <v>4046</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>480</v>
@@ -13221,21 +12414,21 @@
         <v>181</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H344" s="1">
-        <v>4046</v>
+        <v>0</v>
       </c>
       <c r="I344" s="1">
         <v>0</v>
       </c>
       <c r="J344" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>4051</v>
+        <v>4047</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>480</v>
@@ -13250,21 +12443,21 @@
         <v>181</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H345" s="1">
-        <v>0</v>
+        <v>4046</v>
       </c>
       <c r="I345" s="1">
         <v>0</v>
       </c>
       <c r="J345" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>4052</v>
+        <v>4048</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>480</v>
@@ -13279,10 +12472,10 @@
         <v>181</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>398</v>
+        <v>61</v>
       </c>
       <c r="H346" s="1">
-        <v>4051</v>
+        <v>4046</v>
       </c>
       <c r="I346" s="1">
         <v>0</v>
@@ -13293,7 +12486,7 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>4053</v>
+        <v>4049</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>480</v>
@@ -13308,10 +12501,10 @@
         <v>181</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>399</v>
+        <v>62</v>
       </c>
       <c r="H347" s="1">
-        <v>4051</v>
+        <v>4046</v>
       </c>
       <c r="I347" s="1">
         <v>0</v>
@@ -13322,7 +12515,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>4054</v>
+        <v>4050</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>480</v>
@@ -13337,10 +12530,10 @@
         <v>181</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H348" s="1">
-        <v>4051</v>
+        <v>4046</v>
       </c>
       <c r="I348" s="1">
         <v>0</v>
@@ -13351,7 +12544,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>4055</v>
+        <v>4051</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>480</v>
@@ -13366,21 +12559,21 @@
         <v>181</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="H349" s="1">
-        <v>4051</v>
+        <v>0</v>
       </c>
       <c r="I349" s="1">
         <v>0</v>
       </c>
       <c r="J349" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>4056</v>
+        <v>4052</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>480</v>
@@ -13395,21 +12588,21 @@
         <v>181</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="H350" s="1">
-        <v>0</v>
+        <v>4051</v>
       </c>
       <c r="I350" s="1">
         <v>0</v>
       </c>
       <c r="J350" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>4057</v>
+        <v>4053</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>480</v>
@@ -13424,10 +12617,10 @@
         <v>181</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H351" s="1">
-        <v>4056</v>
+        <v>4051</v>
       </c>
       <c r="I351" s="1">
         <v>0</v>
@@ -13438,7 +12631,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>4058</v>
+        <v>4054</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>480</v>
@@ -13453,10 +12646,10 @@
         <v>181</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="H352" s="1">
-        <v>4056</v>
+        <v>4051</v>
       </c>
       <c r="I352" s="1">
         <v>0</v>
@@ -13467,7 +12660,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>4059</v>
+        <v>4055</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>480</v>
@@ -13482,10 +12675,10 @@
         <v>181</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="H353" s="1">
-        <v>4056</v>
+        <v>4051</v>
       </c>
       <c r="I353" s="1">
         <v>0</v>
@@ -13496,7 +12689,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>4060</v>
+        <v>4056</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>480</v>
@@ -13511,21 +12704,21 @@
         <v>181</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="H354" s="1">
-        <v>4056</v>
+        <v>0</v>
       </c>
       <c r="I354" s="1">
         <v>0</v>
       </c>
       <c r="J354" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>4061</v>
+        <v>4057</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>480</v>
@@ -13540,21 +12733,21 @@
         <v>181</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="H355" s="1">
-        <v>0</v>
+        <v>4056</v>
       </c>
       <c r="I355" s="1">
         <v>0</v>
       </c>
       <c r="J355" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>4062</v>
+        <v>4058</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>480</v>
@@ -13569,10 +12762,10 @@
         <v>181</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="H356" s="1">
-        <v>4061</v>
+        <v>4056</v>
       </c>
       <c r="I356" s="1">
         <v>0</v>
@@ -13581,9 +12774,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>4063</v>
+        <v>4059</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>480</v>
@@ -13598,10 +12791,10 @@
         <v>181</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>51</v>
+        <v>405</v>
       </c>
       <c r="H357" s="1">
-        <v>4061</v>
+        <v>4056</v>
       </c>
       <c r="I357" s="1">
         <v>0</v>
@@ -13612,7 +12805,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>4064</v>
+        <v>4060</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>480</v>
@@ -13627,10 +12820,10 @@
         <v>181</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>58</v>
+        <v>406</v>
       </c>
       <c r="H358" s="1">
-        <v>4061</v>
+        <v>4056</v>
       </c>
       <c r="I358" s="1">
         <v>0</v>
@@ -13641,7 +12834,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>4065</v>
+        <v>4061</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>480</v>
@@ -13656,21 +12849,21 @@
         <v>181</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H359" s="1">
-        <v>4061</v>
+        <v>0</v>
       </c>
       <c r="I359" s="1">
         <v>0</v>
       </c>
       <c r="J359" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>4066</v>
+        <v>4062</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>480</v>
@@ -13685,21 +12878,21 @@
         <v>181</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H360" s="1">
-        <v>0</v>
+        <v>4061</v>
       </c>
       <c r="I360" s="1">
         <v>0</v>
       </c>
       <c r="J360" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>4067</v>
+        <v>4063</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>480</v>
@@ -13714,10 +12907,10 @@
         <v>181</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="H361" s="1">
-        <v>4066</v>
+        <v>4061</v>
       </c>
       <c r="I361" s="1">
         <v>0</v>
@@ -13728,7 +12921,7 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>4068</v>
+        <v>4064</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>480</v>
@@ -13743,10 +12936,10 @@
         <v>181</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>411</v>
+        <v>58</v>
       </c>
       <c r="H362" s="1">
-        <v>4066</v>
+        <v>4061</v>
       </c>
       <c r="I362" s="1">
         <v>0</v>
@@ -13755,9 +12948,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>4069</v>
+        <v>4065</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>480</v>
@@ -13772,21 +12965,21 @@
         <v>181</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>65</v>
+        <v>409</v>
       </c>
       <c r="H363" s="1">
+        <v>4061</v>
+      </c>
+      <c r="I363" s="1">
+        <v>0</v>
+      </c>
+      <c r="J363" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A364" s="1">
         <v>4066</v>
-      </c>
-      <c r="I363" s="1">
-        <v>0</v>
-      </c>
-      <c r="J363" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A364" s="1">
-        <v>4070</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>480</v>
@@ -13801,21 +12994,21 @@
         <v>181</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H364" s="1">
-        <v>4066</v>
+        <v>0</v>
       </c>
       <c r="I364" s="1">
         <v>0</v>
       </c>
       <c r="J364" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>4071</v>
+        <v>4067</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>480</v>
@@ -13830,21 +13023,21 @@
         <v>181</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>413</v>
+        <v>81</v>
       </c>
       <c r="H365" s="1">
-        <v>0</v>
+        <v>4066</v>
       </c>
       <c r="I365" s="1">
         <v>0</v>
       </c>
       <c r="J365" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>4072</v>
+        <v>4068</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>480</v>
@@ -13859,10 +13052,10 @@
         <v>181</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>68</v>
+        <v>411</v>
       </c>
       <c r="H366" s="1">
-        <v>4071</v>
+        <v>4066</v>
       </c>
       <c r="I366" s="1">
         <v>0</v>
@@ -13871,9 +13064,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>4073</v>
+        <v>4069</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>480</v>
@@ -13888,10 +13081,10 @@
         <v>181</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="H367" s="1">
-        <v>4071</v>
+        <v>4066</v>
       </c>
       <c r="I367" s="1">
         <v>0</v>
@@ -13902,7 +13095,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>4074</v>
+        <v>4070</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>480</v>
@@ -13917,10 +13110,10 @@
         <v>181</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H368" s="1">
-        <v>4071</v>
+        <v>4066</v>
       </c>
       <c r="I368" s="1">
         <v>0</v>
@@ -13931,7 +13124,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>4075</v>
+        <v>4071</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>480</v>
@@ -13946,21 +13139,21 @@
         <v>181</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H369" s="1">
-        <v>4071</v>
+        <v>0</v>
       </c>
       <c r="I369" s="1">
         <v>0</v>
       </c>
       <c r="J369" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>4076</v>
+        <v>4072</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>480</v>
@@ -13975,21 +13168,21 @@
         <v>181</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>416</v>
+        <v>68</v>
       </c>
       <c r="H370" s="1">
-        <v>0</v>
+        <v>4071</v>
       </c>
       <c r="I370" s="1">
         <v>0</v>
       </c>
       <c r="J370" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>4077</v>
+        <v>4073</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>480</v>
@@ -14004,10 +13197,10 @@
         <v>181</v>
       </c>
       <c r="G371" s="1" t="s">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="H371" s="1">
-        <v>4076</v>
+        <v>4071</v>
       </c>
       <c r="I371" s="1">
         <v>0</v>
@@ -14018,7 +13211,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>4078</v>
+        <v>4074</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>480</v>
@@ -14033,10 +13226,10 @@
         <v>181</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H372" s="1">
-        <v>4076</v>
+        <v>4071</v>
       </c>
       <c r="I372" s="1">
         <v>0</v>
@@ -14047,7 +13240,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>4079</v>
+        <v>4075</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>480</v>
@@ -14062,10 +13255,10 @@
         <v>181</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="H373" s="1">
-        <v>4076</v>
+        <v>4071</v>
       </c>
       <c r="I373" s="1">
         <v>0</v>
@@ -14076,7 +13269,7 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>4080</v>
+        <v>4076</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>480</v>
@@ -14091,21 +13284,21 @@
         <v>181</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H374" s="1">
-        <v>4076</v>
+        <v>0</v>
       </c>
       <c r="I374" s="1">
         <v>0</v>
       </c>
       <c r="J374" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>4081</v>
+        <v>4077</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>480</v>
@@ -14120,21 +13313,21 @@
         <v>181</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="H375" s="1">
-        <v>0</v>
+        <v>4076</v>
       </c>
       <c r="I375" s="1">
         <v>0</v>
       </c>
       <c r="J375" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="376" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>4082</v>
+        <v>4078</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>480</v>
@@ -14149,10 +13342,10 @@
         <v>181</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>80</v>
+        <v>418</v>
       </c>
       <c r="H376" s="1">
-        <v>4081</v>
+        <v>4076</v>
       </c>
       <c r="I376" s="1">
         <v>0</v>
@@ -14161,9 +13354,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>4083</v>
+        <v>4079</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>480</v>
@@ -14178,10 +13371,10 @@
         <v>181</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>59</v>
+        <v>419</v>
       </c>
       <c r="H377" s="1">
-        <v>4081</v>
+        <v>4076</v>
       </c>
       <c r="I377" s="1">
         <v>0</v>
@@ -14190,9 +13383,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>4084</v>
+        <v>4080</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>480</v>
@@ -14207,10 +13400,10 @@
         <v>181</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>329</v>
+        <v>420</v>
       </c>
       <c r="H378" s="1">
-        <v>4081</v>
+        <v>4076</v>
       </c>
       <c r="I378" s="1">
         <v>0</v>
@@ -14221,7 +13414,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>4085</v>
+        <v>4081</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>480</v>
@@ -14236,21 +13429,21 @@
         <v>181</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H379" s="1">
-        <v>4081</v>
+        <v>0</v>
       </c>
       <c r="I379" s="1">
         <v>0</v>
       </c>
       <c r="J379" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>4086</v>
+        <v>4082</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>480</v>
@@ -14265,21 +13458,21 @@
         <v>181</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="H380" s="1">
-        <v>0</v>
+        <v>4081</v>
       </c>
       <c r="I380" s="1">
         <v>0</v>
       </c>
       <c r="J380" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>4087</v>
+        <v>4083</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>480</v>
@@ -14294,10 +13487,10 @@
         <v>181</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>424</v>
+        <v>59</v>
       </c>
       <c r="H381" s="1">
-        <v>4086</v>
+        <v>4081</v>
       </c>
       <c r="I381" s="1">
         <v>0</v>
@@ -14306,9 +13499,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>4088</v>
+        <v>4084</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>480</v>
@@ -14323,10 +13516,10 @@
         <v>181</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>425</v>
+        <v>329</v>
       </c>
       <c r="H382" s="1">
-        <v>4086</v>
+        <v>4081</v>
       </c>
       <c r="I382" s="1">
         <v>0</v>
@@ -14337,7 +13530,7 @@
     </row>
     <row r="383" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>4089</v>
+        <v>4085</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>480</v>
@@ -14352,10 +13545,10 @@
         <v>181</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="H383" s="1">
-        <v>4086</v>
+        <v>4081</v>
       </c>
       <c r="I383" s="1">
         <v>0</v>
@@ -14366,7 +13559,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>4090</v>
+        <v>4086</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>480</v>
@@ -14381,21 +13574,21 @@
         <v>181</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H384" s="1">
-        <v>4086</v>
+        <v>0</v>
       </c>
       <c r="I384" s="1">
         <v>0</v>
       </c>
       <c r="J384" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>4091</v>
+        <v>4087</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>480</v>
@@ -14410,21 +13603,21 @@
         <v>181</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H385" s="1">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="I385" s="1">
         <v>0</v>
       </c>
       <c r="J385" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="386" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>4092</v>
+        <v>4088</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>480</v>
@@ -14439,10 +13632,10 @@
         <v>181</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="H386" s="1">
-        <v>4091</v>
+        <v>4086</v>
       </c>
       <c r="I386" s="1">
         <v>0</v>
@@ -14453,7 +13646,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>4093</v>
+        <v>4089</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>480</v>
@@ -14468,10 +13661,10 @@
         <v>181</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="H387" s="1">
-        <v>4091</v>
+        <v>4086</v>
       </c>
       <c r="I387" s="1">
         <v>0</v>
@@ -14482,7 +13675,7 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>4094</v>
+        <v>4090</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>480</v>
@@ -14497,10 +13690,10 @@
         <v>181</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="H388" s="1">
-        <v>4091</v>
+        <v>4086</v>
       </c>
       <c r="I388" s="1">
         <v>0</v>
@@ -14511,7 +13704,7 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>4095</v>
+        <v>4091</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>480</v>
@@ -14526,21 +13719,21 @@
         <v>181</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="H389" s="1">
-        <v>4091</v>
+        <v>0</v>
       </c>
       <c r="I389" s="1">
         <v>0</v>
       </c>
       <c r="J389" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>4096</v>
+        <v>4092</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>480</v>
@@ -14555,21 +13748,21 @@
         <v>181</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H390" s="1">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="I390" s="1">
         <v>0</v>
       </c>
       <c r="J390" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>4097</v>
+        <v>4093</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>480</v>
@@ -14584,10 +13777,10 @@
         <v>181</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="H391" s="1">
-        <v>4096</v>
+        <v>4091</v>
       </c>
       <c r="I391" s="1">
         <v>0</v>
@@ -14598,7 +13791,7 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>4098</v>
+        <v>4094</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>480</v>
@@ -14613,10 +13806,10 @@
         <v>181</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="H392" s="1">
-        <v>4096</v>
+        <v>4091</v>
       </c>
       <c r="I392" s="1">
         <v>0</v>
@@ -14627,7 +13820,7 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>4099</v>
+        <v>4095</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>480</v>
@@ -14642,10 +13835,10 @@
         <v>181</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H393" s="1">
-        <v>4096</v>
+        <v>4091</v>
       </c>
       <c r="I393" s="1">
         <v>0</v>
@@ -14656,7 +13849,7 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>4100</v>
+        <v>4096</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>480</v>
@@ -14671,21 +13864,21 @@
         <v>181</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="H394" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="I394" s="1">
         <v>0</v>
       </c>
       <c r="J394" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>4101</v>
+        <v>4097</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>480</v>
@@ -14700,21 +13893,21 @@
         <v>181</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="H395" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="I395" s="1">
         <v>0</v>
       </c>
       <c r="J395" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>4102</v>
+        <v>4098</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>480</v>
@@ -14729,10 +13922,10 @@
         <v>181</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>83</v>
+        <v>435</v>
       </c>
       <c r="H396" s="1">
-        <v>4101</v>
+        <v>4096</v>
       </c>
       <c r="I396" s="1">
         <v>0</v>
@@ -14743,7 +13936,7 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>4103</v>
+        <v>4099</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>480</v>
@@ -14758,10 +13951,10 @@
         <v>181</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>74</v>
+        <v>436</v>
       </c>
       <c r="H397" s="1">
-        <v>4101</v>
+        <v>4096</v>
       </c>
       <c r="I397" s="1">
         <v>0</v>
@@ -14770,9 +13963,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>4104</v>
+        <v>4100</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>480</v>
@@ -14787,21 +13980,21 @@
         <v>181</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>218</v>
+        <v>437</v>
       </c>
       <c r="H398" s="1">
+        <v>4096</v>
+      </c>
+      <c r="I398" s="1">
+        <v>0</v>
+      </c>
+      <c r="J398" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A399" s="1">
         <v>4101</v>
-      </c>
-      <c r="I398" s="1">
-        <v>0</v>
-      </c>
-      <c r="J398" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A399" s="1">
-        <v>4105</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>480</v>
@@ -14816,21 +14009,21 @@
         <v>181</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H399" s="1">
-        <v>4101</v>
+        <v>0</v>
       </c>
       <c r="I399" s="1">
         <v>0</v>
       </c>
       <c r="J399" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>4106</v>
+        <v>4102</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>480</v>
@@ -14845,21 +14038,21 @@
         <v>181</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>440</v>
+        <v>83</v>
       </c>
       <c r="H400" s="1">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="I400" s="1">
         <v>0</v>
       </c>
       <c r="J400" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>4107</v>
+        <v>4103</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>480</v>
@@ -14874,10 +14067,10 @@
         <v>181</v>
       </c>
       <c r="G401" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H401" s="1">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="I401" s="1">
         <v>0</v>
@@ -14888,7 +14081,7 @@
     </row>
     <row r="402" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>4108</v>
+        <v>4104</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>480</v>
@@ -14903,10 +14096,10 @@
         <v>181</v>
       </c>
       <c r="G402" s="1" t="s">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="H402" s="1">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="I402" s="1">
         <v>0</v>
@@ -14917,7 +14110,7 @@
     </row>
     <row r="403" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
-        <v>4109</v>
+        <v>4105</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>480</v>
@@ -14932,10 +14125,10 @@
         <v>181</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>67</v>
+        <v>439</v>
       </c>
       <c r="H403" s="1">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="I403" s="1">
         <v>0</v>
@@ -14946,7 +14139,7 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
-        <v>4110</v>
+        <v>4106</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>480</v>
@@ -14961,21 +14154,21 @@
         <v>181</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H404" s="1">
-        <v>4106</v>
+        <v>0</v>
       </c>
       <c r="I404" s="1">
         <v>0</v>
       </c>
       <c r="J404" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
-        <v>4111</v>
+        <v>4107</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>480</v>
@@ -14990,21 +14183,21 @@
         <v>181</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>442</v>
+        <v>75</v>
       </c>
       <c r="H405" s="1">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="I405" s="1">
         <v>0</v>
       </c>
       <c r="J405" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
-        <v>4112</v>
+        <v>4108</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>480</v>
@@ -15019,10 +14212,10 @@
         <v>181</v>
       </c>
       <c r="G406" s="1" t="s">
-        <v>443</v>
+        <v>57</v>
       </c>
       <c r="H406" s="1">
-        <v>4111</v>
+        <v>4106</v>
       </c>
       <c r="I406" s="1">
         <v>0</v>
@@ -15031,9 +14224,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
-        <v>4113</v>
+        <v>4109</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>480</v>
@@ -15048,10 +14241,10 @@
         <v>181</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>444</v>
+        <v>67</v>
       </c>
       <c r="H407" s="1">
-        <v>4111</v>
+        <v>4106</v>
       </c>
       <c r="I407" s="1">
         <v>0</v>
@@ -15062,7 +14255,7 @@
     </row>
     <row r="408" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
-        <v>4114</v>
+        <v>4110</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>480</v>
@@ -15076,11 +14269,11 @@
       <c r="F408" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G408" s="2" t="s">
-        <v>445</v>
+      <c r="G408" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="H408" s="1">
-        <v>4111</v>
+        <v>4106</v>
       </c>
       <c r="I408" s="1">
         <v>0</v>
@@ -15091,7 +14284,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
-        <v>4115</v>
+        <v>4111</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>480</v>
@@ -15106,21 +14299,21 @@
         <v>181</v>
       </c>
       <c r="G409" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="H409" s="1">
-        <v>4111</v>
+        <v>0</v>
       </c>
       <c r="I409" s="1">
         <v>0</v>
       </c>
       <c r="J409" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
-        <v>4116</v>
+        <v>4112</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>480</v>
@@ -15135,21 +14328,21 @@
         <v>181</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H410" s="1">
-        <v>0</v>
+        <v>4111</v>
       </c>
       <c r="I410" s="1">
         <v>0</v>
       </c>
       <c r="J410" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="411" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
-        <v>4117</v>
+        <v>4113</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>480</v>
@@ -15164,10 +14357,10 @@
         <v>181</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>70</v>
+        <v>444</v>
       </c>
       <c r="H411" s="1">
-        <v>4116</v>
+        <v>4111</v>
       </c>
       <c r="I411" s="1">
         <v>0</v>
@@ -15178,7 +14371,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
-        <v>4118</v>
+        <v>4114</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>480</v>
@@ -15192,11 +14385,11 @@
       <c r="F412" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G412" s="1" t="s">
-        <v>54</v>
+      <c r="G412" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="H412" s="1">
-        <v>4116</v>
+        <v>4111</v>
       </c>
       <c r="I412" s="1">
         <v>0</v>
@@ -15205,9 +14398,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
-        <v>4119</v>
+        <v>4115</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>480</v>
@@ -15222,21 +14415,21 @@
         <v>181</v>
       </c>
       <c r="G413" s="1" t="s">
-        <v>63</v>
+        <v>446</v>
       </c>
       <c r="H413" s="1">
+        <v>4111</v>
+      </c>
+      <c r="I413" s="1">
+        <v>0</v>
+      </c>
+      <c r="J413" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A414" s="1">
         <v>4116</v>
-      </c>
-      <c r="I413" s="1">
-        <v>0</v>
-      </c>
-      <c r="J413" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="414" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A414" s="1">
-        <v>4120</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>480</v>
@@ -15251,21 +14444,21 @@
         <v>181</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H414" s="1">
-        <v>4116</v>
+        <v>0</v>
       </c>
       <c r="I414" s="1">
         <v>0</v>
       </c>
       <c r="J414" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
-        <v>4121</v>
+        <v>4117</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>480</v>
@@ -15280,21 +14473,21 @@
         <v>181</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>449</v>
+        <v>70</v>
       </c>
       <c r="H415" s="1">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="I415" s="1">
         <v>0</v>
       </c>
       <c r="J415" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
-        <v>4122</v>
+        <v>4118</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>480</v>
@@ -15309,10 +14502,10 @@
         <v>181</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>450</v>
+        <v>54</v>
       </c>
       <c r="H416" s="1">
-        <v>4121</v>
+        <v>4116</v>
       </c>
       <c r="I416" s="1">
         <v>0</v>
@@ -15321,9 +14514,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
-        <v>4123</v>
+        <v>4119</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>480</v>
@@ -15338,10 +14531,10 @@
         <v>181</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>451</v>
+        <v>63</v>
       </c>
       <c r="H417" s="1">
-        <v>4121</v>
+        <v>4116</v>
       </c>
       <c r="I417" s="1">
         <v>0</v>
@@ -15350,9 +14543,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
-        <v>4124</v>
+        <v>4120</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>480</v>
@@ -15367,10 +14560,10 @@
         <v>181</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="H418" s="1">
-        <v>4121</v>
+        <v>4116</v>
       </c>
       <c r="I418" s="1">
         <v>0</v>
@@ -15381,7 +14574,7 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
-        <v>4125</v>
+        <v>4121</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>480</v>
@@ -15396,21 +14589,21 @@
         <v>181</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H419" s="1">
-        <v>4121</v>
+        <v>0</v>
       </c>
       <c r="I419" s="1">
         <v>0</v>
       </c>
       <c r="J419" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
-        <v>4126</v>
+        <v>4122</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>480</v>
@@ -15425,21 +14618,21 @@
         <v>181</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="H420" s="1">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="I420" s="1">
         <v>0</v>
       </c>
       <c r="J420" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
-        <v>4127</v>
+        <v>4123</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>480</v>
@@ -15454,10 +14647,10 @@
         <v>181</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>71</v>
+        <v>451</v>
       </c>
       <c r="H421" s="1">
-        <v>4126</v>
+        <v>4121</v>
       </c>
       <c r="I421" s="1">
         <v>0</v>
@@ -15468,7 +14661,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
-        <v>4128</v>
+        <v>4124</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>480</v>
@@ -15483,10 +14676,10 @@
         <v>181</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>77</v>
+        <v>452</v>
       </c>
       <c r="H422" s="1">
-        <v>4126</v>
+        <v>4121</v>
       </c>
       <c r="I422" s="1">
         <v>0</v>
@@ -15495,9 +14688,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
-        <v>4129</v>
+        <v>4125</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>480</v>
@@ -15512,10 +14705,10 @@
         <v>181</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="H423" s="1">
-        <v>4126</v>
+        <v>4121</v>
       </c>
       <c r="I423" s="1">
         <v>0</v>
@@ -15526,7 +14719,7 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
-        <v>4130</v>
+        <v>4126</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>480</v>
@@ -15541,21 +14734,21 @@
         <v>181</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>55</v>
+        <v>454</v>
       </c>
       <c r="H424" s="1">
-        <v>4126</v>
+        <v>0</v>
       </c>
       <c r="I424" s="1">
         <v>0</v>
       </c>
       <c r="J424" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="425" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
-        <v>4131</v>
+        <v>4127</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>480</v>
@@ -15570,7 +14763,7 @@
         <v>181</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>455</v>
+        <v>71</v>
       </c>
       <c r="H425" s="1">
         <v>4126</v>
@@ -15584,7 +14777,7 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
-        <v>4132</v>
+        <v>4128</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>480</v>
@@ -15599,21 +14792,21 @@
         <v>181</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>456</v>
+        <v>77</v>
       </c>
       <c r="H426" s="1">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="I426" s="1">
         <v>0</v>
       </c>
       <c r="J426" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="427" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
-        <v>4133</v>
+        <v>4129</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>480</v>
@@ -15628,10 +14821,10 @@
         <v>181</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H427" s="1">
-        <v>4132</v>
+        <v>4126</v>
       </c>
       <c r="I427" s="1">
         <v>0</v>
@@ -15640,9 +14833,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
-        <v>4134</v>
+        <v>4130</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>480</v>
@@ -15657,10 +14850,10 @@
         <v>181</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>457</v>
+        <v>55</v>
       </c>
       <c r="H428" s="1">
-        <v>4132</v>
+        <v>4126</v>
       </c>
       <c r="I428" s="1">
         <v>0</v>
@@ -15669,9 +14862,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
-        <v>4135</v>
+        <v>4131</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>480</v>
@@ -15686,21 +14879,21 @@
         <v>181</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>66</v>
+        <v>455</v>
       </c>
       <c r="H429" s="1">
+        <v>4126</v>
+      </c>
+      <c r="I429" s="1">
+        <v>0</v>
+      </c>
+      <c r="J429" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A430" s="1">
         <v>4132</v>
-      </c>
-      <c r="I429" s="1">
-        <v>0</v>
-      </c>
-      <c r="J429" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="430" spans="1:10" ht="27" x14ac:dyDescent="0.15">
-      <c r="A430" s="1">
-        <v>4136</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>480</v>
@@ -15715,21 +14908,21 @@
         <v>181</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H430" s="1">
-        <v>4132</v>
+        <v>0</v>
       </c>
       <c r="I430" s="1">
         <v>0</v>
       </c>
       <c r="J430" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
-        <v>4137</v>
+        <v>4133</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>480</v>
@@ -15744,21 +14937,21 @@
         <v>181</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="H431" s="1">
-        <v>0</v>
+        <v>4132</v>
       </c>
       <c r="I431" s="1">
         <v>0</v>
       </c>
       <c r="J431" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
-        <v>4138</v>
+        <v>4134</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>480</v>
@@ -15773,10 +14966,10 @@
         <v>181</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="H432" s="1">
-        <v>4137</v>
+        <v>4132</v>
       </c>
       <c r="I432" s="1">
         <v>0</v>
@@ -15785,9 +14978,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
-        <v>4139</v>
+        <v>4135</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>480</v>
@@ -15802,10 +14995,10 @@
         <v>181</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>461</v>
+        <v>66</v>
       </c>
       <c r="H433" s="1">
-        <v>4137</v>
+        <v>4132</v>
       </c>
       <c r="I433" s="1">
         <v>0</v>
@@ -15814,9 +15007,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
-        <v>4140</v>
+        <v>4136</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>480</v>
@@ -15831,10 +15024,10 @@
         <v>181</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="H434" s="1">
-        <v>4137</v>
+        <v>4132</v>
       </c>
       <c r="I434" s="1">
         <v>0</v>
@@ -15845,7 +15038,7 @@
     </row>
     <row r="435" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
-        <v>4141</v>
+        <v>4137</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>480</v>
@@ -15860,21 +15053,21 @@
         <v>181</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H435" s="1">
-        <v>4137</v>
+        <v>0</v>
       </c>
       <c r="I435" s="1">
         <v>0</v>
       </c>
       <c r="J435" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
-        <v>4142</v>
+        <v>4138</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>480</v>
@@ -15889,21 +15082,21 @@
         <v>181</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="H436" s="1">
-        <v>0</v>
+        <v>4137</v>
       </c>
       <c r="I436" s="1">
         <v>0</v>
       </c>
       <c r="J436" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
-        <v>4143</v>
+        <v>4139</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>480</v>
@@ -15918,10 +15111,10 @@
         <v>181</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H437" s="1">
-        <v>4142</v>
+        <v>4137</v>
       </c>
       <c r="I437" s="1">
         <v>0</v>
@@ -15930,9 +15123,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
-        <v>4144</v>
+        <v>4140</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>480</v>
@@ -15947,10 +15140,10 @@
         <v>181</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>48</v>
+        <v>462</v>
       </c>
       <c r="H438" s="1">
-        <v>4142</v>
+        <v>4137</v>
       </c>
       <c r="I438" s="1">
         <v>0</v>
@@ -15961,7 +15154,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
-        <v>4145</v>
+        <v>4141</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>480</v>
@@ -15976,10 +15169,10 @@
         <v>181</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>60</v>
+        <v>463</v>
       </c>
       <c r="H439" s="1">
-        <v>4142</v>
+        <v>4137</v>
       </c>
       <c r="I439" s="1">
         <v>0</v>
@@ -15990,7 +15183,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
-        <v>4146</v>
+        <v>4142</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>480</v>
@@ -16005,21 +15198,21 @@
         <v>181</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H440" s="1">
-        <v>4142</v>
+        <v>0</v>
       </c>
       <c r="I440" s="1">
         <v>0</v>
       </c>
       <c r="J440" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
-        <v>4147</v>
+        <v>4143</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>480</v>
@@ -16034,21 +15227,21 @@
         <v>181</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H441" s="1">
-        <v>0</v>
+        <v>4142</v>
       </c>
       <c r="I441" s="1">
         <v>0</v>
       </c>
       <c r="J441" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
-        <v>4148</v>
+        <v>4144</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>480</v>
@@ -16063,10 +15256,10 @@
         <v>181</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="H442" s="1">
-        <v>4147</v>
+        <v>4142</v>
       </c>
       <c r="I442" s="1">
         <v>0</v>
@@ -16077,7 +15270,7 @@
     </row>
     <row r="443" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
-        <v>4149</v>
+        <v>4145</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>480</v>
@@ -16092,10 +15285,10 @@
         <v>181</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>468</v>
+        <v>60</v>
       </c>
       <c r="H443" s="1">
-        <v>4147</v>
+        <v>4142</v>
       </c>
       <c r="I443" s="1">
         <v>0</v>
@@ -16106,7 +15299,7 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
-        <v>4150</v>
+        <v>4146</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>480</v>
@@ -16121,10 +15314,10 @@
         <v>181</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H444" s="1">
-        <v>4147</v>
+        <v>4142</v>
       </c>
       <c r="I444" s="1">
         <v>0</v>
@@ -16135,7 +15328,7 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
-        <v>4151</v>
+        <v>4147</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>480</v>
@@ -16150,21 +15343,21 @@
         <v>181</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H445" s="1">
-        <v>4147</v>
+        <v>0</v>
       </c>
       <c r="I445" s="1">
         <v>0</v>
       </c>
       <c r="J445" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
-        <v>4152</v>
+        <v>4148</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>480</v>
@@ -16179,21 +15372,21 @@
         <v>181</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>471</v>
+        <v>79</v>
       </c>
       <c r="H446" s="1">
-        <v>0</v>
+        <v>4147</v>
       </c>
       <c r="I446" s="1">
         <v>0</v>
       </c>
       <c r="J446" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
-        <v>4153</v>
+        <v>4149</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>480</v>
@@ -16208,10 +15401,10 @@
         <v>181</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="H447" s="1">
-        <v>4152</v>
+        <v>4147</v>
       </c>
       <c r="I447" s="1">
         <v>0</v>
@@ -16222,7 +15415,7 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
-        <v>4154</v>
+        <v>4150</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>480</v>
@@ -16237,10 +15430,10 @@
         <v>181</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="H448" s="1">
-        <v>4152</v>
+        <v>4147</v>
       </c>
       <c r="I448" s="1">
         <v>0</v>
@@ -16251,7 +15444,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
-        <v>4155</v>
+        <v>4151</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>480</v>
@@ -16266,10 +15459,10 @@
         <v>181</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H449" s="1">
-        <v>4152</v>
+        <v>4147</v>
       </c>
       <c r="I449" s="1">
         <v>0</v>
@@ -16280,7 +15473,7 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
-        <v>4156</v>
+        <v>4152</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>480</v>
@@ -16295,21 +15488,21 @@
         <v>181</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="H450" s="1">
-        <v>4152</v>
+        <v>0</v>
       </c>
       <c r="I450" s="1">
         <v>0</v>
       </c>
       <c r="J450" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
-        <v>4157</v>
+        <v>4153</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>480</v>
@@ -16324,21 +15517,21 @@
         <v>181</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="H451" s="1">
-        <v>0</v>
+        <v>4152</v>
       </c>
       <c r="I451" s="1">
         <v>0</v>
       </c>
       <c r="J451" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="452" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
-        <v>4158</v>
+        <v>4154</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>480</v>
@@ -16353,10 +15546,10 @@
         <v>181</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>52</v>
+        <v>473</v>
       </c>
       <c r="H452" s="1">
-        <v>4157</v>
+        <v>4152</v>
       </c>
       <c r="I452" s="1">
         <v>0</v>
@@ -16367,7 +15560,7 @@
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
-        <v>4159</v>
+        <v>4155</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>480</v>
@@ -16382,10 +15575,10 @@
         <v>181</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H453" s="1">
-        <v>4157</v>
+        <v>4152</v>
       </c>
       <c r="I453" s="1">
         <v>0</v>
@@ -16396,7 +15589,7 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
-        <v>4160</v>
+        <v>4156</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>480</v>
@@ -16411,10 +15604,10 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="H454" s="1">
-        <v>4157</v>
+        <v>4152</v>
       </c>
       <c r="I454" s="1">
         <v>0</v>
@@ -16425,7 +15618,7 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
-        <v>4161</v>
+        <v>4157</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>480</v>
@@ -16440,39 +15633,39 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H455" s="1">
+        <v>0</v>
+      </c>
+      <c r="I455" s="1">
+        <v>0</v>
+      </c>
+      <c r="J455" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A456" s="1">
+        <v>4158</v>
+      </c>
+      <c r="B456" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D456" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E456" s="1">
+        <v>0</v>
+      </c>
+      <c r="F456" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G456" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H456" s="1">
         <v>4157</v>
-      </c>
-      <c r="I455" s="1">
-        <v>0</v>
-      </c>
-      <c r="J455" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A456" s="1">
-        <v>5001</v>
-      </c>
-      <c r="B456" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D456" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E456" s="1">
-        <v>0</v>
-      </c>
-      <c r="F456" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G456" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="H456" s="1">
-        <v>0</v>
       </c>
       <c r="I456" s="1">
         <v>0</v>
@@ -16483,13 +15676,13 @@
     </row>
     <row r="457" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
-        <v>6000</v>
+        <v>4159</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="E457" s="1">
         <v>0</v>
@@ -16498,10 +15691,10 @@
         <v>181</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>292</v>
+        <v>477</v>
       </c>
       <c r="H457" s="1">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="I457" s="1">
         <v>0</v>
@@ -16512,13 +15705,13 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
-        <v>6001</v>
+        <v>4160</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="E458" s="1">
         <v>0</v>
@@ -16527,10 +15720,10 @@
         <v>181</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>293</v>
+        <v>478</v>
       </c>
       <c r="H458" s="1">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="I458" s="1">
         <v>0</v>
@@ -16541,13 +15734,13 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
-        <v>6002</v>
+        <v>4161</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="E459" s="1">
         <v>0</v>
@@ -16556,10 +15749,10 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>294</v>
+        <v>479</v>
       </c>
       <c r="H459" s="1">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="I459" s="1">
         <v>0</v>
@@ -16570,7 +15763,7 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
-        <v>6003</v>
+        <v>5001</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>284</v>
@@ -16585,7 +15778,7 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="H460" s="1">
         <v>0</v>
@@ -16599,7 +15792,7 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
-        <v>6004</v>
+        <v>6000</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>284</v>
@@ -16614,7 +15807,7 @@
         <v>181</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="H461" s="1">
         <v>0</v>
@@ -16628,7 +15821,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
-        <v>6005</v>
+        <v>6001</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>284</v>
@@ -16643,7 +15836,7 @@
         <v>181</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H462" s="1">
         <v>0</v>
@@ -16657,7 +15850,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>6006</v>
+        <v>6002</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>284</v>
@@ -16672,7 +15865,7 @@
         <v>181</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H463" s="1">
         <v>0</v>
@@ -16686,7 +15879,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>6100</v>
+        <v>6003</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>284</v>
@@ -16701,7 +15894,7 @@
         <v>181</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="H464" s="1">
         <v>0</v>
@@ -16715,35 +15908,151 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
+        <v>6004</v>
+      </c>
+      <c r="B465" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D465" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E465" s="1">
+        <v>0</v>
+      </c>
+      <c r="F465" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G465" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="H465" s="1">
+        <v>0</v>
+      </c>
+      <c r="I465" s="1">
+        <v>0</v>
+      </c>
+      <c r="J465" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A466" s="1">
+        <v>6005</v>
+      </c>
+      <c r="B466" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D466" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E466" s="1">
+        <v>0</v>
+      </c>
+      <c r="F466" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G466" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H466" s="1">
+        <v>0</v>
+      </c>
+      <c r="I466" s="1">
+        <v>0</v>
+      </c>
+      <c r="J466" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A467" s="1">
+        <v>6006</v>
+      </c>
+      <c r="B467" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D467" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E467" s="1">
+        <v>0</v>
+      </c>
+      <c r="F467" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G467" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H467" s="1">
+        <v>0</v>
+      </c>
+      <c r="I467" s="1">
+        <v>0</v>
+      </c>
+      <c r="J467" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A468" s="1">
+        <v>6100</v>
+      </c>
+      <c r="B468" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D468" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E468" s="1">
+        <v>0</v>
+      </c>
+      <c r="F468" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G468" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H468" s="1">
+        <v>0</v>
+      </c>
+      <c r="I468" s="1">
+        <v>0</v>
+      </c>
+      <c r="J468" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A469" s="1">
         <v>8100</v>
       </c>
-      <c r="B465" s="3" t="s">
+      <c r="B469" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D465" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E465" s="1">
-        <v>0</v>
-      </c>
-      <c r="F465" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G465" s="1" t="s">
+      <c r="D469" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E469" s="1">
+        <v>0</v>
+      </c>
+      <c r="F469" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G469" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H465" s="1">
-        <v>0</v>
-      </c>
-      <c r="I465" s="1">
-        <v>0</v>
-      </c>
-      <c r="J465" s="1" t="b">
+      <c r="H469" s="1">
+        <v>0</v>
+      </c>
+      <c r="I469" s="1">
+        <v>0</v>
+      </c>
+      <c r="J469" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J465"/>
+  <autoFilter ref="A3:J469"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$469</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$470</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="580">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1916,6 +1916,10 @@
   </si>
   <si>
     <t>打起精神来，现在前进吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我没有镰刀，没办法收割</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2305,7 +2309,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J469"/>
+  <dimension ref="A2:J470"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -11007,7 +11011,7 @@
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A296" s="1">
-        <v>3200</v>
+        <v>3015</v>
       </c>
       <c r="B296" s="3">
         <v>2</v>
@@ -11022,7 +11026,7 @@
         <v>181</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>304</v>
+        <v>579</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -11036,7 +11040,7 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B297" s="3">
         <v>2</v>
@@ -11051,7 +11055,7 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -11065,10 +11069,10 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>4000</v>
-      </c>
-      <c r="B298" s="3" t="s">
-        <v>480</v>
+        <v>3201</v>
+      </c>
+      <c r="B298" s="3">
+        <v>2</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>274</v>
@@ -11080,7 +11084,7 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>353</v>
+        <v>305</v>
       </c>
       <c r="H298" s="1">
         <v>0</v>
@@ -11089,12 +11093,12 @@
         <v>0</v>
       </c>
       <c r="J298" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>480</v>
@@ -11109,21 +11113,21 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H299" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I299" s="1">
         <v>0</v>
       </c>
       <c r="J299" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>480</v>
@@ -11138,7 +11142,7 @@
         <v>181</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>45</v>
+        <v>354</v>
       </c>
       <c r="H300" s="1">
         <v>4000</v>
@@ -11150,9 +11154,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>480</v>
@@ -11167,7 +11171,7 @@
         <v>181</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>355</v>
+        <v>45</v>
       </c>
       <c r="H301" s="1">
         <v>4000</v>
@@ -11179,9 +11183,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>480</v>
@@ -11196,7 +11200,7 @@
         <v>181</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H302" s="1">
         <v>4000</v>
@@ -11210,7 +11214,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>480</v>
@@ -11225,21 +11229,21 @@
         <v>181</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H303" s="1">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I303" s="1">
         <v>0</v>
       </c>
       <c r="J303" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>480</v>
@@ -11254,21 +11258,21 @@
         <v>181</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H304" s="1">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="I304" s="1">
         <v>0</v>
       </c>
       <c r="J304" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>480</v>
@@ -11283,7 +11287,7 @@
         <v>181</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H305" s="1">
         <v>4005</v>
@@ -11297,7 +11301,7 @@
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>480</v>
@@ -11312,7 +11316,7 @@
         <v>181</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H306" s="1">
         <v>4005</v>
@@ -11326,7 +11330,7 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>480</v>
@@ -11341,7 +11345,7 @@
         <v>181</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H307" s="1">
         <v>4005</v>
@@ -11355,7 +11359,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>480</v>
@@ -11370,7 +11374,7 @@
         <v>181</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H308" s="1">
         <v>4005</v>
@@ -11384,7 +11388,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>480</v>
@@ -11399,21 +11403,21 @@
         <v>181</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H309" s="1">
-        <v>0</v>
+        <v>4005</v>
       </c>
       <c r="I309" s="1">
         <v>0</v>
       </c>
       <c r="J309" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="310" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>480</v>
@@ -11428,21 +11432,21 @@
         <v>181</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>49</v>
+        <v>363</v>
       </c>
       <c r="H310" s="1">
-        <v>4011</v>
+        <v>0</v>
       </c>
       <c r="I310" s="1">
         <v>0</v>
       </c>
       <c r="J310" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>480</v>
@@ -11457,7 +11461,7 @@
         <v>181</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>364</v>
+        <v>49</v>
       </c>
       <c r="H311" s="1">
         <v>4011</v>
@@ -11469,9 +11473,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>480</v>
@@ -11486,7 +11490,7 @@
         <v>181</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H312" s="1">
         <v>4011</v>
@@ -11500,7 +11504,7 @@
     </row>
     <row r="313" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>480</v>
@@ -11515,7 +11519,7 @@
         <v>181</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H313" s="1">
         <v>4011</v>
@@ -11529,7 +11533,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>480</v>
@@ -11544,21 +11548,21 @@
         <v>181</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H314" s="1">
-        <v>0</v>
+        <v>4011</v>
       </c>
       <c r="I314" s="1">
         <v>0</v>
       </c>
       <c r="J314" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="315" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>480</v>
@@ -11573,21 +11577,21 @@
         <v>181</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>56</v>
+        <v>367</v>
       </c>
       <c r="H315" s="1">
-        <v>4016</v>
+        <v>0</v>
       </c>
       <c r="I315" s="1">
         <v>0</v>
       </c>
       <c r="J315" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>480</v>
@@ -11602,7 +11606,7 @@
         <v>181</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>368</v>
+        <v>56</v>
       </c>
       <c r="H316" s="1">
         <v>4016</v>
@@ -11616,7 +11620,7 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>480</v>
@@ -11631,7 +11635,7 @@
         <v>181</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H317" s="1">
         <v>4016</v>
@@ -11645,7 +11649,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>480</v>
@@ -11660,7 +11664,7 @@
         <v>181</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H318" s="1">
         <v>4016</v>
@@ -11674,7 +11678,7 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>480</v>
@@ -11689,21 +11693,21 @@
         <v>181</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H319" s="1">
-        <v>0</v>
+        <v>4016</v>
       </c>
       <c r="I319" s="1">
         <v>0</v>
       </c>
       <c r="J319" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>480</v>
@@ -11718,21 +11722,21 @@
         <v>181</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H320" s="1">
-        <v>4021</v>
+        <v>0</v>
       </c>
       <c r="I320" s="1">
         <v>0</v>
       </c>
       <c r="J320" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>480</v>
@@ -11747,7 +11751,7 @@
         <v>181</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H321" s="1">
         <v>4021</v>
@@ -11759,9 +11763,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>480</v>
@@ -11776,7 +11780,7 @@
         <v>181</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H322" s="1">
         <v>4021</v>
@@ -11788,9 +11792,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>480</v>
@@ -11805,7 +11809,7 @@
         <v>181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H323" s="1">
         <v>4021</v>
@@ -11817,9 +11821,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>480</v>
@@ -11834,21 +11838,21 @@
         <v>181</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H324" s="1">
-        <v>0</v>
+        <v>4021</v>
       </c>
       <c r="I324" s="1">
         <v>0</v>
       </c>
       <c r="J324" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>480</v>
@@ -11863,21 +11867,21 @@
         <v>181</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H325" s="1">
-        <v>4026</v>
+        <v>0</v>
       </c>
       <c r="I325" s="1">
         <v>0</v>
       </c>
       <c r="J325" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>480</v>
@@ -11892,7 +11896,7 @@
         <v>181</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H326" s="1">
         <v>4026</v>
@@ -11906,7 +11910,7 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>480</v>
@@ -11921,7 +11925,7 @@
         <v>181</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H327" s="1">
         <v>4026</v>
@@ -11935,7 +11939,7 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>480</v>
@@ -11950,7 +11954,7 @@
         <v>181</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H328" s="1">
         <v>4026</v>
@@ -11964,7 +11968,7 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>480</v>
@@ -11979,21 +11983,21 @@
         <v>181</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H329" s="1">
-        <v>0</v>
+        <v>4026</v>
       </c>
       <c r="I329" s="1">
         <v>0</v>
       </c>
       <c r="J329" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>480</v>
@@ -12008,21 +12012,21 @@
         <v>181</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H330" s="1">
-        <v>4031</v>
+        <v>0</v>
       </c>
       <c r="I330" s="1">
         <v>0</v>
       </c>
       <c r="J330" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>480</v>
@@ -12037,7 +12041,7 @@
         <v>181</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H331" s="1">
         <v>4031</v>
@@ -12049,9 +12053,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>480</v>
@@ -12066,7 +12070,7 @@
         <v>181</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H332" s="1">
         <v>4031</v>
@@ -12078,9 +12082,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>480</v>
@@ -12095,7 +12099,7 @@
         <v>181</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H333" s="1">
         <v>4031</v>
@@ -12107,9 +12111,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>480</v>
@@ -12124,21 +12128,21 @@
         <v>181</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H334" s="1">
-        <v>0</v>
+        <v>4031</v>
       </c>
       <c r="I334" s="1">
         <v>0</v>
       </c>
       <c r="J334" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>480</v>
@@ -12153,21 +12157,21 @@
         <v>181</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H335" s="1">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="I335" s="1">
         <v>0</v>
       </c>
       <c r="J335" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>480</v>
@@ -12182,7 +12186,7 @@
         <v>181</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H336" s="1">
         <v>4036</v>
@@ -12196,7 +12200,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>480</v>
@@ -12211,7 +12215,7 @@
         <v>181</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H337" s="1">
         <v>4036</v>
@@ -12225,7 +12229,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>480</v>
@@ -12240,7 +12244,7 @@
         <v>181</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H338" s="1">
         <v>4036</v>
@@ -12254,7 +12258,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>480</v>
@@ -12269,21 +12273,21 @@
         <v>181</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H339" s="1">
-        <v>0</v>
+        <v>4036</v>
       </c>
       <c r="I339" s="1">
         <v>0</v>
       </c>
       <c r="J339" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>480</v>
@@ -12298,21 +12302,21 @@
         <v>181</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H340" s="1">
-        <v>4041</v>
+        <v>0</v>
       </c>
       <c r="I340" s="1">
         <v>0</v>
       </c>
       <c r="J340" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>480</v>
@@ -12327,7 +12331,7 @@
         <v>181</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="H341" s="1">
         <v>4041</v>
@@ -12339,9 +12343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>480</v>
@@ -12356,7 +12360,7 @@
         <v>181</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="H342" s="1">
         <v>4041</v>
@@ -12370,7 +12374,7 @@
     </row>
     <row r="343" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>480</v>
@@ -12385,7 +12389,7 @@
         <v>181</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>393</v>
+        <v>219</v>
       </c>
       <c r="H343" s="1">
         <v>4041</v>
@@ -12399,7 +12403,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>480</v>
@@ -12414,21 +12418,21 @@
         <v>181</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H344" s="1">
-        <v>0</v>
+        <v>4041</v>
       </c>
       <c r="I344" s="1">
         <v>0</v>
       </c>
       <c r="J344" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>480</v>
@@ -12443,21 +12447,21 @@
         <v>181</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H345" s="1">
-        <v>4046</v>
+        <v>0</v>
       </c>
       <c r="I345" s="1">
         <v>0</v>
       </c>
       <c r="J345" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>480</v>
@@ -12472,7 +12476,7 @@
         <v>181</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>61</v>
+        <v>395</v>
       </c>
       <c r="H346" s="1">
         <v>4046</v>
@@ -12484,9 +12488,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>480</v>
@@ -12501,7 +12505,7 @@
         <v>181</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H347" s="1">
         <v>4046</v>
@@ -12515,7 +12519,7 @@
     </row>
     <row r="348" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>4050</v>
+        <v>4049</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>480</v>
@@ -12530,7 +12534,7 @@
         <v>181</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>396</v>
+        <v>62</v>
       </c>
       <c r="H348" s="1">
         <v>4046</v>
@@ -12544,7 +12548,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>480</v>
@@ -12559,21 +12563,21 @@
         <v>181</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H349" s="1">
-        <v>0</v>
+        <v>4046</v>
       </c>
       <c r="I349" s="1">
         <v>0</v>
       </c>
       <c r="J349" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>480</v>
@@ -12588,21 +12592,21 @@
         <v>181</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H350" s="1">
-        <v>4051</v>
+        <v>0</v>
       </c>
       <c r="I350" s="1">
         <v>0</v>
       </c>
       <c r="J350" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>480</v>
@@ -12617,7 +12621,7 @@
         <v>181</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H351" s="1">
         <v>4051</v>
@@ -12631,7 +12635,7 @@
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>480</v>
@@ -12646,7 +12650,7 @@
         <v>181</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H352" s="1">
         <v>4051</v>
@@ -12660,7 +12664,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>480</v>
@@ -12675,7 +12679,7 @@
         <v>181</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H353" s="1">
         <v>4051</v>
@@ -12689,7 +12693,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>4056</v>
+        <v>4055</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>480</v>
@@ -12704,21 +12708,21 @@
         <v>181</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H354" s="1">
-        <v>0</v>
+        <v>4051</v>
       </c>
       <c r="I354" s="1">
         <v>0</v>
       </c>
       <c r="J354" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>480</v>
@@ -12733,21 +12737,21 @@
         <v>181</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H355" s="1">
-        <v>4056</v>
+        <v>0</v>
       </c>
       <c r="I355" s="1">
         <v>0</v>
       </c>
       <c r="J355" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>480</v>
@@ -12762,7 +12766,7 @@
         <v>181</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H356" s="1">
         <v>4056</v>
@@ -12776,7 +12780,7 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>480</v>
@@ -12791,7 +12795,7 @@
         <v>181</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H357" s="1">
         <v>4056</v>
@@ -12805,7 +12809,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>480</v>
@@ -12820,7 +12824,7 @@
         <v>181</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H358" s="1">
         <v>4056</v>
@@ -12834,7 +12838,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>4061</v>
+        <v>4060</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>480</v>
@@ -12849,21 +12853,21 @@
         <v>181</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H359" s="1">
-        <v>0</v>
+        <v>4056</v>
       </c>
       <c r="I359" s="1">
         <v>0</v>
       </c>
       <c r="J359" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>480</v>
@@ -12878,21 +12882,21 @@
         <v>181</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H360" s="1">
-        <v>4061</v>
+        <v>0</v>
       </c>
       <c r="I360" s="1">
         <v>0</v>
       </c>
       <c r="J360" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>480</v>
@@ -12907,7 +12911,7 @@
         <v>181</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>51</v>
+        <v>408</v>
       </c>
       <c r="H361" s="1">
         <v>4061</v>
@@ -12919,9 +12923,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>480</v>
@@ -12936,7 +12940,7 @@
         <v>181</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H362" s="1">
         <v>4061</v>
@@ -12950,7 +12954,7 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>480</v>
@@ -12965,7 +12969,7 @@
         <v>181</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>409</v>
+        <v>58</v>
       </c>
       <c r="H363" s="1">
         <v>4061</v>
@@ -12977,9 +12981,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>4066</v>
+        <v>4065</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>480</v>
@@ -12994,21 +12998,21 @@
         <v>181</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H364" s="1">
-        <v>0</v>
+        <v>4061</v>
       </c>
       <c r="I364" s="1">
         <v>0</v>
       </c>
       <c r="J364" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>480</v>
@@ -13023,21 +13027,21 @@
         <v>181</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>81</v>
+        <v>410</v>
       </c>
       <c r="H365" s="1">
-        <v>4066</v>
+        <v>0</v>
       </c>
       <c r="I365" s="1">
         <v>0</v>
       </c>
       <c r="J365" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>480</v>
@@ -13052,7 +13056,7 @@
         <v>181</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>411</v>
+        <v>81</v>
       </c>
       <c r="H366" s="1">
         <v>4066</v>
@@ -13064,9 +13068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>4069</v>
+        <v>4068</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>480</v>
@@ -13081,7 +13085,7 @@
         <v>181</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>65</v>
+        <v>411</v>
       </c>
       <c r="H367" s="1">
         <v>4066</v>
@@ -13093,9 +13097,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>480</v>
@@ -13110,7 +13114,7 @@
         <v>181</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>412</v>
+        <v>65</v>
       </c>
       <c r="H368" s="1">
         <v>4066</v>
@@ -13124,7 +13128,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>480</v>
@@ -13139,21 +13143,21 @@
         <v>181</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H369" s="1">
-        <v>0</v>
+        <v>4066</v>
       </c>
       <c r="I369" s="1">
         <v>0</v>
       </c>
       <c r="J369" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="370" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>480</v>
@@ -13168,21 +13172,21 @@
         <v>181</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>68</v>
+        <v>413</v>
       </c>
       <c r="H370" s="1">
-        <v>4071</v>
+        <v>0</v>
       </c>
       <c r="I370" s="1">
         <v>0</v>
       </c>
       <c r="J370" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>480</v>
@@ -13197,7 +13201,7 @@
         <v>181</v>
       </c>
       <c r="G371" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H371" s="1">
         <v>4071</v>
@@ -13211,7 +13215,7 @@
     </row>
     <row r="372" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>480</v>
@@ -13226,7 +13230,7 @@
         <v>181</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="H372" s="1">
         <v>4071</v>
@@ -13240,7 +13244,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>480</v>
@@ -13255,7 +13259,7 @@
         <v>181</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H373" s="1">
         <v>4071</v>
@@ -13269,7 +13273,7 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>480</v>
@@ -13284,21 +13288,21 @@
         <v>181</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H374" s="1">
-        <v>0</v>
+        <v>4071</v>
       </c>
       <c r="I374" s="1">
         <v>0</v>
       </c>
       <c r="J374" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>480</v>
@@ -13313,21 +13317,21 @@
         <v>181</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H375" s="1">
-        <v>4076</v>
+        <v>0</v>
       </c>
       <c r="I375" s="1">
         <v>0</v>
       </c>
       <c r="J375" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>480</v>
@@ -13342,7 +13346,7 @@
         <v>181</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H376" s="1">
         <v>4076</v>
@@ -13356,7 +13360,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>480</v>
@@ -13371,7 +13375,7 @@
         <v>181</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H377" s="1">
         <v>4076</v>
@@ -13385,7 +13389,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>4080</v>
+        <v>4079</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>480</v>
@@ -13400,7 +13404,7 @@
         <v>181</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H378" s="1">
         <v>4076</v>
@@ -13414,7 +13418,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>4081</v>
+        <v>4080</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>480</v>
@@ -13429,21 +13433,21 @@
         <v>181</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H379" s="1">
-        <v>0</v>
+        <v>4076</v>
       </c>
       <c r="I379" s="1">
         <v>0</v>
       </c>
       <c r="J379" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="380" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>480</v>
@@ -13458,21 +13462,21 @@
         <v>181</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>80</v>
+        <v>421</v>
       </c>
       <c r="H380" s="1">
-        <v>4081</v>
+        <v>0</v>
       </c>
       <c r="I380" s="1">
         <v>0</v>
       </c>
       <c r="J380" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>480</v>
@@ -13487,7 +13491,7 @@
         <v>181</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H381" s="1">
         <v>4081</v>
@@ -13501,7 +13505,7 @@
     </row>
     <row r="382" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>4084</v>
+        <v>4083</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>480</v>
@@ -13516,7 +13520,7 @@
         <v>181</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>329</v>
+        <v>59</v>
       </c>
       <c r="H382" s="1">
         <v>4081</v>
@@ -13528,9 +13532,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>480</v>
@@ -13545,7 +13549,7 @@
         <v>181</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>422</v>
+        <v>329</v>
       </c>
       <c r="H383" s="1">
         <v>4081</v>
@@ -13559,7 +13563,7 @@
     </row>
     <row r="384" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>480</v>
@@ -13574,21 +13578,21 @@
         <v>181</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H384" s="1">
-        <v>0</v>
+        <v>4081</v>
       </c>
       <c r="I384" s="1">
         <v>0</v>
       </c>
       <c r="J384" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>4087</v>
+        <v>4086</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>480</v>
@@ -13603,21 +13607,21 @@
         <v>181</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H385" s="1">
-        <v>4086</v>
+        <v>0</v>
       </c>
       <c r="I385" s="1">
         <v>0</v>
       </c>
       <c r="J385" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>4088</v>
+        <v>4087</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>480</v>
@@ -13632,7 +13636,7 @@
         <v>181</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H386" s="1">
         <v>4086</v>
@@ -13646,7 +13650,7 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>4089</v>
+        <v>4088</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>480</v>
@@ -13661,7 +13665,7 @@
         <v>181</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H387" s="1">
         <v>4086</v>
@@ -13675,7 +13679,7 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>480</v>
@@ -13690,7 +13694,7 @@
         <v>181</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H388" s="1">
         <v>4086</v>
@@ -13704,7 +13708,7 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>4091</v>
+        <v>4090</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>480</v>
@@ -13719,21 +13723,21 @@
         <v>181</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H389" s="1">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="I389" s="1">
         <v>0</v>
       </c>
       <c r="J389" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>480</v>
@@ -13748,21 +13752,21 @@
         <v>181</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H390" s="1">
-        <v>4091</v>
+        <v>0</v>
       </c>
       <c r="I390" s="1">
         <v>0</v>
       </c>
       <c r="J390" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>4093</v>
+        <v>4092</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>480</v>
@@ -13777,7 +13781,7 @@
         <v>181</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H391" s="1">
         <v>4091</v>
@@ -13791,7 +13795,7 @@
     </row>
     <row r="392" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>4094</v>
+        <v>4093</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>480</v>
@@ -13806,7 +13810,7 @@
         <v>181</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H392" s="1">
         <v>4091</v>
@@ -13820,7 +13824,7 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>4095</v>
+        <v>4094</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>480</v>
@@ -13835,7 +13839,7 @@
         <v>181</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H393" s="1">
         <v>4091</v>
@@ -13849,7 +13853,7 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>480</v>
@@ -13864,21 +13868,21 @@
         <v>181</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H394" s="1">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="I394" s="1">
         <v>0</v>
       </c>
       <c r="J394" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>4097</v>
+        <v>4096</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>480</v>
@@ -13893,21 +13897,21 @@
         <v>181</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H395" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="I395" s="1">
         <v>0</v>
       </c>
       <c r="J395" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>4098</v>
+        <v>4097</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>480</v>
@@ -13922,7 +13926,7 @@
         <v>181</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H396" s="1">
         <v>4096</v>
@@ -13936,7 +13940,7 @@
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>4099</v>
+        <v>4098</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>480</v>
@@ -13951,7 +13955,7 @@
         <v>181</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H397" s="1">
         <v>4096</v>
@@ -13965,7 +13969,7 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>4100</v>
+        <v>4099</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>480</v>
@@ -13980,7 +13984,7 @@
         <v>181</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H398" s="1">
         <v>4096</v>
@@ -13994,7 +13998,7 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>480</v>
@@ -14009,21 +14013,21 @@
         <v>181</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H399" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="I399" s="1">
         <v>0</v>
       </c>
       <c r="J399" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>480</v>
@@ -14038,21 +14042,21 @@
         <v>181</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="H400" s="1">
-        <v>4101</v>
+        <v>0</v>
       </c>
       <c r="I400" s="1">
         <v>0</v>
       </c>
       <c r="J400" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>480</v>
@@ -14067,7 +14071,7 @@
         <v>181</v>
       </c>
       <c r="G401" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H401" s="1">
         <v>4101</v>
@@ -14079,9 +14083,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>480</v>
@@ -14096,7 +14100,7 @@
         <v>181</v>
       </c>
       <c r="G402" s="1" t="s">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="H402" s="1">
         <v>4101</v>
@@ -14110,7 +14114,7 @@
     </row>
     <row r="403" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>480</v>
@@ -14125,7 +14129,7 @@
         <v>181</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>439</v>
+        <v>218</v>
       </c>
       <c r="H403" s="1">
         <v>4101</v>
@@ -14137,9 +14141,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>480</v>
@@ -14154,21 +14158,21 @@
         <v>181</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H404" s="1">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="I404" s="1">
         <v>0</v>
       </c>
       <c r="J404" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="405" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>480</v>
@@ -14183,21 +14187,21 @@
         <v>181</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="H405" s="1">
-        <v>4106</v>
+        <v>0</v>
       </c>
       <c r="I405" s="1">
         <v>0</v>
       </c>
       <c r="J405" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="406" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>480</v>
@@ -14212,7 +14216,7 @@
         <v>181</v>
       </c>
       <c r="G406" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="H406" s="1">
         <v>4106</v>
@@ -14226,7 +14230,7 @@
     </row>
     <row r="407" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>480</v>
@@ -14241,7 +14245,7 @@
         <v>181</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H407" s="1">
         <v>4106</v>
@@ -14253,9 +14257,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>480</v>
@@ -14270,7 +14274,7 @@
         <v>181</v>
       </c>
       <c r="G408" s="1" t="s">
-        <v>441</v>
+        <v>67</v>
       </c>
       <c r="H408" s="1">
         <v>4106</v>
@@ -14284,7 +14288,7 @@
     </row>
     <row r="409" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>480</v>
@@ -14299,21 +14303,21 @@
         <v>181</v>
       </c>
       <c r="G409" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H409" s="1">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="I409" s="1">
         <v>0</v>
       </c>
       <c r="J409" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>480</v>
@@ -14328,21 +14332,21 @@
         <v>181</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H410" s="1">
-        <v>4111</v>
+        <v>0</v>
       </c>
       <c r="I410" s="1">
         <v>0</v>
       </c>
       <c r="J410" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>480</v>
@@ -14357,7 +14361,7 @@
         <v>181</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H411" s="1">
         <v>4111</v>
@@ -14371,7 +14375,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>480</v>
@@ -14385,8 +14389,8 @@
       <c r="F412" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G412" s="2" t="s">
-        <v>445</v>
+      <c r="G412" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="H412" s="1">
         <v>4111</v>
@@ -14400,7 +14404,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>480</v>
@@ -14414,8 +14418,8 @@
       <c r="F413" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G413" s="1" t="s">
-        <v>446</v>
+      <c r="G413" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="H413" s="1">
         <v>4111</v>
@@ -14429,7 +14433,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>480</v>
@@ -14444,21 +14448,21 @@
         <v>181</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H414" s="1">
-        <v>0</v>
+        <v>4111</v>
       </c>
       <c r="I414" s="1">
         <v>0</v>
       </c>
       <c r="J414" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="415" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>480</v>
@@ -14473,21 +14477,21 @@
         <v>181</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>70</v>
+        <v>447</v>
       </c>
       <c r="H415" s="1">
-        <v>4116</v>
+        <v>0</v>
       </c>
       <c r="I415" s="1">
         <v>0</v>
       </c>
       <c r="J415" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>480</v>
@@ -14502,7 +14506,7 @@
         <v>181</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="H416" s="1">
         <v>4116</v>
@@ -14514,9 +14518,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>480</v>
@@ -14531,7 +14535,7 @@
         <v>181</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H417" s="1">
         <v>4116</v>
@@ -14545,7 +14549,7 @@
     </row>
     <row r="418" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>480</v>
@@ -14560,7 +14564,7 @@
         <v>181</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>448</v>
+        <v>63</v>
       </c>
       <c r="H418" s="1">
         <v>4116</v>
@@ -14572,9 +14576,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
-        <v>4121</v>
+        <v>4120</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>480</v>
@@ -14589,21 +14593,21 @@
         <v>181</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H419" s="1">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="I419" s="1">
         <v>0</v>
       </c>
       <c r="J419" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>480</v>
@@ -14618,21 +14622,21 @@
         <v>181</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H420" s="1">
-        <v>4121</v>
+        <v>0</v>
       </c>
       <c r="I420" s="1">
         <v>0</v>
       </c>
       <c r="J420" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>480</v>
@@ -14647,7 +14651,7 @@
         <v>181</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H421" s="1">
         <v>4121</v>
@@ -14661,7 +14665,7 @@
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
-        <v>4124</v>
+        <v>4123</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>480</v>
@@ -14676,7 +14680,7 @@
         <v>181</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H422" s="1">
         <v>4121</v>
@@ -14690,7 +14694,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
-        <v>4125</v>
+        <v>4124</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>480</v>
@@ -14705,7 +14709,7 @@
         <v>181</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H423" s="1">
         <v>4121</v>
@@ -14719,7 +14723,7 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
-        <v>4126</v>
+        <v>4125</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>480</v>
@@ -14734,21 +14738,21 @@
         <v>181</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H424" s="1">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="I424" s="1">
         <v>0</v>
       </c>
       <c r="J424" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>480</v>
@@ -14763,21 +14767,21 @@
         <v>181</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>71</v>
+        <v>454</v>
       </c>
       <c r="H425" s="1">
-        <v>4126</v>
+        <v>0</v>
       </c>
       <c r="I425" s="1">
         <v>0</v>
       </c>
       <c r="J425" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>480</v>
@@ -14792,7 +14796,7 @@
         <v>181</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H426" s="1">
         <v>4126</v>
@@ -14804,9 +14808,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
-        <v>4129</v>
+        <v>4128</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>480</v>
@@ -14821,7 +14825,7 @@
         <v>181</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H427" s="1">
         <v>4126</v>
@@ -14833,9 +14837,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
-        <v>4130</v>
+        <v>4129</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>480</v>
@@ -14850,7 +14854,7 @@
         <v>181</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H428" s="1">
         <v>4126</v>
@@ -14862,9 +14866,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>480</v>
@@ -14879,7 +14883,7 @@
         <v>181</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>455</v>
+        <v>55</v>
       </c>
       <c r="H429" s="1">
         <v>4126</v>
@@ -14891,9 +14895,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>480</v>
@@ -14908,21 +14912,21 @@
         <v>181</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H430" s="1">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="I430" s="1">
         <v>0</v>
       </c>
       <c r="J430" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="431" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>480</v>
@@ -14937,21 +14941,21 @@
         <v>181</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="H431" s="1">
-        <v>4132</v>
+        <v>0</v>
       </c>
       <c r="I431" s="1">
         <v>0</v>
       </c>
       <c r="J431" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
-        <v>4134</v>
+        <v>4133</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>480</v>
@@ -14966,7 +14970,7 @@
         <v>181</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="H432" s="1">
         <v>4132</v>
@@ -14978,9 +14982,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
-        <v>4135</v>
+        <v>4134</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>480</v>
@@ -14995,7 +14999,7 @@
         <v>181</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>66</v>
+        <v>457</v>
       </c>
       <c r="H433" s="1">
         <v>4132</v>
@@ -15007,9 +15011,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
-        <v>4136</v>
+        <v>4135</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>480</v>
@@ -15024,7 +15028,7 @@
         <v>181</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>458</v>
+        <v>66</v>
       </c>
       <c r="H434" s="1">
         <v>4132</v>
@@ -15036,9 +15040,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
-        <v>4137</v>
+        <v>4136</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>480</v>
@@ -15053,21 +15057,21 @@
         <v>181</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H435" s="1">
-        <v>0</v>
+        <v>4132</v>
       </c>
       <c r="I435" s="1">
         <v>0</v>
       </c>
       <c r="J435" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
-        <v>4138</v>
+        <v>4137</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>480</v>
@@ -15082,21 +15086,21 @@
         <v>181</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H436" s="1">
-        <v>4137</v>
+        <v>0</v>
       </c>
       <c r="I436" s="1">
         <v>0</v>
       </c>
       <c r="J436" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="437" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
-        <v>4139</v>
+        <v>4138</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>480</v>
@@ -15111,7 +15115,7 @@
         <v>181</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H437" s="1">
         <v>4137</v>
@@ -15123,9 +15127,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>480</v>
@@ -15140,7 +15144,7 @@
         <v>181</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H438" s="1">
         <v>4137</v>
@@ -15154,7 +15158,7 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
-        <v>4141</v>
+        <v>4140</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>480</v>
@@ -15169,7 +15173,7 @@
         <v>181</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H439" s="1">
         <v>4137</v>
@@ -15183,7 +15187,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>480</v>
@@ -15198,21 +15202,21 @@
         <v>181</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H440" s="1">
-        <v>0</v>
+        <v>4137</v>
       </c>
       <c r="I440" s="1">
         <v>0</v>
       </c>
       <c r="J440" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
-        <v>4143</v>
+        <v>4142</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>480</v>
@@ -15227,21 +15231,21 @@
         <v>181</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H441" s="1">
-        <v>4142</v>
+        <v>0</v>
       </c>
       <c r="I441" s="1">
         <v>0</v>
       </c>
       <c r="J441" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
-        <v>4144</v>
+        <v>4143</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>480</v>
@@ -15256,7 +15260,7 @@
         <v>181</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>48</v>
+        <v>465</v>
       </c>
       <c r="H442" s="1">
         <v>4142</v>
@@ -15268,9 +15272,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
-        <v>4145</v>
+        <v>4144</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>480</v>
@@ -15285,7 +15289,7 @@
         <v>181</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H443" s="1">
         <v>4142</v>
@@ -15299,7 +15303,7 @@
     </row>
     <row r="444" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>480</v>
@@ -15314,7 +15318,7 @@
         <v>181</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>466</v>
+        <v>60</v>
       </c>
       <c r="H444" s="1">
         <v>4142</v>
@@ -15328,7 +15332,7 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>480</v>
@@ -15343,21 +15347,21 @@
         <v>181</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H445" s="1">
-        <v>0</v>
+        <v>4142</v>
       </c>
       <c r="I445" s="1">
         <v>0</v>
       </c>
       <c r="J445" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>480</v>
@@ -15372,21 +15376,21 @@
         <v>181</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>79</v>
+        <v>467</v>
       </c>
       <c r="H446" s="1">
-        <v>4147</v>
+        <v>0</v>
       </c>
       <c r="I446" s="1">
         <v>0</v>
       </c>
       <c r="J446" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>480</v>
@@ -15401,7 +15405,7 @@
         <v>181</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>468</v>
+        <v>79</v>
       </c>
       <c r="H447" s="1">
         <v>4147</v>
@@ -15415,7 +15419,7 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>480</v>
@@ -15430,7 +15434,7 @@
         <v>181</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H448" s="1">
         <v>4147</v>
@@ -15444,7 +15448,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>480</v>
@@ -15459,7 +15463,7 @@
         <v>181</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H449" s="1">
         <v>4147</v>
@@ -15473,7 +15477,7 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>480</v>
@@ -15488,21 +15492,21 @@
         <v>181</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H450" s="1">
-        <v>0</v>
+        <v>4147</v>
       </c>
       <c r="I450" s="1">
         <v>0</v>
       </c>
       <c r="J450" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>480</v>
@@ -15517,21 +15521,21 @@
         <v>181</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H451" s="1">
-        <v>4152</v>
+        <v>0</v>
       </c>
       <c r="I451" s="1">
         <v>0</v>
       </c>
       <c r="J451" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
-        <v>4154</v>
+        <v>4153</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>480</v>
@@ -15546,7 +15550,7 @@
         <v>181</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H452" s="1">
         <v>4152</v>
@@ -15560,7 +15564,7 @@
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
-        <v>4155</v>
+        <v>4154</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>480</v>
@@ -15575,7 +15579,7 @@
         <v>181</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H453" s="1">
         <v>4152</v>
@@ -15589,7 +15593,7 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
-        <v>4156</v>
+        <v>4155</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>480</v>
@@ -15604,7 +15608,7 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H454" s="1">
         <v>4152</v>
@@ -15618,7 +15622,7 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
-        <v>4157</v>
+        <v>4156</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>480</v>
@@ -15633,21 +15637,21 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H455" s="1">
-        <v>0</v>
+        <v>4152</v>
       </c>
       <c r="I455" s="1">
         <v>0</v>
       </c>
       <c r="J455" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="456" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
-        <v>4158</v>
+        <v>4157</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>480</v>
@@ -15662,21 +15666,21 @@
         <v>181</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>52</v>
+        <v>476</v>
       </c>
       <c r="H456" s="1">
-        <v>4157</v>
+        <v>0</v>
       </c>
       <c r="I456" s="1">
         <v>0</v>
       </c>
       <c r="J456" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>480</v>
@@ -15691,7 +15695,7 @@
         <v>181</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>477</v>
+        <v>52</v>
       </c>
       <c r="H457" s="1">
         <v>4157</v>
@@ -15705,7 +15709,7 @@
     </row>
     <row r="458" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>480</v>
@@ -15720,7 +15724,7 @@
         <v>181</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H458" s="1">
         <v>4157</v>
@@ -15734,7 +15738,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
-        <v>4161</v>
+        <v>4160</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>480</v>
@@ -15749,7 +15753,7 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H459" s="1">
         <v>4157</v>
@@ -15763,13 +15767,13 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
-        <v>5001</v>
+        <v>4161</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>284</v>
+        <v>480</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="E460" s="1">
         <v>0</v>
@@ -15778,10 +15782,10 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>291</v>
+        <v>479</v>
       </c>
       <c r="H460" s="1">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="I460" s="1">
         <v>0</v>
@@ -15792,7 +15796,7 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
-        <v>6000</v>
+        <v>5001</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>284</v>
@@ -15807,7 +15811,7 @@
         <v>181</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H461" s="1">
         <v>0</v>
@@ -15821,7 +15825,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>284</v>
@@ -15836,7 +15840,7 @@
         <v>181</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H462" s="1">
         <v>0</v>
@@ -15850,7 +15854,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>284</v>
@@ -15865,7 +15869,7 @@
         <v>181</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H463" s="1">
         <v>0</v>
@@ -15879,7 +15883,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>284</v>
@@ -15894,7 +15898,7 @@
         <v>181</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H464" s="1">
         <v>0</v>
@@ -15908,7 +15912,7 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>284</v>
@@ -15923,7 +15927,7 @@
         <v>181</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H465" s="1">
         <v>0</v>
@@ -15937,7 +15941,7 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>284</v>
@@ -15952,7 +15956,7 @@
         <v>181</v>
       </c>
       <c r="G466" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H466" s="1">
         <v>0</v>
@@ -15966,7 +15970,7 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A467" s="1">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>284</v>
@@ -15981,7 +15985,7 @@
         <v>181</v>
       </c>
       <c r="G467" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H467" s="1">
         <v>0</v>
@@ -15995,7 +15999,7 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
-        <v>6100</v>
+        <v>6006</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>284</v>
@@ -16010,7 +16014,7 @@
         <v>181</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H468" s="1">
         <v>0</v>
@@ -16024,35 +16028,64 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
+        <v>6100</v>
+      </c>
+      <c r="B469" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D469" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E469" s="1">
+        <v>0</v>
+      </c>
+      <c r="F469" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G469" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H469" s="1">
+        <v>0</v>
+      </c>
+      <c r="I469" s="1">
+        <v>0</v>
+      </c>
+      <c r="J469" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A470" s="1">
         <v>8100</v>
       </c>
-      <c r="B469" s="3" t="s">
+      <c r="B470" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="D469" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E469" s="1">
-        <v>0</v>
-      </c>
-      <c r="F469" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G469" s="1" t="s">
+      <c r="D470" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E470" s="1">
+        <v>0</v>
+      </c>
+      <c r="F470" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G470" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H469" s="1">
-        <v>0</v>
-      </c>
-      <c r="I469" s="1">
-        <v>0</v>
-      </c>
-      <c r="J469" s="1" t="b">
+      <c r="H470" s="1">
+        <v>0</v>
+      </c>
+      <c r="I470" s="1">
+        <v>0</v>
+      </c>
+      <c r="J470" s="1" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J469"/>
+  <autoFilter ref="A3:J470"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="652">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1920,6 +1920,241 @@
   </si>
   <si>
     <t>我没有镰刀，没办法收割</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年轻人，这小镇的清晨不错吧？</t>
+  </si>
+  <si>
+    <t>嗯，空气很清新。</t>
+  </si>
+  <si>
+    <t>我正考虑给店里进些新货，你有啥建议？</t>
+  </si>
+  <si>
+    <t>你看着挺精神，昨晚休息得好？</t>
+  </si>
+  <si>
+    <t>还可以。您这店每天很早就开门吗？</t>
+  </si>
+  <si>
+    <t>对，习惯了。你要是有空可以来帮忙整理下。</t>
+  </si>
+  <si>
+    <t>你初来乍到，有没有去小镇周边转转？</t>
+  </si>
+  <si>
+    <t>还没有。周边有什么好玩的地方吗？</t>
+  </si>
+  <si>
+    <t>有个小湖泊，景色很美。你可以去看看。</t>
+  </si>
+  <si>
+    <t>我店里新到了一些家具，你想看看吗？</t>
+  </si>
+  <si>
+    <t>现在没时间。都是些什么风格的家具？</t>
+  </si>
+  <si>
+    <t>古典和简约的都有。你有空了来品鉴下。</t>
+  </si>
+  <si>
+    <t>你在镇上有没有交到新朋友？</t>
+  </si>
+  <si>
+    <t>认识了几个。交朋友对在这生活很重要吗？</t>
+  </si>
+  <si>
+    <t>当然，朋友多了路好走。你可以多参加些活动。</t>
+  </si>
+  <si>
+    <t>我最近在研究新的家具摆放方式，你有啥想法？</t>
+  </si>
+  <si>
+    <t>我不太懂。是不是可以根据功能分区摆放？</t>
+  </si>
+  <si>
+    <t>有点道理。你要是有了新灵感随时告诉我。</t>
+  </si>
+  <si>
+    <t>你觉得小镇的居民们对家具的需求大吗？</t>
+  </si>
+  <si>
+    <t>不太清楚。应该会需要一些实用的家具吧。</t>
+  </si>
+  <si>
+    <t>我也这么认为。你帮我留意下大家的喜好。</t>
+  </si>
+  <si>
+    <t>早啊，小家伙。我正想改进家具的细节，你觉得从哪入手？</t>
+  </si>
+  <si>
+    <t>可以从打磨工艺上试试。</t>
+  </si>
+  <si>
+    <t>嗨，你看这小镇的建筑风格，对家具设计有启发吗？</t>
+  </si>
+  <si>
+    <t>我觉得可以借鉴一些线条和色彩搭配。</t>
+  </si>
+  <si>
+    <t>很有见地。你能帮我画些草图吗？</t>
+  </si>
+  <si>
+    <t>我打算用旧木材打造复古家具，你觉得可行吗？</t>
+  </si>
+  <si>
+    <t>应该可以，会很有韵味。</t>
+  </si>
+  <si>
+    <t>对。你知道哪里能找到更多旧木材吗？</t>
+  </si>
+  <si>
+    <t>你在镇上参加过手工制作的活动吗？</t>
+  </si>
+  <si>
+    <t>可以学习一些新技巧。你有兴趣的话我带你去。</t>
+  </si>
+  <si>
+    <t>我想在家具上镶嵌一些特色石头，你有推荐吗？</t>
+  </si>
+  <si>
+    <t>像玛瑙或者水晶石应该不错。</t>
+  </si>
+  <si>
+    <t>有道理。你能帮我找些性价比高的吗？</t>
+  </si>
+  <si>
+    <t>你觉得家具的舒适度和美观度怎么平衡？</t>
+  </si>
+  <si>
+    <t>先保证舒适度，再用装饰提升美观度。</t>
+  </si>
+  <si>
+    <t>我要举办一个小型家具展览，你能帮忙宣传吗？</t>
+  </si>
+  <si>
+    <t>我可以试试。需要我做什么？</t>
+  </si>
+  <si>
+    <t>我觉得淡色系比较清新。</t>
+  </si>
+  <si>
+    <t>嗯，值得考虑。你能帮我选些样板吗？</t>
+  </si>
+  <si>
+    <t>哟，早哇。我想去河边钓鱼，顺便找找灵感，一起不？</t>
+  </si>
+  <si>
+    <t>我还有事。你钓鱼能找到什么家具灵感？</t>
+  </si>
+  <si>
+    <t>比如鱼的形状和纹理可以用在装饰上。</t>
+  </si>
+  <si>
+    <t>嗨，我打算用兽皮做些特殊的家具配饰，你见过吗？</t>
+  </si>
+  <si>
+    <t>只要处理好就没问题。你有渠道获取吗？</t>
+  </si>
+  <si>
+    <t>我想在家具里安装音乐盒，一打开就有音乐，怎样？</t>
+  </si>
+  <si>
+    <t>我最近得到一些散发香味的木材，做什么家具好？</t>
+  </si>
+  <si>
+    <t>可以做个香薰柜，存放香料。</t>
+  </si>
+  <si>
+    <t>我想打造一款能折叠成小物件的家具，你觉得可能吗？</t>
+  </si>
+  <si>
+    <t>有可能，像折叠椅就很实用。</t>
+  </si>
+  <si>
+    <t>嘿，我设计了一款带有魔法储物空间的家具，神奇吧？</t>
+  </si>
+  <si>
+    <t>哇，太神奇了！怎么实现储物空间的魔法呢？</t>
+  </si>
+  <si>
+    <t>用魔法水晶驱动。你在镇上见过魔法水晶吗？</t>
+  </si>
+  <si>
+    <t>我不太清楚。我先去吃个早饭，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我今天有事。不好意思，我得走了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的。我突然想起有事，先走一步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的。我先去了，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我有点忙，先撤了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太清楚。我去打听下。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有。这类活动和家具制作有关吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我找找看。不好意思，我得赶紧走了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让我想想再告诉你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我在研究新的涂料，你对颜色有偏好吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不太会。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挺有趣。我忙完来找你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没见过呢。这样合适吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有。要不去问问别人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">好有创意！ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你在镇上逛过那些古老的小巷吗？可以从巷子里的图案找设计灵感。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太清楚。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你知道怎么处理木材香味吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没见过。我去探索下。我先去了，回见。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1959,7 +2194,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1969,6 +2204,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1987,7 +2228,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2002,6 +2243,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2309,7 +2559,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J470"/>
+  <dimension ref="A2:J542"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -16082,6 +16332,770 @@
       </c>
       <c r="J470" s="1" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A471" s="6">
+        <v>44001</v>
+      </c>
+      <c r="B471" s="7"/>
+      <c r="F471" s="7"/>
+      <c r="G471" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="H471" s="6">
+        <v>44002</v>
+      </c>
+    </row>
+    <row r="472" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A472" s="1">
+        <v>44002</v>
+      </c>
+      <c r="E472" s="1">
+        <v>0</v>
+      </c>
+      <c r="G472" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="473" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A473" s="1">
+        <v>44003</v>
+      </c>
+      <c r="G473" t="s">
+        <v>582</v>
+      </c>
+      <c r="H473" s="1">
+        <v>44004</v>
+      </c>
+    </row>
+    <row r="474" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A474" s="1">
+        <v>44004</v>
+      </c>
+      <c r="E474" s="1">
+        <v>0</v>
+      </c>
+      <c r="G474" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A475" s="1">
+        <v>44005</v>
+      </c>
+      <c r="G475" t="s">
+        <v>583</v>
+      </c>
+      <c r="H475" s="1">
+        <v>44006</v>
+      </c>
+    </row>
+    <row r="476" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A476" s="1">
+        <v>44006</v>
+      </c>
+      <c r="E476" s="1">
+        <v>0</v>
+      </c>
+      <c r="G476" t="s">
+        <v>584</v>
+      </c>
+      <c r="H476" s="1">
+        <v>44007</v>
+      </c>
+    </row>
+    <row r="477" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A477" s="1">
+        <v>44007</v>
+      </c>
+      <c r="G477" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A478" s="1">
+        <v>44008</v>
+      </c>
+      <c r="E478" s="1">
+        <v>0</v>
+      </c>
+      <c r="G478" t="s">
+        <v>634</v>
+      </c>
+      <c r="H478" s="1">
+        <v>44009</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A479" s="1">
+        <v>44009</v>
+      </c>
+      <c r="G479" t="s">
+        <v>586</v>
+      </c>
+      <c r="H479" s="1">
+        <v>44010</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A480" s="1">
+        <v>44010</v>
+      </c>
+      <c r="E480" s="1">
+        <v>0</v>
+      </c>
+      <c r="G480" t="s">
+        <v>587</v>
+      </c>
+      <c r="H480" s="1">
+        <v>44011</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A481" s="1">
+        <v>44011</v>
+      </c>
+      <c r="G481" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A482" s="1">
+        <v>44012</v>
+      </c>
+      <c r="G482" t="s">
+        <v>589</v>
+      </c>
+      <c r="H482" s="1">
+        <v>44013</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A483" s="1">
+        <v>44013</v>
+      </c>
+      <c r="E483" s="1">
+        <v>0</v>
+      </c>
+      <c r="G483" t="s">
+        <v>590</v>
+      </c>
+      <c r="H483" s="1">
+        <v>44014</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A484" s="1">
+        <v>44014</v>
+      </c>
+      <c r="G484" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A485" s="1">
+        <v>44015</v>
+      </c>
+      <c r="G485" t="s">
+        <v>592</v>
+      </c>
+      <c r="H485" s="1">
+        <v>44016</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A486" s="1">
+        <v>44016</v>
+      </c>
+      <c r="E486" s="1">
+        <v>0</v>
+      </c>
+      <c r="G486" t="s">
+        <v>593</v>
+      </c>
+      <c r="H486" s="1">
+        <v>44017</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A487" s="1">
+        <v>44017</v>
+      </c>
+      <c r="G487" t="s">
+        <v>594</v>
+      </c>
+      <c r="H487" s="1">
+        <v>44018</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A488" s="1">
+        <v>44018</v>
+      </c>
+      <c r="E488" s="1">
+        <v>0</v>
+      </c>
+      <c r="G488" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A489" s="1">
+        <v>44019</v>
+      </c>
+      <c r="G489" t="s">
+        <v>595</v>
+      </c>
+      <c r="H489" s="1">
+        <v>44020</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A490" s="1">
+        <v>44020</v>
+      </c>
+      <c r="E490" s="1">
+        <v>0</v>
+      </c>
+      <c r="G490" t="s">
+        <v>596</v>
+      </c>
+      <c r="H490" s="1">
+        <v>44021</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A491" s="1">
+        <v>44021</v>
+      </c>
+      <c r="G491" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A492" s="1">
+        <v>44022</v>
+      </c>
+      <c r="G492" t="s">
+        <v>598</v>
+      </c>
+      <c r="H492" s="1">
+        <v>44023</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A493" s="1">
+        <v>44023</v>
+      </c>
+      <c r="E493" s="1">
+        <v>0</v>
+      </c>
+      <c r="G493" t="s">
+        <v>599</v>
+      </c>
+      <c r="H493" s="1">
+        <v>44024</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A494" s="1">
+        <v>44024</v>
+      </c>
+      <c r="G494" t="s">
+        <v>600</v>
+      </c>
+      <c r="H494" s="1">
+        <v>44025</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A495" s="1">
+        <v>44025</v>
+      </c>
+      <c r="E495" s="1">
+        <v>0</v>
+      </c>
+      <c r="G495" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A496" s="6">
+        <v>44026</v>
+      </c>
+      <c r="B496" s="7"/>
+      <c r="F496" s="7"/>
+      <c r="G496" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="H496" s="6">
+        <v>44027</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A497" s="1">
+        <v>44027</v>
+      </c>
+      <c r="E497" s="1">
+        <v>0</v>
+      </c>
+      <c r="G497" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A498" s="1">
+        <v>44028</v>
+      </c>
+      <c r="G498" t="s">
+        <v>603</v>
+      </c>
+      <c r="H498" s="1">
+        <v>44029</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A499" s="1">
+        <v>44029</v>
+      </c>
+      <c r="G499" t="s">
+        <v>604</v>
+      </c>
+      <c r="H499" s="1">
+        <v>44030</v>
+      </c>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A500" s="1">
+        <v>44030</v>
+      </c>
+      <c r="G500" t="s">
+        <v>605</v>
+      </c>
+      <c r="H500" s="1">
+        <v>44031</v>
+      </c>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A501" s="1">
+        <v>44031</v>
+      </c>
+      <c r="G501" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="502" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A502" s="1">
+        <v>44032</v>
+      </c>
+      <c r="G502" t="s">
+        <v>606</v>
+      </c>
+      <c r="H502" s="1">
+        <v>44033</v>
+      </c>
+    </row>
+    <row r="503" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A503" s="1">
+        <v>44033</v>
+      </c>
+      <c r="G503" t="s">
+        <v>607</v>
+      </c>
+      <c r="H503" s="1">
+        <v>44034</v>
+      </c>
+    </row>
+    <row r="504" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A504" s="1">
+        <v>44034</v>
+      </c>
+      <c r="G504" t="s">
+        <v>608</v>
+      </c>
+      <c r="H504" s="1">
+        <v>44035</v>
+      </c>
+    </row>
+    <row r="505" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A505" s="1">
+        <v>44035</v>
+      </c>
+      <c r="G505" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A506" s="1">
+        <v>44036</v>
+      </c>
+      <c r="G506" t="s">
+        <v>609</v>
+      </c>
+      <c r="H506" s="1">
+        <v>44037</v>
+      </c>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A507" s="1">
+        <v>44037</v>
+      </c>
+      <c r="G507" t="s">
+        <v>639</v>
+      </c>
+      <c r="H507" s="1">
+        <v>44038</v>
+      </c>
+    </row>
+    <row r="508" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A508" s="1">
+        <v>44038</v>
+      </c>
+      <c r="G508" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="509" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A509" s="1">
+        <v>44039</v>
+      </c>
+      <c r="G509" t="s">
+        <v>611</v>
+      </c>
+      <c r="H509" s="1">
+        <v>44040</v>
+      </c>
+    </row>
+    <row r="510" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A510" s="1">
+        <v>44040</v>
+      </c>
+      <c r="G510" t="s">
+        <v>612</v>
+      </c>
+      <c r="H510" s="1">
+        <v>44041</v>
+      </c>
+    </row>
+    <row r="511" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A511" s="1">
+        <v>44041</v>
+      </c>
+      <c r="G511" t="s">
+        <v>613</v>
+      </c>
+      <c r="H511" s="1">
+        <v>44042</v>
+      </c>
+    </row>
+    <row r="512" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A512" s="1">
+        <v>44042</v>
+      </c>
+      <c r="G512" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="513" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A513" s="1">
+        <v>44043</v>
+      </c>
+      <c r="G513" t="s">
+        <v>614</v>
+      </c>
+      <c r="H513" s="1">
+        <v>44044</v>
+      </c>
+    </row>
+    <row r="514" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A514" s="1">
+        <v>44044</v>
+      </c>
+      <c r="G514" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="515" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A515" s="1">
+        <v>44045</v>
+      </c>
+      <c r="G515" t="s">
+        <v>616</v>
+      </c>
+      <c r="H515" s="1">
+        <v>44046</v>
+      </c>
+    </row>
+    <row r="516" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A516" s="1">
+        <v>44046</v>
+      </c>
+      <c r="G516" t="s">
+        <v>617</v>
+      </c>
+      <c r="H516" s="1">
+        <v>44047</v>
+      </c>
+    </row>
+    <row r="517" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A517" s="1">
+        <v>44047</v>
+      </c>
+      <c r="G517" s="1" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="518" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A518" s="1">
+        <v>44048</v>
+      </c>
+      <c r="G518" t="s">
+        <v>642</v>
+      </c>
+      <c r="H518" s="1">
+        <v>44049</v>
+      </c>
+    </row>
+    <row r="519" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A519" s="1">
+        <v>44049</v>
+      </c>
+      <c r="G519" t="s">
+        <v>618</v>
+      </c>
+      <c r="H519" s="1">
+        <v>44050</v>
+      </c>
+    </row>
+    <row r="520" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A520" s="1">
+        <v>44050</v>
+      </c>
+      <c r="G520" t="s">
+        <v>619</v>
+      </c>
+      <c r="H520" s="1">
+        <v>44051</v>
+      </c>
+    </row>
+    <row r="521" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A521" s="1">
+        <v>44051</v>
+      </c>
+      <c r="G521" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="522" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A522" s="1">
+        <v>44052</v>
+      </c>
+      <c r="B522" s="7"/>
+      <c r="F522" s="7"/>
+      <c r="G522" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="H522" s="1">
+        <v>44053</v>
+      </c>
+    </row>
+    <row r="523" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A523" s="1">
+        <v>44053</v>
+      </c>
+      <c r="G523" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H523" s="1">
+        <v>44054</v>
+      </c>
+    </row>
+    <row r="524" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A524" s="1">
+        <v>44054</v>
+      </c>
+      <c r="G524" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="H524" s="1">
+        <v>44055</v>
+      </c>
+    </row>
+    <row r="525" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A525" s="1">
+        <v>44055</v>
+      </c>
+      <c r="G525" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="526" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A526" s="1">
+        <v>44056</v>
+      </c>
+      <c r="G526" t="s">
+        <v>623</v>
+      </c>
+      <c r="H526" s="1">
+        <v>44057</v>
+      </c>
+    </row>
+    <row r="527" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A527" s="1">
+        <v>44057</v>
+      </c>
+      <c r="G527" t="s">
+        <v>645</v>
+      </c>
+      <c r="H527" s="1">
+        <v>44058</v>
+      </c>
+    </row>
+    <row r="528" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A528" s="1">
+        <v>44058</v>
+      </c>
+      <c r="G528" t="s">
+        <v>624</v>
+      </c>
+      <c r="H528" s="1">
+        <v>44059</v>
+      </c>
+    </row>
+    <row r="529" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A529" s="1">
+        <v>44059</v>
+      </c>
+      <c r="G529" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="530" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A530" s="1">
+        <v>44060</v>
+      </c>
+      <c r="G530" t="s">
+        <v>625</v>
+      </c>
+      <c r="H530" s="1">
+        <v>44061</v>
+      </c>
+    </row>
+    <row r="531" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A531" s="1">
+        <v>44061</v>
+      </c>
+      <c r="G531" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="532" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A532" s="1">
+        <v>44062</v>
+      </c>
+      <c r="G532" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="533" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A533" s="1">
+        <v>44063</v>
+      </c>
+      <c r="G533" t="s">
+        <v>626</v>
+      </c>
+      <c r="H533" s="1">
+        <v>44064</v>
+      </c>
+    </row>
+    <row r="534" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A534" s="1">
+        <v>44064</v>
+      </c>
+      <c r="G534" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="535" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A535" s="1">
+        <v>44065</v>
+      </c>
+      <c r="G535" t="s">
+        <v>650</v>
+      </c>
+      <c r="H535" s="1">
+        <v>44066</v>
+      </c>
+    </row>
+    <row r="536" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A536" s="1">
+        <v>44066</v>
+      </c>
+      <c r="G536" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="537" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A537" s="1">
+        <v>44067</v>
+      </c>
+      <c r="G537" t="s">
+        <v>628</v>
+      </c>
+      <c r="H537" s="1">
+        <v>44068</v>
+      </c>
+    </row>
+    <row r="538" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A538" s="1">
+        <v>44068</v>
+      </c>
+      <c r="G538" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="539" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A539" s="1">
+        <v>44069</v>
+      </c>
+      <c r="B539" s="7"/>
+      <c r="F539" s="7"/>
+      <c r="G539" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="H539" s="1">
+        <v>44070</v>
+      </c>
+    </row>
+    <row r="540" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A540" s="1">
+        <v>44070</v>
+      </c>
+      <c r="G540" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H540" s="1">
+        <v>44071</v>
+      </c>
+    </row>
+    <row r="541" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A541" s="1">
+        <v>44071</v>
+      </c>
+      <c r="G541" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="H541" s="1">
+        <v>44071</v>
+      </c>
+    </row>
+    <row r="542" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A542" s="1">
+        <v>44071</v>
+      </c>
+      <c r="G542" s="1" t="s">
+        <v>651</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -13,7 +13,8 @@
   </bookViews>
   <sheets>
     <sheet name="TalkData" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$470</definedName>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="666">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1014,1147 +1015,1203 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>我没有鱼竿，没法钓鱼！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我缺少鱼饵，不能钓鱼！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风带来了你的讯息..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这种枯燥的工作,果然还是需要你的陪伴,今天过来是想干什么呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你发现了奇怪的食材,请一定要告诉我。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个小镇里应该有一个古代遗迹的,但是我怎么也找不到。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里真是一个神奇的地方,你知道吗,在小镇的四周竟然分布着四季。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意,不要走得太远,外面可是有很多可怕的怪物。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好孩子饮食要均衡哦,不论是蔬菜还是肉类都不能挑食。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果有一天你要组成家庭,那么你一定要到这里购买家具啊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果可以的话,希望你能多来找格吉尔玩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的妈妈好厉害的,很多料理都是她自己发明的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呵呵,和你说这么多,你也不懂吧,像你这种小孩子还要多多进行人生历练啊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近师父获得了一些魔法药剂的配方,我们正在收集材料调配。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一定不要吝啬装备哦,即使不用的装备也可以售卖获得金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传说中这个世界曾经被魔族统治,不知道是不是真的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虽然我的道具屋里都是些过时的老东西,但是很用哦。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果遇到了危险,一定要向我求助,我可是时刻准备着。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的女儿可是我的心肝宝贝,你可不要想轻易就将他们欺骗到手。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法=百分之九九的天赋+百分之一的努力,所以你似乎无法成为魔法师了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经过我的研究,我推断在远古时代有一个伟大的文明,但是不知为何消失了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我其实一直在锻炼,因为我知道有一天命运会安排我成为救世主。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>见到你,多莉丝真高兴,真像能和你一样到处去玩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可爱的小家伙们,今天又来问候我啊,真的谢谢你们了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我一定要成为将军那样强大的军人,为此我得坚持锻炼。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
+  </si>
+  <si>
+    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在那场战争中,本来王国军处于劣势,但是凭着我的活跃表现,才逆转获得胜利。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你喜欢吃什么料理呢？奥蒂莉亚喜欢烤海鲜噢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真高兴你能来找我玩,明天你还会来吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在这个宁静的小镇,我找到了久违的安心,我想我还会再住一阵子吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>究竟怎样才能和是否一样优秀呢？这真让我困扰。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我一定要把布拉德利培养成一个优秀的男人,这就是我生活的意义。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我曾经走过大山和大海,追寻财富的脚步永不停息,你能理解吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作料理一定要有想象力,只有这样才能将美味融入其中。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>像我这样的天才果然不应该困在这种小店里吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没必要活得太累,偶尔停下脚步欣赏一下自然也是很好的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果不是那件事,王国的军队的总司令官非我莫属了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不管下雨还是晴天,我觉得每一天的天气都很好,你觉得呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实班尼迪克先生不是你看到的那样,他也有温柔的一面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天都要记得喂养动物啊,不要让他们挨饿。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和你说一会话,真的很轻松,可是我还有工作,不能在和你再聊了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>师父是个大美人吧,不过你可不要打她的主意哦,师父可不是你能驾驭的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你学会了制作的话,你就可以自己制作装备了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在这个世界上除了人类还有一些奇怪的种族,可是为什么是人类占据了大陆呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你听到了什么？可不要到处乱说啊,这都是我们年轻时发生的事。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实一个人站岗也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>想不到还会有年轻人来找我这个老头子聊天,真令人高兴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实水里也有很多有意思的地方,如果你能在水里生存的话……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欢迎光临，有什么需要的吗</t>
+  </si>
+  <si>
+    <t>如果每天都能下雨就好了，这样就不需要为植物浇水了。</t>
+  </si>
+  <si>
+    <t>种植是很有学问的,一定要在合适的季节种植作物哦,\n否则作物的生长时间会变的很长。</t>
+  </si>
+  <si>
+    <t>我要好好帮助玛德琳奶奶。</t>
+  </si>
+  <si>
+    <t>你好呀，小家伙，需要我的帮助吗？</t>
+  </si>
+  <si>
+    <t>帕特里克那个老固执在干什么呢？..明明过去那么久了…</t>
+  </si>
+  <si>
+    <t>布莱兹是个好孩子，如果他的父母还在的话…</t>
+  </si>
+  <si>
+    <t>年轻真好呀，要好好享受生活哟..</t>
+  </si>
+  <si>
+    <t>有烦心事的话，来和奶奶说，我会帮助你的。</t>
+  </si>
+  <si>
+    <t>做一个好农夫也不容易呢，要加油哦！</t>
+  </si>
+  <si>
+    <t>你好，有什么事吗？</t>
+  </si>
+  <si>
+    <t>格吉尔总是想着去冒险，我还是希望他能在小镇安稳的生活。</t>
+  </si>
+  <si>
+    <t>平静的生活就是最大的幸福，你觉得的呢？</t>
+  </si>
+  <si>
+    <t>我很喜欢和动物们相处，它们既单纯又可爱。</t>
+  </si>
+  <si>
+    <t>准备干些什么？</t>
+  </si>
+  <si>
+    <t>相比温顺的动物，我更喜欢能和我一起战斗的伙伴。</t>
+  </si>
+  <si>
+    <t>你如果要去冒险的话，一定要带上我呀。</t>
+  </si>
+  <si>
+    <t>有的人天生就是主角，你看我像不像，哈哈。</t>
+  </si>
+  <si>
+    <t>风儿带来了你的讯息，你有什么想要倾诉？</t>
+  </si>
+  <si>
+    <t>人的生命如此短暂，你是否已经准备好接受自己的命运…</t>
+  </si>
+  <si>
+    <t>高山之后是大海，大海之边是高山，不知山海相连何处是尽头…</t>
+  </si>
+  <si>
+    <t>人无法跨过两次同一条河流，那么河里的鱼是否相同…</t>
+  </si>
+  <si>
+    <t>美丽的人啊，偎依在河岸，我只敢远远欣赏不敢靠近，害怕，你那美丽的面庞将我的眼睛灼伤…</t>
+  </si>
+  <si>
+    <t>愿主保佑你，想要祈祷什么？</t>
+  </si>
+  <si>
+    <t>一切存在都源自内心，如果希望世界更好，那么就让自己的内心更纯净吧。</t>
+  </si>
+  <si>
+    <t>现在的年轻人都不知道敬畏上帝了，平时都不来礼拜了。</t>
+  </si>
+  <si>
+    <t>愿主的荣光照耀在你身上。</t>
+  </si>
+  <si>
+    <t>希望每一个远行的人都能平安的归来…</t>
+  </si>
+  <si>
+    <t>命运还是要把握在自己手里，想知道什么？</t>
+  </si>
+  <si>
+    <t>我知道很多，但我不能都告诉你。</t>
+  </si>
+  <si>
+    <t>从远方而来的人啊，你的故乡在何处，你可知你的真名，我在此等候你的倾诉..</t>
+  </si>
+  <si>
+    <t>年轻人，探索精神固然可贵，但不要盲目冒险呐。</t>
+  </si>
+  <si>
+    <t>即使知道了命运，依然能够笑着面对的人才是真正的勇士。</t>
+  </si>
+  <si>
+    <t>你好呀，想要点什么吗？</t>
+  </si>
+  <si>
+    <t>尽管每天都很忙，但我们都很快乐。</t>
+  </si>
+  <si>
+    <t>美食和美景都不能错过。</t>
+  </si>
+  <si>
+    <t>你笑起来真好看，多笑笑嘛。</t>
+  </si>
+  <si>
+    <t>平时多出来和我们一起玩吧，不要老呆在家里嘛。</t>
+  </si>
+  <si>
+    <t>你好，今天也很精神呀，需要我做什么吗？</t>
+  </si>
+  <si>
+    <t>班尼迪克先生是个好人。</t>
+  </si>
+  <si>
+    <t>一切安好，也希望你也能开开心心。</t>
+  </si>
+  <si>
+    <t>有什么可以为你服务的吗？</t>
+  </si>
+  <si>
+    <t>今天也是平静而美好的。</t>
+  </si>
+  <si>
+    <t>看着环境变得干净卫生，我会很舒心。</t>
+  </si>
+  <si>
+    <t>是你啊，有事的话，请尽管吩咐。</t>
+  </si>
+  <si>
+    <t>如果能发挥我的特长的话就太好了。</t>
+  </si>
+  <si>
+    <t>这个小镇能如此安宁是很多人付出的结果。</t>
+  </si>
+  <si>
+    <t>守护家人是我的职责。</t>
+  </si>
+  <si>
+    <t>其实回到这个养育我的小镇，我很开心。</t>
+  </si>
+  <si>
+    <t>哟，找我有事？</t>
+  </si>
+  <si>
+    <t>真是无聊，这样的日子何时才能结束。</t>
+  </si>
+  <si>
+    <t>看着别人四处旅行，我却只能在这里，真羡慕啊。</t>
+  </si>
+  <si>
+    <t>如果以后你要出去旅行的话，希望我们可以同行。</t>
+  </si>
+  <si>
+    <t>我已经准备了很久行囊，就是没有机会出发。</t>
+  </si>
+  <si>
+    <t>你是来找我的吗？不知道能为你做些什么？</t>
+  </si>
+  <si>
+    <t>我有一个感觉，这个小镇是我的归宿。</t>
+  </si>
+  <si>
+    <t>繁华终归会褪去，回归平淡才是真正的人生。</t>
+  </si>
+  <si>
+    <t>虽然我的魔力还不够，但我会努力的，你有什么需要我的？</t>
+  </si>
+  <si>
+    <t>究竟怎样才能和师父一样优秀呢？这真让我困扰。</t>
+  </si>
+  <si>
+    <t>我的梦想是成为一个大魔导师。</t>
+  </si>
+  <si>
+    <t>是遇到什么疑难了吗？</t>
+  </si>
+  <si>
+    <t>别看我单身一人，年轻时候的我也是很受欢迎的。</t>
+  </si>
+  <si>
+    <t>看见你，就想让我想到了年轻时候的我，真怀念呐。</t>
+  </si>
+  <si>
+    <t>我不会拒绝对弱者的怜悯，所以你有什么事？</t>
+  </si>
+  <si>
+    <t>这个小镇虽然不是很繁华，但我却很喜欢。</t>
+  </si>
+  <si>
+    <t>你想来找我学习贵族礼仪吗?</t>
+  </si>
+  <si>
+    <t>你愿意来找我，我心里还是有一点高兴的。</t>
+  </si>
+  <si>
+    <t>可不要误会，这只是基本的贵族礼仪。</t>
+  </si>
+  <si>
+    <t>你想要了解魔法的力量吗？</t>
+  </si>
+  <si>
+    <t>魔法的力量远超你的想象，</t>
+  </si>
+  <si>
+    <t>嗨，有啥事？</t>
+  </si>
+  <si>
+    <t>要想获得丰厚的渔获，必须要打理好网具。</t>
+  </si>
+  <si>
+    <t>这个小镇靠近大海，可以时常吃到一些海鲜菜肴。</t>
+  </si>
+  <si>
+    <t>据说大海的深处有美人鱼，不知道是不是真的。</t>
+  </si>
+  <si>
+    <t>如果你有时间的话，学习一下钓鱼吧，你会很有收获。</t>
+  </si>
+  <si>
+    <t>你找我是有什么事？</t>
+  </si>
+  <si>
+    <t>这个镇子虽小，却拥有完善的海港，常有舰船航行往来于各大陆之间。</t>
+  </si>
+  <si>
+    <t>经历了长时间的海上漂泊，我需要在岸上好好休息一下。</t>
+  </si>
+  <si>
+    <t>大海里有很多财富，也有很多风险。</t>
+  </si>
+  <si>
+    <t>你如果想去海那边，可以乘坐我的船。</t>
+  </si>
+  <si>
+    <t>找我吗？我也可以为你做事吗？</t>
+  </si>
+  <si>
+    <t>乘船出海游遍世界一直是我的愿望。</t>
+  </si>
+  <si>
+    <t>虽然海上的生活令人神往，但在这个小镇也还不错。</t>
+  </si>
+  <si>
+    <t>大家都很努力啊，我也不能懈怠。</t>
+  </si>
+  <si>
+    <t>如果我也有自己的船就好了。</t>
+  </si>
+  <si>
+    <t>静待你的委托</t>
+  </si>
+  <si>
+    <t>别人的秘密，何必要探究到底呢，只要不危害大家就好了。</t>
+  </si>
+  <si>
+    <t>你好，你想知道什么吗？</t>
+  </si>
+  <si>
+    <t>如果四季可以同时存在，会发生什么呢…</t>
+  </si>
+  <si>
+    <t>需要我的帮忙吗？</t>
+  </si>
+  <si>
+    <t>虽然我对神依然很崇敬，但我还是想干些其他的事情。</t>
+  </si>
+  <si>
+    <t>在战斗中祈求上帝是没有用了，我们只能依靠自己。</t>
+  </si>
+  <si>
+    <t>不知道上帝能不能听到我的心声，让我早日得偿所愿。</t>
+  </si>
+  <si>
+    <t>无论信不信上帝，都要坚守爱与和平。</t>
+  </si>
+  <si>
+    <t>我可以为你做些什么？</t>
+  </si>
+  <si>
+    <t>其实一个人巡逻也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
+  </si>
+  <si>
+    <t>很高兴能为你服务。</t>
+  </si>
+  <si>
+    <t>守护小姐是我的职责。</t>
+  </si>
+  <si>
+    <t>在这个镇子里，我经常会想起关于老主人的事。</t>
+  </si>
+  <si>
+    <t>回想过去，好像刚刚发生在昨天，那时小姐还是个孩子…</t>
+  </si>
+  <si>
+    <t>如果有更多的人陪伴小姐，小姐应该会更开心吧</t>
+  </si>
+  <si>
+    <t>如果有什么事情，我会尽力而为。</t>
+  </si>
+  <si>
+    <t>一个料理如果缺少调味料，就会寡淡无味，不要忘记购买呀。</t>
+  </si>
+  <si>
+    <t>好的装备可以大大促进劳动效率，我需要做什么？</t>
+  </si>
+  <si>
+    <t>我一定要把布拉德利培养成一个优秀的人,这就是我生活的意义。</t>
+  </si>
+  <si>
+    <t>布拉德利再长大一些的话，我会让他自己选择自己的道路。</t>
+  </si>
+  <si>
+    <t>你好，需要什么服务吗？</t>
+  </si>
+  <si>
+    <t>姐姐应该有更广阔的前景的，现在却被困住这个小镇…</t>
+  </si>
+  <si>
+    <t>如果我能更强大一些的话，姐姐就可以去追求自己的梦想了。</t>
+  </si>
+  <si>
+    <t>你可以帮助我，鼓励我一直坚强吗？</t>
+  </si>
+  <si>
+    <t>如果你愿意的话，可以随时来找我和我的姐姐。</t>
+  </si>
+  <si>
+    <t>有什么搞不定的事情？</t>
+  </si>
+  <si>
+    <t>注意,不要走得太远,外面可是有很多怪物。</t>
+  </si>
+  <si>
+    <t>听说你在征讨小镇周边的怪物，做的不错。</t>
+  </si>
+  <si>
+    <t>招待不周了，有什么事情吗？</t>
+  </si>
+  <si>
+    <t>有妹妹和妈妈陪着我，我觉得很幸福。</t>
+  </si>
+  <si>
+    <t>如果爸爸还在的话…</t>
+  </si>
+  <si>
+    <t>我要努力支撑我的家，可以为我加油吗？</t>
+  </si>
+  <si>
+    <t>可有什么事情需要我为你而做的？</t>
+  </si>
+  <si>
+    <t>纺织可是化腐朽为神奇的技术。</t>
+  </si>
+  <si>
+    <t>如果你想学习纺织技术的话，我可以教你。</t>
+  </si>
+  <si>
+    <t>我有时也会为缺少传承而烦恼呢。</t>
+  </si>
+  <si>
+    <t>相比能赚到钱，我更希望有人可以将我的技术传承下去。</t>
+  </si>
+  <si>
+    <t>我拥有的比你知道的还多，你有什么需要的吗？</t>
+  </si>
+  <si>
+    <t>固守成见是不行的，只有变革才能带来新的机遇。</t>
+  </si>
+  <si>
+    <t>放心吧，你的外公只是去了他想去的地方。</t>
+  </si>
+  <si>
+    <t>好好在这里生活吧，你的外公也会很欣慰的。</t>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+  </si>
+  <si>
+    <t>格吉尔</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+  </si>
+  <si>
+    <t>别墅二楼</t>
+  </si>
+  <si>
+    <t>酒馆卧室</t>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>教堂</t>
+  </si>
+  <si>
+    <t>村公所卧室</t>
+  </si>
+  <si>
+    <t>后山</t>
+  </si>
+  <si>
+    <t>俱乐部阁楼</t>
+  </si>
+  <si>
+    <t>客栈二楼</t>
+  </si>
+  <si>
+    <t>武器店</t>
+  </si>
+  <si>
+    <t>船坞</t>
+  </si>
+  <si>
+    <t>我的农场</t>
+  </si>
+  <si>
+    <t>村公所大厅</t>
+  </si>
+  <si>
+    <t>工坊</t>
+  </si>
+  <si>
+    <t>畜牧店</t>
+  </si>
+  <si>
+    <t>俱乐部</t>
+  </si>
+  <si>
+    <t>塔楼顶部</t>
+  </si>
+  <si>
+    <t>家具店偏室</t>
+  </si>
+  <si>
+    <t>山坡</t>
+  </si>
+  <si>
+    <t>水车房内部</t>
+  </si>
+  <si>
+    <t>小木屋</t>
+  </si>
+  <si>
+    <t>家具店</t>
+  </si>
+  <si>
+    <t>中央广场</t>
+  </si>
+  <si>
+    <t>纺织店</t>
+  </si>
+  <si>
+    <t>商店街</t>
+  </si>
+  <si>
+    <t>塔楼</t>
+  </si>
+  <si>
+    <t>治安室</t>
+  </si>
+  <si>
+    <t>占卜屋</t>
+  </si>
+  <si>
+    <t>帐篷内部</t>
+  </si>
+  <si>
+    <t>风车内部</t>
+  </si>
+  <si>
+    <t>客栈一楼</t>
+  </si>
+  <si>
+    <t>码头</t>
+  </si>
+  <si>
+    <t>鱼摊内部</t>
+  </si>
+  <si>
+    <t>船坞二层</t>
+  </si>
+  <si>
+    <t>住宅区</t>
+  </si>
+  <si>
+    <t>别墅大厅</t>
+  </si>
+  <si>
+    <t>教堂二楼</t>
+  </si>
+  <si>
+    <t>酒馆</t>
+  </si>
+  <si>
+    <t>村公所宴会厅</t>
+  </si>
+  <si>
+    <t>科学研究室</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>城门</t>
+  </si>
+  <si>
+    <t>武器店二楼</t>
+  </si>
+  <si>
+    <t>许可清单你可以随时去看看。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那么，现在我应该做些什么呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从最简单的售卖开始吧，看到前面的柜台了么,将东西放到上面就行了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对了，有些商品只能放在特定柜台上，你可以仔细观察一下。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好，现在去把商店的招牌换成营业吧，只有营业状态时才会有客人上门。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做的不错，你可以再熟悉一下售卖商品，我在外面等你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>植物店里拥有各种植物种子,来跟我去熟悉熟悉吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这就是新来小镇的孩子吧，欢迎你哟，想来点什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买好了种子了，我们回农场种植吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>植物生长需要几天时间,在此期间,不如去野外探险一下,也许会获得想不到的收获哦。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看来你已经掌握了售卖物品的方法了,如此一来,你的种植许可也开放了,那么现在去买一些种子回来吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等一下，我这里有一些种植工具，送给你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一步,先将农具从背包里拿出来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在走到农田上，使用锄头将田地锄松吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好,就是这样,现在选择种子进行播种吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>别急,还差最后一步呢,种下的植物需要浇水,现在去河边打水回来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢，我会好好使用的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里就是农场，以后就归你管理了,现在准备种植吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前面就是春之山脉的入口，今天就让我这个老头子陪你闯一下吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在前进走到光圈中，开始今天的探索。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打起精神来，现在前进吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我没有镰刀，没办法收割</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年轻人，这小镇的清晨不错吧？</t>
+  </si>
+  <si>
+    <t>嗯，空气很清新。</t>
+  </si>
+  <si>
+    <t>我正考虑给店里进些新货，你有啥建议？</t>
+  </si>
+  <si>
+    <t>你看着挺精神，昨晚休息得好？</t>
+  </si>
+  <si>
+    <t>还可以。您这店每天很早就开门吗？</t>
+  </si>
+  <si>
+    <t>对，习惯了。你要是有空可以来帮忙整理下。</t>
+  </si>
+  <si>
+    <t>你初来乍到，有没有去小镇周边转转？</t>
+  </si>
+  <si>
+    <t>还没有。周边有什么好玩的地方吗？</t>
+  </si>
+  <si>
+    <t>有个小湖泊，景色很美。你可以去看看。</t>
+  </si>
+  <si>
+    <t>我店里新到了一些家具，你想看看吗？</t>
+  </si>
+  <si>
+    <t>现在没时间。都是些什么风格的家具？</t>
+  </si>
+  <si>
+    <t>古典和简约的都有。你有空了来品鉴下。</t>
+  </si>
+  <si>
+    <t>你在镇上有没有交到新朋友？</t>
+  </si>
+  <si>
+    <t>认识了几个。交朋友对在这生活很重要吗？</t>
+  </si>
+  <si>
+    <t>当然，朋友多了路好走。你可以多参加些活动。</t>
+  </si>
+  <si>
+    <t>我最近在研究新的家具摆放方式，你有啥想法？</t>
+  </si>
+  <si>
+    <t>我不太懂。是不是可以根据功能分区摆放？</t>
+  </si>
+  <si>
+    <t>有点道理。你要是有了新灵感随时告诉我。</t>
+  </si>
+  <si>
+    <t>你觉得小镇的居民们对家具的需求大吗？</t>
+  </si>
+  <si>
+    <t>不太清楚。应该会需要一些实用的家具吧。</t>
+  </si>
+  <si>
+    <t>我也这么认为。你帮我留意下大家的喜好。</t>
+  </si>
+  <si>
+    <t>早啊，小家伙。我正想改进家具的细节，你觉得从哪入手？</t>
+  </si>
+  <si>
+    <t>可以从打磨工艺上试试。</t>
+  </si>
+  <si>
+    <t>嗨，你看这小镇的建筑风格，对家具设计有启发吗？</t>
+  </si>
+  <si>
+    <t>我觉得可以借鉴一些线条和色彩搭配。</t>
+  </si>
+  <si>
+    <t>很有见地。你能帮我画些草图吗？</t>
+  </si>
+  <si>
+    <t>我打算用旧木材打造复古家具，你觉得可行吗？</t>
+  </si>
+  <si>
+    <t>应该可以，会很有韵味。</t>
+  </si>
+  <si>
+    <t>对。你知道哪里能找到更多旧木材吗？</t>
+  </si>
+  <si>
+    <t>你在镇上参加过手工制作的活动吗？</t>
+  </si>
+  <si>
+    <t>可以学习一些新技巧。你有兴趣的话我带你去。</t>
+  </si>
+  <si>
+    <t>我想在家具上镶嵌一些特色石头，你有推荐吗？</t>
+  </si>
+  <si>
+    <t>像玛瑙或者水晶石应该不错。</t>
+  </si>
+  <si>
+    <t>有道理。你能帮我找些性价比高的吗？</t>
+  </si>
+  <si>
+    <t>你觉得家具的舒适度和美观度怎么平衡？</t>
+  </si>
+  <si>
+    <t>先保证舒适度，再用装饰提升美观度。</t>
+  </si>
+  <si>
+    <t>我要举办一个小型家具展览，你能帮忙宣传吗？</t>
+  </si>
+  <si>
+    <t>我可以试试。需要我做什么？</t>
+  </si>
+  <si>
+    <t>我觉得淡色系比较清新。</t>
+  </si>
+  <si>
+    <t>嗯，值得考虑。你能帮我选些样板吗？</t>
+  </si>
+  <si>
+    <t>哟，早哇。我想去河边钓鱼，顺便找找灵感，一起不？</t>
+  </si>
+  <si>
+    <t>我还有事。你钓鱼能找到什么家具灵感？</t>
+  </si>
+  <si>
+    <t>比如鱼的形状和纹理可以用在装饰上。</t>
+  </si>
+  <si>
+    <t>嗨，我打算用兽皮做些特殊的家具配饰，你见过吗？</t>
+  </si>
+  <si>
+    <t>只要处理好就没问题。你有渠道获取吗？</t>
+  </si>
+  <si>
+    <t>我想在家具里安装音乐盒，一打开就有音乐，怎样？</t>
+  </si>
+  <si>
+    <t>我最近得到一些散发香味的木材，做什么家具好？</t>
+  </si>
+  <si>
+    <t>可以做个香薰柜，存放香料。</t>
+  </si>
+  <si>
+    <t>我想打造一款能折叠成小物件的家具，你觉得可能吗？</t>
+  </si>
+  <si>
+    <t>有可能，像折叠椅就很实用。</t>
+  </si>
+  <si>
+    <t>嘿，我设计了一款带有魔法储物空间的家具，神奇吧？</t>
+  </si>
+  <si>
+    <t>哇，太神奇了！怎么实现储物空间的魔法呢？</t>
+  </si>
+  <si>
+    <t>用魔法水晶驱动。你在镇上见过魔法水晶吗？</t>
+  </si>
+  <si>
+    <t>我不太清楚。我先去吃个早饭，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我今天有事。不好意思，我得走了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的。我突然想起有事，先走一步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的。我先去了，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我有点忙，先撤了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太清楚。我去打听下。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有。这类活动和家具制作有关吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我找找看。不好意思，我得赶紧走了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让我想想再告诉你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我在研究新的涂料，你对颜色有偏好吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不太会。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挺有趣。我忙完来找你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没见过呢。这样合适吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有。要不去问问别人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">好有创意！ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你在镇上逛过那些古老的小巷吗？可以从巷子里的图案找设计灵感。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太清楚。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你知道怎么处理木材香味吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没见过。我去探索下。我先去了，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>咯咯..咯咯..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我没有鱼竿，没法钓鱼！</t>
+    <t>叽叽..叽叽..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我缺少鱼饵，不能钓鱼！</t>
+    <t>嘎嘎..嘎嘎..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>风带来了你的讯息..</t>
+    <t>呷呷..呷呷..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这种枯燥的工作,果然还是需要你的陪伴,今天过来是想干什么呢？</t>
+    <t>噗呼..噗呼..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果你发现了奇怪的食材,请一定要告诉我。</t>
+    <t>咩咩..咩咩..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这个小镇里应该有一个古代遗迹的,但是我怎么也找不到。</t>
+    <t>哼哼..哼哼..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这里真是一个神奇的地方,你知道吗,在小镇的四周竟然分布着四季。</t>
+    <t>吱吱..吱吱..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>注意,不要走得太远,外面可是有很多可怕的怪物。</t>
+    <t>嘶嘶..嘶嘶..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>好孩子饮食要均衡哦,不论是蔬菜还是肉类都不能挑食。</t>
+    <t>噗呼..噗呼..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果有一天你要组成家庭,那么你一定要到这里购买家具啊。</t>
+    <t>咕噜..咕噜..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>如果可以的话,希望你能多来找格吉尔玩。</t>
+    <t>呦呦..呦呦..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我的妈妈好厉害的,很多料理都是她自己发明的。</t>
+    <t>哞～哞～</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>呵呵,和你说这么多,你也不懂吧,像你这种小孩子还要多多进行人生历练啊。</t>
+    <t>呜～呜～</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>最近师父获得了一些魔法药剂的配方,我们正在收集材料调配。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一定不要吝啬装备哦,即使不用的装备也可以售卖获得金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>传说中这个世界曾经被魔族统治,不知道是不是真的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虽然我的道具屋里都是些过时的老东西,但是很用哦。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果遇到了危险,一定要向我求助,我可是时刻准备着。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我的女儿可是我的心肝宝贝,你可不要想轻易就将他们欺骗到手。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法=百分之九九的天赋+百分之一的努力,所以你似乎无法成为魔法师了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经过我的研究,我推断在远古时代有一个伟大的文明,但是不知为何消失了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我其实一直在锻炼,因为我知道有一天命运会安排我成为救世主。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>见到你,多莉丝真高兴,真像能和你一样到处去玩。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可爱的小家伙们,今天又来问候我啊,真的谢谢你们了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我一定要成为将军那样强大的军人,为此我得坚持锻炼。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
-  </si>
-  <si>
-    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在那场战争中,本来王国军处于劣势,但是凭着我的活跃表现,才逆转获得胜利。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你喜欢吃什么料理呢？奥蒂莉亚喜欢烤海鲜噢。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>真高兴你能来找我玩,明天你还会来吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在这个宁静的小镇,我找到了久违的安心,我想我还会再住一阵子吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>究竟怎样才能和是否一样优秀呢？这真让我困扰。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我一定要把布拉德利培养成一个优秀的男人,这就是我生活的意义。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我曾经走过大山和大海,追寻财富的脚步永不停息,你能理解吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>制作料理一定要有想象力,只有这样才能将美味融入其中。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>像我这样的天才果然不应该困在这种小店里吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没必要活得太累,偶尔停下脚步欣赏一下自然也是很好的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果不是那件事,王国的军队的总司令官非我莫属了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不管下雨还是晴天,我觉得每一天的天气都很好,你觉得呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其实班尼迪克先生不是你看到的那样,他也有温柔的一面。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每天都要记得喂养动物啊,不要让他们挨饿。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>和你说一会话,真的很轻松,可是我还有工作,不能在和你再聊了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>师父是个大美人吧,不过你可不要打她的主意哦,师父可不是你能驾驭的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果你学会了制作的话,你就可以自己制作装备了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在这个世界上除了人类还有一些奇怪的种族,可是为什么是人类占据了大陆呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你听到了什么？可不要到处乱说啊,这都是我们年轻时发生的事。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其实一个人站岗也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>想不到还会有年轻人来找我这个老头子聊天,真令人高兴。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其实水里也有很多有意思的地方,如果你能在水里生存的话……</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>欢迎光临，有什么需要的吗</t>
-  </si>
-  <si>
-    <t>如果每天都能下雨就好了，这样就不需要为植物浇水了。</t>
-  </si>
-  <si>
-    <t>种植是很有学问的,一定要在合适的季节种植作物哦,\n否则作物的生长时间会变的很长。</t>
-  </si>
-  <si>
-    <t>我要好好帮助玛德琳奶奶。</t>
-  </si>
-  <si>
-    <t>你好呀，小家伙，需要我的帮助吗？</t>
-  </si>
-  <si>
-    <t>帕特里克那个老固执在干什么呢？..明明过去那么久了…</t>
-  </si>
-  <si>
-    <t>布莱兹是个好孩子，如果他的父母还在的话…</t>
-  </si>
-  <si>
-    <t>年轻真好呀，要好好享受生活哟..</t>
-  </si>
-  <si>
-    <t>有烦心事的话，来和奶奶说，我会帮助你的。</t>
-  </si>
-  <si>
-    <t>做一个好农夫也不容易呢，要加油哦！</t>
-  </si>
-  <si>
-    <t>你好，有什么事吗？</t>
-  </si>
-  <si>
-    <t>格吉尔总是想着去冒险，我还是希望他能在小镇安稳的生活。</t>
-  </si>
-  <si>
-    <t>平静的生活就是最大的幸福，你觉得的呢？</t>
-  </si>
-  <si>
-    <t>我很喜欢和动物们相处，它们既单纯又可爱。</t>
-  </si>
-  <si>
-    <t>准备干些什么？</t>
-  </si>
-  <si>
-    <t>相比温顺的动物，我更喜欢能和我一起战斗的伙伴。</t>
-  </si>
-  <si>
-    <t>你如果要去冒险的话，一定要带上我呀。</t>
-  </si>
-  <si>
-    <t>有的人天生就是主角，你看我像不像，哈哈。</t>
-  </si>
-  <si>
-    <t>风儿带来了你的讯息，你有什么想要倾诉？</t>
-  </si>
-  <si>
-    <t>人的生命如此短暂，你是否已经准备好接受自己的命运…</t>
-  </si>
-  <si>
-    <t>高山之后是大海，大海之边是高山，不知山海相连何处是尽头…</t>
-  </si>
-  <si>
-    <t>人无法跨过两次同一条河流，那么河里的鱼是否相同…</t>
-  </si>
-  <si>
-    <t>美丽的人啊，偎依在河岸，我只敢远远欣赏不敢靠近，害怕，你那美丽的面庞将我的眼睛灼伤…</t>
-  </si>
-  <si>
-    <t>愿主保佑你，想要祈祷什么？</t>
-  </si>
-  <si>
-    <t>一切存在都源自内心，如果希望世界更好，那么就让自己的内心更纯净吧。</t>
-  </si>
-  <si>
-    <t>现在的年轻人都不知道敬畏上帝了，平时都不来礼拜了。</t>
-  </si>
-  <si>
-    <t>愿主的荣光照耀在你身上。</t>
-  </si>
-  <si>
-    <t>希望每一个远行的人都能平安的归来…</t>
-  </si>
-  <si>
-    <t>命运还是要把握在自己手里，想知道什么？</t>
-  </si>
-  <si>
-    <t>我知道很多，但我不能都告诉你。</t>
-  </si>
-  <si>
-    <t>从远方而来的人啊，你的故乡在何处，你可知你的真名，我在此等候你的倾诉..</t>
-  </si>
-  <si>
-    <t>年轻人，探索精神固然可贵，但不要盲目冒险呐。</t>
-  </si>
-  <si>
-    <t>即使知道了命运，依然能够笑着面对的人才是真正的勇士。</t>
-  </si>
-  <si>
-    <t>你好呀，想要点什么吗？</t>
-  </si>
-  <si>
-    <t>尽管每天都很忙，但我们都很快乐。</t>
-  </si>
-  <si>
-    <t>美食和美景都不能错过。</t>
-  </si>
-  <si>
-    <t>你笑起来真好看，多笑笑嘛。</t>
-  </si>
-  <si>
-    <t>平时多出来和我们一起玩吧，不要老呆在家里嘛。</t>
-  </si>
-  <si>
-    <t>你好，今天也很精神呀，需要我做什么吗？</t>
-  </si>
-  <si>
-    <t>班尼迪克先生是个好人。</t>
-  </si>
-  <si>
-    <t>一切安好，也希望你也能开开心心。</t>
-  </si>
-  <si>
-    <t>有什么可以为你服务的吗？</t>
-  </si>
-  <si>
-    <t>今天也是平静而美好的。</t>
-  </si>
-  <si>
-    <t>看着环境变得干净卫生，我会很舒心。</t>
-  </si>
-  <si>
-    <t>是你啊，有事的话，请尽管吩咐。</t>
-  </si>
-  <si>
-    <t>如果能发挥我的特长的话就太好了。</t>
-  </si>
-  <si>
-    <t>这个小镇能如此安宁是很多人付出的结果。</t>
-  </si>
-  <si>
-    <t>守护家人是我的职责。</t>
-  </si>
-  <si>
-    <t>其实回到这个养育我的小镇，我很开心。</t>
-  </si>
-  <si>
-    <t>哟，找我有事？</t>
-  </si>
-  <si>
-    <t>真是无聊，这样的日子何时才能结束。</t>
-  </si>
-  <si>
-    <t>看着别人四处旅行，我却只能在这里，真羡慕啊。</t>
-  </si>
-  <si>
-    <t>如果以后你要出去旅行的话，希望我们可以同行。</t>
-  </si>
-  <si>
-    <t>我已经准备了很久行囊，就是没有机会出发。</t>
-  </si>
-  <si>
-    <t>你是来找我的吗？不知道能为你做些什么？</t>
-  </si>
-  <si>
-    <t>我有一个感觉，这个小镇是我的归宿。</t>
-  </si>
-  <si>
-    <t>繁华终归会褪去，回归平淡才是真正的人生。</t>
-  </si>
-  <si>
-    <t>虽然我的魔力还不够，但我会努力的，你有什么需要我的？</t>
-  </si>
-  <si>
-    <t>究竟怎样才能和师父一样优秀呢？这真让我困扰。</t>
-  </si>
-  <si>
-    <t>我的梦想是成为一个大魔导师。</t>
-  </si>
-  <si>
-    <t>是遇到什么疑难了吗？</t>
-  </si>
-  <si>
-    <t>别看我单身一人，年轻时候的我也是很受欢迎的。</t>
-  </si>
-  <si>
-    <t>看见你，就想让我想到了年轻时候的我，真怀念呐。</t>
-  </si>
-  <si>
-    <t>我不会拒绝对弱者的怜悯，所以你有什么事？</t>
-  </si>
-  <si>
-    <t>这个小镇虽然不是很繁华，但我却很喜欢。</t>
-  </si>
-  <si>
-    <t>你想来找我学习贵族礼仪吗?</t>
-  </si>
-  <si>
-    <t>你愿意来找我，我心里还是有一点高兴的。</t>
-  </si>
-  <si>
-    <t>可不要误会，这只是基本的贵族礼仪。</t>
-  </si>
-  <si>
-    <t>你想要了解魔法的力量吗？</t>
-  </si>
-  <si>
-    <t>魔法的力量远超你的想象，</t>
-  </si>
-  <si>
-    <t>嗨，有啥事？</t>
-  </si>
-  <si>
-    <t>要想获得丰厚的渔获，必须要打理好网具。</t>
-  </si>
-  <si>
-    <t>这个小镇靠近大海，可以时常吃到一些海鲜菜肴。</t>
-  </si>
-  <si>
-    <t>据说大海的深处有美人鱼，不知道是不是真的。</t>
-  </si>
-  <si>
-    <t>如果你有时间的话，学习一下钓鱼吧，你会很有收获。</t>
-  </si>
-  <si>
-    <t>你找我是有什么事？</t>
-  </si>
-  <si>
-    <t>这个镇子虽小，却拥有完善的海港，常有舰船航行往来于各大陆之间。</t>
-  </si>
-  <si>
-    <t>经历了长时间的海上漂泊，我需要在岸上好好休息一下。</t>
-  </si>
-  <si>
-    <t>大海里有很多财富，也有很多风险。</t>
-  </si>
-  <si>
-    <t>你如果想去海那边，可以乘坐我的船。</t>
-  </si>
-  <si>
-    <t>找我吗？我也可以为你做事吗？</t>
-  </si>
-  <si>
-    <t>乘船出海游遍世界一直是我的愿望。</t>
-  </si>
-  <si>
-    <t>虽然海上的生活令人神往，但在这个小镇也还不错。</t>
-  </si>
-  <si>
-    <t>大家都很努力啊，我也不能懈怠。</t>
-  </si>
-  <si>
-    <t>如果我也有自己的船就好了。</t>
-  </si>
-  <si>
-    <t>静待你的委托</t>
-  </si>
-  <si>
-    <t>别人的秘密，何必要探究到底呢，只要不危害大家就好了。</t>
-  </si>
-  <si>
-    <t>你好，你想知道什么吗？</t>
-  </si>
-  <si>
-    <t>如果四季可以同时存在，会发生什么呢…</t>
-  </si>
-  <si>
-    <t>需要我的帮忙吗？</t>
-  </si>
-  <si>
-    <t>虽然我对神依然很崇敬，但我还是想干些其他的事情。</t>
-  </si>
-  <si>
-    <t>在战斗中祈求上帝是没有用了，我们只能依靠自己。</t>
-  </si>
-  <si>
-    <t>不知道上帝能不能听到我的心声，让我早日得偿所愿。</t>
-  </si>
-  <si>
-    <t>无论信不信上帝，都要坚守爱与和平。</t>
-  </si>
-  <si>
-    <t>我可以为你做些什么？</t>
-  </si>
-  <si>
-    <t>其实一个人巡逻也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
-  </si>
-  <si>
-    <t>很高兴能为你服务。</t>
-  </si>
-  <si>
-    <t>守护小姐是我的职责。</t>
-  </si>
-  <si>
-    <t>在这个镇子里，我经常会想起关于老主人的事。</t>
-  </si>
-  <si>
-    <t>回想过去，好像刚刚发生在昨天，那时小姐还是个孩子…</t>
-  </si>
-  <si>
-    <t>如果有更多的人陪伴小姐，小姐应该会更开心吧</t>
-  </si>
-  <si>
-    <t>如果有什么事情，我会尽力而为。</t>
-  </si>
-  <si>
-    <t>一个料理如果缺少调味料，就会寡淡无味，不要忘记购买呀。</t>
-  </si>
-  <si>
-    <t>好的装备可以大大促进劳动效率，我需要做什么？</t>
-  </si>
-  <si>
-    <t>我一定要把布拉德利培养成一个优秀的人,这就是我生活的意义。</t>
-  </si>
-  <si>
-    <t>布拉德利再长大一些的话，我会让他自己选择自己的道路。</t>
-  </si>
-  <si>
-    <t>你好，需要什么服务吗？</t>
-  </si>
-  <si>
-    <t>姐姐应该有更广阔的前景的，现在却被困住这个小镇…</t>
-  </si>
-  <si>
-    <t>如果我能更强大一些的话，姐姐就可以去追求自己的梦想了。</t>
-  </si>
-  <si>
-    <t>你可以帮助我，鼓励我一直坚强吗？</t>
-  </si>
-  <si>
-    <t>如果你愿意的话，可以随时来找我和我的姐姐。</t>
-  </si>
-  <si>
-    <t>有什么搞不定的事情？</t>
-  </si>
-  <si>
-    <t>注意,不要走得太远,外面可是有很多怪物。</t>
-  </si>
-  <si>
-    <t>听说你在征讨小镇周边的怪物，做的不错。</t>
-  </si>
-  <si>
-    <t>招待不周了，有什么事情吗？</t>
-  </si>
-  <si>
-    <t>有妹妹和妈妈陪着我，我觉得很幸福。</t>
-  </si>
-  <si>
-    <t>如果爸爸还在的话…</t>
-  </si>
-  <si>
-    <t>我要努力支撑我的家，可以为我加油吗？</t>
-  </si>
-  <si>
-    <t>可有什么事情需要我为你而做的？</t>
-  </si>
-  <si>
-    <t>纺织可是化腐朽为神奇的技术。</t>
-  </si>
-  <si>
-    <t>如果你想学习纺织技术的话，我可以教你。</t>
-  </si>
-  <si>
-    <t>我有时也会为缺少传承而烦恼呢。</t>
-  </si>
-  <si>
-    <t>相比能赚到钱，我更希望有人可以将我的技术传承下去。</t>
-  </si>
-  <si>
-    <t>我拥有的比你知道的还多，你有什么需要的吗？</t>
-  </si>
-  <si>
-    <t>固守成见是不行的，只有变革才能带来新的机遇。</t>
-  </si>
-  <si>
-    <t>放心吧，你的外公只是去了他想去的地方。</t>
-  </si>
-  <si>
-    <t>好好在这里生活吧，你的外公也会很欣慰的。</t>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-  </si>
-  <si>
-    <t>丝特芬妮</t>
-  </si>
-  <si>
-    <t>格吉尔</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-  </si>
-  <si>
-    <t>琼</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>希拉</t>
-  </si>
-  <si>
-    <t>希尔达</t>
-  </si>
-  <si>
-    <t>布拉德利</t>
-  </si>
-  <si>
-    <t>布蓝达</t>
-  </si>
-  <si>
-    <t>希贝儿</t>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-  </si>
-  <si>
-    <t>梅林</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-  </si>
-  <si>
-    <t>考波特</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-  </si>
-  <si>
-    <t>强尼</t>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-  </si>
-  <si>
-    <t>阿普敦</t>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-  </si>
-  <si>
-    <t>莱特</t>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-  </si>
-  <si>
-    <t>别墅二楼</t>
-  </si>
-  <si>
-    <t>酒馆卧室</t>
-  </si>
-  <si>
-    <t>植物店</t>
-  </si>
-  <si>
-    <t>教堂</t>
-  </si>
-  <si>
-    <t>村公所卧室</t>
-  </si>
-  <si>
-    <t>后山</t>
-  </si>
-  <si>
-    <t>俱乐部阁楼</t>
-  </si>
-  <si>
-    <t>客栈二楼</t>
-  </si>
-  <si>
-    <t>武器店</t>
-  </si>
-  <si>
-    <t>船坞</t>
-  </si>
-  <si>
-    <t>我的农场</t>
-  </si>
-  <si>
-    <t>村公所大厅</t>
-  </si>
-  <si>
-    <t>工坊</t>
-  </si>
-  <si>
-    <t>畜牧店</t>
-  </si>
-  <si>
-    <t>俱乐部</t>
-  </si>
-  <si>
-    <t>塔楼顶部</t>
-  </si>
-  <si>
-    <t>家具店偏室</t>
-  </si>
-  <si>
-    <t>山坡</t>
-  </si>
-  <si>
-    <t>水车房内部</t>
-  </si>
-  <si>
-    <t>小木屋</t>
-  </si>
-  <si>
-    <t>家具店</t>
-  </si>
-  <si>
-    <t>中央广场</t>
-  </si>
-  <si>
-    <t>纺织店</t>
-  </si>
-  <si>
-    <t>商店街</t>
-  </si>
-  <si>
-    <t>塔楼</t>
-  </si>
-  <si>
-    <t>治安室</t>
-  </si>
-  <si>
-    <t>占卜屋</t>
-  </si>
-  <si>
-    <t>帐篷内部</t>
-  </si>
-  <si>
-    <t>风车内部</t>
-  </si>
-  <si>
-    <t>客栈一楼</t>
-  </si>
-  <si>
-    <t>码头</t>
-  </si>
-  <si>
-    <t>鱼摊内部</t>
-  </si>
-  <si>
-    <t>船坞二层</t>
-  </si>
-  <si>
-    <t>住宅区</t>
-  </si>
-  <si>
-    <t>别墅大厅</t>
-  </si>
-  <si>
-    <t>教堂二楼</t>
-  </si>
-  <si>
-    <t>酒馆</t>
-  </si>
-  <si>
-    <t>村公所宴会厅</t>
-  </si>
-  <si>
-    <t>科学研究室</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>城门</t>
-  </si>
-  <si>
-    <t>武器店二楼</t>
-  </si>
-  <si>
-    <t>许可清单你可以随时去看看。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>那么，现在我应该做些什么呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从最简单的售卖开始吧，看到前面的柜台了么,将东西放到上面就行了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对了，有些商品只能放在特定柜台上，你可以仔细观察一下。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好，现在去把商店的招牌换成营业吧，只有营业状态时才会有客人上门。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>做的不错，你可以再熟悉一下售卖商品，我在外面等你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>植物店里拥有各种植物种子,来跟我去熟悉熟悉吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这就是新来小镇的孩子吧，欢迎你哟，想来点什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买好了种子了，我们回农场种植吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>植物生长需要几天时间,在此期间,不如去野外探险一下,也许会获得想不到的收获哦。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>看来你已经掌握了售卖物品的方法了,如此一来,你的种植许可也开放了,那么现在去买一些种子回来吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等一下，我这里有一些种植工具，送给你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一步,先将农具从背包里拿出来。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在走到农田上，使用锄头将田地锄松吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好,就是这样,现在选择种子进行播种吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>别急,还差最后一步呢,种下的植物需要浇水,现在去河边打水回来。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldWoman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢，我会好好使用的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里就是农场，以后就归你管理了,现在准备种植吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前面就是春之山脉的入口，今天就让我这个老头子陪你闯一下吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在前进走到光圈中，开始今天的探索。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打起精神来，现在前进吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我没有镰刀，没办法收割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年轻人，这小镇的清晨不错吧？</t>
-  </si>
-  <si>
-    <t>嗯，空气很清新。</t>
-  </si>
-  <si>
-    <t>我正考虑给店里进些新货，你有啥建议？</t>
-  </si>
-  <si>
-    <t>你看着挺精神，昨晚休息得好？</t>
-  </si>
-  <si>
-    <t>还可以。您这店每天很早就开门吗？</t>
-  </si>
-  <si>
-    <t>对，习惯了。你要是有空可以来帮忙整理下。</t>
-  </si>
-  <si>
-    <t>你初来乍到，有没有去小镇周边转转？</t>
-  </si>
-  <si>
-    <t>还没有。周边有什么好玩的地方吗？</t>
-  </si>
-  <si>
-    <t>有个小湖泊，景色很美。你可以去看看。</t>
-  </si>
-  <si>
-    <t>我店里新到了一些家具，你想看看吗？</t>
-  </si>
-  <si>
-    <t>现在没时间。都是些什么风格的家具？</t>
-  </si>
-  <si>
-    <t>古典和简约的都有。你有空了来品鉴下。</t>
-  </si>
-  <si>
-    <t>你在镇上有没有交到新朋友？</t>
-  </si>
-  <si>
-    <t>认识了几个。交朋友对在这生活很重要吗？</t>
-  </si>
-  <si>
-    <t>当然，朋友多了路好走。你可以多参加些活动。</t>
-  </si>
-  <si>
-    <t>我最近在研究新的家具摆放方式，你有啥想法？</t>
-  </si>
-  <si>
-    <t>我不太懂。是不是可以根据功能分区摆放？</t>
-  </si>
-  <si>
-    <t>有点道理。你要是有了新灵感随时告诉我。</t>
-  </si>
-  <si>
-    <t>你觉得小镇的居民们对家具的需求大吗？</t>
-  </si>
-  <si>
-    <t>不太清楚。应该会需要一些实用的家具吧。</t>
-  </si>
-  <si>
-    <t>我也这么认为。你帮我留意下大家的喜好。</t>
-  </si>
-  <si>
-    <t>早啊，小家伙。我正想改进家具的细节，你觉得从哪入手？</t>
-  </si>
-  <si>
-    <t>可以从打磨工艺上试试。</t>
-  </si>
-  <si>
-    <t>嗨，你看这小镇的建筑风格，对家具设计有启发吗？</t>
-  </si>
-  <si>
-    <t>我觉得可以借鉴一些线条和色彩搭配。</t>
-  </si>
-  <si>
-    <t>很有见地。你能帮我画些草图吗？</t>
-  </si>
-  <si>
-    <t>我打算用旧木材打造复古家具，你觉得可行吗？</t>
-  </si>
-  <si>
-    <t>应该可以，会很有韵味。</t>
-  </si>
-  <si>
-    <t>对。你知道哪里能找到更多旧木材吗？</t>
-  </si>
-  <si>
-    <t>你在镇上参加过手工制作的活动吗？</t>
-  </si>
-  <si>
-    <t>可以学习一些新技巧。你有兴趣的话我带你去。</t>
-  </si>
-  <si>
-    <t>我想在家具上镶嵌一些特色石头，你有推荐吗？</t>
-  </si>
-  <si>
-    <t>像玛瑙或者水晶石应该不错。</t>
-  </si>
-  <si>
-    <t>有道理。你能帮我找些性价比高的吗？</t>
-  </si>
-  <si>
-    <t>你觉得家具的舒适度和美观度怎么平衡？</t>
-  </si>
-  <si>
-    <t>先保证舒适度，再用装饰提升美观度。</t>
-  </si>
-  <si>
-    <t>我要举办一个小型家具展览，你能帮忙宣传吗？</t>
-  </si>
-  <si>
-    <t>我可以试试。需要我做什么？</t>
-  </si>
-  <si>
-    <t>我觉得淡色系比较清新。</t>
-  </si>
-  <si>
-    <t>嗯，值得考虑。你能帮我选些样板吗？</t>
-  </si>
-  <si>
-    <t>哟，早哇。我想去河边钓鱼，顺便找找灵感，一起不？</t>
-  </si>
-  <si>
-    <t>我还有事。你钓鱼能找到什么家具灵感？</t>
-  </si>
-  <si>
-    <t>比如鱼的形状和纹理可以用在装饰上。</t>
-  </si>
-  <si>
-    <t>嗨，我打算用兽皮做些特殊的家具配饰，你见过吗？</t>
-  </si>
-  <si>
-    <t>只要处理好就没问题。你有渠道获取吗？</t>
-  </si>
-  <si>
-    <t>我想在家具里安装音乐盒，一打开就有音乐，怎样？</t>
-  </si>
-  <si>
-    <t>我最近得到一些散发香味的木材，做什么家具好？</t>
-  </si>
-  <si>
-    <t>可以做个香薰柜，存放香料。</t>
-  </si>
-  <si>
-    <t>我想打造一款能折叠成小物件的家具，你觉得可能吗？</t>
-  </si>
-  <si>
-    <t>有可能，像折叠椅就很实用。</t>
-  </si>
-  <si>
-    <t>嘿，我设计了一款带有魔法储物空间的家具，神奇吧？</t>
-  </si>
-  <si>
-    <t>哇，太神奇了！怎么实现储物空间的魔法呢？</t>
-  </si>
-  <si>
-    <t>用魔法水晶驱动。你在镇上见过魔法水晶吗？</t>
-  </si>
-  <si>
-    <t>我不太清楚。我先去吃个早饭，回见。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我今天有事。不好意思，我得走了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的。我突然想起有事，先走一步。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的。我先去了，回见。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我有点忙，先撤了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不太清楚。我去打听下。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有。这类活动和家具制作有关吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我找找看。不好意思，我得赶紧走了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>让我想想再告诉你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我在研究新的涂料，你对颜色有偏好吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我不太会。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挺有趣。我忙完来找你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没见过呢。这样合适吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有。要不去问问别人。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">好有创意！ </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你在镇上逛过那些古老的小巷吗？可以从巷子里的图案找设计灵感。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不太清楚。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你知道怎么处理木材香味吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没见过。我去探索下。我先去了，回见。</t>
+    <t>咳咳..咳咳..</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2559,15 +2616,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J542"/>
+  <dimension ref="A2:J486"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="48.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="10.625" style="1" customWidth="1"/>
@@ -2858,7 +2915,7 @@
         <v>181</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -4656,7 +4713,7 @@
         <v>181</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -4685,7 +4742,7 @@
         <v>181</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -4714,7 +4771,7 @@
         <v>181</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -4743,7 +4800,7 @@
         <v>181</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -4830,7 +4887,7 @@
         <v>181</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -4859,7 +4916,7 @@
         <v>181</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -4888,7 +4945,7 @@
         <v>181</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -4917,7 +4974,7 @@
         <v>181</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -4975,7 +5032,7 @@
         <v>181</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
@@ -5004,7 +5061,7 @@
         <v>181</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -5033,7 +5090,7 @@
         <v>181</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H86" s="1">
         <v>0</v>
@@ -5062,7 +5119,7 @@
         <v>181</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -5091,7 +5148,7 @@
         <v>181</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -5120,7 +5177,7 @@
         <v>181</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -5149,7 +5206,7 @@
         <v>181</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -5178,7 +5235,7 @@
         <v>181</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -5207,7 +5264,7 @@
         <v>181</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -5236,7 +5293,7 @@
         <v>181</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
@@ -5265,7 +5322,7 @@
         <v>181</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -5294,7 +5351,7 @@
         <v>181</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -5323,7 +5380,7 @@
         <v>181</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -5352,7 +5409,7 @@
         <v>181</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -5410,7 +5467,7 @@
         <v>181</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -5439,7 +5496,7 @@
         <v>181</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -5468,7 +5525,7 @@
         <v>181</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -5497,7 +5554,7 @@
         <v>181</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -5555,7 +5612,7 @@
         <v>181</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -5584,7 +5641,7 @@
         <v>181</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -5671,7 +5728,7 @@
         <v>181</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -5700,7 +5757,7 @@
         <v>181</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -5758,7 +5815,7 @@
         <v>181</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -5787,7 +5844,7 @@
         <v>181</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -5816,7 +5873,7 @@
         <v>181</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -5845,7 +5902,7 @@
         <v>181</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -5874,7 +5931,7 @@
         <v>181</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -5903,7 +5960,7 @@
         <v>181</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -5932,7 +5989,7 @@
         <v>181</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -5961,7 +6018,7 @@
         <v>181</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -5990,7 +6047,7 @@
         <v>181</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -6019,7 +6076,7 @@
         <v>181</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -6048,7 +6105,7 @@
         <v>181</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -6077,7 +6134,7 @@
         <v>181</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -6106,7 +6163,7 @@
         <v>181</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
@@ -6135,7 +6192,7 @@
         <v>181</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
@@ -7227,7 +7284,7 @@
         <v>255</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H160" s="1">
         <v>1416</v>
@@ -7259,7 +7316,7 @@
         <v>189</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H161" s="1">
         <v>1417</v>
@@ -7291,7 +7348,7 @@
         <v>189</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H162" s="1">
         <v>1418</v>
@@ -7323,7 +7380,7 @@
         <v>255</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
@@ -7355,7 +7412,7 @@
         <v>189</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H164" s="1">
         <v>0</v>
@@ -7387,7 +7444,7 @@
         <v>189</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H165" s="1">
         <v>0</v>
@@ -7419,7 +7476,7 @@
         <v>255</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H166" s="1">
         <v>1422</v>
@@ -7436,7 +7493,7 @@
         <v>1422</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>8</v>
@@ -7483,7 +7540,7 @@
         <v>189</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
@@ -7506,7 +7563,7 @@
         <v>10</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -7515,7 +7572,7 @@
         <v>181</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
@@ -7547,7 +7604,7 @@
         <v>189</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H170" s="1">
         <v>1426</v>
@@ -7570,7 +7627,7 @@
         <v>10</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -7579,7 +7636,7 @@
         <v>189</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
@@ -7596,7 +7653,7 @@
         <v>1427</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>8</v>
@@ -7611,7 +7668,7 @@
         <v>189</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
@@ -7643,7 +7700,7 @@
         <v>181</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H173" s="1">
         <v>1429</v>
@@ -7675,7 +7732,7 @@
         <v>181</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H174" s="1">
         <v>0</v>
@@ -7707,7 +7764,7 @@
         <v>181</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
@@ -7739,7 +7796,7 @@
         <v>181</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -7756,7 +7813,7 @@
         <v>1432</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>8</v>
@@ -7788,7 +7845,7 @@
         <v>1433</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>9</v>
@@ -7803,7 +7860,7 @@
         <v>255</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
@@ -7867,7 +7924,7 @@
         <v>255</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -7899,7 +7956,7 @@
         <v>255</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -7931,7 +7988,7 @@
         <v>255</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -7948,7 +8005,7 @@
         <v>1439</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>9</v>
@@ -7963,7 +8020,7 @@
         <v>255</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -9097,7 +9154,7 @@
         <v>255</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -11276,7 +11333,7 @@
         <v>181</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -11305,7 +11362,7 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -11334,7 +11391,7 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H298" s="1">
         <v>0</v>
@@ -11351,7 +11408,7 @@
         <v>4000</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>274</v>
@@ -11363,7 +11420,7 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
@@ -11380,7 +11437,7 @@
         <v>4001</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>274</v>
@@ -11392,7 +11449,7 @@
         <v>181</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H300" s="1">
         <v>4000</v>
@@ -11409,7 +11466,7 @@
         <v>4002</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>274</v>
@@ -11438,7 +11495,7 @@
         <v>4003</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>274</v>
@@ -11450,7 +11507,7 @@
         <v>181</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H302" s="1">
         <v>4000</v>
@@ -11467,7 +11524,7 @@
         <v>4004</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>274</v>
@@ -11479,7 +11536,7 @@
         <v>181</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H303" s="1">
         <v>4000</v>
@@ -11496,7 +11553,7 @@
         <v>4005</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>274</v>
@@ -11508,7 +11565,7 @@
         <v>181</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -11525,7 +11582,7 @@
         <v>4006</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>274</v>
@@ -11537,7 +11594,7 @@
         <v>181</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H305" s="1">
         <v>4005</v>
@@ -11554,7 +11611,7 @@
         <v>4007</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>274</v>
@@ -11566,7 +11623,7 @@
         <v>181</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H306" s="1">
         <v>4005</v>
@@ -11583,7 +11640,7 @@
         <v>4008</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>274</v>
@@ -11595,7 +11652,7 @@
         <v>181</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H307" s="1">
         <v>4005</v>
@@ -11612,7 +11669,7 @@
         <v>4009</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>274</v>
@@ -11624,7 +11681,7 @@
         <v>181</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H308" s="1">
         <v>4005</v>
@@ -11641,7 +11698,7 @@
         <v>4010</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>274</v>
@@ -11653,7 +11710,7 @@
         <v>181</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H309" s="1">
         <v>4005</v>
@@ -11670,7 +11727,7 @@
         <v>4011</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>274</v>
@@ -11682,7 +11739,7 @@
         <v>181</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H310" s="1">
         <v>0</v>
@@ -11699,7 +11756,7 @@
         <v>4012</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>274</v>
@@ -11728,7 +11785,7 @@
         <v>4013</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>274</v>
@@ -11740,7 +11797,7 @@
         <v>181</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H312" s="1">
         <v>4011</v>
@@ -11757,7 +11814,7 @@
         <v>4014</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>274</v>
@@ -11769,7 +11826,7 @@
         <v>181</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H313" s="1">
         <v>4011</v>
@@ -11786,7 +11843,7 @@
         <v>4015</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>274</v>
@@ -11798,7 +11855,7 @@
         <v>181</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H314" s="1">
         <v>4011</v>
@@ -11815,7 +11872,7 @@
         <v>4016</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>274</v>
@@ -11827,7 +11884,7 @@
         <v>181</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H315" s="1">
         <v>0</v>
@@ -11844,7 +11901,7 @@
         <v>4017</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>274</v>
@@ -11873,7 +11930,7 @@
         <v>4018</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>274</v>
@@ -11885,7 +11942,7 @@
         <v>181</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H317" s="1">
         <v>4016</v>
@@ -11902,7 +11959,7 @@
         <v>4019</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>274</v>
@@ -11914,7 +11971,7 @@
         <v>181</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H318" s="1">
         <v>4016</v>
@@ -11931,7 +11988,7 @@
         <v>4020</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>274</v>
@@ -11943,7 +12000,7 @@
         <v>181</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H319" s="1">
         <v>4016</v>
@@ -11960,7 +12017,7 @@
         <v>4021</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>274</v>
@@ -11972,7 +12029,7 @@
         <v>181</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H320" s="1">
         <v>0</v>
@@ -11989,7 +12046,7 @@
         <v>4022</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>274</v>
@@ -12001,7 +12058,7 @@
         <v>181</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H321" s="1">
         <v>4021</v>
@@ -12018,7 +12075,7 @@
         <v>4023</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>274</v>
@@ -12030,7 +12087,7 @@
         <v>181</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H322" s="1">
         <v>4021</v>
@@ -12047,7 +12104,7 @@
         <v>4024</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>274</v>
@@ -12059,7 +12116,7 @@
         <v>181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H323" s="1">
         <v>4021</v>
@@ -12076,7 +12133,7 @@
         <v>4025</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>274</v>
@@ -12088,7 +12145,7 @@
         <v>181</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H324" s="1">
         <v>4021</v>
@@ -12105,7 +12162,7 @@
         <v>4026</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>274</v>
@@ -12117,7 +12174,7 @@
         <v>181</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H325" s="1">
         <v>0</v>
@@ -12134,7 +12191,7 @@
         <v>4027</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>274</v>
@@ -12146,7 +12203,7 @@
         <v>181</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H326" s="1">
         <v>4026</v>
@@ -12163,7 +12220,7 @@
         <v>4028</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>274</v>
@@ -12175,7 +12232,7 @@
         <v>181</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H327" s="1">
         <v>4026</v>
@@ -12192,7 +12249,7 @@
         <v>4029</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>274</v>
@@ -12204,7 +12261,7 @@
         <v>181</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H328" s="1">
         <v>4026</v>
@@ -12221,7 +12278,7 @@
         <v>4030</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>274</v>
@@ -12233,7 +12290,7 @@
         <v>181</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H329" s="1">
         <v>4026</v>
@@ -12250,7 +12307,7 @@
         <v>4031</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>274</v>
@@ -12262,7 +12319,7 @@
         <v>181</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H330" s="1">
         <v>0</v>
@@ -12279,7 +12336,7 @@
         <v>4032</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>274</v>
@@ -12291,7 +12348,7 @@
         <v>181</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H331" s="1">
         <v>4031</v>
@@ -12308,7 +12365,7 @@
         <v>4033</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>274</v>
@@ -12320,7 +12377,7 @@
         <v>181</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H332" s="1">
         <v>4031</v>
@@ -12337,7 +12394,7 @@
         <v>4034</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>274</v>
@@ -12349,7 +12406,7 @@
         <v>181</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H333" s="1">
         <v>4031</v>
@@ -12366,7 +12423,7 @@
         <v>4035</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>274</v>
@@ -12378,7 +12435,7 @@
         <v>181</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H334" s="1">
         <v>4031</v>
@@ -12395,7 +12452,7 @@
         <v>4036</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>274</v>
@@ -12407,7 +12464,7 @@
         <v>181</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H335" s="1">
         <v>0</v>
@@ -12424,7 +12481,7 @@
         <v>4037</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>274</v>
@@ -12436,7 +12493,7 @@
         <v>181</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H336" s="1">
         <v>4036</v>
@@ -12453,7 +12510,7 @@
         <v>4038</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>274</v>
@@ -12465,7 +12522,7 @@
         <v>181</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H337" s="1">
         <v>4036</v>
@@ -12482,7 +12539,7 @@
         <v>4039</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>274</v>
@@ -12494,7 +12551,7 @@
         <v>181</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H338" s="1">
         <v>4036</v>
@@ -12511,7 +12568,7 @@
         <v>4040</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>274</v>
@@ -12523,7 +12580,7 @@
         <v>181</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H339" s="1">
         <v>4036</v>
@@ -12540,7 +12597,7 @@
         <v>4041</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>274</v>
@@ -12552,7 +12609,7 @@
         <v>181</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H340" s="1">
         <v>0</v>
@@ -12569,7 +12626,7 @@
         <v>4042</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>274</v>
@@ -12581,7 +12638,7 @@
         <v>181</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H341" s="1">
         <v>4041</v>
@@ -12598,7 +12655,7 @@
         <v>4043</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>274</v>
@@ -12627,7 +12684,7 @@
         <v>4044</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>274</v>
@@ -12656,7 +12713,7 @@
         <v>4045</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>274</v>
@@ -12668,7 +12725,7 @@
         <v>181</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H344" s="1">
         <v>4041</v>
@@ -12685,7 +12742,7 @@
         <v>4046</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>274</v>
@@ -12697,7 +12754,7 @@
         <v>181</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H345" s="1">
         <v>0</v>
@@ -12714,7 +12771,7 @@
         <v>4047</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>274</v>
@@ -12726,7 +12783,7 @@
         <v>181</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H346" s="1">
         <v>4046</v>
@@ -12743,7 +12800,7 @@
         <v>4048</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>274</v>
@@ -12772,7 +12829,7 @@
         <v>4049</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>274</v>
@@ -12801,7 +12858,7 @@
         <v>4050</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>274</v>
@@ -12813,7 +12870,7 @@
         <v>181</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H349" s="1">
         <v>4046</v>
@@ -12830,7 +12887,7 @@
         <v>4051</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>274</v>
@@ -12842,7 +12899,7 @@
         <v>181</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H350" s="1">
         <v>0</v>
@@ -12859,7 +12916,7 @@
         <v>4052</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>274</v>
@@ -12871,7 +12928,7 @@
         <v>181</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H351" s="1">
         <v>4051</v>
@@ -12888,7 +12945,7 @@
         <v>4053</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>274</v>
@@ -12900,7 +12957,7 @@
         <v>181</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H352" s="1">
         <v>4051</v>
@@ -12917,7 +12974,7 @@
         <v>4054</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>274</v>
@@ -12929,7 +12986,7 @@
         <v>181</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H353" s="1">
         <v>4051</v>
@@ -12946,7 +13003,7 @@
         <v>4055</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>274</v>
@@ -12958,7 +13015,7 @@
         <v>181</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H354" s="1">
         <v>4051</v>
@@ -12975,7 +13032,7 @@
         <v>4056</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>274</v>
@@ -12987,7 +13044,7 @@
         <v>181</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H355" s="1">
         <v>0</v>
@@ -13004,7 +13061,7 @@
         <v>4057</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>274</v>
@@ -13016,7 +13073,7 @@
         <v>181</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H356" s="1">
         <v>4056</v>
@@ -13033,7 +13090,7 @@
         <v>4058</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>274</v>
@@ -13045,7 +13102,7 @@
         <v>181</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H357" s="1">
         <v>4056</v>
@@ -13062,7 +13119,7 @@
         <v>4059</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>274</v>
@@ -13074,7 +13131,7 @@
         <v>181</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H358" s="1">
         <v>4056</v>
@@ -13091,7 +13148,7 @@
         <v>4060</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>274</v>
@@ -13103,7 +13160,7 @@
         <v>181</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H359" s="1">
         <v>4056</v>
@@ -13120,7 +13177,7 @@
         <v>4061</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>274</v>
@@ -13132,7 +13189,7 @@
         <v>181</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H360" s="1">
         <v>0</v>
@@ -13149,7 +13206,7 @@
         <v>4062</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>274</v>
@@ -13161,7 +13218,7 @@
         <v>181</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H361" s="1">
         <v>4061</v>
@@ -13178,7 +13235,7 @@
         <v>4063</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>274</v>
@@ -13207,7 +13264,7 @@
         <v>4064</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>274</v>
@@ -13236,7 +13293,7 @@
         <v>4065</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>274</v>
@@ -13248,7 +13305,7 @@
         <v>181</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H364" s="1">
         <v>4061</v>
@@ -13265,7 +13322,7 @@
         <v>4066</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>274</v>
@@ -13277,7 +13334,7 @@
         <v>181</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H365" s="1">
         <v>0</v>
@@ -13294,7 +13351,7 @@
         <v>4067</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>274</v>
@@ -13323,7 +13380,7 @@
         <v>4068</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>274</v>
@@ -13335,7 +13392,7 @@
         <v>181</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H367" s="1">
         <v>4066</v>
@@ -13352,7 +13409,7 @@
         <v>4069</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>274</v>
@@ -13381,7 +13438,7 @@
         <v>4070</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>274</v>
@@ -13393,7 +13450,7 @@
         <v>181</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H369" s="1">
         <v>4066</v>
@@ -13410,7 +13467,7 @@
         <v>4071</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>274</v>
@@ -13422,7 +13479,7 @@
         <v>181</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H370" s="1">
         <v>0</v>
@@ -13439,7 +13496,7 @@
         <v>4072</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>274</v>
@@ -13468,7 +13525,7 @@
         <v>4073</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>274</v>
@@ -13497,7 +13554,7 @@
         <v>4074</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>274</v>
@@ -13509,7 +13566,7 @@
         <v>181</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H373" s="1">
         <v>4071</v>
@@ -13526,7 +13583,7 @@
         <v>4075</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>274</v>
@@ -13538,7 +13595,7 @@
         <v>181</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H374" s="1">
         <v>4071</v>
@@ -13555,7 +13612,7 @@
         <v>4076</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>274</v>
@@ -13567,7 +13624,7 @@
         <v>181</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H375" s="1">
         <v>0</v>
@@ -13584,7 +13641,7 @@
         <v>4077</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>274</v>
@@ -13596,7 +13653,7 @@
         <v>181</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H376" s="1">
         <v>4076</v>
@@ -13613,7 +13670,7 @@
         <v>4078</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>274</v>
@@ -13625,7 +13682,7 @@
         <v>181</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H377" s="1">
         <v>4076</v>
@@ -13642,7 +13699,7 @@
         <v>4079</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>274</v>
@@ -13654,7 +13711,7 @@
         <v>181</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H378" s="1">
         <v>4076</v>
@@ -13671,7 +13728,7 @@
         <v>4080</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>274</v>
@@ -13683,7 +13740,7 @@
         <v>181</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H379" s="1">
         <v>4076</v>
@@ -13700,7 +13757,7 @@
         <v>4081</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>274</v>
@@ -13712,7 +13769,7 @@
         <v>181</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H380" s="1">
         <v>0</v>
@@ -13729,7 +13786,7 @@
         <v>4082</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>274</v>
@@ -13758,7 +13815,7 @@
         <v>4083</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>274</v>
@@ -13787,7 +13844,7 @@
         <v>4084</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>274</v>
@@ -13799,7 +13856,7 @@
         <v>181</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H383" s="1">
         <v>4081</v>
@@ -13816,7 +13873,7 @@
         <v>4085</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>274</v>
@@ -13828,7 +13885,7 @@
         <v>181</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H384" s="1">
         <v>4081</v>
@@ -13845,7 +13902,7 @@
         <v>4086</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D385" s="1" t="s">
         <v>274</v>
@@ -13857,7 +13914,7 @@
         <v>181</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H385" s="1">
         <v>0</v>
@@ -13874,7 +13931,7 @@
         <v>4087</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>274</v>
@@ -13886,7 +13943,7 @@
         <v>181</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H386" s="1">
         <v>4086</v>
@@ -13903,7 +13960,7 @@
         <v>4088</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>274</v>
@@ -13915,7 +13972,7 @@
         <v>181</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H387" s="1">
         <v>4086</v>
@@ -13932,7 +13989,7 @@
         <v>4089</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>274</v>
@@ -13944,7 +14001,7 @@
         <v>181</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H388" s="1">
         <v>4086</v>
@@ -13961,7 +14018,7 @@
         <v>4090</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>274</v>
@@ -13973,7 +14030,7 @@
         <v>181</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H389" s="1">
         <v>4086</v>
@@ -13990,7 +14047,7 @@
         <v>4091</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>274</v>
@@ -14002,7 +14059,7 @@
         <v>181</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H390" s="1">
         <v>0</v>
@@ -14019,7 +14076,7 @@
         <v>4092</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>274</v>
@@ -14031,7 +14088,7 @@
         <v>181</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H391" s="1">
         <v>4091</v>
@@ -14048,7 +14105,7 @@
         <v>4093</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>274</v>
@@ -14060,7 +14117,7 @@
         <v>181</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H392" s="1">
         <v>4091</v>
@@ -14077,7 +14134,7 @@
         <v>4094</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>274</v>
@@ -14089,7 +14146,7 @@
         <v>181</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H393" s="1">
         <v>4091</v>
@@ -14106,7 +14163,7 @@
         <v>4095</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>274</v>
@@ -14118,7 +14175,7 @@
         <v>181</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H394" s="1">
         <v>4091</v>
@@ -14135,7 +14192,7 @@
         <v>4096</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>274</v>
@@ -14147,7 +14204,7 @@
         <v>181</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H395" s="1">
         <v>0</v>
@@ -14164,7 +14221,7 @@
         <v>4097</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>274</v>
@@ -14176,7 +14233,7 @@
         <v>181</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H396" s="1">
         <v>4096</v>
@@ -14193,7 +14250,7 @@
         <v>4098</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>274</v>
@@ -14205,7 +14262,7 @@
         <v>181</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H397" s="1">
         <v>4096</v>
@@ -14222,7 +14279,7 @@
         <v>4099</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>274</v>
@@ -14234,7 +14291,7 @@
         <v>181</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H398" s="1">
         <v>4096</v>
@@ -14251,7 +14308,7 @@
         <v>4100</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>274</v>
@@ -14263,7 +14320,7 @@
         <v>181</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H399" s="1">
         <v>4096</v>
@@ -14280,7 +14337,7 @@
         <v>4101</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>274</v>
@@ -14292,7 +14349,7 @@
         <v>181</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H400" s="1">
         <v>0</v>
@@ -14309,7 +14366,7 @@
         <v>4102</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>274</v>
@@ -14338,7 +14395,7 @@
         <v>4103</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>274</v>
@@ -14367,7 +14424,7 @@
         <v>4104</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>274</v>
@@ -14396,7 +14453,7 @@
         <v>4105</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>274</v>
@@ -14408,7 +14465,7 @@
         <v>181</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H404" s="1">
         <v>4101</v>
@@ -14425,7 +14482,7 @@
         <v>4106</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>274</v>
@@ -14437,7 +14494,7 @@
         <v>181</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H405" s="1">
         <v>0</v>
@@ -14454,7 +14511,7 @@
         <v>4107</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>274</v>
@@ -14483,7 +14540,7 @@
         <v>4108</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>274</v>
@@ -14512,7 +14569,7 @@
         <v>4109</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>274</v>
@@ -14541,7 +14598,7 @@
         <v>4110</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>274</v>
@@ -14553,7 +14610,7 @@
         <v>181</v>
       </c>
       <c r="G409" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H409" s="1">
         <v>4106</v>
@@ -14570,7 +14627,7 @@
         <v>4111</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D410" s="1" t="s">
         <v>274</v>
@@ -14582,7 +14639,7 @@
         <v>181</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H410" s="1">
         <v>0</v>
@@ -14599,7 +14656,7 @@
         <v>4112</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D411" s="1" t="s">
         <v>274</v>
@@ -14611,7 +14668,7 @@
         <v>181</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H411" s="1">
         <v>4111</v>
@@ -14628,7 +14685,7 @@
         <v>4113</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D412" s="1" t="s">
         <v>274</v>
@@ -14640,7 +14697,7 @@
         <v>181</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H412" s="1">
         <v>4111</v>
@@ -14657,7 +14714,7 @@
         <v>4114</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D413" s="1" t="s">
         <v>274</v>
@@ -14669,7 +14726,7 @@
         <v>181</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H413" s="1">
         <v>4111</v>
@@ -14686,7 +14743,7 @@
         <v>4115</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D414" s="1" t="s">
         <v>274</v>
@@ -14698,7 +14755,7 @@
         <v>181</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H414" s="1">
         <v>4111</v>
@@ -14715,7 +14772,7 @@
         <v>4116</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D415" s="1" t="s">
         <v>274</v>
@@ -14727,7 +14784,7 @@
         <v>181</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H415" s="1">
         <v>0</v>
@@ -14744,7 +14801,7 @@
         <v>4117</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D416" s="1" t="s">
         <v>274</v>
@@ -14773,7 +14830,7 @@
         <v>4118</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>274</v>
@@ -14802,7 +14859,7 @@
         <v>4119</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>274</v>
@@ -14831,7 +14888,7 @@
         <v>4120</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D419" s="1" t="s">
         <v>274</v>
@@ -14843,7 +14900,7 @@
         <v>181</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H419" s="1">
         <v>4116</v>
@@ -14860,7 +14917,7 @@
         <v>4121</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D420" s="1" t="s">
         <v>274</v>
@@ -14872,7 +14929,7 @@
         <v>181</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H420" s="1">
         <v>0</v>
@@ -14889,7 +14946,7 @@
         <v>4122</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D421" s="1" t="s">
         <v>274</v>
@@ -14901,7 +14958,7 @@
         <v>181</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H421" s="1">
         <v>4121</v>
@@ -14918,7 +14975,7 @@
         <v>4123</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D422" s="1" t="s">
         <v>274</v>
@@ -14930,7 +14987,7 @@
         <v>181</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H422" s="1">
         <v>4121</v>
@@ -14947,7 +15004,7 @@
         <v>4124</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D423" s="1" t="s">
         <v>274</v>
@@ -14959,7 +15016,7 @@
         <v>181</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H423" s="1">
         <v>4121</v>
@@ -14976,7 +15033,7 @@
         <v>4125</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D424" s="1" t="s">
         <v>274</v>
@@ -14988,7 +15045,7 @@
         <v>181</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H424" s="1">
         <v>4121</v>
@@ -15005,7 +15062,7 @@
         <v>4126</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D425" s="1" t="s">
         <v>274</v>
@@ -15017,7 +15074,7 @@
         <v>181</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H425" s="1">
         <v>0</v>
@@ -15034,7 +15091,7 @@
         <v>4127</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D426" s="1" t="s">
         <v>274</v>
@@ -15063,7 +15120,7 @@
         <v>4128</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D427" s="1" t="s">
         <v>274</v>
@@ -15092,7 +15149,7 @@
         <v>4129</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D428" s="1" t="s">
         <v>274</v>
@@ -15121,7 +15178,7 @@
         <v>4130</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D429" s="1" t="s">
         <v>274</v>
@@ -15150,7 +15207,7 @@
         <v>4131</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>274</v>
@@ -15162,7 +15219,7 @@
         <v>181</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H430" s="1">
         <v>4126</v>
@@ -15179,7 +15236,7 @@
         <v>4132</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>274</v>
@@ -15191,7 +15248,7 @@
         <v>181</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H431" s="1">
         <v>0</v>
@@ -15208,7 +15265,7 @@
         <v>4133</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>274</v>
@@ -15237,7 +15294,7 @@
         <v>4134</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D433" s="1" t="s">
         <v>274</v>
@@ -15249,7 +15306,7 @@
         <v>181</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H433" s="1">
         <v>4132</v>
@@ -15266,7 +15323,7 @@
         <v>4135</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>274</v>
@@ -15295,7 +15352,7 @@
         <v>4136</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>274</v>
@@ -15307,7 +15364,7 @@
         <v>181</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H435" s="1">
         <v>4132</v>
@@ -15324,7 +15381,7 @@
         <v>4137</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D436" s="1" t="s">
         <v>274</v>
@@ -15336,7 +15393,7 @@
         <v>181</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H436" s="1">
         <v>0</v>
@@ -15353,7 +15410,7 @@
         <v>4138</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D437" s="1" t="s">
         <v>274</v>
@@ -15365,7 +15422,7 @@
         <v>181</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H437" s="1">
         <v>4137</v>
@@ -15382,7 +15439,7 @@
         <v>4139</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>274</v>
@@ -15394,7 +15451,7 @@
         <v>181</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H438" s="1">
         <v>4137</v>
@@ -15411,7 +15468,7 @@
         <v>4140</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>274</v>
@@ -15423,7 +15480,7 @@
         <v>181</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H439" s="1">
         <v>4137</v>
@@ -15440,7 +15497,7 @@
         <v>4141</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>274</v>
@@ -15452,7 +15509,7 @@
         <v>181</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H440" s="1">
         <v>4137</v>
@@ -15469,7 +15526,7 @@
         <v>4142</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D441" s="1" t="s">
         <v>274</v>
@@ -15481,7 +15538,7 @@
         <v>181</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H441" s="1">
         <v>0</v>
@@ -15498,7 +15555,7 @@
         <v>4143</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D442" s="1" t="s">
         <v>274</v>
@@ -15510,7 +15567,7 @@
         <v>181</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H442" s="1">
         <v>4142</v>
@@ -15527,7 +15584,7 @@
         <v>4144</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D443" s="1" t="s">
         <v>274</v>
@@ -15556,7 +15613,7 @@
         <v>4145</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D444" s="1" t="s">
         <v>274</v>
@@ -15585,7 +15642,7 @@
         <v>4146</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>274</v>
@@ -15597,7 +15654,7 @@
         <v>181</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H445" s="1">
         <v>4142</v>
@@ -15614,7 +15671,7 @@
         <v>4147</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D446" s="1" t="s">
         <v>274</v>
@@ -15626,7 +15683,7 @@
         <v>181</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H446" s="1">
         <v>0</v>
@@ -15643,7 +15700,7 @@
         <v>4148</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>274</v>
@@ -15672,7 +15729,7 @@
         <v>4149</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>274</v>
@@ -15684,7 +15741,7 @@
         <v>181</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H448" s="1">
         <v>4147</v>
@@ -15701,7 +15758,7 @@
         <v>4150</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>274</v>
@@ -15713,7 +15770,7 @@
         <v>181</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H449" s="1">
         <v>4147</v>
@@ -15730,7 +15787,7 @@
         <v>4151</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>274</v>
@@ -15742,7 +15799,7 @@
         <v>181</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H450" s="1">
         <v>4147</v>
@@ -15759,7 +15816,7 @@
         <v>4152</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>274</v>
@@ -15771,7 +15828,7 @@
         <v>181</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H451" s="1">
         <v>0</v>
@@ -15788,7 +15845,7 @@
         <v>4153</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D452" s="1" t="s">
         <v>274</v>
@@ -15800,7 +15857,7 @@
         <v>181</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H452" s="1">
         <v>4152</v>
@@ -15817,7 +15874,7 @@
         <v>4154</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>274</v>
@@ -15829,7 +15886,7 @@
         <v>181</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H453" s="1">
         <v>4152</v>
@@ -15846,7 +15903,7 @@
         <v>4155</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D454" s="1" t="s">
         <v>274</v>
@@ -15858,7 +15915,7 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H454" s="1">
         <v>4152</v>
@@ -15875,7 +15932,7 @@
         <v>4156</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D455" s="1" t="s">
         <v>274</v>
@@ -15887,7 +15944,7 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H455" s="1">
         <v>4152</v>
@@ -15904,7 +15961,7 @@
         <v>4157</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D456" s="1" t="s">
         <v>274</v>
@@ -15916,7 +15973,7 @@
         <v>181</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H456" s="1">
         <v>0</v>
@@ -15933,7 +15990,7 @@
         <v>4158</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D457" s="1" t="s">
         <v>274</v>
@@ -15962,7 +16019,7 @@
         <v>4159</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>274</v>
@@ -15974,7 +16031,7 @@
         <v>181</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H458" s="1">
         <v>4157</v>
@@ -15991,7 +16048,7 @@
         <v>4160</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D459" s="1" t="s">
         <v>274</v>
@@ -16003,7 +16060,7 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H459" s="1">
         <v>4157</v>
@@ -16020,7 +16077,7 @@
         <v>4161</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>274</v>
@@ -16032,7 +16089,7 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H460" s="1">
         <v>4157</v>
@@ -16322,7 +16379,7 @@
         <v>181</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>303</v>
+        <v>652</v>
       </c>
       <c r="H470" s="1">
         <v>0</v>
@@ -16334,768 +16391,468 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A471" s="6">
-        <v>44001</v>
-      </c>
-      <c r="B471" s="7"/>
-      <c r="F471" s="7"/>
-      <c r="G471" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="H471" s="6">
-        <v>44002</v>
+    <row r="471" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A471" s="1">
+        <v>8101</v>
+      </c>
+      <c r="B471" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D471" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E471" s="1">
+        <v>0</v>
+      </c>
+      <c r="F471" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G471" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="H471" s="1">
+        <v>0</v>
+      </c>
+      <c r="I471" s="1">
+        <v>0</v>
+      </c>
+      <c r="J471" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
-        <v>44002</v>
+        <v>8102</v>
+      </c>
+      <c r="B472" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D472" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E472" s="1">
         <v>0</v>
       </c>
-      <c r="G472" t="s">
-        <v>581</v>
+      <c r="F472" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G472" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="H472" s="1">
+        <v>0</v>
+      </c>
+      <c r="I472" s="1">
+        <v>0</v>
+      </c>
+      <c r="J472" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
-        <v>44003</v>
-      </c>
-      <c r="G473" t="s">
-        <v>582</v>
+        <v>8103</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D473" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E473" s="1">
+        <v>0</v>
+      </c>
+      <c r="F473" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G473" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="H473" s="1">
-        <v>44004</v>
+        <v>0</v>
+      </c>
+      <c r="I473" s="1">
+        <v>0</v>
+      </c>
+      <c r="J473" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
-        <v>44004</v>
+        <v>8104</v>
+      </c>
+      <c r="B474" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D474" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E474" s="1">
         <v>0</v>
       </c>
-      <c r="G474" t="s">
-        <v>633</v>
+      <c r="F474" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G474" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="H474" s="1">
+        <v>0</v>
+      </c>
+      <c r="I474" s="1">
+        <v>0</v>
+      </c>
+      <c r="J474" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
-        <v>44005</v>
-      </c>
-      <c r="G475" t="s">
-        <v>583</v>
+        <v>8105</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D475" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E475" s="1">
+        <v>0</v>
+      </c>
+      <c r="F475" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G475" s="1" t="s">
+        <v>656</v>
       </c>
       <c r="H475" s="1">
-        <v>44006</v>
+        <v>0</v>
+      </c>
+      <c r="I475" s="1">
+        <v>0</v>
+      </c>
+      <c r="J475" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
-        <v>44006</v>
+        <v>8106</v>
+      </c>
+      <c r="B476" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D476" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E476" s="1">
         <v>0</v>
       </c>
-      <c r="G476" t="s">
-        <v>584</v>
+      <c r="F476" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G476" s="1" t="s">
+        <v>657</v>
       </c>
       <c r="H476" s="1">
-        <v>44007</v>
+        <v>0</v>
+      </c>
+      <c r="I476" s="1">
+        <v>0</v>
+      </c>
+      <c r="J476" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
-        <v>44007</v>
-      </c>
-      <c r="G477" t="s">
-        <v>585</v>
+        <v>8107</v>
+      </c>
+      <c r="B477" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D477" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E477" s="1">
+        <v>0</v>
+      </c>
+      <c r="F477" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G477" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="H477" s="1">
+        <v>0</v>
+      </c>
+      <c r="I477" s="1">
+        <v>0</v>
+      </c>
+      <c r="J477" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
-        <v>44008</v>
+        <v>8108</v>
+      </c>
+      <c r="B478" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D478" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E478" s="1">
         <v>0</v>
       </c>
-      <c r="G478" t="s">
-        <v>634</v>
+      <c r="F478" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G478" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="H478" s="1">
-        <v>44009</v>
+        <v>0</v>
+      </c>
+      <c r="I478" s="1">
+        <v>0</v>
+      </c>
+      <c r="J478" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
-        <v>44009</v>
-      </c>
-      <c r="G479" t="s">
-        <v>586</v>
+        <v>8109</v>
+      </c>
+      <c r="B479" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D479" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E479" s="1">
+        <v>0</v>
+      </c>
+      <c r="F479" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G479" s="1" t="s">
+        <v>658</v>
       </c>
       <c r="H479" s="1">
-        <v>44010</v>
+        <v>0</v>
+      </c>
+      <c r="I479" s="1">
+        <v>0</v>
+      </c>
+      <c r="J479" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
-        <v>44010</v>
+        <v>8110</v>
+      </c>
+      <c r="B480" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D480" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E480" s="1">
         <v>0</v>
       </c>
-      <c r="G480" t="s">
-        <v>587</v>
+      <c r="F480" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G480" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="H480" s="1">
-        <v>44011</v>
-      </c>
-    </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="I480" s="1">
+        <v>0</v>
+      </c>
+      <c r="J480" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
-        <v>44011</v>
-      </c>
-      <c r="G481" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.15">
+        <v>8111</v>
+      </c>
+      <c r="B481" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D481" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E481" s="1">
+        <v>0</v>
+      </c>
+      <c r="F481" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G481" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="H481" s="1">
+        <v>0</v>
+      </c>
+      <c r="I481" s="1">
+        <v>0</v>
+      </c>
+      <c r="J481" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
-        <v>44012</v>
-      </c>
-      <c r="G482" t="s">
-        <v>589</v>
+        <v>8112</v>
+      </c>
+      <c r="B482" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D482" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E482" s="1">
+        <v>0</v>
+      </c>
+      <c r="F482" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G482" s="1" t="s">
+        <v>662</v>
       </c>
       <c r="H482" s="1">
-        <v>44013</v>
-      </c>
-    </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="I482" s="1">
+        <v>0</v>
+      </c>
+      <c r="J482" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
-        <v>44013</v>
+        <v>8113</v>
+      </c>
+      <c r="B483" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D483" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E483" s="1">
         <v>0</v>
       </c>
-      <c r="G483" t="s">
-        <v>590</v>
+      <c r="F483" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G483" s="1" t="s">
+        <v>652</v>
       </c>
       <c r="H483" s="1">
-        <v>44014</v>
-      </c>
-    </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="I483" s="1">
+        <v>0</v>
+      </c>
+      <c r="J483" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
-        <v>44014</v>
-      </c>
-      <c r="G484" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.15">
+        <v>8114</v>
+      </c>
+      <c r="B484" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D484" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E484" s="1">
+        <v>0</v>
+      </c>
+      <c r="F484" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G484" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="H484" s="1">
+        <v>0</v>
+      </c>
+      <c r="I484" s="1">
+        <v>0</v>
+      </c>
+      <c r="J484" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
-        <v>44015</v>
-      </c>
-      <c r="G485" t="s">
-        <v>592</v>
+        <v>8115</v>
+      </c>
+      <c r="B485" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D485" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E485" s="1">
+        <v>0</v>
+      </c>
+      <c r="F485" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G485" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="H485" s="1">
-        <v>44016</v>
-      </c>
-    </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="I485" s="1">
+        <v>0</v>
+      </c>
+      <c r="J485" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
-        <v>44016</v>
+        <v>8116</v>
+      </c>
+      <c r="B486" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D486" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E486" s="1">
         <v>0</v>
       </c>
-      <c r="G486" t="s">
-        <v>593</v>
+      <c r="F486" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G486" s="1" t="s">
+        <v>665</v>
       </c>
       <c r="H486" s="1">
-        <v>44017</v>
-      </c>
-    </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A487" s="1">
-        <v>44017</v>
-      </c>
-      <c r="G487" t="s">
-        <v>594</v>
-      </c>
-      <c r="H487" s="1">
-        <v>44018</v>
-      </c>
-    </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A488" s="1">
-        <v>44018</v>
-      </c>
-      <c r="E488" s="1">
-        <v>0</v>
-      </c>
-      <c r="G488" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A489" s="1">
-        <v>44019</v>
-      </c>
-      <c r="G489" t="s">
-        <v>595</v>
-      </c>
-      <c r="H489" s="1">
-        <v>44020</v>
-      </c>
-    </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A490" s="1">
-        <v>44020</v>
-      </c>
-      <c r="E490" s="1">
-        <v>0</v>
-      </c>
-      <c r="G490" t="s">
-        <v>596</v>
-      </c>
-      <c r="H490" s="1">
-        <v>44021</v>
-      </c>
-    </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A491" s="1">
-        <v>44021</v>
-      </c>
-      <c r="G491" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A492" s="1">
-        <v>44022</v>
-      </c>
-      <c r="G492" t="s">
-        <v>598</v>
-      </c>
-      <c r="H492" s="1">
-        <v>44023</v>
-      </c>
-    </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A493" s="1">
-        <v>44023</v>
-      </c>
-      <c r="E493" s="1">
-        <v>0</v>
-      </c>
-      <c r="G493" t="s">
-        <v>599</v>
-      </c>
-      <c r="H493" s="1">
-        <v>44024</v>
-      </c>
-    </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A494" s="1">
-        <v>44024</v>
-      </c>
-      <c r="G494" t="s">
-        <v>600</v>
-      </c>
-      <c r="H494" s="1">
-        <v>44025</v>
-      </c>
-    </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A495" s="1">
-        <v>44025</v>
-      </c>
-      <c r="E495" s="1">
-        <v>0</v>
-      </c>
-      <c r="G495" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="496" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A496" s="6">
-        <v>44026</v>
-      </c>
-      <c r="B496" s="7"/>
-      <c r="F496" s="7"/>
-      <c r="G496" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="H496" s="6">
-        <v>44027</v>
-      </c>
-    </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A497" s="1">
-        <v>44027</v>
-      </c>
-      <c r="E497" s="1">
-        <v>0</v>
-      </c>
-      <c r="G497" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A498" s="1">
-        <v>44028</v>
-      </c>
-      <c r="G498" t="s">
-        <v>603</v>
-      </c>
-      <c r="H498" s="1">
-        <v>44029</v>
-      </c>
-    </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A499" s="1">
-        <v>44029</v>
-      </c>
-      <c r="G499" t="s">
-        <v>604</v>
-      </c>
-      <c r="H499" s="1">
-        <v>44030</v>
-      </c>
-    </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A500" s="1">
-        <v>44030</v>
-      </c>
-      <c r="G500" t="s">
-        <v>605</v>
-      </c>
-      <c r="H500" s="1">
-        <v>44031</v>
-      </c>
-    </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A501" s="1">
-        <v>44031</v>
-      </c>
-      <c r="G501" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A502" s="1">
-        <v>44032</v>
-      </c>
-      <c r="G502" t="s">
-        <v>606</v>
-      </c>
-      <c r="H502" s="1">
-        <v>44033</v>
-      </c>
-    </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A503" s="1">
-        <v>44033</v>
-      </c>
-      <c r="G503" t="s">
-        <v>607</v>
-      </c>
-      <c r="H503" s="1">
-        <v>44034</v>
-      </c>
-    </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A504" s="1">
-        <v>44034</v>
-      </c>
-      <c r="G504" t="s">
-        <v>608</v>
-      </c>
-      <c r="H504" s="1">
-        <v>44035</v>
-      </c>
-    </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A505" s="1">
-        <v>44035</v>
-      </c>
-      <c r="G505" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A506" s="1">
-        <v>44036</v>
-      </c>
-      <c r="G506" t="s">
-        <v>609</v>
-      </c>
-      <c r="H506" s="1">
-        <v>44037</v>
-      </c>
-    </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A507" s="1">
-        <v>44037</v>
-      </c>
-      <c r="G507" t="s">
-        <v>639</v>
-      </c>
-      <c r="H507" s="1">
-        <v>44038</v>
-      </c>
-    </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A508" s="1">
-        <v>44038</v>
-      </c>
-      <c r="G508" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A509" s="1">
-        <v>44039</v>
-      </c>
-      <c r="G509" t="s">
-        <v>611</v>
-      </c>
-      <c r="H509" s="1">
-        <v>44040</v>
-      </c>
-    </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A510" s="1">
-        <v>44040</v>
-      </c>
-      <c r="G510" t="s">
-        <v>612</v>
-      </c>
-      <c r="H510" s="1">
-        <v>44041</v>
-      </c>
-    </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A511" s="1">
-        <v>44041</v>
-      </c>
-      <c r="G511" t="s">
-        <v>613</v>
-      </c>
-      <c r="H511" s="1">
-        <v>44042</v>
-      </c>
-    </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A512" s="1">
-        <v>44042</v>
-      </c>
-      <c r="G512" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A513" s="1">
-        <v>44043</v>
-      </c>
-      <c r="G513" t="s">
-        <v>614</v>
-      </c>
-      <c r="H513" s="1">
-        <v>44044</v>
-      </c>
-    </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A514" s="1">
-        <v>44044</v>
-      </c>
-      <c r="G514" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A515" s="1">
-        <v>44045</v>
-      </c>
-      <c r="G515" t="s">
-        <v>616</v>
-      </c>
-      <c r="H515" s="1">
-        <v>44046</v>
-      </c>
-    </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A516" s="1">
-        <v>44046</v>
-      </c>
-      <c r="G516" t="s">
-        <v>617</v>
-      </c>
-      <c r="H516" s="1">
-        <v>44047</v>
-      </c>
-    </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A517" s="1">
-        <v>44047</v>
-      </c>
-      <c r="G517" s="1" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A518" s="1">
-        <v>44048</v>
-      </c>
-      <c r="G518" t="s">
-        <v>642</v>
-      </c>
-      <c r="H518" s="1">
-        <v>44049</v>
-      </c>
-    </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A519" s="1">
-        <v>44049</v>
-      </c>
-      <c r="G519" t="s">
-        <v>618</v>
-      </c>
-      <c r="H519" s="1">
-        <v>44050</v>
-      </c>
-    </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A520" s="1">
-        <v>44050</v>
-      </c>
-      <c r="G520" t="s">
-        <v>619</v>
-      </c>
-      <c r="H520" s="1">
-        <v>44051</v>
-      </c>
-    </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A521" s="1">
-        <v>44051</v>
-      </c>
-      <c r="G521" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="522" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A522" s="1">
-        <v>44052</v>
-      </c>
-      <c r="B522" s="7"/>
-      <c r="F522" s="7"/>
-      <c r="G522" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="H522" s="1">
-        <v>44053</v>
-      </c>
-    </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A523" s="1">
-        <v>44053</v>
-      </c>
-      <c r="G523" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="H523" s="1">
-        <v>44054</v>
-      </c>
-    </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A524" s="1">
-        <v>44054</v>
-      </c>
-      <c r="G524" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="H524" s="1">
-        <v>44055</v>
-      </c>
-    </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A525" s="1">
-        <v>44055</v>
-      </c>
-      <c r="G525" s="1" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A526" s="1">
-        <v>44056</v>
-      </c>
-      <c r="G526" t="s">
-        <v>623</v>
-      </c>
-      <c r="H526" s="1">
-        <v>44057</v>
-      </c>
-    </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A527" s="1">
-        <v>44057</v>
-      </c>
-      <c r="G527" t="s">
-        <v>645</v>
-      </c>
-      <c r="H527" s="1">
-        <v>44058</v>
-      </c>
-    </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A528" s="1">
-        <v>44058</v>
-      </c>
-      <c r="G528" t="s">
-        <v>624</v>
-      </c>
-      <c r="H528" s="1">
-        <v>44059</v>
-      </c>
-    </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A529" s="1">
-        <v>44059</v>
-      </c>
-      <c r="G529" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A530" s="1">
-        <v>44060</v>
-      </c>
-      <c r="G530" t="s">
-        <v>625</v>
-      </c>
-      <c r="H530" s="1">
-        <v>44061</v>
-      </c>
-    </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A531" s="1">
-        <v>44061</v>
-      </c>
-      <c r="G531" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A532" s="1">
-        <v>44062</v>
-      </c>
-      <c r="G532" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A533" s="1">
-        <v>44063</v>
-      </c>
-      <c r="G533" t="s">
-        <v>626</v>
-      </c>
-      <c r="H533" s="1">
-        <v>44064</v>
-      </c>
-    </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A534" s="1">
-        <v>44064</v>
-      </c>
-      <c r="G534" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A535" s="1">
-        <v>44065</v>
-      </c>
-      <c r="G535" t="s">
-        <v>650</v>
-      </c>
-      <c r="H535" s="1">
-        <v>44066</v>
-      </c>
-    </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A536" s="1">
-        <v>44066</v>
-      </c>
-      <c r="G536" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A537" s="1">
-        <v>44067</v>
-      </c>
-      <c r="G537" t="s">
-        <v>628</v>
-      </c>
-      <c r="H537" s="1">
-        <v>44068</v>
-      </c>
-    </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A538" s="1">
-        <v>44068</v>
-      </c>
-      <c r="G538" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="539" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A539" s="1">
-        <v>44069</v>
-      </c>
-      <c r="B539" s="7"/>
-      <c r="F539" s="7"/>
-      <c r="G539" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="H539" s="1">
-        <v>44070</v>
-      </c>
-    </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A540" s="1">
-        <v>44070</v>
-      </c>
-      <c r="G540" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="H540" s="1">
-        <v>44071</v>
-      </c>
-    </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A541" s="1">
-        <v>44071</v>
-      </c>
-      <c r="G541" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="H541" s="1">
-        <v>44071</v>
-      </c>
-    </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A542" s="1">
-        <v>44071</v>
-      </c>
-      <c r="G542" s="1" t="s">
-        <v>651</v>
+        <v>0</v>
+      </c>
+      <c r="I486" s="1">
+        <v>0</v>
+      </c>
+      <c r="J486" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -17109,6 +16866,917 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="6">
+        <v>44001</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="H1" s="6">
+        <v>44002</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1">
+        <v>44002</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="1">
+        <v>44003</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" t="s">
+        <v>581</v>
+      </c>
+      <c r="H3" s="1">
+        <v>44004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="1">
+        <v>44004</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="1">
+        <v>44005</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" t="s">
+        <v>582</v>
+      </c>
+      <c r="H5" s="1">
+        <v>44006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="1">
+        <v>44006</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" t="s">
+        <v>583</v>
+      </c>
+      <c r="H6" s="1">
+        <v>44007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="1">
+        <v>44007</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="1">
+        <v>44008</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" t="s">
+        <v>633</v>
+      </c>
+      <c r="H8" s="1">
+        <v>44009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="1">
+        <v>44009</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" t="s">
+        <v>585</v>
+      </c>
+      <c r="H9" s="1">
+        <v>44010</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="1">
+        <v>44010</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" t="s">
+        <v>586</v>
+      </c>
+      <c r="H10" s="1">
+        <v>44011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1">
+        <v>44011</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1">
+        <v>44012</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" t="s">
+        <v>588</v>
+      </c>
+      <c r="H12" s="1">
+        <v>44013</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1">
+        <v>44013</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" t="s">
+        <v>589</v>
+      </c>
+      <c r="H13" s="1">
+        <v>44014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1">
+        <v>44014</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1">
+        <v>44015</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" t="s">
+        <v>591</v>
+      </c>
+      <c r="H15" s="1">
+        <v>44016</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
+        <v>44016</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" t="s">
+        <v>592</v>
+      </c>
+      <c r="H16" s="1">
+        <v>44017</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
+        <v>44017</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" t="s">
+        <v>593</v>
+      </c>
+      <c r="H17" s="1">
+        <v>44018</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
+        <v>44018</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
+        <v>44019</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" t="s">
+        <v>594</v>
+      </c>
+      <c r="H19" s="1">
+        <v>44020</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
+        <v>44020</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" t="s">
+        <v>595</v>
+      </c>
+      <c r="H20" s="1">
+        <v>44021</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
+        <v>44021</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
+        <v>44022</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" t="s">
+        <v>597</v>
+      </c>
+      <c r="H22" s="1">
+        <v>44023</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
+        <v>44023</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" t="s">
+        <v>598</v>
+      </c>
+      <c r="H23" s="1">
+        <v>44024</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
+        <v>44024</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" t="s">
+        <v>599</v>
+      </c>
+      <c r="H24" s="1">
+        <v>44025</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
+        <v>44025</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="6">
+        <v>44026</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="H26" s="6">
+        <v>44027</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
+        <v>44027</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
+        <v>44028</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" t="s">
+        <v>602</v>
+      </c>
+      <c r="H28" s="1">
+        <v>44029</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
+        <v>44029</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" t="s">
+        <v>603</v>
+      </c>
+      <c r="H29" s="1">
+        <v>44030</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
+        <v>44030</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" t="s">
+        <v>604</v>
+      </c>
+      <c r="H30" s="1">
+        <v>44031</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
+        <v>44031</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
+        <v>44032</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" t="s">
+        <v>605</v>
+      </c>
+      <c r="H32" s="1">
+        <v>44033</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>44033</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" t="s">
+        <v>606</v>
+      </c>
+      <c r="H33" s="1">
+        <v>44034</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
+        <v>44034</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" t="s">
+        <v>607</v>
+      </c>
+      <c r="H34" s="1">
+        <v>44035</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="1">
+        <v>44035</v>
+      </c>
+      <c r="B35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="1">
+        <v>44036</v>
+      </c>
+      <c r="B36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" t="s">
+        <v>608</v>
+      </c>
+      <c r="H36" s="1">
+        <v>44037</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="1">
+        <v>44037</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" t="s">
+        <v>638</v>
+      </c>
+      <c r="H37" s="1">
+        <v>44038</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="1">
+        <v>44038</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="1">
+        <v>44039</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" t="s">
+        <v>610</v>
+      </c>
+      <c r="H39" s="1">
+        <v>44040</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="1">
+        <v>44040</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" t="s">
+        <v>611</v>
+      </c>
+      <c r="H40" s="1">
+        <v>44041</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="1">
+        <v>44041</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" t="s">
+        <v>612</v>
+      </c>
+      <c r="H41" s="1">
+        <v>44042</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="1">
+        <v>44042</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="1">
+        <v>44043</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" t="s">
+        <v>613</v>
+      </c>
+      <c r="H43" s="1">
+        <v>44044</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="1">
+        <v>44044</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="1">
+        <v>44045</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" t="s">
+        <v>615</v>
+      </c>
+      <c r="H45" s="1">
+        <v>44046</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>44046</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" t="s">
+        <v>616</v>
+      </c>
+      <c r="H46" s="1">
+        <v>44047</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" s="1" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A47" s="1">
+        <v>44047</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="1">
+        <v>44048</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" t="s">
+        <v>641</v>
+      </c>
+      <c r="H48" s="1">
+        <v>44049</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="1">
+        <v>44049</v>
+      </c>
+      <c r="B49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" t="s">
+        <v>617</v>
+      </c>
+      <c r="H49" s="1">
+        <v>44050</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A50" s="1">
+        <v>44050</v>
+      </c>
+      <c r="B50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" t="s">
+        <v>618</v>
+      </c>
+      <c r="H50" s="1">
+        <v>44051</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="1">
+        <v>44051</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" s="6" customFormat="1" ht="94.5" x14ac:dyDescent="0.15">
+      <c r="A52" s="1">
+        <v>44052</v>
+      </c>
+      <c r="B52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="H52" s="1">
+        <v>44053</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" s="1" customFormat="1" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>44053</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="H53" s="1">
+        <v>44054</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" s="1" customFormat="1" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>44054</v>
+      </c>
+      <c r="B54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H54" s="1">
+        <v>44055</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" s="1" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A55" s="1">
+        <v>44055</v>
+      </c>
+      <c r="B55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A56" s="1">
+        <v>44056</v>
+      </c>
+      <c r="B56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" t="s">
+        <v>622</v>
+      </c>
+      <c r="H56" s="1">
+        <v>44057</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>44057</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" t="s">
+        <v>644</v>
+      </c>
+      <c r="H57" s="1">
+        <v>44058</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="1">
+        <v>44058</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" t="s">
+        <v>623</v>
+      </c>
+      <c r="H58" s="1">
+        <v>44059</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A59" s="1">
+        <v>44059</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="1">
+        <v>44060</v>
+      </c>
+      <c r="B60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" t="s">
+        <v>624</v>
+      </c>
+      <c r="H60" s="1">
+        <v>44061</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="1">
+        <v>44061</v>
+      </c>
+      <c r="B61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="1">
+        <v>44062</v>
+      </c>
+      <c r="B62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="1">
+        <v>44063</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" t="s">
+        <v>625</v>
+      </c>
+      <c r="H63" s="1">
+        <v>44064</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A64" s="1">
+        <v>44064</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
+        <v>44065</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" t="s">
+        <v>649</v>
+      </c>
+      <c r="H65" s="1">
+        <v>44066</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A66" s="1">
+        <v>44066</v>
+      </c>
+      <c r="B66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
+        <v>44067</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" t="s">
+        <v>627</v>
+      </c>
+      <c r="H67" s="1">
+        <v>44068</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="1">
+        <v>44068</v>
+      </c>
+      <c r="B68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" s="6" customFormat="1" ht="81" x14ac:dyDescent="0.15">
+      <c r="A69" s="1">
+        <v>44069</v>
+      </c>
+      <c r="B69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="H69" s="1">
+        <v>44070</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" s="1" customFormat="1" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A70" s="1">
+        <v>44070</v>
+      </c>
+      <c r="B70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="H70" s="1">
+        <v>44071</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" s="1" customFormat="1" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A71" s="1">
+        <v>44071</v>
+      </c>
+      <c r="B71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="H71" s="1">
+        <v>44071</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="1" customFormat="1" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A72" s="1">
+        <v>44071</v>
+      </c>
+      <c r="B72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AQ33"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -17119,135 +17787,135 @@
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.15">
       <c r="B1" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="AN1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>550</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.15">
@@ -17257,62 +17925,62 @@
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.15">
@@ -17322,84 +17990,84 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B17" s="5"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B26" s="5"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.15">

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -1015,1203 +1015,1203 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>风带来了你的讯息..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这种枯燥的工作,果然还是需要你的陪伴,今天过来是想干什么呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你发现了奇怪的食材,请一定要告诉我。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个小镇里应该有一个古代遗迹的,但是我怎么也找不到。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里真是一个神奇的地方,你知道吗,在小镇的四周竟然分布着四季。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意,不要走得太远,外面可是有很多可怕的怪物。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好孩子饮食要均衡哦,不论是蔬菜还是肉类都不能挑食。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果有一天你要组成家庭,那么你一定要到这里购买家具啊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果可以的话,希望你能多来找格吉尔玩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的妈妈好厉害的,很多料理都是她自己发明的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呵呵,和你说这么多,你也不懂吧,像你这种小孩子还要多多进行人生历练啊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近师父获得了一些魔法药剂的配方,我们正在收集材料调配。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一定不要吝啬装备哦,即使不用的装备也可以售卖获得金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传说中这个世界曾经被魔族统治,不知道是不是真的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虽然我的道具屋里都是些过时的老东西,但是很用哦。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果遇到了危险,一定要向我求助,我可是时刻准备着。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的女儿可是我的心肝宝贝,你可不要想轻易就将他们欺骗到手。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法=百分之九九的天赋+百分之一的努力,所以你似乎无法成为魔法师了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经过我的研究,我推断在远古时代有一个伟大的文明,但是不知为何消失了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我其实一直在锻炼,因为我知道有一天命运会安排我成为救世主。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>见到你,多莉丝真高兴,真像能和你一样到处去玩。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可爱的小家伙们,今天又来问候我啊,真的谢谢你们了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我一定要成为将军那样强大的军人,为此我得坚持锻炼。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
+  </si>
+  <si>
+    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在那场战争中,本来王国军处于劣势,但是凭着我的活跃表现,才逆转获得胜利。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你喜欢吃什么料理呢？奥蒂莉亚喜欢烤海鲜噢。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真高兴你能来找我玩,明天你还会来吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在这个宁静的小镇,我找到了久违的安心,我想我还会再住一阵子吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>究竟怎样才能和是否一样优秀呢？这真让我困扰。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我一定要把布拉德利培养成一个优秀的男人,这就是我生活的意义。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我曾经走过大山和大海,追寻财富的脚步永不停息,你能理解吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作料理一定要有想象力,只有这样才能将美味融入其中。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>像我这样的天才果然不应该困在这种小店里吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没必要活得太累,偶尔停下脚步欣赏一下自然也是很好的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果不是那件事,王国的军队的总司令官非我莫属了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不管下雨还是晴天,我觉得每一天的天气都很好,你觉得呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实班尼迪克先生不是你看到的那样,他也有温柔的一面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天都要记得喂养动物啊,不要让他们挨饿。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和你说一会话,真的很轻松,可是我还有工作,不能在和你再聊了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>师父是个大美人吧,不过你可不要打她的主意哦,师父可不是你能驾驭的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你学会了制作的话,你就可以自己制作装备了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在这个世界上除了人类还有一些奇怪的种族,可是为什么是人类占据了大陆呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你听到了什么？可不要到处乱说啊,这都是我们年轻时发生的事。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实一个人站岗也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>想不到还会有年轻人来找我这个老头子聊天,真令人高兴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其实水里也有很多有意思的地方,如果你能在水里生存的话……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欢迎光临，有什么需要的吗</t>
+  </si>
+  <si>
+    <t>如果每天都能下雨就好了，这样就不需要为植物浇水了。</t>
+  </si>
+  <si>
+    <t>种植是很有学问的,一定要在合适的季节种植作物哦,\n否则作物的生长时间会变的很长。</t>
+  </si>
+  <si>
+    <t>我要好好帮助玛德琳奶奶。</t>
+  </si>
+  <si>
+    <t>你好呀，小家伙，需要我的帮助吗？</t>
+  </si>
+  <si>
+    <t>帕特里克那个老固执在干什么呢？..明明过去那么久了…</t>
+  </si>
+  <si>
+    <t>布莱兹是个好孩子，如果他的父母还在的话…</t>
+  </si>
+  <si>
+    <t>年轻真好呀，要好好享受生活哟..</t>
+  </si>
+  <si>
+    <t>有烦心事的话，来和奶奶说，我会帮助你的。</t>
+  </si>
+  <si>
+    <t>做一个好农夫也不容易呢，要加油哦！</t>
+  </si>
+  <si>
+    <t>你好，有什么事吗？</t>
+  </si>
+  <si>
+    <t>格吉尔总是想着去冒险，我还是希望他能在小镇安稳的生活。</t>
+  </si>
+  <si>
+    <t>平静的生活就是最大的幸福，你觉得的呢？</t>
+  </si>
+  <si>
+    <t>我很喜欢和动物们相处，它们既单纯又可爱。</t>
+  </si>
+  <si>
+    <t>准备干些什么？</t>
+  </si>
+  <si>
+    <t>相比温顺的动物，我更喜欢能和我一起战斗的伙伴。</t>
+  </si>
+  <si>
+    <t>你如果要去冒险的话，一定要带上我呀。</t>
+  </si>
+  <si>
+    <t>有的人天生就是主角，你看我像不像，哈哈。</t>
+  </si>
+  <si>
+    <t>风儿带来了你的讯息，你有什么想要倾诉？</t>
+  </si>
+  <si>
+    <t>人的生命如此短暂，你是否已经准备好接受自己的命运…</t>
+  </si>
+  <si>
+    <t>高山之后是大海，大海之边是高山，不知山海相连何处是尽头…</t>
+  </si>
+  <si>
+    <t>人无法跨过两次同一条河流，那么河里的鱼是否相同…</t>
+  </si>
+  <si>
+    <t>美丽的人啊，偎依在河岸，我只敢远远欣赏不敢靠近，害怕，你那美丽的面庞将我的眼睛灼伤…</t>
+  </si>
+  <si>
+    <t>愿主保佑你，想要祈祷什么？</t>
+  </si>
+  <si>
+    <t>一切存在都源自内心，如果希望世界更好，那么就让自己的内心更纯净吧。</t>
+  </si>
+  <si>
+    <t>现在的年轻人都不知道敬畏上帝了，平时都不来礼拜了。</t>
+  </si>
+  <si>
+    <t>愿主的荣光照耀在你身上。</t>
+  </si>
+  <si>
+    <t>希望每一个远行的人都能平安的归来…</t>
+  </si>
+  <si>
+    <t>命运还是要把握在自己手里，想知道什么？</t>
+  </si>
+  <si>
+    <t>我知道很多，但我不能都告诉你。</t>
+  </si>
+  <si>
+    <t>从远方而来的人啊，你的故乡在何处，你可知你的真名，我在此等候你的倾诉..</t>
+  </si>
+  <si>
+    <t>年轻人，探索精神固然可贵，但不要盲目冒险呐。</t>
+  </si>
+  <si>
+    <t>即使知道了命运，依然能够笑着面对的人才是真正的勇士。</t>
+  </si>
+  <si>
+    <t>你好呀，想要点什么吗？</t>
+  </si>
+  <si>
+    <t>尽管每天都很忙，但我们都很快乐。</t>
+  </si>
+  <si>
+    <t>美食和美景都不能错过。</t>
+  </si>
+  <si>
+    <t>你笑起来真好看，多笑笑嘛。</t>
+  </si>
+  <si>
+    <t>平时多出来和我们一起玩吧，不要老呆在家里嘛。</t>
+  </si>
+  <si>
+    <t>你好，今天也很精神呀，需要我做什么吗？</t>
+  </si>
+  <si>
+    <t>班尼迪克先生是个好人。</t>
+  </si>
+  <si>
+    <t>一切安好，也希望你也能开开心心。</t>
+  </si>
+  <si>
+    <t>有什么可以为你服务的吗？</t>
+  </si>
+  <si>
+    <t>今天也是平静而美好的。</t>
+  </si>
+  <si>
+    <t>看着环境变得干净卫生，我会很舒心。</t>
+  </si>
+  <si>
+    <t>是你啊，有事的话，请尽管吩咐。</t>
+  </si>
+  <si>
+    <t>如果能发挥我的特长的话就太好了。</t>
+  </si>
+  <si>
+    <t>这个小镇能如此安宁是很多人付出的结果。</t>
+  </si>
+  <si>
+    <t>守护家人是我的职责。</t>
+  </si>
+  <si>
+    <t>其实回到这个养育我的小镇，我很开心。</t>
+  </si>
+  <si>
+    <t>哟，找我有事？</t>
+  </si>
+  <si>
+    <t>真是无聊，这样的日子何时才能结束。</t>
+  </si>
+  <si>
+    <t>看着别人四处旅行，我却只能在这里，真羡慕啊。</t>
+  </si>
+  <si>
+    <t>如果以后你要出去旅行的话，希望我们可以同行。</t>
+  </si>
+  <si>
+    <t>我已经准备了很久行囊，就是没有机会出发。</t>
+  </si>
+  <si>
+    <t>你是来找我的吗？不知道能为你做些什么？</t>
+  </si>
+  <si>
+    <t>我有一个感觉，这个小镇是我的归宿。</t>
+  </si>
+  <si>
+    <t>繁华终归会褪去，回归平淡才是真正的人生。</t>
+  </si>
+  <si>
+    <t>虽然我的魔力还不够，但我会努力的，你有什么需要我的？</t>
+  </si>
+  <si>
+    <t>究竟怎样才能和师父一样优秀呢？这真让我困扰。</t>
+  </si>
+  <si>
+    <t>我的梦想是成为一个大魔导师。</t>
+  </si>
+  <si>
+    <t>是遇到什么疑难了吗？</t>
+  </si>
+  <si>
+    <t>别看我单身一人，年轻时候的我也是很受欢迎的。</t>
+  </si>
+  <si>
+    <t>看见你，就想让我想到了年轻时候的我，真怀念呐。</t>
+  </si>
+  <si>
+    <t>我不会拒绝对弱者的怜悯，所以你有什么事？</t>
+  </si>
+  <si>
+    <t>这个小镇虽然不是很繁华，但我却很喜欢。</t>
+  </si>
+  <si>
+    <t>你想来找我学习贵族礼仪吗?</t>
+  </si>
+  <si>
+    <t>你愿意来找我，我心里还是有一点高兴的。</t>
+  </si>
+  <si>
+    <t>可不要误会，这只是基本的贵族礼仪。</t>
+  </si>
+  <si>
+    <t>你想要了解魔法的力量吗？</t>
+  </si>
+  <si>
+    <t>魔法的力量远超你的想象，</t>
+  </si>
+  <si>
+    <t>嗨，有啥事？</t>
+  </si>
+  <si>
+    <t>要想获得丰厚的渔获，必须要打理好网具。</t>
+  </si>
+  <si>
+    <t>这个小镇靠近大海，可以时常吃到一些海鲜菜肴。</t>
+  </si>
+  <si>
+    <t>据说大海的深处有美人鱼，不知道是不是真的。</t>
+  </si>
+  <si>
+    <t>如果你有时间的话，学习一下钓鱼吧，你会很有收获。</t>
+  </si>
+  <si>
+    <t>你找我是有什么事？</t>
+  </si>
+  <si>
+    <t>这个镇子虽小，却拥有完善的海港，常有舰船航行往来于各大陆之间。</t>
+  </si>
+  <si>
+    <t>经历了长时间的海上漂泊，我需要在岸上好好休息一下。</t>
+  </si>
+  <si>
+    <t>大海里有很多财富，也有很多风险。</t>
+  </si>
+  <si>
+    <t>你如果想去海那边，可以乘坐我的船。</t>
+  </si>
+  <si>
+    <t>找我吗？我也可以为你做事吗？</t>
+  </si>
+  <si>
+    <t>乘船出海游遍世界一直是我的愿望。</t>
+  </si>
+  <si>
+    <t>虽然海上的生活令人神往，但在这个小镇也还不错。</t>
+  </si>
+  <si>
+    <t>大家都很努力啊，我也不能懈怠。</t>
+  </si>
+  <si>
+    <t>如果我也有自己的船就好了。</t>
+  </si>
+  <si>
+    <t>静待你的委托</t>
+  </si>
+  <si>
+    <t>别人的秘密，何必要探究到底呢，只要不危害大家就好了。</t>
+  </si>
+  <si>
+    <t>你好，你想知道什么吗？</t>
+  </si>
+  <si>
+    <t>如果四季可以同时存在，会发生什么呢…</t>
+  </si>
+  <si>
+    <t>需要我的帮忙吗？</t>
+  </si>
+  <si>
+    <t>虽然我对神依然很崇敬，但我还是想干些其他的事情。</t>
+  </si>
+  <si>
+    <t>在战斗中祈求上帝是没有用了，我们只能依靠自己。</t>
+  </si>
+  <si>
+    <t>不知道上帝能不能听到我的心声，让我早日得偿所愿。</t>
+  </si>
+  <si>
+    <t>无论信不信上帝，都要坚守爱与和平。</t>
+  </si>
+  <si>
+    <t>我可以为你做些什么？</t>
+  </si>
+  <si>
+    <t>其实一个人巡逻也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
+  </si>
+  <si>
+    <t>很高兴能为你服务。</t>
+  </si>
+  <si>
+    <t>守护小姐是我的职责。</t>
+  </si>
+  <si>
+    <t>在这个镇子里，我经常会想起关于老主人的事。</t>
+  </si>
+  <si>
+    <t>回想过去，好像刚刚发生在昨天，那时小姐还是个孩子…</t>
+  </si>
+  <si>
+    <t>如果有更多的人陪伴小姐，小姐应该会更开心吧</t>
+  </si>
+  <si>
+    <t>如果有什么事情，我会尽力而为。</t>
+  </si>
+  <si>
+    <t>一个料理如果缺少调味料，就会寡淡无味，不要忘记购买呀。</t>
+  </si>
+  <si>
+    <t>好的装备可以大大促进劳动效率，我需要做什么？</t>
+  </si>
+  <si>
+    <t>我一定要把布拉德利培养成一个优秀的人,这就是我生活的意义。</t>
+  </si>
+  <si>
+    <t>布拉德利再长大一些的话，我会让他自己选择自己的道路。</t>
+  </si>
+  <si>
+    <t>你好，需要什么服务吗？</t>
+  </si>
+  <si>
+    <t>姐姐应该有更广阔的前景的，现在却被困住这个小镇…</t>
+  </si>
+  <si>
+    <t>如果我能更强大一些的话，姐姐就可以去追求自己的梦想了。</t>
+  </si>
+  <si>
+    <t>你可以帮助我，鼓励我一直坚强吗？</t>
+  </si>
+  <si>
+    <t>如果你愿意的话，可以随时来找我和我的姐姐。</t>
+  </si>
+  <si>
+    <t>有什么搞不定的事情？</t>
+  </si>
+  <si>
+    <t>注意,不要走得太远,外面可是有很多怪物。</t>
+  </si>
+  <si>
+    <t>听说你在征讨小镇周边的怪物，做的不错。</t>
+  </si>
+  <si>
+    <t>招待不周了，有什么事情吗？</t>
+  </si>
+  <si>
+    <t>有妹妹和妈妈陪着我，我觉得很幸福。</t>
+  </si>
+  <si>
+    <t>如果爸爸还在的话…</t>
+  </si>
+  <si>
+    <t>我要努力支撑我的家，可以为我加油吗？</t>
+  </si>
+  <si>
+    <t>可有什么事情需要我为你而做的？</t>
+  </si>
+  <si>
+    <t>纺织可是化腐朽为神奇的技术。</t>
+  </si>
+  <si>
+    <t>如果你想学习纺织技术的话，我可以教你。</t>
+  </si>
+  <si>
+    <t>我有时也会为缺少传承而烦恼呢。</t>
+  </si>
+  <si>
+    <t>相比能赚到钱，我更希望有人可以将我的技术传承下去。</t>
+  </si>
+  <si>
+    <t>我拥有的比你知道的还多，你有什么需要的吗？</t>
+  </si>
+  <si>
+    <t>固守成见是不行的，只有变革才能带来新的机遇。</t>
+  </si>
+  <si>
+    <t>放心吧，你的外公只是去了他想去的地方。</t>
+  </si>
+  <si>
+    <t>好好在这里生活吧，你的外公也会很欣慰的。</t>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+  </si>
+  <si>
+    <t>格吉尔</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+  </si>
+  <si>
+    <t>别墅二楼</t>
+  </si>
+  <si>
+    <t>酒馆卧室</t>
+  </si>
+  <si>
+    <t>植物店</t>
+  </si>
+  <si>
+    <t>教堂</t>
+  </si>
+  <si>
+    <t>村公所卧室</t>
+  </si>
+  <si>
+    <t>后山</t>
+  </si>
+  <si>
+    <t>俱乐部阁楼</t>
+  </si>
+  <si>
+    <t>客栈二楼</t>
+  </si>
+  <si>
+    <t>武器店</t>
+  </si>
+  <si>
+    <t>船坞</t>
+  </si>
+  <si>
+    <t>我的农场</t>
+  </si>
+  <si>
+    <t>村公所大厅</t>
+  </si>
+  <si>
+    <t>工坊</t>
+  </si>
+  <si>
+    <t>畜牧店</t>
+  </si>
+  <si>
+    <t>俱乐部</t>
+  </si>
+  <si>
+    <t>塔楼顶部</t>
+  </si>
+  <si>
+    <t>家具店偏室</t>
+  </si>
+  <si>
+    <t>山坡</t>
+  </si>
+  <si>
+    <t>水车房内部</t>
+  </si>
+  <si>
+    <t>小木屋</t>
+  </si>
+  <si>
+    <t>家具店</t>
+  </si>
+  <si>
+    <t>中央广场</t>
+  </si>
+  <si>
+    <t>纺织店</t>
+  </si>
+  <si>
+    <t>商店街</t>
+  </si>
+  <si>
+    <t>塔楼</t>
+  </si>
+  <si>
+    <t>治安室</t>
+  </si>
+  <si>
+    <t>占卜屋</t>
+  </si>
+  <si>
+    <t>帐篷内部</t>
+  </si>
+  <si>
+    <t>风车内部</t>
+  </si>
+  <si>
+    <t>客栈一楼</t>
+  </si>
+  <si>
+    <t>码头</t>
+  </si>
+  <si>
+    <t>鱼摊内部</t>
+  </si>
+  <si>
+    <t>船坞二层</t>
+  </si>
+  <si>
+    <t>住宅区</t>
+  </si>
+  <si>
+    <t>别墅大厅</t>
+  </si>
+  <si>
+    <t>教堂二楼</t>
+  </si>
+  <si>
+    <t>酒馆</t>
+  </si>
+  <si>
+    <t>村公所宴会厅</t>
+  </si>
+  <si>
+    <t>科学研究室</t>
+  </si>
+  <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>城门</t>
+  </si>
+  <si>
+    <t>武器店二楼</t>
+  </si>
+  <si>
+    <t>许可清单你可以随时去看看。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那么，现在我应该做些什么呢？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从最简单的售卖开始吧，看到前面的柜台了么,将东西放到上面就行了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对了，有些商品只能放在特定柜台上，你可以仔细观察一下。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好，现在去把商店的招牌换成营业吧，只有营业状态时才会有客人上门。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做的不错，你可以再熟悉一下售卖商品，我在外面等你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>植物店里拥有各种植物种子,来跟我去熟悉熟悉吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这就是新来小镇的孩子吧，欢迎你哟，想来点什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买好了种子了，我们回农场种植吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>植物生长需要几天时间,在此期间,不如去野外探险一下,也许会获得想不到的收获哦。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看来你已经掌握了售卖物品的方法了,如此一来,你的种植许可也开放了,那么现在去买一些种子回来吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等一下，我这里有一些种植工具，送给你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一步,先将农具从背包里拿出来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在走到农田上，使用锄头将田地锄松吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好,就是这样,现在选择种子进行播种吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>别急,还差最后一步呢,种下的植物需要浇水,现在去河边打水回来。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head/OldWoman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谢谢，我会好好使用的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里就是农场，以后就归你管理了,现在准备种植吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前面就是春之山脉的入口，今天就让我这个老头子陪你闯一下吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在前进走到光圈中，开始今天的探索。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打起精神来，现在前进吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我没有镰刀，没办法收割</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年轻人，这小镇的清晨不错吧？</t>
+  </si>
+  <si>
+    <t>嗯，空气很清新。</t>
+  </si>
+  <si>
+    <t>我正考虑给店里进些新货，你有啥建议？</t>
+  </si>
+  <si>
+    <t>你看着挺精神，昨晚休息得好？</t>
+  </si>
+  <si>
+    <t>还可以。您这店每天很早就开门吗？</t>
+  </si>
+  <si>
+    <t>对，习惯了。你要是有空可以来帮忙整理下。</t>
+  </si>
+  <si>
+    <t>你初来乍到，有没有去小镇周边转转？</t>
+  </si>
+  <si>
+    <t>还没有。周边有什么好玩的地方吗？</t>
+  </si>
+  <si>
+    <t>有个小湖泊，景色很美。你可以去看看。</t>
+  </si>
+  <si>
+    <t>我店里新到了一些家具，你想看看吗？</t>
+  </si>
+  <si>
+    <t>现在没时间。都是些什么风格的家具？</t>
+  </si>
+  <si>
+    <t>古典和简约的都有。你有空了来品鉴下。</t>
+  </si>
+  <si>
+    <t>你在镇上有没有交到新朋友？</t>
+  </si>
+  <si>
+    <t>认识了几个。交朋友对在这生活很重要吗？</t>
+  </si>
+  <si>
+    <t>当然，朋友多了路好走。你可以多参加些活动。</t>
+  </si>
+  <si>
+    <t>我最近在研究新的家具摆放方式，你有啥想法？</t>
+  </si>
+  <si>
+    <t>我不太懂。是不是可以根据功能分区摆放？</t>
+  </si>
+  <si>
+    <t>有点道理。你要是有了新灵感随时告诉我。</t>
+  </si>
+  <si>
+    <t>你觉得小镇的居民们对家具的需求大吗？</t>
+  </si>
+  <si>
+    <t>不太清楚。应该会需要一些实用的家具吧。</t>
+  </si>
+  <si>
+    <t>我也这么认为。你帮我留意下大家的喜好。</t>
+  </si>
+  <si>
+    <t>早啊，小家伙。我正想改进家具的细节，你觉得从哪入手？</t>
+  </si>
+  <si>
+    <t>可以从打磨工艺上试试。</t>
+  </si>
+  <si>
+    <t>嗨，你看这小镇的建筑风格，对家具设计有启发吗？</t>
+  </si>
+  <si>
+    <t>我觉得可以借鉴一些线条和色彩搭配。</t>
+  </si>
+  <si>
+    <t>很有见地。你能帮我画些草图吗？</t>
+  </si>
+  <si>
+    <t>我打算用旧木材打造复古家具，你觉得可行吗？</t>
+  </si>
+  <si>
+    <t>应该可以，会很有韵味。</t>
+  </si>
+  <si>
+    <t>对。你知道哪里能找到更多旧木材吗？</t>
+  </si>
+  <si>
+    <t>你在镇上参加过手工制作的活动吗？</t>
+  </si>
+  <si>
+    <t>可以学习一些新技巧。你有兴趣的话我带你去。</t>
+  </si>
+  <si>
+    <t>我想在家具上镶嵌一些特色石头，你有推荐吗？</t>
+  </si>
+  <si>
+    <t>像玛瑙或者水晶石应该不错。</t>
+  </si>
+  <si>
+    <t>有道理。你能帮我找些性价比高的吗？</t>
+  </si>
+  <si>
+    <t>你觉得家具的舒适度和美观度怎么平衡？</t>
+  </si>
+  <si>
+    <t>先保证舒适度，再用装饰提升美观度。</t>
+  </si>
+  <si>
+    <t>我要举办一个小型家具展览，你能帮忙宣传吗？</t>
+  </si>
+  <si>
+    <t>我可以试试。需要我做什么？</t>
+  </si>
+  <si>
+    <t>我觉得淡色系比较清新。</t>
+  </si>
+  <si>
+    <t>嗯，值得考虑。你能帮我选些样板吗？</t>
+  </si>
+  <si>
+    <t>哟，早哇。我想去河边钓鱼，顺便找找灵感，一起不？</t>
+  </si>
+  <si>
+    <t>我还有事。你钓鱼能找到什么家具灵感？</t>
+  </si>
+  <si>
+    <t>比如鱼的形状和纹理可以用在装饰上。</t>
+  </si>
+  <si>
+    <t>嗨，我打算用兽皮做些特殊的家具配饰，你见过吗？</t>
+  </si>
+  <si>
+    <t>只要处理好就没问题。你有渠道获取吗？</t>
+  </si>
+  <si>
+    <t>我想在家具里安装音乐盒，一打开就有音乐，怎样？</t>
+  </si>
+  <si>
+    <t>我最近得到一些散发香味的木材，做什么家具好？</t>
+  </si>
+  <si>
+    <t>可以做个香薰柜，存放香料。</t>
+  </si>
+  <si>
+    <t>我想打造一款能折叠成小物件的家具，你觉得可能吗？</t>
+  </si>
+  <si>
+    <t>有可能，像折叠椅就很实用。</t>
+  </si>
+  <si>
+    <t>嘿，我设计了一款带有魔法储物空间的家具，神奇吧？</t>
+  </si>
+  <si>
+    <t>哇，太神奇了！怎么实现储物空间的魔法呢？</t>
+  </si>
+  <si>
+    <t>用魔法水晶驱动。你在镇上见过魔法水晶吗？</t>
+  </si>
+  <si>
+    <t>我不太清楚。我先去吃个早饭，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我今天有事。不好意思，我得走了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的。我突然想起有事，先走一步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的。我先去了，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我有点忙，先撤了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太清楚。我去打听下。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有。这类活动和家具制作有关吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我找找看。不好意思，我得赶紧走了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>让我想想再告诉你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我在研究新的涂料，你对颜色有偏好吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不太会。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挺有趣。我忙完来找你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没见过呢。这样合适吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有。要不去问问别人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">好有创意！ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你在镇上逛过那些古老的小巷吗？可以从巷子里的图案找设计灵感。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太清楚。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你知道怎么处理木材香味吗？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没见过。我去探索下。我先去了，回见。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咯咯..咯咯..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叽叽..叽叽..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘎嘎..嘎嘎..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呷呷..呷呷..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>噗呼..噗呼..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咩咩..咩咩..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哼哼..哼哼..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吱吱..吱吱..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘶嘶..嘶嘶..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>噗呼..噗呼..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咕噜..咕噜..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呦呦..呦呦..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哞～哞～</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呜～呜～</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咳咳..咳咳..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>我没有鱼竿，没法钓鱼！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我缺少鱼饵，不能钓鱼！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>风带来了你的讯息..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这种枯燥的工作,果然还是需要你的陪伴,今天过来是想干什么呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果你发现了奇怪的食材,请一定要告诉我。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这个小镇里应该有一个古代遗迹的,但是我怎么也找不到。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里真是一个神奇的地方,你知道吗,在小镇的四周竟然分布着四季。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>注意,不要走得太远,外面可是有很多可怕的怪物。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>好孩子饮食要均衡哦,不论是蔬菜还是肉类都不能挑食。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果有一天你要组成家庭,那么你一定要到这里购买家具啊。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果可以的话,希望你能多来找格吉尔玩。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我的妈妈好厉害的,很多料理都是她自己发明的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呵呵,和你说这么多,你也不懂吧,像你这种小孩子还要多多进行人生历练啊。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最近师父获得了一些魔法药剂的配方,我们正在收集材料调配。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一定不要吝啬装备哦,即使不用的装备也可以售卖获得金币。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>传说中这个世界曾经被魔族统治,不知道是不是真的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>虽然我的道具屋里都是些过时的老东西,但是很用哦。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果遇到了危险,一定要向我求助,我可是时刻准备着。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我的女儿可是我的心肝宝贝,你可不要想轻易就将他们欺骗到手。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔法=百分之九九的天赋+百分之一的努力,所以你似乎无法成为魔法师了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经过我的研究,我推断在远古时代有一个伟大的文明,但是不知为何消失了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我其实一直在锻炼,因为我知道有一天命运会安排我成为救世主。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>见到你,多莉丝真高兴,真像能和你一样到处去玩。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可爱的小家伙们,今天又来问候我啊,真的谢谢你们了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我一定要成为将军那样强大的军人,为此我得坚持锻炼。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
-  </si>
-  <si>
-    <t>现在的人类真是太羸弱了,如果是古代那些强悍的战士,周围就不会有怪物存在了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在那场战争中,本来王国军处于劣势,但是凭着我的活跃表现,才逆转获得胜利。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你喜欢吃什么料理呢？奥蒂莉亚喜欢烤海鲜噢。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>真高兴你能来找我玩,明天你还会来吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在这个宁静的小镇,我找到了久违的安心,我想我还会再住一阵子吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>究竟怎样才能和是否一样优秀呢？这真让我困扰。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我一定要把布拉德利培养成一个优秀的男人,这就是我生活的意义。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我曾经走过大山和大海,追寻财富的脚步永不停息,你能理解吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>制作料理一定要有想象力,只有这样才能将美味融入其中。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>像我这样的天才果然不应该困在这种小店里吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没必要活得太累,偶尔停下脚步欣赏一下自然也是很好的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果不是那件事,王国的军队的总司令官非我莫属了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不管下雨还是晴天,我觉得每一天的天气都很好,你觉得呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其实班尼迪克先生不是你看到的那样,他也有温柔的一面。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每天都要记得喂养动物啊,不要让他们挨饿。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>和你说一会话,真的很轻松,可是我还有工作,不能在和你再聊了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>师父是个大美人吧,不过你可不要打她的主意哦,师父可不是你能驾驭的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果你学会了制作的话,你就可以自己制作装备了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在这个世界上除了人类还有一些奇怪的种族,可是为什么是人类占据了大陆呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你听到了什么？可不要到处乱说啊,这都是我们年轻时发生的事。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其实一个人站岗也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>想不到还会有年轻人来找我这个老头子聊天,真令人高兴。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其实水里也有很多有意思的地方,如果你能在水里生存的话……</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>欢迎光临，有什么需要的吗</t>
-  </si>
-  <si>
-    <t>如果每天都能下雨就好了，这样就不需要为植物浇水了。</t>
-  </si>
-  <si>
-    <t>种植是很有学问的,一定要在合适的季节种植作物哦,\n否则作物的生长时间会变的很长。</t>
-  </si>
-  <si>
-    <t>我要好好帮助玛德琳奶奶。</t>
-  </si>
-  <si>
-    <t>你好呀，小家伙，需要我的帮助吗？</t>
-  </si>
-  <si>
-    <t>帕特里克那个老固执在干什么呢？..明明过去那么久了…</t>
-  </si>
-  <si>
-    <t>布莱兹是个好孩子，如果他的父母还在的话…</t>
-  </si>
-  <si>
-    <t>年轻真好呀，要好好享受生活哟..</t>
-  </si>
-  <si>
-    <t>有烦心事的话，来和奶奶说，我会帮助你的。</t>
-  </si>
-  <si>
-    <t>做一个好农夫也不容易呢，要加油哦！</t>
-  </si>
-  <si>
-    <t>你好，有什么事吗？</t>
-  </si>
-  <si>
-    <t>格吉尔总是想着去冒险，我还是希望他能在小镇安稳的生活。</t>
-  </si>
-  <si>
-    <t>平静的生活就是最大的幸福，你觉得的呢？</t>
-  </si>
-  <si>
-    <t>我很喜欢和动物们相处，它们既单纯又可爱。</t>
-  </si>
-  <si>
-    <t>准备干些什么？</t>
-  </si>
-  <si>
-    <t>相比温顺的动物，我更喜欢能和我一起战斗的伙伴。</t>
-  </si>
-  <si>
-    <t>你如果要去冒险的话，一定要带上我呀。</t>
-  </si>
-  <si>
-    <t>有的人天生就是主角，你看我像不像，哈哈。</t>
-  </si>
-  <si>
-    <t>风儿带来了你的讯息，你有什么想要倾诉？</t>
-  </si>
-  <si>
-    <t>人的生命如此短暂，你是否已经准备好接受自己的命运…</t>
-  </si>
-  <si>
-    <t>高山之后是大海，大海之边是高山，不知山海相连何处是尽头…</t>
-  </si>
-  <si>
-    <t>人无法跨过两次同一条河流，那么河里的鱼是否相同…</t>
-  </si>
-  <si>
-    <t>美丽的人啊，偎依在河岸，我只敢远远欣赏不敢靠近，害怕，你那美丽的面庞将我的眼睛灼伤…</t>
-  </si>
-  <si>
-    <t>愿主保佑你，想要祈祷什么？</t>
-  </si>
-  <si>
-    <t>一切存在都源自内心，如果希望世界更好，那么就让自己的内心更纯净吧。</t>
-  </si>
-  <si>
-    <t>现在的年轻人都不知道敬畏上帝了，平时都不来礼拜了。</t>
-  </si>
-  <si>
-    <t>愿主的荣光照耀在你身上。</t>
-  </si>
-  <si>
-    <t>希望每一个远行的人都能平安的归来…</t>
-  </si>
-  <si>
-    <t>命运还是要把握在自己手里，想知道什么？</t>
-  </si>
-  <si>
-    <t>我知道很多，但我不能都告诉你。</t>
-  </si>
-  <si>
-    <t>从远方而来的人啊，你的故乡在何处，你可知你的真名，我在此等候你的倾诉..</t>
-  </si>
-  <si>
-    <t>年轻人，探索精神固然可贵，但不要盲目冒险呐。</t>
-  </si>
-  <si>
-    <t>即使知道了命运，依然能够笑着面对的人才是真正的勇士。</t>
-  </si>
-  <si>
-    <t>你好呀，想要点什么吗？</t>
-  </si>
-  <si>
-    <t>尽管每天都很忙，但我们都很快乐。</t>
-  </si>
-  <si>
-    <t>美食和美景都不能错过。</t>
-  </si>
-  <si>
-    <t>你笑起来真好看，多笑笑嘛。</t>
-  </si>
-  <si>
-    <t>平时多出来和我们一起玩吧，不要老呆在家里嘛。</t>
-  </si>
-  <si>
-    <t>你好，今天也很精神呀，需要我做什么吗？</t>
-  </si>
-  <si>
-    <t>班尼迪克先生是个好人。</t>
-  </si>
-  <si>
-    <t>一切安好，也希望你也能开开心心。</t>
-  </si>
-  <si>
-    <t>有什么可以为你服务的吗？</t>
-  </si>
-  <si>
-    <t>今天也是平静而美好的。</t>
-  </si>
-  <si>
-    <t>看着环境变得干净卫生，我会很舒心。</t>
-  </si>
-  <si>
-    <t>是你啊，有事的话，请尽管吩咐。</t>
-  </si>
-  <si>
-    <t>如果能发挥我的特长的话就太好了。</t>
-  </si>
-  <si>
-    <t>这个小镇能如此安宁是很多人付出的结果。</t>
-  </si>
-  <si>
-    <t>守护家人是我的职责。</t>
-  </si>
-  <si>
-    <t>其实回到这个养育我的小镇，我很开心。</t>
-  </si>
-  <si>
-    <t>哟，找我有事？</t>
-  </si>
-  <si>
-    <t>真是无聊，这样的日子何时才能结束。</t>
-  </si>
-  <si>
-    <t>看着别人四处旅行，我却只能在这里，真羡慕啊。</t>
-  </si>
-  <si>
-    <t>如果以后你要出去旅行的话，希望我们可以同行。</t>
-  </si>
-  <si>
-    <t>我已经准备了很久行囊，就是没有机会出发。</t>
-  </si>
-  <si>
-    <t>你是来找我的吗？不知道能为你做些什么？</t>
-  </si>
-  <si>
-    <t>我有一个感觉，这个小镇是我的归宿。</t>
-  </si>
-  <si>
-    <t>繁华终归会褪去，回归平淡才是真正的人生。</t>
-  </si>
-  <si>
-    <t>虽然我的魔力还不够，但我会努力的，你有什么需要我的？</t>
-  </si>
-  <si>
-    <t>究竟怎样才能和师父一样优秀呢？这真让我困扰。</t>
-  </si>
-  <si>
-    <t>我的梦想是成为一个大魔导师。</t>
-  </si>
-  <si>
-    <t>是遇到什么疑难了吗？</t>
-  </si>
-  <si>
-    <t>别看我单身一人，年轻时候的我也是很受欢迎的。</t>
-  </si>
-  <si>
-    <t>看见你，就想让我想到了年轻时候的我，真怀念呐。</t>
-  </si>
-  <si>
-    <t>我不会拒绝对弱者的怜悯，所以你有什么事？</t>
-  </si>
-  <si>
-    <t>这个小镇虽然不是很繁华，但我却很喜欢。</t>
-  </si>
-  <si>
-    <t>你想来找我学习贵族礼仪吗?</t>
-  </si>
-  <si>
-    <t>你愿意来找我，我心里还是有一点高兴的。</t>
-  </si>
-  <si>
-    <t>可不要误会，这只是基本的贵族礼仪。</t>
-  </si>
-  <si>
-    <t>你想要了解魔法的力量吗？</t>
-  </si>
-  <si>
-    <t>魔法的力量远超你的想象，</t>
-  </si>
-  <si>
-    <t>嗨，有啥事？</t>
-  </si>
-  <si>
-    <t>要想获得丰厚的渔获，必须要打理好网具。</t>
-  </si>
-  <si>
-    <t>这个小镇靠近大海，可以时常吃到一些海鲜菜肴。</t>
-  </si>
-  <si>
-    <t>据说大海的深处有美人鱼，不知道是不是真的。</t>
-  </si>
-  <si>
-    <t>如果你有时间的话，学习一下钓鱼吧，你会很有收获。</t>
-  </si>
-  <si>
-    <t>你找我是有什么事？</t>
-  </si>
-  <si>
-    <t>这个镇子虽小，却拥有完善的海港，常有舰船航行往来于各大陆之间。</t>
-  </si>
-  <si>
-    <t>经历了长时间的海上漂泊，我需要在岸上好好休息一下。</t>
-  </si>
-  <si>
-    <t>大海里有很多财富，也有很多风险。</t>
-  </si>
-  <si>
-    <t>你如果想去海那边，可以乘坐我的船。</t>
-  </si>
-  <si>
-    <t>找我吗？我也可以为你做事吗？</t>
-  </si>
-  <si>
-    <t>乘船出海游遍世界一直是我的愿望。</t>
-  </si>
-  <si>
-    <t>虽然海上的生活令人神往，但在这个小镇也还不错。</t>
-  </si>
-  <si>
-    <t>大家都很努力啊，我也不能懈怠。</t>
-  </si>
-  <si>
-    <t>如果我也有自己的船就好了。</t>
-  </si>
-  <si>
-    <t>静待你的委托</t>
-  </si>
-  <si>
-    <t>别人的秘密，何必要探究到底呢，只要不危害大家就好了。</t>
-  </si>
-  <si>
-    <t>你好，你想知道什么吗？</t>
-  </si>
-  <si>
-    <t>如果四季可以同时存在，会发生什么呢…</t>
-  </si>
-  <si>
-    <t>需要我的帮忙吗？</t>
-  </si>
-  <si>
-    <t>虽然我对神依然很崇敬，但我还是想干些其他的事情。</t>
-  </si>
-  <si>
-    <t>在战斗中祈求上帝是没有用了，我们只能依靠自己。</t>
-  </si>
-  <si>
-    <t>不知道上帝能不能听到我的心声，让我早日得偿所愿。</t>
-  </si>
-  <si>
-    <t>无论信不信上帝，都要坚守爱与和平。</t>
-  </si>
-  <si>
-    <t>我可以为你做些什么？</t>
-  </si>
-  <si>
-    <t>其实一个人巡逻也挺无聊的,如果有人来和我聊聊的话,我会很高兴。</t>
-  </si>
-  <si>
-    <t>很高兴能为你服务。</t>
-  </si>
-  <si>
-    <t>守护小姐是我的职责。</t>
-  </si>
-  <si>
-    <t>在这个镇子里，我经常会想起关于老主人的事。</t>
-  </si>
-  <si>
-    <t>回想过去，好像刚刚发生在昨天，那时小姐还是个孩子…</t>
-  </si>
-  <si>
-    <t>如果有更多的人陪伴小姐，小姐应该会更开心吧</t>
-  </si>
-  <si>
-    <t>如果有什么事情，我会尽力而为。</t>
-  </si>
-  <si>
-    <t>一个料理如果缺少调味料，就会寡淡无味，不要忘记购买呀。</t>
-  </si>
-  <si>
-    <t>好的装备可以大大促进劳动效率，我需要做什么？</t>
-  </si>
-  <si>
-    <t>我一定要把布拉德利培养成一个优秀的人,这就是我生活的意义。</t>
-  </si>
-  <si>
-    <t>布拉德利再长大一些的话，我会让他自己选择自己的道路。</t>
-  </si>
-  <si>
-    <t>你好，需要什么服务吗？</t>
-  </si>
-  <si>
-    <t>姐姐应该有更广阔的前景的，现在却被困住这个小镇…</t>
-  </si>
-  <si>
-    <t>如果我能更强大一些的话，姐姐就可以去追求自己的梦想了。</t>
-  </si>
-  <si>
-    <t>你可以帮助我，鼓励我一直坚强吗？</t>
-  </si>
-  <si>
-    <t>如果你愿意的话，可以随时来找我和我的姐姐。</t>
-  </si>
-  <si>
-    <t>有什么搞不定的事情？</t>
-  </si>
-  <si>
-    <t>注意,不要走得太远,外面可是有很多怪物。</t>
-  </si>
-  <si>
-    <t>听说你在征讨小镇周边的怪物，做的不错。</t>
-  </si>
-  <si>
-    <t>招待不周了，有什么事情吗？</t>
-  </si>
-  <si>
-    <t>有妹妹和妈妈陪着我，我觉得很幸福。</t>
-  </si>
-  <si>
-    <t>如果爸爸还在的话…</t>
-  </si>
-  <si>
-    <t>我要努力支撑我的家，可以为我加油吗？</t>
-  </si>
-  <si>
-    <t>可有什么事情需要我为你而做的？</t>
-  </si>
-  <si>
-    <t>纺织可是化腐朽为神奇的技术。</t>
-  </si>
-  <si>
-    <t>如果你想学习纺织技术的话，我可以教你。</t>
-  </si>
-  <si>
-    <t>我有时也会为缺少传承而烦恼呢。</t>
-  </si>
-  <si>
-    <t>相比能赚到钱，我更希望有人可以将我的技术传承下去。</t>
-  </si>
-  <si>
-    <t>我拥有的比你知道的还多，你有什么需要的吗？</t>
-  </si>
-  <si>
-    <t>固守成见是不行的，只有变革才能带来新的机遇。</t>
-  </si>
-  <si>
-    <t>放心吧，你的外公只是去了他想去的地方。</t>
-  </si>
-  <si>
-    <t>好好在这里生活吧，你的外公也会很欣慰的。</t>
-  </si>
-  <si>
-    <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-  </si>
-  <si>
-    <t>丝特芬妮</t>
-  </si>
-  <si>
-    <t>格吉尔</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-  </si>
-  <si>
-    <t>琼</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>希拉</t>
-  </si>
-  <si>
-    <t>希尔达</t>
-  </si>
-  <si>
-    <t>布拉德利</t>
-  </si>
-  <si>
-    <t>布蓝达</t>
-  </si>
-  <si>
-    <t>希贝儿</t>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-  </si>
-  <si>
-    <t>梅林</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-  </si>
-  <si>
-    <t>考波特</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-  </si>
-  <si>
-    <t>强尼</t>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-  </si>
-  <si>
-    <t>阿普敦</t>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-  </si>
-  <si>
-    <t>莱特</t>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-  </si>
-  <si>
-    <t>别墅二楼</t>
-  </si>
-  <si>
-    <t>酒馆卧室</t>
-  </si>
-  <si>
-    <t>植物店</t>
-  </si>
-  <si>
-    <t>教堂</t>
-  </si>
-  <si>
-    <t>村公所卧室</t>
-  </si>
-  <si>
-    <t>后山</t>
-  </si>
-  <si>
-    <t>俱乐部阁楼</t>
-  </si>
-  <si>
-    <t>客栈二楼</t>
-  </si>
-  <si>
-    <t>武器店</t>
-  </si>
-  <si>
-    <t>船坞</t>
-  </si>
-  <si>
-    <t>我的农场</t>
-  </si>
-  <si>
-    <t>村公所大厅</t>
-  </si>
-  <si>
-    <t>工坊</t>
-  </si>
-  <si>
-    <t>畜牧店</t>
-  </si>
-  <si>
-    <t>俱乐部</t>
-  </si>
-  <si>
-    <t>塔楼顶部</t>
-  </si>
-  <si>
-    <t>家具店偏室</t>
-  </si>
-  <si>
-    <t>山坡</t>
-  </si>
-  <si>
-    <t>水车房内部</t>
-  </si>
-  <si>
-    <t>小木屋</t>
-  </si>
-  <si>
-    <t>家具店</t>
-  </si>
-  <si>
-    <t>中央广场</t>
-  </si>
-  <si>
-    <t>纺织店</t>
-  </si>
-  <si>
-    <t>商店街</t>
-  </si>
-  <si>
-    <t>塔楼</t>
-  </si>
-  <si>
-    <t>治安室</t>
-  </si>
-  <si>
-    <t>占卜屋</t>
-  </si>
-  <si>
-    <t>帐篷内部</t>
-  </si>
-  <si>
-    <t>风车内部</t>
-  </si>
-  <si>
-    <t>客栈一楼</t>
-  </si>
-  <si>
-    <t>码头</t>
-  </si>
-  <si>
-    <t>鱼摊内部</t>
-  </si>
-  <si>
-    <t>船坞二层</t>
-  </si>
-  <si>
-    <t>住宅区</t>
-  </si>
-  <si>
-    <t>别墅大厅</t>
-  </si>
-  <si>
-    <t>教堂二楼</t>
-  </si>
-  <si>
-    <t>酒馆</t>
-  </si>
-  <si>
-    <t>村公所宴会厅</t>
-  </si>
-  <si>
-    <t>科学研究室</t>
-  </si>
-  <si>
-    <t>商店</t>
-  </si>
-  <si>
-    <t>城门</t>
-  </si>
-  <si>
-    <t>武器店二楼</t>
-  </si>
-  <si>
-    <t>许可清单你可以随时去看看。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>那么，现在我应该做些什么呢？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从最简单的售卖开始吧，看到前面的柜台了么,将东西放到上面就行了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对了，有些商品只能放在特定柜台上，你可以仔细观察一下。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好，现在去把商店的招牌换成营业吧，只有营业状态时才会有客人上门。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>做的不错，你可以再熟悉一下售卖商品，我在外面等你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>植物店里拥有各种植物种子,来跟我去熟悉熟悉吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这就是新来小镇的孩子吧，欢迎你哟，想来点什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>买好了种子了，我们回农场种植吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>植物生长需要几天时间,在此期间,不如去野外探险一下,也许会获得想不到的收获哦。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>看来你已经掌握了售卖物品的方法了,如此一来,你的种植许可也开放了,那么现在去买一些种子回来吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等一下，我这里有一些种植工具，送给你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第一步,先将农具从背包里拿出来。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在走到农田上，使用锄头将田地锄松吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好,就是这样,现在选择种子进行播种吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>别急,还差最后一步呢,种下的植物需要浇水,现在去河边打水回来。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Head/OldWoman</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谢谢，我会好好使用的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这里就是农场，以后就归你管理了,现在准备种植吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前面就是春之山脉的入口，今天就让我这个老头子陪你闯一下吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在前进走到光圈中，开始今天的探索。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打起精神来，现在前进吧。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我没有镰刀，没办法收割</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年轻人，这小镇的清晨不错吧？</t>
-  </si>
-  <si>
-    <t>嗯，空气很清新。</t>
-  </si>
-  <si>
-    <t>我正考虑给店里进些新货，你有啥建议？</t>
-  </si>
-  <si>
-    <t>你看着挺精神，昨晚休息得好？</t>
-  </si>
-  <si>
-    <t>还可以。您这店每天很早就开门吗？</t>
-  </si>
-  <si>
-    <t>对，习惯了。你要是有空可以来帮忙整理下。</t>
-  </si>
-  <si>
-    <t>你初来乍到，有没有去小镇周边转转？</t>
-  </si>
-  <si>
-    <t>还没有。周边有什么好玩的地方吗？</t>
-  </si>
-  <si>
-    <t>有个小湖泊，景色很美。你可以去看看。</t>
-  </si>
-  <si>
-    <t>我店里新到了一些家具，你想看看吗？</t>
-  </si>
-  <si>
-    <t>现在没时间。都是些什么风格的家具？</t>
-  </si>
-  <si>
-    <t>古典和简约的都有。你有空了来品鉴下。</t>
-  </si>
-  <si>
-    <t>你在镇上有没有交到新朋友？</t>
-  </si>
-  <si>
-    <t>认识了几个。交朋友对在这生活很重要吗？</t>
-  </si>
-  <si>
-    <t>当然，朋友多了路好走。你可以多参加些活动。</t>
-  </si>
-  <si>
-    <t>我最近在研究新的家具摆放方式，你有啥想法？</t>
-  </si>
-  <si>
-    <t>我不太懂。是不是可以根据功能分区摆放？</t>
-  </si>
-  <si>
-    <t>有点道理。你要是有了新灵感随时告诉我。</t>
-  </si>
-  <si>
-    <t>你觉得小镇的居民们对家具的需求大吗？</t>
-  </si>
-  <si>
-    <t>不太清楚。应该会需要一些实用的家具吧。</t>
-  </si>
-  <si>
-    <t>我也这么认为。你帮我留意下大家的喜好。</t>
-  </si>
-  <si>
-    <t>早啊，小家伙。我正想改进家具的细节，你觉得从哪入手？</t>
-  </si>
-  <si>
-    <t>可以从打磨工艺上试试。</t>
-  </si>
-  <si>
-    <t>嗨，你看这小镇的建筑风格，对家具设计有启发吗？</t>
-  </si>
-  <si>
-    <t>我觉得可以借鉴一些线条和色彩搭配。</t>
-  </si>
-  <si>
-    <t>很有见地。你能帮我画些草图吗？</t>
-  </si>
-  <si>
-    <t>我打算用旧木材打造复古家具，你觉得可行吗？</t>
-  </si>
-  <si>
-    <t>应该可以，会很有韵味。</t>
-  </si>
-  <si>
-    <t>对。你知道哪里能找到更多旧木材吗？</t>
-  </si>
-  <si>
-    <t>你在镇上参加过手工制作的活动吗？</t>
-  </si>
-  <si>
-    <t>可以学习一些新技巧。你有兴趣的话我带你去。</t>
-  </si>
-  <si>
-    <t>我想在家具上镶嵌一些特色石头，你有推荐吗？</t>
-  </si>
-  <si>
-    <t>像玛瑙或者水晶石应该不错。</t>
-  </si>
-  <si>
-    <t>有道理。你能帮我找些性价比高的吗？</t>
-  </si>
-  <si>
-    <t>你觉得家具的舒适度和美观度怎么平衡？</t>
-  </si>
-  <si>
-    <t>先保证舒适度，再用装饰提升美观度。</t>
-  </si>
-  <si>
-    <t>我要举办一个小型家具展览，你能帮忙宣传吗？</t>
-  </si>
-  <si>
-    <t>我可以试试。需要我做什么？</t>
-  </si>
-  <si>
-    <t>我觉得淡色系比较清新。</t>
-  </si>
-  <si>
-    <t>嗯，值得考虑。你能帮我选些样板吗？</t>
-  </si>
-  <si>
-    <t>哟，早哇。我想去河边钓鱼，顺便找找灵感，一起不？</t>
-  </si>
-  <si>
-    <t>我还有事。你钓鱼能找到什么家具灵感？</t>
-  </si>
-  <si>
-    <t>比如鱼的形状和纹理可以用在装饰上。</t>
-  </si>
-  <si>
-    <t>嗨，我打算用兽皮做些特殊的家具配饰，你见过吗？</t>
-  </si>
-  <si>
-    <t>只要处理好就没问题。你有渠道获取吗？</t>
-  </si>
-  <si>
-    <t>我想在家具里安装音乐盒，一打开就有音乐，怎样？</t>
-  </si>
-  <si>
-    <t>我最近得到一些散发香味的木材，做什么家具好？</t>
-  </si>
-  <si>
-    <t>可以做个香薰柜，存放香料。</t>
-  </si>
-  <si>
-    <t>我想打造一款能折叠成小物件的家具，你觉得可能吗？</t>
-  </si>
-  <si>
-    <t>有可能，像折叠椅就很实用。</t>
-  </si>
-  <si>
-    <t>嘿，我设计了一款带有魔法储物空间的家具，神奇吧？</t>
-  </si>
-  <si>
-    <t>哇，太神奇了！怎么实现储物空间的魔法呢？</t>
-  </si>
-  <si>
-    <t>用魔法水晶驱动。你在镇上见过魔法水晶吗？</t>
-  </si>
-  <si>
-    <t>我不太清楚。我先去吃个早饭，回见。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我今天有事。不好意思，我得走了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的。我突然想起有事，先走一步。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>好的。我先去了，回见。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我有点忙，先撤了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不太清楚。我去打听下。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有。这类活动和家具制作有关吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我找找看。不好意思，我得赶紧走了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>让我想想再告诉你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我在研究新的涂料，你对颜色有偏好吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我不太会。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>挺有趣。我忙完来找你。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没见过呢。这样合适吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有。要不去问问别人。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">好有创意！ </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你在镇上逛过那些古老的小巷吗？可以从巷子里的图案找设计灵感。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不太清楚。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你知道怎么处理木材香味吗？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>没见过。我去探索下。我先去了，回见。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>咯咯..咯咯..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>叽叽..叽叽..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘎嘎..嘎嘎..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呷呷..呷呷..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>噗呼..噗呼..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>咩咩..咩咩..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哼哼..哼哼..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吱吱..吱吱..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘶嘶..嘶嘶..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>噗呼..噗呼..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>咕噜..咕噜..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呦呦..呦呦..</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哞～哞～</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呜～呜～</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>咳咳..咳咳..</t>
+    <t>我需要装备鱼饵，否则不能钓鱼！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2915,7 +2915,7 @@
         <v>181</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>181</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -4742,7 +4742,7 @@
         <v>181</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -4771,7 +4771,7 @@
         <v>181</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -4800,7 +4800,7 @@
         <v>181</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>181</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>181</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -4945,7 +4945,7 @@
         <v>181</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -4974,7 +4974,7 @@
         <v>181</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>181</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H84" s="1">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>181</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>181</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H86" s="1">
         <v>0</v>
@@ -5119,7 +5119,7 @@
         <v>181</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         <v>181</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -5177,7 +5177,7 @@
         <v>181</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -5206,7 +5206,7 @@
         <v>181</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -5235,7 +5235,7 @@
         <v>181</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -5264,7 +5264,7 @@
         <v>181</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -5293,7 +5293,7 @@
         <v>181</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
@@ -5322,7 +5322,7 @@
         <v>181</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>181</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -5380,7 +5380,7 @@
         <v>181</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -5409,7 +5409,7 @@
         <v>181</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>181</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -5496,7 +5496,7 @@
         <v>181</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H100" s="1">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>181</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -5554,7 +5554,7 @@
         <v>181</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -5612,7 +5612,7 @@
         <v>181</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -5641,7 +5641,7 @@
         <v>181</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>181</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>181</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -5815,7 +5815,7 @@
         <v>181</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -5844,7 +5844,7 @@
         <v>181</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -5873,7 +5873,7 @@
         <v>181</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>181</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -5931,7 +5931,7 @@
         <v>181</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -5960,7 +5960,7 @@
         <v>181</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -5989,7 +5989,7 @@
         <v>181</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -6018,7 +6018,7 @@
         <v>181</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -6047,7 +6047,7 @@
         <v>181</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
@@ -6076,7 +6076,7 @@
         <v>181</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -6105,7 +6105,7 @@
         <v>181</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -6134,7 +6134,7 @@
         <v>181</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -6163,7 +6163,7 @@
         <v>181</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
@@ -6192,7 +6192,7 @@
         <v>181</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
@@ -7284,7 +7284,7 @@
         <v>255</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="H160" s="1">
         <v>1416</v>
@@ -7316,7 +7316,7 @@
         <v>189</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H161" s="1">
         <v>1417</v>
@@ -7348,7 +7348,7 @@
         <v>189</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="H162" s="1">
         <v>1418</v>
@@ -7380,7 +7380,7 @@
         <v>255</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
@@ -7412,7 +7412,7 @@
         <v>189</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H164" s="1">
         <v>0</v>
@@ -7444,7 +7444,7 @@
         <v>189</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H165" s="1">
         <v>0</v>
@@ -7476,7 +7476,7 @@
         <v>255</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H166" s="1">
         <v>1422</v>
@@ -7493,7 +7493,7 @@
         <v>1422</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>8</v>
@@ -7540,7 +7540,7 @@
         <v>189</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
@@ -7563,7 +7563,7 @@
         <v>10</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -7572,7 +7572,7 @@
         <v>181</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
@@ -7604,7 +7604,7 @@
         <v>189</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H170" s="1">
         <v>1426</v>
@@ -7627,7 +7627,7 @@
         <v>10</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -7636,7 +7636,7 @@
         <v>189</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
@@ -7653,7 +7653,7 @@
         <v>1427</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>8</v>
@@ -7668,7 +7668,7 @@
         <v>189</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
@@ -7700,7 +7700,7 @@
         <v>181</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H173" s="1">
         <v>1429</v>
@@ -7732,7 +7732,7 @@
         <v>181</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H174" s="1">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>181</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
@@ -7796,7 +7796,7 @@
         <v>181</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -7813,7 +7813,7 @@
         <v>1432</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>8</v>
@@ -7845,7 +7845,7 @@
         <v>1433</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>9</v>
@@ -7860,7 +7860,7 @@
         <v>255</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
@@ -7924,7 +7924,7 @@
         <v>255</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>255</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -7988,7 +7988,7 @@
         <v>255</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -8005,7 +8005,7 @@
         <v>1439</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>9</v>
@@ -8020,7 +8020,7 @@
         <v>255</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -9154,7 +9154,7 @@
         <v>255</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
@@ -11333,7 +11333,7 @@
         <v>181</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -11362,7 +11362,7 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>303</v>
+        <v>664</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -11391,7 +11391,7 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>304</v>
+        <v>665</v>
       </c>
       <c r="H298" s="1">
         <v>0</v>
@@ -11408,7 +11408,7 @@
         <v>4000</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>274</v>
@@ -11420,7 +11420,7 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
@@ -11437,7 +11437,7 @@
         <v>4001</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>274</v>
@@ -11449,7 +11449,7 @@
         <v>181</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="H300" s="1">
         <v>4000</v>
@@ -11466,7 +11466,7 @@
         <v>4002</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>274</v>
@@ -11495,7 +11495,7 @@
         <v>4003</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>274</v>
@@ -11507,7 +11507,7 @@
         <v>181</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H302" s="1">
         <v>4000</v>
@@ -11524,7 +11524,7 @@
         <v>4004</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>274</v>
@@ -11536,7 +11536,7 @@
         <v>181</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="H303" s="1">
         <v>4000</v>
@@ -11553,7 +11553,7 @@
         <v>4005</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>274</v>
@@ -11565,7 +11565,7 @@
         <v>181</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
@@ -11582,7 +11582,7 @@
         <v>4006</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>274</v>
@@ -11594,7 +11594,7 @@
         <v>181</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H305" s="1">
         <v>4005</v>
@@ -11611,7 +11611,7 @@
         <v>4007</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>274</v>
@@ -11623,7 +11623,7 @@
         <v>181</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H306" s="1">
         <v>4005</v>
@@ -11640,7 +11640,7 @@
         <v>4008</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>274</v>
@@ -11652,7 +11652,7 @@
         <v>181</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H307" s="1">
         <v>4005</v>
@@ -11669,7 +11669,7 @@
         <v>4009</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>274</v>
@@ -11681,7 +11681,7 @@
         <v>181</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H308" s="1">
         <v>4005</v>
@@ -11698,7 +11698,7 @@
         <v>4010</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>274</v>
@@ -11710,7 +11710,7 @@
         <v>181</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H309" s="1">
         <v>4005</v>
@@ -11727,7 +11727,7 @@
         <v>4011</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>274</v>
@@ -11739,7 +11739,7 @@
         <v>181</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H310" s="1">
         <v>0</v>
@@ -11756,7 +11756,7 @@
         <v>4012</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>274</v>
@@ -11785,7 +11785,7 @@
         <v>4013</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>274</v>
@@ -11797,7 +11797,7 @@
         <v>181</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H312" s="1">
         <v>4011</v>
@@ -11814,7 +11814,7 @@
         <v>4014</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>274</v>
@@ -11826,7 +11826,7 @@
         <v>181</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H313" s="1">
         <v>4011</v>
@@ -11843,7 +11843,7 @@
         <v>4015</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>274</v>
@@ -11855,7 +11855,7 @@
         <v>181</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="H314" s="1">
         <v>4011</v>
@@ -11872,7 +11872,7 @@
         <v>4016</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>274</v>
@@ -11884,7 +11884,7 @@
         <v>181</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H315" s="1">
         <v>0</v>
@@ -11901,7 +11901,7 @@
         <v>4017</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>274</v>
@@ -11930,7 +11930,7 @@
         <v>4018</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>274</v>
@@ -11942,7 +11942,7 @@
         <v>181</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H317" s="1">
         <v>4016</v>
@@ -11959,7 +11959,7 @@
         <v>4019</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>274</v>
@@ -11971,7 +11971,7 @@
         <v>181</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H318" s="1">
         <v>4016</v>
@@ -11988,7 +11988,7 @@
         <v>4020</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>274</v>
@@ -12000,7 +12000,7 @@
         <v>181</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H319" s="1">
         <v>4016</v>
@@ -12017,7 +12017,7 @@
         <v>4021</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>274</v>
@@ -12029,7 +12029,7 @@
         <v>181</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H320" s="1">
         <v>0</v>
@@ -12046,7 +12046,7 @@
         <v>4022</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>274</v>
@@ -12058,7 +12058,7 @@
         <v>181</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H321" s="1">
         <v>4021</v>
@@ -12075,7 +12075,7 @@
         <v>4023</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>274</v>
@@ -12087,7 +12087,7 @@
         <v>181</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="H322" s="1">
         <v>4021</v>
@@ -12104,7 +12104,7 @@
         <v>4024</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>274</v>
@@ -12116,7 +12116,7 @@
         <v>181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H323" s="1">
         <v>4021</v>
@@ -12133,7 +12133,7 @@
         <v>4025</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>274</v>
@@ -12145,7 +12145,7 @@
         <v>181</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H324" s="1">
         <v>4021</v>
@@ -12162,7 +12162,7 @@
         <v>4026</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>274</v>
@@ -12174,7 +12174,7 @@
         <v>181</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H325" s="1">
         <v>0</v>
@@ -12191,7 +12191,7 @@
         <v>4027</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>274</v>
@@ -12203,7 +12203,7 @@
         <v>181</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H326" s="1">
         <v>4026</v>
@@ -12220,7 +12220,7 @@
         <v>4028</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>274</v>
@@ -12232,7 +12232,7 @@
         <v>181</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H327" s="1">
         <v>4026</v>
@@ -12249,7 +12249,7 @@
         <v>4029</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>274</v>
@@ -12261,7 +12261,7 @@
         <v>181</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H328" s="1">
         <v>4026</v>
@@ -12278,7 +12278,7 @@
         <v>4030</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>274</v>
@@ -12290,7 +12290,7 @@
         <v>181</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H329" s="1">
         <v>4026</v>
@@ -12307,7 +12307,7 @@
         <v>4031</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>274</v>
@@ -12319,7 +12319,7 @@
         <v>181</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H330" s="1">
         <v>0</v>
@@ -12336,7 +12336,7 @@
         <v>4032</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>274</v>
@@ -12348,7 +12348,7 @@
         <v>181</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="H331" s="1">
         <v>4031</v>
@@ -12365,7 +12365,7 @@
         <v>4033</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>274</v>
@@ -12377,7 +12377,7 @@
         <v>181</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="H332" s="1">
         <v>4031</v>
@@ -12394,7 +12394,7 @@
         <v>4034</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>274</v>
@@ -12406,7 +12406,7 @@
         <v>181</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H333" s="1">
         <v>4031</v>
@@ -12423,7 +12423,7 @@
         <v>4035</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>274</v>
@@ -12435,7 +12435,7 @@
         <v>181</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H334" s="1">
         <v>4031</v>
@@ -12452,7 +12452,7 @@
         <v>4036</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>274</v>
@@ -12464,7 +12464,7 @@
         <v>181</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H335" s="1">
         <v>0</v>
@@ -12481,7 +12481,7 @@
         <v>4037</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>274</v>
@@ -12493,7 +12493,7 @@
         <v>181</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H336" s="1">
         <v>4036</v>
@@ -12510,7 +12510,7 @@
         <v>4038</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>274</v>
@@ -12522,7 +12522,7 @@
         <v>181</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H337" s="1">
         <v>4036</v>
@@ -12539,7 +12539,7 @@
         <v>4039</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>274</v>
@@ -12551,7 +12551,7 @@
         <v>181</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H338" s="1">
         <v>4036</v>
@@ -12568,7 +12568,7 @@
         <v>4040</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>274</v>
@@ -12580,7 +12580,7 @@
         <v>181</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H339" s="1">
         <v>4036</v>
@@ -12597,7 +12597,7 @@
         <v>4041</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>274</v>
@@ -12609,7 +12609,7 @@
         <v>181</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H340" s="1">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>4042</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>274</v>
@@ -12638,7 +12638,7 @@
         <v>181</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H341" s="1">
         <v>4041</v>
@@ -12655,7 +12655,7 @@
         <v>4043</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>274</v>
@@ -12684,7 +12684,7 @@
         <v>4044</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>274</v>
@@ -12713,7 +12713,7 @@
         <v>4045</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>274</v>
@@ -12725,7 +12725,7 @@
         <v>181</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H344" s="1">
         <v>4041</v>
@@ -12742,7 +12742,7 @@
         <v>4046</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>274</v>
@@ -12754,7 +12754,7 @@
         <v>181</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H345" s="1">
         <v>0</v>
@@ -12771,7 +12771,7 @@
         <v>4047</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>274</v>
@@ -12783,7 +12783,7 @@
         <v>181</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H346" s="1">
         <v>4046</v>
@@ -12800,7 +12800,7 @@
         <v>4048</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>274</v>
@@ -12829,7 +12829,7 @@
         <v>4049</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>274</v>
@@ -12858,7 +12858,7 @@
         <v>4050</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>274</v>
@@ -12870,7 +12870,7 @@
         <v>181</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H349" s="1">
         <v>4046</v>
@@ -12887,7 +12887,7 @@
         <v>4051</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>274</v>
@@ -12899,7 +12899,7 @@
         <v>181</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H350" s="1">
         <v>0</v>
@@ -12916,7 +12916,7 @@
         <v>4052</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>274</v>
@@ -12928,7 +12928,7 @@
         <v>181</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H351" s="1">
         <v>4051</v>
@@ -12945,7 +12945,7 @@
         <v>4053</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>274</v>
@@ -12957,7 +12957,7 @@
         <v>181</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H352" s="1">
         <v>4051</v>
@@ -12974,7 +12974,7 @@
         <v>4054</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>274</v>
@@ -12986,7 +12986,7 @@
         <v>181</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="H353" s="1">
         <v>4051</v>
@@ -13003,7 +13003,7 @@
         <v>4055</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>274</v>
@@ -13015,7 +13015,7 @@
         <v>181</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H354" s="1">
         <v>4051</v>
@@ -13032,7 +13032,7 @@
         <v>4056</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>274</v>
@@ -13044,7 +13044,7 @@
         <v>181</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H355" s="1">
         <v>0</v>
@@ -13061,7 +13061,7 @@
         <v>4057</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>274</v>
@@ -13073,7 +13073,7 @@
         <v>181</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H356" s="1">
         <v>4056</v>
@@ -13090,7 +13090,7 @@
         <v>4058</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>274</v>
@@ -13102,7 +13102,7 @@
         <v>181</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H357" s="1">
         <v>4056</v>
@@ -13119,7 +13119,7 @@
         <v>4059</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>274</v>
@@ -13131,7 +13131,7 @@
         <v>181</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H358" s="1">
         <v>4056</v>
@@ -13148,7 +13148,7 @@
         <v>4060</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>274</v>
@@ -13160,7 +13160,7 @@
         <v>181</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H359" s="1">
         <v>4056</v>
@@ -13177,7 +13177,7 @@
         <v>4061</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>274</v>
@@ -13189,7 +13189,7 @@
         <v>181</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H360" s="1">
         <v>0</v>
@@ -13206,7 +13206,7 @@
         <v>4062</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>274</v>
@@ -13218,7 +13218,7 @@
         <v>181</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H361" s="1">
         <v>4061</v>
@@ -13235,7 +13235,7 @@
         <v>4063</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>274</v>
@@ -13264,7 +13264,7 @@
         <v>4064</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>274</v>
@@ -13293,7 +13293,7 @@
         <v>4065</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>274</v>
@@ -13305,7 +13305,7 @@
         <v>181</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H364" s="1">
         <v>4061</v>
@@ -13322,7 +13322,7 @@
         <v>4066</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>274</v>
@@ -13334,7 +13334,7 @@
         <v>181</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H365" s="1">
         <v>0</v>
@@ -13351,7 +13351,7 @@
         <v>4067</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>274</v>
@@ -13380,7 +13380,7 @@
         <v>4068</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>274</v>
@@ -13392,7 +13392,7 @@
         <v>181</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H367" s="1">
         <v>4066</v>
@@ -13409,7 +13409,7 @@
         <v>4069</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>274</v>
@@ -13438,7 +13438,7 @@
         <v>4070</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>274</v>
@@ -13450,7 +13450,7 @@
         <v>181</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H369" s="1">
         <v>4066</v>
@@ -13467,7 +13467,7 @@
         <v>4071</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>274</v>
@@ -13479,7 +13479,7 @@
         <v>181</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H370" s="1">
         <v>0</v>
@@ -13496,7 +13496,7 @@
         <v>4072</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>274</v>
@@ -13525,7 +13525,7 @@
         <v>4073</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>274</v>
@@ -13554,7 +13554,7 @@
         <v>4074</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>274</v>
@@ -13566,7 +13566,7 @@
         <v>181</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H373" s="1">
         <v>4071</v>
@@ -13583,7 +13583,7 @@
         <v>4075</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>274</v>
@@ -13595,7 +13595,7 @@
         <v>181</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H374" s="1">
         <v>4071</v>
@@ -13612,7 +13612,7 @@
         <v>4076</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>274</v>
@@ -13624,7 +13624,7 @@
         <v>181</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H375" s="1">
         <v>0</v>
@@ -13641,7 +13641,7 @@
         <v>4077</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>274</v>
@@ -13653,7 +13653,7 @@
         <v>181</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H376" s="1">
         <v>4076</v>
@@ -13670,7 +13670,7 @@
         <v>4078</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>274</v>
@@ -13682,7 +13682,7 @@
         <v>181</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H377" s="1">
         <v>4076</v>
@@ -13699,7 +13699,7 @@
         <v>4079</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>274</v>
@@ -13711,7 +13711,7 @@
         <v>181</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H378" s="1">
         <v>4076</v>
@@ -13728,7 +13728,7 @@
         <v>4080</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>274</v>
@@ -13740,7 +13740,7 @@
         <v>181</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H379" s="1">
         <v>4076</v>
@@ -13757,7 +13757,7 @@
         <v>4081</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>274</v>
@@ -13769,7 +13769,7 @@
         <v>181</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H380" s="1">
         <v>0</v>
@@ -13786,7 +13786,7 @@
         <v>4082</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>274</v>
@@ -13815,7 +13815,7 @@
         <v>4083</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>274</v>
@@ -13844,7 +13844,7 @@
         <v>4084</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>274</v>
@@ -13856,7 +13856,7 @@
         <v>181</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H383" s="1">
         <v>4081</v>
@@ -13873,7 +13873,7 @@
         <v>4085</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>274</v>
@@ -13885,7 +13885,7 @@
         <v>181</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H384" s="1">
         <v>4081</v>
@@ -13902,7 +13902,7 @@
         <v>4086</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D385" s="1" t="s">
         <v>274</v>
@@ -13914,7 +13914,7 @@
         <v>181</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H385" s="1">
         <v>0</v>
@@ -13931,7 +13931,7 @@
         <v>4087</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>274</v>
@@ -13943,7 +13943,7 @@
         <v>181</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H386" s="1">
         <v>4086</v>
@@ -13960,7 +13960,7 @@
         <v>4088</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>274</v>
@@ -13972,7 +13972,7 @@
         <v>181</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H387" s="1">
         <v>4086</v>
@@ -13989,7 +13989,7 @@
         <v>4089</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>274</v>
@@ -14001,7 +14001,7 @@
         <v>181</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H388" s="1">
         <v>4086</v>
@@ -14018,7 +14018,7 @@
         <v>4090</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>274</v>
@@ -14030,7 +14030,7 @@
         <v>181</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H389" s="1">
         <v>4086</v>
@@ -14047,7 +14047,7 @@
         <v>4091</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>274</v>
@@ -14059,7 +14059,7 @@
         <v>181</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H390" s="1">
         <v>0</v>
@@ -14076,7 +14076,7 @@
         <v>4092</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>274</v>
@@ -14088,7 +14088,7 @@
         <v>181</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H391" s="1">
         <v>4091</v>
@@ -14105,7 +14105,7 @@
         <v>4093</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>274</v>
@@ -14117,7 +14117,7 @@
         <v>181</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H392" s="1">
         <v>4091</v>
@@ -14134,7 +14134,7 @@
         <v>4094</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>274</v>
@@ -14146,7 +14146,7 @@
         <v>181</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H393" s="1">
         <v>4091</v>
@@ -14163,7 +14163,7 @@
         <v>4095</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>274</v>
@@ -14175,7 +14175,7 @@
         <v>181</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H394" s="1">
         <v>4091</v>
@@ -14192,7 +14192,7 @@
         <v>4096</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>274</v>
@@ -14204,7 +14204,7 @@
         <v>181</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H395" s="1">
         <v>0</v>
@@ -14221,7 +14221,7 @@
         <v>4097</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>274</v>
@@ -14233,7 +14233,7 @@
         <v>181</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H396" s="1">
         <v>4096</v>
@@ -14250,7 +14250,7 @@
         <v>4098</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>274</v>
@@ -14262,7 +14262,7 @@
         <v>181</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H397" s="1">
         <v>4096</v>
@@ -14279,7 +14279,7 @@
         <v>4099</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>274</v>
@@ -14291,7 +14291,7 @@
         <v>181</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H398" s="1">
         <v>4096</v>
@@ -14308,7 +14308,7 @@
         <v>4100</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>274</v>
@@ -14320,7 +14320,7 @@
         <v>181</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H399" s="1">
         <v>4096</v>
@@ -14337,7 +14337,7 @@
         <v>4101</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>274</v>
@@ -14349,7 +14349,7 @@
         <v>181</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H400" s="1">
         <v>0</v>
@@ -14366,7 +14366,7 @@
         <v>4102</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>274</v>
@@ -14395,7 +14395,7 @@
         <v>4103</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>274</v>
@@ -14424,7 +14424,7 @@
         <v>4104</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>274</v>
@@ -14453,7 +14453,7 @@
         <v>4105</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>274</v>
@@ -14465,7 +14465,7 @@
         <v>181</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H404" s="1">
         <v>4101</v>
@@ -14482,7 +14482,7 @@
         <v>4106</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>274</v>
@@ -14494,7 +14494,7 @@
         <v>181</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H405" s="1">
         <v>0</v>
@@ -14511,7 +14511,7 @@
         <v>4107</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>274</v>
@@ -14540,7 +14540,7 @@
         <v>4108</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>274</v>
@@ -14569,7 +14569,7 @@
         <v>4109</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>274</v>
@@ -14598,7 +14598,7 @@
         <v>4110</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>274</v>
@@ -14610,7 +14610,7 @@
         <v>181</v>
       </c>
       <c r="G409" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H409" s="1">
         <v>4106</v>
@@ -14627,7 +14627,7 @@
         <v>4111</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D410" s="1" t="s">
         <v>274</v>
@@ -14639,7 +14639,7 @@
         <v>181</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H410" s="1">
         <v>0</v>
@@ -14656,7 +14656,7 @@
         <v>4112</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D411" s="1" t="s">
         <v>274</v>
@@ -14668,7 +14668,7 @@
         <v>181</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H411" s="1">
         <v>4111</v>
@@ -14685,7 +14685,7 @@
         <v>4113</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D412" s="1" t="s">
         <v>274</v>
@@ -14697,7 +14697,7 @@
         <v>181</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H412" s="1">
         <v>4111</v>
@@ -14714,7 +14714,7 @@
         <v>4114</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D413" s="1" t="s">
         <v>274</v>
@@ -14726,7 +14726,7 @@
         <v>181</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H413" s="1">
         <v>4111</v>
@@ -14743,7 +14743,7 @@
         <v>4115</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D414" s="1" t="s">
         <v>274</v>
@@ -14755,7 +14755,7 @@
         <v>181</v>
       </c>
       <c r="G414" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H414" s="1">
         <v>4111</v>
@@ -14772,7 +14772,7 @@
         <v>4116</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D415" s="1" t="s">
         <v>274</v>
@@ -14784,7 +14784,7 @@
         <v>181</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H415" s="1">
         <v>0</v>
@@ -14801,7 +14801,7 @@
         <v>4117</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D416" s="1" t="s">
         <v>274</v>
@@ -14830,7 +14830,7 @@
         <v>4118</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>274</v>
@@ -14859,7 +14859,7 @@
         <v>4119</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>274</v>
@@ -14888,7 +14888,7 @@
         <v>4120</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D419" s="1" t="s">
         <v>274</v>
@@ -14900,7 +14900,7 @@
         <v>181</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H419" s="1">
         <v>4116</v>
@@ -14917,7 +14917,7 @@
         <v>4121</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D420" s="1" t="s">
         <v>274</v>
@@ -14929,7 +14929,7 @@
         <v>181</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H420" s="1">
         <v>0</v>
@@ -14946,7 +14946,7 @@
         <v>4122</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D421" s="1" t="s">
         <v>274</v>
@@ -14958,7 +14958,7 @@
         <v>181</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H421" s="1">
         <v>4121</v>
@@ -14975,7 +14975,7 @@
         <v>4123</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D422" s="1" t="s">
         <v>274</v>
@@ -14987,7 +14987,7 @@
         <v>181</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H422" s="1">
         <v>4121</v>
@@ -15004,7 +15004,7 @@
         <v>4124</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D423" s="1" t="s">
         <v>274</v>
@@ -15016,7 +15016,7 @@
         <v>181</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H423" s="1">
         <v>4121</v>
@@ -15033,7 +15033,7 @@
         <v>4125</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D424" s="1" t="s">
         <v>274</v>
@@ -15045,7 +15045,7 @@
         <v>181</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H424" s="1">
         <v>4121</v>
@@ -15062,7 +15062,7 @@
         <v>4126</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D425" s="1" t="s">
         <v>274</v>
@@ -15074,7 +15074,7 @@
         <v>181</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H425" s="1">
         <v>0</v>
@@ -15091,7 +15091,7 @@
         <v>4127</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D426" s="1" t="s">
         <v>274</v>
@@ -15120,7 +15120,7 @@
         <v>4128</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D427" s="1" t="s">
         <v>274</v>
@@ -15149,7 +15149,7 @@
         <v>4129</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D428" s="1" t="s">
         <v>274</v>
@@ -15178,7 +15178,7 @@
         <v>4130</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D429" s="1" t="s">
         <v>274</v>
@@ -15207,7 +15207,7 @@
         <v>4131</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>274</v>
@@ -15219,7 +15219,7 @@
         <v>181</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H430" s="1">
         <v>4126</v>
@@ -15236,7 +15236,7 @@
         <v>4132</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>274</v>
@@ -15248,7 +15248,7 @@
         <v>181</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H431" s="1">
         <v>0</v>
@@ -15265,7 +15265,7 @@
         <v>4133</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>274</v>
@@ -15294,7 +15294,7 @@
         <v>4134</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D433" s="1" t="s">
         <v>274</v>
@@ -15306,7 +15306,7 @@
         <v>181</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H433" s="1">
         <v>4132</v>
@@ -15323,7 +15323,7 @@
         <v>4135</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>274</v>
@@ -15352,7 +15352,7 @@
         <v>4136</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>274</v>
@@ -15364,7 +15364,7 @@
         <v>181</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H435" s="1">
         <v>4132</v>
@@ -15381,7 +15381,7 @@
         <v>4137</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D436" s="1" t="s">
         <v>274</v>
@@ -15393,7 +15393,7 @@
         <v>181</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H436" s="1">
         <v>0</v>
@@ -15410,7 +15410,7 @@
         <v>4138</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D437" s="1" t="s">
         <v>274</v>
@@ -15422,7 +15422,7 @@
         <v>181</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H437" s="1">
         <v>4137</v>
@@ -15439,7 +15439,7 @@
         <v>4139</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>274</v>
@@ -15451,7 +15451,7 @@
         <v>181</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H438" s="1">
         <v>4137</v>
@@ -15468,7 +15468,7 @@
         <v>4140</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>274</v>
@@ -15480,7 +15480,7 @@
         <v>181</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H439" s="1">
         <v>4137</v>
@@ -15497,7 +15497,7 @@
         <v>4141</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>274</v>
@@ -15509,7 +15509,7 @@
         <v>181</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H440" s="1">
         <v>4137</v>
@@ -15526,7 +15526,7 @@
         <v>4142</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D441" s="1" t="s">
         <v>274</v>
@@ -15538,7 +15538,7 @@
         <v>181</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H441" s="1">
         <v>0</v>
@@ -15555,7 +15555,7 @@
         <v>4143</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D442" s="1" t="s">
         <v>274</v>
@@ -15567,7 +15567,7 @@
         <v>181</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H442" s="1">
         <v>4142</v>
@@ -15584,7 +15584,7 @@
         <v>4144</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D443" s="1" t="s">
         <v>274</v>
@@ -15613,7 +15613,7 @@
         <v>4145</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D444" s="1" t="s">
         <v>274</v>
@@ -15642,7 +15642,7 @@
         <v>4146</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>274</v>
@@ -15654,7 +15654,7 @@
         <v>181</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H445" s="1">
         <v>4142</v>
@@ -15671,7 +15671,7 @@
         <v>4147</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D446" s="1" t="s">
         <v>274</v>
@@ -15683,7 +15683,7 @@
         <v>181</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H446" s="1">
         <v>0</v>
@@ -15700,7 +15700,7 @@
         <v>4148</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>274</v>
@@ -15729,7 +15729,7 @@
         <v>4149</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>274</v>
@@ -15741,7 +15741,7 @@
         <v>181</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H448" s="1">
         <v>4147</v>
@@ -15758,7 +15758,7 @@
         <v>4150</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>274</v>
@@ -15770,7 +15770,7 @@
         <v>181</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H449" s="1">
         <v>4147</v>
@@ -15787,7 +15787,7 @@
         <v>4151</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>274</v>
@@ -15799,7 +15799,7 @@
         <v>181</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H450" s="1">
         <v>4147</v>
@@ -15816,7 +15816,7 @@
         <v>4152</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>274</v>
@@ -15828,7 +15828,7 @@
         <v>181</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H451" s="1">
         <v>0</v>
@@ -15845,7 +15845,7 @@
         <v>4153</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D452" s="1" t="s">
         <v>274</v>
@@ -15857,7 +15857,7 @@
         <v>181</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H452" s="1">
         <v>4152</v>
@@ -15874,7 +15874,7 @@
         <v>4154</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>274</v>
@@ -15886,7 +15886,7 @@
         <v>181</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H453" s="1">
         <v>4152</v>
@@ -15903,7 +15903,7 @@
         <v>4155</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D454" s="1" t="s">
         <v>274</v>
@@ -15915,7 +15915,7 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H454" s="1">
         <v>4152</v>
@@ -15932,7 +15932,7 @@
         <v>4156</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D455" s="1" t="s">
         <v>274</v>
@@ -15944,7 +15944,7 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H455" s="1">
         <v>4152</v>
@@ -15961,7 +15961,7 @@
         <v>4157</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D456" s="1" t="s">
         <v>274</v>
@@ -15973,7 +15973,7 @@
         <v>181</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H456" s="1">
         <v>0</v>
@@ -15990,7 +15990,7 @@
         <v>4158</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D457" s="1" t="s">
         <v>274</v>
@@ -16019,7 +16019,7 @@
         <v>4159</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>274</v>
@@ -16031,7 +16031,7 @@
         <v>181</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H458" s="1">
         <v>4157</v>
@@ -16048,7 +16048,7 @@
         <v>4160</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D459" s="1" t="s">
         <v>274</v>
@@ -16060,7 +16060,7 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H459" s="1">
         <v>4157</v>
@@ -16077,7 +16077,7 @@
         <v>4161</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>274</v>
@@ -16089,7 +16089,7 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H460" s="1">
         <v>4157</v>
@@ -16379,7 +16379,7 @@
         <v>181</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H470" s="1">
         <v>0</v>
@@ -16408,7 +16408,7 @@
         <v>181</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="H471" s="1">
         <v>0</v>
@@ -16437,7 +16437,7 @@
         <v>181</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H472" s="1">
         <v>0</v>
@@ -16466,7 +16466,7 @@
         <v>181</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H473" s="1">
         <v>0</v>
@@ -16495,7 +16495,7 @@
         <v>181</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H474" s="1">
         <v>0</v>
@@ -16524,7 +16524,7 @@
         <v>181</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="H475" s="1">
         <v>0</v>
@@ -16553,7 +16553,7 @@
         <v>181</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H476" s="1">
         <v>0</v>
@@ -16582,7 +16582,7 @@
         <v>181</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H477" s="1">
         <v>0</v>
@@ -16611,7 +16611,7 @@
         <v>181</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H478" s="1">
         <v>0</v>
@@ -16640,7 +16640,7 @@
         <v>181</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="H479" s="1">
         <v>0</v>
@@ -16669,7 +16669,7 @@
         <v>181</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="H480" s="1">
         <v>0</v>
@@ -16698,7 +16698,7 @@
         <v>181</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H481" s="1">
         <v>0</v>
@@ -16727,7 +16727,7 @@
         <v>181</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="H482" s="1">
         <v>0</v>
@@ -16756,7 +16756,7 @@
         <v>181</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H483" s="1">
         <v>0</v>
@@ -16785,7 +16785,7 @@
         <v>181</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H484" s="1">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>181</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H485" s="1">
         <v>0</v>
@@ -16843,7 +16843,7 @@
         <v>181</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H486" s="1">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       <c r="B1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="8" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H1" s="6">
         <v>44002</v>
@@ -16892,7 +16892,7 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -16902,7 +16902,7 @@
       <c r="B3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="H3" s="1">
         <v>44004</v>
@@ -16918,7 +16918,7 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -16928,7 +16928,7 @@
       <c r="B5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H5" s="1">
         <v>44006</v>
@@ -16944,7 +16944,7 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="H6" s="1">
         <v>44007</v>
@@ -16957,7 +16957,7 @@
       <c r="B7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H8" s="1">
         <v>44009</v>
@@ -16983,7 +16983,7 @@
       <c r="B9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="H9" s="1">
         <v>44010</v>
@@ -16999,7 +16999,7 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H10" s="1">
         <v>44011</v>
@@ -17012,7 +17012,7 @@
       <c r="B11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17022,7 +17022,7 @@
       <c r="B12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="H12" s="1">
         <v>44013</v>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="H13" s="1">
         <v>44014</v>
@@ -17051,7 +17051,7 @@
       <c r="B14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17061,7 +17061,7 @@
       <c r="B15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H15" s="1">
         <v>44016</v>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="H16" s="1">
         <v>44017</v>
@@ -17090,7 +17090,7 @@
       <c r="B17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H17" s="1">
         <v>44018</v>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17116,7 +17116,7 @@
       <c r="B19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="H19" s="1">
         <v>44020</v>
@@ -17132,7 +17132,7 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H20" s="1">
         <v>44021</v>
@@ -17145,7 +17145,7 @@
       <c r="B21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17155,7 +17155,7 @@
       <c r="B22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H22" s="1">
         <v>44023</v>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="F23" s="3"/>
       <c r="G23" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H23" s="1">
         <v>44024</v>
@@ -17184,7 +17184,7 @@
       <c r="B24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H24" s="1">
         <v>44025</v>
@@ -17200,7 +17200,7 @@
       </c>
       <c r="F25" s="3"/>
       <c r="G25" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
@@ -17210,7 +17210,7 @@
       <c r="B26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="8" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H26" s="6">
         <v>44027</v>
@@ -17226,7 +17226,7 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17236,7 +17236,7 @@
       <c r="B28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H28" s="1">
         <v>44029</v>
@@ -17249,7 +17249,7 @@
       <c r="B29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H29" s="1">
         <v>44030</v>
@@ -17262,7 +17262,7 @@
       <c r="B30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H30" s="1">
         <v>44031</v>
@@ -17275,7 +17275,7 @@
       <c r="B31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17285,7 +17285,7 @@
       <c r="B32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H32" s="1">
         <v>44033</v>
@@ -17298,7 +17298,7 @@
       <c r="B33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="H33" s="1">
         <v>44034</v>
@@ -17311,7 +17311,7 @@
       <c r="B34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H34" s="1">
         <v>44035</v>
@@ -17324,7 +17324,7 @@
       <c r="B35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17334,7 +17334,7 @@
       <c r="B36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H36" s="1">
         <v>44037</v>
@@ -17347,7 +17347,7 @@
       <c r="B37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="H37" s="1">
         <v>44038</v>
@@ -17360,7 +17360,7 @@
       <c r="B38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17370,7 +17370,7 @@
       <c r="B39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H39" s="1">
         <v>44040</v>
@@ -17383,7 +17383,7 @@
       <c r="B40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H40" s="1">
         <v>44041</v>
@@ -17396,7 +17396,7 @@
       <c r="B41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H41" s="1">
         <v>44042</v>
@@ -17409,7 +17409,7 @@
       <c r="B42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17419,7 +17419,7 @@
       <c r="B43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="H43" s="1">
         <v>44044</v>
@@ -17432,7 +17432,7 @@
       <c r="B44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17442,7 +17442,7 @@
       <c r="B45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H45" s="1">
         <v>44046</v>
@@ -17455,7 +17455,7 @@
       <c r="B46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H46" s="1">
         <v>44047</v>
@@ -17468,7 +17468,7 @@
       <c r="B47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17478,7 +17478,7 @@
       <c r="B48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H48" s="1">
         <v>44049</v>
@@ -17491,7 +17491,7 @@
       <c r="B49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H49" s="1">
         <v>44050</v>
@@ -17504,7 +17504,7 @@
       <c r="B50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H50" s="1">
         <v>44051</v>
@@ -17517,7 +17517,7 @@
       <c r="B51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" ht="94.5" x14ac:dyDescent="0.15">
@@ -17527,7 +17527,7 @@
       <c r="B52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H52" s="1">
         <v>44053</v>
@@ -17540,7 +17540,7 @@
       <c r="B53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="H53" s="1">
         <v>44054</v>
@@ -17553,7 +17553,7 @@
       <c r="B54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H54" s="1">
         <v>44055</v>
@@ -17566,7 +17566,7 @@
       <c r="B55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17576,7 +17576,7 @@
       <c r="B56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H56" s="1">
         <v>44057</v>
@@ -17589,7 +17589,7 @@
       <c r="B57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H57" s="1">
         <v>44058</v>
@@ -17602,7 +17602,7 @@
       <c r="B58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="H58" s="1">
         <v>44059</v>
@@ -17615,7 +17615,7 @@
       <c r="B59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17625,7 +17625,7 @@
       <c r="B60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H60" s="1">
         <v>44061</v>
@@ -17638,7 +17638,7 @@
       <c r="B61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17648,7 +17648,7 @@
       <c r="B62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17658,7 +17658,7 @@
       <c r="B63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H63" s="1">
         <v>44064</v>
@@ -17671,7 +17671,7 @@
       <c r="B64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17681,7 +17681,7 @@
       <c r="B65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H65" s="1">
         <v>44066</v>
@@ -17694,7 +17694,7 @@
       <c r="B66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17704,7 +17704,7 @@
       <c r="B67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H67" s="1">
         <v>44068</v>
@@ -17717,7 +17717,7 @@
       <c r="B68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="81" x14ac:dyDescent="0.15">
@@ -17727,7 +17727,7 @@
       <c r="B69" s="7"/>
       <c r="F69" s="7"/>
       <c r="G69" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="H69" s="1">
         <v>44070</v>
@@ -17740,7 +17740,7 @@
       <c r="B70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H70" s="1">
         <v>44071</v>
@@ -17753,7 +17753,7 @@
       <c r="B71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H71" s="1">
         <v>44071</v>
@@ -17766,7 +17766,7 @@
       <c r="B72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -17787,135 +17787,135 @@
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.15">
       <c r="B1" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="AN1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="AP1" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.15">
@@ -17925,62 +17925,62 @@
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.15">
@@ -17990,84 +17990,84 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B17" s="5"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B26" s="5"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.15">

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$470</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$471</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="667">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -2212,6 +2212,10 @@
   </si>
   <si>
     <t>我需要装备鱼饵，否则不能钓鱼！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我需要先装备斧头</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2616,7 +2620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J486"/>
+  <dimension ref="A2:J487"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -11347,7 +11351,7 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A297" s="1">
-        <v>3200</v>
+        <v>3016</v>
       </c>
       <c r="B297" s="3">
         <v>2</v>
@@ -11362,7 +11366,7 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -11376,7 +11380,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A298" s="1">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="B298" s="3">
         <v>2</v>
@@ -11391,7 +11395,7 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H298" s="1">
         <v>0</v>
@@ -11405,10 +11409,10 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A299" s="1">
-        <v>4000</v>
-      </c>
-      <c r="B299" s="3" t="s">
-        <v>477</v>
+        <v>3201</v>
+      </c>
+      <c r="B299" s="3">
+        <v>2</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>274</v>
@@ -11420,7 +11424,7 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>350</v>
+        <v>665</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
@@ -11429,12 +11433,12 @@
         <v>0</v>
       </c>
       <c r="J299" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A300" s="1">
-        <v>4001</v>
+        <v>4000</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>477</v>
@@ -11449,21 +11453,21 @@
         <v>181</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H300" s="1">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="I300" s="1">
         <v>0</v>
       </c>
       <c r="J300" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A301" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>477</v>
@@ -11478,7 +11482,7 @@
         <v>181</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>45</v>
+        <v>351</v>
       </c>
       <c r="H301" s="1">
         <v>4000</v>
@@ -11490,9 +11494,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A302" s="1">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>477</v>
@@ -11507,7 +11511,7 @@
         <v>181</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>352</v>
+        <v>45</v>
       </c>
       <c r="H302" s="1">
         <v>4000</v>
@@ -11519,9 +11523,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A303" s="1">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>477</v>
@@ -11536,7 +11540,7 @@
         <v>181</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H303" s="1">
         <v>4000</v>
@@ -11550,7 +11554,7 @@
     </row>
     <row r="304" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A304" s="1">
-        <v>4005</v>
+        <v>4004</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>477</v>
@@ -11565,21 +11569,21 @@
         <v>181</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H304" s="1">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I304" s="1">
         <v>0</v>
       </c>
       <c r="J304" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A305" s="1">
-        <v>4006</v>
+        <v>4005</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>477</v>
@@ -11594,21 +11598,21 @@
         <v>181</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H305" s="1">
-        <v>4005</v>
+        <v>0</v>
       </c>
       <c r="I305" s="1">
         <v>0</v>
       </c>
       <c r="J305" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A306" s="1">
-        <v>4007</v>
+        <v>4006</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>477</v>
@@ -11623,7 +11627,7 @@
         <v>181</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H306" s="1">
         <v>4005</v>
@@ -11637,7 +11641,7 @@
     </row>
     <row r="307" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A307" s="1">
-        <v>4008</v>
+        <v>4007</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>477</v>
@@ -11652,7 +11656,7 @@
         <v>181</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H307" s="1">
         <v>4005</v>
@@ -11666,7 +11670,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A308" s="1">
-        <v>4009</v>
+        <v>4008</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>477</v>
@@ -11681,7 +11685,7 @@
         <v>181</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H308" s="1">
         <v>4005</v>
@@ -11695,7 +11699,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A309" s="1">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>477</v>
@@ -11710,7 +11714,7 @@
         <v>181</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H309" s="1">
         <v>4005</v>
@@ -11724,7 +11728,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A310" s="1">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>477</v>
@@ -11739,21 +11743,21 @@
         <v>181</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H310" s="1">
-        <v>0</v>
+        <v>4005</v>
       </c>
       <c r="I310" s="1">
         <v>0</v>
       </c>
       <c r="J310" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A311" s="1">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>477</v>
@@ -11768,21 +11772,21 @@
         <v>181</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>49</v>
+        <v>360</v>
       </c>
       <c r="H311" s="1">
-        <v>4011</v>
+        <v>0</v>
       </c>
       <c r="I311" s="1">
         <v>0</v>
       </c>
       <c r="J311" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A312" s="1">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>477</v>
@@ -11797,7 +11801,7 @@
         <v>181</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>361</v>
+        <v>49</v>
       </c>
       <c r="H312" s="1">
         <v>4011</v>
@@ -11809,9 +11813,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A313" s="1">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>477</v>
@@ -11826,7 +11830,7 @@
         <v>181</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H313" s="1">
         <v>4011</v>
@@ -11840,7 +11844,7 @@
     </row>
     <row r="314" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A314" s="1">
-        <v>4015</v>
+        <v>4014</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>477</v>
@@ -11855,7 +11859,7 @@
         <v>181</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H314" s="1">
         <v>4011</v>
@@ -11869,7 +11873,7 @@
     </row>
     <row r="315" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A315" s="1">
-        <v>4016</v>
+        <v>4015</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>477</v>
@@ -11884,21 +11888,21 @@
         <v>181</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H315" s="1">
-        <v>0</v>
+        <v>4011</v>
       </c>
       <c r="I315" s="1">
         <v>0</v>
       </c>
       <c r="J315" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="316" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A316" s="1">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>477</v>
@@ -11913,21 +11917,21 @@
         <v>181</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>56</v>
+        <v>364</v>
       </c>
       <c r="H316" s="1">
-        <v>4016</v>
+        <v>0</v>
       </c>
       <c r="I316" s="1">
         <v>0</v>
       </c>
       <c r="J316" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A317" s="1">
-        <v>4018</v>
+        <v>4017</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>477</v>
@@ -11942,7 +11946,7 @@
         <v>181</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>365</v>
+        <v>56</v>
       </c>
       <c r="H317" s="1">
         <v>4016</v>
@@ -11956,7 +11960,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A318" s="1">
-        <v>4019</v>
+        <v>4018</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>477</v>
@@ -11971,7 +11975,7 @@
         <v>181</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H318" s="1">
         <v>4016</v>
@@ -11985,7 +11989,7 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A319" s="1">
-        <v>4020</v>
+        <v>4019</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>477</v>
@@ -12000,7 +12004,7 @@
         <v>181</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H319" s="1">
         <v>4016</v>
@@ -12014,7 +12018,7 @@
     </row>
     <row r="320" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A320" s="1">
-        <v>4021</v>
+        <v>4020</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>477</v>
@@ -12029,21 +12033,21 @@
         <v>181</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H320" s="1">
-        <v>0</v>
+        <v>4016</v>
       </c>
       <c r="I320" s="1">
         <v>0</v>
       </c>
       <c r="J320" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A321" s="1">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>477</v>
@@ -12058,21 +12062,21 @@
         <v>181</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H321" s="1">
-        <v>4021</v>
+        <v>0</v>
       </c>
       <c r="I321" s="1">
         <v>0</v>
       </c>
       <c r="J321" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A322" s="1">
-        <v>4023</v>
+        <v>4022</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>477</v>
@@ -12087,7 +12091,7 @@
         <v>181</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H322" s="1">
         <v>4021</v>
@@ -12099,9 +12103,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A323" s="1">
-        <v>4024</v>
+        <v>4023</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>477</v>
@@ -12116,7 +12120,7 @@
         <v>181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H323" s="1">
         <v>4021</v>
@@ -12128,9 +12132,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A324" s="1">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>477</v>
@@ -12145,7 +12149,7 @@
         <v>181</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H324" s="1">
         <v>4021</v>
@@ -12157,9 +12161,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A325" s="1">
-        <v>4026</v>
+        <v>4025</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>477</v>
@@ -12174,21 +12178,21 @@
         <v>181</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H325" s="1">
-        <v>0</v>
+        <v>4021</v>
       </c>
       <c r="I325" s="1">
         <v>0</v>
       </c>
       <c r="J325" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A326" s="1">
-        <v>4027</v>
+        <v>4026</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>477</v>
@@ -12203,21 +12207,21 @@
         <v>181</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H326" s="1">
-        <v>4026</v>
+        <v>0</v>
       </c>
       <c r="I326" s="1">
         <v>0</v>
       </c>
       <c r="J326" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A327" s="1">
-        <v>4028</v>
+        <v>4027</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>477</v>
@@ -12232,7 +12236,7 @@
         <v>181</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H327" s="1">
         <v>4026</v>
@@ -12246,7 +12250,7 @@
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A328" s="1">
-        <v>4029</v>
+        <v>4028</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>477</v>
@@ -12261,7 +12265,7 @@
         <v>181</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H328" s="1">
         <v>4026</v>
@@ -12275,7 +12279,7 @@
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A329" s="1">
-        <v>4030</v>
+        <v>4029</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>477</v>
@@ -12290,7 +12294,7 @@
         <v>181</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H329" s="1">
         <v>4026</v>
@@ -12304,7 +12308,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A330" s="1">
-        <v>4031</v>
+        <v>4030</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>477</v>
@@ -12319,21 +12323,21 @@
         <v>181</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H330" s="1">
-        <v>0</v>
+        <v>4026</v>
       </c>
       <c r="I330" s="1">
         <v>0</v>
       </c>
       <c r="J330" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A331" s="1">
-        <v>4032</v>
+        <v>4031</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>477</v>
@@ -12348,21 +12352,21 @@
         <v>181</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H331" s="1">
-        <v>4031</v>
+        <v>0</v>
       </c>
       <c r="I331" s="1">
         <v>0</v>
       </c>
       <c r="J331" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A332" s="1">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>477</v>
@@ -12377,7 +12381,7 @@
         <v>181</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H332" s="1">
         <v>4031</v>
@@ -12389,9 +12393,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A333" s="1">
-        <v>4034</v>
+        <v>4033</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>477</v>
@@ -12406,7 +12410,7 @@
         <v>181</v>
       </c>
       <c r="G333" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H333" s="1">
         <v>4031</v>
@@ -12418,9 +12422,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A334" s="1">
-        <v>4035</v>
+        <v>4034</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>477</v>
@@ -12435,7 +12439,7 @@
         <v>181</v>
       </c>
       <c r="G334" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H334" s="1">
         <v>4031</v>
@@ -12447,9 +12451,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A335" s="1">
-        <v>4036</v>
+        <v>4035</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>477</v>
@@ -12464,21 +12468,21 @@
         <v>181</v>
       </c>
       <c r="G335" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H335" s="1">
-        <v>0</v>
+        <v>4031</v>
       </c>
       <c r="I335" s="1">
         <v>0</v>
       </c>
       <c r="J335" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A336" s="1">
-        <v>4037</v>
+        <v>4036</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>477</v>
@@ -12493,21 +12497,21 @@
         <v>181</v>
       </c>
       <c r="G336" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H336" s="1">
-        <v>4036</v>
+        <v>0</v>
       </c>
       <c r="I336" s="1">
         <v>0</v>
       </c>
       <c r="J336" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A337" s="1">
-        <v>4038</v>
+        <v>4037</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>477</v>
@@ -12522,7 +12526,7 @@
         <v>181</v>
       </c>
       <c r="G337" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H337" s="1">
         <v>4036</v>
@@ -12536,7 +12540,7 @@
     </row>
     <row r="338" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A338" s="1">
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>477</v>
@@ -12551,7 +12555,7 @@
         <v>181</v>
       </c>
       <c r="G338" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H338" s="1">
         <v>4036</v>
@@ -12565,7 +12569,7 @@
     </row>
     <row r="339" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A339" s="1">
-        <v>4040</v>
+        <v>4039</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>477</v>
@@ -12580,7 +12584,7 @@
         <v>181</v>
       </c>
       <c r="G339" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H339" s="1">
         <v>4036</v>
@@ -12594,7 +12598,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A340" s="1">
-        <v>4041</v>
+        <v>4040</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>477</v>
@@ -12609,21 +12613,21 @@
         <v>181</v>
       </c>
       <c r="G340" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H340" s="1">
-        <v>0</v>
+        <v>4036</v>
       </c>
       <c r="I340" s="1">
         <v>0</v>
       </c>
       <c r="J340" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A341" s="1">
-        <v>4042</v>
+        <v>4041</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>477</v>
@@ -12638,21 +12642,21 @@
         <v>181</v>
       </c>
       <c r="G341" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H341" s="1">
-        <v>4041</v>
+        <v>0</v>
       </c>
       <c r="I341" s="1">
         <v>0</v>
       </c>
       <c r="J341" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A342" s="1">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>477</v>
@@ -12667,7 +12671,7 @@
         <v>181</v>
       </c>
       <c r="G342" s="1" t="s">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="H342" s="1">
         <v>4041</v>
@@ -12679,9 +12683,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A343" s="1">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>477</v>
@@ -12696,7 +12700,7 @@
         <v>181</v>
       </c>
       <c r="G343" s="1" t="s">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="H343" s="1">
         <v>4041</v>
@@ -12710,7 +12714,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A344" s="1">
-        <v>4045</v>
+        <v>4044</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>477</v>
@@ -12725,7 +12729,7 @@
         <v>181</v>
       </c>
       <c r="G344" s="1" t="s">
-        <v>390</v>
+        <v>219</v>
       </c>
       <c r="H344" s="1">
         <v>4041</v>
@@ -12739,7 +12743,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A345" s="1">
-        <v>4046</v>
+        <v>4045</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>477</v>
@@ -12754,21 +12758,21 @@
         <v>181</v>
       </c>
       <c r="G345" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H345" s="1">
-        <v>0</v>
+        <v>4041</v>
       </c>
       <c r="I345" s="1">
         <v>0</v>
       </c>
       <c r="J345" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A346" s="1">
-        <v>4047</v>
+        <v>4046</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>477</v>
@@ -12783,21 +12787,21 @@
         <v>181</v>
       </c>
       <c r="G346" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H346" s="1">
-        <v>4046</v>
+        <v>0</v>
       </c>
       <c r="I346" s="1">
         <v>0</v>
       </c>
       <c r="J346" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A347" s="1">
-        <v>4048</v>
+        <v>4047</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>477</v>
@@ -12812,7 +12816,7 @@
         <v>181</v>
       </c>
       <c r="G347" s="1" t="s">
-        <v>61</v>
+        <v>392</v>
       </c>
       <c r="H347" s="1">
         <v>4046</v>
@@ -12824,9 +12828,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A348" s="1">
-        <v>4049</v>
+        <v>4048</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>477</v>
@@ -12841,7 +12845,7 @@
         <v>181</v>
       </c>
       <c r="G348" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H348" s="1">
         <v>4046</v>
@@ -12855,7 +12859,7 @@
     </row>
     <row r="349" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A349" s="1">
-        <v>4050</v>
+        <v>4049</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>477</v>
@@ -12870,7 +12874,7 @@
         <v>181</v>
       </c>
       <c r="G349" s="1" t="s">
-        <v>393</v>
+        <v>62</v>
       </c>
       <c r="H349" s="1">
         <v>4046</v>
@@ -12884,7 +12888,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A350" s="1">
-        <v>4051</v>
+        <v>4050</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>477</v>
@@ -12899,21 +12903,21 @@
         <v>181</v>
       </c>
       <c r="G350" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H350" s="1">
-        <v>0</v>
+        <v>4046</v>
       </c>
       <c r="I350" s="1">
         <v>0</v>
       </c>
       <c r="J350" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A351" s="1">
-        <v>4052</v>
+        <v>4051</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>477</v>
@@ -12928,21 +12932,21 @@
         <v>181</v>
       </c>
       <c r="G351" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H351" s="1">
-        <v>4051</v>
+        <v>0</v>
       </c>
       <c r="I351" s="1">
         <v>0</v>
       </c>
       <c r="J351" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A352" s="1">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>477</v>
@@ -12957,7 +12961,7 @@
         <v>181</v>
       </c>
       <c r="G352" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H352" s="1">
         <v>4051</v>
@@ -12971,7 +12975,7 @@
     </row>
     <row r="353" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A353" s="1">
-        <v>4054</v>
+        <v>4053</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>477</v>
@@ -12986,7 +12990,7 @@
         <v>181</v>
       </c>
       <c r="G353" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H353" s="1">
         <v>4051</v>
@@ -13000,7 +13004,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A354" s="1">
-        <v>4055</v>
+        <v>4054</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>477</v>
@@ -13015,7 +13019,7 @@
         <v>181</v>
       </c>
       <c r="G354" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H354" s="1">
         <v>4051</v>
@@ -13029,7 +13033,7 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A355" s="1">
-        <v>4056</v>
+        <v>4055</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>477</v>
@@ -13044,21 +13048,21 @@
         <v>181</v>
       </c>
       <c r="G355" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H355" s="1">
-        <v>0</v>
+        <v>4051</v>
       </c>
       <c r="I355" s="1">
         <v>0</v>
       </c>
       <c r="J355" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A356" s="1">
-        <v>4057</v>
+        <v>4056</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>477</v>
@@ -13073,21 +13077,21 @@
         <v>181</v>
       </c>
       <c r="G356" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H356" s="1">
-        <v>4056</v>
+        <v>0</v>
       </c>
       <c r="I356" s="1">
         <v>0</v>
       </c>
       <c r="J356" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A357" s="1">
-        <v>4058</v>
+        <v>4057</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>477</v>
@@ -13102,7 +13106,7 @@
         <v>181</v>
       </c>
       <c r="G357" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H357" s="1">
         <v>4056</v>
@@ -13116,7 +13120,7 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A358" s="1">
-        <v>4059</v>
+        <v>4058</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>477</v>
@@ -13131,7 +13135,7 @@
         <v>181</v>
       </c>
       <c r="G358" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H358" s="1">
         <v>4056</v>
@@ -13145,7 +13149,7 @@
     </row>
     <row r="359" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A359" s="1">
-        <v>4060</v>
+        <v>4059</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>477</v>
@@ -13160,7 +13164,7 @@
         <v>181</v>
       </c>
       <c r="G359" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H359" s="1">
         <v>4056</v>
@@ -13174,7 +13178,7 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A360" s="1">
-        <v>4061</v>
+        <v>4060</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>477</v>
@@ -13189,21 +13193,21 @@
         <v>181</v>
       </c>
       <c r="G360" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H360" s="1">
-        <v>0</v>
+        <v>4056</v>
       </c>
       <c r="I360" s="1">
         <v>0</v>
       </c>
       <c r="J360" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A361" s="1">
-        <v>4062</v>
+        <v>4061</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>477</v>
@@ -13218,21 +13222,21 @@
         <v>181</v>
       </c>
       <c r="G361" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H361" s="1">
-        <v>4061</v>
+        <v>0</v>
       </c>
       <c r="I361" s="1">
         <v>0</v>
       </c>
       <c r="J361" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A362" s="1">
-        <v>4063</v>
+        <v>4062</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>477</v>
@@ -13247,7 +13251,7 @@
         <v>181</v>
       </c>
       <c r="G362" s="1" t="s">
-        <v>51</v>
+        <v>405</v>
       </c>
       <c r="H362" s="1">
         <v>4061</v>
@@ -13259,9 +13263,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A363" s="1">
-        <v>4064</v>
+        <v>4063</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>477</v>
@@ -13276,7 +13280,7 @@
         <v>181</v>
       </c>
       <c r="G363" s="1" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H363" s="1">
         <v>4061</v>
@@ -13290,7 +13294,7 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A364" s="1">
-        <v>4065</v>
+        <v>4064</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>477</v>
@@ -13305,7 +13309,7 @@
         <v>181</v>
       </c>
       <c r="G364" s="1" t="s">
-        <v>406</v>
+        <v>58</v>
       </c>
       <c r="H364" s="1">
         <v>4061</v>
@@ -13317,9 +13321,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A365" s="1">
-        <v>4066</v>
+        <v>4065</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>477</v>
@@ -13334,21 +13338,21 @@
         <v>181</v>
       </c>
       <c r="G365" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H365" s="1">
-        <v>0</v>
+        <v>4061</v>
       </c>
       <c r="I365" s="1">
         <v>0</v>
       </c>
       <c r="J365" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A366" s="1">
-        <v>4067</v>
+        <v>4066</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>477</v>
@@ -13363,21 +13367,21 @@
         <v>181</v>
       </c>
       <c r="G366" s="1" t="s">
-        <v>81</v>
+        <v>407</v>
       </c>
       <c r="H366" s="1">
-        <v>4066</v>
+        <v>0</v>
       </c>
       <c r="I366" s="1">
         <v>0</v>
       </c>
       <c r="J366" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A367" s="1">
-        <v>4068</v>
+        <v>4067</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>477</v>
@@ -13392,7 +13396,7 @@
         <v>181</v>
       </c>
       <c r="G367" s="1" t="s">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="H367" s="1">
         <v>4066</v>
@@ -13404,9 +13408,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A368" s="1">
-        <v>4069</v>
+        <v>4068</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>477</v>
@@ -13421,7 +13425,7 @@
         <v>181</v>
       </c>
       <c r="G368" s="1" t="s">
-        <v>65</v>
+        <v>408</v>
       </c>
       <c r="H368" s="1">
         <v>4066</v>
@@ -13433,9 +13437,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A369" s="1">
-        <v>4070</v>
+        <v>4069</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>477</v>
@@ -13450,7 +13454,7 @@
         <v>181</v>
       </c>
       <c r="G369" s="1" t="s">
-        <v>409</v>
+        <v>65</v>
       </c>
       <c r="H369" s="1">
         <v>4066</v>
@@ -13464,7 +13468,7 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A370" s="1">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>477</v>
@@ -13479,21 +13483,21 @@
         <v>181</v>
       </c>
       <c r="G370" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H370" s="1">
-        <v>0</v>
+        <v>4066</v>
       </c>
       <c r="I370" s="1">
         <v>0</v>
       </c>
       <c r="J370" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="371" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A371" s="1">
-        <v>4072</v>
+        <v>4071</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>477</v>
@@ -13508,21 +13512,21 @@
         <v>181</v>
       </c>
       <c r="G371" s="1" t="s">
-        <v>68</v>
+        <v>410</v>
       </c>
       <c r="H371" s="1">
-        <v>4071</v>
+        <v>0</v>
       </c>
       <c r="I371" s="1">
         <v>0</v>
       </c>
       <c r="J371" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A372" s="1">
-        <v>4073</v>
+        <v>4072</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>477</v>
@@ -13537,7 +13541,7 @@
         <v>181</v>
       </c>
       <c r="G372" s="1" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H372" s="1">
         <v>4071</v>
@@ -13551,7 +13555,7 @@
     </row>
     <row r="373" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A373" s="1">
-        <v>4074</v>
+        <v>4073</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>477</v>
@@ -13566,7 +13570,7 @@
         <v>181</v>
       </c>
       <c r="G373" s="1" t="s">
-        <v>411</v>
+        <v>84</v>
       </c>
       <c r="H373" s="1">
         <v>4071</v>
@@ -13580,7 +13584,7 @@
     </row>
     <row r="374" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A374" s="1">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>477</v>
@@ -13595,7 +13599,7 @@
         <v>181</v>
       </c>
       <c r="G374" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H374" s="1">
         <v>4071</v>
@@ -13609,7 +13613,7 @@
     </row>
     <row r="375" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A375" s="1">
-        <v>4076</v>
+        <v>4075</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>477</v>
@@ -13624,21 +13628,21 @@
         <v>181</v>
       </c>
       <c r="G375" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H375" s="1">
-        <v>0</v>
+        <v>4071</v>
       </c>
       <c r="I375" s="1">
         <v>0</v>
       </c>
       <c r="J375" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A376" s="1">
-        <v>4077</v>
+        <v>4076</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>477</v>
@@ -13653,21 +13657,21 @@
         <v>181</v>
       </c>
       <c r="G376" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H376" s="1">
-        <v>4076</v>
+        <v>0</v>
       </c>
       <c r="I376" s="1">
         <v>0</v>
       </c>
       <c r="J376" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A377" s="1">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>477</v>
@@ -13682,7 +13686,7 @@
         <v>181</v>
       </c>
       <c r="G377" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H377" s="1">
         <v>4076</v>
@@ -13696,7 +13700,7 @@
     </row>
     <row r="378" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A378" s="1">
-        <v>4079</v>
+        <v>4078</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>477</v>
@@ -13711,7 +13715,7 @@
         <v>181</v>
       </c>
       <c r="G378" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H378" s="1">
         <v>4076</v>
@@ -13725,7 +13729,7 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A379" s="1">
-        <v>4080</v>
+        <v>4079</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>477</v>
@@ -13740,7 +13744,7 @@
         <v>181</v>
       </c>
       <c r="G379" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H379" s="1">
         <v>4076</v>
@@ -13754,7 +13758,7 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A380" s="1">
-        <v>4081</v>
+        <v>4080</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>477</v>
@@ -13769,21 +13773,21 @@
         <v>181</v>
       </c>
       <c r="G380" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H380" s="1">
-        <v>0</v>
+        <v>4076</v>
       </c>
       <c r="I380" s="1">
         <v>0</v>
       </c>
       <c r="J380" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="381" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A381" s="1">
-        <v>4082</v>
+        <v>4081</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>477</v>
@@ -13798,21 +13802,21 @@
         <v>181</v>
       </c>
       <c r="G381" s="1" t="s">
-        <v>80</v>
+        <v>418</v>
       </c>
       <c r="H381" s="1">
-        <v>4081</v>
+        <v>0</v>
       </c>
       <c r="I381" s="1">
         <v>0</v>
       </c>
       <c r="J381" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A382" s="1">
-        <v>4083</v>
+        <v>4082</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>477</v>
@@ -13827,7 +13831,7 @@
         <v>181</v>
       </c>
       <c r="G382" s="1" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="H382" s="1">
         <v>4081</v>
@@ -13841,7 +13845,7 @@
     </row>
     <row r="383" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A383" s="1">
-        <v>4084</v>
+        <v>4083</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>477</v>
@@ -13856,7 +13860,7 @@
         <v>181</v>
       </c>
       <c r="G383" s="1" t="s">
-        <v>326</v>
+        <v>59</v>
       </c>
       <c r="H383" s="1">
         <v>4081</v>
@@ -13868,9 +13872,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A384" s="1">
-        <v>4085</v>
+        <v>4084</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>477</v>
@@ -13885,7 +13889,7 @@
         <v>181</v>
       </c>
       <c r="G384" s="1" t="s">
-        <v>419</v>
+        <v>326</v>
       </c>
       <c r="H384" s="1">
         <v>4081</v>
@@ -13899,7 +13903,7 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A385" s="1">
-        <v>4086</v>
+        <v>4085</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>477</v>
@@ -13914,21 +13918,21 @@
         <v>181</v>
       </c>
       <c r="G385" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H385" s="1">
-        <v>0</v>
+        <v>4081</v>
       </c>
       <c r="I385" s="1">
         <v>0</v>
       </c>
       <c r="J385" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A386" s="1">
-        <v>4087</v>
+        <v>4086</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>477</v>
@@ -13943,21 +13947,21 @@
         <v>181</v>
       </c>
       <c r="G386" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H386" s="1">
-        <v>4086</v>
+        <v>0</v>
       </c>
       <c r="I386" s="1">
         <v>0</v>
       </c>
       <c r="J386" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A387" s="1">
-        <v>4088</v>
+        <v>4087</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>477</v>
@@ -13972,7 +13976,7 @@
         <v>181</v>
       </c>
       <c r="G387" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H387" s="1">
         <v>4086</v>
@@ -13986,7 +13990,7 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A388" s="1">
-        <v>4089</v>
+        <v>4088</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>477</v>
@@ -14001,7 +14005,7 @@
         <v>181</v>
       </c>
       <c r="G388" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H388" s="1">
         <v>4086</v>
@@ -14015,7 +14019,7 @@
     </row>
     <row r="389" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A389" s="1">
-        <v>4090</v>
+        <v>4089</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>477</v>
@@ -14030,7 +14034,7 @@
         <v>181</v>
       </c>
       <c r="G389" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H389" s="1">
         <v>4086</v>
@@ -14044,7 +14048,7 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A390" s="1">
-        <v>4091</v>
+        <v>4090</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>477</v>
@@ -14059,21 +14063,21 @@
         <v>181</v>
       </c>
       <c r="G390" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H390" s="1">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="I390" s="1">
         <v>0</v>
       </c>
       <c r="J390" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A391" s="1">
-        <v>4092</v>
+        <v>4091</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>477</v>
@@ -14088,21 +14092,21 @@
         <v>181</v>
       </c>
       <c r="G391" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H391" s="1">
-        <v>4091</v>
+        <v>0</v>
       </c>
       <c r="I391" s="1">
         <v>0</v>
       </c>
       <c r="J391" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A392" s="1">
-        <v>4093</v>
+        <v>4092</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>477</v>
@@ -14117,7 +14121,7 @@
         <v>181</v>
       </c>
       <c r="G392" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H392" s="1">
         <v>4091</v>
@@ -14131,7 +14135,7 @@
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A393" s="1">
-        <v>4094</v>
+        <v>4093</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>477</v>
@@ -14146,7 +14150,7 @@
         <v>181</v>
       </c>
       <c r="G393" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H393" s="1">
         <v>4091</v>
@@ -14160,7 +14164,7 @@
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A394" s="1">
-        <v>4095</v>
+        <v>4094</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>477</v>
@@ -14175,7 +14179,7 @@
         <v>181</v>
       </c>
       <c r="G394" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H394" s="1">
         <v>4091</v>
@@ -14189,7 +14193,7 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A395" s="1">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>477</v>
@@ -14204,21 +14208,21 @@
         <v>181</v>
       </c>
       <c r="G395" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H395" s="1">
-        <v>0</v>
+        <v>4091</v>
       </c>
       <c r="I395" s="1">
         <v>0</v>
       </c>
       <c r="J395" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A396" s="1">
-        <v>4097</v>
+        <v>4096</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>477</v>
@@ -14233,21 +14237,21 @@
         <v>181</v>
       </c>
       <c r="G396" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H396" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="I396" s="1">
         <v>0</v>
       </c>
       <c r="J396" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A397" s="1">
-        <v>4098</v>
+        <v>4097</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>477</v>
@@ -14262,7 +14266,7 @@
         <v>181</v>
       </c>
       <c r="G397" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H397" s="1">
         <v>4096</v>
@@ -14276,7 +14280,7 @@
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A398" s="1">
-        <v>4099</v>
+        <v>4098</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>477</v>
@@ -14291,7 +14295,7 @@
         <v>181</v>
       </c>
       <c r="G398" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H398" s="1">
         <v>4096</v>
@@ -14305,7 +14309,7 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A399" s="1">
-        <v>4100</v>
+        <v>4099</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>477</v>
@@ -14320,7 +14324,7 @@
         <v>181</v>
       </c>
       <c r="G399" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H399" s="1">
         <v>4096</v>
@@ -14334,7 +14338,7 @@
     </row>
     <row r="400" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A400" s="1">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>477</v>
@@ -14349,21 +14353,21 @@
         <v>181</v>
       </c>
       <c r="G400" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H400" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="I400" s="1">
         <v>0</v>
       </c>
       <c r="J400" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A401" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>477</v>
@@ -14378,21 +14382,21 @@
         <v>181</v>
       </c>
       <c r="G401" s="1" t="s">
-        <v>83</v>
+        <v>435</v>
       </c>
       <c r="H401" s="1">
-        <v>4101</v>
+        <v>0</v>
       </c>
       <c r="I401" s="1">
         <v>0</v>
       </c>
       <c r="J401" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A402" s="1">
-        <v>4103</v>
+        <v>4102</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>477</v>
@@ -14407,7 +14411,7 @@
         <v>181</v>
       </c>
       <c r="G402" s="1" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H402" s="1">
         <v>4101</v>
@@ -14419,9 +14423,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A403" s="1">
-        <v>4104</v>
+        <v>4103</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>477</v>
@@ -14436,7 +14440,7 @@
         <v>181</v>
       </c>
       <c r="G403" s="1" t="s">
-        <v>218</v>
+        <v>74</v>
       </c>
       <c r="H403" s="1">
         <v>4101</v>
@@ -14450,7 +14454,7 @@
     </row>
     <row r="404" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A404" s="1">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>477</v>
@@ -14465,7 +14469,7 @@
         <v>181</v>
       </c>
       <c r="G404" s="1" t="s">
-        <v>436</v>
+        <v>218</v>
       </c>
       <c r="H404" s="1">
         <v>4101</v>
@@ -14477,9 +14481,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A405" s="1">
-        <v>4106</v>
+        <v>4105</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>477</v>
@@ -14494,21 +14498,21 @@
         <v>181</v>
       </c>
       <c r="G405" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H405" s="1">
-        <v>0</v>
+        <v>4101</v>
       </c>
       <c r="I405" s="1">
         <v>0</v>
       </c>
       <c r="J405" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A406" s="1">
-        <v>4107</v>
+        <v>4106</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>477</v>
@@ -14523,21 +14527,21 @@
         <v>181</v>
       </c>
       <c r="G406" s="1" t="s">
-        <v>75</v>
+        <v>437</v>
       </c>
       <c r="H406" s="1">
-        <v>4106</v>
+        <v>0</v>
       </c>
       <c r="I406" s="1">
         <v>0</v>
       </c>
       <c r="J406" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="407" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A407" s="1">
-        <v>4108</v>
+        <v>4107</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>477</v>
@@ -14552,7 +14556,7 @@
         <v>181</v>
       </c>
       <c r="G407" s="1" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="H407" s="1">
         <v>4106</v>
@@ -14566,7 +14570,7 @@
     </row>
     <row r="408" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A408" s="1">
-        <v>4109</v>
+        <v>4108</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>477</v>
@@ -14581,7 +14585,7 @@
         <v>181</v>
       </c>
       <c r="G408" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="H408" s="1">
         <v>4106</v>
@@ -14593,9 +14597,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A409" s="1">
-        <v>4110</v>
+        <v>4109</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>477</v>
@@ -14610,7 +14614,7 @@
         <v>181</v>
       </c>
       <c r="G409" s="1" t="s">
-        <v>438</v>
+        <v>67</v>
       </c>
       <c r="H409" s="1">
         <v>4106</v>
@@ -14624,7 +14628,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A410" s="1">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>477</v>
@@ -14639,21 +14643,21 @@
         <v>181</v>
       </c>
       <c r="G410" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H410" s="1">
-        <v>0</v>
+        <v>4106</v>
       </c>
       <c r="I410" s="1">
         <v>0</v>
       </c>
       <c r="J410" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A411" s="1">
-        <v>4112</v>
+        <v>4111</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>477</v>
@@ -14668,21 +14672,21 @@
         <v>181</v>
       </c>
       <c r="G411" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H411" s="1">
-        <v>4111</v>
+        <v>0</v>
       </c>
       <c r="I411" s="1">
         <v>0</v>
       </c>
       <c r="J411" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A412" s="1">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>477</v>
@@ -14697,7 +14701,7 @@
         <v>181</v>
       </c>
       <c r="G412" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H412" s="1">
         <v>4111</v>
@@ -14711,7 +14715,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A413" s="1">
-        <v>4114</v>
+        <v>4113</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>477</v>
@@ -14725,8 +14729,8 @@
       <c r="F413" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G413" s="2" t="s">
-        <v>442</v>
+      <c r="G413" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="H413" s="1">
         <v>4111</v>
@@ -14740,7 +14744,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A414" s="1">
-        <v>4115</v>
+        <v>4114</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>477</v>
@@ -14754,8 +14758,8 @@
       <c r="F414" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G414" s="1" t="s">
-        <v>443</v>
+      <c r="G414" s="2" t="s">
+        <v>442</v>
       </c>
       <c r="H414" s="1">
         <v>4111</v>
@@ -14769,7 +14773,7 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A415" s="1">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>477</v>
@@ -14784,21 +14788,21 @@
         <v>181</v>
       </c>
       <c r="G415" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H415" s="1">
-        <v>0</v>
+        <v>4111</v>
       </c>
       <c r="I415" s="1">
         <v>0</v>
       </c>
       <c r="J415" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="416" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A416" s="1">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>477</v>
@@ -14813,21 +14817,21 @@
         <v>181</v>
       </c>
       <c r="G416" s="1" t="s">
-        <v>70</v>
+        <v>444</v>
       </c>
       <c r="H416" s="1">
-        <v>4116</v>
+        <v>0</v>
       </c>
       <c r="I416" s="1">
         <v>0</v>
       </c>
       <c r="J416" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A417" s="1">
-        <v>4118</v>
+        <v>4117</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>477</v>
@@ -14842,7 +14846,7 @@
         <v>181</v>
       </c>
       <c r="G417" s="1" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="H417" s="1">
         <v>4116</v>
@@ -14854,9 +14858,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A418" s="1">
-        <v>4119</v>
+        <v>4118</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>477</v>
@@ -14871,7 +14875,7 @@
         <v>181</v>
       </c>
       <c r="G418" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H418" s="1">
         <v>4116</v>
@@ -14885,7 +14889,7 @@
     </row>
     <row r="419" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A419" s="1">
-        <v>4120</v>
+        <v>4119</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>477</v>
@@ -14900,7 +14904,7 @@
         <v>181</v>
       </c>
       <c r="G419" s="1" t="s">
-        <v>445</v>
+        <v>63</v>
       </c>
       <c r="H419" s="1">
         <v>4116</v>
@@ -14912,9 +14916,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A420" s="1">
-        <v>4121</v>
+        <v>4120</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>477</v>
@@ -14929,21 +14933,21 @@
         <v>181</v>
       </c>
       <c r="G420" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H420" s="1">
-        <v>0</v>
+        <v>4116</v>
       </c>
       <c r="I420" s="1">
         <v>0</v>
       </c>
       <c r="J420" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A421" s="1">
-        <v>4122</v>
+        <v>4121</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>477</v>
@@ -14958,21 +14962,21 @@
         <v>181</v>
       </c>
       <c r="G421" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H421" s="1">
-        <v>4121</v>
+        <v>0</v>
       </c>
       <c r="I421" s="1">
         <v>0</v>
       </c>
       <c r="J421" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="422" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A422" s="1">
-        <v>4123</v>
+        <v>4122</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>477</v>
@@ -14987,7 +14991,7 @@
         <v>181</v>
       </c>
       <c r="G422" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H422" s="1">
         <v>4121</v>
@@ -15001,7 +15005,7 @@
     </row>
     <row r="423" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A423" s="1">
-        <v>4124</v>
+        <v>4123</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>477</v>
@@ -15016,7 +15020,7 @@
         <v>181</v>
       </c>
       <c r="G423" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H423" s="1">
         <v>4121</v>
@@ -15030,7 +15034,7 @@
     </row>
     <row r="424" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A424" s="1">
-        <v>4125</v>
+        <v>4124</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>477</v>
@@ -15045,7 +15049,7 @@
         <v>181</v>
       </c>
       <c r="G424" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H424" s="1">
         <v>4121</v>
@@ -15059,7 +15063,7 @@
     </row>
     <row r="425" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A425" s="1">
-        <v>4126</v>
+        <v>4125</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>477</v>
@@ -15074,21 +15078,21 @@
         <v>181</v>
       </c>
       <c r="G425" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H425" s="1">
-        <v>0</v>
+        <v>4121</v>
       </c>
       <c r="I425" s="1">
         <v>0</v>
       </c>
       <c r="J425" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A426" s="1">
-        <v>4127</v>
+        <v>4126</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>477</v>
@@ -15103,21 +15107,21 @@
         <v>181</v>
       </c>
       <c r="G426" s="1" t="s">
-        <v>71</v>
+        <v>451</v>
       </c>
       <c r="H426" s="1">
-        <v>4126</v>
+        <v>0</v>
       </c>
       <c r="I426" s="1">
         <v>0</v>
       </c>
       <c r="J426" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A427" s="1">
-        <v>4128</v>
+        <v>4127</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>477</v>
@@ -15132,7 +15136,7 @@
         <v>181</v>
       </c>
       <c r="G427" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H427" s="1">
         <v>4126</v>
@@ -15144,9 +15148,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A428" s="1">
-        <v>4129</v>
+        <v>4128</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>477</v>
@@ -15161,7 +15165,7 @@
         <v>181</v>
       </c>
       <c r="G428" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H428" s="1">
         <v>4126</v>
@@ -15173,9 +15177,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A429" s="1">
-        <v>4130</v>
+        <v>4129</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>477</v>
@@ -15190,7 +15194,7 @@
         <v>181</v>
       </c>
       <c r="G429" s="1" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="H429" s="1">
         <v>4126</v>
@@ -15202,9 +15206,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A430" s="1">
-        <v>4131</v>
+        <v>4130</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>477</v>
@@ -15219,7 +15223,7 @@
         <v>181</v>
       </c>
       <c r="G430" s="1" t="s">
-        <v>452</v>
+        <v>55</v>
       </c>
       <c r="H430" s="1">
         <v>4126</v>
@@ -15231,9 +15235,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A431" s="1">
-        <v>4132</v>
+        <v>4131</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>477</v>
@@ -15248,21 +15252,21 @@
         <v>181</v>
       </c>
       <c r="G431" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H431" s="1">
-        <v>0</v>
+        <v>4126</v>
       </c>
       <c r="I431" s="1">
         <v>0</v>
       </c>
       <c r="J431" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="432" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A432" s="1">
-        <v>4133</v>
+        <v>4132</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>477</v>
@@ -15277,21 +15281,21 @@
         <v>181</v>
       </c>
       <c r="G432" s="1" t="s">
-        <v>82</v>
+        <v>453</v>
       </c>
       <c r="H432" s="1">
-        <v>4132</v>
+        <v>0</v>
       </c>
       <c r="I432" s="1">
         <v>0</v>
       </c>
       <c r="J432" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A433" s="1">
-        <v>4134</v>
+        <v>4133</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>477</v>
@@ -15306,7 +15310,7 @@
         <v>181</v>
       </c>
       <c r="G433" s="1" t="s">
-        <v>454</v>
+        <v>82</v>
       </c>
       <c r="H433" s="1">
         <v>4132</v>
@@ -15318,9 +15322,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A434" s="1">
-        <v>4135</v>
+        <v>4134</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>477</v>
@@ -15335,7 +15339,7 @@
         <v>181</v>
       </c>
       <c r="G434" s="1" t="s">
-        <v>66</v>
+        <v>454</v>
       </c>
       <c r="H434" s="1">
         <v>4132</v>
@@ -15347,9 +15351,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A435" s="1">
-        <v>4136</v>
+        <v>4135</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>477</v>
@@ -15364,7 +15368,7 @@
         <v>181</v>
       </c>
       <c r="G435" s="1" t="s">
-        <v>455</v>
+        <v>66</v>
       </c>
       <c r="H435" s="1">
         <v>4132</v>
@@ -15376,9 +15380,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A436" s="1">
-        <v>4137</v>
+        <v>4136</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>477</v>
@@ -15393,21 +15397,21 @@
         <v>181</v>
       </c>
       <c r="G436" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H436" s="1">
-        <v>0</v>
+        <v>4132</v>
       </c>
       <c r="I436" s="1">
         <v>0</v>
       </c>
       <c r="J436" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A437" s="1">
-        <v>4138</v>
+        <v>4137</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>477</v>
@@ -15422,21 +15426,21 @@
         <v>181</v>
       </c>
       <c r="G437" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H437" s="1">
-        <v>4137</v>
+        <v>0</v>
       </c>
       <c r="I437" s="1">
         <v>0</v>
       </c>
       <c r="J437" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="438" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A438" s="1">
-        <v>4139</v>
+        <v>4138</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>477</v>
@@ -15451,7 +15455,7 @@
         <v>181</v>
       </c>
       <c r="G438" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H438" s="1">
         <v>4137</v>
@@ -15463,9 +15467,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A439" s="1">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>477</v>
@@ -15480,7 +15484,7 @@
         <v>181</v>
       </c>
       <c r="G439" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H439" s="1">
         <v>4137</v>
@@ -15494,7 +15498,7 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A440" s="1">
-        <v>4141</v>
+        <v>4140</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>477</v>
@@ -15509,7 +15513,7 @@
         <v>181</v>
       </c>
       <c r="G440" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H440" s="1">
         <v>4137</v>
@@ -15523,7 +15527,7 @@
     </row>
     <row r="441" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A441" s="1">
-        <v>4142</v>
+        <v>4141</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>477</v>
@@ -15538,21 +15542,21 @@
         <v>181</v>
       </c>
       <c r="G441" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H441" s="1">
-        <v>0</v>
+        <v>4137</v>
       </c>
       <c r="I441" s="1">
         <v>0</v>
       </c>
       <c r="J441" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A442" s="1">
-        <v>4143</v>
+        <v>4142</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>477</v>
@@ -15567,21 +15571,21 @@
         <v>181</v>
       </c>
       <c r="G442" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H442" s="1">
-        <v>4142</v>
+        <v>0</v>
       </c>
       <c r="I442" s="1">
         <v>0</v>
       </c>
       <c r="J442" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="443" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A443" s="1">
-        <v>4144</v>
+        <v>4143</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>477</v>
@@ -15596,7 +15600,7 @@
         <v>181</v>
       </c>
       <c r="G443" s="1" t="s">
-        <v>48</v>
+        <v>462</v>
       </c>
       <c r="H443" s="1">
         <v>4142</v>
@@ -15608,9 +15612,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A444" s="1">
-        <v>4145</v>
+        <v>4144</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>477</v>
@@ -15625,7 +15629,7 @@
         <v>181</v>
       </c>
       <c r="G444" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H444" s="1">
         <v>4142</v>
@@ -15639,7 +15643,7 @@
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A445" s="1">
-        <v>4146</v>
+        <v>4145</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>477</v>
@@ -15654,7 +15658,7 @@
         <v>181</v>
       </c>
       <c r="G445" s="1" t="s">
-        <v>463</v>
+        <v>60</v>
       </c>
       <c r="H445" s="1">
         <v>4142</v>
@@ -15668,7 +15672,7 @@
     </row>
     <row r="446" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A446" s="1">
-        <v>4147</v>
+        <v>4146</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>477</v>
@@ -15683,21 +15687,21 @@
         <v>181</v>
       </c>
       <c r="G446" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H446" s="1">
-        <v>0</v>
+        <v>4142</v>
       </c>
       <c r="I446" s="1">
         <v>0</v>
       </c>
       <c r="J446" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A447" s="1">
-        <v>4148</v>
+        <v>4147</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>477</v>
@@ -15712,21 +15716,21 @@
         <v>181</v>
       </c>
       <c r="G447" s="1" t="s">
-        <v>79</v>
+        <v>464</v>
       </c>
       <c r="H447" s="1">
-        <v>4147</v>
+        <v>0</v>
       </c>
       <c r="I447" s="1">
         <v>0</v>
       </c>
       <c r="J447" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A448" s="1">
-        <v>4149</v>
+        <v>4148</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>477</v>
@@ -15741,7 +15745,7 @@
         <v>181</v>
       </c>
       <c r="G448" s="1" t="s">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="H448" s="1">
         <v>4147</v>
@@ -15755,7 +15759,7 @@
     </row>
     <row r="449" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A449" s="1">
-        <v>4150</v>
+        <v>4149</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>477</v>
@@ -15770,7 +15774,7 @@
         <v>181</v>
       </c>
       <c r="G449" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H449" s="1">
         <v>4147</v>
@@ -15784,7 +15788,7 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A450" s="1">
-        <v>4151</v>
+        <v>4150</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>477</v>
@@ -15799,7 +15803,7 @@
         <v>181</v>
       </c>
       <c r="G450" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H450" s="1">
         <v>4147</v>
@@ -15813,7 +15817,7 @@
     </row>
     <row r="451" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A451" s="1">
-        <v>4152</v>
+        <v>4151</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>477</v>
@@ -15828,21 +15832,21 @@
         <v>181</v>
       </c>
       <c r="G451" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H451" s="1">
-        <v>0</v>
+        <v>4147</v>
       </c>
       <c r="I451" s="1">
         <v>0</v>
       </c>
       <c r="J451" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A452" s="1">
-        <v>4153</v>
+        <v>4152</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>477</v>
@@ -15857,21 +15861,21 @@
         <v>181</v>
       </c>
       <c r="G452" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H452" s="1">
-        <v>4152</v>
+        <v>0</v>
       </c>
       <c r="I452" s="1">
         <v>0</v>
       </c>
       <c r="J452" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A453" s="1">
-        <v>4154</v>
+        <v>4153</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>477</v>
@@ -15886,7 +15890,7 @@
         <v>181</v>
       </c>
       <c r="G453" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H453" s="1">
         <v>4152</v>
@@ -15900,7 +15904,7 @@
     </row>
     <row r="454" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A454" s="1">
-        <v>4155</v>
+        <v>4154</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>477</v>
@@ -15915,7 +15919,7 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H454" s="1">
         <v>4152</v>
@@ -15929,7 +15933,7 @@
     </row>
     <row r="455" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A455" s="1">
-        <v>4156</v>
+        <v>4155</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>477</v>
@@ -15944,7 +15948,7 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H455" s="1">
         <v>4152</v>
@@ -15958,7 +15962,7 @@
     </row>
     <row r="456" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A456" s="1">
-        <v>4157</v>
+        <v>4156</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>477</v>
@@ -15973,21 +15977,21 @@
         <v>181</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H456" s="1">
-        <v>0</v>
+        <v>4152</v>
       </c>
       <c r="I456" s="1">
         <v>0</v>
       </c>
       <c r="J456" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="457" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A457" s="1">
-        <v>4158</v>
+        <v>4157</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>477</v>
@@ -16002,21 +16006,21 @@
         <v>181</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>52</v>
+        <v>473</v>
       </c>
       <c r="H457" s="1">
-        <v>4157</v>
+        <v>0</v>
       </c>
       <c r="I457" s="1">
         <v>0</v>
       </c>
       <c r="J457" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A458" s="1">
-        <v>4159</v>
+        <v>4158</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>477</v>
@@ -16031,7 +16035,7 @@
         <v>181</v>
       </c>
       <c r="G458" s="1" t="s">
-        <v>474</v>
+        <v>52</v>
       </c>
       <c r="H458" s="1">
         <v>4157</v>
@@ -16045,7 +16049,7 @@
     </row>
     <row r="459" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A459" s="1">
-        <v>4160</v>
+        <v>4159</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>477</v>
@@ -16060,7 +16064,7 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H459" s="1">
         <v>4157</v>
@@ -16074,7 +16078,7 @@
     </row>
     <row r="460" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A460" s="1">
-        <v>4161</v>
+        <v>4160</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>477</v>
@@ -16089,7 +16093,7 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H460" s="1">
         <v>4157</v>
@@ -16103,13 +16107,13 @@
     </row>
     <row r="461" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A461" s="1">
-        <v>5001</v>
+        <v>4161</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>284</v>
+        <v>477</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="E461" s="1">
         <v>0</v>
@@ -16118,10 +16122,10 @@
         <v>181</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>291</v>
+        <v>476</v>
       </c>
       <c r="H461" s="1">
-        <v>0</v>
+        <v>4157</v>
       </c>
       <c r="I461" s="1">
         <v>0</v>
@@ -16132,7 +16136,7 @@
     </row>
     <row r="462" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A462" s="1">
-        <v>6000</v>
+        <v>5001</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>284</v>
@@ -16147,7 +16151,7 @@
         <v>181</v>
       </c>
       <c r="G462" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H462" s="1">
         <v>0</v>
@@ -16161,7 +16165,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>6001</v>
+        <v>6000</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>284</v>
@@ -16176,7 +16180,7 @@
         <v>181</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H463" s="1">
         <v>0</v>
@@ -16190,7 +16194,7 @@
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>6002</v>
+        <v>6001</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>284</v>
@@ -16205,7 +16209,7 @@
         <v>181</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H464" s="1">
         <v>0</v>
@@ -16219,7 +16223,7 @@
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
-        <v>6003</v>
+        <v>6002</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>284</v>
@@ -16234,7 +16238,7 @@
         <v>181</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H465" s="1">
         <v>0</v>
@@ -16248,7 +16252,7 @@
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
-        <v>6004</v>
+        <v>6003</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>284</v>
@@ -16263,7 +16267,7 @@
         <v>181</v>
       </c>
       <c r="G466" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H466" s="1">
         <v>0</v>
@@ -16277,7 +16281,7 @@
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A467" s="1">
-        <v>6005</v>
+        <v>6004</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>284</v>
@@ -16292,7 +16296,7 @@
         <v>181</v>
       </c>
       <c r="G467" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H467" s="1">
         <v>0</v>
@@ -16306,7 +16310,7 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>284</v>
@@ -16321,7 +16325,7 @@
         <v>181</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H468" s="1">
         <v>0</v>
@@ -16335,7 +16339,7 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
-        <v>6100</v>
+        <v>6006</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>284</v>
@@ -16350,7 +16354,7 @@
         <v>181</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H469" s="1">
         <v>0</v>
@@ -16364,10 +16368,10 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A470" s="1">
-        <v>8100</v>
+        <v>6100</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D470" s="1" t="s">
         <v>183</v>
@@ -16379,7 +16383,7 @@
         <v>181</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>650</v>
+        <v>299</v>
       </c>
       <c r="H470" s="1">
         <v>0</v>
@@ -16388,15 +16392,15 @@
         <v>0</v>
       </c>
       <c r="J470" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A471" s="1">
-        <v>8101</v>
+        <v>8100</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D471" s="1" t="s">
         <v>183</v>
@@ -16408,7 +16412,7 @@
         <v>181</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H471" s="1">
         <v>0</v>
@@ -16422,7 +16426,7 @@
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
-        <v>8102</v>
+        <v>8101</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>284</v>
@@ -16437,7 +16441,7 @@
         <v>181</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="H472" s="1">
         <v>0</v>
@@ -16451,7 +16455,7 @@
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
-        <v>8103</v>
+        <v>8102</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>284</v>
@@ -16466,7 +16470,7 @@
         <v>181</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H473" s="1">
         <v>0</v>
@@ -16480,7 +16484,7 @@
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>284</v>
@@ -16495,7 +16499,7 @@
         <v>181</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H474" s="1">
         <v>0</v>
@@ -16509,7 +16513,7 @@
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
-        <v>8105</v>
+        <v>8104</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>284</v>
@@ -16524,7 +16528,7 @@
         <v>181</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H475" s="1">
         <v>0</v>
@@ -16538,7 +16542,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
-        <v>8106</v>
+        <v>8105</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>284</v>
@@ -16553,7 +16557,7 @@
         <v>181</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H476" s="1">
         <v>0</v>
@@ -16567,7 +16571,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
-        <v>8107</v>
+        <v>8106</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>284</v>
@@ -16582,7 +16586,7 @@
         <v>181</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="H477" s="1">
         <v>0</v>
@@ -16596,7 +16600,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>284</v>
@@ -16611,7 +16615,7 @@
         <v>181</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="H478" s="1">
         <v>0</v>
@@ -16625,7 +16629,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
-        <v>8109</v>
+        <v>8108</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>284</v>
@@ -16640,7 +16644,7 @@
         <v>181</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H479" s="1">
         <v>0</v>
@@ -16654,7 +16658,7 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
-        <v>8110</v>
+        <v>8109</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>284</v>
@@ -16669,7 +16673,7 @@
         <v>181</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="H480" s="1">
         <v>0</v>
@@ -16683,7 +16687,7 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
-        <v>8111</v>
+        <v>8110</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>284</v>
@@ -16698,7 +16702,7 @@
         <v>181</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H481" s="1">
         <v>0</v>
@@ -16712,7 +16716,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
-        <v>8112</v>
+        <v>8111</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>284</v>
@@ -16727,7 +16731,7 @@
         <v>181</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H482" s="1">
         <v>0</v>
@@ -16741,7 +16745,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
-        <v>8113</v>
+        <v>8112</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>284</v>
@@ -16756,7 +16760,7 @@
         <v>181</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="H483" s="1">
         <v>0</v>
@@ -16770,7 +16774,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
-        <v>8114</v>
+        <v>8113</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>284</v>
@@ -16785,7 +16789,7 @@
         <v>181</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="H484" s="1">
         <v>0</v>
@@ -16799,7 +16803,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
-        <v>8115</v>
+        <v>8114</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>284</v>
@@ -16814,7 +16818,7 @@
         <v>181</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="H485" s="1">
         <v>0</v>
@@ -16828,7 +16832,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
-        <v>8116</v>
+        <v>8115</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>284</v>
@@ -16843,7 +16847,7 @@
         <v>181</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="H486" s="1">
         <v>0</v>
@@ -16855,8 +16859,37 @@
         <v>1</v>
       </c>
     </row>
+    <row r="487" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A487" s="1">
+        <v>8116</v>
+      </c>
+      <c r="B487" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D487" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E487" s="1">
+        <v>0</v>
+      </c>
+      <c r="F487" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G487" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="H487" s="1">
+        <v>0</v>
+      </c>
+      <c r="I487" s="1">
+        <v>0</v>
+      </c>
+      <c r="J487" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J470"/>
+  <autoFilter ref="A3:J471"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$471</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$475</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1887" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="671">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -1562,9 +1562,6 @@
     <t>纺织可是化腐朽为神奇的技术。</t>
   </si>
   <si>
-    <t>如果你想学习纺织技术的话，我可以教你。</t>
-  </si>
-  <si>
     <t>我有时也会为缺少传承而烦恼呢。</t>
   </si>
   <si>
@@ -2216,6 +2213,26 @@
   </si>
   <si>
     <t>我需要先装备斧头</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果你想学习纺织技术的话，我可以教你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的队伍已经满员了，还是下次再说吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的身体还没有恢复，改天吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我先回家修养身体了，你自己保重。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>造物主还没来得及创造这种感情，请耐心等待吧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2620,7 +2637,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J487"/>
+  <dimension ref="A2:J491"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -7288,7 +7305,7 @@
         <v>255</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H160" s="1">
         <v>1416</v>
@@ -7320,7 +7337,7 @@
         <v>189</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H161" s="1">
         <v>1417</v>
@@ -7352,7 +7369,7 @@
         <v>189</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H162" s="1">
         <v>1418</v>
@@ -7384,7 +7401,7 @@
         <v>255</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
@@ -7416,7 +7433,7 @@
         <v>189</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H164" s="1">
         <v>0</v>
@@ -7448,7 +7465,7 @@
         <v>189</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H165" s="1">
         <v>0</v>
@@ -7480,7 +7497,7 @@
         <v>255</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H166" s="1">
         <v>1422</v>
@@ -7497,7 +7514,7 @@
         <v>1422</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>8</v>
@@ -7544,7 +7561,7 @@
         <v>189</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
@@ -7567,7 +7584,7 @@
         <v>10</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -7576,7 +7593,7 @@
         <v>181</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
@@ -7608,7 +7625,7 @@
         <v>189</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H170" s="1">
         <v>1426</v>
@@ -7631,7 +7648,7 @@
         <v>10</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -7640,7 +7657,7 @@
         <v>189</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
@@ -7657,7 +7674,7 @@
         <v>1427</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>8</v>
@@ -7672,7 +7689,7 @@
         <v>189</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
@@ -7704,7 +7721,7 @@
         <v>181</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H173" s="1">
         <v>1429</v>
@@ -7736,7 +7753,7 @@
         <v>181</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H174" s="1">
         <v>0</v>
@@ -7768,7 +7785,7 @@
         <v>181</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
@@ -7800,7 +7817,7 @@
         <v>181</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
@@ -7817,7 +7834,7 @@
         <v>1432</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>8</v>
@@ -7849,7 +7866,7 @@
         <v>1433</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>9</v>
@@ -7864,7 +7881,7 @@
         <v>255</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
@@ -7928,7 +7945,7 @@
         <v>255</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
@@ -7960,7 +7977,7 @@
         <v>255</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -7992,7 +8009,7 @@
         <v>255</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
@@ -8009,7 +8026,7 @@
         <v>1439</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>9</v>
@@ -8024,7 +8041,7 @@
         <v>255</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -11337,7 +11354,7 @@
         <v>181</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
@@ -11366,7 +11383,7 @@
         <v>181</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
@@ -11395,7 +11412,7 @@
         <v>181</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H298" s="1">
         <v>0</v>
@@ -11424,7 +11441,7 @@
         <v>181</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
@@ -11441,7 +11458,7 @@
         <v>4000</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>274</v>
@@ -11470,7 +11487,7 @@
         <v>4001</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>274</v>
@@ -11499,7 +11516,7 @@
         <v>4002</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D302" s="1" t="s">
         <v>274</v>
@@ -11528,7 +11545,7 @@
         <v>4003</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D303" s="1" t="s">
         <v>274</v>
@@ -11557,7 +11574,7 @@
         <v>4004</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>274</v>
@@ -11586,7 +11603,7 @@
         <v>4005</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>274</v>
@@ -11615,7 +11632,7 @@
         <v>4006</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>274</v>
@@ -11644,7 +11661,7 @@
         <v>4007</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D307" s="1" t="s">
         <v>274</v>
@@ -11673,7 +11690,7 @@
         <v>4008</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>274</v>
@@ -11702,7 +11719,7 @@
         <v>4009</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>274</v>
@@ -11731,7 +11748,7 @@
         <v>4010</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>274</v>
@@ -11760,7 +11777,7 @@
         <v>4011</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>274</v>
@@ -11789,7 +11806,7 @@
         <v>4012</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>274</v>
@@ -11818,7 +11835,7 @@
         <v>4013</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>274</v>
@@ -11847,7 +11864,7 @@
         <v>4014</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>274</v>
@@ -11876,7 +11893,7 @@
         <v>4015</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>274</v>
@@ -11905,7 +11922,7 @@
         <v>4016</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>274</v>
@@ -11934,7 +11951,7 @@
         <v>4017</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>274</v>
@@ -11963,7 +11980,7 @@
         <v>4018</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>274</v>
@@ -11992,7 +12009,7 @@
         <v>4019</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>274</v>
@@ -12021,7 +12038,7 @@
         <v>4020</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>274</v>
@@ -12050,7 +12067,7 @@
         <v>4021</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>274</v>
@@ -12079,7 +12096,7 @@
         <v>4022</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>274</v>
@@ -12108,7 +12125,7 @@
         <v>4023</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>274</v>
@@ -12137,7 +12154,7 @@
         <v>4024</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>274</v>
@@ -12166,7 +12183,7 @@
         <v>4025</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>274</v>
@@ -12195,7 +12212,7 @@
         <v>4026</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>274</v>
@@ -12224,7 +12241,7 @@
         <v>4027</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>274</v>
@@ -12253,7 +12270,7 @@
         <v>4028</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>274</v>
@@ -12282,7 +12299,7 @@
         <v>4029</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>274</v>
@@ -12311,7 +12328,7 @@
         <v>4030</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>274</v>
@@ -12340,7 +12357,7 @@
         <v>4031</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>274</v>
@@ -12369,7 +12386,7 @@
         <v>4032</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D332" s="1" t="s">
         <v>274</v>
@@ -12398,7 +12415,7 @@
         <v>4033</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>274</v>
@@ -12427,7 +12444,7 @@
         <v>4034</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D334" s="1" t="s">
         <v>274</v>
@@ -12456,7 +12473,7 @@
         <v>4035</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>274</v>
@@ -12485,7 +12502,7 @@
         <v>4036</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>274</v>
@@ -12514,7 +12531,7 @@
         <v>4037</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D337" s="1" t="s">
         <v>274</v>
@@ -12543,7 +12560,7 @@
         <v>4038</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>274</v>
@@ -12572,7 +12589,7 @@
         <v>4039</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>274</v>
@@ -12601,7 +12618,7 @@
         <v>4040</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>274</v>
@@ -12630,7 +12647,7 @@
         <v>4041</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D341" s="1" t="s">
         <v>274</v>
@@ -12659,7 +12676,7 @@
         <v>4042</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>274</v>
@@ -12688,7 +12705,7 @@
         <v>4043</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>274</v>
@@ -12717,7 +12734,7 @@
         <v>4044</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>274</v>
@@ -12746,7 +12763,7 @@
         <v>4045</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>274</v>
@@ -12775,7 +12792,7 @@
         <v>4046</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>274</v>
@@ -12804,7 +12821,7 @@
         <v>4047</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>274</v>
@@ -12833,7 +12850,7 @@
         <v>4048</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>274</v>
@@ -12862,7 +12879,7 @@
         <v>4049</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>274</v>
@@ -12891,7 +12908,7 @@
         <v>4050</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>274</v>
@@ -12920,7 +12937,7 @@
         <v>4051</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>274</v>
@@ -12949,7 +12966,7 @@
         <v>4052</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>274</v>
@@ -12978,7 +12995,7 @@
         <v>4053</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>274</v>
@@ -13007,7 +13024,7 @@
         <v>4054</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>274</v>
@@ -13036,7 +13053,7 @@
         <v>4055</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D355" s="1" t="s">
         <v>274</v>
@@ -13065,7 +13082,7 @@
         <v>4056</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>274</v>
@@ -13094,7 +13111,7 @@
         <v>4057</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>274</v>
@@ -13123,7 +13140,7 @@
         <v>4058</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>274</v>
@@ -13152,7 +13169,7 @@
         <v>4059</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>274</v>
@@ -13181,7 +13198,7 @@
         <v>4060</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>274</v>
@@ -13210,7 +13227,7 @@
         <v>4061</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>274</v>
@@ -13239,7 +13256,7 @@
         <v>4062</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>274</v>
@@ -13268,7 +13285,7 @@
         <v>4063</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>274</v>
@@ -13297,7 +13314,7 @@
         <v>4064</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D364" s="1" t="s">
         <v>274</v>
@@ -13326,7 +13343,7 @@
         <v>4065</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D365" s="1" t="s">
         <v>274</v>
@@ -13355,7 +13372,7 @@
         <v>4066</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D366" s="1" t="s">
         <v>274</v>
@@ -13384,7 +13401,7 @@
         <v>4067</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>274</v>
@@ -13413,7 +13430,7 @@
         <v>4068</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D368" s="1" t="s">
         <v>274</v>
@@ -13442,7 +13459,7 @@
         <v>4069</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>274</v>
@@ -13471,7 +13488,7 @@
         <v>4070</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>274</v>
@@ -13500,7 +13517,7 @@
         <v>4071</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>274</v>
@@ -13529,7 +13546,7 @@
         <v>4072</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>274</v>
@@ -13558,7 +13575,7 @@
         <v>4073</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>274</v>
@@ -13587,7 +13604,7 @@
         <v>4074</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>274</v>
@@ -13616,7 +13633,7 @@
         <v>4075</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>274</v>
@@ -13645,7 +13662,7 @@
         <v>4076</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>274</v>
@@ -13674,7 +13691,7 @@
         <v>4077</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D377" s="1" t="s">
         <v>274</v>
@@ -13703,7 +13720,7 @@
         <v>4078</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D378" s="1" t="s">
         <v>274</v>
@@ -13732,7 +13749,7 @@
         <v>4079</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D379" s="1" t="s">
         <v>274</v>
@@ -13761,7 +13778,7 @@
         <v>4080</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D380" s="1" t="s">
         <v>274</v>
@@ -13790,7 +13807,7 @@
         <v>4081</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D381" s="1" t="s">
         <v>274</v>
@@ -13819,7 +13836,7 @@
         <v>4082</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D382" s="1" t="s">
         <v>274</v>
@@ -13848,7 +13865,7 @@
         <v>4083</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D383" s="1" t="s">
         <v>274</v>
@@ -13877,7 +13894,7 @@
         <v>4084</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D384" s="1" t="s">
         <v>274</v>
@@ -13906,7 +13923,7 @@
         <v>4085</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D385" s="1" t="s">
         <v>274</v>
@@ -13935,7 +13952,7 @@
         <v>4086</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D386" s="1" t="s">
         <v>274</v>
@@ -13964,7 +13981,7 @@
         <v>4087</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D387" s="1" t="s">
         <v>274</v>
@@ -13993,7 +14010,7 @@
         <v>4088</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D388" s="1" t="s">
         <v>274</v>
@@ -14022,7 +14039,7 @@
         <v>4089</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D389" s="1" t="s">
         <v>274</v>
@@ -14051,7 +14068,7 @@
         <v>4090</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D390" s="1" t="s">
         <v>274</v>
@@ -14080,7 +14097,7 @@
         <v>4091</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D391" s="1" t="s">
         <v>274</v>
@@ -14109,7 +14126,7 @@
         <v>4092</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D392" s="1" t="s">
         <v>274</v>
@@ -14138,7 +14155,7 @@
         <v>4093</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D393" s="1" t="s">
         <v>274</v>
@@ -14167,7 +14184,7 @@
         <v>4094</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D394" s="1" t="s">
         <v>274</v>
@@ -14196,7 +14213,7 @@
         <v>4095</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D395" s="1" t="s">
         <v>274</v>
@@ -14225,7 +14242,7 @@
         <v>4096</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D396" s="1" t="s">
         <v>274</v>
@@ -14254,7 +14271,7 @@
         <v>4097</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D397" s="1" t="s">
         <v>274</v>
@@ -14283,7 +14300,7 @@
         <v>4098</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D398" s="1" t="s">
         <v>274</v>
@@ -14312,7 +14329,7 @@
         <v>4099</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D399" s="1" t="s">
         <v>274</v>
@@ -14341,7 +14358,7 @@
         <v>4100</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D400" s="1" t="s">
         <v>274</v>
@@ -14370,7 +14387,7 @@
         <v>4101</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D401" s="1" t="s">
         <v>274</v>
@@ -14399,7 +14416,7 @@
         <v>4102</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D402" s="1" t="s">
         <v>274</v>
@@ -14428,7 +14445,7 @@
         <v>4103</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D403" s="1" t="s">
         <v>274</v>
@@ -14457,7 +14474,7 @@
         <v>4104</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D404" s="1" t="s">
         <v>274</v>
@@ -14486,7 +14503,7 @@
         <v>4105</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D405" s="1" t="s">
         <v>274</v>
@@ -14515,7 +14532,7 @@
         <v>4106</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D406" s="1" t="s">
         <v>274</v>
@@ -14544,7 +14561,7 @@
         <v>4107</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D407" s="1" t="s">
         <v>274</v>
@@ -14573,7 +14590,7 @@
         <v>4108</v>
       </c>
       <c r="B408" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D408" s="1" t="s">
         <v>274</v>
@@ -14602,7 +14619,7 @@
         <v>4109</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D409" s="1" t="s">
         <v>274</v>
@@ -14631,7 +14648,7 @@
         <v>4110</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D410" s="1" t="s">
         <v>274</v>
@@ -14660,7 +14677,7 @@
         <v>4111</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D411" s="1" t="s">
         <v>274</v>
@@ -14689,7 +14706,7 @@
         <v>4112</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D412" s="1" t="s">
         <v>274</v>
@@ -14718,7 +14735,7 @@
         <v>4113</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D413" s="1" t="s">
         <v>274</v>
@@ -14747,7 +14764,7 @@
         <v>4114</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D414" s="1" t="s">
         <v>274</v>
@@ -14776,7 +14793,7 @@
         <v>4115</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D415" s="1" t="s">
         <v>274</v>
@@ -14805,7 +14822,7 @@
         <v>4116</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D416" s="1" t="s">
         <v>274</v>
@@ -14834,7 +14851,7 @@
         <v>4117</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D417" s="1" t="s">
         <v>274</v>
@@ -14863,7 +14880,7 @@
         <v>4118</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D418" s="1" t="s">
         <v>274</v>
@@ -14892,7 +14909,7 @@
         <v>4119</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D419" s="1" t="s">
         <v>274</v>
@@ -14921,7 +14938,7 @@
         <v>4120</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D420" s="1" t="s">
         <v>274</v>
@@ -14950,7 +14967,7 @@
         <v>4121</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D421" s="1" t="s">
         <v>274</v>
@@ -14979,7 +14996,7 @@
         <v>4122</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D422" s="1" t="s">
         <v>274</v>
@@ -15008,7 +15025,7 @@
         <v>4123</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D423" s="1" t="s">
         <v>274</v>
@@ -15037,7 +15054,7 @@
         <v>4124</v>
       </c>
       <c r="B424" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D424" s="1" t="s">
         <v>274</v>
@@ -15066,7 +15083,7 @@
         <v>4125</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D425" s="1" t="s">
         <v>274</v>
@@ -15095,7 +15112,7 @@
         <v>4126</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D426" s="1" t="s">
         <v>274</v>
@@ -15124,7 +15141,7 @@
         <v>4127</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D427" s="1" t="s">
         <v>274</v>
@@ -15153,7 +15170,7 @@
         <v>4128</v>
       </c>
       <c r="B428" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D428" s="1" t="s">
         <v>274</v>
@@ -15182,7 +15199,7 @@
         <v>4129</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D429" s="1" t="s">
         <v>274</v>
@@ -15211,7 +15228,7 @@
         <v>4130</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D430" s="1" t="s">
         <v>274</v>
@@ -15240,7 +15257,7 @@
         <v>4131</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D431" s="1" t="s">
         <v>274</v>
@@ -15269,7 +15286,7 @@
         <v>4132</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D432" s="1" t="s">
         <v>274</v>
@@ -15298,7 +15315,7 @@
         <v>4133</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D433" s="1" t="s">
         <v>274</v>
@@ -15327,7 +15344,7 @@
         <v>4134</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D434" s="1" t="s">
         <v>274</v>
@@ -15356,7 +15373,7 @@
         <v>4135</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D435" s="1" t="s">
         <v>274</v>
@@ -15385,7 +15402,7 @@
         <v>4136</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D436" s="1" t="s">
         <v>274</v>
@@ -15414,7 +15431,7 @@
         <v>4137</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D437" s="1" t="s">
         <v>274</v>
@@ -15443,7 +15460,7 @@
         <v>4138</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D438" s="1" t="s">
         <v>274</v>
@@ -15472,7 +15489,7 @@
         <v>4139</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D439" s="1" t="s">
         <v>274</v>
@@ -15501,7 +15518,7 @@
         <v>4140</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D440" s="1" t="s">
         <v>274</v>
@@ -15530,7 +15547,7 @@
         <v>4141</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D441" s="1" t="s">
         <v>274</v>
@@ -15559,7 +15576,7 @@
         <v>4142</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D442" s="1" t="s">
         <v>274</v>
@@ -15588,7 +15605,7 @@
         <v>4143</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D443" s="1" t="s">
         <v>274</v>
@@ -15617,7 +15634,7 @@
         <v>4144</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D444" s="1" t="s">
         <v>274</v>
@@ -15646,7 +15663,7 @@
         <v>4145</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D445" s="1" t="s">
         <v>274</v>
@@ -15675,7 +15692,7 @@
         <v>4146</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D446" s="1" t="s">
         <v>274</v>
@@ -15704,7 +15721,7 @@
         <v>4147</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D447" s="1" t="s">
         <v>274</v>
@@ -15733,7 +15750,7 @@
         <v>4148</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D448" s="1" t="s">
         <v>274</v>
@@ -15762,7 +15779,7 @@
         <v>4149</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D449" s="1" t="s">
         <v>274</v>
@@ -15791,7 +15808,7 @@
         <v>4150</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>274</v>
@@ -15820,7 +15837,7 @@
         <v>4151</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>274</v>
@@ -15849,7 +15866,7 @@
         <v>4152</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D452" s="1" t="s">
         <v>274</v>
@@ -15878,7 +15895,7 @@
         <v>4153</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D453" s="1" t="s">
         <v>274</v>
@@ -15907,7 +15924,7 @@
         <v>4154</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D454" s="1" t="s">
         <v>274</v>
@@ -15919,7 +15936,7 @@
         <v>181</v>
       </c>
       <c r="G454" s="1" t="s">
-        <v>470</v>
+        <v>666</v>
       </c>
       <c r="H454" s="1">
         <v>4152</v>
@@ -15936,7 +15953,7 @@
         <v>4155</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D455" s="1" t="s">
         <v>274</v>
@@ -15948,7 +15965,7 @@
         <v>181</v>
       </c>
       <c r="G455" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H455" s="1">
         <v>4152</v>
@@ -15965,7 +15982,7 @@
         <v>4156</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D456" s="1" t="s">
         <v>274</v>
@@ -15977,7 +15994,7 @@
         <v>181</v>
       </c>
       <c r="G456" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H456" s="1">
         <v>4152</v>
@@ -15994,7 +16011,7 @@
         <v>4157</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D457" s="1" t="s">
         <v>274</v>
@@ -16006,7 +16023,7 @@
         <v>181</v>
       </c>
       <c r="G457" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H457" s="1">
         <v>0</v>
@@ -16023,7 +16040,7 @@
         <v>4158</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D458" s="1" t="s">
         <v>274</v>
@@ -16052,7 +16069,7 @@
         <v>4159</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D459" s="1" t="s">
         <v>274</v>
@@ -16064,7 +16081,7 @@
         <v>181</v>
       </c>
       <c r="G459" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H459" s="1">
         <v>4157</v>
@@ -16081,7 +16098,7 @@
         <v>4160</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D460" s="1" t="s">
         <v>274</v>
@@ -16093,7 +16110,7 @@
         <v>181</v>
       </c>
       <c r="G460" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H460" s="1">
         <v>4157</v>
@@ -16110,7 +16127,7 @@
         <v>4161</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D461" s="1" t="s">
         <v>274</v>
@@ -16122,7 +16139,7 @@
         <v>181</v>
       </c>
       <c r="G461" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H461" s="1">
         <v>4157</v>
@@ -16165,7 +16182,7 @@
     </row>
     <row r="463" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A463" s="1">
-        <v>6000</v>
+        <v>5002</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>284</v>
@@ -16180,7 +16197,7 @@
         <v>181</v>
       </c>
       <c r="G463" s="1" t="s">
-        <v>292</v>
+        <v>667</v>
       </c>
       <c r="H463" s="1">
         <v>0</v>
@@ -16189,12 +16206,12 @@
         <v>0</v>
       </c>
       <c r="J463" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="464" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A464" s="1">
-        <v>6001</v>
+        <v>5003</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>284</v>
@@ -16209,7 +16226,7 @@
         <v>181</v>
       </c>
       <c r="G464" s="1" t="s">
-        <v>293</v>
+        <v>668</v>
       </c>
       <c r="H464" s="1">
         <v>0</v>
@@ -16218,12 +16235,12 @@
         <v>0</v>
       </c>
       <c r="J464" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A465" s="1">
-        <v>6002</v>
+        <v>5004</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>284</v>
@@ -16238,7 +16255,7 @@
         <v>181</v>
       </c>
       <c r="G465" s="1" t="s">
-        <v>294</v>
+        <v>669</v>
       </c>
       <c r="H465" s="1">
         <v>0</v>
@@ -16247,12 +16264,12 @@
         <v>0</v>
       </c>
       <c r="J465" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="466" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
-        <v>6003</v>
+        <v>5005</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>284</v>
@@ -16267,7 +16284,7 @@
         <v>181</v>
       </c>
       <c r="G466" s="1" t="s">
-        <v>295</v>
+        <v>670</v>
       </c>
       <c r="H466" s="1">
         <v>0</v>
@@ -16276,12 +16293,12 @@
         <v>0</v>
       </c>
       <c r="J466" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A467" s="1">
-        <v>6004</v>
+        <v>6000</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>284</v>
@@ -16296,7 +16313,7 @@
         <v>181</v>
       </c>
       <c r="G467" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="H467" s="1">
         <v>0</v>
@@ -16310,7 +16327,7 @@
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
-        <v>6005</v>
+        <v>6001</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>284</v>
@@ -16325,7 +16342,7 @@
         <v>181</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="H468" s="1">
         <v>0</v>
@@ -16339,7 +16356,7 @@
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
-        <v>6006</v>
+        <v>6002</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>284</v>
@@ -16354,7 +16371,7 @@
         <v>181</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="H469" s="1">
         <v>0</v>
@@ -16368,7 +16385,7 @@
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A470" s="1">
-        <v>6100</v>
+        <v>6003</v>
       </c>
       <c r="B470" s="3" t="s">
         <v>284</v>
@@ -16383,7 +16400,7 @@
         <v>181</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="H470" s="1">
         <v>0</v>
@@ -16397,10 +16414,10 @@
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A471" s="1">
-        <v>8100</v>
+        <v>6004</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D471" s="1" t="s">
         <v>183</v>
@@ -16412,7 +16429,7 @@
         <v>181</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>650</v>
+        <v>296</v>
       </c>
       <c r="H471" s="1">
         <v>0</v>
@@ -16421,12 +16438,12 @@
         <v>0</v>
       </c>
       <c r="J471" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
-        <v>8101</v>
+        <v>6005</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>284</v>
@@ -16441,7 +16458,7 @@
         <v>181</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>649</v>
+        <v>297</v>
       </c>
       <c r="H472" s="1">
         <v>0</v>
@@ -16450,12 +16467,12 @@
         <v>0</v>
       </c>
       <c r="J472" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
-        <v>8102</v>
+        <v>6006</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>284</v>
@@ -16470,7 +16487,7 @@
         <v>181</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>652</v>
+        <v>298</v>
       </c>
       <c r="H473" s="1">
         <v>0</v>
@@ -16479,12 +16496,12 @@
         <v>0</v>
       </c>
       <c r="J473" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
-        <v>8103</v>
+        <v>6100</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>284</v>
@@ -16499,7 +16516,7 @@
         <v>181</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>651</v>
+        <v>299</v>
       </c>
       <c r="H474" s="1">
         <v>0</v>
@@ -16508,15 +16525,15 @@
         <v>0</v>
       </c>
       <c r="J474" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
-        <v>8104</v>
+        <v>8100</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D475" s="1" t="s">
         <v>183</v>
@@ -16528,7 +16545,7 @@
         <v>181</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="H475" s="1">
         <v>0</v>
@@ -16542,7 +16559,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
-        <v>8105</v>
+        <v>8101</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>284</v>
@@ -16557,7 +16574,7 @@
         <v>181</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="H476" s="1">
         <v>0</v>
@@ -16571,7 +16588,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
-        <v>8106</v>
+        <v>8102</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>284</v>
@@ -16586,7 +16603,7 @@
         <v>181</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="H477" s="1">
         <v>0</v>
@@ -16600,7 +16617,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
-        <v>8107</v>
+        <v>8103</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>284</v>
@@ -16615,7 +16632,7 @@
         <v>181</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="H478" s="1">
         <v>0</v>
@@ -16629,7 +16646,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
-        <v>8108</v>
+        <v>8104</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>284</v>
@@ -16644,7 +16661,7 @@
         <v>181</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="H479" s="1">
         <v>0</v>
@@ -16658,7 +16675,7 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
-        <v>8109</v>
+        <v>8105</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>284</v>
@@ -16673,7 +16690,7 @@
         <v>181</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H480" s="1">
         <v>0</v>
@@ -16687,7 +16704,7 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
-        <v>8110</v>
+        <v>8106</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>284</v>
@@ -16702,7 +16719,7 @@
         <v>181</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="H481" s="1">
         <v>0</v>
@@ -16716,7 +16733,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
-        <v>8111</v>
+        <v>8107</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>284</v>
@@ -16731,7 +16748,7 @@
         <v>181</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H482" s="1">
         <v>0</v>
@@ -16745,7 +16762,7 @@
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
-        <v>8112</v>
+        <v>8108</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>284</v>
@@ -16760,7 +16777,7 @@
         <v>181</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="H483" s="1">
         <v>0</v>
@@ -16774,7 +16791,7 @@
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
-        <v>8113</v>
+        <v>8109</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>284</v>
@@ -16789,7 +16806,7 @@
         <v>181</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="H484" s="1">
         <v>0</v>
@@ -16803,7 +16820,7 @@
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
-        <v>8114</v>
+        <v>8110</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>284</v>
@@ -16818,7 +16835,7 @@
         <v>181</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="H485" s="1">
         <v>0</v>
@@ -16832,7 +16849,7 @@
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
-        <v>8115</v>
+        <v>8111</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>284</v>
@@ -16847,7 +16864,7 @@
         <v>181</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="H486" s="1">
         <v>0</v>
@@ -16861,7 +16878,7 @@
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A487" s="1">
-        <v>8116</v>
+        <v>8112</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>284</v>
@@ -16876,7 +16893,7 @@
         <v>181</v>
       </c>
       <c r="G487" s="1" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="H487" s="1">
         <v>0</v>
@@ -16888,8 +16905,124 @@
         <v>1</v>
       </c>
     </row>
+    <row r="488" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A488" s="1">
+        <v>8113</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D488" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E488" s="1">
+        <v>0</v>
+      </c>
+      <c r="F488" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G488" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="H488" s="1">
+        <v>0</v>
+      </c>
+      <c r="I488" s="1">
+        <v>0</v>
+      </c>
+      <c r="J488" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A489" s="1">
+        <v>8114</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D489" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E489" s="1">
+        <v>0</v>
+      </c>
+      <c r="F489" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G489" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="H489" s="1">
+        <v>0</v>
+      </c>
+      <c r="I489" s="1">
+        <v>0</v>
+      </c>
+      <c r="J489" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A490" s="1">
+        <v>8115</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D490" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E490" s="1">
+        <v>0</v>
+      </c>
+      <c r="F490" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G490" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="H490" s="1">
+        <v>0</v>
+      </c>
+      <c r="I490" s="1">
+        <v>0</v>
+      </c>
+      <c r="J490" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A491" s="1">
+        <v>8116</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D491" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E491" s="1">
+        <v>0</v>
+      </c>
+      <c r="F491" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G491" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="H491" s="1">
+        <v>0</v>
+      </c>
+      <c r="I491" s="1">
+        <v>0</v>
+      </c>
+      <c r="J491" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J471"/>
+  <autoFilter ref="A3:J475"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16909,7 +17042,7 @@
       <c r="B1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="8" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1" s="6">
         <v>44002</v>
@@ -16925,7 +17058,7 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -16935,7 +17068,7 @@
       <c r="B3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H3" s="1">
         <v>44004</v>
@@ -16951,7 +17084,7 @@
       </c>
       <c r="F4" s="3"/>
       <c r="G4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -16961,7 +17094,7 @@
       <c r="B5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H5" s="1">
         <v>44006</v>
@@ -16977,7 +17110,7 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H6" s="1">
         <v>44007</v>
@@ -16990,7 +17123,7 @@
       <c r="B7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17003,7 +17136,7 @@
       </c>
       <c r="F8" s="3"/>
       <c r="G8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H8" s="1">
         <v>44009</v>
@@ -17016,7 +17149,7 @@
       <c r="B9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H9" s="1">
         <v>44010</v>
@@ -17032,7 +17165,7 @@
       </c>
       <c r="F10" s="3"/>
       <c r="G10" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H10" s="1">
         <v>44011</v>
@@ -17045,7 +17178,7 @@
       <c r="B11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17055,7 +17188,7 @@
       <c r="B12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H12" s="1">
         <v>44013</v>
@@ -17071,7 +17204,7 @@
       </c>
       <c r="F13" s="3"/>
       <c r="G13" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H13" s="1">
         <v>44014</v>
@@ -17084,7 +17217,7 @@
       <c r="B14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17094,7 +17227,7 @@
       <c r="B15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H15" s="1">
         <v>44016</v>
@@ -17110,7 +17243,7 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H16" s="1">
         <v>44017</v>
@@ -17123,7 +17256,7 @@
       <c r="B17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H17" s="1">
         <v>44018</v>
@@ -17139,7 +17272,7 @@
       </c>
       <c r="F18" s="3"/>
       <c r="G18" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17149,7 +17282,7 @@
       <c r="B19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H19" s="1">
         <v>44020</v>
@@ -17165,7 +17298,7 @@
       </c>
       <c r="F20" s="3"/>
       <c r="G20" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H20" s="1">
         <v>44021</v>
@@ -17178,7 +17311,7 @@
       <c r="B21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17188,7 +17321,7 @@
       <c r="B22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H22" s="1">
         <v>44023</v>
@@ -17204,7 +17337,7 @@
       </c>
       <c r="F23" s="3"/>
       <c r="G23" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H23" s="1">
         <v>44024</v>
@@ -17217,7 +17350,7 @@
       <c r="B24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H24" s="1">
         <v>44025</v>
@@ -17233,7 +17366,7 @@
       </c>
       <c r="F25" s="3"/>
       <c r="G25" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="26" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.15">
@@ -17243,7 +17376,7 @@
       <c r="B26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H26" s="6">
         <v>44027</v>
@@ -17259,7 +17392,7 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="28" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17269,7 +17402,7 @@
       <c r="B28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H28" s="1">
         <v>44029</v>
@@ -17282,7 +17415,7 @@
       <c r="B29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H29" s="1">
         <v>44030</v>
@@ -17295,7 +17428,7 @@
       <c r="B30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H30" s="1">
         <v>44031</v>
@@ -17308,7 +17441,7 @@
       <c r="B31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17318,7 +17451,7 @@
       <c r="B32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H32" s="1">
         <v>44033</v>
@@ -17331,7 +17464,7 @@
       <c r="B33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H33" s="1">
         <v>44034</v>
@@ -17344,7 +17477,7 @@
       <c r="B34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H34" s="1">
         <v>44035</v>
@@ -17357,7 +17490,7 @@
       <c r="B35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="36" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17367,7 +17500,7 @@
       <c r="B36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H36" s="1">
         <v>44037</v>
@@ -17380,7 +17513,7 @@
       <c r="B37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H37" s="1">
         <v>44038</v>
@@ -17393,7 +17526,7 @@
       <c r="B38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="39" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17403,7 +17536,7 @@
       <c r="B39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H39" s="1">
         <v>44040</v>
@@ -17416,7 +17549,7 @@
       <c r="B40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H40" s="1">
         <v>44041</v>
@@ -17429,7 +17562,7 @@
       <c r="B41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H41" s="1">
         <v>44042</v>
@@ -17442,7 +17575,7 @@
       <c r="B42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="43" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17452,7 +17585,7 @@
       <c r="B43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H43" s="1">
         <v>44044</v>
@@ -17465,7 +17598,7 @@
       <c r="B44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="45" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17475,7 +17608,7 @@
       <c r="B45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H45" s="1">
         <v>44046</v>
@@ -17488,7 +17621,7 @@
       <c r="B46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H46" s="1">
         <v>44047</v>
@@ -17501,7 +17634,7 @@
       <c r="B47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="48" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17511,7 +17644,7 @@
       <c r="B48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H48" s="1">
         <v>44049</v>
@@ -17524,7 +17657,7 @@
       <c r="B49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H49" s="1">
         <v>44050</v>
@@ -17537,7 +17670,7 @@
       <c r="B50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H50" s="1">
         <v>44051</v>
@@ -17550,7 +17683,7 @@
       <c r="B51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="52" spans="1:8" s="6" customFormat="1" ht="94.5" x14ac:dyDescent="0.15">
@@ -17560,7 +17693,7 @@
       <c r="B52" s="7"/>
       <c r="F52" s="7"/>
       <c r="G52" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H52" s="1">
         <v>44053</v>
@@ -17573,7 +17706,7 @@
       <c r="B53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H53" s="1">
         <v>44054</v>
@@ -17586,7 +17719,7 @@
       <c r="B54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H54" s="1">
         <v>44055</v>
@@ -17599,7 +17732,7 @@
       <c r="B55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="56" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17609,7 +17742,7 @@
       <c r="B56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H56" s="1">
         <v>44057</v>
@@ -17622,7 +17755,7 @@
       <c r="B57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H57" s="1">
         <v>44058</v>
@@ -17635,7 +17768,7 @@
       <c r="B58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H58" s="1">
         <v>44059</v>
@@ -17648,7 +17781,7 @@
       <c r="B59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="60" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17658,7 +17791,7 @@
       <c r="B60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H60" s="1">
         <v>44061</v>
@@ -17671,7 +17804,7 @@
       <c r="B61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="62" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17681,7 +17814,7 @@
       <c r="B62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="63" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17691,7 +17824,7 @@
       <c r="B63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H63" s="1">
         <v>44064</v>
@@ -17704,7 +17837,7 @@
       <c r="B64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="65" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17714,7 +17847,7 @@
       <c r="B65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H65" s="1">
         <v>44066</v>
@@ -17727,7 +17860,7 @@
       <c r="B66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="67" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.15">
@@ -17737,7 +17870,7 @@
       <c r="B67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H67" s="1">
         <v>44068</v>
@@ -17750,7 +17883,7 @@
       <c r="B68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="69" spans="1:8" s="6" customFormat="1" ht="81" x14ac:dyDescent="0.15">
@@ -17760,7 +17893,7 @@
       <c r="B69" s="7"/>
       <c r="F69" s="7"/>
       <c r="G69" s="6" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H69" s="1">
         <v>44070</v>
@@ -17773,7 +17906,7 @@
       <c r="B70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H70" s="1">
         <v>44071</v>
@@ -17786,7 +17919,7 @@
       <c r="B71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H71" s="1">
         <v>44071</v>
@@ -17799,7 +17932,7 @@
       <c r="B72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -17820,135 +17953,135 @@
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.15">
       <c r="B1" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>525</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AH1" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AI1" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AK1" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="AL1" s="4" t="s">
+      <c r="AM1" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="AM1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="AN1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="AO1" s="4" t="s">
+      <c r="AP1" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.15">
@@ -17958,62 +18091,62 @@
     </row>
     <row r="4" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.15">
@@ -18023,84 +18156,84 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B17" s="5"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B26" s="5"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.15">

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$475</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TalkData!$A$3:$J$490</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1963" uniqueCount="686">
   <si>
     <t>班尼迪克</t>
   </si>
@@ -2233,6 +2233,66 @@
   </si>
   <si>
     <t>造物主还没来得及创造这种感情，请耐心等待吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉，我们的关系还没亲密到现在一起组队的程度。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在还不行哦，想和我一起组队，你还得加倍努力呀。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我还有事情要做，不能和你组队。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果我们更亲密一些的话，我会同意的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对不起，我现在不能和你一起外出。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我还需要磨练意志，如果你能感化我的话也许可行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我现在还不能完全信任你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以让我安心将后背给你吗？做不到吧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作为一个好船长，必须懂得挑选自己的团队，你现在还不行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对不起，我不是很习惯和不熟悉的人一起行动。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱歉了，我的时间很宝贵，你得先取得我的信任才行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我需要照顾大小姐，除非我们更加亲密。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很高兴你来邀请我，但是请允许我拒绝。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我的职责很可是很重要的，除非你能证明你更重要。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我们的关系还不够啊，我还是不能同意。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2637,15 +2697,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:J491"/>
+  <dimension ref="A2:J506"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="16.125" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="3" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.375" style="3" customWidth="1"/>
     <col min="7" max="7" width="48.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.375" style="1" customWidth="1"/>
     <col min="9" max="9" width="10.625" style="1" customWidth="1"/>
@@ -16267,7 +16327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="1">
         <v>5005</v>
       </c>
@@ -16296,38 +16356,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A467" s="1">
-        <v>6000</v>
+    <row r="467" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A467" s="6">
+        <v>5006</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D467" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E467" s="1">
-        <v>0</v>
-      </c>
-      <c r="F467" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G467" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="H467" s="1">
-        <v>0</v>
-      </c>
-      <c r="I467" s="1">
-        <v>0</v>
-      </c>
-      <c r="J467" s="1" t="b">
-        <v>0</v>
+      <c r="D467" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E467" s="6">
+        <v>0</v>
+      </c>
+      <c r="F467" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G467" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="H467" s="6">
+        <v>0</v>
+      </c>
+      <c r="I467" s="6">
+        <v>0</v>
+      </c>
+      <c r="J467" s="6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="468" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A468" s="1">
-        <v>6001</v>
+        <v>5007</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>284</v>
@@ -16342,7 +16402,7 @@
         <v>181</v>
       </c>
       <c r="G468" s="1" t="s">
-        <v>293</v>
+        <v>672</v>
       </c>
       <c r="H468" s="1">
         <v>0</v>
@@ -16351,12 +16411,12 @@
         <v>0</v>
       </c>
       <c r="J468" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A469" s="1">
-        <v>6002</v>
+        <v>5008</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>284</v>
@@ -16371,7 +16431,7 @@
         <v>181</v>
       </c>
       <c r="G469" s="1" t="s">
-        <v>294</v>
+        <v>673</v>
       </c>
       <c r="H469" s="1">
         <v>0</v>
@@ -16380,12 +16440,12 @@
         <v>0</v>
       </c>
       <c r="J469" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A470" s="1">
-        <v>6003</v>
+        <v>5009</v>
       </c>
       <c r="B470" s="3" t="s">
         <v>284</v>
@@ -16400,7 +16460,7 @@
         <v>181</v>
       </c>
       <c r="G470" s="1" t="s">
-        <v>295</v>
+        <v>674</v>
       </c>
       <c r="H470" s="1">
         <v>0</v>
@@ -16409,12 +16469,12 @@
         <v>0</v>
       </c>
       <c r="J470" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A471" s="1">
-        <v>6004</v>
+        <v>5010</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>284</v>
@@ -16429,7 +16489,7 @@
         <v>181</v>
       </c>
       <c r="G471" s="1" t="s">
-        <v>296</v>
+        <v>675</v>
       </c>
       <c r="H471" s="1">
         <v>0</v>
@@ -16438,12 +16498,12 @@
         <v>0</v>
       </c>
       <c r="J471" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A472" s="1">
-        <v>6005</v>
+        <v>5011</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>284</v>
@@ -16458,7 +16518,7 @@
         <v>181</v>
       </c>
       <c r="G472" s="1" t="s">
-        <v>297</v>
+        <v>676</v>
       </c>
       <c r="H472" s="1">
         <v>0</v>
@@ -16467,12 +16527,12 @@
         <v>0</v>
       </c>
       <c r="J472" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="473" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
-        <v>6006</v>
+        <v>5012</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>284</v>
@@ -16487,7 +16547,7 @@
         <v>181</v>
       </c>
       <c r="G473" s="1" t="s">
-        <v>298</v>
+        <v>677</v>
       </c>
       <c r="H473" s="1">
         <v>0</v>
@@ -16496,12 +16556,12 @@
         <v>0</v>
       </c>
       <c r="J473" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="474" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
-        <v>6100</v>
+        <v>5013</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>284</v>
@@ -16516,7 +16576,7 @@
         <v>181</v>
       </c>
       <c r="G474" s="1" t="s">
-        <v>299</v>
+        <v>678</v>
       </c>
       <c r="H474" s="1">
         <v>0</v>
@@ -16525,15 +16585,15 @@
         <v>0</v>
       </c>
       <c r="J474" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:10" ht="27" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
-        <v>8100</v>
+        <v>5014</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="D475" s="1" t="s">
         <v>183</v>
@@ -16545,7 +16605,7 @@
         <v>181</v>
       </c>
       <c r="G475" s="1" t="s">
-        <v>649</v>
+        <v>679</v>
       </c>
       <c r="H475" s="1">
         <v>0</v>
@@ -16559,7 +16619,7 @@
     </row>
     <row r="476" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
-        <v>8101</v>
+        <v>5015</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>284</v>
@@ -16574,7 +16634,7 @@
         <v>181</v>
       </c>
       <c r="G476" s="1" t="s">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="H476" s="1">
         <v>0</v>
@@ -16588,7 +16648,7 @@
     </row>
     <row r="477" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
-        <v>8102</v>
+        <v>5016</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>284</v>
@@ -16603,7 +16663,7 @@
         <v>181</v>
       </c>
       <c r="G477" s="1" t="s">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="H477" s="1">
         <v>0</v>
@@ -16617,7 +16677,7 @@
     </row>
     <row r="478" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
-        <v>8103</v>
+        <v>5017</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>284</v>
@@ -16632,7 +16692,7 @@
         <v>181</v>
       </c>
       <c r="G478" s="1" t="s">
-        <v>650</v>
+        <v>682</v>
       </c>
       <c r="H478" s="1">
         <v>0</v>
@@ -16646,7 +16706,7 @@
     </row>
     <row r="479" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
-        <v>8104</v>
+        <v>5018</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>284</v>
@@ -16661,7 +16721,7 @@
         <v>181</v>
       </c>
       <c r="G479" s="1" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="H479" s="1">
         <v>0</v>
@@ -16675,7 +16735,7 @@
     </row>
     <row r="480" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
-        <v>8105</v>
+        <v>5019</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>284</v>
@@ -16690,7 +16750,7 @@
         <v>181</v>
       </c>
       <c r="G480" s="1" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="H480" s="1">
         <v>0</v>
@@ -16704,7 +16764,7 @@
     </row>
     <row r="481" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
-        <v>8106</v>
+        <v>5020</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>284</v>
@@ -16719,7 +16779,7 @@
         <v>181</v>
       </c>
       <c r="G481" s="1" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="H481" s="1">
         <v>0</v>
@@ -16733,7 +16793,7 @@
     </row>
     <row r="482" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
-        <v>8107</v>
+        <v>6000</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>284</v>
@@ -16748,7 +16808,7 @@
         <v>181</v>
       </c>
       <c r="G482" s="1" t="s">
-        <v>660</v>
+        <v>292</v>
       </c>
       <c r="H482" s="1">
         <v>0</v>
@@ -16757,12 +16817,12 @@
         <v>0</v>
       </c>
       <c r="J482" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
-        <v>8108</v>
+        <v>6001</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>284</v>
@@ -16777,7 +16837,7 @@
         <v>181</v>
       </c>
       <c r="G483" s="1" t="s">
-        <v>656</v>
+        <v>293</v>
       </c>
       <c r="H483" s="1">
         <v>0</v>
@@ -16786,12 +16846,12 @@
         <v>0</v>
       </c>
       <c r="J483" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
-        <v>8109</v>
+        <v>6002</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>284</v>
@@ -16806,7 +16866,7 @@
         <v>181</v>
       </c>
       <c r="G484" s="1" t="s">
-        <v>655</v>
+        <v>294</v>
       </c>
       <c r="H484" s="1">
         <v>0</v>
@@ -16815,12 +16875,12 @@
         <v>0</v>
       </c>
       <c r="J484" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
-        <v>8110</v>
+        <v>6003</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>284</v>
@@ -16835,7 +16895,7 @@
         <v>181</v>
       </c>
       <c r="G485" s="1" t="s">
-        <v>657</v>
+        <v>295</v>
       </c>
       <c r="H485" s="1">
         <v>0</v>
@@ -16844,12 +16904,12 @@
         <v>0</v>
       </c>
       <c r="J485" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
-        <v>8111</v>
+        <v>6004</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>284</v>
@@ -16864,7 +16924,7 @@
         <v>181</v>
       </c>
       <c r="G486" s="1" t="s">
-        <v>658</v>
+        <v>296</v>
       </c>
       <c r="H486" s="1">
         <v>0</v>
@@ -16873,12 +16933,12 @@
         <v>0</v>
       </c>
       <c r="J486" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A487" s="1">
-        <v>8112</v>
+        <v>6005</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>284</v>
@@ -16893,7 +16953,7 @@
         <v>181</v>
       </c>
       <c r="G487" s="1" t="s">
-        <v>659</v>
+        <v>297</v>
       </c>
       <c r="H487" s="1">
         <v>0</v>
@@ -16902,12 +16962,12 @@
         <v>0</v>
       </c>
       <c r="J487" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A488" s="1">
-        <v>8113</v>
+        <v>6006</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>284</v>
@@ -16922,7 +16982,7 @@
         <v>181</v>
       </c>
       <c r="G488" s="1" t="s">
-        <v>649</v>
+        <v>298</v>
       </c>
       <c r="H488" s="1">
         <v>0</v>
@@ -16931,12 +16991,12 @@
         <v>0</v>
       </c>
       <c r="J488" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A489" s="1">
-        <v>8114</v>
+        <v>6100</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>284</v>
@@ -16951,7 +17011,7 @@
         <v>181</v>
       </c>
       <c r="G489" s="1" t="s">
-        <v>661</v>
+        <v>299</v>
       </c>
       <c r="H489" s="1">
         <v>0</v>
@@ -16960,15 +17020,15 @@
         <v>0</v>
       </c>
       <c r="J489" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A490" s="1">
-        <v>8115</v>
+        <v>8100</v>
       </c>
       <c r="B490" s="3" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D490" s="1" t="s">
         <v>183</v>
@@ -16980,7 +17040,7 @@
         <v>181</v>
       </c>
       <c r="G490" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H490" s="1">
         <v>0</v>
@@ -16994,7 +17054,7 @@
     </row>
     <row r="491" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A491" s="1">
-        <v>8116</v>
+        <v>8101</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>284</v>
@@ -17009,7 +17069,7 @@
         <v>181</v>
       </c>
       <c r="G491" s="1" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="H491" s="1">
         <v>0</v>
@@ -17021,8 +17081,443 @@
         <v>1</v>
       </c>
     </row>
+    <row r="492" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A492" s="1">
+        <v>8102</v>
+      </c>
+      <c r="B492" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D492" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E492" s="1">
+        <v>0</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G492" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="H492" s="1">
+        <v>0</v>
+      </c>
+      <c r="I492" s="1">
+        <v>0</v>
+      </c>
+      <c r="J492" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A493" s="1">
+        <v>8103</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D493" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E493" s="1">
+        <v>0</v>
+      </c>
+      <c r="F493" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G493" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="H493" s="1">
+        <v>0</v>
+      </c>
+      <c r="I493" s="1">
+        <v>0</v>
+      </c>
+      <c r="J493" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A494" s="1">
+        <v>8104</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D494" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E494" s="1">
+        <v>0</v>
+      </c>
+      <c r="F494" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G494" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="H494" s="1">
+        <v>0</v>
+      </c>
+      <c r="I494" s="1">
+        <v>0</v>
+      </c>
+      <c r="J494" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A495" s="1">
+        <v>8105</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D495" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E495" s="1">
+        <v>0</v>
+      </c>
+      <c r="F495" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G495" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="H495" s="1">
+        <v>0</v>
+      </c>
+      <c r="I495" s="1">
+        <v>0</v>
+      </c>
+      <c r="J495" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A496" s="1">
+        <v>8106</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D496" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E496" s="1">
+        <v>0</v>
+      </c>
+      <c r="F496" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G496" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="H496" s="1">
+        <v>0</v>
+      </c>
+      <c r="I496" s="1">
+        <v>0</v>
+      </c>
+      <c r="J496" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A497" s="1">
+        <v>8107</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D497" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E497" s="1">
+        <v>0</v>
+      </c>
+      <c r="F497" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G497" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="H497" s="1">
+        <v>0</v>
+      </c>
+      <c r="I497" s="1">
+        <v>0</v>
+      </c>
+      <c r="J497" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A498" s="1">
+        <v>8108</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D498" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E498" s="1">
+        <v>0</v>
+      </c>
+      <c r="F498" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G498" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H498" s="1">
+        <v>0</v>
+      </c>
+      <c r="I498" s="1">
+        <v>0</v>
+      </c>
+      <c r="J498" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A499" s="1">
+        <v>8109</v>
+      </c>
+      <c r="B499" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E499" s="1">
+        <v>0</v>
+      </c>
+      <c r="F499" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G499" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="H499" s="1">
+        <v>0</v>
+      </c>
+      <c r="I499" s="1">
+        <v>0</v>
+      </c>
+      <c r="J499" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A500" s="1">
+        <v>8110</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D500" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E500" s="1">
+        <v>0</v>
+      </c>
+      <c r="F500" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G500" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H500" s="1">
+        <v>0</v>
+      </c>
+      <c r="I500" s="1">
+        <v>0</v>
+      </c>
+      <c r="J500" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A501" s="1">
+        <v>8111</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D501" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E501" s="1">
+        <v>0</v>
+      </c>
+      <c r="F501" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G501" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="H501" s="1">
+        <v>0</v>
+      </c>
+      <c r="I501" s="1">
+        <v>0</v>
+      </c>
+      <c r="J501" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A502" s="1">
+        <v>8112</v>
+      </c>
+      <c r="B502" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D502" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E502" s="1">
+        <v>0</v>
+      </c>
+      <c r="F502" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G502" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="H502" s="1">
+        <v>0</v>
+      </c>
+      <c r="I502" s="1">
+        <v>0</v>
+      </c>
+      <c r="J502" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A503" s="1">
+        <v>8113</v>
+      </c>
+      <c r="B503" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D503" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E503" s="1">
+        <v>0</v>
+      </c>
+      <c r="F503" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G503" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="H503" s="1">
+        <v>0</v>
+      </c>
+      <c r="I503" s="1">
+        <v>0</v>
+      </c>
+      <c r="J503" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A504" s="1">
+        <v>8114</v>
+      </c>
+      <c r="B504" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D504" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E504" s="1">
+        <v>0</v>
+      </c>
+      <c r="F504" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G504" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="H504" s="1">
+        <v>0</v>
+      </c>
+      <c r="I504" s="1">
+        <v>0</v>
+      </c>
+      <c r="J504" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A505" s="1">
+        <v>8115</v>
+      </c>
+      <c r="B505" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D505" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E505" s="1">
+        <v>0</v>
+      </c>
+      <c r="F505" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G505" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="H505" s="1">
+        <v>0</v>
+      </c>
+      <c r="I505" s="1">
+        <v>0</v>
+      </c>
+      <c r="J505" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A506" s="1">
+        <v>8116</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D506" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E506" s="1">
+        <v>0</v>
+      </c>
+      <c r="F506" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G506" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="H506" s="1">
+        <v>0</v>
+      </c>
+      <c r="I506" s="1">
+        <v>0</v>
+      </c>
+      <c r="J506" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J475"/>
+  <autoFilter ref="A3:J490"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Datas/TalkData.xlsx
+++ b/Datas/TalkData.xlsx
@@ -8140,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="I184" s="1">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="J184" s="1" t="b">
         <v>0</v>
